--- a/DUOL.xlsx
+++ b/DUOL.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10802"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4824FFDB-B3D4-3842-B69C-FBCB7198CED1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E23FF4B1-97DF-3848-840E-94276066BDD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -119,7 +119,7 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="5">
+  <futureMetadata name="XLRICHVALUE" count="2">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -130,28 +130,7 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="3"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="4"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="5"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="8"/>
         </ext>
       </extLst>
     </bk>
@@ -161,21 +140,12 @@
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="5">
+  <valueMetadata count="2">
     <bk>
       <rc t="2" v="0"/>
     </bk>
     <bk>
       <rc t="2" v="1"/>
-    </bk>
-    <bk>
-      <rc t="2" v="2"/>
-    </bk>
-    <bk>
-      <rc t="2" v="3"/>
-    </bk>
-    <bk>
-      <rc t="2" v="4"/>
     </bk>
   </valueMetadata>
 </metadata>
@@ -2440,9 +2410,6 @@
     <xf numFmtId="39" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="10" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="39" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2450,6 +2417,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2461,10 +2437,10 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2474,12 +2450,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -13169,7 +13139,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="9">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="6">
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=c2mtim&amp;q=XNAS%3aDUOL&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
@@ -13186,11 +13156,13 @@
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>468</v>
+    <v>353</v>
     <v>87.89</v>
-    <v>0.86160000000000003</v>
-    <v>5.17</v>
-    <v>4.2176999999999999E-2</v>
+    <v>1.0437000000000001</v>
+    <v>-4.3600000000000003</v>
+    <v>-2.7452000000000001E-2</v>
+    <v>0.04</v>
+    <v>2.5900000000000001E-4</v>
     <v>USD</v>
     <v>Duolingo, Inc. is a technology company. The Company is engaged in offering a mobile learning platform, as well as a digital English language proficiency assessment exam. It operates a freemium business model, namely, the app and the Website are accessible free of charge, although Duolingo also offers premium services for a subscription fee. Its solutions consist of the Duolingo App, Super Duolingo, Duolingo Max, Duolingo English Test: AI-Driven Language Assessment, Duolingo for Schools, and Duolingo ABC. The Duolingo App offers courses in over 40 different languages, including Spanish, English, French, German, Italian, Portuguese, Japanese and Chinese. Duolingo can also be accessed on desktop computers via a Web browser. Its subscription offering, Super Duolingo, offers learners additional features to enhance their learning experience. The Duolingo English Test is an online, on-demand, high-stakes English proficiency assessment. It also operates an animation and motion design studio.</v>
     <v>900</v>
@@ -13198,49 +13170,35 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>5900 PENN AVE, SECOND FLOOR, PITTSBURGH, PA, 15206 US</v>
-    <v>129.4999</v>
+    <v>158.31</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46241.781591492967</v>
+    <v>46269.897677916408</v>
     <v>0</v>
-    <v>122.98</v>
-    <v>5968991000</v>
+    <v>153</v>
+    <v>7226607264</v>
     <v>DUOLINGO, INC.</v>
     <v>DUOLINGO, INC.</v>
-    <v>122.98</v>
-    <v>14.784700000000001</v>
-    <v>122.58</v>
-    <v>127.75</v>
-    <v>46724000</v>
+    <v>157.46</v>
+    <v>18.411100000000001</v>
+    <v>158.82</v>
+    <v>154.46</v>
+    <v>154.5</v>
+    <v>46786270</v>
     <v>DUOL</v>
     <v>DUOLINGO, INC. (XNAS:DUOL)</v>
-    <v>975411</v>
-    <v>1185621</v>
+    <v>1055836</v>
+    <v>1353949</v>
     <v>2011</v>
   </rv>
   <rv s="2">
     <v>1</v>
   </rv>
-  <rv s="3">
-    <v>12</v>
-    <v>Price (Extended hours)</v>
-    <v>0</v>
-  </rv>
-  <rv s="3">
-    <v>12</v>
-    <v>Change (extended hours)</v>
-    <v>0</v>
-  </rv>
-  <rv s="3">
-    <v>12</v>
-    <v>Change % (extended hours)</v>
-    <v>0</v>
-  </rv>
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a33knm&amp;q=10+Y+TSY+YLD+NDX&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="4">
+  <rv s="3">
     <v>5</v>
     <v>10 Y TSY YLD NDX</v>
     <v>6</v>
@@ -13252,30 +13210,30 @@
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>47.47</v>
+    <v>48.06</v>
     <v>39.47</v>
-    <v>0.53</v>
-    <v>1.1479E-2</v>
+    <v>-0.34</v>
+    <v>-7.0889999999999998E-3</v>
     <v>US</v>
-    <v>46.76</v>
+    <v>47.68</v>
     <v>Index</v>
-    <v>6</v>
-    <v>46.35</v>
+    <v>3</v>
+    <v>47.32</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>46.43</v>
-    <v>46.17</v>
-    <v>46.7</v>
+    <v>47.66</v>
+    <v>47.96</v>
+    <v>47.62</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
   <rv s="2">
-    <v>7</v>
+    <v>4</v>
   </rv>
 </rvData>
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="5">
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="4">
   <s t="_hyperlink">
     <k n="Address" t="s"/>
     <k n="Text" t="s"/>
@@ -13297,6 +13255,8 @@
     <k n="Beta"/>
     <k n="Change"/>
     <k n="Change (%)"/>
+    <k n="Change (Extended hours)"/>
+    <k n="Change % (Extended hours)"/>
     <k n="Currency" t="s"/>
     <k n="Description" t="s"/>
     <k n="Employees"/>
@@ -13317,6 +13277,7 @@
     <k n="P/E"/>
     <k n="Previous close"/>
     <k n="Price"/>
+    <k n="Price (Extended hours)"/>
     <k n="Shares outstanding"/>
     <k n="Ticker symbol" t="s"/>
     <k n="UniqueName" t="s"/>
@@ -13326,11 +13287,6 @@
   </s>
   <s t="_linkedentity">
     <k n="%cvi" t="r"/>
-  </s>
-  <s t="_error">
-    <k n="errorType" t="i"/>
-    <k n="field" t="s"/>
-    <k n="subType" t="i"/>
   </s>
   <s t="_linkedentitycore">
     <k n="_Display" t="spb"/>
@@ -13366,7 +13322,7 @@
 <file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
 <supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
   <spbArrays count="2">
-    <a count="42">
+    <a count="45">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%IsRefreshable</v>
@@ -13377,13 +13333,16 @@
       <v t="s">Name</v>
       <v t="s">_SubLabel</v>
       <v t="s">Price</v>
+      <v t="s">Price (Extended hours)</v>
       <v t="s">Exchange</v>
       <v t="s">Official name</v>
       <v t="s">Last trade time</v>
       <v t="s">Ticker symbol</v>
       <v t="s">Exchange abbreviation</v>
       <v t="s">Change</v>
+      <v t="s">Change (Extended hours)</v>
       <v t="s">Change (%)</v>
+      <v t="s">Change % (Extended hours)</v>
       <v t="s">Currency</v>
       <v t="s">Previous close</v>
       <v t="s">Open</v>
@@ -13477,13 +13436,19 @@
       <v>8</v>
       <v>9</v>
       <v>4</v>
+      <v>1</v>
+      <v>1</v>
+      <v>5</v>
     </spb>
     <spb s="4">
-      <v>Real-Time Nasdaq Last Sale</v>
+      <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
       <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
+      <v>Real-Time Nasdaq Last Sale</v>
+      <v>from close</v>
+      <v>from close</v>
     </spb>
     <spb s="0">
       <v>1</v>
@@ -13555,6 +13520,9 @@
     <k n="Year incorporated" t="i"/>
     <k n="`%EntityServiceId" t="i"/>
     <k n="Shares outstanding" t="i"/>
+    <k n="Price (Extended hours)" t="i"/>
+    <k n="Change (Extended hours)" t="i"/>
+    <k n="Change % (Extended hours)" t="i"/>
   </s>
   <s>
     <k n="Price" t="s"/>
@@ -13562,6 +13530,9 @@
     <k n="Change (%)" t="s"/>
     <k n="ExchangeID" t="s"/>
     <k n="Last trade time" t="s"/>
+    <k n="Price (Extended hours)" t="s"/>
+    <k n="Change (Extended hours)" t="s"/>
+    <k n="Change % (Extended hours)" t="s"/>
   </s>
   <s>
     <k n="UniqueName" t="spb"/>
@@ -14046,18 +14017,18 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="257" t="s">
+      <c r="B2" s="256" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="258"/>
-      <c r="E2" s="257" t="s">
+      <c r="C2" s="257"/>
+      <c r="E2" s="256" t="s">
         <v>296</v>
       </c>
-      <c r="F2" s="258"/>
-      <c r="H2" s="257" t="s">
+      <c r="F2" s="257"/>
+      <c r="H2" s="256" t="s">
         <v>338</v>
       </c>
-      <c r="I2" s="258"/>
+      <c r="I2" s="257"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="187" t="s">
@@ -14072,7 +14043,7 @@
       </c>
       <c r="F3" s="189">
         <f ca="1">Statement!AC149</f>
-        <v>6403085.5</v>
+        <v>7741844.1200000001</v>
       </c>
       <c r="H3" s="187" t="str">
         <f>'AVG target price'!B5</f>
@@ -14096,7 +14067,7 @@
       </c>
       <c r="F4" s="190">
         <f ca="1">Statement!AC150</f>
-        <v>4986526.5</v>
+        <v>6325285.1200000001</v>
       </c>
       <c r="H4" s="187" t="str">
         <f>'AVG target price'!B6</f>
@@ -14113,7 +14084,7 @@
       </c>
       <c r="C5" s="210" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>127.75</v>
+        <v>154.46</v>
       </c>
       <c r="E5" s="187" t="s">
         <v>252</v>
@@ -14135,16 +14106,16 @@
       <c r="B6" s="187" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="210" t="e" cm="1" vm="2">
-        <f t="array" ref="C6">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C6" s="210" cm="1">
+        <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
+        <v>154.5</v>
       </c>
       <c r="E6" s="187" t="s">
         <v>246</v>
       </c>
       <c r="F6" s="192">
         <f ca="1">Statement!AC146</f>
-        <v>40.676980665771602</v>
+        <v>49.181733335695355</v>
       </c>
       <c r="H6" s="187" t="str">
         <f>'AVG target price'!B8</f>
@@ -14161,14 +14132,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>5.17</v>
+        <v>-4.3600000000000003</v>
       </c>
       <c r="E7" s="188" t="s">
         <v>205</v>
       </c>
       <c r="F7" s="193">
         <f ca="1">Statement!AC147</f>
-        <v>5.486156425273955</v>
+        <v>6.6332032990044238</v>
       </c>
       <c r="H7" s="186" t="str">
         <f>'AVG target price'!B9</f>
@@ -14183,16 +14154,16 @@
       <c r="B8" s="187" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="6" t="e" cm="1" vm="3">
-        <f t="array" ref="C8">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C8" s="6" cm="1">
+        <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
+        <v>0.04</v>
       </c>
       <c r="E8" s="187" t="s">
         <v>274</v>
       </c>
       <c r="F8" s="194">
         <f ca="1">Statement!AC157</f>
-        <v>3.9484089350360851E-2</v>
+        <v>3.2656302049129865E-2</v>
       </c>
       <c r="H8" s="186" t="str">
         <f>'AVG target price'!B11</f>
@@ -14200,7 +14171,7 @@
       </c>
       <c r="I8" s="215">
         <f ca="1">'AVG target price'!C11</f>
-        <v>0.28798873623637516</v>
+        <v>6.5263246498749969E-2</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -14209,30 +14180,30 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>4.2176999999999999E-2</v>
+        <v>-2.7452000000000001E-2</v>
       </c>
       <c r="E9" s="187" t="s">
         <v>297</v>
       </c>
       <c r="F9" s="194">
         <f ca="1">Statement!AC158</f>
-        <v>2.4583928886380415E-2</v>
+        <v>2.0332752267480887E-2</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B10" s="187" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="73" t="e" cm="1" vm="4">
-        <f t="array" ref="C10">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C10" s="73" cm="1">
+        <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
+        <v>2.5900000000000001E-4</v>
       </c>
       <c r="E10" s="187" t="s">
         <v>302</v>
       </c>
       <c r="F10" s="194">
         <f ca="1">Statement!AC160</f>
-        <v>1.0870228111119241E-2</v>
+        <v>8.9904935983133698E-3</v>
       </c>
       <c r="H10" s="186" t="s">
         <v>429</v>
@@ -14248,7 +14219,7 @@
       </c>
       <c r="C11" s="211" cm="1">
         <f t="array" aca="1" ref="C11" ca="1">_FV(C3,"52 week high",TRUE)</f>
-        <v>468</v>
+        <v>353</v>
       </c>
       <c r="E11" s="188" t="s">
         <v>298</v>
@@ -14280,7 +14251,7 @@
       </c>
       <c r="C13" s="211" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>0.86160000000000003</v>
+        <v>1.0437000000000001</v>
       </c>
       <c r="E13" s="187" t="s">
         <v>104</v>
@@ -14296,7 +14267,7 @@
       </c>
       <c r="C14" s="212" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>1185621</v>
+        <v>1353949</v>
       </c>
       <c r="E14" s="188" t="s">
         <v>105</v>
@@ -14312,7 +14283,7 @@
       </c>
       <c r="F15" s="194">
         <f ca="1">Statement!AC172</f>
-        <v>0.22123068636206716</v>
+        <v>0.1829743634776258</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -14325,10 +14296,10 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="259" t="s">
+      <c r="B17" s="258" t="s">
         <v>90</v>
       </c>
-      <c r="C17" s="259"/>
+      <c r="C17" s="258"/>
       <c r="E17" s="186" t="s">
         <v>305</v>
       </c>
@@ -14401,14 +14372,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="259" t="s">
+      <c r="B25" s="258" t="s">
         <v>107</v>
       </c>
-      <c r="C25" s="259"/>
-      <c r="E25" s="257" t="s">
+      <c r="C25" s="258"/>
+      <c r="E25" s="256" t="s">
         <v>351</v>
       </c>
-      <c r="F25" s="258"/>
+      <c r="F25" s="257"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="186" t="s">
@@ -14417,12 +14388,12 @@
       <c r="C26" s="172">
         <v>0.21</v>
       </c>
-      <c r="E26" s="187" t="e" vm="5">
+      <c r="E26" s="187" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
       <c r="F26" s="221" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>46.7</v>
+        <v>47.62</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -14437,7 +14408,7 @@
       </c>
       <c r="F27" s="222">
         <f ca="1">F26/1000</f>
-        <v>4.6700000000000005E-2</v>
+        <v>4.7619999999999996E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -14457,15 +14428,15 @@
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="256" t="s">
+      <c r="B33" s="259" t="s">
         <v>346</v>
       </c>
-      <c r="C33" s="256"/>
-      <c r="D33" s="256"/>
-      <c r="E33" s="256"/>
-      <c r="F33" s="256"/>
-      <c r="G33" s="256"/>
-      <c r="H33" s="256"/>
+      <c r="C33" s="259"/>
+      <c r="D33" s="259"/>
+      <c r="E33" s="259"/>
+      <c r="F33" s="259"/>
+      <c r="G33" s="259"/>
+      <c r="H33" s="259"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
@@ -14484,24 +14455,24 @@
       </c>
     </row>
     <row r="39" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="256"/>
-      <c r="C39" s="256"/>
-      <c r="D39" s="256"/>
-      <c r="E39" s="256"/>
-      <c r="F39" s="256"/>
-      <c r="G39" s="256"/>
-      <c r="H39" s="256"/>
+      <c r="B39" s="259"/>
+      <c r="C39" s="259"/>
+      <c r="D39" s="259"/>
+      <c r="E39" s="259"/>
+      <c r="F39" s="259"/>
+      <c r="G39" s="259"/>
+      <c r="H39" s="259"/>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B42" s="256" t="s">
+      <c r="B42" s="259" t="s">
         <v>349</v>
       </c>
-      <c r="C42" s="256"/>
-      <c r="D42" s="256"/>
-      <c r="E42" s="256"/>
-      <c r="F42" s="256"/>
-      <c r="G42" s="256"/>
-      <c r="H42" s="256"/>
+      <c r="C42" s="259"/>
+      <c r="D42" s="259"/>
+      <c r="E42" s="259"/>
+      <c r="F42" s="259"/>
+      <c r="G42" s="259"/>
+      <c r="H42" s="259"/>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="41" t="s">
@@ -14540,24 +14511,24 @@
       </c>
     </row>
     <row r="50" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B50" s="256"/>
-      <c r="C50" s="256"/>
-      <c r="D50" s="256"/>
-      <c r="E50" s="256"/>
-      <c r="F50" s="256"/>
-      <c r="G50" s="256"/>
-      <c r="H50" s="256"/>
+      <c r="B50" s="259"/>
+      <c r="C50" s="259"/>
+      <c r="D50" s="259"/>
+      <c r="E50" s="259"/>
+      <c r="F50" s="259"/>
+      <c r="G50" s="259"/>
+      <c r="H50" s="259"/>
     </row>
     <row r="53" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B53" s="256" t="s">
+      <c r="B53" s="259" t="s">
         <v>109</v>
       </c>
-      <c r="C53" s="256"/>
-      <c r="D53" s="256"/>
-      <c r="E53" s="256"/>
-      <c r="F53" s="256"/>
-      <c r="G53" s="256"/>
-      <c r="H53" s="256"/>
+      <c r="C53" s="259"/>
+      <c r="D53" s="259"/>
+      <c r="E53" s="259"/>
+      <c r="F53" s="259"/>
+      <c r="G53" s="259"/>
+      <c r="H53" s="259"/>
     </row>
     <row r="58" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B58" s="41" t="s">
@@ -14628,28 +14599,28 @@
       </c>
     </row>
     <row r="66" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B66" s="256"/>
-      <c r="C66" s="256"/>
-      <c r="D66" s="256"/>
-      <c r="E66" s="256"/>
-      <c r="F66" s="256"/>
-      <c r="G66" s="256"/>
-      <c r="H66" s="256"/>
+      <c r="B66" s="259"/>
+      <c r="C66" s="259"/>
+      <c r="D66" s="259"/>
+      <c r="E66" s="259"/>
+      <c r="F66" s="259"/>
+      <c r="G66" s="259"/>
+      <c r="H66" s="259"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B53:H53"/>
+    <mergeCell ref="B66:H66"/>
+    <mergeCell ref="B33:H33"/>
+    <mergeCell ref="B39:H39"/>
+    <mergeCell ref="B42:H42"/>
+    <mergeCell ref="B50:H50"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="E25:F25"/>
-    <mergeCell ref="B53:H53"/>
-    <mergeCell ref="B66:H66"/>
-    <mergeCell ref="B33:H33"/>
-    <mergeCell ref="B39:H39"/>
-    <mergeCell ref="B42:H42"/>
-    <mergeCell ref="B50:H50"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C10">
     <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
@@ -14719,36 +14690,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="256" t="s">
+      <c r="C2" s="259" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="256"/>
-      <c r="E2" s="256"/>
-      <c r="F2" s="256"/>
-      <c r="G2" s="268"/>
-      <c r="H2" s="269" t="s">
+      <c r="D2" s="259"/>
+      <c r="E2" s="259"/>
+      <c r="F2" s="259"/>
+      <c r="G2" s="265"/>
+      <c r="H2" s="266" t="s">
         <v>114</v>
       </c>
-      <c r="I2" s="256"/>
-      <c r="J2" s="256"/>
-      <c r="K2" s="256"/>
-      <c r="L2" s="256"/>
+      <c r="I2" s="259"/>
+      <c r="J2" s="259"/>
+      <c r="K2" s="259"/>
+      <c r="L2" s="259"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="256" t="s">
+      <c r="S2" s="259" t="s">
         <v>113</v>
       </c>
-      <c r="T2" s="256"/>
-      <c r="U2" s="256"/>
-      <c r="V2" s="256"/>
-      <c r="W2" s="256"/>
-      <c r="X2" s="256"/>
-      <c r="Y2" s="256"/>
-      <c r="Z2" s="256"/>
-      <c r="AA2" s="256" t="s">
+      <c r="T2" s="259"/>
+      <c r="U2" s="259"/>
+      <c r="V2" s="259"/>
+      <c r="W2" s="259"/>
+      <c r="X2" s="259"/>
+      <c r="Y2" s="259"/>
+      <c r="Z2" s="259"/>
+      <c r="AA2" s="259" t="s">
         <v>114</v>
       </c>
-      <c r="AB2" s="256"/>
-      <c r="AC2" s="256"/>
+      <c r="AB2" s="259"/>
+      <c r="AC2" s="259"/>
       <c r="AE2" s="86" t="s">
         <v>85</v>
       </c>
@@ -14759,32 +14730,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="265" t="s">
+      <c r="C4" s="267" t="s">
         <v>116</v>
       </c>
-      <c r="D4" s="265"/>
-      <c r="E4" s="265"/>
-      <c r="F4" s="265"/>
-      <c r="G4" s="265"/>
-      <c r="H4" s="265"/>
-      <c r="I4" s="265"/>
-      <c r="J4" s="265"/>
-      <c r="K4" s="265"/>
-      <c r="L4" s="265"/>
+      <c r="D4" s="267"/>
+      <c r="E4" s="267"/>
+      <c r="F4" s="267"/>
+      <c r="G4" s="267"/>
+      <c r="H4" s="267"/>
+      <c r="I4" s="267"/>
+      <c r="J4" s="267"/>
+      <c r="K4" s="267"/>
+      <c r="L4" s="267"/>
       <c r="O4" s="5"/>
-      <c r="S4" s="266" t="s">
+      <c r="S4" s="268" t="s">
         <v>116</v>
       </c>
-      <c r="T4" s="267"/>
-      <c r="U4" s="267"/>
-      <c r="V4" s="267"/>
-      <c r="W4" s="267"/>
-      <c r="X4" s="267"/>
-      <c r="Y4" s="267"/>
-      <c r="Z4" s="267"/>
-      <c r="AA4" s="267"/>
-      <c r="AB4" s="267"/>
-      <c r="AC4" s="267"/>
+      <c r="T4" s="269"/>
+      <c r="U4" s="269"/>
+      <c r="V4" s="269"/>
+      <c r="W4" s="269"/>
+      <c r="X4" s="269"/>
+      <c r="Y4" s="269"/>
+      <c r="Z4" s="269"/>
+      <c r="AA4" s="269"/>
+      <c r="AB4" s="269"/>
+      <c r="AC4" s="269"/>
       <c r="AE4" s="88"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -15472,33 +15443,33 @@
       <c r="Q12" s="92"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="265" t="s">
+      <c r="C13" s="267" t="s">
         <v>122</v>
       </c>
-      <c r="D13" s="265"/>
-      <c r="E13" s="265"/>
-      <c r="F13" s="265"/>
-      <c r="G13" s="265"/>
-      <c r="H13" s="265"/>
-      <c r="I13" s="265"/>
-      <c r="J13" s="265"/>
-      <c r="K13" s="265"/>
-      <c r="L13" s="265"/>
+      <c r="D13" s="267"/>
+      <c r="E13" s="267"/>
+      <c r="F13" s="267"/>
+      <c r="G13" s="267"/>
+      <c r="H13" s="267"/>
+      <c r="I13" s="267"/>
+      <c r="J13" s="267"/>
+      <c r="K13" s="267"/>
+      <c r="L13" s="267"/>
       <c r="O13" s="5"/>
       <c r="Q13" s="92"/>
-      <c r="S13" s="266" t="s">
+      <c r="S13" s="268" t="s">
         <v>122</v>
       </c>
-      <c r="T13" s="267"/>
-      <c r="U13" s="267"/>
-      <c r="V13" s="267"/>
-      <c r="W13" s="267"/>
-      <c r="X13" s="267"/>
-      <c r="Y13" s="267"/>
-      <c r="Z13" s="267"/>
-      <c r="AA13" s="267"/>
-      <c r="AB13" s="267"/>
-      <c r="AC13" s="267"/>
+      <c r="T13" s="269"/>
+      <c r="U13" s="269"/>
+      <c r="V13" s="269"/>
+      <c r="W13" s="269"/>
+      <c r="X13" s="269"/>
+      <c r="Y13" s="269"/>
+      <c r="Z13" s="269"/>
+      <c r="AA13" s="269"/>
+      <c r="AB13" s="269"/>
+      <c r="AC13" s="269"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B14" s="16" t="s">
@@ -16107,33 +16078,33 @@
       <c r="Q22" s="92"/>
     </row>
     <row r="23" spans="2:31" x14ac:dyDescent="0.2">
-      <c r="C23" s="265" t="s">
+      <c r="C23" s="267" t="s">
         <v>124</v>
       </c>
-      <c r="D23" s="265"/>
-      <c r="E23" s="265"/>
-      <c r="F23" s="265"/>
-      <c r="G23" s="265"/>
-      <c r="H23" s="265"/>
-      <c r="I23" s="265"/>
-      <c r="J23" s="265"/>
-      <c r="K23" s="265"/>
-      <c r="L23" s="265"/>
+      <c r="D23" s="267"/>
+      <c r="E23" s="267"/>
+      <c r="F23" s="267"/>
+      <c r="G23" s="267"/>
+      <c r="H23" s="267"/>
+      <c r="I23" s="267"/>
+      <c r="J23" s="267"/>
+      <c r="K23" s="267"/>
+      <c r="L23" s="267"/>
       <c r="O23" s="5"/>
       <c r="Q23" s="92"/>
-      <c r="S23" s="266" t="s">
+      <c r="S23" s="268" t="s">
         <v>124</v>
       </c>
-      <c r="T23" s="267"/>
-      <c r="U23" s="267"/>
-      <c r="V23" s="267"/>
-      <c r="W23" s="267"/>
-      <c r="X23" s="267"/>
-      <c r="Y23" s="267"/>
-      <c r="Z23" s="267"/>
-      <c r="AA23" s="267"/>
-      <c r="AB23" s="267"/>
-      <c r="AC23" s="267"/>
+      <c r="T23" s="269"/>
+      <c r="U23" s="269"/>
+      <c r="V23" s="269"/>
+      <c r="W23" s="269"/>
+      <c r="X23" s="269"/>
+      <c r="Y23" s="269"/>
+      <c r="Z23" s="269"/>
+      <c r="AA23" s="269"/>
+      <c r="AB23" s="269"/>
+      <c r="AC23" s="269"/>
       <c r="AE23" s="88" t="str">
         <f>AE2</f>
         <v>TTM/YTD</v>
@@ -17452,32 +17423,32 @@
       <c r="O39" s="5"/>
     </row>
     <row r="40" spans="2:31" x14ac:dyDescent="0.2">
-      <c r="C40" s="265" t="s">
+      <c r="C40" s="267" t="s">
         <v>126</v>
       </c>
-      <c r="D40" s="265"/>
-      <c r="E40" s="265"/>
-      <c r="F40" s="265"/>
-      <c r="G40" s="265"/>
-      <c r="H40" s="265"/>
-      <c r="I40" s="265"/>
-      <c r="J40" s="265"/>
-      <c r="K40" s="265"/>
-      <c r="L40" s="265"/>
+      <c r="D40" s="267"/>
+      <c r="E40" s="267"/>
+      <c r="F40" s="267"/>
+      <c r="G40" s="267"/>
+      <c r="H40" s="267"/>
+      <c r="I40" s="267"/>
+      <c r="J40" s="267"/>
+      <c r="K40" s="267"/>
+      <c r="L40" s="267"/>
       <c r="O40" s="5"/>
-      <c r="S40" s="266" t="s">
+      <c r="S40" s="268" t="s">
         <v>126</v>
       </c>
-      <c r="T40" s="267"/>
-      <c r="U40" s="267"/>
-      <c r="V40" s="267"/>
-      <c r="W40" s="267"/>
-      <c r="X40" s="267"/>
-      <c r="Y40" s="267"/>
-      <c r="Z40" s="267"/>
-      <c r="AA40" s="267"/>
-      <c r="AB40" s="267"/>
-      <c r="AC40" s="267"/>
+      <c r="T40" s="269"/>
+      <c r="U40" s="269"/>
+      <c r="V40" s="269"/>
+      <c r="W40" s="269"/>
+      <c r="X40" s="269"/>
+      <c r="Y40" s="269"/>
+      <c r="Z40" s="269"/>
+      <c r="AA40" s="269"/>
+      <c r="AB40" s="269"/>
+      <c r="AC40" s="269"/>
     </row>
     <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -18044,18 +18015,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="C13:L13"/>
+    <mergeCell ref="S13:AC13"/>
+    <mergeCell ref="C23:L23"/>
+    <mergeCell ref="S23:AC23"/>
+    <mergeCell ref="C40:L40"/>
+    <mergeCell ref="S40:AC40"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="S2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
-    <mergeCell ref="C13:L13"/>
-    <mergeCell ref="S13:AC13"/>
-    <mergeCell ref="C23:L23"/>
-    <mergeCell ref="S23:AC23"/>
-    <mergeCell ref="C40:L40"/>
-    <mergeCell ref="S40:AC40"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -18089,35 +18060,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="256" t="s">
+      <c r="C2" s="259" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="256"/>
-      <c r="E2" s="256"/>
-      <c r="F2" s="256"/>
-      <c r="G2" s="268"/>
-      <c r="H2" s="269" t="s">
+      <c r="D2" s="259"/>
+      <c r="E2" s="259"/>
+      <c r="F2" s="259"/>
+      <c r="G2" s="265"/>
+      <c r="H2" s="266" t="s">
         <v>114</v>
       </c>
-      <c r="I2" s="256"/>
-      <c r="J2" s="256"/>
-      <c r="K2" s="256"/>
-      <c r="L2" s="256"/>
-      <c r="P2" s="256" t="s">
+      <c r="I2" s="259"/>
+      <c r="J2" s="259"/>
+      <c r="K2" s="259"/>
+      <c r="L2" s="259"/>
+      <c r="P2" s="259" t="s">
         <v>113</v>
       </c>
-      <c r="Q2" s="256"/>
-      <c r="R2" s="256"/>
-      <c r="S2" s="256"/>
-      <c r="T2" s="256"/>
-      <c r="U2" s="256"/>
-      <c r="V2" s="256"/>
-      <c r="W2" s="256"/>
-      <c r="X2" s="256" t="s">
+      <c r="Q2" s="259"/>
+      <c r="R2" s="259"/>
+      <c r="S2" s="259"/>
+      <c r="T2" s="259"/>
+      <c r="U2" s="259"/>
+      <c r="V2" s="259"/>
+      <c r="W2" s="259"/>
+      <c r="X2" s="259" t="s">
         <v>114</v>
       </c>
-      <c r="Y2" s="256"/>
-      <c r="Z2" s="256"/>
+      <c r="Y2" s="259"/>
+      <c r="Z2" s="259"/>
       <c r="AB2" s="86" t="s">
         <v>115</v>
       </c>
@@ -18126,31 +18097,31 @@
     <row r="4" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="265" t="s">
+      <c r="C4" s="267" t="s">
         <v>116</v>
       </c>
-      <c r="D4" s="265"/>
-      <c r="E4" s="265"/>
-      <c r="F4" s="265"/>
-      <c r="G4" s="265"/>
-      <c r="H4" s="265"/>
-      <c r="I4" s="265"/>
-      <c r="J4" s="265"/>
-      <c r="K4" s="265"/>
-      <c r="L4" s="265"/>
-      <c r="P4" s="267" t="s">
+      <c r="D4" s="267"/>
+      <c r="E4" s="267"/>
+      <c r="F4" s="267"/>
+      <c r="G4" s="267"/>
+      <c r="H4" s="267"/>
+      <c r="I4" s="267"/>
+      <c r="J4" s="267"/>
+      <c r="K4" s="267"/>
+      <c r="L4" s="267"/>
+      <c r="P4" s="269" t="s">
         <v>116</v>
       </c>
-      <c r="Q4" s="267"/>
-      <c r="R4" s="267"/>
-      <c r="S4" s="267"/>
-      <c r="T4" s="267"/>
-      <c r="U4" s="267"/>
-      <c r="V4" s="267"/>
-      <c r="W4" s="267"/>
-      <c r="X4" s="267"/>
-      <c r="Y4" s="267"/>
-      <c r="Z4" s="267"/>
+      <c r="Q4" s="269"/>
+      <c r="R4" s="269"/>
+      <c r="S4" s="269"/>
+      <c r="T4" s="269"/>
+      <c r="U4" s="269"/>
+      <c r="V4" s="269"/>
+      <c r="W4" s="269"/>
+      <c r="X4" s="269"/>
+      <c r="Y4" s="269"/>
+      <c r="Z4" s="269"/>
       <c r="AB4" s="88"/>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
@@ -18345,32 +18316,32 @@
       <c r="N8" s="92"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C9" s="265" t="s">
+      <c r="C9" s="267" t="s">
         <v>129</v>
       </c>
-      <c r="D9" s="265"/>
-      <c r="E9" s="265"/>
-      <c r="F9" s="265"/>
-      <c r="G9" s="265"/>
-      <c r="H9" s="265"/>
-      <c r="I9" s="265"/>
-      <c r="J9" s="265"/>
-      <c r="K9" s="265"/>
-      <c r="L9" s="265"/>
+      <c r="D9" s="267"/>
+      <c r="E9" s="267"/>
+      <c r="F9" s="267"/>
+      <c r="G9" s="267"/>
+      <c r="H9" s="267"/>
+      <c r="I9" s="267"/>
+      <c r="J9" s="267"/>
+      <c r="K9" s="267"/>
+      <c r="L9" s="267"/>
       <c r="N9" s="92"/>
-      <c r="P9" s="267" t="s">
+      <c r="P9" s="269" t="s">
         <v>130</v>
       </c>
-      <c r="Q9" s="267"/>
-      <c r="R9" s="267"/>
-      <c r="S9" s="267"/>
-      <c r="T9" s="267"/>
-      <c r="U9" s="267"/>
-      <c r="V9" s="267"/>
-      <c r="W9" s="267"/>
-      <c r="X9" s="267"/>
-      <c r="Y9" s="267"/>
-      <c r="Z9" s="267"/>
+      <c r="Q9" s="269"/>
+      <c r="R9" s="269"/>
+      <c r="S9" s="269"/>
+      <c r="T9" s="269"/>
+      <c r="U9" s="269"/>
+      <c r="V9" s="269"/>
+      <c r="W9" s="269"/>
+      <c r="X9" s="269"/>
+      <c r="Y9" s="269"/>
+      <c r="Z9" s="269"/>
       <c r="AB9" s="88">
         <f>AB4</f>
         <v>0</v>
@@ -18940,31 +18911,31 @@
       </c>
     </row>
     <row r="18" spans="2:26" x14ac:dyDescent="0.2">
-      <c r="C18" s="265" t="s">
+      <c r="C18" s="267" t="s">
         <v>132</v>
       </c>
-      <c r="D18" s="265"/>
-      <c r="E18" s="265"/>
-      <c r="F18" s="265"/>
-      <c r="G18" s="265"/>
-      <c r="H18" s="265"/>
-      <c r="I18" s="265"/>
-      <c r="J18" s="265"/>
-      <c r="K18" s="265"/>
-      <c r="L18" s="265"/>
-      <c r="P18" s="267" t="s">
+      <c r="D18" s="267"/>
+      <c r="E18" s="267"/>
+      <c r="F18" s="267"/>
+      <c r="G18" s="267"/>
+      <c r="H18" s="267"/>
+      <c r="I18" s="267"/>
+      <c r="J18" s="267"/>
+      <c r="K18" s="267"/>
+      <c r="L18" s="267"/>
+      <c r="P18" s="269" t="s">
         <v>132</v>
       </c>
-      <c r="Q18" s="267"/>
-      <c r="R18" s="267"/>
-      <c r="S18" s="267"/>
-      <c r="T18" s="267"/>
-      <c r="U18" s="267"/>
-      <c r="V18" s="267"/>
-      <c r="W18" s="267"/>
-      <c r="X18" s="267"/>
-      <c r="Y18" s="267"/>
-      <c r="Z18" s="267"/>
+      <c r="Q18" s="269"/>
+      <c r="R18" s="269"/>
+      <c r="S18" s="269"/>
+      <c r="T18" s="269"/>
+      <c r="U18" s="269"/>
+      <c r="V18" s="269"/>
+      <c r="W18" s="269"/>
+      <c r="X18" s="269"/>
+      <c r="Y18" s="269"/>
+      <c r="Z18" s="269"/>
     </row>
     <row r="19" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -19524,20 +19495,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="256" t="s">
+      <c r="C3" s="259" t="s">
         <v>113</v>
       </c>
-      <c r="D3" s="256"/>
-      <c r="E3" s="256"/>
-      <c r="F3" s="256"/>
-      <c r="G3" s="268"/>
-      <c r="H3" s="269" t="s">
+      <c r="D3" s="259"/>
+      <c r="E3" s="259"/>
+      <c r="F3" s="259"/>
+      <c r="G3" s="265"/>
+      <c r="H3" s="266" t="s">
         <v>114</v>
       </c>
-      <c r="I3" s="256"/>
-      <c r="J3" s="256"/>
-      <c r="K3" s="256"/>
-      <c r="L3" s="256"/>
+      <c r="I3" s="259"/>
+      <c r="J3" s="259"/>
+      <c r="K3" s="259"/>
+      <c r="L3" s="259"/>
       <c r="P3" s="270"/>
       <c r="Q3" s="270"/>
       <c r="R3" s="270"/>
@@ -19555,18 +19526,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="87"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="265" t="s">
+      <c r="C5" s="267" t="s">
         <v>116</v>
       </c>
-      <c r="D5" s="265"/>
-      <c r="E5" s="265"/>
-      <c r="F5" s="265"/>
-      <c r="G5" s="265"/>
-      <c r="H5" s="265"/>
-      <c r="I5" s="265"/>
-      <c r="J5" s="265"/>
-      <c r="K5" s="265"/>
-      <c r="L5" s="265"/>
+      <c r="D5" s="267"/>
+      <c r="E5" s="267"/>
+      <c r="F5" s="267"/>
+      <c r="G5" s="267"/>
+      <c r="H5" s="267"/>
+      <c r="I5" s="267"/>
+      <c r="J5" s="267"/>
+      <c r="K5" s="267"/>
+      <c r="L5" s="267"/>
       <c r="P5" s="270"/>
       <c r="Q5" s="270"/>
       <c r="R5" s="270"/>
@@ -19763,18 +19734,18 @@
       <c r="N10" s="92"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="265" t="s">
+      <c r="C11" s="267" t="s">
         <v>136</v>
       </c>
-      <c r="D11" s="265"/>
-      <c r="E11" s="265"/>
-      <c r="F11" s="265"/>
-      <c r="G11" s="265"/>
-      <c r="H11" s="265"/>
-      <c r="I11" s="265"/>
-      <c r="J11" s="265"/>
-      <c r="K11" s="265"/>
-      <c r="L11" s="265"/>
+      <c r="D11" s="267"/>
+      <c r="E11" s="267"/>
+      <c r="F11" s="267"/>
+      <c r="G11" s="267"/>
+      <c r="H11" s="267"/>
+      <c r="I11" s="267"/>
+      <c r="J11" s="267"/>
+      <c r="K11" s="267"/>
+      <c r="L11" s="267"/>
       <c r="N11" s="92"/>
       <c r="P11" s="270"/>
       <c r="Q11" s="270"/>
@@ -20028,18 +19999,18 @@
       <c r="D16" s="24"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="265" t="s">
+      <c r="C18" s="267" t="s">
         <v>141</v>
       </c>
-      <c r="D18" s="265"/>
-      <c r="E18" s="265"/>
-      <c r="F18" s="265"/>
-      <c r="G18" s="265"/>
-      <c r="H18" s="265"/>
-      <c r="I18" s="265"/>
-      <c r="J18" s="265"/>
-      <c r="K18" s="265"/>
-      <c r="L18" s="265"/>
+      <c r="D18" s="267"/>
+      <c r="E18" s="267"/>
+      <c r="F18" s="267"/>
+      <c r="G18" s="267"/>
+      <c r="H18" s="267"/>
+      <c r="I18" s="267"/>
+      <c r="J18" s="267"/>
+      <c r="K18" s="267"/>
+      <c r="L18" s="267"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -20257,18 +20228,18 @@
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="111"/>
-      <c r="C26" s="265" t="s">
+      <c r="C26" s="267" t="s">
         <v>147</v>
       </c>
-      <c r="D26" s="265"/>
-      <c r="E26" s="265"/>
-      <c r="F26" s="265"/>
-      <c r="G26" s="265"/>
-      <c r="H26" s="265"/>
-      <c r="I26" s="265"/>
-      <c r="J26" s="265"/>
-      <c r="K26" s="265"/>
-      <c r="L26" s="265"/>
+      <c r="D26" s="267"/>
+      <c r="E26" s="267"/>
+      <c r="F26" s="267"/>
+      <c r="G26" s="267"/>
+      <c r="H26" s="267"/>
+      <c r="I26" s="267"/>
+      <c r="J26" s="267"/>
+      <c r="K26" s="267"/>
+      <c r="L26" s="267"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="16" t="s">
@@ -20460,18 +20431,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="111"/>
-      <c r="C33" s="265" t="s">
+      <c r="C33" s="267" t="s">
         <v>151</v>
       </c>
-      <c r="D33" s="265"/>
-      <c r="E33" s="265"/>
-      <c r="F33" s="265"/>
-      <c r="G33" s="265"/>
-      <c r="H33" s="265"/>
-      <c r="I33" s="265"/>
-      <c r="J33" s="265"/>
-      <c r="K33" s="265"/>
-      <c r="L33" s="265"/>
+      <c r="D33" s="267"/>
+      <c r="E33" s="267"/>
+      <c r="F33" s="267"/>
+      <c r="G33" s="267"/>
+      <c r="H33" s="267"/>
+      <c r="I33" s="267"/>
+      <c r="J33" s="267"/>
+      <c r="K33" s="267"/>
+      <c r="L33" s="267"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
@@ -20655,18 +20626,18 @@
       <c r="C39" s="127"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="265" t="s">
+      <c r="C40" s="267" t="s">
         <v>154</v>
       </c>
-      <c r="D40" s="265"/>
-      <c r="E40" s="265"/>
-      <c r="F40" s="265"/>
-      <c r="G40" s="265"/>
-      <c r="H40" s="265"/>
-      <c r="I40" s="265"/>
-      <c r="J40" s="265"/>
-      <c r="K40" s="265"/>
-      <c r="L40" s="265"/>
+      <c r="D40" s="267"/>
+      <c r="E40" s="267"/>
+      <c r="F40" s="267"/>
+      <c r="G40" s="267"/>
+      <c r="H40" s="267"/>
+      <c r="I40" s="267"/>
+      <c r="J40" s="267"/>
+      <c r="K40" s="267"/>
+      <c r="L40" s="267"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -20930,6 +20901,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -20937,12 +20914,6 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -20980,20 +20951,20 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="256" t="s">
+      <c r="C2" s="259" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="256"/>
-      <c r="E2" s="256"/>
-      <c r="F2" s="256"/>
-      <c r="G2" s="268"/>
-      <c r="H2" s="269" t="s">
+      <c r="D2" s="259"/>
+      <c r="E2" s="259"/>
+      <c r="F2" s="259"/>
+      <c r="G2" s="265"/>
+      <c r="H2" s="266" t="s">
         <v>114</v>
       </c>
-      <c r="I2" s="256"/>
-      <c r="J2" s="256"/>
-      <c r="K2" s="256"/>
-      <c r="L2" s="256"/>
+      <c r="I2" s="259"/>
+      <c r="J2" s="259"/>
+      <c r="K2" s="259"/>
+      <c r="L2" s="259"/>
       <c r="S2" s="270"/>
       <c r="T2" s="270"/>
       <c r="U2" s="270"/>
@@ -21011,18 +20982,18 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="265" t="s">
+      <c r="C4" s="267" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="265"/>
-      <c r="E4" s="265"/>
-      <c r="F4" s="265"/>
-      <c r="G4" s="265"/>
-      <c r="H4" s="265"/>
-      <c r="I4" s="265"/>
-      <c r="J4" s="265"/>
-      <c r="K4" s="265"/>
-      <c r="L4" s="265"/>
+      <c r="D4" s="267"/>
+      <c r="E4" s="267"/>
+      <c r="F4" s="267"/>
+      <c r="G4" s="267"/>
+      <c r="H4" s="267"/>
+      <c r="I4" s="267"/>
+      <c r="J4" s="267"/>
+      <c r="K4" s="267"/>
+      <c r="L4" s="267"/>
       <c r="S4" s="270"/>
       <c r="T4" s="270"/>
       <c r="U4" s="270"/>
@@ -21396,18 +21367,18 @@
       <c r="AE10" s="64"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="265" t="s">
+      <c r="C13" s="267" t="s">
         <v>162</v>
       </c>
-      <c r="D13" s="265"/>
-      <c r="E13" s="265"/>
-      <c r="F13" s="265"/>
-      <c r="G13" s="265"/>
-      <c r="H13" s="265"/>
-      <c r="I13" s="265"/>
-      <c r="J13" s="265"/>
-      <c r="K13" s="265"/>
-      <c r="L13" s="265"/>
+      <c r="D13" s="267"/>
+      <c r="E13" s="267"/>
+      <c r="F13" s="267"/>
+      <c r="G13" s="267"/>
+      <c r="H13" s="267"/>
+      <c r="I13" s="267"/>
+      <c r="J13" s="267"/>
+      <c r="K13" s="267"/>
+      <c r="L13" s="267"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="12">
@@ -21500,18 +21471,18 @@
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C18" s="265" t="s">
+      <c r="C18" s="267" t="s">
         <v>163</v>
       </c>
-      <c r="D18" s="265"/>
-      <c r="E18" s="265"/>
-      <c r="F18" s="265"/>
-      <c r="G18" s="265"/>
-      <c r="H18" s="265"/>
-      <c r="I18" s="265"/>
-      <c r="J18" s="265"/>
-      <c r="K18" s="265"/>
-      <c r="L18" s="265"/>
+      <c r="D18" s="267"/>
+      <c r="E18" s="267"/>
+      <c r="F18" s="267"/>
+      <c r="G18" s="267"/>
+      <c r="H18" s="267"/>
+      <c r="I18" s="267"/>
+      <c r="J18" s="267"/>
+      <c r="K18" s="267"/>
+      <c r="L18" s="267"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -21703,18 +21674,18 @@
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C25" s="265" t="s">
+      <c r="C25" s="267" t="s">
         <v>271</v>
       </c>
-      <c r="D25" s="265"/>
-      <c r="E25" s="265"/>
-      <c r="F25" s="265"/>
-      <c r="G25" s="265"/>
-      <c r="H25" s="265"/>
-      <c r="I25" s="265"/>
-      <c r="J25" s="265"/>
-      <c r="K25" s="265"/>
-      <c r="L25" s="265"/>
+      <c r="D25" s="267"/>
+      <c r="E25" s="267"/>
+      <c r="F25" s="267"/>
+      <c r="G25" s="267"/>
+      <c r="H25" s="267"/>
+      <c r="I25" s="267"/>
+      <c r="J25" s="267"/>
+      <c r="K25" s="267"/>
+      <c r="L25" s="267"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B26" s="16" t="s">
@@ -21852,18 +21823,18 @@
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C31" s="265" t="s">
+      <c r="C31" s="267" t="s">
         <v>78</v>
       </c>
-      <c r="D31" s="265"/>
-      <c r="E31" s="265"/>
-      <c r="F31" s="265"/>
-      <c r="G31" s="265"/>
-      <c r="H31" s="265"/>
-      <c r="I31" s="265"/>
-      <c r="J31" s="265"/>
-      <c r="K31" s="265"/>
-      <c r="L31" s="265"/>
+      <c r="D31" s="267"/>
+      <c r="E31" s="267"/>
+      <c r="F31" s="267"/>
+      <c r="G31" s="267"/>
+      <c r="H31" s="267"/>
+      <c r="I31" s="267"/>
+      <c r="J31" s="267"/>
+      <c r="K31" s="267"/>
+      <c r="L31" s="267"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="16" t="s">
@@ -22002,16 +21973,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="S4:AC4"/>
+    <mergeCell ref="C13:L13"/>
+    <mergeCell ref="C18:L18"/>
     <mergeCell ref="C31:L31"/>
     <mergeCell ref="C25:L25"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="S2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="S4:AC4"/>
-    <mergeCell ref="C13:L13"/>
-    <mergeCell ref="C18:L18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -22074,10 +22045,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="256" t="s">
+      <c r="B4" s="259" t="s">
         <v>170</v>
       </c>
-      <c r="C4" s="256"/>
+      <c r="C4" s="259"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -22094,7 +22065,7 @@
       </c>
       <c r="C6" s="135">
         <f ca="1">Overview!C5</f>
-        <v>127.75</v>
+        <v>154.46</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22103,7 +22074,7 @@
       </c>
       <c r="C7" s="136">
         <f ca="1">C5*C6</f>
-        <v>6403085.5</v>
+        <v>7741844.1200000001</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22121,7 +22092,7 @@
       </c>
       <c r="C9" s="137">
         <f ca="1">Overview!F27</f>
-        <v>4.6700000000000005E-2</v>
+        <v>4.7619999999999996E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22130,7 +22101,7 @@
       </c>
       <c r="C10" s="135">
         <f ca="1">Overview!C13</f>
-        <v>0.86160000000000003</v>
+        <v>1.0437000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22162,10 +22133,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="256" t="s">
+      <c r="B15" s="259" t="s">
         <v>177</v>
       </c>
-      <c r="C15" s="256"/>
+      <c r="C15" s="259"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -22200,7 +22171,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>8.5472000000000006E-2</v>
+        <v>9.458649999999999E-2</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22209,7 +22180,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>8.5472000000000006E-2</v>
+        <v>9.458649999999999E-2</v>
       </c>
     </row>
   </sheetData>
@@ -22254,20 +22225,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="256" t="s">
+      <c r="C3" s="259" t="s">
         <v>113</v>
       </c>
-      <c r="D3" s="256"/>
-      <c r="E3" s="256"/>
-      <c r="F3" s="256"/>
-      <c r="G3" s="268"/>
-      <c r="H3" s="269" t="s">
+      <c r="D3" s="259"/>
+      <c r="E3" s="259"/>
+      <c r="F3" s="259"/>
+      <c r="G3" s="265"/>
+      <c r="H3" s="266" t="s">
         <v>114</v>
       </c>
-      <c r="I3" s="256"/>
-      <c r="J3" s="256"/>
-      <c r="K3" s="256"/>
-      <c r="L3" s="256"/>
+      <c r="I3" s="259"/>
+      <c r="J3" s="259"/>
+      <c r="K3" s="259"/>
+      <c r="L3" s="259"/>
       <c r="P3" s="270"/>
       <c r="Q3" s="270"/>
       <c r="R3" s="270"/>
@@ -22285,18 +22256,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="87"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="265" t="s">
+      <c r="C5" s="267" t="s">
         <v>184</v>
       </c>
-      <c r="D5" s="265"/>
-      <c r="E5" s="265"/>
-      <c r="F5" s="265"/>
-      <c r="G5" s="265"/>
-      <c r="H5" s="265"/>
-      <c r="I5" s="265"/>
-      <c r="J5" s="265"/>
-      <c r="K5" s="265"/>
-      <c r="L5" s="265"/>
+      <c r="D5" s="267"/>
+      <c r="E5" s="267"/>
+      <c r="F5" s="267"/>
+      <c r="G5" s="267"/>
+      <c r="H5" s="267"/>
+      <c r="I5" s="267"/>
+      <c r="J5" s="267"/>
+      <c r="K5" s="267"/>
+      <c r="L5" s="267"/>
       <c r="P5" s="270"/>
       <c r="Q5" s="270"/>
       <c r="R5" s="270"/>
@@ -22553,10 +22524,10 @@
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="256" t="s">
+      <c r="B13" s="259" t="s">
         <v>188</v>
       </c>
-      <c r="C13" s="256"/>
+      <c r="C13" s="259"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -22576,10 +22547,10 @@
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="256" t="s">
+      <c r="B18" s="259" t="s">
         <v>190</v>
       </c>
-      <c r="C18" s="256"/>
+      <c r="C18" s="259"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -22693,37 +22664,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="256" t="s">
+      <c r="C2" s="259" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="256"/>
-      <c r="E2" s="256"/>
-      <c r="F2" s="256"/>
-      <c r="G2" s="268"/>
-      <c r="H2" s="269" t="s">
+      <c r="D2" s="259"/>
+      <c r="E2" s="259"/>
+      <c r="F2" s="259"/>
+      <c r="G2" s="265"/>
+      <c r="H2" s="266" t="s">
         <v>114</v>
       </c>
-      <c r="I2" s="256"/>
-      <c r="J2" s="256"/>
-      <c r="K2" s="256"/>
-      <c r="L2" s="256"/>
+      <c r="I2" s="259"/>
+      <c r="J2" s="259"/>
+      <c r="K2" s="259"/>
+      <c r="L2" s="259"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="265" t="s">
+      <c r="C4" s="267" t="s">
         <v>198</v>
       </c>
-      <c r="D4" s="265"/>
-      <c r="E4" s="265"/>
-      <c r="F4" s="265"/>
-      <c r="G4" s="265"/>
-      <c r="H4" s="265"/>
-      <c r="I4" s="265"/>
-      <c r="J4" s="265"/>
-      <c r="K4" s="265"/>
-      <c r="L4" s="265"/>
+      <c r="D4" s="267"/>
+      <c r="E4" s="267"/>
+      <c r="F4" s="267"/>
+      <c r="G4" s="267"/>
+      <c r="H4" s="267"/>
+      <c r="I4" s="267"/>
+      <c r="J4" s="267"/>
+      <c r="K4" s="267"/>
+      <c r="L4" s="267"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -22912,18 +22883,18 @@
       <c r="N9" s="92"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C10" s="265" t="s">
+      <c r="C10" s="267" t="s">
         <v>122</v>
       </c>
-      <c r="D10" s="265"/>
-      <c r="E10" s="265"/>
-      <c r="F10" s="265"/>
-      <c r="G10" s="265"/>
-      <c r="H10" s="265"/>
-      <c r="I10" s="265"/>
-      <c r="J10" s="265"/>
-      <c r="K10" s="265"/>
-      <c r="L10" s="265"/>
+      <c r="D10" s="267"/>
+      <c r="E10" s="267"/>
+      <c r="F10" s="267"/>
+      <c r="G10" s="267"/>
+      <c r="H10" s="267"/>
+      <c r="I10" s="267"/>
+      <c r="J10" s="267"/>
+      <c r="K10" s="267"/>
+      <c r="L10" s="267"/>
       <c r="N10" s="92"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -23117,18 +23088,18 @@
       <c r="N15" s="92"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C16" s="265" t="s">
+      <c r="C16" s="267" t="s">
         <v>200</v>
       </c>
-      <c r="D16" s="265"/>
-      <c r="E16" s="265"/>
-      <c r="F16" s="265"/>
-      <c r="G16" s="265"/>
-      <c r="H16" s="265"/>
-      <c r="I16" s="265"/>
-      <c r="J16" s="265"/>
-      <c r="K16" s="265"/>
-      <c r="L16" s="265"/>
+      <c r="D16" s="267"/>
+      <c r="E16" s="267"/>
+      <c r="F16" s="267"/>
+      <c r="G16" s="267"/>
+      <c r="H16" s="267"/>
+      <c r="I16" s="267"/>
+      <c r="J16" s="267"/>
+      <c r="K16" s="267"/>
+      <c r="L16" s="267"/>
       <c r="N16" s="92"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
@@ -23262,18 +23233,18 @@
       <c r="N20" s="92"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C21" s="265" t="s">
+      <c r="C21" s="267" t="s">
         <v>203</v>
       </c>
-      <c r="D21" s="265"/>
-      <c r="E21" s="265"/>
-      <c r="F21" s="265"/>
-      <c r="G21" s="265"/>
-      <c r="H21" s="265"/>
-      <c r="I21" s="265"/>
-      <c r="J21" s="265"/>
-      <c r="K21" s="265"/>
-      <c r="L21" s="265"/>
+      <c r="D21" s="267"/>
+      <c r="E21" s="267"/>
+      <c r="F21" s="267"/>
+      <c r="G21" s="267"/>
+      <c r="H21" s="267"/>
+      <c r="I21" s="267"/>
+      <c r="J21" s="267"/>
+      <c r="K21" s="267"/>
+      <c r="L21" s="267"/>
       <c r="N21" s="92"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
@@ -23357,18 +23328,18 @@
       <c r="N25" s="92"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C26" s="265" t="s">
+      <c r="C26" s="267" t="s">
         <v>204</v>
       </c>
-      <c r="D26" s="265"/>
-      <c r="E26" s="265"/>
-      <c r="F26" s="265"/>
-      <c r="G26" s="265"/>
-      <c r="H26" s="265"/>
-      <c r="I26" s="265"/>
-      <c r="J26" s="265"/>
-      <c r="K26" s="265"/>
-      <c r="L26" s="265"/>
+      <c r="D26" s="267"/>
+      <c r="E26" s="267"/>
+      <c r="F26" s="267"/>
+      <c r="G26" s="267"/>
+      <c r="H26" s="267"/>
+      <c r="I26" s="267"/>
+      <c r="J26" s="267"/>
+      <c r="K26" s="267"/>
+      <c r="L26" s="267"/>
       <c r="N26" s="92"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
@@ -23638,10 +23609,10 @@
       <c r="N36" s="92"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B37" s="256" t="s">
+      <c r="B37" s="259" t="s">
         <v>209</v>
       </c>
-      <c r="C37" s="256"/>
+      <c r="C37" s="259"/>
       <c r="N37" s="92"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
@@ -23734,10 +23705,10 @@
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B49" s="256" t="s">
+      <c r="B49" s="259" t="s">
         <v>214</v>
       </c>
-      <c r="C49" s="256"/>
+      <c r="C49" s="259"/>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B50" s="1" t="s">
@@ -23793,10 +23764,10 @@
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B57" s="256" t="s">
+      <c r="B57" s="259" t="s">
         <v>332</v>
       </c>
-      <c r="C57" s="256"/>
+      <c r="C57" s="259"/>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B58" s="1" t="s">
@@ -23936,10 +23907,10 @@
       <c r="N3" s="92"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="256" t="s">
+      <c r="B4" s="259" t="s">
         <v>219</v>
       </c>
-      <c r="C4" s="256"/>
+      <c r="C4" s="259"/>
       <c r="N4" s="92"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -23993,7 +23964,7 @@
       </c>
       <c r="C10" s="135">
         <f ca="1">Overview!C5</f>
-        <v>127.75</v>
+        <v>154.46</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -24002,7 +23973,7 @@
       </c>
       <c r="C11" s="156">
         <f ca="1">(C9-C10)/C10</f>
-        <v>0.28798873623637516</v>
+        <v>6.5263246498749969E-2</v>
       </c>
     </row>
   </sheetData>
@@ -24058,37 +24029,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="256" t="s">
+      <c r="C2" s="259" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="256"/>
-      <c r="E2" s="256"/>
-      <c r="F2" s="256"/>
-      <c r="G2" s="268"/>
-      <c r="H2" s="269" t="s">
+      <c r="D2" s="259"/>
+      <c r="E2" s="259"/>
+      <c r="F2" s="259"/>
+      <c r="G2" s="265"/>
+      <c r="H2" s="266" t="s">
         <v>114</v>
       </c>
-      <c r="I2" s="256"/>
-      <c r="J2" s="256"/>
-      <c r="K2" s="256"/>
-      <c r="L2" s="256"/>
+      <c r="I2" s="259"/>
+      <c r="J2" s="259"/>
+      <c r="K2" s="259"/>
+      <c r="L2" s="259"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="265" t="s">
+      <c r="C4" s="267" t="s">
         <v>198</v>
       </c>
-      <c r="D4" s="265"/>
-      <c r="E4" s="265"/>
-      <c r="F4" s="265"/>
-      <c r="G4" s="265"/>
-      <c r="H4" s="265"/>
-      <c r="I4" s="265"/>
-      <c r="J4" s="265"/>
-      <c r="K4" s="265"/>
-      <c r="L4" s="265"/>
+      <c r="D4" s="267"/>
+      <c r="E4" s="267"/>
+      <c r="F4" s="267"/>
+      <c r="G4" s="267"/>
+      <c r="H4" s="267"/>
+      <c r="I4" s="267"/>
+      <c r="J4" s="267"/>
+      <c r="K4" s="267"/>
+      <c r="L4" s="267"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -24201,18 +24172,18 @@
       <c r="N8" s="92"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C9" s="265" t="s">
+      <c r="C9" s="267" t="s">
         <v>122</v>
       </c>
-      <c r="D9" s="265"/>
-      <c r="E9" s="265"/>
-      <c r="F9" s="265"/>
-      <c r="G9" s="265"/>
-      <c r="H9" s="265"/>
-      <c r="I9" s="265"/>
-      <c r="J9" s="265"/>
-      <c r="K9" s="265"/>
-      <c r="L9" s="265"/>
+      <c r="D9" s="267"/>
+      <c r="E9" s="267"/>
+      <c r="F9" s="267"/>
+      <c r="G9" s="267"/>
+      <c r="H9" s="267"/>
+      <c r="I9" s="267"/>
+      <c r="J9" s="267"/>
+      <c r="K9" s="267"/>
+      <c r="L9" s="267"/>
       <c r="N9" s="92"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -24333,18 +24304,18 @@
       <c r="N13" s="92"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C14" s="265" t="s">
+      <c r="C14" s="267" t="s">
         <v>422</v>
       </c>
-      <c r="D14" s="265"/>
-      <c r="E14" s="265"/>
-      <c r="F14" s="265"/>
-      <c r="G14" s="265"/>
-      <c r="H14" s="265"/>
-      <c r="I14" s="265"/>
-      <c r="J14" s="265"/>
-      <c r="K14" s="265"/>
-      <c r="L14" s="265"/>
+      <c r="D14" s="267"/>
+      <c r="E14" s="267"/>
+      <c r="F14" s="267"/>
+      <c r="G14" s="267"/>
+      <c r="H14" s="267"/>
+      <c r="I14" s="267"/>
+      <c r="J14" s="267"/>
+      <c r="K14" s="267"/>
+      <c r="L14" s="267"/>
       <c r="N14" s="92"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
@@ -24434,10 +24405,10 @@
       <c r="N19" s="92"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B20" s="256" t="s">
+      <c r="B20" s="259" t="s">
         <v>424</v>
       </c>
-      <c r="C20" s="256"/>
+      <c r="C20" s="259"/>
       <c r="N20" s="92"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
@@ -24539,20 +24510,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="256" t="s">
+      <c r="C3" s="259" t="s">
         <v>113</v>
       </c>
-      <c r="D3" s="256"/>
-      <c r="E3" s="256"/>
-      <c r="F3" s="256"/>
-      <c r="G3" s="268"/>
-      <c r="H3" s="269" t="s">
+      <c r="D3" s="259"/>
+      <c r="E3" s="259"/>
+      <c r="F3" s="259"/>
+      <c r="G3" s="265"/>
+      <c r="H3" s="266" t="s">
         <v>114</v>
       </c>
-      <c r="I3" s="256"/>
-      <c r="J3" s="256"/>
-      <c r="K3" s="256"/>
-      <c r="L3" s="256"/>
+      <c r="I3" s="259"/>
+      <c r="J3" s="259"/>
+      <c r="K3" s="259"/>
+      <c r="L3" s="259"/>
       <c r="P3" s="270"/>
       <c r="Q3" s="270"/>
       <c r="R3" s="270"/>
@@ -24570,18 +24541,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="87"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="265" t="s">
+      <c r="C5" s="267" t="s">
         <v>184</v>
       </c>
-      <c r="D5" s="265"/>
-      <c r="E5" s="265"/>
-      <c r="F5" s="265"/>
-      <c r="G5" s="265"/>
-      <c r="H5" s="265"/>
-      <c r="I5" s="265"/>
-      <c r="J5" s="265"/>
-      <c r="K5" s="265"/>
-      <c r="L5" s="265"/>
+      <c r="D5" s="267"/>
+      <c r="E5" s="267"/>
+      <c r="F5" s="267"/>
+      <c r="G5" s="267"/>
+      <c r="H5" s="267"/>
+      <c r="I5" s="267"/>
+      <c r="J5" s="267"/>
+      <c r="K5" s="267"/>
+      <c r="L5" s="267"/>
       <c r="P5" s="270"/>
       <c r="Q5" s="270"/>
       <c r="R5" s="270"/>
@@ -24832,7 +24803,7 @@
       </c>
       <c r="C15" s="158">
         <f ca="1">Overview!C5</f>
-        <v>127.75</v>
+        <v>154.46</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -24898,7 +24869,7 @@
       </c>
       <c r="C23" s="163">
         <f ca="1">C15*C22</f>
-        <v>5976911.5</v>
+        <v>7226565.5600000005</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -24925,7 +24896,7 @@
       </c>
       <c r="C26" s="164">
         <f ca="1">C23+C25-C24</f>
-        <v>4560352.5</v>
+        <v>5810006.5600000005</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -25008,18 +24979,18 @@
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C39" s="265" t="s">
+      <c r="C39" s="267" t="s">
         <v>233</v>
       </c>
-      <c r="D39" s="265"/>
-      <c r="E39" s="265"/>
-      <c r="F39" s="265"/>
-      <c r="G39" s="265"/>
-      <c r="H39" s="265"/>
-      <c r="I39" s="265"/>
-      <c r="J39" s="265"/>
-      <c r="K39" s="265"/>
-      <c r="L39" s="265"/>
+      <c r="D39" s="267"/>
+      <c r="E39" s="267"/>
+      <c r="F39" s="267"/>
+      <c r="G39" s="267"/>
+      <c r="H39" s="267"/>
+      <c r="I39" s="267"/>
+      <c r="J39" s="267"/>
+      <c r="K39" s="267"/>
+      <c r="L39" s="267"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="12">
@@ -25451,17 +25422,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C39:L39"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C39:L39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -32153,7 +32124,7 @@
       </c>
       <c r="AC116" s="63">
         <f ca="1">Overview!C5</f>
-        <v>127.75</v>
+        <v>154.46</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -32224,7 +32195,7 @@
       </c>
       <c r="AC117" s="65">
         <f ca="1">AC116/AC85</f>
-        <v>127.75</v>
+        <v>154.46</v>
       </c>
     </row>
     <row r="119" spans="1:31" x14ac:dyDescent="0.2">
@@ -33334,7 +33305,7 @@
       <c r="AA146" s="49"/>
       <c r="AC146" s="72">
         <f ca="1">AC117/Statement!AC26</f>
-        <v>40.676980665771602</v>
+        <v>49.181733335695355</v>
       </c>
     </row>
     <row r="147" spans="2:29" x14ac:dyDescent="0.2">
@@ -33371,7 +33342,7 @@
       <c r="AA147" s="49"/>
       <c r="AC147" s="72">
         <f ca="1">AC117/(Statement!AC5/Statement!AC22)</f>
-        <v>5.486156425273955</v>
+        <v>6.6332032990044238</v>
       </c>
     </row>
     <row r="148" spans="2:29" x14ac:dyDescent="0.2">
@@ -33432,7 +33403,7 @@
       </c>
       <c r="AC148" s="72">
         <f ca="1">AC117/(Statement!AC49/Statement!AC75)</f>
-        <v>4.2397201048135047</v>
+        <v>5.1261617799569006</v>
       </c>
     </row>
     <row r="149" spans="2:29" x14ac:dyDescent="0.2">
@@ -33493,7 +33464,7 @@
       </c>
       <c r="AC149" s="145">
         <f ca="1">Statement!AC117*Statement!AC78</f>
-        <v>6403085.5</v>
+        <v>7741844.1200000001</v>
       </c>
     </row>
     <row r="150" spans="2:29" x14ac:dyDescent="0.2">
@@ -33554,7 +33525,7 @@
       </c>
       <c r="AC150" s="145">
         <f ca="1">AC149+AC108-AC107+AC48+AC45</f>
-        <v>4986526.5</v>
+        <v>6325285.1200000001</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -33591,7 +33562,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="185">
         <f ca="1">AC150/AC5</f>
-        <v>4.3550373711137622</v>
+        <v>5.5242568309924351</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -33628,7 +33599,7 @@
       <c r="AA152" s="49"/>
       <c r="AC152" s="185">
         <f ca="1">AC150/AC12</f>
-        <v>31.744128974758887</v>
+        <v>40.266639844670081</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -33763,7 +33734,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="72">
         <f t="shared" ref="AC155:AC156" ca="1" si="151">AC149/AC153</f>
-        <v>25.326657305592914</v>
+        <v>30.621960762597897</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -33800,7 +33771,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="72">
         <f t="shared" ca="1" si="151"/>
-        <v>29.907557870628398</v>
+        <v>37.93699497528484</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -33837,7 +33808,7 @@
       <c r="AA157" s="49"/>
       <c r="AC157" s="74">
         <f t="shared" ref="AC157" ca="1" si="154">AC153/AC149</f>
-        <v>3.9484089350360851E-2</v>
+        <v>3.2656302049129865E-2</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
@@ -33874,7 +33845,7 @@
       <c r="AA158" s="49"/>
       <c r="AC158" s="74">
         <f ca="1">AC26/AC117</f>
-        <v>2.4583928886380415E-2</v>
+        <v>2.0332752267480887E-2</v>
       </c>
     </row>
     <row r="159" spans="2:29" x14ac:dyDescent="0.2">
@@ -33948,7 +33919,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="156">
         <f ca="1">-AC63/AC149</f>
-        <v>1.0870228111119241E-2</v>
+        <v>8.9904935983133698E-3</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -33985,7 +33956,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="156">
         <f ca="1">-(AC63+AC64)/AC149</f>
-        <v>1.0870228111119241E-2</v>
+        <v>8.9904935983133698E-3</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -34488,7 +34459,7 @@
       <c r="AA172" s="49"/>
       <c r="AC172" s="156">
         <f ca="1">(AC107-AC108)/AC149</f>
-        <v>0.22123068636206716</v>
+        <v>0.1829743634776258</v>
       </c>
     </row>
     <row r="173" spans="2:29" x14ac:dyDescent="0.2">
@@ -36410,15 +36381,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="256" t="s">
+      <c r="B4" s="259" t="s">
         <v>242</v>
       </c>
-      <c r="C4" s="256"/>
-      <c r="E4" s="256" t="s">
+      <c r="C4" s="259"/>
+      <c r="E4" s="259" t="s">
         <v>249</v>
       </c>
-      <c r="F4" s="256"/>
-      <c r="G4" s="256"/>
+      <c r="F4" s="259"/>
+      <c r="G4" s="259"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -36426,7 +36397,7 @@
       </c>
       <c r="C5" s="174">
         <f ca="1">Overview!C5</f>
-        <v>127.75</v>
+        <v>154.46</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="134" t="s">
@@ -36442,7 +36413,7 @@
       </c>
       <c r="C6" s="175">
         <f ca="1">Statement!AC149</f>
-        <v>6403085.5</v>
+        <v>7741844.1200000001</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>20</v>
@@ -36462,7 +36433,7 @@
       </c>
       <c r="C7" s="175">
         <f ca="1">Statement!AC150</f>
-        <v>4986526.5</v>
+        <v>6325285.1200000001</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>32</v>
@@ -36482,7 +36453,7 @@
       </c>
       <c r="C8" s="176">
         <f ca="1">Statement!AC146</f>
-        <v>40.676980665771602</v>
+        <v>49.181733335695355</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>252</v>
@@ -36502,7 +36473,7 @@
       </c>
       <c r="C9" s="176">
         <f ca="1">Statement!AC147</f>
-        <v>5.486156425273955</v>
+        <v>6.6332032990044238</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>253</v>
@@ -36522,7 +36493,7 @@
       </c>
       <c r="C10" s="176">
         <f ca="1">Statement!AC148</f>
-        <v>4.2397201048135047</v>
+        <v>5.1261617799569006</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -36542,7 +36513,7 @@
       </c>
       <c r="C11" s="176">
         <f ca="1">Statement!AC151</f>
-        <v>4.3550373711137622</v>
+        <v>5.5242568309924351</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -36551,18 +36522,18 @@
       </c>
       <c r="C12" s="176">
         <f ca="1">Statement!AC152</f>
-        <v>31.744128974758887</v>
+        <v>40.266639844670081</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="256" t="s">
+      <c r="B15" s="259" t="s">
         <v>78</v>
       </c>
-      <c r="C15" s="256"/>
-      <c r="E15" s="256" t="s">
+      <c r="C15" s="259"/>
+      <c r="E15" s="259" t="s">
         <v>255</v>
       </c>
-      <c r="F15" s="256"/>
+      <c r="F15" s="259"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -36613,14 +36584,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="256" t="s">
+      <c r="B21" s="259" t="s">
         <v>254</v>
       </c>
-      <c r="C21" s="256"/>
-      <c r="E21" s="256" t="s">
+      <c r="C21" s="259"/>
+      <c r="E21" s="259" t="s">
         <v>258</v>
       </c>
-      <c r="F21" s="256"/>
+      <c r="F21" s="259"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -36689,14 +36660,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="256" t="s">
+      <c r="B29" s="259" t="s">
         <v>259</v>
       </c>
-      <c r="C29" s="256"/>
-      <c r="E29" s="256" t="s">
+      <c r="C29" s="259"/>
+      <c r="E29" s="259" t="s">
         <v>265</v>
       </c>
-      <c r="F29" s="256"/>
+      <c r="F29" s="259"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -36772,14 +36743,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="256" t="s">
+      <c r="B37" s="259" t="s">
         <v>277</v>
       </c>
-      <c r="C37" s="256"/>
-      <c r="E37" s="256" t="s">
+      <c r="C37" s="259"/>
+      <c r="E37" s="259" t="s">
         <v>280</v>
       </c>
-      <c r="F37" s="256"/>
+      <c r="F37" s="259"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -36787,7 +36758,7 @@
       </c>
       <c r="C38" s="177">
         <f ca="1">Statement!AC158</f>
-        <v>2.4583928886380415E-2</v>
+        <v>2.0332752267480887E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>279</v>
@@ -36803,7 +36774,7 @@
       </c>
       <c r="C39" s="217">
         <f ca="1">Statement!AC157</f>
-        <v>3.9484089350360851E-2</v>
+        <v>3.2656302049129865E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>281</v>
@@ -36835,7 +36806,7 @@
       </c>
       <c r="C41" s="177">
         <f ca="1">Statement!AC160</f>
-        <v>1.0870228111119241E-2</v>
+        <v>8.9904935983133698E-3</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -36844,18 +36815,18 @@
       </c>
       <c r="C42" s="177">
         <f ca="1">Statement!AC161</f>
-        <v>1.0870228111119241E-2</v>
+        <v>8.9904935983133698E-3</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="256" t="s">
+      <c r="B45" s="259" t="s">
         <v>288</v>
       </c>
-      <c r="C45" s="256"/>
-      <c r="E45" s="256" t="s">
+      <c r="C45" s="259"/>
+      <c r="E45" s="259" t="s">
         <v>294</v>
       </c>
-      <c r="F45" s="256"/>
+      <c r="F45" s="259"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -36888,18 +36859,18 @@
       </c>
       <c r="F48" s="177">
         <f ca="1">Statement!AC172</f>
-        <v>0.22123068636206716</v>
+        <v>0.1829743634776258</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="256" t="s">
+      <c r="B51" s="259" t="s">
         <v>291</v>
       </c>
-      <c r="C51" s="256"/>
-      <c r="E51" s="256" t="s">
+      <c r="C51" s="259"/>
+      <c r="E51" s="259" t="s">
         <v>312</v>
       </c>
-      <c r="F51" s="256"/>
+      <c r="F51" s="259"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -37067,7 +37038,7 @@
       </c>
       <c r="I6" s="174">
         <f ca="1">Statement!AC116</f>
-        <v>127.75</v>
+        <v>154.46</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -37096,7 +37067,7 @@
       </c>
       <c r="I7" s="175">
         <f ca="1">Statement!AC149</f>
-        <v>6403085.5</v>
+        <v>7741844.1200000001</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -37125,7 +37096,7 @@
       </c>
       <c r="I8" s="175">
         <f ca="1">Statement!AC150</f>
-        <v>4986526.5</v>
+        <v>6325285.1200000001</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -37154,7 +37125,7 @@
       </c>
       <c r="I9" s="176">
         <f ca="1">Statement!AC146</f>
-        <v>40.676980665771602</v>
+        <v>49.181733335695355</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -37183,7 +37154,7 @@
       </c>
       <c r="I10" s="176">
         <f ca="1">Statement!AC147</f>
-        <v>5.486156425273955</v>
+        <v>6.6332032990044238</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -37212,7 +37183,7 @@
       </c>
       <c r="I11" s="176">
         <f ca="1">Statement!AC148</f>
-        <v>4.2397201048135047</v>
+        <v>5.1261617799569006</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -37241,7 +37212,7 @@
       </c>
       <c r="I12" s="176">
         <f ca="1">Statement!AC151</f>
-        <v>4.3550373711137622</v>
+        <v>5.5242568309924351</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -37270,7 +37241,7 @@
       </c>
       <c r="I13" s="176">
         <f ca="1">Statement!AC152</f>
-        <v>31.744128974758887</v>
+        <v>40.266639844670081</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -38043,7 +38014,7 @@
       </c>
       <c r="I51" s="177">
         <f ca="1">Statement!AC158</f>
-        <v>2.4583928886380415E-2</v>
+        <v>2.0332752267480887E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -38072,7 +38043,7 @@
       </c>
       <c r="I52" s="177">
         <f ca="1">Statement!AC157</f>
-        <v>3.9484089350360851E-2</v>
+        <v>3.2656302049129865E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -38130,7 +38101,7 @@
       </c>
       <c r="I54" s="177">
         <f ca="1">Statement!AC160</f>
-        <v>1.0870228111119241E-2</v>
+        <v>8.9904935983133698E-3</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -38159,7 +38130,7 @@
       </c>
       <c r="I55" s="177">
         <f ca="1">Statement!AC161</f>
-        <v>1.0870228111119241E-2</v>
+        <v>8.9904935983133698E-3</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -38395,7 +38366,7 @@
       </c>
       <c r="I68" s="198">
         <f ca="1">Statement!AC172</f>
-        <v>0.22123068636206716</v>
+        <v>0.1829743634776258</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -38938,14 +38909,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="260" t="s">
+      <c r="C3" s="262" t="s">
         <v>322</v>
       </c>
-      <c r="D3" s="261"/>
-      <c r="F3" s="262" t="s">
+      <c r="D3" s="263"/>
+      <c r="F3" s="264" t="s">
         <v>323</v>
       </c>
-      <c r="G3" s="261"/>
+      <c r="G3" s="263"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -39012,19 +38983,19 @@
       <c r="B7" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C7" s="263">
+      <c r="C7" s="260">
         <f>Statement!AA89</f>
         <v>2.2218264392893719E-2</v>
       </c>
-      <c r="D7" s="264"/>
-      <c r="F7" s="263">
+      <c r="D7" s="261"/>
+      <c r="F7" s="260">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.18309713991239371</v>
       </c>
-      <c r="G7" s="264"/>
+      <c r="G7" s="261"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="209" t="s">
@@ -39051,19 +39022,19 @@
       <c r="B9" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C9" s="263">
+      <c r="C9" s="260">
         <f>Statement!AA90</f>
         <v>3.6046202026093238E-2</v>
       </c>
-      <c r="D9" s="264"/>
-      <c r="F9" s="263">
+      <c r="D9" s="261"/>
+      <c r="F9" s="260">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.17263647322197348</v>
       </c>
-      <c r="G9" s="264"/>
+      <c r="G9" s="261"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="209" t="s">
@@ -39090,19 +39061,19 @@
       <c r="B11" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C11" s="263">
+      <c r="C11" s="260">
         <f>Statement!AA91</f>
         <v>1.710027405488606E-2</v>
       </c>
-      <c r="D11" s="264"/>
-      <c r="F11" s="263">
+      <c r="D11" s="261"/>
+      <c r="F11" s="260">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>0.1870895657269924</v>
       </c>
-      <c r="G11" s="264"/>
+      <c r="G11" s="261"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="209" t="s">
@@ -39129,19 +39100,19 @@
       <c r="B13" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C13" s="263">
+      <c r="C13" s="260">
         <f>Statement!AA95</f>
         <v>8.4392741251357012E-2</v>
       </c>
-      <c r="D13" s="264"/>
-      <c r="F13" s="263">
+      <c r="D13" s="261"/>
+      <c r="F13" s="260">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.22501976973287405</v>
       </c>
-      <c r="G13" s="264"/>
+      <c r="G13" s="261"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="209" t="s">
@@ -39168,19 +39139,19 @@
       <c r="B15" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C15" s="263">
+      <c r="C15" s="260">
         <f>Statement!AA96</f>
         <v>-0.23765355851505829</v>
       </c>
-      <c r="D15" s="264"/>
-      <c r="F15" s="263">
+      <c r="D15" s="261"/>
+      <c r="F15" s="260">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>1.7444474417768186E-2</v>
       </c>
-      <c r="G15" s="264"/>
+      <c r="G15" s="261"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="209" t="s">
@@ -39207,19 +39178,19 @@
       <c r="B17" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C17" s="263">
+      <c r="C17" s="260">
         <f>Statement!AA98</f>
         <v>-0.23704555913483663</v>
       </c>
-      <c r="D17" s="264"/>
-      <c r="F17" s="263">
+      <c r="D17" s="261"/>
+      <c r="F17" s="260">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>-0.25955204216073779</v>
       </c>
-      <c r="G17" s="264"/>
+      <c r="G17" s="261"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="209" t="s">
@@ -39246,22 +39217,22 @@
       <c r="B19" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C19" s="263">
+      <c r="C19" s="260">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>2.5565842762241744E-2</v>
       </c>
-      <c r="D19" s="264"/>
-      <c r="F19" s="263">
+      <c r="D19" s="261"/>
+      <c r="F19" s="260">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>2.5293753865182372E-2</v>
       </c>
-      <c r="G19" s="264"/>
+      <c r="G19" s="261"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="209" t="s">
@@ -39288,22 +39259,22 @@
       <c r="B21" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C21" s="263">
+      <c r="C21" s="260">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>-0.2584269662921348</v>
       </c>
-      <c r="D21" s="264"/>
-      <c r="F21" s="263">
+      <c r="D21" s="261"/>
+      <c r="F21" s="260">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>-0.27472527472527469</v>
       </c>
-      <c r="G21" s="264"/>
+      <c r="G21" s="261"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -39352,22 +39323,22 @@
       <c r="B25" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C25" s="263">
+      <c r="C25" s="260">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>2.840483364420425E-2</v>
       </c>
-      <c r="D25" s="264"/>
-      <c r="F25" s="263">
+      <c r="D25" s="261"/>
+      <c r="F25" s="260">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>0.22478379327694395</v>
       </c>
-      <c r="G25" s="264"/>
+      <c r="G25" s="261"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="str">
@@ -39395,22 +39366,22 @@
       <c r="B27" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C27" s="263">
+      <c r="C27" s="260">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>2.1247695740758708E-2</v>
       </c>
-      <c r="D27" s="264"/>
-      <c r="F27" s="263">
+      <c r="D27" s="261"/>
+      <c r="F27" s="260">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>2.1792942775323981E-2</v>
       </c>
-      <c r="G27" s="264"/>
+      <c r="G27" s="261"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="str">
@@ -39438,22 +39409,22 @@
       <c r="B29" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C29" s="263">
+      <c r="C29" s="260">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>-0.10674206945303526</v>
       </c>
-      <c r="D29" s="264"/>
-      <c r="F29" s="263">
+      <c r="D29" s="261"/>
+      <c r="F29" s="260">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>2.0816812053925456E-3</v>
       </c>
-      <c r="G29" s="264"/>
+      <c r="G29" s="261"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="str">
@@ -39481,22 +39452,22 @@
       <c r="B31" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C31" s="263">
+      <c r="C31" s="260">
         <f>IF(C30=0,
 IF(D30=0,0,IF(D30&gt;0,1,-1)),
 (D30-C30)/ABS(C30)
 )</f>
         <v>-5.2569263556713236E-2</v>
       </c>
-      <c r="D31" s="264"/>
-      <c r="F31" s="263">
+      <c r="D31" s="261"/>
+      <c r="F31" s="260">
         <f>IF(F30=0,
 IF(G30=0,0,IF(G30&gt;0,1,-1)),
 (G30-F30)/ABS(F30)
 )</f>
         <v>-0.22983638113570742</v>
       </c>
-      <c r="G31" s="264"/>
+      <c r="G31" s="261"/>
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B32" s="20" t="str">
@@ -39524,22 +39495,22 @@
       <c r="B33" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C33" s="263">
+      <c r="C33" s="260">
         <f>IF(C32=0,
 IF(D32=0,0,IF(D32&gt;0,1,-1)),
 (D32-C32)/ABS(C32)
 )</f>
         <v>0.84164222873900296</v>
       </c>
-      <c r="D33" s="264"/>
-      <c r="F33" s="263">
+      <c r="D33" s="261"/>
+      <c r="F33" s="260">
         <f>IF(F32=0,
 IF(G32=0,0,IF(G32&gt;0,1,-1)),
 (G32-F32)/ABS(F32)
 )</f>
         <v>1.482213438735178</v>
       </c>
-      <c r="G33" s="264"/>
+      <c r="G33" s="261"/>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B35" s="8" t="s">
@@ -39588,22 +39559,22 @@
       <c r="B37" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C37" s="263">
+      <c r="C37" s="260">
         <f>IF(C36=0,
 IF(D36=0,0,IF(D36&gt;0,1,-1)),
 (D36-C36)/ABS(C36)
 )</f>
         <v>3.8938053097345132E-2</v>
       </c>
-      <c r="D37" s="264"/>
-      <c r="F37" s="263">
+      <c r="D37" s="261"/>
+      <c r="F37" s="260">
         <f>IF(F36=0,
 IF(G36=0,0,IF(G36&gt;0,1,-1)),
 (G36-F36)/ABS(F36)
 )</f>
         <v>0.23060796645702306</v>
       </c>
-      <c r="G37" s="264"/>
+      <c r="G37" s="261"/>
     </row>
     <row r="38" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="str">
@@ -39631,22 +39602,22 @@
       <c r="B39" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C39" s="263">
+      <c r="C39" s="260">
         <f>IF(C38=0,
 IF(D38=0,0,IF(D38&gt;0,1,-1)),
 (D38-C38)/ABS(C38)
 )</f>
         <v>2.0319303338171262E-2</v>
       </c>
-      <c r="D39" s="264"/>
-      <c r="F39" s="263">
+      <c r="D39" s="261"/>
+      <c r="F39" s="260">
         <f>IF(F38=0,
 IF(G38=0,0,IF(G38&gt;0,1,-1)),
 (G38-F38)/ABS(F38)
 )</f>
         <v>9.5869056897895558E-2</v>
       </c>
-      <c r="G39" s="264"/>
+      <c r="G39" s="261"/>
     </row>
     <row r="40" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B40" s="20" t="str">
@@ -39674,22 +39645,22 @@
       <c r="B41" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C41" s="263">
+      <c r="C41" s="260">
         <f>IF(C40=0,
 IF(D40=0,0,IF(D40&gt;0,1,-1)),
 (D40-C40)/ABS(C40)
 )</f>
         <v>1.6E-2</v>
       </c>
-      <c r="D41" s="264"/>
-      <c r="F41" s="263">
+      <c r="D41" s="261"/>
+      <c r="F41" s="260">
         <f>IF(F40=0,
 IF(G40=0,0,IF(G40&gt;0,1,-1)),
 (G40-F40)/ABS(F40)
 )</f>
         <v>0.16513761467889909</v>
       </c>
-      <c r="G41" s="264"/>
+      <c r="G41" s="261"/>
     </row>
     <row r="42" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B42" s="20" t="str">
@@ -39717,22 +39688,22 @@
       <c r="B43" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C43" s="263">
+      <c r="C43" s="260">
         <f>IF(C42=0,
 IF(D42=0,0,IF(D42&gt;0,1,-1)),
 (D42-C42)/ABS(C42)
 )</f>
         <v>2.0750199521149242E-2</v>
       </c>
-      <c r="D43" s="264"/>
-      <c r="F43" s="263">
+      <c r="D43" s="261"/>
+      <c r="F43" s="260">
         <f>IF(F42=0,
 IF(G42=0,0,IF(G42&gt;0,1,-1)),
 (G42-F42)/ABS(F42)
 )</f>
         <v>8.9437819420783646E-2</v>
       </c>
-      <c r="G43" s="264"/>
+      <c r="G43" s="261"/>
     </row>
     <row r="44" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B44" s="20" t="str">
@@ -39760,22 +39731,22 @@
       <c r="B45" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C45" s="263">
+      <c r="C45" s="260">
         <f>IF(C44=0,
 IF(D44=0,0,IF(D44&gt;0,1,-1)),
 (D44-C44)/ABS(C44)
 )</f>
         <v>1.2209481933271921E-2</v>
       </c>
-      <c r="D45" s="264"/>
-      <c r="F45" s="263">
+      <c r="D45" s="261"/>
+      <c r="F45" s="260">
         <f>IF(F44=0,
 IF(G44=0,0,IF(G44&gt;0,1,-1)),
 (G44-F44)/ABS(F44)
 )</f>
         <v>5.119238950540856E-2</v>
       </c>
-      <c r="G45" s="264"/>
+      <c r="G45" s="261"/>
     </row>
     <row r="46" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="str">
@@ -39803,22 +39774,22 @@
       <c r="B47" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C47" s="263">
+      <c r="C47" s="260">
         <f>IF(C46=0,
 IF(D46=0,0,IF(D46&gt;0,1,-1)),
 (D46-C46)/ABS(C46)
 )</f>
         <v>1.8247963846473435E-2</v>
       </c>
-      <c r="D47" s="264"/>
-      <c r="F47" s="263">
+      <c r="D47" s="261"/>
+      <c r="F47" s="260">
         <f>IF(F46=0,
 IF(G46=0,0,IF(G46&gt;0,1,-1)),
 (G46-F46)/ABS(F46)
 )</f>
         <v>0.1229516507570132</v>
       </c>
-      <c r="G47" s="264"/>
+      <c r="G47" s="261"/>
     </row>
     <row r="48" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B48" s="20" t="str">
@@ -39846,22 +39817,22 @@
       <c r="B49" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C49" s="263">
+      <c r="C49" s="260">
         <f>IF(C48=0,
 IF(D48=0,0,IF(D48&gt;0,1,-1)),
 (D48-C48)/ABS(C48)
 )</f>
         <v>-4.2332859174963834E-3</v>
       </c>
-      <c r="D49" s="264"/>
-      <c r="F49" s="263">
+      <c r="D49" s="261"/>
+      <c r="F49" s="260">
         <f>IF(F48=0,
 IF(G48=0,0,IF(G48&gt;0,1,-1)),
 (G48-F48)/ABS(F48)
 )</f>
         <v>6.3208790635154666E-2</v>
       </c>
-      <c r="G49" s="264"/>
+      <c r="G49" s="261"/>
     </row>
     <row r="50" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B50" s="20" t="str">
@@ -39889,22 +39860,22 @@
       <c r="B51" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C51" s="263">
+      <c r="C51" s="260">
         <f>IF(C50=0,
 IF(D50=0,0,IF(D50&gt;0,1,-1)),
 (D50-C50)/ABS(C50)
 )</f>
         <v>4.8738292663854846E-4</v>
       </c>
-      <c r="D51" s="264"/>
-      <c r="F51" s="263">
+      <c r="D51" s="261"/>
+      <c r="F51" s="260">
         <f>IF(F50=0,
 IF(G50=0,0,IF(G50&gt;0,1,-1)),
 (G50-F50)/ABS(F50)
 )</f>
         <v>-6.2091544317255373E-2</v>
       </c>
-      <c r="G51" s="264"/>
+      <c r="G51" s="261"/>
     </row>
     <row r="52" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="str">
@@ -39932,39 +39903,43 @@
       <c r="B53" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C53" s="263">
+      <c r="C53" s="260">
         <f>IF(C52=0,
 IF(D52=0,0,IF(D52&gt;0,1,-1)),
 (D52-C52)/ABS(C52)
 )</f>
         <v>-8.8077740902117604E-2</v>
       </c>
-      <c r="D53" s="264"/>
-      <c r="F53" s="263">
+      <c r="D53" s="261"/>
+      <c r="F53" s="260">
         <f>IF(F52=0,
 IF(G52=0,0,IF(G52&gt;0,1,-1)),
 (G52-F52)/ABS(F52)
 )</f>
         <v>-0.37416005758387127</v>
       </c>
-      <c r="G53" s="264"/>
+      <c r="G53" s="261"/>
     </row>
   </sheetData>
   <mergeCells count="46">
-    <mergeCell ref="C53:D53"/>
-    <mergeCell ref="F53:G53"/>
-    <mergeCell ref="C47:D47"/>
-    <mergeCell ref="F47:G47"/>
-    <mergeCell ref="C49:D49"/>
-    <mergeCell ref="F49:G49"/>
-    <mergeCell ref="C51:D51"/>
-    <mergeCell ref="F51:G51"/>
-    <mergeCell ref="C41:D41"/>
-    <mergeCell ref="F41:G41"/>
-    <mergeCell ref="C43:D43"/>
-    <mergeCell ref="F43:G43"/>
-    <mergeCell ref="C45:D45"/>
-    <mergeCell ref="F45:G45"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
     <mergeCell ref="C37:D37"/>
     <mergeCell ref="F37:G37"/>
     <mergeCell ref="C39:D39"/>
@@ -39979,24 +39954,20 @@
     <mergeCell ref="F31:G31"/>
     <mergeCell ref="C33:D33"/>
     <mergeCell ref="F33:G33"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="F41:G41"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="F43:G43"/>
+    <mergeCell ref="C45:D45"/>
+    <mergeCell ref="F45:G45"/>
+    <mergeCell ref="C53:D53"/>
+    <mergeCell ref="F53:G53"/>
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="F47:G47"/>
+    <mergeCell ref="C49:D49"/>
+    <mergeCell ref="F49:G49"/>
+    <mergeCell ref="C51:D51"/>
+    <mergeCell ref="F51:G51"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/DUOL.xlsx
+++ b/DUOL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E23FF4B1-97DF-3848-840E-94276066BDD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28A8BBA0-A261-D441-A705-76A9D16852C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -2410,6 +2410,9 @@
     <xf numFmtId="39" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="10" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="39" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2417,15 +2420,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2437,10 +2431,10 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2450,6 +2444,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -12931,7 +12931,7 @@
       <sheetData sheetId="0">
         <row r="12">
           <cell r="C12">
-            <v>4.4999999999999998E-2</v>
+            <v>4.3999999999999997E-2</v>
           </cell>
         </row>
       </sheetData>
@@ -13158,11 +13158,11 @@
     <v>Powered by Refinitiv</v>
     <v>353</v>
     <v>87.89</v>
-    <v>1.0437000000000001</v>
-    <v>-4.3600000000000003</v>
-    <v>-2.7452000000000001E-2</v>
-    <v>0.04</v>
-    <v>2.5900000000000001E-4</v>
+    <v>1.0487</v>
+    <v>-1.48</v>
+    <v>-1.0196E-2</v>
+    <v>0.52</v>
+    <v>3.6189999999999998E-3</v>
     <v>USD</v>
     <v>Duolingo, Inc. is a technology company. The Company is engaged in offering a mobile learning platform, as well as a digital English language proficiency assessment exam. It operates a freemium business model, namely, the app and the Website are accessible free of charge, although Duolingo also offers premium services for a subscription fee. Its solutions consist of the Duolingo App, Super Duolingo, Duolingo Max, Duolingo English Test: AI-Driven Language Assessment, Duolingo for Schools, and Duolingo ABC. The Duolingo App offers courses in over 40 different languages, including Spanish, English, French, German, Italian, Portuguese, Japanese and Chinese. Duolingo can also be accessed on desktop computers via a Web browser. Its subscription offering, Super Duolingo, offers learners additional features to enhance their learning experience. The Duolingo English Test is an online, on-demand, high-stakes English proficiency assessment. It also operates an animation and motion design studio.</v>
     <v>900</v>
@@ -13170,25 +13170,25 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>5900 PENN AVE, SECOND FLOOR, PITTSBURGH, PA, 15206 US</v>
-    <v>158.31</v>
+    <v>146.44999999999999</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46269.897677916408</v>
+    <v>46276.983224698437</v>
     <v>0</v>
-    <v>153</v>
-    <v>7226607264</v>
+    <v>141.53</v>
+    <v>6722251273</v>
     <v>DUOLINGO, INC.</v>
     <v>DUOLINGO, INC.</v>
-    <v>157.46</v>
-    <v>18.411100000000001</v>
-    <v>158.82</v>
-    <v>154.46</v>
-    <v>154.5</v>
+    <v>145.06</v>
+    <v>17.302600000000002</v>
+    <v>145.16</v>
+    <v>143.68</v>
+    <v>144.19999999999999</v>
     <v>46786270</v>
     <v>DUOL</v>
     <v>DUOLINGO, INC. (XNAS:DUOL)</v>
-    <v>1055836</v>
-    <v>1353949</v>
+    <v>980262</v>
+    <v>1311929</v>
     <v>2011</v>
   </rv>
   <rv s="2">
@@ -13210,19 +13210,19 @@
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>48.06</v>
+    <v>48.12</v>
     <v>39.47</v>
-    <v>-0.34</v>
-    <v>-7.0889999999999998E-3</v>
+    <v>0.22</v>
+    <v>4.62E-3</v>
     <v>US</v>
-    <v>47.68</v>
+    <v>48.12</v>
     <v>Index</v>
     <v>3</v>
-    <v>47.32</v>
+    <v>47.48</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>47.66</v>
-    <v>47.96</v>
+    <v>47.54</v>
     <v>47.62</v>
+    <v>47.84</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -13444,9 +13444,9 @@
       <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq Last Sale</v>
+      <v>Source: Nasdaq</v>
       <v>GMT</v>
-      <v>Real-Time Nasdaq Last Sale</v>
+      <v>Delayed 15 minutes</v>
       <v>from close</v>
       <v>from close</v>
     </spb>
@@ -14017,18 +14017,18 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="256" t="s">
+      <c r="B2" s="257" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="257"/>
-      <c r="E2" s="256" t="s">
+      <c r="C2" s="258"/>
+      <c r="E2" s="257" t="s">
         <v>296</v>
       </c>
-      <c r="F2" s="257"/>
-      <c r="H2" s="256" t="s">
+      <c r="F2" s="258"/>
+      <c r="H2" s="257" t="s">
         <v>338</v>
       </c>
-      <c r="I2" s="257"/>
+      <c r="I2" s="258"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="187" t="s">
@@ -14043,7 +14043,7 @@
       </c>
       <c r="F3" s="189">
         <f ca="1">Statement!AC149</f>
-        <v>7741844.1200000001</v>
+        <v>7201528.96</v>
       </c>
       <c r="H3" s="187" t="str">
         <f>'AVG target price'!B5</f>
@@ -14067,7 +14067,7 @@
       </c>
       <c r="F4" s="190">
         <f ca="1">Statement!AC150</f>
-        <v>6325285.1200000001</v>
+        <v>5784969.96</v>
       </c>
       <c r="H4" s="187" t="str">
         <f>'AVG target price'!B6</f>
@@ -14084,7 +14084,7 @@
       </c>
       <c r="C5" s="210" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>154.46</v>
+        <v>143.68</v>
       </c>
       <c r="E5" s="187" t="s">
         <v>252</v>
@@ -14108,14 +14108,14 @@
       </c>
       <c r="C6" s="210" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>154.5</v>
+        <v>144.19999999999999</v>
       </c>
       <c r="E6" s="187" t="s">
         <v>246</v>
       </c>
       <c r="F6" s="192">
         <f ca="1">Statement!AC146</f>
-        <v>49.181733335695355</v>
+        <v>45.749264830200104</v>
       </c>
       <c r="H6" s="187" t="str">
         <f>'AVG target price'!B8</f>
@@ -14132,14 +14132,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>-4.3600000000000003</v>
+        <v>-1.48</v>
       </c>
       <c r="E7" s="188" t="s">
         <v>205</v>
       </c>
       <c r="F7" s="193">
         <f ca="1">Statement!AC147</f>
-        <v>6.6332032990044238</v>
+        <v>6.1702618801045945</v>
       </c>
       <c r="H7" s="186" t="str">
         <f>'AVG target price'!B9</f>
@@ -14156,14 +14156,14 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>0.04</v>
+        <v>0.52</v>
       </c>
       <c r="E8" s="187" t="s">
         <v>274</v>
       </c>
       <c r="F8" s="194">
         <f ca="1">Statement!AC157</f>
-        <v>3.2656302049129865E-2</v>
+        <v>3.5106433842626662E-2</v>
       </c>
       <c r="H8" s="186" t="str">
         <f>'AVG target price'!B11</f>
@@ -14171,7 +14171,7 @@
       </c>
       <c r="I8" s="215">
         <f ca="1">'AVG target price'!C11</f>
-        <v>6.5263246498749969E-2</v>
+        <v>0.14518764653533492</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -14180,14 +14180,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>-2.7452000000000001E-2</v>
+        <v>-1.0196E-2</v>
       </c>
       <c r="E9" s="187" t="s">
         <v>297</v>
       </c>
       <c r="F9" s="194">
         <f ca="1">Statement!AC158</f>
-        <v>2.0332752267480887E-2</v>
+        <v>2.1858274744119555E-2</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -14196,14 +14196,14 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>2.5900000000000001E-4</v>
+        <v>3.6189999999999998E-3</v>
       </c>
       <c r="E10" s="187" t="s">
         <v>302</v>
       </c>
       <c r="F10" s="194">
         <f ca="1">Statement!AC160</f>
-        <v>8.9904935983133698E-3</v>
+        <v>9.665030910324909E-3</v>
       </c>
       <c r="H10" s="186" t="s">
         <v>429</v>
@@ -14251,7 +14251,7 @@
       </c>
       <c r="C13" s="211" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>1.0437000000000001</v>
+        <v>1.0487</v>
       </c>
       <c r="E13" s="187" t="s">
         <v>104</v>
@@ -14267,7 +14267,7 @@
       </c>
       <c r="C14" s="212" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>1353949</v>
+        <v>1311929</v>
       </c>
       <c r="E14" s="188" t="s">
         <v>105</v>
@@ -14283,7 +14283,7 @@
       </c>
       <c r="F15" s="194">
         <f ca="1">Statement!AC172</f>
-        <v>0.1829743634776258</v>
+        <v>0.1967025346795245</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -14296,10 +14296,10 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="258" t="s">
+      <c r="B17" s="259" t="s">
         <v>90</v>
       </c>
-      <c r="C17" s="258"/>
+      <c r="C17" s="259"/>
       <c r="E17" s="186" t="s">
         <v>305</v>
       </c>
@@ -14372,14 +14372,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="258" t="s">
+      <c r="B25" s="259" t="s">
         <v>107</v>
       </c>
-      <c r="C25" s="258"/>
-      <c r="E25" s="256" t="s">
+      <c r="C25" s="259"/>
+      <c r="E25" s="257" t="s">
         <v>351</v>
       </c>
-      <c r="F25" s="257"/>
+      <c r="F25" s="258"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="186" t="s">
@@ -14393,7 +14393,7 @@
       </c>
       <c r="F26" s="221" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>47.62</v>
+        <v>47.84</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -14408,7 +14408,7 @@
       </c>
       <c r="F27" s="222">
         <f ca="1">F26/1000</f>
-        <v>4.7619999999999996E-2</v>
+        <v>4.7840000000000001E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -14428,15 +14428,15 @@
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="259" t="s">
+      <c r="B33" s="256" t="s">
         <v>346</v>
       </c>
-      <c r="C33" s="259"/>
-      <c r="D33" s="259"/>
-      <c r="E33" s="259"/>
-      <c r="F33" s="259"/>
-      <c r="G33" s="259"/>
-      <c r="H33" s="259"/>
+      <c r="C33" s="256"/>
+      <c r="D33" s="256"/>
+      <c r="E33" s="256"/>
+      <c r="F33" s="256"/>
+      <c r="G33" s="256"/>
+      <c r="H33" s="256"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
@@ -14455,24 +14455,24 @@
       </c>
     </row>
     <row r="39" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="259"/>
-      <c r="C39" s="259"/>
-      <c r="D39" s="259"/>
-      <c r="E39" s="259"/>
-      <c r="F39" s="259"/>
-      <c r="G39" s="259"/>
-      <c r="H39" s="259"/>
+      <c r="B39" s="256"/>
+      <c r="C39" s="256"/>
+      <c r="D39" s="256"/>
+      <c r="E39" s="256"/>
+      <c r="F39" s="256"/>
+      <c r="G39" s="256"/>
+      <c r="H39" s="256"/>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B42" s="259" t="s">
+      <c r="B42" s="256" t="s">
         <v>349</v>
       </c>
-      <c r="C42" s="259"/>
-      <c r="D42" s="259"/>
-      <c r="E42" s="259"/>
-      <c r="F42" s="259"/>
-      <c r="G42" s="259"/>
-      <c r="H42" s="259"/>
+      <c r="C42" s="256"/>
+      <c r="D42" s="256"/>
+      <c r="E42" s="256"/>
+      <c r="F42" s="256"/>
+      <c r="G42" s="256"/>
+      <c r="H42" s="256"/>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="41" t="s">
@@ -14511,24 +14511,24 @@
       </c>
     </row>
     <row r="50" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B50" s="259"/>
-      <c r="C50" s="259"/>
-      <c r="D50" s="259"/>
-      <c r="E50" s="259"/>
-      <c r="F50" s="259"/>
-      <c r="G50" s="259"/>
-      <c r="H50" s="259"/>
+      <c r="B50" s="256"/>
+      <c r="C50" s="256"/>
+      <c r="D50" s="256"/>
+      <c r="E50" s="256"/>
+      <c r="F50" s="256"/>
+      <c r="G50" s="256"/>
+      <c r="H50" s="256"/>
     </row>
     <row r="53" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B53" s="259" t="s">
+      <c r="B53" s="256" t="s">
         <v>109</v>
       </c>
-      <c r="C53" s="259"/>
-      <c r="D53" s="259"/>
-      <c r="E53" s="259"/>
-      <c r="F53" s="259"/>
-      <c r="G53" s="259"/>
-      <c r="H53" s="259"/>
+      <c r="C53" s="256"/>
+      <c r="D53" s="256"/>
+      <c r="E53" s="256"/>
+      <c r="F53" s="256"/>
+      <c r="G53" s="256"/>
+      <c r="H53" s="256"/>
     </row>
     <row r="58" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B58" s="41" t="s">
@@ -14599,28 +14599,28 @@
       </c>
     </row>
     <row r="66" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B66" s="259"/>
-      <c r="C66" s="259"/>
-      <c r="D66" s="259"/>
-      <c r="E66" s="259"/>
-      <c r="F66" s="259"/>
-      <c r="G66" s="259"/>
-      <c r="H66" s="259"/>
+      <c r="B66" s="256"/>
+      <c r="C66" s="256"/>
+      <c r="D66" s="256"/>
+      <c r="E66" s="256"/>
+      <c r="F66" s="256"/>
+      <c r="G66" s="256"/>
+      <c r="H66" s="256"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="E25:F25"/>
     <mergeCell ref="B53:H53"/>
     <mergeCell ref="B66:H66"/>
     <mergeCell ref="B33:H33"/>
     <mergeCell ref="B39:H39"/>
     <mergeCell ref="B42:H42"/>
     <mergeCell ref="B50:H50"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="E25:F25"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C10">
     <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
@@ -14690,36 +14690,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="259" t="s">
+      <c r="C2" s="256" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="259"/>
-      <c r="E2" s="259"/>
-      <c r="F2" s="259"/>
-      <c r="G2" s="265"/>
-      <c r="H2" s="266" t="s">
+      <c r="D2" s="256"/>
+      <c r="E2" s="256"/>
+      <c r="F2" s="256"/>
+      <c r="G2" s="268"/>
+      <c r="H2" s="269" t="s">
         <v>114</v>
       </c>
-      <c r="I2" s="259"/>
-      <c r="J2" s="259"/>
-      <c r="K2" s="259"/>
-      <c r="L2" s="259"/>
+      <c r="I2" s="256"/>
+      <c r="J2" s="256"/>
+      <c r="K2" s="256"/>
+      <c r="L2" s="256"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="259" t="s">
+      <c r="S2" s="256" t="s">
         <v>113</v>
       </c>
-      <c r="T2" s="259"/>
-      <c r="U2" s="259"/>
-      <c r="V2" s="259"/>
-      <c r="W2" s="259"/>
-      <c r="X2" s="259"/>
-      <c r="Y2" s="259"/>
-      <c r="Z2" s="259"/>
-      <c r="AA2" s="259" t="s">
+      <c r="T2" s="256"/>
+      <c r="U2" s="256"/>
+      <c r="V2" s="256"/>
+      <c r="W2" s="256"/>
+      <c r="X2" s="256"/>
+      <c r="Y2" s="256"/>
+      <c r="Z2" s="256"/>
+      <c r="AA2" s="256" t="s">
         <v>114</v>
       </c>
-      <c r="AB2" s="259"/>
-      <c r="AC2" s="259"/>
+      <c r="AB2" s="256"/>
+      <c r="AC2" s="256"/>
       <c r="AE2" s="86" t="s">
         <v>85</v>
       </c>
@@ -14730,32 +14730,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="267" t="s">
+      <c r="C4" s="265" t="s">
         <v>116</v>
       </c>
-      <c r="D4" s="267"/>
-      <c r="E4" s="267"/>
-      <c r="F4" s="267"/>
-      <c r="G4" s="267"/>
-      <c r="H4" s="267"/>
-      <c r="I4" s="267"/>
-      <c r="J4" s="267"/>
-      <c r="K4" s="267"/>
-      <c r="L4" s="267"/>
+      <c r="D4" s="265"/>
+      <c r="E4" s="265"/>
+      <c r="F4" s="265"/>
+      <c r="G4" s="265"/>
+      <c r="H4" s="265"/>
+      <c r="I4" s="265"/>
+      <c r="J4" s="265"/>
+      <c r="K4" s="265"/>
+      <c r="L4" s="265"/>
       <c r="O4" s="5"/>
-      <c r="S4" s="268" t="s">
+      <c r="S4" s="266" t="s">
         <v>116</v>
       </c>
-      <c r="T4" s="269"/>
-      <c r="U4" s="269"/>
-      <c r="V4" s="269"/>
-      <c r="W4" s="269"/>
-      <c r="X4" s="269"/>
-      <c r="Y4" s="269"/>
-      <c r="Z4" s="269"/>
-      <c r="AA4" s="269"/>
-      <c r="AB4" s="269"/>
-      <c r="AC4" s="269"/>
+      <c r="T4" s="267"/>
+      <c r="U4" s="267"/>
+      <c r="V4" s="267"/>
+      <c r="W4" s="267"/>
+      <c r="X4" s="267"/>
+      <c r="Y4" s="267"/>
+      <c r="Z4" s="267"/>
+      <c r="AA4" s="267"/>
+      <c r="AB4" s="267"/>
+      <c r="AC4" s="267"/>
       <c r="AE4" s="88"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -15443,33 +15443,33 @@
       <c r="Q12" s="92"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="267" t="s">
+      <c r="C13" s="265" t="s">
         <v>122</v>
       </c>
-      <c r="D13" s="267"/>
-      <c r="E13" s="267"/>
-      <c r="F13" s="267"/>
-      <c r="G13" s="267"/>
-      <c r="H13" s="267"/>
-      <c r="I13" s="267"/>
-      <c r="J13" s="267"/>
-      <c r="K13" s="267"/>
-      <c r="L13" s="267"/>
+      <c r="D13" s="265"/>
+      <c r="E13" s="265"/>
+      <c r="F13" s="265"/>
+      <c r="G13" s="265"/>
+      <c r="H13" s="265"/>
+      <c r="I13" s="265"/>
+      <c r="J13" s="265"/>
+      <c r="K13" s="265"/>
+      <c r="L13" s="265"/>
       <c r="O13" s="5"/>
       <c r="Q13" s="92"/>
-      <c r="S13" s="268" t="s">
+      <c r="S13" s="266" t="s">
         <v>122</v>
       </c>
-      <c r="T13" s="269"/>
-      <c r="U13" s="269"/>
-      <c r="V13" s="269"/>
-      <c r="W13" s="269"/>
-      <c r="X13" s="269"/>
-      <c r="Y13" s="269"/>
-      <c r="Z13" s="269"/>
-      <c r="AA13" s="269"/>
-      <c r="AB13" s="269"/>
-      <c r="AC13" s="269"/>
+      <c r="T13" s="267"/>
+      <c r="U13" s="267"/>
+      <c r="V13" s="267"/>
+      <c r="W13" s="267"/>
+      <c r="X13" s="267"/>
+      <c r="Y13" s="267"/>
+      <c r="Z13" s="267"/>
+      <c r="AA13" s="267"/>
+      <c r="AB13" s="267"/>
+      <c r="AC13" s="267"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B14" s="16" t="s">
@@ -16078,33 +16078,33 @@
       <c r="Q22" s="92"/>
     </row>
     <row r="23" spans="2:31" x14ac:dyDescent="0.2">
-      <c r="C23" s="267" t="s">
+      <c r="C23" s="265" t="s">
         <v>124</v>
       </c>
-      <c r="D23" s="267"/>
-      <c r="E23" s="267"/>
-      <c r="F23" s="267"/>
-      <c r="G23" s="267"/>
-      <c r="H23" s="267"/>
-      <c r="I23" s="267"/>
-      <c r="J23" s="267"/>
-      <c r="K23" s="267"/>
-      <c r="L23" s="267"/>
+      <c r="D23" s="265"/>
+      <c r="E23" s="265"/>
+      <c r="F23" s="265"/>
+      <c r="G23" s="265"/>
+      <c r="H23" s="265"/>
+      <c r="I23" s="265"/>
+      <c r="J23" s="265"/>
+      <c r="K23" s="265"/>
+      <c r="L23" s="265"/>
       <c r="O23" s="5"/>
       <c r="Q23" s="92"/>
-      <c r="S23" s="268" t="s">
+      <c r="S23" s="266" t="s">
         <v>124</v>
       </c>
-      <c r="T23" s="269"/>
-      <c r="U23" s="269"/>
-      <c r="V23" s="269"/>
-      <c r="W23" s="269"/>
-      <c r="X23" s="269"/>
-      <c r="Y23" s="269"/>
-      <c r="Z23" s="269"/>
-      <c r="AA23" s="269"/>
-      <c r="AB23" s="269"/>
-      <c r="AC23" s="269"/>
+      <c r="T23" s="267"/>
+      <c r="U23" s="267"/>
+      <c r="V23" s="267"/>
+      <c r="W23" s="267"/>
+      <c r="X23" s="267"/>
+      <c r="Y23" s="267"/>
+      <c r="Z23" s="267"/>
+      <c r="AA23" s="267"/>
+      <c r="AB23" s="267"/>
+      <c r="AC23" s="267"/>
       <c r="AE23" s="88" t="str">
         <f>AE2</f>
         <v>TTM/YTD</v>
@@ -17423,32 +17423,32 @@
       <c r="O39" s="5"/>
     </row>
     <row r="40" spans="2:31" x14ac:dyDescent="0.2">
-      <c r="C40" s="267" t="s">
+      <c r="C40" s="265" t="s">
         <v>126</v>
       </c>
-      <c r="D40" s="267"/>
-      <c r="E40" s="267"/>
-      <c r="F40" s="267"/>
-      <c r="G40" s="267"/>
-      <c r="H40" s="267"/>
-      <c r="I40" s="267"/>
-      <c r="J40" s="267"/>
-      <c r="K40" s="267"/>
-      <c r="L40" s="267"/>
+      <c r="D40" s="265"/>
+      <c r="E40" s="265"/>
+      <c r="F40" s="265"/>
+      <c r="G40" s="265"/>
+      <c r="H40" s="265"/>
+      <c r="I40" s="265"/>
+      <c r="J40" s="265"/>
+      <c r="K40" s="265"/>
+      <c r="L40" s="265"/>
       <c r="O40" s="5"/>
-      <c r="S40" s="268" t="s">
+      <c r="S40" s="266" t="s">
         <v>126</v>
       </c>
-      <c r="T40" s="269"/>
-      <c r="U40" s="269"/>
-      <c r="V40" s="269"/>
-      <c r="W40" s="269"/>
-      <c r="X40" s="269"/>
-      <c r="Y40" s="269"/>
-      <c r="Z40" s="269"/>
-      <c r="AA40" s="269"/>
-      <c r="AB40" s="269"/>
-      <c r="AC40" s="269"/>
+      <c r="T40" s="267"/>
+      <c r="U40" s="267"/>
+      <c r="V40" s="267"/>
+      <c r="W40" s="267"/>
+      <c r="X40" s="267"/>
+      <c r="Y40" s="267"/>
+      <c r="Z40" s="267"/>
+      <c r="AA40" s="267"/>
+      <c r="AB40" s="267"/>
+      <c r="AC40" s="267"/>
     </row>
     <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -18015,18 +18015,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="S2:Z2"/>
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="S4:AC4"/>
     <mergeCell ref="C13:L13"/>
     <mergeCell ref="S13:AC13"/>
     <mergeCell ref="C23:L23"/>
     <mergeCell ref="S23:AC23"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="S40:AC40"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="S2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="S4:AC4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -18060,35 +18060,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="259" t="s">
+      <c r="C2" s="256" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="259"/>
-      <c r="E2" s="259"/>
-      <c r="F2" s="259"/>
-      <c r="G2" s="265"/>
-      <c r="H2" s="266" t="s">
+      <c r="D2" s="256"/>
+      <c r="E2" s="256"/>
+      <c r="F2" s="256"/>
+      <c r="G2" s="268"/>
+      <c r="H2" s="269" t="s">
         <v>114</v>
       </c>
-      <c r="I2" s="259"/>
-      <c r="J2" s="259"/>
-      <c r="K2" s="259"/>
-      <c r="L2" s="259"/>
-      <c r="P2" s="259" t="s">
+      <c r="I2" s="256"/>
+      <c r="J2" s="256"/>
+      <c r="K2" s="256"/>
+      <c r="L2" s="256"/>
+      <c r="P2" s="256" t="s">
         <v>113</v>
       </c>
-      <c r="Q2" s="259"/>
-      <c r="R2" s="259"/>
-      <c r="S2" s="259"/>
-      <c r="T2" s="259"/>
-      <c r="U2" s="259"/>
-      <c r="V2" s="259"/>
-      <c r="W2" s="259"/>
-      <c r="X2" s="259" t="s">
+      <c r="Q2" s="256"/>
+      <c r="R2" s="256"/>
+      <c r="S2" s="256"/>
+      <c r="T2" s="256"/>
+      <c r="U2" s="256"/>
+      <c r="V2" s="256"/>
+      <c r="W2" s="256"/>
+      <c r="X2" s="256" t="s">
         <v>114</v>
       </c>
-      <c r="Y2" s="259"/>
-      <c r="Z2" s="259"/>
+      <c r="Y2" s="256"/>
+      <c r="Z2" s="256"/>
       <c r="AB2" s="86" t="s">
         <v>115</v>
       </c>
@@ -18097,31 +18097,31 @@
     <row r="4" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="267" t="s">
+      <c r="C4" s="265" t="s">
         <v>116</v>
       </c>
-      <c r="D4" s="267"/>
-      <c r="E4" s="267"/>
-      <c r="F4" s="267"/>
-      <c r="G4" s="267"/>
-      <c r="H4" s="267"/>
-      <c r="I4" s="267"/>
-      <c r="J4" s="267"/>
-      <c r="K4" s="267"/>
-      <c r="L4" s="267"/>
-      <c r="P4" s="269" t="s">
+      <c r="D4" s="265"/>
+      <c r="E4" s="265"/>
+      <c r="F4" s="265"/>
+      <c r="G4" s="265"/>
+      <c r="H4" s="265"/>
+      <c r="I4" s="265"/>
+      <c r="J4" s="265"/>
+      <c r="K4" s="265"/>
+      <c r="L4" s="265"/>
+      <c r="P4" s="267" t="s">
         <v>116</v>
       </c>
-      <c r="Q4" s="269"/>
-      <c r="R4" s="269"/>
-      <c r="S4" s="269"/>
-      <c r="T4" s="269"/>
-      <c r="U4" s="269"/>
-      <c r="V4" s="269"/>
-      <c r="W4" s="269"/>
-      <c r="X4" s="269"/>
-      <c r="Y4" s="269"/>
-      <c r="Z4" s="269"/>
+      <c r="Q4" s="267"/>
+      <c r="R4" s="267"/>
+      <c r="S4" s="267"/>
+      <c r="T4" s="267"/>
+      <c r="U4" s="267"/>
+      <c r="V4" s="267"/>
+      <c r="W4" s="267"/>
+      <c r="X4" s="267"/>
+      <c r="Y4" s="267"/>
+      <c r="Z4" s="267"/>
       <c r="AB4" s="88"/>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
@@ -18316,32 +18316,32 @@
       <c r="N8" s="92"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C9" s="267" t="s">
+      <c r="C9" s="265" t="s">
         <v>129</v>
       </c>
-      <c r="D9" s="267"/>
-      <c r="E9" s="267"/>
-      <c r="F9" s="267"/>
-      <c r="G9" s="267"/>
-      <c r="H9" s="267"/>
-      <c r="I9" s="267"/>
-      <c r="J9" s="267"/>
-      <c r="K9" s="267"/>
-      <c r="L9" s="267"/>
+      <c r="D9" s="265"/>
+      <c r="E9" s="265"/>
+      <c r="F9" s="265"/>
+      <c r="G9" s="265"/>
+      <c r="H9" s="265"/>
+      <c r="I9" s="265"/>
+      <c r="J9" s="265"/>
+      <c r="K9" s="265"/>
+      <c r="L9" s="265"/>
       <c r="N9" s="92"/>
-      <c r="P9" s="269" t="s">
+      <c r="P9" s="267" t="s">
         <v>130</v>
       </c>
-      <c r="Q9" s="269"/>
-      <c r="R9" s="269"/>
-      <c r="S9" s="269"/>
-      <c r="T9" s="269"/>
-      <c r="U9" s="269"/>
-      <c r="V9" s="269"/>
-      <c r="W9" s="269"/>
-      <c r="X9" s="269"/>
-      <c r="Y9" s="269"/>
-      <c r="Z9" s="269"/>
+      <c r="Q9" s="267"/>
+      <c r="R9" s="267"/>
+      <c r="S9" s="267"/>
+      <c r="T9" s="267"/>
+      <c r="U9" s="267"/>
+      <c r="V9" s="267"/>
+      <c r="W9" s="267"/>
+      <c r="X9" s="267"/>
+      <c r="Y9" s="267"/>
+      <c r="Z9" s="267"/>
       <c r="AB9" s="88">
         <f>AB4</f>
         <v>0</v>
@@ -18911,31 +18911,31 @@
       </c>
     </row>
     <row r="18" spans="2:26" x14ac:dyDescent="0.2">
-      <c r="C18" s="267" t="s">
+      <c r="C18" s="265" t="s">
         <v>132</v>
       </c>
-      <c r="D18" s="267"/>
-      <c r="E18" s="267"/>
-      <c r="F18" s="267"/>
-      <c r="G18" s="267"/>
-      <c r="H18" s="267"/>
-      <c r="I18" s="267"/>
-      <c r="J18" s="267"/>
-      <c r="K18" s="267"/>
-      <c r="L18" s="267"/>
-      <c r="P18" s="269" t="s">
+      <c r="D18" s="265"/>
+      <c r="E18" s="265"/>
+      <c r="F18" s="265"/>
+      <c r="G18" s="265"/>
+      <c r="H18" s="265"/>
+      <c r="I18" s="265"/>
+      <c r="J18" s="265"/>
+      <c r="K18" s="265"/>
+      <c r="L18" s="265"/>
+      <c r="P18" s="267" t="s">
         <v>132</v>
       </c>
-      <c r="Q18" s="269"/>
-      <c r="R18" s="269"/>
-      <c r="S18" s="269"/>
-      <c r="T18" s="269"/>
-      <c r="U18" s="269"/>
-      <c r="V18" s="269"/>
-      <c r="W18" s="269"/>
-      <c r="X18" s="269"/>
-      <c r="Y18" s="269"/>
-      <c r="Z18" s="269"/>
+      <c r="Q18" s="267"/>
+      <c r="R18" s="267"/>
+      <c r="S18" s="267"/>
+      <c r="T18" s="267"/>
+      <c r="U18" s="267"/>
+      <c r="V18" s="267"/>
+      <c r="W18" s="267"/>
+      <c r="X18" s="267"/>
+      <c r="Y18" s="267"/>
+      <c r="Z18" s="267"/>
     </row>
     <row r="19" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -19495,20 +19495,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="259" t="s">
+      <c r="C3" s="256" t="s">
         <v>113</v>
       </c>
-      <c r="D3" s="259"/>
-      <c r="E3" s="259"/>
-      <c r="F3" s="259"/>
-      <c r="G3" s="265"/>
-      <c r="H3" s="266" t="s">
+      <c r="D3" s="256"/>
+      <c r="E3" s="256"/>
+      <c r="F3" s="256"/>
+      <c r="G3" s="268"/>
+      <c r="H3" s="269" t="s">
         <v>114</v>
       </c>
-      <c r="I3" s="259"/>
-      <c r="J3" s="259"/>
-      <c r="K3" s="259"/>
-      <c r="L3" s="259"/>
+      <c r="I3" s="256"/>
+      <c r="J3" s="256"/>
+      <c r="K3" s="256"/>
+      <c r="L3" s="256"/>
       <c r="P3" s="270"/>
       <c r="Q3" s="270"/>
       <c r="R3" s="270"/>
@@ -19526,18 +19526,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="87"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="267" t="s">
+      <c r="C5" s="265" t="s">
         <v>116</v>
       </c>
-      <c r="D5" s="267"/>
-      <c r="E5" s="267"/>
-      <c r="F5" s="267"/>
-      <c r="G5" s="267"/>
-      <c r="H5" s="267"/>
-      <c r="I5" s="267"/>
-      <c r="J5" s="267"/>
-      <c r="K5" s="267"/>
-      <c r="L5" s="267"/>
+      <c r="D5" s="265"/>
+      <c r="E5" s="265"/>
+      <c r="F5" s="265"/>
+      <c r="G5" s="265"/>
+      <c r="H5" s="265"/>
+      <c r="I5" s="265"/>
+      <c r="J5" s="265"/>
+      <c r="K5" s="265"/>
+      <c r="L5" s="265"/>
       <c r="P5" s="270"/>
       <c r="Q5" s="270"/>
       <c r="R5" s="270"/>
@@ -19734,18 +19734,18 @@
       <c r="N10" s="92"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="267" t="s">
+      <c r="C11" s="265" t="s">
         <v>136</v>
       </c>
-      <c r="D11" s="267"/>
-      <c r="E11" s="267"/>
-      <c r="F11" s="267"/>
-      <c r="G11" s="267"/>
-      <c r="H11" s="267"/>
-      <c r="I11" s="267"/>
-      <c r="J11" s="267"/>
-      <c r="K11" s="267"/>
-      <c r="L11" s="267"/>
+      <c r="D11" s="265"/>
+      <c r="E11" s="265"/>
+      <c r="F11" s="265"/>
+      <c r="G11" s="265"/>
+      <c r="H11" s="265"/>
+      <c r="I11" s="265"/>
+      <c r="J11" s="265"/>
+      <c r="K11" s="265"/>
+      <c r="L11" s="265"/>
       <c r="N11" s="92"/>
       <c r="P11" s="270"/>
       <c r="Q11" s="270"/>
@@ -19999,18 +19999,18 @@
       <c r="D16" s="24"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="267" t="s">
+      <c r="C18" s="265" t="s">
         <v>141</v>
       </c>
-      <c r="D18" s="267"/>
-      <c r="E18" s="267"/>
-      <c r="F18" s="267"/>
-      <c r="G18" s="267"/>
-      <c r="H18" s="267"/>
-      <c r="I18" s="267"/>
-      <c r="J18" s="267"/>
-      <c r="K18" s="267"/>
-      <c r="L18" s="267"/>
+      <c r="D18" s="265"/>
+      <c r="E18" s="265"/>
+      <c r="F18" s="265"/>
+      <c r="G18" s="265"/>
+      <c r="H18" s="265"/>
+      <c r="I18" s="265"/>
+      <c r="J18" s="265"/>
+      <c r="K18" s="265"/>
+      <c r="L18" s="265"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -20228,18 +20228,18 @@
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="111"/>
-      <c r="C26" s="267" t="s">
+      <c r="C26" s="265" t="s">
         <v>147</v>
       </c>
-      <c r="D26" s="267"/>
-      <c r="E26" s="267"/>
-      <c r="F26" s="267"/>
-      <c r="G26" s="267"/>
-      <c r="H26" s="267"/>
-      <c r="I26" s="267"/>
-      <c r="J26" s="267"/>
-      <c r="K26" s="267"/>
-      <c r="L26" s="267"/>
+      <c r="D26" s="265"/>
+      <c r="E26" s="265"/>
+      <c r="F26" s="265"/>
+      <c r="G26" s="265"/>
+      <c r="H26" s="265"/>
+      <c r="I26" s="265"/>
+      <c r="J26" s="265"/>
+      <c r="K26" s="265"/>
+      <c r="L26" s="265"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="16" t="s">
@@ -20431,18 +20431,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="111"/>
-      <c r="C33" s="267" t="s">
+      <c r="C33" s="265" t="s">
         <v>151</v>
       </c>
-      <c r="D33" s="267"/>
-      <c r="E33" s="267"/>
-      <c r="F33" s="267"/>
-      <c r="G33" s="267"/>
-      <c r="H33" s="267"/>
-      <c r="I33" s="267"/>
-      <c r="J33" s="267"/>
-      <c r="K33" s="267"/>
-      <c r="L33" s="267"/>
+      <c r="D33" s="265"/>
+      <c r="E33" s="265"/>
+      <c r="F33" s="265"/>
+      <c r="G33" s="265"/>
+      <c r="H33" s="265"/>
+      <c r="I33" s="265"/>
+      <c r="J33" s="265"/>
+      <c r="K33" s="265"/>
+      <c r="L33" s="265"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
@@ -20626,18 +20626,18 @@
       <c r="C39" s="127"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="267" t="s">
+      <c r="C40" s="265" t="s">
         <v>154</v>
       </c>
-      <c r="D40" s="267"/>
-      <c r="E40" s="267"/>
-      <c r="F40" s="267"/>
-      <c r="G40" s="267"/>
-      <c r="H40" s="267"/>
-      <c r="I40" s="267"/>
-      <c r="J40" s="267"/>
-      <c r="K40" s="267"/>
-      <c r="L40" s="267"/>
+      <c r="D40" s="265"/>
+      <c r="E40" s="265"/>
+      <c r="F40" s="265"/>
+      <c r="G40" s="265"/>
+      <c r="H40" s="265"/>
+      <c r="I40" s="265"/>
+      <c r="J40" s="265"/>
+      <c r="K40" s="265"/>
+      <c r="L40" s="265"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -20901,12 +20901,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -20914,6 +20908,12 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -20951,20 +20951,20 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="259" t="s">
+      <c r="C2" s="256" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="259"/>
-      <c r="E2" s="259"/>
-      <c r="F2" s="259"/>
-      <c r="G2" s="265"/>
-      <c r="H2" s="266" t="s">
+      <c r="D2" s="256"/>
+      <c r="E2" s="256"/>
+      <c r="F2" s="256"/>
+      <c r="G2" s="268"/>
+      <c r="H2" s="269" t="s">
         <v>114</v>
       </c>
-      <c r="I2" s="259"/>
-      <c r="J2" s="259"/>
-      <c r="K2" s="259"/>
-      <c r="L2" s="259"/>
+      <c r="I2" s="256"/>
+      <c r="J2" s="256"/>
+      <c r="K2" s="256"/>
+      <c r="L2" s="256"/>
       <c r="S2" s="270"/>
       <c r="T2" s="270"/>
       <c r="U2" s="270"/>
@@ -20982,18 +20982,18 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="267" t="s">
+      <c r="C4" s="265" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="267"/>
-      <c r="E4" s="267"/>
-      <c r="F4" s="267"/>
-      <c r="G4" s="267"/>
-      <c r="H4" s="267"/>
-      <c r="I4" s="267"/>
-      <c r="J4" s="267"/>
-      <c r="K4" s="267"/>
-      <c r="L4" s="267"/>
+      <c r="D4" s="265"/>
+      <c r="E4" s="265"/>
+      <c r="F4" s="265"/>
+      <c r="G4" s="265"/>
+      <c r="H4" s="265"/>
+      <c r="I4" s="265"/>
+      <c r="J4" s="265"/>
+      <c r="K4" s="265"/>
+      <c r="L4" s="265"/>
       <c r="S4" s="270"/>
       <c r="T4" s="270"/>
       <c r="U4" s="270"/>
@@ -21367,18 +21367,18 @@
       <c r="AE10" s="64"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="267" t="s">
+      <c r="C13" s="265" t="s">
         <v>162</v>
       </c>
-      <c r="D13" s="267"/>
-      <c r="E13" s="267"/>
-      <c r="F13" s="267"/>
-      <c r="G13" s="267"/>
-      <c r="H13" s="267"/>
-      <c r="I13" s="267"/>
-      <c r="J13" s="267"/>
-      <c r="K13" s="267"/>
-      <c r="L13" s="267"/>
+      <c r="D13" s="265"/>
+      <c r="E13" s="265"/>
+      <c r="F13" s="265"/>
+      <c r="G13" s="265"/>
+      <c r="H13" s="265"/>
+      <c r="I13" s="265"/>
+      <c r="J13" s="265"/>
+      <c r="K13" s="265"/>
+      <c r="L13" s="265"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="12">
@@ -21471,18 +21471,18 @@
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C18" s="267" t="s">
+      <c r="C18" s="265" t="s">
         <v>163</v>
       </c>
-      <c r="D18" s="267"/>
-      <c r="E18" s="267"/>
-      <c r="F18" s="267"/>
-      <c r="G18" s="267"/>
-      <c r="H18" s="267"/>
-      <c r="I18" s="267"/>
-      <c r="J18" s="267"/>
-      <c r="K18" s="267"/>
-      <c r="L18" s="267"/>
+      <c r="D18" s="265"/>
+      <c r="E18" s="265"/>
+      <c r="F18" s="265"/>
+      <c r="G18" s="265"/>
+      <c r="H18" s="265"/>
+      <c r="I18" s="265"/>
+      <c r="J18" s="265"/>
+      <c r="K18" s="265"/>
+      <c r="L18" s="265"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -21674,18 +21674,18 @@
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C25" s="267" t="s">
+      <c r="C25" s="265" t="s">
         <v>271</v>
       </c>
-      <c r="D25" s="267"/>
-      <c r="E25" s="267"/>
-      <c r="F25" s="267"/>
-      <c r="G25" s="267"/>
-      <c r="H25" s="267"/>
-      <c r="I25" s="267"/>
-      <c r="J25" s="267"/>
-      <c r="K25" s="267"/>
-      <c r="L25" s="267"/>
+      <c r="D25" s="265"/>
+      <c r="E25" s="265"/>
+      <c r="F25" s="265"/>
+      <c r="G25" s="265"/>
+      <c r="H25" s="265"/>
+      <c r="I25" s="265"/>
+      <c r="J25" s="265"/>
+      <c r="K25" s="265"/>
+      <c r="L25" s="265"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B26" s="16" t="s">
@@ -21823,18 +21823,18 @@
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C31" s="267" t="s">
+      <c r="C31" s="265" t="s">
         <v>78</v>
       </c>
-      <c r="D31" s="267"/>
-      <c r="E31" s="267"/>
-      <c r="F31" s="267"/>
-      <c r="G31" s="267"/>
-      <c r="H31" s="267"/>
-      <c r="I31" s="267"/>
-      <c r="J31" s="267"/>
-      <c r="K31" s="267"/>
-      <c r="L31" s="267"/>
+      <c r="D31" s="265"/>
+      <c r="E31" s="265"/>
+      <c r="F31" s="265"/>
+      <c r="G31" s="265"/>
+      <c r="H31" s="265"/>
+      <c r="I31" s="265"/>
+      <c r="J31" s="265"/>
+      <c r="K31" s="265"/>
+      <c r="L31" s="265"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="16" t="s">
@@ -21973,16 +21973,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C31:L31"/>
+    <mergeCell ref="C25:L25"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="S2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
     <mergeCell ref="C13:L13"/>
     <mergeCell ref="C18:L18"/>
-    <mergeCell ref="C31:L31"/>
-    <mergeCell ref="C25:L25"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="S2:Z2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -22045,10 +22045,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="259" t="s">
+      <c r="B4" s="256" t="s">
         <v>170</v>
       </c>
-      <c r="C4" s="259"/>
+      <c r="C4" s="256"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -22065,7 +22065,7 @@
       </c>
       <c r="C6" s="135">
         <f ca="1">Overview!C5</f>
-        <v>154.46</v>
+        <v>143.68</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22074,7 +22074,7 @@
       </c>
       <c r="C7" s="136">
         <f ca="1">C5*C6</f>
-        <v>7741844.1200000001</v>
+        <v>7201528.96</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22092,7 +22092,7 @@
       </c>
       <c r="C9" s="137">
         <f ca="1">Overview!F27</f>
-        <v>4.7619999999999996E-2</v>
+        <v>4.7840000000000001E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22101,7 +22101,7 @@
       </c>
       <c r="C10" s="135">
         <f ca="1">Overview!C13</f>
-        <v>1.0437000000000001</v>
+        <v>1.0487</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22110,7 +22110,7 @@
       </c>
       <c r="C11" s="137">
         <f>[1]Sheet1!$C$12</f>
-        <v>4.4999999999999998E-2</v>
+        <v>4.3999999999999997E-2</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22133,10 +22133,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="259" t="s">
+      <c r="B15" s="256" t="s">
         <v>177</v>
       </c>
-      <c r="C15" s="259"/>
+      <c r="C15" s="256"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -22171,7 +22171,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>9.458649999999999E-2</v>
+        <v>9.3982800000000005E-2</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22180,7 +22180,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>9.458649999999999E-2</v>
+        <v>9.3982800000000005E-2</v>
       </c>
     </row>
   </sheetData>
@@ -22225,20 +22225,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="259" t="s">
+      <c r="C3" s="256" t="s">
         <v>113</v>
       </c>
-      <c r="D3" s="259"/>
-      <c r="E3" s="259"/>
-      <c r="F3" s="259"/>
-      <c r="G3" s="265"/>
-      <c r="H3" s="266" t="s">
+      <c r="D3" s="256"/>
+      <c r="E3" s="256"/>
+      <c r="F3" s="256"/>
+      <c r="G3" s="268"/>
+      <c r="H3" s="269" t="s">
         <v>114</v>
       </c>
-      <c r="I3" s="259"/>
-      <c r="J3" s="259"/>
-      <c r="K3" s="259"/>
-      <c r="L3" s="259"/>
+      <c r="I3" s="256"/>
+      <c r="J3" s="256"/>
+      <c r="K3" s="256"/>
+      <c r="L3" s="256"/>
       <c r="P3" s="270"/>
       <c r="Q3" s="270"/>
       <c r="R3" s="270"/>
@@ -22256,18 +22256,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="87"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="267" t="s">
+      <c r="C5" s="265" t="s">
         <v>184</v>
       </c>
-      <c r="D5" s="267"/>
-      <c r="E5" s="267"/>
-      <c r="F5" s="267"/>
-      <c r="G5" s="267"/>
-      <c r="H5" s="267"/>
-      <c r="I5" s="267"/>
-      <c r="J5" s="267"/>
-      <c r="K5" s="267"/>
-      <c r="L5" s="267"/>
+      <c r="D5" s="265"/>
+      <c r="E5" s="265"/>
+      <c r="F5" s="265"/>
+      <c r="G5" s="265"/>
+      <c r="H5" s="265"/>
+      <c r="I5" s="265"/>
+      <c r="J5" s="265"/>
+      <c r="K5" s="265"/>
+      <c r="L5" s="265"/>
       <c r="P5" s="270"/>
       <c r="Q5" s="270"/>
       <c r="R5" s="270"/>
@@ -22524,10 +22524,10 @@
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="259" t="s">
+      <c r="B13" s="256" t="s">
         <v>188</v>
       </c>
-      <c r="C13" s="259"/>
+      <c r="C13" s="256"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -22547,10 +22547,10 @@
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="259" t="s">
+      <c r="B18" s="256" t="s">
         <v>190</v>
       </c>
-      <c r="C18" s="259"/>
+      <c r="C18" s="256"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -22664,37 +22664,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="259" t="s">
+      <c r="C2" s="256" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="259"/>
-      <c r="E2" s="259"/>
-      <c r="F2" s="259"/>
-      <c r="G2" s="265"/>
-      <c r="H2" s="266" t="s">
+      <c r="D2" s="256"/>
+      <c r="E2" s="256"/>
+      <c r="F2" s="256"/>
+      <c r="G2" s="268"/>
+      <c r="H2" s="269" t="s">
         <v>114</v>
       </c>
-      <c r="I2" s="259"/>
-      <c r="J2" s="259"/>
-      <c r="K2" s="259"/>
-      <c r="L2" s="259"/>
+      <c r="I2" s="256"/>
+      <c r="J2" s="256"/>
+      <c r="K2" s="256"/>
+      <c r="L2" s="256"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="267" t="s">
+      <c r="C4" s="265" t="s">
         <v>198</v>
       </c>
-      <c r="D4" s="267"/>
-      <c r="E4" s="267"/>
-      <c r="F4" s="267"/>
-      <c r="G4" s="267"/>
-      <c r="H4" s="267"/>
-      <c r="I4" s="267"/>
-      <c r="J4" s="267"/>
-      <c r="K4" s="267"/>
-      <c r="L4" s="267"/>
+      <c r="D4" s="265"/>
+      <c r="E4" s="265"/>
+      <c r="F4" s="265"/>
+      <c r="G4" s="265"/>
+      <c r="H4" s="265"/>
+      <c r="I4" s="265"/>
+      <c r="J4" s="265"/>
+      <c r="K4" s="265"/>
+      <c r="L4" s="265"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -22883,18 +22883,18 @@
       <c r="N9" s="92"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C10" s="267" t="s">
+      <c r="C10" s="265" t="s">
         <v>122</v>
       </c>
-      <c r="D10" s="267"/>
-      <c r="E10" s="267"/>
-      <c r="F10" s="267"/>
-      <c r="G10" s="267"/>
-      <c r="H10" s="267"/>
-      <c r="I10" s="267"/>
-      <c r="J10" s="267"/>
-      <c r="K10" s="267"/>
-      <c r="L10" s="267"/>
+      <c r="D10" s="265"/>
+      <c r="E10" s="265"/>
+      <c r="F10" s="265"/>
+      <c r="G10" s="265"/>
+      <c r="H10" s="265"/>
+      <c r="I10" s="265"/>
+      <c r="J10" s="265"/>
+      <c r="K10" s="265"/>
+      <c r="L10" s="265"/>
       <c r="N10" s="92"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -23088,18 +23088,18 @@
       <c r="N15" s="92"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C16" s="267" t="s">
+      <c r="C16" s="265" t="s">
         <v>200</v>
       </c>
-      <c r="D16" s="267"/>
-      <c r="E16" s="267"/>
-      <c r="F16" s="267"/>
-      <c r="G16" s="267"/>
-      <c r="H16" s="267"/>
-      <c r="I16" s="267"/>
-      <c r="J16" s="267"/>
-      <c r="K16" s="267"/>
-      <c r="L16" s="267"/>
+      <c r="D16" s="265"/>
+      <c r="E16" s="265"/>
+      <c r="F16" s="265"/>
+      <c r="G16" s="265"/>
+      <c r="H16" s="265"/>
+      <c r="I16" s="265"/>
+      <c r="J16" s="265"/>
+      <c r="K16" s="265"/>
+      <c r="L16" s="265"/>
       <c r="N16" s="92"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
@@ -23233,18 +23233,18 @@
       <c r="N20" s="92"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C21" s="267" t="s">
+      <c r="C21" s="265" t="s">
         <v>203</v>
       </c>
-      <c r="D21" s="267"/>
-      <c r="E21" s="267"/>
-      <c r="F21" s="267"/>
-      <c r="G21" s="267"/>
-      <c r="H21" s="267"/>
-      <c r="I21" s="267"/>
-      <c r="J21" s="267"/>
-      <c r="K21" s="267"/>
-      <c r="L21" s="267"/>
+      <c r="D21" s="265"/>
+      <c r="E21" s="265"/>
+      <c r="F21" s="265"/>
+      <c r="G21" s="265"/>
+      <c r="H21" s="265"/>
+      <c r="I21" s="265"/>
+      <c r="J21" s="265"/>
+      <c r="K21" s="265"/>
+      <c r="L21" s="265"/>
       <c r="N21" s="92"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
@@ -23328,18 +23328,18 @@
       <c r="N25" s="92"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C26" s="267" t="s">
+      <c r="C26" s="265" t="s">
         <v>204</v>
       </c>
-      <c r="D26" s="267"/>
-      <c r="E26" s="267"/>
-      <c r="F26" s="267"/>
-      <c r="G26" s="267"/>
-      <c r="H26" s="267"/>
-      <c r="I26" s="267"/>
-      <c r="J26" s="267"/>
-      <c r="K26" s="267"/>
-      <c r="L26" s="267"/>
+      <c r="D26" s="265"/>
+      <c r="E26" s="265"/>
+      <c r="F26" s="265"/>
+      <c r="G26" s="265"/>
+      <c r="H26" s="265"/>
+      <c r="I26" s="265"/>
+      <c r="J26" s="265"/>
+      <c r="K26" s="265"/>
+      <c r="L26" s="265"/>
       <c r="N26" s="92"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
@@ -23609,10 +23609,10 @@
       <c r="N36" s="92"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B37" s="259" t="s">
+      <c r="B37" s="256" t="s">
         <v>209</v>
       </c>
-      <c r="C37" s="259"/>
+      <c r="C37" s="256"/>
       <c r="N37" s="92"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
@@ -23705,10 +23705,10 @@
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B49" s="259" t="s">
+      <c r="B49" s="256" t="s">
         <v>214</v>
       </c>
-      <c r="C49" s="259"/>
+      <c r="C49" s="256"/>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B50" s="1" t="s">
@@ -23764,10 +23764,10 @@
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B57" s="259" t="s">
+      <c r="B57" s="256" t="s">
         <v>332</v>
       </c>
-      <c r="C57" s="259"/>
+      <c r="C57" s="256"/>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B58" s="1" t="s">
@@ -23907,10 +23907,10 @@
       <c r="N3" s="92"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="259" t="s">
+      <c r="B4" s="256" t="s">
         <v>219</v>
       </c>
-      <c r="C4" s="259"/>
+      <c r="C4" s="256"/>
       <c r="N4" s="92"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -23964,7 +23964,7 @@
       </c>
       <c r="C10" s="135">
         <f ca="1">Overview!C5</f>
-        <v>154.46</v>
+        <v>143.68</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -23973,7 +23973,7 @@
       </c>
       <c r="C11" s="156">
         <f ca="1">(C9-C10)/C10</f>
-        <v>6.5263246498749969E-2</v>
+        <v>0.14518764653533492</v>
       </c>
     </row>
   </sheetData>
@@ -24029,37 +24029,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="259" t="s">
+      <c r="C2" s="256" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="259"/>
-      <c r="E2" s="259"/>
-      <c r="F2" s="259"/>
-      <c r="G2" s="265"/>
-      <c r="H2" s="266" t="s">
+      <c r="D2" s="256"/>
+      <c r="E2" s="256"/>
+      <c r="F2" s="256"/>
+      <c r="G2" s="268"/>
+      <c r="H2" s="269" t="s">
         <v>114</v>
       </c>
-      <c r="I2" s="259"/>
-      <c r="J2" s="259"/>
-      <c r="K2" s="259"/>
-      <c r="L2" s="259"/>
+      <c r="I2" s="256"/>
+      <c r="J2" s="256"/>
+      <c r="K2" s="256"/>
+      <c r="L2" s="256"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="267" t="s">
+      <c r="C4" s="265" t="s">
         <v>198</v>
       </c>
-      <c r="D4" s="267"/>
-      <c r="E4" s="267"/>
-      <c r="F4" s="267"/>
-      <c r="G4" s="267"/>
-      <c r="H4" s="267"/>
-      <c r="I4" s="267"/>
-      <c r="J4" s="267"/>
-      <c r="K4" s="267"/>
-      <c r="L4" s="267"/>
+      <c r="D4" s="265"/>
+      <c r="E4" s="265"/>
+      <c r="F4" s="265"/>
+      <c r="G4" s="265"/>
+      <c r="H4" s="265"/>
+      <c r="I4" s="265"/>
+      <c r="J4" s="265"/>
+      <c r="K4" s="265"/>
+      <c r="L4" s="265"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -24172,18 +24172,18 @@
       <c r="N8" s="92"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C9" s="267" t="s">
+      <c r="C9" s="265" t="s">
         <v>122</v>
       </c>
-      <c r="D9" s="267"/>
-      <c r="E9" s="267"/>
-      <c r="F9" s="267"/>
-      <c r="G9" s="267"/>
-      <c r="H9" s="267"/>
-      <c r="I9" s="267"/>
-      <c r="J9" s="267"/>
-      <c r="K9" s="267"/>
-      <c r="L9" s="267"/>
+      <c r="D9" s="265"/>
+      <c r="E9" s="265"/>
+      <c r="F9" s="265"/>
+      <c r="G9" s="265"/>
+      <c r="H9" s="265"/>
+      <c r="I9" s="265"/>
+      <c r="J9" s="265"/>
+      <c r="K9" s="265"/>
+      <c r="L9" s="265"/>
       <c r="N9" s="92"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -24304,18 +24304,18 @@
       <c r="N13" s="92"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C14" s="267" t="s">
+      <c r="C14" s="265" t="s">
         <v>422</v>
       </c>
-      <c r="D14" s="267"/>
-      <c r="E14" s="267"/>
-      <c r="F14" s="267"/>
-      <c r="G14" s="267"/>
-      <c r="H14" s="267"/>
-      <c r="I14" s="267"/>
-      <c r="J14" s="267"/>
-      <c r="K14" s="267"/>
-      <c r="L14" s="267"/>
+      <c r="D14" s="265"/>
+      <c r="E14" s="265"/>
+      <c r="F14" s="265"/>
+      <c r="G14" s="265"/>
+      <c r="H14" s="265"/>
+      <c r="I14" s="265"/>
+      <c r="J14" s="265"/>
+      <c r="K14" s="265"/>
+      <c r="L14" s="265"/>
       <c r="N14" s="92"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
@@ -24405,10 +24405,10 @@
       <c r="N19" s="92"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B20" s="259" t="s">
+      <c r="B20" s="256" t="s">
         <v>424</v>
       </c>
-      <c r="C20" s="259"/>
+      <c r="C20" s="256"/>
       <c r="N20" s="92"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
@@ -24510,20 +24510,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="259" t="s">
+      <c r="C3" s="256" t="s">
         <v>113</v>
       </c>
-      <c r="D3" s="259"/>
-      <c r="E3" s="259"/>
-      <c r="F3" s="259"/>
-      <c r="G3" s="265"/>
-      <c r="H3" s="266" t="s">
+      <c r="D3" s="256"/>
+      <c r="E3" s="256"/>
+      <c r="F3" s="256"/>
+      <c r="G3" s="268"/>
+      <c r="H3" s="269" t="s">
         <v>114</v>
       </c>
-      <c r="I3" s="259"/>
-      <c r="J3" s="259"/>
-      <c r="K3" s="259"/>
-      <c r="L3" s="259"/>
+      <c r="I3" s="256"/>
+      <c r="J3" s="256"/>
+      <c r="K3" s="256"/>
+      <c r="L3" s="256"/>
       <c r="P3" s="270"/>
       <c r="Q3" s="270"/>
       <c r="R3" s="270"/>
@@ -24541,18 +24541,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="87"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="267" t="s">
+      <c r="C5" s="265" t="s">
         <v>184</v>
       </c>
-      <c r="D5" s="267"/>
-      <c r="E5" s="267"/>
-      <c r="F5" s="267"/>
-      <c r="G5" s="267"/>
-      <c r="H5" s="267"/>
-      <c r="I5" s="267"/>
-      <c r="J5" s="267"/>
-      <c r="K5" s="267"/>
-      <c r="L5" s="267"/>
+      <c r="D5" s="265"/>
+      <c r="E5" s="265"/>
+      <c r="F5" s="265"/>
+      <c r="G5" s="265"/>
+      <c r="H5" s="265"/>
+      <c r="I5" s="265"/>
+      <c r="J5" s="265"/>
+      <c r="K5" s="265"/>
+      <c r="L5" s="265"/>
       <c r="P5" s="270"/>
       <c r="Q5" s="270"/>
       <c r="R5" s="270"/>
@@ -24803,7 +24803,7 @@
       </c>
       <c r="C15" s="158">
         <f ca="1">Overview!C5</f>
-        <v>154.46</v>
+        <v>143.68</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -24869,7 +24869,7 @@
       </c>
       <c r="C23" s="163">
         <f ca="1">C15*C22</f>
-        <v>7226565.5600000005</v>
+        <v>6722212.4800000004</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -24896,7 +24896,7 @@
       </c>
       <c r="C26" s="164">
         <f ca="1">C23+C25-C24</f>
-        <v>5810006.5600000005</v>
+        <v>5305653.4800000004</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -24979,18 +24979,18 @@
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C39" s="267" t="s">
+      <c r="C39" s="265" t="s">
         <v>233</v>
       </c>
-      <c r="D39" s="267"/>
-      <c r="E39" s="267"/>
-      <c r="F39" s="267"/>
-      <c r="G39" s="267"/>
-      <c r="H39" s="267"/>
-      <c r="I39" s="267"/>
-      <c r="J39" s="267"/>
-      <c r="K39" s="267"/>
-      <c r="L39" s="267"/>
+      <c r="D39" s="265"/>
+      <c r="E39" s="265"/>
+      <c r="F39" s="265"/>
+      <c r="G39" s="265"/>
+      <c r="H39" s="265"/>
+      <c r="I39" s="265"/>
+      <c r="J39" s="265"/>
+      <c r="K39" s="265"/>
+      <c r="L39" s="265"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="12">
@@ -25422,17 +25422,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C39:L39"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C39:L39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -32124,7 +32124,7 @@
       </c>
       <c r="AC116" s="63">
         <f ca="1">Overview!C5</f>
-        <v>154.46</v>
+        <v>143.68</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -32195,7 +32195,7 @@
       </c>
       <c r="AC117" s="65">
         <f ca="1">AC116/AC85</f>
-        <v>154.46</v>
+        <v>143.68</v>
       </c>
     </row>
     <row r="119" spans="1:31" x14ac:dyDescent="0.2">
@@ -33305,7 +33305,7 @@
       <c r="AA146" s="49"/>
       <c r="AC146" s="72">
         <f ca="1">AC117/Statement!AC26</f>
-        <v>49.181733335695355</v>
+        <v>45.749264830200104</v>
       </c>
     </row>
     <row r="147" spans="2:29" x14ac:dyDescent="0.2">
@@ -33342,7 +33342,7 @@
       <c r="AA147" s="49"/>
       <c r="AC147" s="72">
         <f ca="1">AC117/(Statement!AC5/Statement!AC22)</f>
-        <v>6.6332032990044238</v>
+        <v>6.1702618801045945</v>
       </c>
     </row>
     <row r="148" spans="2:29" x14ac:dyDescent="0.2">
@@ -33403,7 +33403,7 @@
       </c>
       <c r="AC148" s="72">
         <f ca="1">AC117/(Statement!AC49/Statement!AC75)</f>
-        <v>5.1261617799569006</v>
+        <v>4.7683990971397607</v>
       </c>
     </row>
     <row r="149" spans="2:29" x14ac:dyDescent="0.2">
@@ -33464,7 +33464,7 @@
       </c>
       <c r="AC149" s="145">
         <f ca="1">Statement!AC117*Statement!AC78</f>
-        <v>7741844.1200000001</v>
+        <v>7201528.96</v>
       </c>
     </row>
     <row r="150" spans="2:29" x14ac:dyDescent="0.2">
@@ -33525,7 +33525,7 @@
       </c>
       <c r="AC150" s="145">
         <f ca="1">AC149+AC108-AC107+AC48+AC45</f>
-        <v>6325285.1200000001</v>
+        <v>5784969.96</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -33562,7 +33562,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="185">
         <f ca="1">AC150/AC5</f>
-        <v>5.5242568309924351</v>
+        <v>5.052366685822383</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -33599,7 +33599,7 @@
       <c r="AA152" s="49"/>
       <c r="AC152" s="185">
         <f ca="1">AC150/AC12</f>
-        <v>40.266639844670081</v>
+        <v>36.827004233376833</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -33734,7 +33734,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="72">
         <f t="shared" ref="AC155:AC156" ca="1" si="151">AC149/AC153</f>
-        <v>30.621960762597897</v>
+        <v>28.484807214619096</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -33771,7 +33771,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="72">
         <f t="shared" ca="1" si="151"/>
-        <v>37.93699497528484</v>
+        <v>34.696361055846559</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -33808,7 +33808,7 @@
       <c r="AA157" s="49"/>
       <c r="AC157" s="74">
         <f t="shared" ref="AC157" ca="1" si="154">AC153/AC149</f>
-        <v>3.2656302049129865E-2</v>
+        <v>3.5106433842626662E-2</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
@@ -33845,7 +33845,7 @@
       <c r="AA158" s="49"/>
       <c r="AC158" s="74">
         <f ca="1">AC26/AC117</f>
-        <v>2.0332752267480887E-2</v>
+        <v>2.1858274744119555E-2</v>
       </c>
     </row>
     <row r="159" spans="2:29" x14ac:dyDescent="0.2">
@@ -33919,7 +33919,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="156">
         <f ca="1">-AC63/AC149</f>
-        <v>8.9904935983133698E-3</v>
+        <v>9.665030910324909E-3</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -33956,7 +33956,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="156">
         <f ca="1">-(AC63+AC64)/AC149</f>
-        <v>8.9904935983133698E-3</v>
+        <v>9.665030910324909E-3</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -34459,7 +34459,7 @@
       <c r="AA172" s="49"/>
       <c r="AC172" s="156">
         <f ca="1">(AC107-AC108)/AC149</f>
-        <v>0.1829743634776258</v>
+        <v>0.1967025346795245</v>
       </c>
     </row>
     <row r="173" spans="2:29" x14ac:dyDescent="0.2">
@@ -36381,15 +36381,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="259" t="s">
+      <c r="B4" s="256" t="s">
         <v>242</v>
       </c>
-      <c r="C4" s="259"/>
-      <c r="E4" s="259" t="s">
+      <c r="C4" s="256"/>
+      <c r="E4" s="256" t="s">
         <v>249</v>
       </c>
-      <c r="F4" s="259"/>
-      <c r="G4" s="259"/>
+      <c r="F4" s="256"/>
+      <c r="G4" s="256"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -36397,7 +36397,7 @@
       </c>
       <c r="C5" s="174">
         <f ca="1">Overview!C5</f>
-        <v>154.46</v>
+        <v>143.68</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="134" t="s">
@@ -36413,7 +36413,7 @@
       </c>
       <c r="C6" s="175">
         <f ca="1">Statement!AC149</f>
-        <v>7741844.1200000001</v>
+        <v>7201528.96</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>20</v>
@@ -36433,7 +36433,7 @@
       </c>
       <c r="C7" s="175">
         <f ca="1">Statement!AC150</f>
-        <v>6325285.1200000001</v>
+        <v>5784969.96</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>32</v>
@@ -36453,7 +36453,7 @@
       </c>
       <c r="C8" s="176">
         <f ca="1">Statement!AC146</f>
-        <v>49.181733335695355</v>
+        <v>45.749264830200104</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>252</v>
@@ -36473,7 +36473,7 @@
       </c>
       <c r="C9" s="176">
         <f ca="1">Statement!AC147</f>
-        <v>6.6332032990044238</v>
+        <v>6.1702618801045945</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>253</v>
@@ -36493,7 +36493,7 @@
       </c>
       <c r="C10" s="176">
         <f ca="1">Statement!AC148</f>
-        <v>5.1261617799569006</v>
+        <v>4.7683990971397607</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -36513,7 +36513,7 @@
       </c>
       <c r="C11" s="176">
         <f ca="1">Statement!AC151</f>
-        <v>5.5242568309924351</v>
+        <v>5.052366685822383</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -36522,18 +36522,18 @@
       </c>
       <c r="C12" s="176">
         <f ca="1">Statement!AC152</f>
-        <v>40.266639844670081</v>
+        <v>36.827004233376833</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="259" t="s">
+      <c r="B15" s="256" t="s">
         <v>78</v>
       </c>
-      <c r="C15" s="259"/>
-      <c r="E15" s="259" t="s">
+      <c r="C15" s="256"/>
+      <c r="E15" s="256" t="s">
         <v>255</v>
       </c>
-      <c r="F15" s="259"/>
+      <c r="F15" s="256"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -36584,14 +36584,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="259" t="s">
+      <c r="B21" s="256" t="s">
         <v>254</v>
       </c>
-      <c r="C21" s="259"/>
-      <c r="E21" s="259" t="s">
+      <c r="C21" s="256"/>
+      <c r="E21" s="256" t="s">
         <v>258</v>
       </c>
-      <c r="F21" s="259"/>
+      <c r="F21" s="256"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -36660,14 +36660,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="259" t="s">
+      <c r="B29" s="256" t="s">
         <v>259</v>
       </c>
-      <c r="C29" s="259"/>
-      <c r="E29" s="259" t="s">
+      <c r="C29" s="256"/>
+      <c r="E29" s="256" t="s">
         <v>265</v>
       </c>
-      <c r="F29" s="259"/>
+      <c r="F29" s="256"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -36743,14 +36743,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="259" t="s">
+      <c r="B37" s="256" t="s">
         <v>277</v>
       </c>
-      <c r="C37" s="259"/>
-      <c r="E37" s="259" t="s">
+      <c r="C37" s="256"/>
+      <c r="E37" s="256" t="s">
         <v>280</v>
       </c>
-      <c r="F37" s="259"/>
+      <c r="F37" s="256"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -36758,7 +36758,7 @@
       </c>
       <c r="C38" s="177">
         <f ca="1">Statement!AC158</f>
-        <v>2.0332752267480887E-2</v>
+        <v>2.1858274744119555E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>279</v>
@@ -36774,7 +36774,7 @@
       </c>
       <c r="C39" s="217">
         <f ca="1">Statement!AC157</f>
-        <v>3.2656302049129865E-2</v>
+        <v>3.5106433842626662E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>281</v>
@@ -36806,7 +36806,7 @@
       </c>
       <c r="C41" s="177">
         <f ca="1">Statement!AC160</f>
-        <v>8.9904935983133698E-3</v>
+        <v>9.665030910324909E-3</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -36815,18 +36815,18 @@
       </c>
       <c r="C42" s="177">
         <f ca="1">Statement!AC161</f>
-        <v>8.9904935983133698E-3</v>
+        <v>9.665030910324909E-3</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="259" t="s">
+      <c r="B45" s="256" t="s">
         <v>288</v>
       </c>
-      <c r="C45" s="259"/>
-      <c r="E45" s="259" t="s">
+      <c r="C45" s="256"/>
+      <c r="E45" s="256" t="s">
         <v>294</v>
       </c>
-      <c r="F45" s="259"/>
+      <c r="F45" s="256"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -36859,18 +36859,18 @@
       </c>
       <c r="F48" s="177">
         <f ca="1">Statement!AC172</f>
-        <v>0.1829743634776258</v>
+        <v>0.1967025346795245</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="259" t="s">
+      <c r="B51" s="256" t="s">
         <v>291</v>
       </c>
-      <c r="C51" s="259"/>
-      <c r="E51" s="259" t="s">
+      <c r="C51" s="256"/>
+      <c r="E51" s="256" t="s">
         <v>312</v>
       </c>
-      <c r="F51" s="259"/>
+      <c r="F51" s="256"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -37038,7 +37038,7 @@
       </c>
       <c r="I6" s="174">
         <f ca="1">Statement!AC116</f>
-        <v>154.46</v>
+        <v>143.68</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -37067,7 +37067,7 @@
       </c>
       <c r="I7" s="175">
         <f ca="1">Statement!AC149</f>
-        <v>7741844.1200000001</v>
+        <v>7201528.96</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -37096,7 +37096,7 @@
       </c>
       <c r="I8" s="175">
         <f ca="1">Statement!AC150</f>
-        <v>6325285.1200000001</v>
+        <v>5784969.96</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -37125,7 +37125,7 @@
       </c>
       <c r="I9" s="176">
         <f ca="1">Statement!AC146</f>
-        <v>49.181733335695355</v>
+        <v>45.749264830200104</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -37154,7 +37154,7 @@
       </c>
       <c r="I10" s="176">
         <f ca="1">Statement!AC147</f>
-        <v>6.6332032990044238</v>
+        <v>6.1702618801045945</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -37183,7 +37183,7 @@
       </c>
       <c r="I11" s="176">
         <f ca="1">Statement!AC148</f>
-        <v>5.1261617799569006</v>
+        <v>4.7683990971397607</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -37212,7 +37212,7 @@
       </c>
       <c r="I12" s="176">
         <f ca="1">Statement!AC151</f>
-        <v>5.5242568309924351</v>
+        <v>5.052366685822383</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -37241,7 +37241,7 @@
       </c>
       <c r="I13" s="176">
         <f ca="1">Statement!AC152</f>
-        <v>40.266639844670081</v>
+        <v>36.827004233376833</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -38014,7 +38014,7 @@
       </c>
       <c r="I51" s="177">
         <f ca="1">Statement!AC158</f>
-        <v>2.0332752267480887E-2</v>
+        <v>2.1858274744119555E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -38043,7 +38043,7 @@
       </c>
       <c r="I52" s="177">
         <f ca="1">Statement!AC157</f>
-        <v>3.2656302049129865E-2</v>
+        <v>3.5106433842626662E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -38101,7 +38101,7 @@
       </c>
       <c r="I54" s="177">
         <f ca="1">Statement!AC160</f>
-        <v>8.9904935983133698E-3</v>
+        <v>9.665030910324909E-3</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -38130,7 +38130,7 @@
       </c>
       <c r="I55" s="177">
         <f ca="1">Statement!AC161</f>
-        <v>8.9904935983133698E-3</v>
+        <v>9.665030910324909E-3</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -38366,7 +38366,7 @@
       </c>
       <c r="I68" s="198">
         <f ca="1">Statement!AC172</f>
-        <v>0.1829743634776258</v>
+        <v>0.1967025346795245</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -38909,14 +38909,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="262" t="s">
+      <c r="C3" s="260" t="s">
         <v>322</v>
       </c>
-      <c r="D3" s="263"/>
-      <c r="F3" s="264" t="s">
+      <c r="D3" s="261"/>
+      <c r="F3" s="262" t="s">
         <v>323</v>
       </c>
-      <c r="G3" s="263"/>
+      <c r="G3" s="261"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -38983,19 +38983,19 @@
       <c r="B7" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C7" s="260">
+      <c r="C7" s="263">
         <f>Statement!AA89</f>
         <v>2.2218264392893719E-2</v>
       </c>
-      <c r="D7" s="261"/>
-      <c r="F7" s="260">
+      <c r="D7" s="264"/>
+      <c r="F7" s="263">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.18309713991239371</v>
       </c>
-      <c r="G7" s="261"/>
+      <c r="G7" s="264"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="209" t="s">
@@ -39022,19 +39022,19 @@
       <c r="B9" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C9" s="260">
+      <c r="C9" s="263">
         <f>Statement!AA90</f>
         <v>3.6046202026093238E-2</v>
       </c>
-      <c r="D9" s="261"/>
-      <c r="F9" s="260">
+      <c r="D9" s="264"/>
+      <c r="F9" s="263">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.17263647322197348</v>
       </c>
-      <c r="G9" s="261"/>
+      <c r="G9" s="264"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="209" t="s">
@@ -39061,19 +39061,19 @@
       <c r="B11" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C11" s="260">
+      <c r="C11" s="263">
         <f>Statement!AA91</f>
         <v>1.710027405488606E-2</v>
       </c>
-      <c r="D11" s="261"/>
-      <c r="F11" s="260">
+      <c r="D11" s="264"/>
+      <c r="F11" s="263">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>0.1870895657269924</v>
       </c>
-      <c r="G11" s="261"/>
+      <c r="G11" s="264"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="209" t="s">
@@ -39100,19 +39100,19 @@
       <c r="B13" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C13" s="260">
+      <c r="C13" s="263">
         <f>Statement!AA95</f>
         <v>8.4392741251357012E-2</v>
       </c>
-      <c r="D13" s="261"/>
-      <c r="F13" s="260">
+      <c r="D13" s="264"/>
+      <c r="F13" s="263">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.22501976973287405</v>
       </c>
-      <c r="G13" s="261"/>
+      <c r="G13" s="264"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="209" t="s">
@@ -39139,19 +39139,19 @@
       <c r="B15" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C15" s="260">
+      <c r="C15" s="263">
         <f>Statement!AA96</f>
         <v>-0.23765355851505829</v>
       </c>
-      <c r="D15" s="261"/>
-      <c r="F15" s="260">
+      <c r="D15" s="264"/>
+      <c r="F15" s="263">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>1.7444474417768186E-2</v>
       </c>
-      <c r="G15" s="261"/>
+      <c r="G15" s="264"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="209" t="s">
@@ -39178,19 +39178,19 @@
       <c r="B17" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C17" s="260">
+      <c r="C17" s="263">
         <f>Statement!AA98</f>
         <v>-0.23704555913483663</v>
       </c>
-      <c r="D17" s="261"/>
-      <c r="F17" s="260">
+      <c r="D17" s="264"/>
+      <c r="F17" s="263">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>-0.25955204216073779</v>
       </c>
-      <c r="G17" s="261"/>
+      <c r="G17" s="264"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="209" t="s">
@@ -39217,22 +39217,22 @@
       <c r="B19" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C19" s="260">
+      <c r="C19" s="263">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>2.5565842762241744E-2</v>
       </c>
-      <c r="D19" s="261"/>
-      <c r="F19" s="260">
+      <c r="D19" s="264"/>
+      <c r="F19" s="263">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>2.5293753865182372E-2</v>
       </c>
-      <c r="G19" s="261"/>
+      <c r="G19" s="264"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="209" t="s">
@@ -39259,22 +39259,22 @@
       <c r="B21" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C21" s="260">
+      <c r="C21" s="263">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>-0.2584269662921348</v>
       </c>
-      <c r="D21" s="261"/>
-      <c r="F21" s="260">
+      <c r="D21" s="264"/>
+      <c r="F21" s="263">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>-0.27472527472527469</v>
       </c>
-      <c r="G21" s="261"/>
+      <c r="G21" s="264"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -39323,22 +39323,22 @@
       <c r="B25" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C25" s="260">
+      <c r="C25" s="263">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>2.840483364420425E-2</v>
       </c>
-      <c r="D25" s="261"/>
-      <c r="F25" s="260">
+      <c r="D25" s="264"/>
+      <c r="F25" s="263">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>0.22478379327694395</v>
       </c>
-      <c r="G25" s="261"/>
+      <c r="G25" s="264"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="str">
@@ -39366,22 +39366,22 @@
       <c r="B27" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C27" s="260">
+      <c r="C27" s="263">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>2.1247695740758708E-2</v>
       </c>
-      <c r="D27" s="261"/>
-      <c r="F27" s="260">
+      <c r="D27" s="264"/>
+      <c r="F27" s="263">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>2.1792942775323981E-2</v>
       </c>
-      <c r="G27" s="261"/>
+      <c r="G27" s="264"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="str">
@@ -39409,22 +39409,22 @@
       <c r="B29" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C29" s="260">
+      <c r="C29" s="263">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>-0.10674206945303526</v>
       </c>
-      <c r="D29" s="261"/>
-      <c r="F29" s="260">
+      <c r="D29" s="264"/>
+      <c r="F29" s="263">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>2.0816812053925456E-3</v>
       </c>
-      <c r="G29" s="261"/>
+      <c r="G29" s="264"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="str">
@@ -39452,22 +39452,22 @@
       <c r="B31" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C31" s="260">
+      <c r="C31" s="263">
         <f>IF(C30=0,
 IF(D30=0,0,IF(D30&gt;0,1,-1)),
 (D30-C30)/ABS(C30)
 )</f>
         <v>-5.2569263556713236E-2</v>
       </c>
-      <c r="D31" s="261"/>
-      <c r="F31" s="260">
+      <c r="D31" s="264"/>
+      <c r="F31" s="263">
         <f>IF(F30=0,
 IF(G30=0,0,IF(G30&gt;0,1,-1)),
 (G30-F30)/ABS(F30)
 )</f>
         <v>-0.22983638113570742</v>
       </c>
-      <c r="G31" s="261"/>
+      <c r="G31" s="264"/>
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B32" s="20" t="str">
@@ -39495,22 +39495,22 @@
       <c r="B33" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C33" s="260">
+      <c r="C33" s="263">
         <f>IF(C32=0,
 IF(D32=0,0,IF(D32&gt;0,1,-1)),
 (D32-C32)/ABS(C32)
 )</f>
         <v>0.84164222873900296</v>
       </c>
-      <c r="D33" s="261"/>
-      <c r="F33" s="260">
+      <c r="D33" s="264"/>
+      <c r="F33" s="263">
         <f>IF(F32=0,
 IF(G32=0,0,IF(G32&gt;0,1,-1)),
 (G32-F32)/ABS(F32)
 )</f>
         <v>1.482213438735178</v>
       </c>
-      <c r="G33" s="261"/>
+      <c r="G33" s="264"/>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B35" s="8" t="s">
@@ -39559,22 +39559,22 @@
       <c r="B37" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C37" s="260">
+      <c r="C37" s="263">
         <f>IF(C36=0,
 IF(D36=0,0,IF(D36&gt;0,1,-1)),
 (D36-C36)/ABS(C36)
 )</f>
         <v>3.8938053097345132E-2</v>
       </c>
-      <c r="D37" s="261"/>
-      <c r="F37" s="260">
+      <c r="D37" s="264"/>
+      <c r="F37" s="263">
         <f>IF(F36=0,
 IF(G36=0,0,IF(G36&gt;0,1,-1)),
 (G36-F36)/ABS(F36)
 )</f>
         <v>0.23060796645702306</v>
       </c>
-      <c r="G37" s="261"/>
+      <c r="G37" s="264"/>
     </row>
     <row r="38" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="str">
@@ -39602,22 +39602,22 @@
       <c r="B39" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C39" s="260">
+      <c r="C39" s="263">
         <f>IF(C38=0,
 IF(D38=0,0,IF(D38&gt;0,1,-1)),
 (D38-C38)/ABS(C38)
 )</f>
         <v>2.0319303338171262E-2</v>
       </c>
-      <c r="D39" s="261"/>
-      <c r="F39" s="260">
+      <c r="D39" s="264"/>
+      <c r="F39" s="263">
         <f>IF(F38=0,
 IF(G38=0,0,IF(G38&gt;0,1,-1)),
 (G38-F38)/ABS(F38)
 )</f>
         <v>9.5869056897895558E-2</v>
       </c>
-      <c r="G39" s="261"/>
+      <c r="G39" s="264"/>
     </row>
     <row r="40" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B40" s="20" t="str">
@@ -39645,22 +39645,22 @@
       <c r="B41" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C41" s="260">
+      <c r="C41" s="263">
         <f>IF(C40=0,
 IF(D40=0,0,IF(D40&gt;0,1,-1)),
 (D40-C40)/ABS(C40)
 )</f>
         <v>1.6E-2</v>
       </c>
-      <c r="D41" s="261"/>
-      <c r="F41" s="260">
+      <c r="D41" s="264"/>
+      <c r="F41" s="263">
         <f>IF(F40=0,
 IF(G40=0,0,IF(G40&gt;0,1,-1)),
 (G40-F40)/ABS(F40)
 )</f>
         <v>0.16513761467889909</v>
       </c>
-      <c r="G41" s="261"/>
+      <c r="G41" s="264"/>
     </row>
     <row r="42" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B42" s="20" t="str">
@@ -39688,22 +39688,22 @@
       <c r="B43" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C43" s="260">
+      <c r="C43" s="263">
         <f>IF(C42=0,
 IF(D42=0,0,IF(D42&gt;0,1,-1)),
 (D42-C42)/ABS(C42)
 )</f>
         <v>2.0750199521149242E-2</v>
       </c>
-      <c r="D43" s="261"/>
-      <c r="F43" s="260">
+      <c r="D43" s="264"/>
+      <c r="F43" s="263">
         <f>IF(F42=0,
 IF(G42=0,0,IF(G42&gt;0,1,-1)),
 (G42-F42)/ABS(F42)
 )</f>
         <v>8.9437819420783646E-2</v>
       </c>
-      <c r="G43" s="261"/>
+      <c r="G43" s="264"/>
     </row>
     <row r="44" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B44" s="20" t="str">
@@ -39731,22 +39731,22 @@
       <c r="B45" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C45" s="260">
+      <c r="C45" s="263">
         <f>IF(C44=0,
 IF(D44=0,0,IF(D44&gt;0,1,-1)),
 (D44-C44)/ABS(C44)
 )</f>
         <v>1.2209481933271921E-2</v>
       </c>
-      <c r="D45" s="261"/>
-      <c r="F45" s="260">
+      <c r="D45" s="264"/>
+      <c r="F45" s="263">
         <f>IF(F44=0,
 IF(G44=0,0,IF(G44&gt;0,1,-1)),
 (G44-F44)/ABS(F44)
 )</f>
         <v>5.119238950540856E-2</v>
       </c>
-      <c r="G45" s="261"/>
+      <c r="G45" s="264"/>
     </row>
     <row r="46" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="str">
@@ -39774,22 +39774,22 @@
       <c r="B47" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C47" s="260">
+      <c r="C47" s="263">
         <f>IF(C46=0,
 IF(D46=0,0,IF(D46&gt;0,1,-1)),
 (D46-C46)/ABS(C46)
 )</f>
         <v>1.8247963846473435E-2</v>
       </c>
-      <c r="D47" s="261"/>
-      <c r="F47" s="260">
+      <c r="D47" s="264"/>
+      <c r="F47" s="263">
         <f>IF(F46=0,
 IF(G46=0,0,IF(G46&gt;0,1,-1)),
 (G46-F46)/ABS(F46)
 )</f>
         <v>0.1229516507570132</v>
       </c>
-      <c r="G47" s="261"/>
+      <c r="G47" s="264"/>
     </row>
     <row r="48" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B48" s="20" t="str">
@@ -39817,22 +39817,22 @@
       <c r="B49" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C49" s="260">
+      <c r="C49" s="263">
         <f>IF(C48=0,
 IF(D48=0,0,IF(D48&gt;0,1,-1)),
 (D48-C48)/ABS(C48)
 )</f>
         <v>-4.2332859174963834E-3</v>
       </c>
-      <c r="D49" s="261"/>
-      <c r="F49" s="260">
+      <c r="D49" s="264"/>
+      <c r="F49" s="263">
         <f>IF(F48=0,
 IF(G48=0,0,IF(G48&gt;0,1,-1)),
 (G48-F48)/ABS(F48)
 )</f>
         <v>6.3208790635154666E-2</v>
       </c>
-      <c r="G49" s="261"/>
+      <c r="G49" s="264"/>
     </row>
     <row r="50" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B50" s="20" t="str">
@@ -39860,22 +39860,22 @@
       <c r="B51" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C51" s="260">
+      <c r="C51" s="263">
         <f>IF(C50=0,
 IF(D50=0,0,IF(D50&gt;0,1,-1)),
 (D50-C50)/ABS(C50)
 )</f>
         <v>4.8738292663854846E-4</v>
       </c>
-      <c r="D51" s="261"/>
-      <c r="F51" s="260">
+      <c r="D51" s="264"/>
+      <c r="F51" s="263">
         <f>IF(F50=0,
 IF(G50=0,0,IF(G50&gt;0,1,-1)),
 (G50-F50)/ABS(F50)
 )</f>
         <v>-6.2091544317255373E-2</v>
       </c>
-      <c r="G51" s="261"/>
+      <c r="G51" s="264"/>
     </row>
     <row r="52" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="str">
@@ -39903,43 +39903,39 @@
       <c r="B53" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C53" s="260">
+      <c r="C53" s="263">
         <f>IF(C52=0,
 IF(D52=0,0,IF(D52&gt;0,1,-1)),
 (D52-C52)/ABS(C52)
 )</f>
         <v>-8.8077740902117604E-2</v>
       </c>
-      <c r="D53" s="261"/>
-      <c r="F53" s="260">
+      <c r="D53" s="264"/>
+      <c r="F53" s="263">
         <f>IF(F52=0,
 IF(G52=0,0,IF(G52&gt;0,1,-1)),
 (G52-F52)/ABS(F52)
 )</f>
         <v>-0.37416005758387127</v>
       </c>
-      <c r="G53" s="261"/>
+      <c r="G53" s="264"/>
     </row>
   </sheetData>
   <mergeCells count="46">
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C53:D53"/>
+    <mergeCell ref="F53:G53"/>
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="F47:G47"/>
+    <mergeCell ref="C49:D49"/>
+    <mergeCell ref="F49:G49"/>
+    <mergeCell ref="C51:D51"/>
+    <mergeCell ref="F51:G51"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="F41:G41"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="F43:G43"/>
+    <mergeCell ref="C45:D45"/>
+    <mergeCell ref="F45:G45"/>
     <mergeCell ref="C37:D37"/>
     <mergeCell ref="F37:G37"/>
     <mergeCell ref="C39:D39"/>
@@ -39954,20 +39950,24 @@
     <mergeCell ref="F31:G31"/>
     <mergeCell ref="C33:D33"/>
     <mergeCell ref="F33:G33"/>
-    <mergeCell ref="C41:D41"/>
-    <mergeCell ref="F41:G41"/>
-    <mergeCell ref="C43:D43"/>
-    <mergeCell ref="F43:G43"/>
-    <mergeCell ref="C45:D45"/>
-    <mergeCell ref="F45:G45"/>
-    <mergeCell ref="C53:D53"/>
-    <mergeCell ref="F53:G53"/>
-    <mergeCell ref="C47:D47"/>
-    <mergeCell ref="F47:G47"/>
-    <mergeCell ref="C49:D49"/>
-    <mergeCell ref="F49:G49"/>
-    <mergeCell ref="C51:D51"/>
-    <mergeCell ref="F51:G51"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/DUOL.xlsx
+++ b/DUOL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28A8BBA0-A261-D441-A705-76A9D16852C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCA0BD60-E7F3-F24A-8A3D-89F8588618FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="4" activeTab="13" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -119,7 +119,7 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="2">
+  <futureMetadata name="XLRICHVALUE" count="5">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -130,7 +130,28 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="3"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="4"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="5"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="8"/>
         </ext>
       </extLst>
     </bk>
@@ -140,12 +161,21 @@
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="2">
+  <valueMetadata count="5">
     <bk>
       <rc t="2" v="0"/>
     </bk>
     <bk>
       <rc t="2" v="1"/>
+    </bk>
+    <bk>
+      <rc t="2" v="2"/>
+    </bk>
+    <bk>
+      <rc t="2" v="3"/>
+    </bk>
+    <bk>
+      <rc t="2" v="4"/>
     </bk>
   </valueMetadata>
 </metadata>
@@ -2410,9 +2440,6 @@
     <xf numFmtId="39" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="10" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="39" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2420,6 +2447,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2431,10 +2467,10 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2444,12 +2480,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -13139,7 +13169,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="6">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="9">
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=c2mtim&amp;q=XNAS%3aDUOL&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
@@ -13158,11 +13188,9 @@
     <v>Powered by Refinitiv</v>
     <v>353</v>
     <v>87.89</v>
-    <v>1.0487</v>
-    <v>-1.48</v>
-    <v>-1.0196E-2</v>
-    <v>0.52</v>
-    <v>3.6189999999999998E-3</v>
+    <v>1.0450999999999999</v>
+    <v>-1.97</v>
+    <v>-1.3184E-2</v>
     <v>USD</v>
     <v>Duolingo, Inc. is a technology company. The Company is engaged in offering a mobile learning platform, as well as a digital English language proficiency assessment exam. It operates a freemium business model, namely, the app and the Website are accessible free of charge, although Duolingo also offers premium services for a subscription fee. Its solutions consist of the Duolingo App, Super Duolingo, Duolingo Max, Duolingo English Test: AI-Driven Language Assessment, Duolingo for Schools, and Duolingo ABC. The Duolingo App offers courses in over 40 different languages, including Spanish, English, French, German, Italian, Portuguese, Japanese and Chinese. Duolingo can also be accessed on desktop computers via a Web browser. Its subscription offering, Super Duolingo, offers learners additional features to enhance their learning experience. The Duolingo English Test is an online, on-demand, high-stakes English proficiency assessment. It also operates an animation and motion design studio.</v>
     <v>900</v>
@@ -13170,35 +13198,49 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>5900 PENN AVE, SECOND FLOOR, PITTSBURGH, PA, 15206 US</v>
-    <v>146.44999999999999</v>
+    <v>152.68</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46276.983224698437</v>
+    <v>46287.768492395313</v>
     <v>0</v>
-    <v>141.53</v>
-    <v>6722251273</v>
+    <v>144.8005</v>
+    <v>6898635511</v>
     <v>DUOLINGO, INC.</v>
     <v>DUOLINGO, INC.</v>
-    <v>145.06</v>
-    <v>17.302600000000002</v>
-    <v>145.16</v>
-    <v>143.68</v>
-    <v>144.19999999999999</v>
+    <v>152.02000000000001</v>
+    <v>17.575500000000002</v>
+    <v>149.41999999999999</v>
+    <v>147.44999999999999</v>
     <v>46786270</v>
     <v>DUOL</v>
     <v>DUOLINGO, INC. (XNAS:DUOL)</v>
-    <v>980262</v>
-    <v>1311929</v>
+    <v>404903</v>
+    <v>1193470</v>
     <v>2011</v>
   </rv>
   <rv s="2">
     <v>1</v>
   </rv>
+  <rv s="3">
+    <v>12</v>
+    <v>Price (Extended hours)</v>
+    <v>0</v>
+  </rv>
+  <rv s="3">
+    <v>12</v>
+    <v>Change (extended hours)</v>
+    <v>0</v>
+  </rv>
+  <rv s="3">
+    <v>12</v>
+    <v>Change % (extended hours)</v>
+    <v>0</v>
+  </rv>
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a33knm&amp;q=10+Y+TSY+YLD+NDX&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="3">
+  <rv s="4">
     <v>5</v>
     <v>10 Y TSY YLD NDX</v>
     <v>6</v>
@@ -13210,30 +13252,30 @@
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>48.12</v>
+    <v>50.16</v>
     <v>39.47</v>
-    <v>0.22</v>
-    <v>4.62E-3</v>
+    <v>-0.35</v>
+    <v>-7.0030000000000005E-3</v>
     <v>US</v>
-    <v>48.12</v>
+    <v>49.76</v>
     <v>Index</v>
-    <v>3</v>
-    <v>47.48</v>
+    <v>6</v>
+    <v>49.51</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>47.54</v>
-    <v>47.62</v>
-    <v>47.84</v>
+    <v>49.53</v>
+    <v>49.98</v>
+    <v>49.63</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
   <rv s="2">
-    <v>4</v>
+    <v>7</v>
   </rv>
 </rvData>
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="4">
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="5">
   <s t="_hyperlink">
     <k n="Address" t="s"/>
     <k n="Text" t="s"/>
@@ -13255,8 +13297,6 @@
     <k n="Beta"/>
     <k n="Change"/>
     <k n="Change (%)"/>
-    <k n="Change (Extended hours)"/>
-    <k n="Change % (Extended hours)"/>
     <k n="Currency" t="s"/>
     <k n="Description" t="s"/>
     <k n="Employees"/>
@@ -13277,7 +13317,6 @@
     <k n="P/E"/>
     <k n="Previous close"/>
     <k n="Price"/>
-    <k n="Price (Extended hours)"/>
     <k n="Shares outstanding"/>
     <k n="Ticker symbol" t="s"/>
     <k n="UniqueName" t="s"/>
@@ -13287,6 +13326,11 @@
   </s>
   <s t="_linkedentity">
     <k n="%cvi" t="r"/>
+  </s>
+  <s t="_error">
+    <k n="errorType" t="i"/>
+    <k n="field" t="s"/>
+    <k n="subType" t="i"/>
   </s>
   <s t="_linkedentitycore">
     <k n="_Display" t="spb"/>
@@ -13322,7 +13366,7 @@
 <file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
 <supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
   <spbArrays count="2">
-    <a count="45">
+    <a count="42">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%IsRefreshable</v>
@@ -13333,16 +13377,13 @@
       <v t="s">Name</v>
       <v t="s">_SubLabel</v>
       <v t="s">Price</v>
-      <v t="s">Price (Extended hours)</v>
       <v t="s">Exchange</v>
       <v t="s">Official name</v>
       <v t="s">Last trade time</v>
       <v t="s">Ticker symbol</v>
       <v t="s">Exchange abbreviation</v>
       <v t="s">Change</v>
-      <v t="s">Change (Extended hours)</v>
       <v t="s">Change (%)</v>
-      <v t="s">Change % (Extended hours)</v>
       <v t="s">Currency</v>
       <v t="s">Previous close</v>
       <v t="s">Open</v>
@@ -13436,19 +13477,13 @@
       <v>8</v>
       <v>9</v>
       <v>4</v>
-      <v>1</v>
-      <v>1</v>
-      <v>5</v>
     </spb>
     <spb s="4">
-      <v>at close</v>
+      <v>Real-Time Nasdaq Last Sale</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq</v>
+      <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
-      <v>Delayed 15 minutes</v>
-      <v>from close</v>
-      <v>from close</v>
     </spb>
     <spb s="0">
       <v>1</v>
@@ -13520,9 +13555,6 @@
     <k n="Year incorporated" t="i"/>
     <k n="`%EntityServiceId" t="i"/>
     <k n="Shares outstanding" t="i"/>
-    <k n="Price (Extended hours)" t="i"/>
-    <k n="Change (Extended hours)" t="i"/>
-    <k n="Change % (Extended hours)" t="i"/>
   </s>
   <s>
     <k n="Price" t="s"/>
@@ -13530,9 +13562,6 @@
     <k n="Change (%)" t="s"/>
     <k n="ExchangeID" t="s"/>
     <k n="Last trade time" t="s"/>
-    <k n="Price (Extended hours)" t="s"/>
-    <k n="Change (Extended hours)" t="s"/>
-    <k n="Change % (Extended hours)" t="s"/>
   </s>
   <s>
     <k n="UniqueName" t="spb"/>
@@ -14017,18 +14046,18 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="257" t="s">
+      <c r="B2" s="256" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="258"/>
-      <c r="E2" s="257" t="s">
+      <c r="C2" s="257"/>
+      <c r="E2" s="256" t="s">
         <v>296</v>
       </c>
-      <c r="F2" s="258"/>
-      <c r="H2" s="257" t="s">
+      <c r="F2" s="257"/>
+      <c r="H2" s="256" t="s">
         <v>338</v>
       </c>
-      <c r="I2" s="258"/>
+      <c r="I2" s="257"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="187" t="s">
@@ -14043,7 +14072,7 @@
       </c>
       <c r="F3" s="189">
         <f ca="1">Statement!AC149</f>
-        <v>7201528.96</v>
+        <v>7390488.8999999994</v>
       </c>
       <c r="H3" s="187" t="str">
         <f>'AVG target price'!B5</f>
@@ -14067,7 +14096,7 @@
       </c>
       <c r="F4" s="190">
         <f ca="1">Statement!AC150</f>
-        <v>5784969.96</v>
+        <v>5973929.8999999994</v>
       </c>
       <c r="H4" s="187" t="str">
         <f>'AVG target price'!B6</f>
@@ -14084,7 +14113,7 @@
       </c>
       <c r="C5" s="210" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>143.68</v>
+        <v>147.44999999999999</v>
       </c>
       <c r="E5" s="187" t="s">
         <v>252</v>
@@ -14106,16 +14135,16 @@
       <c r="B6" s="187" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="210" cm="1">
-        <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>144.19999999999999</v>
+      <c r="C6" s="210" t="e" cm="1" vm="2">
+        <f t="array" ref="C6">_FV(C3,"Price (Extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E6" s="187" t="s">
         <v>246</v>
       </c>
       <c r="F6" s="192">
         <f ca="1">Statement!AC146</f>
-        <v>45.749264830200104</v>
+        <v>46.949673574700761</v>
       </c>
       <c r="H6" s="187" t="str">
         <f>'AVG target price'!B8</f>
@@ -14132,14 +14161,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>-1.48</v>
+        <v>-1.97</v>
       </c>
       <c r="E7" s="188" t="s">
         <v>205</v>
       </c>
       <c r="F7" s="193">
         <f ca="1">Statement!AC147</f>
-        <v>6.1702618801045945</v>
+        <v>6.3321625433005453</v>
       </c>
       <c r="H7" s="186" t="str">
         <f>'AVG target price'!B9</f>
@@ -14154,16 +14183,16 @@
       <c r="B8" s="187" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="6" cm="1">
-        <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>0.52</v>
+      <c r="C8" s="6" t="e" cm="1" vm="3">
+        <f t="array" ref="C8">_FV(C3,"Change (extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E8" s="187" t="s">
         <v>274</v>
       </c>
       <c r="F8" s="194">
         <f ca="1">Statement!AC157</f>
-        <v>3.5106433842626662E-2</v>
+        <v>3.4208832923083077E-2</v>
       </c>
       <c r="H8" s="186" t="str">
         <f>'AVG target price'!B11</f>
@@ -14171,7 +14200,7 @@
       </c>
       <c r="I8" s="215">
         <f ca="1">'AVG target price'!C11</f>
-        <v>0.14518764653533492</v>
+        <v>0.11590750121530648</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -14180,30 +14209,30 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>-1.0196E-2</v>
+        <v>-1.3184E-2</v>
       </c>
       <c r="E9" s="187" t="s">
         <v>297</v>
       </c>
       <c r="F9" s="194">
         <f ca="1">Statement!AC158</f>
-        <v>2.1858274744119555E-2</v>
+        <v>2.129940261264902E-2</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B10" s="187" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="73" cm="1">
-        <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>3.6189999999999998E-3</v>
+      <c r="C10" s="73" t="e" cm="1" vm="4">
+        <f t="array" ref="C10">_FV(C3,"Change % (extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E10" s="187" t="s">
         <v>302</v>
       </c>
       <c r="F10" s="194">
         <f ca="1">Statement!AC160</f>
-        <v>9.665030910324909E-3</v>
+        <v>9.417915504886288E-3</v>
       </c>
       <c r="H10" s="186" t="s">
         <v>429</v>
@@ -14251,7 +14280,7 @@
       </c>
       <c r="C13" s="211" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>1.0487</v>
+        <v>1.0450999999999999</v>
       </c>
       <c r="E13" s="187" t="s">
         <v>104</v>
@@ -14267,7 +14296,7 @@
       </c>
       <c r="C14" s="212" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>1311929</v>
+        <v>1193470</v>
       </c>
       <c r="E14" s="188" t="s">
         <v>105</v>
@@ -14283,7 +14312,7 @@
       </c>
       <c r="F15" s="194">
         <f ca="1">Statement!AC172</f>
-        <v>0.1967025346795245</v>
+        <v>0.19167324640728439</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -14296,10 +14325,10 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="259" t="s">
+      <c r="B17" s="258" t="s">
         <v>90</v>
       </c>
-      <c r="C17" s="259"/>
+      <c r="C17" s="258"/>
       <c r="E17" s="186" t="s">
         <v>305</v>
       </c>
@@ -14372,14 +14401,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="259" t="s">
+      <c r="B25" s="258" t="s">
         <v>107</v>
       </c>
-      <c r="C25" s="259"/>
-      <c r="E25" s="257" t="s">
+      <c r="C25" s="258"/>
+      <c r="E25" s="256" t="s">
         <v>351</v>
       </c>
-      <c r="F25" s="258"/>
+      <c r="F25" s="257"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="186" t="s">
@@ -14388,12 +14417,12 @@
       <c r="C26" s="172">
         <v>0.21</v>
       </c>
-      <c r="E26" s="187" t="e" vm="2">
+      <c r="E26" s="187" t="e" vm="5">
         <v>#VALUE!</v>
       </c>
       <c r="F26" s="221" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>47.84</v>
+        <v>49.63</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -14408,7 +14437,7 @@
       </c>
       <c r="F27" s="222">
         <f ca="1">F26/1000</f>
-        <v>4.7840000000000001E-2</v>
+        <v>4.9630000000000001E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -14428,15 +14457,15 @@
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="256" t="s">
+      <c r="B33" s="259" t="s">
         <v>346</v>
       </c>
-      <c r="C33" s="256"/>
-      <c r="D33" s="256"/>
-      <c r="E33" s="256"/>
-      <c r="F33" s="256"/>
-      <c r="G33" s="256"/>
-      <c r="H33" s="256"/>
+      <c r="C33" s="259"/>
+      <c r="D33" s="259"/>
+      <c r="E33" s="259"/>
+      <c r="F33" s="259"/>
+      <c r="G33" s="259"/>
+      <c r="H33" s="259"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
@@ -14455,24 +14484,24 @@
       </c>
     </row>
     <row r="39" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="256"/>
-      <c r="C39" s="256"/>
-      <c r="D39" s="256"/>
-      <c r="E39" s="256"/>
-      <c r="F39" s="256"/>
-      <c r="G39" s="256"/>
-      <c r="H39" s="256"/>
+      <c r="B39" s="259"/>
+      <c r="C39" s="259"/>
+      <c r="D39" s="259"/>
+      <c r="E39" s="259"/>
+      <c r="F39" s="259"/>
+      <c r="G39" s="259"/>
+      <c r="H39" s="259"/>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B42" s="256" t="s">
+      <c r="B42" s="259" t="s">
         <v>349</v>
       </c>
-      <c r="C42" s="256"/>
-      <c r="D42" s="256"/>
-      <c r="E42" s="256"/>
-      <c r="F42" s="256"/>
-      <c r="G42" s="256"/>
-      <c r="H42" s="256"/>
+      <c r="C42" s="259"/>
+      <c r="D42" s="259"/>
+      <c r="E42" s="259"/>
+      <c r="F42" s="259"/>
+      <c r="G42" s="259"/>
+      <c r="H42" s="259"/>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="41" t="s">
@@ -14511,24 +14540,24 @@
       </c>
     </row>
     <row r="50" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B50" s="256"/>
-      <c r="C50" s="256"/>
-      <c r="D50" s="256"/>
-      <c r="E50" s="256"/>
-      <c r="F50" s="256"/>
-      <c r="G50" s="256"/>
-      <c r="H50" s="256"/>
+      <c r="B50" s="259"/>
+      <c r="C50" s="259"/>
+      <c r="D50" s="259"/>
+      <c r="E50" s="259"/>
+      <c r="F50" s="259"/>
+      <c r="G50" s="259"/>
+      <c r="H50" s="259"/>
     </row>
     <row r="53" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B53" s="256" t="s">
+      <c r="B53" s="259" t="s">
         <v>109</v>
       </c>
-      <c r="C53" s="256"/>
-      <c r="D53" s="256"/>
-      <c r="E53" s="256"/>
-      <c r="F53" s="256"/>
-      <c r="G53" s="256"/>
-      <c r="H53" s="256"/>
+      <c r="C53" s="259"/>
+      <c r="D53" s="259"/>
+      <c r="E53" s="259"/>
+      <c r="F53" s="259"/>
+      <c r="G53" s="259"/>
+      <c r="H53" s="259"/>
     </row>
     <row r="58" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B58" s="41" t="s">
@@ -14599,28 +14628,28 @@
       </c>
     </row>
     <row r="66" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B66" s="256"/>
-      <c r="C66" s="256"/>
-      <c r="D66" s="256"/>
-      <c r="E66" s="256"/>
-      <c r="F66" s="256"/>
-      <c r="G66" s="256"/>
-      <c r="H66" s="256"/>
+      <c r="B66" s="259"/>
+      <c r="C66" s="259"/>
+      <c r="D66" s="259"/>
+      <c r="E66" s="259"/>
+      <c r="F66" s="259"/>
+      <c r="G66" s="259"/>
+      <c r="H66" s="259"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B53:H53"/>
+    <mergeCell ref="B66:H66"/>
+    <mergeCell ref="B33:H33"/>
+    <mergeCell ref="B39:H39"/>
+    <mergeCell ref="B42:H42"/>
+    <mergeCell ref="B50:H50"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="E25:F25"/>
-    <mergeCell ref="B53:H53"/>
-    <mergeCell ref="B66:H66"/>
-    <mergeCell ref="B33:H33"/>
-    <mergeCell ref="B39:H39"/>
-    <mergeCell ref="B42:H42"/>
-    <mergeCell ref="B50:H50"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C10">
     <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
@@ -14690,36 +14719,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="256" t="s">
+      <c r="C2" s="259" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="256"/>
-      <c r="E2" s="256"/>
-      <c r="F2" s="256"/>
-      <c r="G2" s="268"/>
-      <c r="H2" s="269" t="s">
+      <c r="D2" s="259"/>
+      <c r="E2" s="259"/>
+      <c r="F2" s="259"/>
+      <c r="G2" s="265"/>
+      <c r="H2" s="266" t="s">
         <v>114</v>
       </c>
-      <c r="I2" s="256"/>
-      <c r="J2" s="256"/>
-      <c r="K2" s="256"/>
-      <c r="L2" s="256"/>
+      <c r="I2" s="259"/>
+      <c r="J2" s="259"/>
+      <c r="K2" s="259"/>
+      <c r="L2" s="259"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="256" t="s">
+      <c r="S2" s="259" t="s">
         <v>113</v>
       </c>
-      <c r="T2" s="256"/>
-      <c r="U2" s="256"/>
-      <c r="V2" s="256"/>
-      <c r="W2" s="256"/>
-      <c r="X2" s="256"/>
-      <c r="Y2" s="256"/>
-      <c r="Z2" s="256"/>
-      <c r="AA2" s="256" t="s">
+      <c r="T2" s="259"/>
+      <c r="U2" s="259"/>
+      <c r="V2" s="259"/>
+      <c r="W2" s="259"/>
+      <c r="X2" s="259"/>
+      <c r="Y2" s="259"/>
+      <c r="Z2" s="259"/>
+      <c r="AA2" s="259" t="s">
         <v>114</v>
       </c>
-      <c r="AB2" s="256"/>
-      <c r="AC2" s="256"/>
+      <c r="AB2" s="259"/>
+      <c r="AC2" s="259"/>
       <c r="AE2" s="86" t="s">
         <v>85</v>
       </c>
@@ -14730,32 +14759,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="265" t="s">
+      <c r="C4" s="267" t="s">
         <v>116</v>
       </c>
-      <c r="D4" s="265"/>
-      <c r="E4" s="265"/>
-      <c r="F4" s="265"/>
-      <c r="G4" s="265"/>
-      <c r="H4" s="265"/>
-      <c r="I4" s="265"/>
-      <c r="J4" s="265"/>
-      <c r="K4" s="265"/>
-      <c r="L4" s="265"/>
+      <c r="D4" s="267"/>
+      <c r="E4" s="267"/>
+      <c r="F4" s="267"/>
+      <c r="G4" s="267"/>
+      <c r="H4" s="267"/>
+      <c r="I4" s="267"/>
+      <c r="J4" s="267"/>
+      <c r="K4" s="267"/>
+      <c r="L4" s="267"/>
       <c r="O4" s="5"/>
-      <c r="S4" s="266" t="s">
+      <c r="S4" s="268" t="s">
         <v>116</v>
       </c>
-      <c r="T4" s="267"/>
-      <c r="U4" s="267"/>
-      <c r="V4" s="267"/>
-      <c r="W4" s="267"/>
-      <c r="X4" s="267"/>
-      <c r="Y4" s="267"/>
-      <c r="Z4" s="267"/>
-      <c r="AA4" s="267"/>
-      <c r="AB4" s="267"/>
-      <c r="AC4" s="267"/>
+      <c r="T4" s="269"/>
+      <c r="U4" s="269"/>
+      <c r="V4" s="269"/>
+      <c r="W4" s="269"/>
+      <c r="X4" s="269"/>
+      <c r="Y4" s="269"/>
+      <c r="Z4" s="269"/>
+      <c r="AA4" s="269"/>
+      <c r="AB4" s="269"/>
+      <c r="AC4" s="269"/>
       <c r="AE4" s="88"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -15443,33 +15472,33 @@
       <c r="Q12" s="92"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="265" t="s">
+      <c r="C13" s="267" t="s">
         <v>122</v>
       </c>
-      <c r="D13" s="265"/>
-      <c r="E13" s="265"/>
-      <c r="F13" s="265"/>
-      <c r="G13" s="265"/>
-      <c r="H13" s="265"/>
-      <c r="I13" s="265"/>
-      <c r="J13" s="265"/>
-      <c r="K13" s="265"/>
-      <c r="L13" s="265"/>
+      <c r="D13" s="267"/>
+      <c r="E13" s="267"/>
+      <c r="F13" s="267"/>
+      <c r="G13" s="267"/>
+      <c r="H13" s="267"/>
+      <c r="I13" s="267"/>
+      <c r="J13" s="267"/>
+      <c r="K13" s="267"/>
+      <c r="L13" s="267"/>
       <c r="O13" s="5"/>
       <c r="Q13" s="92"/>
-      <c r="S13" s="266" t="s">
+      <c r="S13" s="268" t="s">
         <v>122</v>
       </c>
-      <c r="T13" s="267"/>
-      <c r="U13" s="267"/>
-      <c r="V13" s="267"/>
-      <c r="W13" s="267"/>
-      <c r="X13" s="267"/>
-      <c r="Y13" s="267"/>
-      <c r="Z13" s="267"/>
-      <c r="AA13" s="267"/>
-      <c r="AB13" s="267"/>
-      <c r="AC13" s="267"/>
+      <c r="T13" s="269"/>
+      <c r="U13" s="269"/>
+      <c r="V13" s="269"/>
+      <c r="W13" s="269"/>
+      <c r="X13" s="269"/>
+      <c r="Y13" s="269"/>
+      <c r="Z13" s="269"/>
+      <c r="AA13" s="269"/>
+      <c r="AB13" s="269"/>
+      <c r="AC13" s="269"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B14" s="16" t="s">
@@ -16078,33 +16107,33 @@
       <c r="Q22" s="92"/>
     </row>
     <row r="23" spans="2:31" x14ac:dyDescent="0.2">
-      <c r="C23" s="265" t="s">
+      <c r="C23" s="267" t="s">
         <v>124</v>
       </c>
-      <c r="D23" s="265"/>
-      <c r="E23" s="265"/>
-      <c r="F23" s="265"/>
-      <c r="G23" s="265"/>
-      <c r="H23" s="265"/>
-      <c r="I23" s="265"/>
-      <c r="J23" s="265"/>
-      <c r="K23" s="265"/>
-      <c r="L23" s="265"/>
+      <c r="D23" s="267"/>
+      <c r="E23" s="267"/>
+      <c r="F23" s="267"/>
+      <c r="G23" s="267"/>
+      <c r="H23" s="267"/>
+      <c r="I23" s="267"/>
+      <c r="J23" s="267"/>
+      <c r="K23" s="267"/>
+      <c r="L23" s="267"/>
       <c r="O23" s="5"/>
       <c r="Q23" s="92"/>
-      <c r="S23" s="266" t="s">
+      <c r="S23" s="268" t="s">
         <v>124</v>
       </c>
-      <c r="T23" s="267"/>
-      <c r="U23" s="267"/>
-      <c r="V23" s="267"/>
-      <c r="W23" s="267"/>
-      <c r="X23" s="267"/>
-      <c r="Y23" s="267"/>
-      <c r="Z23" s="267"/>
-      <c r="AA23" s="267"/>
-      <c r="AB23" s="267"/>
-      <c r="AC23" s="267"/>
+      <c r="T23" s="269"/>
+      <c r="U23" s="269"/>
+      <c r="V23" s="269"/>
+      <c r="W23" s="269"/>
+      <c r="X23" s="269"/>
+      <c r="Y23" s="269"/>
+      <c r="Z23" s="269"/>
+      <c r="AA23" s="269"/>
+      <c r="AB23" s="269"/>
+      <c r="AC23" s="269"/>
       <c r="AE23" s="88" t="str">
         <f>AE2</f>
         <v>TTM/YTD</v>
@@ -17423,32 +17452,32 @@
       <c r="O39" s="5"/>
     </row>
     <row r="40" spans="2:31" x14ac:dyDescent="0.2">
-      <c r="C40" s="265" t="s">
+      <c r="C40" s="267" t="s">
         <v>126</v>
       </c>
-      <c r="D40" s="265"/>
-      <c r="E40" s="265"/>
-      <c r="F40" s="265"/>
-      <c r="G40" s="265"/>
-      <c r="H40" s="265"/>
-      <c r="I40" s="265"/>
-      <c r="J40" s="265"/>
-      <c r="K40" s="265"/>
-      <c r="L40" s="265"/>
+      <c r="D40" s="267"/>
+      <c r="E40" s="267"/>
+      <c r="F40" s="267"/>
+      <c r="G40" s="267"/>
+      <c r="H40" s="267"/>
+      <c r="I40" s="267"/>
+      <c r="J40" s="267"/>
+      <c r="K40" s="267"/>
+      <c r="L40" s="267"/>
       <c r="O40" s="5"/>
-      <c r="S40" s="266" t="s">
+      <c r="S40" s="268" t="s">
         <v>126</v>
       </c>
-      <c r="T40" s="267"/>
-      <c r="U40" s="267"/>
-      <c r="V40" s="267"/>
-      <c r="W40" s="267"/>
-      <c r="X40" s="267"/>
-      <c r="Y40" s="267"/>
-      <c r="Z40" s="267"/>
-      <c r="AA40" s="267"/>
-      <c r="AB40" s="267"/>
-      <c r="AC40" s="267"/>
+      <c r="T40" s="269"/>
+      <c r="U40" s="269"/>
+      <c r="V40" s="269"/>
+      <c r="W40" s="269"/>
+      <c r="X40" s="269"/>
+      <c r="Y40" s="269"/>
+      <c r="Z40" s="269"/>
+      <c r="AA40" s="269"/>
+      <c r="AB40" s="269"/>
+      <c r="AC40" s="269"/>
     </row>
     <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -18015,18 +18044,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="C13:L13"/>
+    <mergeCell ref="S13:AC13"/>
+    <mergeCell ref="C23:L23"/>
+    <mergeCell ref="S23:AC23"/>
+    <mergeCell ref="C40:L40"/>
+    <mergeCell ref="S40:AC40"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="S2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
-    <mergeCell ref="C13:L13"/>
-    <mergeCell ref="S13:AC13"/>
-    <mergeCell ref="C23:L23"/>
-    <mergeCell ref="S23:AC23"/>
-    <mergeCell ref="C40:L40"/>
-    <mergeCell ref="S40:AC40"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -18060,35 +18089,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="256" t="s">
+      <c r="C2" s="259" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="256"/>
-      <c r="E2" s="256"/>
-      <c r="F2" s="256"/>
-      <c r="G2" s="268"/>
-      <c r="H2" s="269" t="s">
+      <c r="D2" s="259"/>
+      <c r="E2" s="259"/>
+      <c r="F2" s="259"/>
+      <c r="G2" s="265"/>
+      <c r="H2" s="266" t="s">
         <v>114</v>
       </c>
-      <c r="I2" s="256"/>
-      <c r="J2" s="256"/>
-      <c r="K2" s="256"/>
-      <c r="L2" s="256"/>
-      <c r="P2" s="256" t="s">
+      <c r="I2" s="259"/>
+      <c r="J2" s="259"/>
+      <c r="K2" s="259"/>
+      <c r="L2" s="259"/>
+      <c r="P2" s="259" t="s">
         <v>113</v>
       </c>
-      <c r="Q2" s="256"/>
-      <c r="R2" s="256"/>
-      <c r="S2" s="256"/>
-      <c r="T2" s="256"/>
-      <c r="U2" s="256"/>
-      <c r="V2" s="256"/>
-      <c r="W2" s="256"/>
-      <c r="X2" s="256" t="s">
+      <c r="Q2" s="259"/>
+      <c r="R2" s="259"/>
+      <c r="S2" s="259"/>
+      <c r="T2" s="259"/>
+      <c r="U2" s="259"/>
+      <c r="V2" s="259"/>
+      <c r="W2" s="259"/>
+      <c r="X2" s="259" t="s">
         <v>114</v>
       </c>
-      <c r="Y2" s="256"/>
-      <c r="Z2" s="256"/>
+      <c r="Y2" s="259"/>
+      <c r="Z2" s="259"/>
       <c r="AB2" s="86" t="s">
         <v>115</v>
       </c>
@@ -18097,31 +18126,31 @@
     <row r="4" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="265" t="s">
+      <c r="C4" s="267" t="s">
         <v>116</v>
       </c>
-      <c r="D4" s="265"/>
-      <c r="E4" s="265"/>
-      <c r="F4" s="265"/>
-      <c r="G4" s="265"/>
-      <c r="H4" s="265"/>
-      <c r="I4" s="265"/>
-      <c r="J4" s="265"/>
-      <c r="K4" s="265"/>
-      <c r="L4" s="265"/>
-      <c r="P4" s="267" t="s">
+      <c r="D4" s="267"/>
+      <c r="E4" s="267"/>
+      <c r="F4" s="267"/>
+      <c r="G4" s="267"/>
+      <c r="H4" s="267"/>
+      <c r="I4" s="267"/>
+      <c r="J4" s="267"/>
+      <c r="K4" s="267"/>
+      <c r="L4" s="267"/>
+      <c r="P4" s="269" t="s">
         <v>116</v>
       </c>
-      <c r="Q4" s="267"/>
-      <c r="R4" s="267"/>
-      <c r="S4" s="267"/>
-      <c r="T4" s="267"/>
-      <c r="U4" s="267"/>
-      <c r="V4" s="267"/>
-      <c r="W4" s="267"/>
-      <c r="X4" s="267"/>
-      <c r="Y4" s="267"/>
-      <c r="Z4" s="267"/>
+      <c r="Q4" s="269"/>
+      <c r="R4" s="269"/>
+      <c r="S4" s="269"/>
+      <c r="T4" s="269"/>
+      <c r="U4" s="269"/>
+      <c r="V4" s="269"/>
+      <c r="W4" s="269"/>
+      <c r="X4" s="269"/>
+      <c r="Y4" s="269"/>
+      <c r="Z4" s="269"/>
       <c r="AB4" s="88"/>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
@@ -18316,32 +18345,32 @@
       <c r="N8" s="92"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C9" s="265" t="s">
+      <c r="C9" s="267" t="s">
         <v>129</v>
       </c>
-      <c r="D9" s="265"/>
-      <c r="E9" s="265"/>
-      <c r="F9" s="265"/>
-      <c r="G9" s="265"/>
-      <c r="H9" s="265"/>
-      <c r="I9" s="265"/>
-      <c r="J9" s="265"/>
-      <c r="K9" s="265"/>
-      <c r="L9" s="265"/>
+      <c r="D9" s="267"/>
+      <c r="E9" s="267"/>
+      <c r="F9" s="267"/>
+      <c r="G9" s="267"/>
+      <c r="H9" s="267"/>
+      <c r="I9" s="267"/>
+      <c r="J9" s="267"/>
+      <c r="K9" s="267"/>
+      <c r="L9" s="267"/>
       <c r="N9" s="92"/>
-      <c r="P9" s="267" t="s">
+      <c r="P9" s="269" t="s">
         <v>130</v>
       </c>
-      <c r="Q9" s="267"/>
-      <c r="R9" s="267"/>
-      <c r="S9" s="267"/>
-      <c r="T9" s="267"/>
-      <c r="U9" s="267"/>
-      <c r="V9" s="267"/>
-      <c r="W9" s="267"/>
-      <c r="X9" s="267"/>
-      <c r="Y9" s="267"/>
-      <c r="Z9" s="267"/>
+      <c r="Q9" s="269"/>
+      <c r="R9" s="269"/>
+      <c r="S9" s="269"/>
+      <c r="T9" s="269"/>
+      <c r="U9" s="269"/>
+      <c r="V9" s="269"/>
+      <c r="W9" s="269"/>
+      <c r="X9" s="269"/>
+      <c r="Y9" s="269"/>
+      <c r="Z9" s="269"/>
       <c r="AB9" s="88">
         <f>AB4</f>
         <v>0</v>
@@ -18911,31 +18940,31 @@
       </c>
     </row>
     <row r="18" spans="2:26" x14ac:dyDescent="0.2">
-      <c r="C18" s="265" t="s">
+      <c r="C18" s="267" t="s">
         <v>132</v>
       </c>
-      <c r="D18" s="265"/>
-      <c r="E18" s="265"/>
-      <c r="F18" s="265"/>
-      <c r="G18" s="265"/>
-      <c r="H18" s="265"/>
-      <c r="I18" s="265"/>
-      <c r="J18" s="265"/>
-      <c r="K18" s="265"/>
-      <c r="L18" s="265"/>
-      <c r="P18" s="267" t="s">
+      <c r="D18" s="267"/>
+      <c r="E18" s="267"/>
+      <c r="F18" s="267"/>
+      <c r="G18" s="267"/>
+      <c r="H18" s="267"/>
+      <c r="I18" s="267"/>
+      <c r="J18" s="267"/>
+      <c r="K18" s="267"/>
+      <c r="L18" s="267"/>
+      <c r="P18" s="269" t="s">
         <v>132</v>
       </c>
-      <c r="Q18" s="267"/>
-      <c r="R18" s="267"/>
-      <c r="S18" s="267"/>
-      <c r="T18" s="267"/>
-      <c r="U18" s="267"/>
-      <c r="V18" s="267"/>
-      <c r="W18" s="267"/>
-      <c r="X18" s="267"/>
-      <c r="Y18" s="267"/>
-      <c r="Z18" s="267"/>
+      <c r="Q18" s="269"/>
+      <c r="R18" s="269"/>
+      <c r="S18" s="269"/>
+      <c r="T18" s="269"/>
+      <c r="U18" s="269"/>
+      <c r="V18" s="269"/>
+      <c r="W18" s="269"/>
+      <c r="X18" s="269"/>
+      <c r="Y18" s="269"/>
+      <c r="Z18" s="269"/>
     </row>
     <row r="19" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -19495,20 +19524,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="256" t="s">
+      <c r="C3" s="259" t="s">
         <v>113</v>
       </c>
-      <c r="D3" s="256"/>
-      <c r="E3" s="256"/>
-      <c r="F3" s="256"/>
-      <c r="G3" s="268"/>
-      <c r="H3" s="269" t="s">
+      <c r="D3" s="259"/>
+      <c r="E3" s="259"/>
+      <c r="F3" s="259"/>
+      <c r="G3" s="265"/>
+      <c r="H3" s="266" t="s">
         <v>114</v>
       </c>
-      <c r="I3" s="256"/>
-      <c r="J3" s="256"/>
-      <c r="K3" s="256"/>
-      <c r="L3" s="256"/>
+      <c r="I3" s="259"/>
+      <c r="J3" s="259"/>
+      <c r="K3" s="259"/>
+      <c r="L3" s="259"/>
       <c r="P3" s="270"/>
       <c r="Q3" s="270"/>
       <c r="R3" s="270"/>
@@ -19526,18 +19555,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="87"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="265" t="s">
+      <c r="C5" s="267" t="s">
         <v>116</v>
       </c>
-      <c r="D5" s="265"/>
-      <c r="E5" s="265"/>
-      <c r="F5" s="265"/>
-      <c r="G5" s="265"/>
-      <c r="H5" s="265"/>
-      <c r="I5" s="265"/>
-      <c r="J5" s="265"/>
-      <c r="K5" s="265"/>
-      <c r="L5" s="265"/>
+      <c r="D5" s="267"/>
+      <c r="E5" s="267"/>
+      <c r="F5" s="267"/>
+      <c r="G5" s="267"/>
+      <c r="H5" s="267"/>
+      <c r="I5" s="267"/>
+      <c r="J5" s="267"/>
+      <c r="K5" s="267"/>
+      <c r="L5" s="267"/>
       <c r="P5" s="270"/>
       <c r="Q5" s="270"/>
       <c r="R5" s="270"/>
@@ -19734,18 +19763,18 @@
       <c r="N10" s="92"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="265" t="s">
+      <c r="C11" s="267" t="s">
         <v>136</v>
       </c>
-      <c r="D11" s="265"/>
-      <c r="E11" s="265"/>
-      <c r="F11" s="265"/>
-      <c r="G11" s="265"/>
-      <c r="H11" s="265"/>
-      <c r="I11" s="265"/>
-      <c r="J11" s="265"/>
-      <c r="K11" s="265"/>
-      <c r="L11" s="265"/>
+      <c r="D11" s="267"/>
+      <c r="E11" s="267"/>
+      <c r="F11" s="267"/>
+      <c r="G11" s="267"/>
+      <c r="H11" s="267"/>
+      <c r="I11" s="267"/>
+      <c r="J11" s="267"/>
+      <c r="K11" s="267"/>
+      <c r="L11" s="267"/>
       <c r="N11" s="92"/>
       <c r="P11" s="270"/>
       <c r="Q11" s="270"/>
@@ -19999,18 +20028,18 @@
       <c r="D16" s="24"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="265" t="s">
+      <c r="C18" s="267" t="s">
         <v>141</v>
       </c>
-      <c r="D18" s="265"/>
-      <c r="E18" s="265"/>
-      <c r="F18" s="265"/>
-      <c r="G18" s="265"/>
-      <c r="H18" s="265"/>
-      <c r="I18" s="265"/>
-      <c r="J18" s="265"/>
-      <c r="K18" s="265"/>
-      <c r="L18" s="265"/>
+      <c r="D18" s="267"/>
+      <c r="E18" s="267"/>
+      <c r="F18" s="267"/>
+      <c r="G18" s="267"/>
+      <c r="H18" s="267"/>
+      <c r="I18" s="267"/>
+      <c r="J18" s="267"/>
+      <c r="K18" s="267"/>
+      <c r="L18" s="267"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -20228,18 +20257,18 @@
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="111"/>
-      <c r="C26" s="265" t="s">
+      <c r="C26" s="267" t="s">
         <v>147</v>
       </c>
-      <c r="D26" s="265"/>
-      <c r="E26" s="265"/>
-      <c r="F26" s="265"/>
-      <c r="G26" s="265"/>
-      <c r="H26" s="265"/>
-      <c r="I26" s="265"/>
-      <c r="J26" s="265"/>
-      <c r="K26" s="265"/>
-      <c r="L26" s="265"/>
+      <c r="D26" s="267"/>
+      <c r="E26" s="267"/>
+      <c r="F26" s="267"/>
+      <c r="G26" s="267"/>
+      <c r="H26" s="267"/>
+      <c r="I26" s="267"/>
+      <c r="J26" s="267"/>
+      <c r="K26" s="267"/>
+      <c r="L26" s="267"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="16" t="s">
@@ -20431,18 +20460,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="111"/>
-      <c r="C33" s="265" t="s">
+      <c r="C33" s="267" t="s">
         <v>151</v>
       </c>
-      <c r="D33" s="265"/>
-      <c r="E33" s="265"/>
-      <c r="F33" s="265"/>
-      <c r="G33" s="265"/>
-      <c r="H33" s="265"/>
-      <c r="I33" s="265"/>
-      <c r="J33" s="265"/>
-      <c r="K33" s="265"/>
-      <c r="L33" s="265"/>
+      <c r="D33" s="267"/>
+      <c r="E33" s="267"/>
+      <c r="F33" s="267"/>
+      <c r="G33" s="267"/>
+      <c r="H33" s="267"/>
+      <c r="I33" s="267"/>
+      <c r="J33" s="267"/>
+      <c r="K33" s="267"/>
+      <c r="L33" s="267"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
@@ -20626,18 +20655,18 @@
       <c r="C39" s="127"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="265" t="s">
+      <c r="C40" s="267" t="s">
         <v>154</v>
       </c>
-      <c r="D40" s="265"/>
-      <c r="E40" s="265"/>
-      <c r="F40" s="265"/>
-      <c r="G40" s="265"/>
-      <c r="H40" s="265"/>
-      <c r="I40" s="265"/>
-      <c r="J40" s="265"/>
-      <c r="K40" s="265"/>
-      <c r="L40" s="265"/>
+      <c r="D40" s="267"/>
+      <c r="E40" s="267"/>
+      <c r="F40" s="267"/>
+      <c r="G40" s="267"/>
+      <c r="H40" s="267"/>
+      <c r="I40" s="267"/>
+      <c r="J40" s="267"/>
+      <c r="K40" s="267"/>
+      <c r="L40" s="267"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -20901,6 +20930,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -20908,12 +20943,6 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -20951,20 +20980,20 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="256" t="s">
+      <c r="C2" s="259" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="256"/>
-      <c r="E2" s="256"/>
-      <c r="F2" s="256"/>
-      <c r="G2" s="268"/>
-      <c r="H2" s="269" t="s">
+      <c r="D2" s="259"/>
+      <c r="E2" s="259"/>
+      <c r="F2" s="259"/>
+      <c r="G2" s="265"/>
+      <c r="H2" s="266" t="s">
         <v>114</v>
       </c>
-      <c r="I2" s="256"/>
-      <c r="J2" s="256"/>
-      <c r="K2" s="256"/>
-      <c r="L2" s="256"/>
+      <c r="I2" s="259"/>
+      <c r="J2" s="259"/>
+      <c r="K2" s="259"/>
+      <c r="L2" s="259"/>
       <c r="S2" s="270"/>
       <c r="T2" s="270"/>
       <c r="U2" s="270"/>
@@ -20982,18 +21011,18 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="265" t="s">
+      <c r="C4" s="267" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="265"/>
-      <c r="E4" s="265"/>
-      <c r="F4" s="265"/>
-      <c r="G4" s="265"/>
-      <c r="H4" s="265"/>
-      <c r="I4" s="265"/>
-      <c r="J4" s="265"/>
-      <c r="K4" s="265"/>
-      <c r="L4" s="265"/>
+      <c r="D4" s="267"/>
+      <c r="E4" s="267"/>
+      <c r="F4" s="267"/>
+      <c r="G4" s="267"/>
+      <c r="H4" s="267"/>
+      <c r="I4" s="267"/>
+      <c r="J4" s="267"/>
+      <c r="K4" s="267"/>
+      <c r="L4" s="267"/>
       <c r="S4" s="270"/>
       <c r="T4" s="270"/>
       <c r="U4" s="270"/>
@@ -21367,18 +21396,18 @@
       <c r="AE10" s="64"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="265" t="s">
+      <c r="C13" s="267" t="s">
         <v>162</v>
       </c>
-      <c r="D13" s="265"/>
-      <c r="E13" s="265"/>
-      <c r="F13" s="265"/>
-      <c r="G13" s="265"/>
-      <c r="H13" s="265"/>
-      <c r="I13" s="265"/>
-      <c r="J13" s="265"/>
-      <c r="K13" s="265"/>
-      <c r="L13" s="265"/>
+      <c r="D13" s="267"/>
+      <c r="E13" s="267"/>
+      <c r="F13" s="267"/>
+      <c r="G13" s="267"/>
+      <c r="H13" s="267"/>
+      <c r="I13" s="267"/>
+      <c r="J13" s="267"/>
+      <c r="K13" s="267"/>
+      <c r="L13" s="267"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="12">
@@ -21427,24 +21456,24 @@
         <v>74</v>
       </c>
       <c r="C15" s="131">
-        <f>-Statement!M83</f>
+        <f>Statement!M83</f>
         <v>0</v>
       </c>
       <c r="D15" s="131">
-        <f>-Statement!N83</f>
-        <v>-1.599699843099802E-2</v>
+        <f>Statement!N83</f>
+        <v>1.599699843099802E-2</v>
       </c>
       <c r="E15" s="131">
-        <f>-Statement!O83</f>
-        <v>-9.6191708387241948E-2</v>
+        <f>Statement!O83</f>
+        <v>9.6191708387241948E-2</v>
       </c>
       <c r="F15" s="131">
-        <f>-Statement!P83</f>
-        <v>-0.13422477665044083</v>
+        <f>Statement!P83</f>
+        <v>0.13422477665044083</v>
       </c>
       <c r="G15" s="132">
-        <f>-Statement!Q83</f>
-        <v>-0.13730058659064745</v>
+        <f>Statement!Q83</f>
+        <v>0.13730058659064745</v>
       </c>
       <c r="H15" s="131">
         <f>Overview!$C$26</f>
@@ -21471,18 +21500,18 @@
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C18" s="265" t="s">
+      <c r="C18" s="267" t="s">
         <v>163</v>
       </c>
-      <c r="D18" s="265"/>
-      <c r="E18" s="265"/>
-      <c r="F18" s="265"/>
-      <c r="G18" s="265"/>
-      <c r="H18" s="265"/>
-      <c r="I18" s="265"/>
-      <c r="J18" s="265"/>
-      <c r="K18" s="265"/>
-      <c r="L18" s="265"/>
+      <c r="D18" s="267"/>
+      <c r="E18" s="267"/>
+      <c r="F18" s="267"/>
+      <c r="G18" s="267"/>
+      <c r="H18" s="267"/>
+      <c r="I18" s="267"/>
+      <c r="J18" s="267"/>
+      <c r="K18" s="267"/>
+      <c r="L18" s="267"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -21674,18 +21703,18 @@
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C25" s="265" t="s">
+      <c r="C25" s="267" t="s">
         <v>271</v>
       </c>
-      <c r="D25" s="265"/>
-      <c r="E25" s="265"/>
-      <c r="F25" s="265"/>
-      <c r="G25" s="265"/>
-      <c r="H25" s="265"/>
-      <c r="I25" s="265"/>
-      <c r="J25" s="265"/>
-      <c r="K25" s="265"/>
-      <c r="L25" s="265"/>
+      <c r="D25" s="267"/>
+      <c r="E25" s="267"/>
+      <c r="F25" s="267"/>
+      <c r="G25" s="267"/>
+      <c r="H25" s="267"/>
+      <c r="I25" s="267"/>
+      <c r="J25" s="267"/>
+      <c r="K25" s="267"/>
+      <c r="L25" s="267"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B26" s="16" t="s">
@@ -21742,19 +21771,19 @@
       </c>
       <c r="D27" s="128">
         <f t="shared" ref="D27:L27" si="6">D10*(1-D15)</f>
-        <v>-66237.924312708914</v>
+        <v>-64152.075687291086</v>
       </c>
       <c r="E27" s="128">
         <f t="shared" si="6"/>
-        <v>-14534.40586150644</v>
+        <v>-11983.59413849356</v>
       </c>
       <c r="F27" s="128">
         <f t="shared" si="6"/>
-        <v>70996.799894434342</v>
+        <v>54193.200105565651</v>
       </c>
       <c r="G27" s="133">
         <f t="shared" si="6"/>
-        <v>154183.84052409406</v>
+        <v>116956.15947590592</v>
       </c>
       <c r="H27" s="128">
         <f t="shared" si="6"/>
@@ -21787,19 +21816,19 @@
       </c>
       <c r="D28" s="95">
         <f t="shared" ref="D28:L28" si="7">D27+D20-D21+D22</f>
-        <v>-36951.924312708914</v>
+        <v>-34866.075687291086</v>
       </c>
       <c r="E28" s="95">
         <f t="shared" si="7"/>
-        <v>13774.594138493558</v>
+        <v>16325.405861506442</v>
       </c>
       <c r="F28" s="95">
         <f t="shared" si="7"/>
-        <v>136631.79989443434</v>
+        <v>119828.20010556566</v>
       </c>
       <c r="G28" s="129">
         <f t="shared" si="7"/>
-        <v>190141.84052409406</v>
+        <v>152914.15947590594</v>
       </c>
       <c r="H28" s="95">
         <f t="shared" si="7"/>
@@ -21823,18 +21852,18 @@
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C31" s="265" t="s">
+      <c r="C31" s="267" t="s">
         <v>78</v>
       </c>
-      <c r="D31" s="265"/>
-      <c r="E31" s="265"/>
-      <c r="F31" s="265"/>
-      <c r="G31" s="265"/>
-      <c r="H31" s="265"/>
-      <c r="I31" s="265"/>
-      <c r="J31" s="265"/>
-      <c r="K31" s="265"/>
-      <c r="L31" s="265"/>
+      <c r="D31" s="267"/>
+      <c r="E31" s="267"/>
+      <c r="F31" s="267"/>
+      <c r="G31" s="267"/>
+      <c r="H31" s="267"/>
+      <c r="I31" s="267"/>
+      <c r="J31" s="267"/>
+      <c r="K31" s="267"/>
+      <c r="L31" s="267"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="16" t="s">
@@ -21973,16 +22002,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="S4:AC4"/>
+    <mergeCell ref="C13:L13"/>
+    <mergeCell ref="C18:L18"/>
     <mergeCell ref="C31:L31"/>
     <mergeCell ref="C25:L25"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="S2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="S4:AC4"/>
-    <mergeCell ref="C13:L13"/>
-    <mergeCell ref="C18:L18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -22045,10 +22074,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="256" t="s">
+      <c r="B4" s="259" t="s">
         <v>170</v>
       </c>
-      <c r="C4" s="256"/>
+      <c r="C4" s="259"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -22065,7 +22094,7 @@
       </c>
       <c r="C6" s="135">
         <f ca="1">Overview!C5</f>
-        <v>143.68</v>
+        <v>147.44999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22074,7 +22103,7 @@
       </c>
       <c r="C7" s="136">
         <f ca="1">C5*C6</f>
-        <v>7201528.96</v>
+        <v>7390488.8999999994</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22092,7 +22121,7 @@
       </c>
       <c r="C9" s="137">
         <f ca="1">Overview!F27</f>
-        <v>4.7840000000000001E-2</v>
+        <v>4.9630000000000001E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22101,7 +22130,7 @@
       </c>
       <c r="C10" s="135">
         <f ca="1">Overview!C13</f>
-        <v>1.0487</v>
+        <v>1.0450999999999999</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22133,10 +22162,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="256" t="s">
+      <c r="B15" s="259" t="s">
         <v>177</v>
       </c>
-      <c r="C15" s="256"/>
+      <c r="C15" s="259"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -22171,7 +22200,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>9.3982800000000005E-2</v>
+        <v>9.5614399999999988E-2</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22180,7 +22209,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>9.3982800000000005E-2</v>
+        <v>9.5614399999999988E-2</v>
       </c>
     </row>
   </sheetData>
@@ -22225,20 +22254,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="256" t="s">
+      <c r="C3" s="259" t="s">
         <v>113</v>
       </c>
-      <c r="D3" s="256"/>
-      <c r="E3" s="256"/>
-      <c r="F3" s="256"/>
-      <c r="G3" s="268"/>
-      <c r="H3" s="269" t="s">
+      <c r="D3" s="259"/>
+      <c r="E3" s="259"/>
+      <c r="F3" s="259"/>
+      <c r="G3" s="265"/>
+      <c r="H3" s="266" t="s">
         <v>114</v>
       </c>
-      <c r="I3" s="256"/>
-      <c r="J3" s="256"/>
-      <c r="K3" s="256"/>
-      <c r="L3" s="256"/>
+      <c r="I3" s="259"/>
+      <c r="J3" s="259"/>
+      <c r="K3" s="259"/>
+      <c r="L3" s="259"/>
       <c r="P3" s="270"/>
       <c r="Q3" s="270"/>
       <c r="R3" s="270"/>
@@ -22256,18 +22285,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="87"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="265" t="s">
+      <c r="C5" s="267" t="s">
         <v>184</v>
       </c>
-      <c r="D5" s="265"/>
-      <c r="E5" s="265"/>
-      <c r="F5" s="265"/>
-      <c r="G5" s="265"/>
-      <c r="H5" s="265"/>
-      <c r="I5" s="265"/>
-      <c r="J5" s="265"/>
-      <c r="K5" s="265"/>
-      <c r="L5" s="265"/>
+      <c r="D5" s="267"/>
+      <c r="E5" s="267"/>
+      <c r="F5" s="267"/>
+      <c r="G5" s="267"/>
+      <c r="H5" s="267"/>
+      <c r="I5" s="267"/>
+      <c r="J5" s="267"/>
+      <c r="K5" s="267"/>
+      <c r="L5" s="267"/>
       <c r="P5" s="270"/>
       <c r="Q5" s="270"/>
       <c r="R5" s="270"/>
@@ -22349,19 +22378,19 @@
       </c>
       <c r="D7" s="114">
         <f>'FCF &amp; Other'!D28</f>
-        <v>-36951.924312708914</v>
+        <v>-34866.075687291086</v>
       </c>
       <c r="E7" s="114">
         <f>'FCF &amp; Other'!E28</f>
-        <v>13774.594138493558</v>
+        <v>16325.405861506442</v>
       </c>
       <c r="F7" s="114">
         <f>'FCF &amp; Other'!F28</f>
-        <v>136631.79989443434</v>
+        <v>119828.20010556566</v>
       </c>
       <c r="G7" s="115">
         <f>'FCF &amp; Other'!G28</f>
-        <v>190141.84052409406</v>
+        <v>152914.15947590594</v>
       </c>
       <c r="H7" s="114">
         <f>'FCF &amp; Other'!H28</f>
@@ -22524,10 +22553,10 @@
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="256" t="s">
+      <c r="B13" s="259" t="s">
         <v>188</v>
       </c>
-      <c r="C13" s="256"/>
+      <c r="C13" s="259"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -22547,10 +22576,10 @@
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="256" t="s">
+      <c r="B18" s="259" t="s">
         <v>190</v>
       </c>
-      <c r="C18" s="256"/>
+      <c r="C18" s="259"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -22664,37 +22693,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="256" t="s">
+      <c r="C2" s="259" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="256"/>
-      <c r="E2" s="256"/>
-      <c r="F2" s="256"/>
-      <c r="G2" s="268"/>
-      <c r="H2" s="269" t="s">
+      <c r="D2" s="259"/>
+      <c r="E2" s="259"/>
+      <c r="F2" s="259"/>
+      <c r="G2" s="265"/>
+      <c r="H2" s="266" t="s">
         <v>114</v>
       </c>
-      <c r="I2" s="256"/>
-      <c r="J2" s="256"/>
-      <c r="K2" s="256"/>
-      <c r="L2" s="256"/>
+      <c r="I2" s="259"/>
+      <c r="J2" s="259"/>
+      <c r="K2" s="259"/>
+      <c r="L2" s="259"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="265" t="s">
+      <c r="C4" s="267" t="s">
         <v>198</v>
       </c>
-      <c r="D4" s="265"/>
-      <c r="E4" s="265"/>
-      <c r="F4" s="265"/>
-      <c r="G4" s="265"/>
-      <c r="H4" s="265"/>
-      <c r="I4" s="265"/>
-      <c r="J4" s="265"/>
-      <c r="K4" s="265"/>
-      <c r="L4" s="265"/>
+      <c r="D4" s="267"/>
+      <c r="E4" s="267"/>
+      <c r="F4" s="267"/>
+      <c r="G4" s="267"/>
+      <c r="H4" s="267"/>
+      <c r="I4" s="267"/>
+      <c r="J4" s="267"/>
+      <c r="K4" s="267"/>
+      <c r="L4" s="267"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -22843,19 +22872,19 @@
       </c>
       <c r="D8" s="93">
         <f>'FCF &amp; Other'!D28</f>
-        <v>-36951.924312708914</v>
+        <v>-34866.075687291086</v>
       </c>
       <c r="E8" s="93">
         <f>'FCF &amp; Other'!E28</f>
-        <v>13774.594138493558</v>
+        <v>16325.405861506442</v>
       </c>
       <c r="F8" s="93">
         <f>'FCF &amp; Other'!F28</f>
-        <v>136631.79989443434</v>
+        <v>119828.20010556566</v>
       </c>
       <c r="G8" s="94">
         <f>'FCF &amp; Other'!G28</f>
-        <v>190141.84052409406</v>
+        <v>152914.15947590594</v>
       </c>
       <c r="H8" s="93">
         <f>'FCF &amp; Other'!H28</f>
@@ -22883,18 +22912,18 @@
       <c r="N9" s="92"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C10" s="265" t="s">
+      <c r="C10" s="267" t="s">
         <v>122</v>
       </c>
-      <c r="D10" s="265"/>
-      <c r="E10" s="265"/>
-      <c r="F10" s="265"/>
-      <c r="G10" s="265"/>
-      <c r="H10" s="265"/>
-      <c r="I10" s="265"/>
-      <c r="J10" s="265"/>
-      <c r="K10" s="265"/>
-      <c r="L10" s="265"/>
+      <c r="D10" s="267"/>
+      <c r="E10" s="267"/>
+      <c r="F10" s="267"/>
+      <c r="G10" s="267"/>
+      <c r="H10" s="267"/>
+      <c r="I10" s="267"/>
+      <c r="J10" s="267"/>
+      <c r="K10" s="267"/>
+      <c r="L10" s="267"/>
       <c r="N10" s="92"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -23045,26 +23074,26 @@
 IF(D8=0,0,IF(D8&gt;0,1,-1)),
 (D8-C8)/ABS(C8)
 )</f>
-        <v>2.0154743511112804E-2</v>
+        <v>7.5464687969583E-2</v>
       </c>
       <c r="E14" s="96">
         <f t="shared" ref="E14:L14" si="3">IF(D8=0,
 IF(E8=0,0,IF(E8&gt;0,1,-1)),
 (E8-D8)/ABS(D8)
 )</f>
-        <v>1.3727706850101997</v>
+        <v>1.4682318138676318</v>
       </c>
       <c r="F14" s="96">
         <f t="shared" si="3"/>
-        <v>8.9191162019512618</v>
+        <v>6.3399829151021425</v>
       </c>
       <c r="G14" s="97">
         <f t="shared" si="3"/>
-        <v>0.39163679810266072</v>
+        <v>0.2761116276568652</v>
       </c>
       <c r="H14" s="96">
         <f t="shared" si="3"/>
-        <v>-4.9271998561848156E-2</v>
+        <v>0.18218726539661903</v>
       </c>
       <c r="I14" s="96">
         <f t="shared" si="3"/>
@@ -23088,18 +23117,18 @@
       <c r="N15" s="92"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C16" s="265" t="s">
+      <c r="C16" s="267" t="s">
         <v>200</v>
       </c>
-      <c r="D16" s="265"/>
-      <c r="E16" s="265"/>
-      <c r="F16" s="265"/>
-      <c r="G16" s="265"/>
-      <c r="H16" s="265"/>
-      <c r="I16" s="265"/>
-      <c r="J16" s="265"/>
-      <c r="K16" s="265"/>
-      <c r="L16" s="265"/>
+      <c r="D16" s="267"/>
+      <c r="E16" s="267"/>
+      <c r="F16" s="267"/>
+      <c r="G16" s="267"/>
+      <c r="H16" s="267"/>
+      <c r="I16" s="267"/>
+      <c r="J16" s="267"/>
+      <c r="K16" s="267"/>
+      <c r="L16" s="267"/>
       <c r="N16" s="92"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
@@ -23233,18 +23262,18 @@
       <c r="N20" s="92"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C21" s="265" t="s">
+      <c r="C21" s="267" t="s">
         <v>203</v>
       </c>
-      <c r="D21" s="265"/>
-      <c r="E21" s="265"/>
-      <c r="F21" s="265"/>
-      <c r="G21" s="265"/>
-      <c r="H21" s="265"/>
-      <c r="I21" s="265"/>
-      <c r="J21" s="265"/>
-      <c r="K21" s="265"/>
-      <c r="L21" s="265"/>
+      <c r="D21" s="267"/>
+      <c r="E21" s="267"/>
+      <c r="F21" s="267"/>
+      <c r="G21" s="267"/>
+      <c r="H21" s="267"/>
+      <c r="I21" s="267"/>
+      <c r="J21" s="267"/>
+      <c r="K21" s="267"/>
+      <c r="L21" s="267"/>
       <c r="N21" s="92"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
@@ -23328,18 +23357,18 @@
       <c r="N25" s="92"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C26" s="265" t="s">
+      <c r="C26" s="267" t="s">
         <v>204</v>
       </c>
-      <c r="D26" s="265"/>
-      <c r="E26" s="265"/>
-      <c r="F26" s="265"/>
-      <c r="G26" s="265"/>
-      <c r="H26" s="265"/>
-      <c r="I26" s="265"/>
-      <c r="J26" s="265"/>
-      <c r="K26" s="265"/>
-      <c r="L26" s="265"/>
+      <c r="D26" s="267"/>
+      <c r="E26" s="267"/>
+      <c r="F26" s="267"/>
+      <c r="G26" s="267"/>
+      <c r="H26" s="267"/>
+      <c r="I26" s="267"/>
+      <c r="J26" s="267"/>
+      <c r="K26" s="267"/>
+      <c r="L26" s="267"/>
       <c r="N26" s="92"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
@@ -23581,19 +23610,19 @@
       </c>
       <c r="D34" s="151">
         <f t="shared" ref="D34:G34" si="13">D32/D8</f>
-        <v>-59.518445680610597</v>
+        <v>-63.07911219276297</v>
       </c>
       <c r="E34" s="151">
         <f t="shared" si="13"/>
-        <v>711.88345742957847</v>
+        <v>600.65310370759448</v>
       </c>
       <c r="F34" s="151">
         <f t="shared" si="13"/>
-        <v>104.96317995576803</v>
+        <v>119.68224664449323</v>
       </c>
       <c r="G34" s="152">
         <f t="shared" si="13"/>
-        <v>38.303335710946961</v>
+        <v>47.628465377264675</v>
       </c>
       <c r="H34" s="139"/>
       <c r="I34" s="139"/>
@@ -23609,10 +23638,10 @@
       <c r="N36" s="92"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B37" s="256" t="s">
+      <c r="B37" s="259" t="s">
         <v>209</v>
       </c>
-      <c r="C37" s="256"/>
+      <c r="C37" s="259"/>
       <c r="N37" s="92"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
@@ -23705,10 +23734,10 @@
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B49" s="256" t="s">
+      <c r="B49" s="259" t="s">
         <v>214</v>
       </c>
-      <c r="C49" s="256"/>
+      <c r="C49" s="259"/>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B50" s="1" t="s">
@@ -23764,10 +23793,10 @@
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B57" s="256" t="s">
+      <c r="B57" s="259" t="s">
         <v>332</v>
       </c>
-      <c r="C57" s="256"/>
+      <c r="C57" s="259"/>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B58" s="1" t="s">
@@ -23907,10 +23936,10 @@
       <c r="N3" s="92"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="256" t="s">
+      <c r="B4" s="259" t="s">
         <v>219</v>
       </c>
-      <c r="C4" s="256"/>
+      <c r="C4" s="259"/>
       <c r="N4" s="92"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -23964,7 +23993,7 @@
       </c>
       <c r="C10" s="135">
         <f ca="1">Overview!C5</f>
-        <v>143.68</v>
+        <v>147.44999999999999</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -23973,7 +24002,7 @@
       </c>
       <c r="C11" s="156">
         <f ca="1">(C9-C10)/C10</f>
-        <v>0.14518764653533492</v>
+        <v>0.11590750121530648</v>
       </c>
     </row>
   </sheetData>
@@ -24029,37 +24058,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="256" t="s">
+      <c r="C2" s="259" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="256"/>
-      <c r="E2" s="256"/>
-      <c r="F2" s="256"/>
-      <c r="G2" s="268"/>
-      <c r="H2" s="269" t="s">
+      <c r="D2" s="259"/>
+      <c r="E2" s="259"/>
+      <c r="F2" s="259"/>
+      <c r="G2" s="265"/>
+      <c r="H2" s="266" t="s">
         <v>114</v>
       </c>
-      <c r="I2" s="256"/>
-      <c r="J2" s="256"/>
-      <c r="K2" s="256"/>
-      <c r="L2" s="256"/>
+      <c r="I2" s="259"/>
+      <c r="J2" s="259"/>
+      <c r="K2" s="259"/>
+      <c r="L2" s="259"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="265" t="s">
+      <c r="C4" s="267" t="s">
         <v>198</v>
       </c>
-      <c r="D4" s="265"/>
-      <c r="E4" s="265"/>
-      <c r="F4" s="265"/>
-      <c r="G4" s="265"/>
-      <c r="H4" s="265"/>
-      <c r="I4" s="265"/>
-      <c r="J4" s="265"/>
-      <c r="K4" s="265"/>
-      <c r="L4" s="265"/>
+      <c r="D4" s="267"/>
+      <c r="E4" s="267"/>
+      <c r="F4" s="267"/>
+      <c r="G4" s="267"/>
+      <c r="H4" s="267"/>
+      <c r="I4" s="267"/>
+      <c r="J4" s="267"/>
+      <c r="K4" s="267"/>
+      <c r="L4" s="267"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -24172,18 +24201,18 @@
       <c r="N8" s="92"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C9" s="265" t="s">
+      <c r="C9" s="267" t="s">
         <v>122</v>
       </c>
-      <c r="D9" s="265"/>
-      <c r="E9" s="265"/>
-      <c r="F9" s="265"/>
-      <c r="G9" s="265"/>
-      <c r="H9" s="265"/>
-      <c r="I9" s="265"/>
-      <c r="J9" s="265"/>
-      <c r="K9" s="265"/>
-      <c r="L9" s="265"/>
+      <c r="D9" s="267"/>
+      <c r="E9" s="267"/>
+      <c r="F9" s="267"/>
+      <c r="G9" s="267"/>
+      <c r="H9" s="267"/>
+      <c r="I9" s="267"/>
+      <c r="J9" s="267"/>
+      <c r="K9" s="267"/>
+      <c r="L9" s="267"/>
       <c r="N9" s="92"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -24304,18 +24333,18 @@
       <c r="N13" s="92"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C14" s="265" t="s">
+      <c r="C14" s="267" t="s">
         <v>422</v>
       </c>
-      <c r="D14" s="265"/>
-      <c r="E14" s="265"/>
-      <c r="F14" s="265"/>
-      <c r="G14" s="265"/>
-      <c r="H14" s="265"/>
-      <c r="I14" s="265"/>
-      <c r="J14" s="265"/>
-      <c r="K14" s="265"/>
-      <c r="L14" s="265"/>
+      <c r="D14" s="267"/>
+      <c r="E14" s="267"/>
+      <c r="F14" s="267"/>
+      <c r="G14" s="267"/>
+      <c r="H14" s="267"/>
+      <c r="I14" s="267"/>
+      <c r="J14" s="267"/>
+      <c r="K14" s="267"/>
+      <c r="L14" s="267"/>
       <c r="N14" s="92"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
@@ -24405,10 +24434,10 @@
       <c r="N19" s="92"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B20" s="256" t="s">
+      <c r="B20" s="259" t="s">
         <v>424</v>
       </c>
-      <c r="C20" s="256"/>
+      <c r="C20" s="259"/>
       <c r="N20" s="92"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
@@ -24510,20 +24539,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="256" t="s">
+      <c r="C3" s="259" t="s">
         <v>113</v>
       </c>
-      <c r="D3" s="256"/>
-      <c r="E3" s="256"/>
-      <c r="F3" s="256"/>
-      <c r="G3" s="268"/>
-      <c r="H3" s="269" t="s">
+      <c r="D3" s="259"/>
+      <c r="E3" s="259"/>
+      <c r="F3" s="259"/>
+      <c r="G3" s="265"/>
+      <c r="H3" s="266" t="s">
         <v>114</v>
       </c>
-      <c r="I3" s="256"/>
-      <c r="J3" s="256"/>
-      <c r="K3" s="256"/>
-      <c r="L3" s="256"/>
+      <c r="I3" s="259"/>
+      <c r="J3" s="259"/>
+      <c r="K3" s="259"/>
+      <c r="L3" s="259"/>
       <c r="P3" s="270"/>
       <c r="Q3" s="270"/>
       <c r="R3" s="270"/>
@@ -24541,18 +24570,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="87"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="265" t="s">
+      <c r="C5" s="267" t="s">
         <v>184</v>
       </c>
-      <c r="D5" s="265"/>
-      <c r="E5" s="265"/>
-      <c r="F5" s="265"/>
-      <c r="G5" s="265"/>
-      <c r="H5" s="265"/>
-      <c r="I5" s="265"/>
-      <c r="J5" s="265"/>
-      <c r="K5" s="265"/>
-      <c r="L5" s="265"/>
+      <c r="D5" s="267"/>
+      <c r="E5" s="267"/>
+      <c r="F5" s="267"/>
+      <c r="G5" s="267"/>
+      <c r="H5" s="267"/>
+      <c r="I5" s="267"/>
+      <c r="J5" s="267"/>
+      <c r="K5" s="267"/>
+      <c r="L5" s="267"/>
       <c r="P5" s="270"/>
       <c r="Q5" s="270"/>
       <c r="R5" s="270"/>
@@ -24634,39 +24663,39 @@
       </c>
       <c r="D7" s="114">
         <f>'FCF &amp; Other'!D28</f>
-        <v>-36951.924312708914</v>
+        <v>-34866.075687291086</v>
       </c>
       <c r="E7" s="114">
         <f>'FCF &amp; Other'!E28</f>
-        <v>13774.594138493558</v>
+        <v>16325.405861506442</v>
       </c>
       <c r="F7" s="114">
         <f>'FCF &amp; Other'!F28</f>
-        <v>136631.79989443434</v>
+        <v>119828.20010556566</v>
       </c>
       <c r="G7" s="115">
         <f>'FCF &amp; Other'!G28</f>
-        <v>190141.84052409406</v>
+        <v>152914.15947590594</v>
       </c>
       <c r="H7" s="128">
         <f>G7*(1+$C$17)</f>
-        <v>228170.20862891286</v>
+        <v>183496.99137108712</v>
       </c>
       <c r="I7" s="128">
         <f t="shared" ref="I7:L7" si="0">H7*(1+$C$17)</f>
-        <v>273804.25035469542</v>
+        <v>220196.38964530453</v>
       </c>
       <c r="J7" s="128">
         <f t="shared" si="0"/>
-        <v>328565.10042563447</v>
+        <v>264235.66757436545</v>
       </c>
       <c r="K7" s="128">
         <f t="shared" si="0"/>
-        <v>394278.12051076134</v>
+        <v>317082.80108923855</v>
       </c>
       <c r="L7" s="128">
         <f t="shared" si="0"/>
-        <v>473133.74461291358</v>
+        <v>380499.36130708625</v>
       </c>
       <c r="N7" s="92"/>
       <c r="O7" s="16"/>
@@ -24698,7 +24727,7 @@
       <c r="K8" s="139"/>
       <c r="L8" s="128">
         <f>L7*(1+C20)/(C21-C20)</f>
-        <v>5362182.4389463542</v>
+        <v>4312326.094813644</v>
       </c>
       <c r="N8" s="92"/>
       <c r="O8" s="16"/>
@@ -24752,23 +24781,23 @@
       <c r="G10" s="140"/>
       <c r="H10" s="128">
         <f>H7/(1+$C$21)^H9</f>
-        <v>205558.7465125341</v>
+        <v>165312.60483881721</v>
       </c>
       <c r="I10" s="128">
         <f t="shared" ref="I10:L10" si="1">I7/(1+$C$21)^I9</f>
-        <v>222225.67190544223</v>
+        <v>178716.32955547803</v>
       </c>
       <c r="J10" s="128">
         <f t="shared" si="1"/>
-        <v>240243.96962750508</v>
+        <v>193206.84276267898</v>
       </c>
       <c r="K10" s="128">
         <f t="shared" si="1"/>
-        <v>259723.21040811358</v>
+        <v>208872.26244613942</v>
       </c>
       <c r="L10" s="128">
         <f t="shared" si="1"/>
-        <v>280781.84908985248</v>
+        <v>225807.85129312368</v>
       </c>
       <c r="N10" s="92"/>
     </row>
@@ -24787,7 +24816,7 @@
       <c r="K11" s="139"/>
       <c r="L11" s="128">
         <f>L8/(1+C21)^L9</f>
-        <v>3182194.2896849951</v>
+        <v>2559155.6479887348</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -24803,7 +24832,7 @@
       </c>
       <c r="C15" s="158">
         <f ca="1">Overview!C5</f>
-        <v>143.68</v>
+        <v>147.44999999999999</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -24812,7 +24841,7 @@
       </c>
       <c r="C16" s="158">
         <f>C36</f>
-        <v>124.12445469218233</v>
+        <v>105.75023594419211</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -24869,7 +24898,7 @@
       </c>
       <c r="C23" s="163">
         <f ca="1">C15*C22</f>
-        <v>6722212.4800000004</v>
+        <v>6898595.6999999993</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -24896,7 +24925,7 @@
       </c>
       <c r="C26" s="164">
         <f ca="1">C23+C25-C24</f>
-        <v>5305653.4800000004</v>
+        <v>5482036.6999999993</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -24912,7 +24941,7 @@
       </c>
       <c r="C29" s="163">
         <f>SUM(H10:L10)</f>
-        <v>1208533.4475434474</v>
+        <v>971915.89089623734</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -24921,7 +24950,7 @@
       </c>
       <c r="C30" s="163">
         <f>L11</f>
-        <v>3182194.2896849951</v>
+        <v>2559155.6479887348</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -24930,7 +24959,7 @@
       </c>
       <c r="C31" s="166">
         <f>C29+C30</f>
-        <v>4390727.737228442</v>
+        <v>3531071.5388849722</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -24957,7 +24986,7 @@
       </c>
       <c r="C34" s="166">
         <f>C31+C32-C33</f>
-        <v>5807286.737228442</v>
+        <v>4947630.5388849722</v>
       </c>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.2">
@@ -24975,22 +25004,22 @@
       </c>
       <c r="C36" s="169">
         <f>C34/C35</f>
-        <v>124.12445469218233</v>
+        <v>105.75023594419211</v>
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C39" s="265" t="s">
+      <c r="C39" s="267" t="s">
         <v>233</v>
       </c>
-      <c r="D39" s="265"/>
-      <c r="E39" s="265"/>
-      <c r="F39" s="265"/>
-      <c r="G39" s="265"/>
-      <c r="H39" s="265"/>
-      <c r="I39" s="265"/>
-      <c r="J39" s="265"/>
-      <c r="K39" s="265"/>
-      <c r="L39" s="265"/>
+      <c r="D39" s="267"/>
+      <c r="E39" s="267"/>
+      <c r="F39" s="267"/>
+      <c r="G39" s="267"/>
+      <c r="H39" s="267"/>
+      <c r="I39" s="267"/>
+      <c r="J39" s="267"/>
+      <c r="K39" s="267"/>
+      <c r="L39" s="267"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="12">
@@ -25044,39 +25073,39 @@
       </c>
       <c r="D41" s="114">
         <f t="shared" si="2"/>
-        <v>-36951.924312708914</v>
+        <v>-34866.075687291086</v>
       </c>
       <c r="E41" s="114">
         <f t="shared" si="2"/>
-        <v>13774.594138493558</v>
+        <v>16325.405861506442</v>
       </c>
       <c r="F41" s="114">
         <f t="shared" si="2"/>
-        <v>136631.79989443434</v>
+        <v>119828.20010556566</v>
       </c>
       <c r="G41" s="115">
         <f t="shared" si="2"/>
-        <v>190141.84052409406</v>
+        <v>152914.15947590594</v>
       </c>
       <c r="H41" s="145">
         <f t="shared" si="2"/>
-        <v>228170.20862891286</v>
+        <v>183496.99137108712</v>
       </c>
       <c r="I41" s="145">
         <f t="shared" si="2"/>
-        <v>273804.25035469542</v>
+        <v>220196.38964530453</v>
       </c>
       <c r="J41" s="145">
         <f t="shared" si="2"/>
-        <v>328565.10042563447</v>
+        <v>264235.66757436545</v>
       </c>
       <c r="K41" s="145">
         <f t="shared" si="2"/>
-        <v>394278.12051076134</v>
+        <v>317082.80108923855</v>
       </c>
       <c r="L41" s="145">
         <f t="shared" si="2"/>
-        <v>473133.74461291358</v>
+        <v>380499.36130708625</v>
       </c>
     </row>
     <row r="42" spans="2:12" x14ac:dyDescent="0.2">
@@ -25105,23 +25134,23 @@
       </c>
       <c r="H42" s="145">
         <f>H41/H43</f>
-        <v>175515.54509916375</v>
+        <v>141151.53182391316</v>
       </c>
       <c r="I42" s="145">
         <f t="shared" ref="I42:L42" si="3">I41/I43</f>
-        <v>210618.65411899646</v>
+        <v>169381.83818869578</v>
       </c>
       <c r="J42" s="145">
         <f t="shared" si="3"/>
-        <v>252742.38494279573</v>
+        <v>203258.20582643495</v>
       </c>
       <c r="K42" s="145">
         <f t="shared" si="3"/>
-        <v>303290.86193135486</v>
+        <v>243909.84699172195</v>
       </c>
       <c r="L42" s="145">
         <f t="shared" si="3"/>
-        <v>363949.0343176258</v>
+        <v>292691.81639006635</v>
       </c>
     </row>
     <row r="43" spans="2:12" x14ac:dyDescent="0.2">
@@ -25134,19 +25163,19 @@
       </c>
       <c r="D43" s="96">
         <f t="shared" ref="D43:G43" si="4">D41/D42</f>
-        <v>0.56679077095956609</v>
+        <v>0.5347967740975702</v>
       </c>
       <c r="E43" s="96">
         <f t="shared" si="4"/>
-        <v>-1.0388863517982923</v>
+        <v>-1.2312697685727765</v>
       </c>
       <c r="F43" s="96">
         <f t="shared" si="4"/>
-        <v>2.1827909560577416</v>
+        <v>1.9143414027568602</v>
       </c>
       <c r="G43" s="97">
         <f t="shared" si="4"/>
-        <v>1.4025362581994103</v>
+        <v>1.1279350850181156</v>
       </c>
       <c r="H43" s="170">
         <v>1.3</v>
@@ -25190,23 +25219,23 @@
       </c>
       <c r="H44" s="145">
         <f>H41/H45</f>
-        <v>1267612.2701606271</v>
+        <v>1019427.7298393729</v>
       </c>
       <c r="I44" s="145">
         <f t="shared" ref="I44:L44" si="5">I41/I45</f>
-        <v>1521134.7241927525</v>
+        <v>1223313.2758072475</v>
       </c>
       <c r="J44" s="145">
         <f t="shared" si="5"/>
-        <v>1825361.6690313027</v>
+        <v>1467975.930968697</v>
       </c>
       <c r="K44" s="145">
         <f t="shared" si="5"/>
-        <v>2190434.0028375629</v>
+        <v>1761571.1171624365</v>
       </c>
       <c r="L44" s="145">
         <f t="shared" si="5"/>
-        <v>2628520.8034050753</v>
+        <v>2113885.3405949236</v>
       </c>
     </row>
     <row r="45" spans="2:12" x14ac:dyDescent="0.2">
@@ -25219,19 +25248,19 @@
       </c>
       <c r="D45" s="96">
         <f t="shared" ref="D45:G45" si="6">D41/D44</f>
-        <v>-0.10000656115159587</v>
+        <v>-9.4361427589794405E-2</v>
       </c>
       <c r="E45" s="96">
         <f t="shared" si="6"/>
-        <v>2.5935531385259065E-2</v>
+        <v>3.0738334054791847E-2</v>
       </c>
       <c r="F45" s="96">
         <f t="shared" si="6"/>
-        <v>0.18265697343191439</v>
+        <v>0.16019298860138934</v>
       </c>
       <c r="G45" s="97">
         <f t="shared" si="6"/>
-        <v>0.18325352381732465</v>
+        <v>0.14737449941730871</v>
       </c>
       <c r="H45" s="170">
         <v>0.18</v>
@@ -25256,19 +25285,19 @@
       <c r="C46" s="139"/>
       <c r="D46" s="96">
         <f>D41/C41-1</f>
-        <v>-2.0154743511112794E-2</v>
+        <v>-7.5464687969582944E-2</v>
       </c>
       <c r="E46" s="96">
         <f t="shared" ref="E46:L47" si="7">E41/D41-1</f>
-        <v>-1.3727706850101997</v>
+        <v>-1.4682318138676318</v>
       </c>
       <c r="F46" s="96">
         <f t="shared" si="7"/>
-        <v>8.9191162019512618</v>
+        <v>6.3399829151021425</v>
       </c>
       <c r="G46" s="97">
         <f t="shared" si="7"/>
-        <v>0.39163679810266072</v>
+        <v>0.27611162765686514</v>
       </c>
       <c r="H46" s="171">
         <f t="shared" si="7"/>
@@ -25314,15 +25343,15 @@
       </c>
       <c r="H47" s="171">
         <f t="shared" si="7"/>
-        <v>0.29464885372253269</v>
+        <v>4.117084770902979E-2</v>
       </c>
       <c r="I47" s="171">
         <f t="shared" si="7"/>
-        <v>0.19999999999999973</v>
+        <v>0.19999999999999996</v>
       </c>
       <c r="J47" s="171">
         <f t="shared" si="7"/>
-        <v>0.19999999999999996</v>
+        <v>0.20000000000000018</v>
       </c>
       <c r="K47" s="171">
         <f t="shared" si="7"/>
@@ -25356,7 +25385,7 @@
       </c>
       <c r="H48" s="171">
         <f t="shared" si="8"/>
-        <v>0.22169015878216425</v>
+        <v>-1.7503337217941839E-2</v>
       </c>
       <c r="I48" s="171">
         <f t="shared" si="8"/>
@@ -25364,11 +25393,11 @@
       </c>
       <c r="J48" s="171">
         <f t="shared" si="8"/>
-        <v>0.19999999999999973</v>
+        <v>0.19999999999999996</v>
       </c>
       <c r="K48" s="171">
         <f t="shared" si="8"/>
-        <v>0.19999999999999996</v>
+        <v>0.20000000000000018</v>
       </c>
       <c r="L48" s="171">
         <f t="shared" si="8"/>
@@ -25401,7 +25430,7 @@
       </c>
       <c r="H49" s="171">
         <f t="shared" si="9"/>
-        <v>0.13846153846153847</v>
+        <v>0.13846153846153844</v>
       </c>
       <c r="I49" s="171">
         <f t="shared" si="9"/>
@@ -25413,7 +25442,7 @@
       </c>
       <c r="K49" s="171">
         <f t="shared" si="9"/>
-        <v>0.13846153846153847</v>
+        <v>0.13846153846153844</v>
       </c>
       <c r="L49" s="171">
         <f t="shared" si="9"/>
@@ -25422,17 +25451,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C39:L39"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C39:L39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -32124,7 +32153,7 @@
       </c>
       <c r="AC116" s="63">
         <f ca="1">Overview!C5</f>
-        <v>143.68</v>
+        <v>147.44999999999999</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -32195,7 +32224,7 @@
       </c>
       <c r="AC117" s="65">
         <f ca="1">AC116/AC85</f>
-        <v>143.68</v>
+        <v>147.44999999999999</v>
       </c>
     </row>
     <row r="119" spans="1:31" x14ac:dyDescent="0.2">
@@ -33305,7 +33334,7 @@
       <c r="AA146" s="49"/>
       <c r="AC146" s="72">
         <f ca="1">AC117/Statement!AC26</f>
-        <v>45.749264830200104</v>
+        <v>46.949673574700761</v>
       </c>
     </row>
     <row r="147" spans="2:29" x14ac:dyDescent="0.2">
@@ -33342,7 +33371,7 @@
       <c r="AA147" s="49"/>
       <c r="AC147" s="72">
         <f ca="1">AC117/(Statement!AC5/Statement!AC22)</f>
-        <v>6.1702618801045945</v>
+        <v>6.3321625433005453</v>
       </c>
     </row>
     <row r="148" spans="2:29" x14ac:dyDescent="0.2">
@@ -33403,7 +33432,7 @@
       </c>
       <c r="AC148" s="72">
         <f ca="1">AC117/(Statement!AC49/Statement!AC75)</f>
-        <v>4.7683990971397607</v>
+        <v>4.8935164732270158</v>
       </c>
     </row>
     <row r="149" spans="2:29" x14ac:dyDescent="0.2">
@@ -33464,7 +33493,7 @@
       </c>
       <c r="AC149" s="145">
         <f ca="1">Statement!AC117*Statement!AC78</f>
-        <v>7201528.96</v>
+        <v>7390488.8999999994</v>
       </c>
     </row>
     <row r="150" spans="2:29" x14ac:dyDescent="0.2">
@@ -33525,7 +33554,7 @@
       </c>
       <c r="AC150" s="145">
         <f ca="1">AC149+AC108-AC107+AC48+AC45</f>
-        <v>5784969.96</v>
+        <v>5973929.8999999994</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -33562,7 +33591,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="185">
         <f ca="1">AC150/AC5</f>
-        <v>5.052366685822383</v>
+        <v>5.21739691284382</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -33599,7 +33628,7 @@
       <c r="AA152" s="49"/>
       <c r="AC152" s="185">
         <f ca="1">AC150/AC12</f>
-        <v>36.827004233376833</v>
+        <v>38.029919470350443</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -33734,7 +33763,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="72">
         <f t="shared" ref="AC155:AC156" ca="1" si="151">AC149/AC153</f>
-        <v>28.484807214619096</v>
+        <v>29.232216201249898</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -33771,7 +33800,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="72">
         <f t="shared" ca="1" si="151"/>
-        <v>34.696361055846559</v>
+        <v>35.829681081475712</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -33808,7 +33837,7 @@
       <c r="AA157" s="49"/>
       <c r="AC157" s="74">
         <f t="shared" ref="AC157" ca="1" si="154">AC153/AC149</f>
-        <v>3.5106433842626662E-2</v>
+        <v>3.4208832923083077E-2</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
@@ -33845,7 +33874,7 @@
       <c r="AA158" s="49"/>
       <c r="AC158" s="74">
         <f ca="1">AC26/AC117</f>
-        <v>2.1858274744119555E-2</v>
+        <v>2.129940261264902E-2</v>
       </c>
     </row>
     <row r="159" spans="2:29" x14ac:dyDescent="0.2">
@@ -33919,7 +33948,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="156">
         <f ca="1">-AC63/AC149</f>
-        <v>9.665030910324909E-3</v>
+        <v>9.417915504886288E-3</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -33956,7 +33985,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="156">
         <f ca="1">-(AC63+AC64)/AC149</f>
-        <v>9.665030910324909E-3</v>
+        <v>9.417915504886288E-3</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -34459,7 +34488,7 @@
       <c r="AA172" s="49"/>
       <c r="AC172" s="156">
         <f ca="1">(AC107-AC108)/AC149</f>
-        <v>0.1967025346795245</v>
+        <v>0.19167324640728439</v>
       </c>
     </row>
     <row r="173" spans="2:29" x14ac:dyDescent="0.2">
@@ -36381,15 +36410,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="256" t="s">
+      <c r="B4" s="259" t="s">
         <v>242</v>
       </c>
-      <c r="C4" s="256"/>
-      <c r="E4" s="256" t="s">
+      <c r="C4" s="259"/>
+      <c r="E4" s="259" t="s">
         <v>249</v>
       </c>
-      <c r="F4" s="256"/>
-      <c r="G4" s="256"/>
+      <c r="F4" s="259"/>
+      <c r="G4" s="259"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -36397,7 +36426,7 @@
       </c>
       <c r="C5" s="174">
         <f ca="1">Overview!C5</f>
-        <v>143.68</v>
+        <v>147.44999999999999</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="134" t="s">
@@ -36413,7 +36442,7 @@
       </c>
       <c r="C6" s="175">
         <f ca="1">Statement!AC149</f>
-        <v>7201528.96</v>
+        <v>7390488.8999999994</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>20</v>
@@ -36433,7 +36462,7 @@
       </c>
       <c r="C7" s="175">
         <f ca="1">Statement!AC150</f>
-        <v>5784969.96</v>
+        <v>5973929.8999999994</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>32</v>
@@ -36453,7 +36482,7 @@
       </c>
       <c r="C8" s="176">
         <f ca="1">Statement!AC146</f>
-        <v>45.749264830200104</v>
+        <v>46.949673574700761</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>252</v>
@@ -36473,7 +36502,7 @@
       </c>
       <c r="C9" s="176">
         <f ca="1">Statement!AC147</f>
-        <v>6.1702618801045945</v>
+        <v>6.3321625433005453</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>253</v>
@@ -36493,7 +36522,7 @@
       </c>
       <c r="C10" s="176">
         <f ca="1">Statement!AC148</f>
-        <v>4.7683990971397607</v>
+        <v>4.8935164732270158</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -36513,7 +36542,7 @@
       </c>
       <c r="C11" s="176">
         <f ca="1">Statement!AC151</f>
-        <v>5.052366685822383</v>
+        <v>5.21739691284382</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -36522,18 +36551,18 @@
       </c>
       <c r="C12" s="176">
         <f ca="1">Statement!AC152</f>
-        <v>36.827004233376833</v>
+        <v>38.029919470350443</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="256" t="s">
+      <c r="B15" s="259" t="s">
         <v>78</v>
       </c>
-      <c r="C15" s="256"/>
-      <c r="E15" s="256" t="s">
+      <c r="C15" s="259"/>
+      <c r="E15" s="259" t="s">
         <v>255</v>
       </c>
-      <c r="F15" s="256"/>
+      <c r="F15" s="259"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -36584,14 +36613,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="256" t="s">
+      <c r="B21" s="259" t="s">
         <v>254</v>
       </c>
-      <c r="C21" s="256"/>
-      <c r="E21" s="256" t="s">
+      <c r="C21" s="259"/>
+      <c r="E21" s="259" t="s">
         <v>258</v>
       </c>
-      <c r="F21" s="256"/>
+      <c r="F21" s="259"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -36660,14 +36689,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="256" t="s">
+      <c r="B29" s="259" t="s">
         <v>259</v>
       </c>
-      <c r="C29" s="256"/>
-      <c r="E29" s="256" t="s">
+      <c r="C29" s="259"/>
+      <c r="E29" s="259" t="s">
         <v>265</v>
       </c>
-      <c r="F29" s="256"/>
+      <c r="F29" s="259"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -36743,14 +36772,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="256" t="s">
+      <c r="B37" s="259" t="s">
         <v>277</v>
       </c>
-      <c r="C37" s="256"/>
-      <c r="E37" s="256" t="s">
+      <c r="C37" s="259"/>
+      <c r="E37" s="259" t="s">
         <v>280</v>
       </c>
-      <c r="F37" s="256"/>
+      <c r="F37" s="259"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -36758,7 +36787,7 @@
       </c>
       <c r="C38" s="177">
         <f ca="1">Statement!AC158</f>
-        <v>2.1858274744119555E-2</v>
+        <v>2.129940261264902E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>279</v>
@@ -36774,7 +36803,7 @@
       </c>
       <c r="C39" s="217">
         <f ca="1">Statement!AC157</f>
-        <v>3.5106433842626662E-2</v>
+        <v>3.4208832923083077E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>281</v>
@@ -36806,7 +36835,7 @@
       </c>
       <c r="C41" s="177">
         <f ca="1">Statement!AC160</f>
-        <v>9.665030910324909E-3</v>
+        <v>9.417915504886288E-3</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -36815,18 +36844,18 @@
       </c>
       <c r="C42" s="177">
         <f ca="1">Statement!AC161</f>
-        <v>9.665030910324909E-3</v>
+        <v>9.417915504886288E-3</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="256" t="s">
+      <c r="B45" s="259" t="s">
         <v>288</v>
       </c>
-      <c r="C45" s="256"/>
-      <c r="E45" s="256" t="s">
+      <c r="C45" s="259"/>
+      <c r="E45" s="259" t="s">
         <v>294</v>
       </c>
-      <c r="F45" s="256"/>
+      <c r="F45" s="259"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -36859,18 +36888,18 @@
       </c>
       <c r="F48" s="177">
         <f ca="1">Statement!AC172</f>
-        <v>0.1967025346795245</v>
+        <v>0.19167324640728439</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="256" t="s">
+      <c r="B51" s="259" t="s">
         <v>291</v>
       </c>
-      <c r="C51" s="256"/>
-      <c r="E51" s="256" t="s">
+      <c r="C51" s="259"/>
+      <c r="E51" s="259" t="s">
         <v>312</v>
       </c>
-      <c r="F51" s="256"/>
+      <c r="F51" s="259"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -37038,7 +37067,7 @@
       </c>
       <c r="I6" s="174">
         <f ca="1">Statement!AC116</f>
-        <v>143.68</v>
+        <v>147.44999999999999</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -37067,7 +37096,7 @@
       </c>
       <c r="I7" s="175">
         <f ca="1">Statement!AC149</f>
-        <v>7201528.96</v>
+        <v>7390488.8999999994</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -37096,7 +37125,7 @@
       </c>
       <c r="I8" s="175">
         <f ca="1">Statement!AC150</f>
-        <v>5784969.96</v>
+        <v>5973929.8999999994</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -37125,7 +37154,7 @@
       </c>
       <c r="I9" s="176">
         <f ca="1">Statement!AC146</f>
-        <v>45.749264830200104</v>
+        <v>46.949673574700761</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -37154,7 +37183,7 @@
       </c>
       <c r="I10" s="176">
         <f ca="1">Statement!AC147</f>
-        <v>6.1702618801045945</v>
+        <v>6.3321625433005453</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -37183,7 +37212,7 @@
       </c>
       <c r="I11" s="176">
         <f ca="1">Statement!AC148</f>
-        <v>4.7683990971397607</v>
+        <v>4.8935164732270158</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -37212,7 +37241,7 @@
       </c>
       <c r="I12" s="176">
         <f ca="1">Statement!AC151</f>
-        <v>5.052366685822383</v>
+        <v>5.21739691284382</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -37241,7 +37270,7 @@
       </c>
       <c r="I13" s="176">
         <f ca="1">Statement!AC152</f>
-        <v>36.827004233376833</v>
+        <v>38.029919470350443</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -38014,7 +38043,7 @@
       </c>
       <c r="I51" s="177">
         <f ca="1">Statement!AC158</f>
-        <v>2.1858274744119555E-2</v>
+        <v>2.129940261264902E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -38043,7 +38072,7 @@
       </c>
       <c r="I52" s="177">
         <f ca="1">Statement!AC157</f>
-        <v>3.5106433842626662E-2</v>
+        <v>3.4208832923083077E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -38101,7 +38130,7 @@
       </c>
       <c r="I54" s="177">
         <f ca="1">Statement!AC160</f>
-        <v>9.665030910324909E-3</v>
+        <v>9.417915504886288E-3</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -38130,7 +38159,7 @@
       </c>
       <c r="I55" s="177">
         <f ca="1">Statement!AC161</f>
-        <v>9.665030910324909E-3</v>
+        <v>9.417915504886288E-3</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -38366,7 +38395,7 @@
       </c>
       <c r="I68" s="198">
         <f ca="1">Statement!AC172</f>
-        <v>0.1967025346795245</v>
+        <v>0.19167324640728439</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -38909,14 +38938,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="260" t="s">
+      <c r="C3" s="262" t="s">
         <v>322</v>
       </c>
-      <c r="D3" s="261"/>
-      <c r="F3" s="262" t="s">
+      <c r="D3" s="263"/>
+      <c r="F3" s="264" t="s">
         <v>323</v>
       </c>
-      <c r="G3" s="261"/>
+      <c r="G3" s="263"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -38983,19 +39012,19 @@
       <c r="B7" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C7" s="263">
+      <c r="C7" s="260">
         <f>Statement!AA89</f>
         <v>2.2218264392893719E-2</v>
       </c>
-      <c r="D7" s="264"/>
-      <c r="F7" s="263">
+      <c r="D7" s="261"/>
+      <c r="F7" s="260">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.18309713991239371</v>
       </c>
-      <c r="G7" s="264"/>
+      <c r="G7" s="261"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="209" t="s">
@@ -39022,19 +39051,19 @@
       <c r="B9" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C9" s="263">
+      <c r="C9" s="260">
         <f>Statement!AA90</f>
         <v>3.6046202026093238E-2</v>
       </c>
-      <c r="D9" s="264"/>
-      <c r="F9" s="263">
+      <c r="D9" s="261"/>
+      <c r="F9" s="260">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.17263647322197348</v>
       </c>
-      <c r="G9" s="264"/>
+      <c r="G9" s="261"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="209" t="s">
@@ -39061,19 +39090,19 @@
       <c r="B11" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C11" s="263">
+      <c r="C11" s="260">
         <f>Statement!AA91</f>
         <v>1.710027405488606E-2</v>
       </c>
-      <c r="D11" s="264"/>
-      <c r="F11" s="263">
+      <c r="D11" s="261"/>
+      <c r="F11" s="260">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>0.1870895657269924</v>
       </c>
-      <c r="G11" s="264"/>
+      <c r="G11" s="261"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="209" t="s">
@@ -39100,19 +39129,19 @@
       <c r="B13" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C13" s="263">
+      <c r="C13" s="260">
         <f>Statement!AA95</f>
         <v>8.4392741251357012E-2</v>
       </c>
-      <c r="D13" s="264"/>
-      <c r="F13" s="263">
+      <c r="D13" s="261"/>
+      <c r="F13" s="260">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.22501976973287405</v>
       </c>
-      <c r="G13" s="264"/>
+      <c r="G13" s="261"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="209" t="s">
@@ -39139,19 +39168,19 @@
       <c r="B15" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C15" s="263">
+      <c r="C15" s="260">
         <f>Statement!AA96</f>
         <v>-0.23765355851505829</v>
       </c>
-      <c r="D15" s="264"/>
-      <c r="F15" s="263">
+      <c r="D15" s="261"/>
+      <c r="F15" s="260">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>1.7444474417768186E-2</v>
       </c>
-      <c r="G15" s="264"/>
+      <c r="G15" s="261"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="209" t="s">
@@ -39178,19 +39207,19 @@
       <c r="B17" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C17" s="263">
+      <c r="C17" s="260">
         <f>Statement!AA98</f>
         <v>-0.23704555913483663</v>
       </c>
-      <c r="D17" s="264"/>
-      <c r="F17" s="263">
+      <c r="D17" s="261"/>
+      <c r="F17" s="260">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>-0.25955204216073779</v>
       </c>
-      <c r="G17" s="264"/>
+      <c r="G17" s="261"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="209" t="s">
@@ -39217,22 +39246,22 @@
       <c r="B19" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C19" s="263">
+      <c r="C19" s="260">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>2.5565842762241744E-2</v>
       </c>
-      <c r="D19" s="264"/>
-      <c r="F19" s="263">
+      <c r="D19" s="261"/>
+      <c r="F19" s="260">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>2.5293753865182372E-2</v>
       </c>
-      <c r="G19" s="264"/>
+      <c r="G19" s="261"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="209" t="s">
@@ -39259,22 +39288,22 @@
       <c r="B21" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C21" s="263">
+      <c r="C21" s="260">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>-0.2584269662921348</v>
       </c>
-      <c r="D21" s="264"/>
-      <c r="F21" s="263">
+      <c r="D21" s="261"/>
+      <c r="F21" s="260">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>-0.27472527472527469</v>
       </c>
-      <c r="G21" s="264"/>
+      <c r="G21" s="261"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -39323,22 +39352,22 @@
       <c r="B25" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C25" s="263">
+      <c r="C25" s="260">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>2.840483364420425E-2</v>
       </c>
-      <c r="D25" s="264"/>
-      <c r="F25" s="263">
+      <c r="D25" s="261"/>
+      <c r="F25" s="260">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>0.22478379327694395</v>
       </c>
-      <c r="G25" s="264"/>
+      <c r="G25" s="261"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="str">
@@ -39366,22 +39395,22 @@
       <c r="B27" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C27" s="263">
+      <c r="C27" s="260">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>2.1247695740758708E-2</v>
       </c>
-      <c r="D27" s="264"/>
-      <c r="F27" s="263">
+      <c r="D27" s="261"/>
+      <c r="F27" s="260">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>2.1792942775323981E-2</v>
       </c>
-      <c r="G27" s="264"/>
+      <c r="G27" s="261"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="str">
@@ -39409,22 +39438,22 @@
       <c r="B29" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C29" s="263">
+      <c r="C29" s="260">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>-0.10674206945303526</v>
       </c>
-      <c r="D29" s="264"/>
-      <c r="F29" s="263">
+      <c r="D29" s="261"/>
+      <c r="F29" s="260">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>2.0816812053925456E-3</v>
       </c>
-      <c r="G29" s="264"/>
+      <c r="G29" s="261"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="str">
@@ -39452,22 +39481,22 @@
       <c r="B31" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C31" s="263">
+      <c r="C31" s="260">
         <f>IF(C30=0,
 IF(D30=0,0,IF(D30&gt;0,1,-1)),
 (D30-C30)/ABS(C30)
 )</f>
         <v>-5.2569263556713236E-2</v>
       </c>
-      <c r="D31" s="264"/>
-      <c r="F31" s="263">
+      <c r="D31" s="261"/>
+      <c r="F31" s="260">
         <f>IF(F30=0,
 IF(G30=0,0,IF(G30&gt;0,1,-1)),
 (G30-F30)/ABS(F30)
 )</f>
         <v>-0.22983638113570742</v>
       </c>
-      <c r="G31" s="264"/>
+      <c r="G31" s="261"/>
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B32" s="20" t="str">
@@ -39495,22 +39524,22 @@
       <c r="B33" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C33" s="263">
+      <c r="C33" s="260">
         <f>IF(C32=0,
 IF(D32=0,0,IF(D32&gt;0,1,-1)),
 (D32-C32)/ABS(C32)
 )</f>
         <v>0.84164222873900296</v>
       </c>
-      <c r="D33" s="264"/>
-      <c r="F33" s="263">
+      <c r="D33" s="261"/>
+      <c r="F33" s="260">
         <f>IF(F32=0,
 IF(G32=0,0,IF(G32&gt;0,1,-1)),
 (G32-F32)/ABS(F32)
 )</f>
         <v>1.482213438735178</v>
       </c>
-      <c r="G33" s="264"/>
+      <c r="G33" s="261"/>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B35" s="8" t="s">
@@ -39559,22 +39588,22 @@
       <c r="B37" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C37" s="263">
+      <c r="C37" s="260">
         <f>IF(C36=0,
 IF(D36=0,0,IF(D36&gt;0,1,-1)),
 (D36-C36)/ABS(C36)
 )</f>
         <v>3.8938053097345132E-2</v>
       </c>
-      <c r="D37" s="264"/>
-      <c r="F37" s="263">
+      <c r="D37" s="261"/>
+      <c r="F37" s="260">
         <f>IF(F36=0,
 IF(G36=0,0,IF(G36&gt;0,1,-1)),
 (G36-F36)/ABS(F36)
 )</f>
         <v>0.23060796645702306</v>
       </c>
-      <c r="G37" s="264"/>
+      <c r="G37" s="261"/>
     </row>
     <row r="38" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="str">
@@ -39602,22 +39631,22 @@
       <c r="B39" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C39" s="263">
+      <c r="C39" s="260">
         <f>IF(C38=0,
 IF(D38=0,0,IF(D38&gt;0,1,-1)),
 (D38-C38)/ABS(C38)
 )</f>
         <v>2.0319303338171262E-2</v>
       </c>
-      <c r="D39" s="264"/>
-      <c r="F39" s="263">
+      <c r="D39" s="261"/>
+      <c r="F39" s="260">
         <f>IF(F38=0,
 IF(G38=0,0,IF(G38&gt;0,1,-1)),
 (G38-F38)/ABS(F38)
 )</f>
         <v>9.5869056897895558E-2</v>
       </c>
-      <c r="G39" s="264"/>
+      <c r="G39" s="261"/>
     </row>
     <row r="40" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B40" s="20" t="str">
@@ -39645,22 +39674,22 @@
       <c r="B41" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C41" s="263">
+      <c r="C41" s="260">
         <f>IF(C40=0,
 IF(D40=0,0,IF(D40&gt;0,1,-1)),
 (D40-C40)/ABS(C40)
 )</f>
         <v>1.6E-2</v>
       </c>
-      <c r="D41" s="264"/>
-      <c r="F41" s="263">
+      <c r="D41" s="261"/>
+      <c r="F41" s="260">
         <f>IF(F40=0,
 IF(G40=0,0,IF(G40&gt;0,1,-1)),
 (G40-F40)/ABS(F40)
 )</f>
         <v>0.16513761467889909</v>
       </c>
-      <c r="G41" s="264"/>
+      <c r="G41" s="261"/>
     </row>
     <row r="42" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B42" s="20" t="str">
@@ -39688,22 +39717,22 @@
       <c r="B43" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C43" s="263">
+      <c r="C43" s="260">
         <f>IF(C42=0,
 IF(D42=0,0,IF(D42&gt;0,1,-1)),
 (D42-C42)/ABS(C42)
 )</f>
         <v>2.0750199521149242E-2</v>
       </c>
-      <c r="D43" s="264"/>
-      <c r="F43" s="263">
+      <c r="D43" s="261"/>
+      <c r="F43" s="260">
         <f>IF(F42=0,
 IF(G42=0,0,IF(G42&gt;0,1,-1)),
 (G42-F42)/ABS(F42)
 )</f>
         <v>8.9437819420783646E-2</v>
       </c>
-      <c r="G43" s="264"/>
+      <c r="G43" s="261"/>
     </row>
     <row r="44" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B44" s="20" t="str">
@@ -39731,22 +39760,22 @@
       <c r="B45" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C45" s="263">
+      <c r="C45" s="260">
         <f>IF(C44=0,
 IF(D44=0,0,IF(D44&gt;0,1,-1)),
 (D44-C44)/ABS(C44)
 )</f>
         <v>1.2209481933271921E-2</v>
       </c>
-      <c r="D45" s="264"/>
-      <c r="F45" s="263">
+      <c r="D45" s="261"/>
+      <c r="F45" s="260">
         <f>IF(F44=0,
 IF(G44=0,0,IF(G44&gt;0,1,-1)),
 (G44-F44)/ABS(F44)
 )</f>
         <v>5.119238950540856E-2</v>
       </c>
-      <c r="G45" s="264"/>
+      <c r="G45" s="261"/>
     </row>
     <row r="46" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="str">
@@ -39774,22 +39803,22 @@
       <c r="B47" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C47" s="263">
+      <c r="C47" s="260">
         <f>IF(C46=0,
 IF(D46=0,0,IF(D46&gt;0,1,-1)),
 (D46-C46)/ABS(C46)
 )</f>
         <v>1.8247963846473435E-2</v>
       </c>
-      <c r="D47" s="264"/>
-      <c r="F47" s="263">
+      <c r="D47" s="261"/>
+      <c r="F47" s="260">
         <f>IF(F46=0,
 IF(G46=0,0,IF(G46&gt;0,1,-1)),
 (G46-F46)/ABS(F46)
 )</f>
         <v>0.1229516507570132</v>
       </c>
-      <c r="G47" s="264"/>
+      <c r="G47" s="261"/>
     </row>
     <row r="48" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B48" s="20" t="str">
@@ -39817,22 +39846,22 @@
       <c r="B49" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C49" s="263">
+      <c r="C49" s="260">
         <f>IF(C48=0,
 IF(D48=0,0,IF(D48&gt;0,1,-1)),
 (D48-C48)/ABS(C48)
 )</f>
         <v>-4.2332859174963834E-3</v>
       </c>
-      <c r="D49" s="264"/>
-      <c r="F49" s="263">
+      <c r="D49" s="261"/>
+      <c r="F49" s="260">
         <f>IF(F48=0,
 IF(G48=0,0,IF(G48&gt;0,1,-1)),
 (G48-F48)/ABS(F48)
 )</f>
         <v>6.3208790635154666E-2</v>
       </c>
-      <c r="G49" s="264"/>
+      <c r="G49" s="261"/>
     </row>
     <row r="50" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B50" s="20" t="str">
@@ -39860,22 +39889,22 @@
       <c r="B51" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C51" s="263">
+      <c r="C51" s="260">
         <f>IF(C50=0,
 IF(D50=0,0,IF(D50&gt;0,1,-1)),
 (D50-C50)/ABS(C50)
 )</f>
         <v>4.8738292663854846E-4</v>
       </c>
-      <c r="D51" s="264"/>
-      <c r="F51" s="263">
+      <c r="D51" s="261"/>
+      <c r="F51" s="260">
         <f>IF(F50=0,
 IF(G50=0,0,IF(G50&gt;0,1,-1)),
 (G50-F50)/ABS(F50)
 )</f>
         <v>-6.2091544317255373E-2</v>
       </c>
-      <c r="G51" s="264"/>
+      <c r="G51" s="261"/>
     </row>
     <row r="52" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="str">
@@ -39903,39 +39932,43 @@
       <c r="B53" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C53" s="263">
+      <c r="C53" s="260">
         <f>IF(C52=0,
 IF(D52=0,0,IF(D52&gt;0,1,-1)),
 (D52-C52)/ABS(C52)
 )</f>
         <v>-8.8077740902117604E-2</v>
       </c>
-      <c r="D53" s="264"/>
-      <c r="F53" s="263">
+      <c r="D53" s="261"/>
+      <c r="F53" s="260">
         <f>IF(F52=0,
 IF(G52=0,0,IF(G52&gt;0,1,-1)),
 (G52-F52)/ABS(F52)
 )</f>
         <v>-0.37416005758387127</v>
       </c>
-      <c r="G53" s="264"/>
+      <c r="G53" s="261"/>
     </row>
   </sheetData>
   <mergeCells count="46">
-    <mergeCell ref="C53:D53"/>
-    <mergeCell ref="F53:G53"/>
-    <mergeCell ref="C47:D47"/>
-    <mergeCell ref="F47:G47"/>
-    <mergeCell ref="C49:D49"/>
-    <mergeCell ref="F49:G49"/>
-    <mergeCell ref="C51:D51"/>
-    <mergeCell ref="F51:G51"/>
-    <mergeCell ref="C41:D41"/>
-    <mergeCell ref="F41:G41"/>
-    <mergeCell ref="C43:D43"/>
-    <mergeCell ref="F43:G43"/>
-    <mergeCell ref="C45:D45"/>
-    <mergeCell ref="F45:G45"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
     <mergeCell ref="C37:D37"/>
     <mergeCell ref="F37:G37"/>
     <mergeCell ref="C39:D39"/>
@@ -39950,24 +39983,20 @@
     <mergeCell ref="F31:G31"/>
     <mergeCell ref="C33:D33"/>
     <mergeCell ref="F33:G33"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="F41:G41"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="F43:G43"/>
+    <mergeCell ref="C45:D45"/>
+    <mergeCell ref="F45:G45"/>
+    <mergeCell ref="C53:D53"/>
+    <mergeCell ref="F53:G53"/>
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="F47:G47"/>
+    <mergeCell ref="C49:D49"/>
+    <mergeCell ref="F49:G49"/>
+    <mergeCell ref="C51:D51"/>
+    <mergeCell ref="F51:G51"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/DUOL.xlsx
+++ b/DUOL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7699D9F-686F-A042-89B5-B033C90CC00A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91EF4B5E-7B2B-5F4C-A882-B42EE5CCAAEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="7" activeTab="17" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -119,7 +119,7 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="5">
+  <futureMetadata name="XLRICHVALUE" count="2">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -130,28 +130,7 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="3"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="4"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="5"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="8"/>
         </ext>
       </extLst>
     </bk>
@@ -161,21 +140,12 @@
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="5">
+  <valueMetadata count="2">
     <bk>
       <rc t="2" v="0"/>
     </bk>
     <bk>
       <rc t="2" v="1"/>
-    </bk>
-    <bk>
-      <rc t="2" v="2"/>
-    </bk>
-    <bk>
-      <rc t="2" v="3"/>
-    </bk>
-    <bk>
-      <rc t="2" v="4"/>
     </bk>
   </valueMetadata>
 </metadata>
@@ -2424,6 +2394,9 @@
     <xf numFmtId="39" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="7" fillId="9" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2431,15 +2404,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2451,10 +2415,10 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2464,6 +2428,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -13153,7 +13123,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="9">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="6">
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=c2mtim&amp;q=XNAS%3aDUOL&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
@@ -13173,8 +13143,10 @@
     <v>353</v>
     <v>87.89</v>
     <v>1.0457000000000001</v>
-    <v>-2.4700000000000002</v>
-    <v>-1.6716999999999999E-2</v>
+    <v>-4.24</v>
+    <v>-2.8697E-2</v>
+    <v>0.49</v>
+    <v>3.4139999999999999E-3</v>
     <v>USD</v>
     <v>Duolingo, Inc. is a technology company. The Company is engaged in offering a mobile learning platform, as well as a digital English language proficiency assessment exam. It operates a freemium business model, namely, the app and the Website are accessible free of charge, although Duolingo also offers premium services for a subscription fee. Its solutions consist of the Duolingo App, Super Duolingo, Duolingo Max, Duolingo English Test: AI-Driven Language Assessment, Duolingo for Schools, and Duolingo ABC. The Duolingo App offers courses in over 40 different languages, including Spanish, English, French, German, Italian, Portuguese, Japanese and Chinese. Duolingo can also be accessed on desktop computers via a Web browser. Its subscription offering, Super Duolingo, offers learners additional features to enhance their learning experience. The Duolingo English Test is an online, on-demand, high-stakes English proficiency assessment. It also operates an animation and motion design studio.</v>
     <v>900</v>
@@ -13185,46 +13157,32 @@
     <v>147.49</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46290.736129478908</v>
+    <v>46290.840662476563</v>
     <v>0</v>
-    <v>144.80000000000001</v>
-    <v>6797109305</v>
+    <v>142.16999999999999</v>
+    <v>6714297607</v>
     <v>DUOLINGO, INC.</v>
     <v>DUOLINGO, INC.</v>
     <v>147.22</v>
-    <v>17.3169</v>
+    <v>17.105899999999998</v>
     <v>147.75</v>
-    <v>145.28</v>
+    <v>143.51</v>
+    <v>144</v>
     <v>46786270</v>
     <v>DUOL</v>
     <v>DUOLINGO, INC. (XNAS:DUOL)</v>
-    <v>192061</v>
+    <v>678956</v>
     <v>1102655</v>
     <v>2011</v>
   </rv>
   <rv s="2">
     <v>1</v>
   </rv>
-  <rv s="3">
-    <v>12</v>
-    <v>Price (Extended hours)</v>
-    <v>0</v>
-  </rv>
-  <rv s="3">
-    <v>12</v>
-    <v>Change (extended hours)</v>
-    <v>0</v>
-  </rv>
-  <rv s="3">
-    <v>12</v>
-    <v>Change % (extended hours)</v>
-    <v>0</v>
-  </rv>
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a33knm&amp;q=10+Y+TSY+YLD+NDX&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="4">
+  <rv s="3">
     <v>5</v>
     <v>10 Y TSY YLD NDX</v>
     <v>6</v>
@@ -13243,7 +13201,7 @@
     <v>US</v>
     <v>51.81</v>
     <v>Index</v>
-    <v>6</v>
+    <v>3</v>
     <v>50.87</v>
     <v>10 Y TSY YLD NDX</v>
     <v>51.21</v>
@@ -13253,13 +13211,13 @@
     <v>10 Y TSY YLD NDX</v>
   </rv>
   <rv s="2">
-    <v>7</v>
+    <v>4</v>
   </rv>
 </rvData>
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="5">
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="4">
   <s t="_hyperlink">
     <k n="Address" t="s"/>
     <k n="Text" t="s"/>
@@ -13281,6 +13239,8 @@
     <k n="Beta"/>
     <k n="Change"/>
     <k n="Change (%)"/>
+    <k n="Change (Extended hours)"/>
+    <k n="Change % (Extended hours)"/>
     <k n="Currency" t="s"/>
     <k n="Description" t="s"/>
     <k n="Employees"/>
@@ -13301,6 +13261,7 @@
     <k n="P/E"/>
     <k n="Previous close"/>
     <k n="Price"/>
+    <k n="Price (Extended hours)"/>
     <k n="Shares outstanding"/>
     <k n="Ticker symbol" t="s"/>
     <k n="UniqueName" t="s"/>
@@ -13310,11 +13271,6 @@
   </s>
   <s t="_linkedentity">
     <k n="%cvi" t="r"/>
-  </s>
-  <s t="_error">
-    <k n="errorType" t="i"/>
-    <k n="field" t="s"/>
-    <k n="subType" t="i"/>
   </s>
   <s t="_linkedentitycore">
     <k n="_Display" t="spb"/>
@@ -13350,7 +13306,7 @@
 <file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
 <supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
   <spbArrays count="2">
-    <a count="42">
+    <a count="45">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%IsRefreshable</v>
@@ -13361,13 +13317,16 @@
       <v t="s">Name</v>
       <v t="s">_SubLabel</v>
       <v t="s">Price</v>
+      <v t="s">Price (Extended hours)</v>
       <v t="s">Exchange</v>
       <v t="s">Official name</v>
       <v t="s">Last trade time</v>
       <v t="s">Ticker symbol</v>
       <v t="s">Exchange abbreviation</v>
       <v t="s">Change</v>
+      <v t="s">Change (Extended hours)</v>
       <v t="s">Change (%)</v>
+      <v t="s">Change % (Extended hours)</v>
       <v t="s">Currency</v>
       <v t="s">Previous close</v>
       <v t="s">Open</v>
@@ -13461,13 +13420,19 @@
       <v>8</v>
       <v>9</v>
       <v>4</v>
+      <v>1</v>
+      <v>1</v>
+      <v>5</v>
     </spb>
     <spb s="4">
-      <v>Real-Time Nasdaq Last Sale</v>
+      <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
       <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
+      <v>Real-Time Nasdaq Last Sale</v>
+      <v>from close</v>
+      <v>from close</v>
     </spb>
     <spb s="0">
       <v>1</v>
@@ -13539,6 +13504,9 @@
     <k n="Year incorporated" t="i"/>
     <k n="`%EntityServiceId" t="i"/>
     <k n="Shares outstanding" t="i"/>
+    <k n="Price (Extended hours)" t="i"/>
+    <k n="Change (Extended hours)" t="i"/>
+    <k n="Change % (Extended hours)" t="i"/>
   </s>
   <s>
     <k n="Price" t="s"/>
@@ -13546,6 +13514,9 @@
     <k n="Change (%)" t="s"/>
     <k n="ExchangeID" t="s"/>
     <k n="Last trade time" t="s"/>
+    <k n="Price (Extended hours)" t="s"/>
+    <k n="Change (Extended hours)" t="s"/>
+    <k n="Change % (Extended hours)" t="s"/>
   </s>
   <s>
     <k n="UniqueName" t="spb"/>
@@ -14030,18 +14001,18 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="255" t="s">
+      <c r="B2" s="256" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="256"/>
-      <c r="E2" s="255" t="s">
+      <c r="C2" s="257"/>
+      <c r="E2" s="256" t="s">
         <v>291</v>
       </c>
-      <c r="F2" s="256"/>
-      <c r="H2" s="255" t="s">
+      <c r="F2" s="257"/>
+      <c r="H2" s="256" t="s">
         <v>330</v>
       </c>
-      <c r="I2" s="256"/>
+      <c r="I2" s="257"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="184" t="s">
@@ -14056,7 +14027,7 @@
       </c>
       <c r="F3" s="186">
         <f ca="1">Statement!AC149</f>
-        <v>7281724.1600000001</v>
+        <v>7193008.2199999997</v>
       </c>
       <c r="H3" s="184" t="str">
         <f>'AVG target price'!B5</f>
@@ -14080,7 +14051,7 @@
       </c>
       <c r="F4" s="187">
         <f ca="1">Statement!AC150</f>
-        <v>5865165.1600000001</v>
+        <v>5776449.2199999997</v>
       </c>
       <c r="H4" s="184" t="str">
         <f>'AVG target price'!B6</f>
@@ -14088,7 +14059,7 @@
       </c>
       <c r="I4" s="210">
         <f>'AVG target price'!C6</f>
-        <v>214.55674068081549</v>
+        <v>189.1075367384349</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.2">
@@ -14097,7 +14068,7 @@
       </c>
       <c r="C5" s="207" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>145.28</v>
+        <v>143.51</v>
       </c>
       <c r="E5" s="184" t="s">
         <v>247</v>
@@ -14119,16 +14090,16 @@
       <c r="B6" s="184" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="207" t="e" cm="1" vm="2">
-        <f t="array" ref="C6">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C6" s="207" cm="1">
+        <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
+        <v>144</v>
       </c>
       <c r="E6" s="184" t="s">
         <v>241</v>
       </c>
       <c r="F6" s="189">
         <f ca="1">Statement!AC146</f>
-        <v>46.258722122295872</v>
+        <v>45.695134992914923</v>
       </c>
       <c r="H6" s="184" t="str">
         <f>'AVG target price'!B8</f>
@@ -14136,7 +14107,7 @@
       </c>
       <c r="I6" s="210">
         <f>'AVG target price'!C8</f>
-        <v>219.77946389803776</v>
+        <v>194.3302599556572</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -14145,14 +14116,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>-2.4700000000000002</v>
+        <v>-4.24</v>
       </c>
       <c r="E7" s="185" t="s">
         <v>205</v>
       </c>
       <c r="F7" s="190">
         <f ca="1">Statement!AC147</f>
-        <v>6.2389730368986323</v>
+        <v>6.1629613196952269</v>
       </c>
       <c r="H7" s="183" t="str">
         <f>'AVG target price'!B9</f>
@@ -14160,23 +14131,23 @@
       </c>
       <c r="I7" s="211">
         <f>'AVG target price'!C9</f>
-        <v>176.8253439975197</v>
+        <v>164.10074202632939</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B8" s="184" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="6" t="e" cm="1" vm="3">
-        <f t="array" ref="C8">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C8" s="6" cm="1">
+        <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
+        <v>0.49</v>
       </c>
       <c r="E8" s="184" t="s">
         <v>269</v>
       </c>
       <c r="F8" s="191">
         <f ca="1">Statement!AC157</f>
-        <v>3.4719799108677028E-2</v>
+        <v>3.514802044811232E-2</v>
       </c>
       <c r="H8" s="183" t="str">
         <f>'AVG target price'!B11</f>
@@ -14184,7 +14155,7 @@
       </c>
       <c r="I8" s="212">
         <f ca="1">'AVG target price'!C11</f>
-        <v>0.21713480174504193</v>
+        <v>0.1434794929017448</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -14193,30 +14164,30 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>-1.6716999999999999E-2</v>
+        <v>-2.8697E-2</v>
       </c>
       <c r="E9" s="184" t="s">
         <v>292</v>
       </c>
       <c r="F9" s="191">
         <f ca="1">Statement!AC158</f>
-        <v>2.1617544846056564E-2</v>
+        <v>2.1884167759982566E-2</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B10" s="184" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="73" t="e" cm="1" vm="4">
-        <f t="array" ref="C10">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C10" s="73" cm="1">
+        <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
+        <v>3.4139999999999999E-3</v>
       </c>
       <c r="E10" s="184" t="s">
         <v>297</v>
       </c>
       <c r="F10" s="191">
         <f ca="1">Statement!AC160</f>
-        <v>9.5585878386252963E-3</v>
+        <v>9.6764799748831655E-3</v>
       </c>
       <c r="H10" s="183" t="s">
         <v>420</v>
@@ -14296,7 +14267,7 @@
       </c>
       <c r="F15" s="191">
         <f ca="1">Statement!AC172</f>
-        <v>0.19453620720508039</v>
+        <v>0.19693554583481346</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -14309,10 +14280,10 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="257" t="s">
+      <c r="B17" s="258" t="s">
         <v>90</v>
       </c>
-      <c r="C17" s="257"/>
+      <c r="C17" s="258"/>
       <c r="E17" s="183" t="s">
         <v>300</v>
       </c>
@@ -14385,14 +14356,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="257" t="s">
+      <c r="B25" s="258" t="s">
         <v>107</v>
       </c>
-      <c r="C25" s="257"/>
-      <c r="E25" s="255" t="s">
+      <c r="C25" s="258"/>
+      <c r="E25" s="256" t="s">
         <v>343</v>
       </c>
-      <c r="F25" s="256"/>
+      <c r="F25" s="257"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="183" t="s">
@@ -14401,7 +14372,7 @@
       <c r="C26" s="169">
         <v>0.21</v>
       </c>
-      <c r="E26" s="184" t="e" vm="5">
+      <c r="E26" s="184" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
       <c r="F26" s="218" cm="1">
@@ -14441,15 +14412,15 @@
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="258" t="s">
+      <c r="B33" s="255" t="s">
         <v>338</v>
       </c>
-      <c r="C33" s="258"/>
-      <c r="D33" s="258"/>
-      <c r="E33" s="258"/>
-      <c r="F33" s="258"/>
-      <c r="G33" s="258"/>
-      <c r="H33" s="258"/>
+      <c r="C33" s="255"/>
+      <c r="D33" s="255"/>
+      <c r="E33" s="255"/>
+      <c r="F33" s="255"/>
+      <c r="G33" s="255"/>
+      <c r="H33" s="255"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
@@ -14468,24 +14439,24 @@
       </c>
     </row>
     <row r="39" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="258"/>
-      <c r="C39" s="258"/>
-      <c r="D39" s="258"/>
-      <c r="E39" s="258"/>
-      <c r="F39" s="258"/>
-      <c r="G39" s="258"/>
-      <c r="H39" s="258"/>
+      <c r="B39" s="255"/>
+      <c r="C39" s="255"/>
+      <c r="D39" s="255"/>
+      <c r="E39" s="255"/>
+      <c r="F39" s="255"/>
+      <c r="G39" s="255"/>
+      <c r="H39" s="255"/>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B42" s="258" t="s">
+      <c r="B42" s="255" t="s">
         <v>341</v>
       </c>
-      <c r="C42" s="258"/>
-      <c r="D42" s="258"/>
-      <c r="E42" s="258"/>
-      <c r="F42" s="258"/>
-      <c r="G42" s="258"/>
-      <c r="H42" s="258"/>
+      <c r="C42" s="255"/>
+      <c r="D42" s="255"/>
+      <c r="E42" s="255"/>
+      <c r="F42" s="255"/>
+      <c r="G42" s="255"/>
+      <c r="H42" s="255"/>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="41" t="s">
@@ -14524,24 +14495,24 @@
       </c>
     </row>
     <row r="50" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B50" s="258"/>
-      <c r="C50" s="258"/>
-      <c r="D50" s="258"/>
-      <c r="E50" s="258"/>
-      <c r="F50" s="258"/>
-      <c r="G50" s="258"/>
-      <c r="H50" s="258"/>
+      <c r="B50" s="255"/>
+      <c r="C50" s="255"/>
+      <c r="D50" s="255"/>
+      <c r="E50" s="255"/>
+      <c r="F50" s="255"/>
+      <c r="G50" s="255"/>
+      <c r="H50" s="255"/>
     </row>
     <row r="53" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B53" s="258" t="s">
+      <c r="B53" s="255" t="s">
         <v>109</v>
       </c>
-      <c r="C53" s="258"/>
-      <c r="D53" s="258"/>
-      <c r="E53" s="258"/>
-      <c r="F53" s="258"/>
-      <c r="G53" s="258"/>
-      <c r="H53" s="258"/>
+      <c r="C53" s="255"/>
+      <c r="D53" s="255"/>
+      <c r="E53" s="255"/>
+      <c r="F53" s="255"/>
+      <c r="G53" s="255"/>
+      <c r="H53" s="255"/>
     </row>
     <row r="58" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B58" s="41" t="s">
@@ -14612,28 +14583,28 @@
       </c>
     </row>
     <row r="66" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B66" s="258"/>
-      <c r="C66" s="258"/>
-      <c r="D66" s="258"/>
-      <c r="E66" s="258"/>
-      <c r="F66" s="258"/>
-      <c r="G66" s="258"/>
-      <c r="H66" s="258"/>
+      <c r="B66" s="255"/>
+      <c r="C66" s="255"/>
+      <c r="D66" s="255"/>
+      <c r="E66" s="255"/>
+      <c r="F66" s="255"/>
+      <c r="G66" s="255"/>
+      <c r="H66" s="255"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="E25:F25"/>
     <mergeCell ref="B53:H53"/>
     <mergeCell ref="B66:H66"/>
     <mergeCell ref="B33:H33"/>
     <mergeCell ref="B39:H39"/>
     <mergeCell ref="B42:H42"/>
     <mergeCell ref="B50:H50"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="E25:F25"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C10">
     <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
@@ -14703,36 +14674,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="258" t="s">
+      <c r="C2" s="255" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="258"/>
-      <c r="E2" s="258"/>
-      <c r="F2" s="258"/>
-      <c r="G2" s="264"/>
-      <c r="H2" s="265" t="s">
+      <c r="D2" s="255"/>
+      <c r="E2" s="255"/>
+      <c r="F2" s="255"/>
+      <c r="G2" s="267"/>
+      <c r="H2" s="268" t="s">
         <v>114</v>
       </c>
-      <c r="I2" s="258"/>
-      <c r="J2" s="258"/>
-      <c r="K2" s="258"/>
-      <c r="L2" s="258"/>
+      <c r="I2" s="255"/>
+      <c r="J2" s="255"/>
+      <c r="K2" s="255"/>
+      <c r="L2" s="255"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="258" t="s">
+      <c r="S2" s="255" t="s">
         <v>113</v>
       </c>
-      <c r="T2" s="258"/>
-      <c r="U2" s="258"/>
-      <c r="V2" s="258"/>
-      <c r="W2" s="258"/>
-      <c r="X2" s="258"/>
-      <c r="Y2" s="258"/>
-      <c r="Z2" s="258"/>
-      <c r="AA2" s="258" t="s">
+      <c r="T2" s="255"/>
+      <c r="U2" s="255"/>
+      <c r="V2" s="255"/>
+      <c r="W2" s="255"/>
+      <c r="X2" s="255"/>
+      <c r="Y2" s="255"/>
+      <c r="Z2" s="255"/>
+      <c r="AA2" s="255" t="s">
         <v>114</v>
       </c>
-      <c r="AB2" s="258"/>
-      <c r="AC2" s="258"/>
+      <c r="AB2" s="255"/>
+      <c r="AC2" s="255"/>
       <c r="AE2" s="86" t="s">
         <v>85</v>
       </c>
@@ -14743,32 +14714,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="266" t="s">
+      <c r="C4" s="264" t="s">
         <v>116</v>
       </c>
-      <c r="D4" s="266"/>
-      <c r="E4" s="266"/>
-      <c r="F4" s="266"/>
-      <c r="G4" s="266"/>
-      <c r="H4" s="266"/>
-      <c r="I4" s="266"/>
-      <c r="J4" s="266"/>
-      <c r="K4" s="266"/>
-      <c r="L4" s="266"/>
+      <c r="D4" s="264"/>
+      <c r="E4" s="264"/>
+      <c r="F4" s="264"/>
+      <c r="G4" s="264"/>
+      <c r="H4" s="264"/>
+      <c r="I4" s="264"/>
+      <c r="J4" s="264"/>
+      <c r="K4" s="264"/>
+      <c r="L4" s="264"/>
       <c r="O4" s="5"/>
-      <c r="S4" s="267" t="s">
+      <c r="S4" s="265" t="s">
         <v>116</v>
       </c>
-      <c r="T4" s="268"/>
-      <c r="U4" s="268"/>
-      <c r="V4" s="268"/>
-      <c r="W4" s="268"/>
-      <c r="X4" s="268"/>
-      <c r="Y4" s="268"/>
-      <c r="Z4" s="268"/>
-      <c r="AA4" s="268"/>
-      <c r="AB4" s="268"/>
-      <c r="AC4" s="268"/>
+      <c r="T4" s="266"/>
+      <c r="U4" s="266"/>
+      <c r="V4" s="266"/>
+      <c r="W4" s="266"/>
+      <c r="X4" s="266"/>
+      <c r="Y4" s="266"/>
+      <c r="Z4" s="266"/>
+      <c r="AA4" s="266"/>
+      <c r="AB4" s="266"/>
+      <c r="AC4" s="266"/>
       <c r="AE4" s="88"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -15456,33 +15427,33 @@
       <c r="Q12" s="92"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="266" t="s">
+      <c r="C13" s="264" t="s">
         <v>122</v>
       </c>
-      <c r="D13" s="266"/>
-      <c r="E13" s="266"/>
-      <c r="F13" s="266"/>
-      <c r="G13" s="266"/>
-      <c r="H13" s="266"/>
-      <c r="I13" s="266"/>
-      <c r="J13" s="266"/>
-      <c r="K13" s="266"/>
-      <c r="L13" s="266"/>
+      <c r="D13" s="264"/>
+      <c r="E13" s="264"/>
+      <c r="F13" s="264"/>
+      <c r="G13" s="264"/>
+      <c r="H13" s="264"/>
+      <c r="I13" s="264"/>
+      <c r="J13" s="264"/>
+      <c r="K13" s="264"/>
+      <c r="L13" s="264"/>
       <c r="O13" s="5"/>
       <c r="Q13" s="92"/>
-      <c r="S13" s="267" t="s">
+      <c r="S13" s="265" t="s">
         <v>122</v>
       </c>
-      <c r="T13" s="268"/>
-      <c r="U13" s="268"/>
-      <c r="V13" s="268"/>
-      <c r="W13" s="268"/>
-      <c r="X13" s="268"/>
-      <c r="Y13" s="268"/>
-      <c r="Z13" s="268"/>
-      <c r="AA13" s="268"/>
-      <c r="AB13" s="268"/>
-      <c r="AC13" s="268"/>
+      <c r="T13" s="266"/>
+      <c r="U13" s="266"/>
+      <c r="V13" s="266"/>
+      <c r="W13" s="266"/>
+      <c r="X13" s="266"/>
+      <c r="Y13" s="266"/>
+      <c r="Z13" s="266"/>
+      <c r="AA13" s="266"/>
+      <c r="AB13" s="266"/>
+      <c r="AC13" s="266"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B14" s="16" t="s">
@@ -16091,33 +16062,33 @@
       <c r="Q22" s="92"/>
     </row>
     <row r="23" spans="2:31" x14ac:dyDescent="0.2">
-      <c r="C23" s="266" t="s">
+      <c r="C23" s="264" t="s">
         <v>124</v>
       </c>
-      <c r="D23" s="266"/>
-      <c r="E23" s="266"/>
-      <c r="F23" s="266"/>
-      <c r="G23" s="266"/>
-      <c r="H23" s="266"/>
-      <c r="I23" s="266"/>
-      <c r="J23" s="266"/>
-      <c r="K23" s="266"/>
-      <c r="L23" s="266"/>
+      <c r="D23" s="264"/>
+      <c r="E23" s="264"/>
+      <c r="F23" s="264"/>
+      <c r="G23" s="264"/>
+      <c r="H23" s="264"/>
+      <c r="I23" s="264"/>
+      <c r="J23" s="264"/>
+      <c r="K23" s="264"/>
+      <c r="L23" s="264"/>
       <c r="O23" s="5"/>
       <c r="Q23" s="92"/>
-      <c r="S23" s="267" t="s">
+      <c r="S23" s="265" t="s">
         <v>124</v>
       </c>
-      <c r="T23" s="268"/>
-      <c r="U23" s="268"/>
-      <c r="V23" s="268"/>
-      <c r="W23" s="268"/>
-      <c r="X23" s="268"/>
-      <c r="Y23" s="268"/>
-      <c r="Z23" s="268"/>
-      <c r="AA23" s="268"/>
-      <c r="AB23" s="268"/>
-      <c r="AC23" s="268"/>
+      <c r="T23" s="266"/>
+      <c r="U23" s="266"/>
+      <c r="V23" s="266"/>
+      <c r="W23" s="266"/>
+      <c r="X23" s="266"/>
+      <c r="Y23" s="266"/>
+      <c r="Z23" s="266"/>
+      <c r="AA23" s="266"/>
+      <c r="AB23" s="266"/>
+      <c r="AC23" s="266"/>
       <c r="AE23" s="88" t="str">
         <f>AE2</f>
         <v>TTM/YTD</v>
@@ -17436,32 +17407,32 @@
       <c r="O39" s="5"/>
     </row>
     <row r="40" spans="2:31" x14ac:dyDescent="0.2">
-      <c r="C40" s="266" t="s">
+      <c r="C40" s="264" t="s">
         <v>126</v>
       </c>
-      <c r="D40" s="266"/>
-      <c r="E40" s="266"/>
-      <c r="F40" s="266"/>
-      <c r="G40" s="266"/>
-      <c r="H40" s="266"/>
-      <c r="I40" s="266"/>
-      <c r="J40" s="266"/>
-      <c r="K40" s="266"/>
-      <c r="L40" s="266"/>
+      <c r="D40" s="264"/>
+      <c r="E40" s="264"/>
+      <c r="F40" s="264"/>
+      <c r="G40" s="264"/>
+      <c r="H40" s="264"/>
+      <c r="I40" s="264"/>
+      <c r="J40" s="264"/>
+      <c r="K40" s="264"/>
+      <c r="L40" s="264"/>
       <c r="O40" s="5"/>
-      <c r="S40" s="267" t="s">
+      <c r="S40" s="265" t="s">
         <v>126</v>
       </c>
-      <c r="T40" s="268"/>
-      <c r="U40" s="268"/>
-      <c r="V40" s="268"/>
-      <c r="W40" s="268"/>
-      <c r="X40" s="268"/>
-      <c r="Y40" s="268"/>
-      <c r="Z40" s="268"/>
-      <c r="AA40" s="268"/>
-      <c r="AB40" s="268"/>
-      <c r="AC40" s="268"/>
+      <c r="T40" s="266"/>
+      <c r="U40" s="266"/>
+      <c r="V40" s="266"/>
+      <c r="W40" s="266"/>
+      <c r="X40" s="266"/>
+      <c r="Y40" s="266"/>
+      <c r="Z40" s="266"/>
+      <c r="AA40" s="266"/>
+      <c r="AB40" s="266"/>
+      <c r="AC40" s="266"/>
     </row>
     <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -18028,18 +17999,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="S2:Z2"/>
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="S4:AC4"/>
     <mergeCell ref="C13:L13"/>
     <mergeCell ref="S13:AC13"/>
     <mergeCell ref="C23:L23"/>
     <mergeCell ref="S23:AC23"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="S40:AC40"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="S2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="S4:AC4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -18073,35 +18044,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="258" t="s">
+      <c r="C2" s="255" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="258"/>
-      <c r="E2" s="258"/>
-      <c r="F2" s="258"/>
-      <c r="G2" s="264"/>
-      <c r="H2" s="265" t="s">
+      <c r="D2" s="255"/>
+      <c r="E2" s="255"/>
+      <c r="F2" s="255"/>
+      <c r="G2" s="267"/>
+      <c r="H2" s="268" t="s">
         <v>114</v>
       </c>
-      <c r="I2" s="258"/>
-      <c r="J2" s="258"/>
-      <c r="K2" s="258"/>
-      <c r="L2" s="258"/>
-      <c r="P2" s="258" t="s">
+      <c r="I2" s="255"/>
+      <c r="J2" s="255"/>
+      <c r="K2" s="255"/>
+      <c r="L2" s="255"/>
+      <c r="P2" s="255" t="s">
         <v>113</v>
       </c>
-      <c r="Q2" s="258"/>
-      <c r="R2" s="258"/>
-      <c r="S2" s="258"/>
-      <c r="T2" s="258"/>
-      <c r="U2" s="258"/>
-      <c r="V2" s="258"/>
-      <c r="W2" s="258"/>
-      <c r="X2" s="258" t="s">
+      <c r="Q2" s="255"/>
+      <c r="R2" s="255"/>
+      <c r="S2" s="255"/>
+      <c r="T2" s="255"/>
+      <c r="U2" s="255"/>
+      <c r="V2" s="255"/>
+      <c r="W2" s="255"/>
+      <c r="X2" s="255" t="s">
         <v>114</v>
       </c>
-      <c r="Y2" s="258"/>
-      <c r="Z2" s="258"/>
+      <c r="Y2" s="255"/>
+      <c r="Z2" s="255"/>
       <c r="AB2" s="86" t="s">
         <v>115</v>
       </c>
@@ -18110,31 +18081,31 @@
     <row r="4" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="266" t="s">
+      <c r="C4" s="264" t="s">
         <v>116</v>
       </c>
-      <c r="D4" s="266"/>
-      <c r="E4" s="266"/>
-      <c r="F4" s="266"/>
-      <c r="G4" s="266"/>
-      <c r="H4" s="266"/>
-      <c r="I4" s="266"/>
-      <c r="J4" s="266"/>
-      <c r="K4" s="266"/>
-      <c r="L4" s="266"/>
-      <c r="P4" s="268" t="s">
+      <c r="D4" s="264"/>
+      <c r="E4" s="264"/>
+      <c r="F4" s="264"/>
+      <c r="G4" s="264"/>
+      <c r="H4" s="264"/>
+      <c r="I4" s="264"/>
+      <c r="J4" s="264"/>
+      <c r="K4" s="264"/>
+      <c r="L4" s="264"/>
+      <c r="P4" s="266" t="s">
         <v>116</v>
       </c>
-      <c r="Q4" s="268"/>
-      <c r="R4" s="268"/>
-      <c r="S4" s="268"/>
-      <c r="T4" s="268"/>
-      <c r="U4" s="268"/>
-      <c r="V4" s="268"/>
-      <c r="W4" s="268"/>
-      <c r="X4" s="268"/>
-      <c r="Y4" s="268"/>
-      <c r="Z4" s="268"/>
+      <c r="Q4" s="266"/>
+      <c r="R4" s="266"/>
+      <c r="S4" s="266"/>
+      <c r="T4" s="266"/>
+      <c r="U4" s="266"/>
+      <c r="V4" s="266"/>
+      <c r="W4" s="266"/>
+      <c r="X4" s="266"/>
+      <c r="Y4" s="266"/>
+      <c r="Z4" s="266"/>
       <c r="AB4" s="88"/>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
@@ -18329,32 +18300,32 @@
       <c r="N8" s="92"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C9" s="266" t="s">
+      <c r="C9" s="264" t="s">
         <v>129</v>
       </c>
-      <c r="D9" s="266"/>
-      <c r="E9" s="266"/>
-      <c r="F9" s="266"/>
-      <c r="G9" s="266"/>
-      <c r="H9" s="266"/>
-      <c r="I9" s="266"/>
-      <c r="J9" s="266"/>
-      <c r="K9" s="266"/>
-      <c r="L9" s="266"/>
+      <c r="D9" s="264"/>
+      <c r="E9" s="264"/>
+      <c r="F9" s="264"/>
+      <c r="G9" s="264"/>
+      <c r="H9" s="264"/>
+      <c r="I9" s="264"/>
+      <c r="J9" s="264"/>
+      <c r="K9" s="264"/>
+      <c r="L9" s="264"/>
       <c r="N9" s="92"/>
-      <c r="P9" s="268" t="s">
+      <c r="P9" s="266" t="s">
         <v>130</v>
       </c>
-      <c r="Q9" s="268"/>
-      <c r="R9" s="268"/>
-      <c r="S9" s="268"/>
-      <c r="T9" s="268"/>
-      <c r="U9" s="268"/>
-      <c r="V9" s="268"/>
-      <c r="W9" s="268"/>
-      <c r="X9" s="268"/>
-      <c r="Y9" s="268"/>
-      <c r="Z9" s="268"/>
+      <c r="Q9" s="266"/>
+      <c r="R9" s="266"/>
+      <c r="S9" s="266"/>
+      <c r="T9" s="266"/>
+      <c r="U9" s="266"/>
+      <c r="V9" s="266"/>
+      <c r="W9" s="266"/>
+      <c r="X9" s="266"/>
+      <c r="Y9" s="266"/>
+      <c r="Z9" s="266"/>
       <c r="AB9" s="88">
         <f>AB4</f>
         <v>0</v>
@@ -18924,31 +18895,31 @@
       </c>
     </row>
     <row r="18" spans="2:26" x14ac:dyDescent="0.2">
-      <c r="C18" s="266" t="s">
+      <c r="C18" s="264" t="s">
         <v>132</v>
       </c>
-      <c r="D18" s="266"/>
-      <c r="E18" s="266"/>
-      <c r="F18" s="266"/>
-      <c r="G18" s="266"/>
-      <c r="H18" s="266"/>
-      <c r="I18" s="266"/>
-      <c r="J18" s="266"/>
-      <c r="K18" s="266"/>
-      <c r="L18" s="266"/>
-      <c r="P18" s="268" t="s">
+      <c r="D18" s="264"/>
+      <c r="E18" s="264"/>
+      <c r="F18" s="264"/>
+      <c r="G18" s="264"/>
+      <c r="H18" s="264"/>
+      <c r="I18" s="264"/>
+      <c r="J18" s="264"/>
+      <c r="K18" s="264"/>
+      <c r="L18" s="264"/>
+      <c r="P18" s="266" t="s">
         <v>132</v>
       </c>
-      <c r="Q18" s="268"/>
-      <c r="R18" s="268"/>
-      <c r="S18" s="268"/>
-      <c r="T18" s="268"/>
-      <c r="U18" s="268"/>
-      <c r="V18" s="268"/>
-      <c r="W18" s="268"/>
-      <c r="X18" s="268"/>
-      <c r="Y18" s="268"/>
-      <c r="Z18" s="268"/>
+      <c r="Q18" s="266"/>
+      <c r="R18" s="266"/>
+      <c r="S18" s="266"/>
+      <c r="T18" s="266"/>
+      <c r="U18" s="266"/>
+      <c r="V18" s="266"/>
+      <c r="W18" s="266"/>
+      <c r="X18" s="266"/>
+      <c r="Y18" s="266"/>
+      <c r="Z18" s="266"/>
     </row>
     <row r="19" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -19508,20 +19479,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="258" t="s">
+      <c r="C3" s="255" t="s">
         <v>113</v>
       </c>
-      <c r="D3" s="258"/>
-      <c r="E3" s="258"/>
-      <c r="F3" s="258"/>
-      <c r="G3" s="264"/>
-      <c r="H3" s="265" t="s">
+      <c r="D3" s="255"/>
+      <c r="E3" s="255"/>
+      <c r="F3" s="255"/>
+      <c r="G3" s="267"/>
+      <c r="H3" s="268" t="s">
         <v>114</v>
       </c>
-      <c r="I3" s="258"/>
-      <c r="J3" s="258"/>
-      <c r="K3" s="258"/>
-      <c r="L3" s="258"/>
+      <c r="I3" s="255"/>
+      <c r="J3" s="255"/>
+      <c r="K3" s="255"/>
+      <c r="L3" s="255"/>
       <c r="P3" s="269"/>
       <c r="Q3" s="269"/>
       <c r="R3" s="269"/>
@@ -19539,18 +19510,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="87"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="266" t="s">
+      <c r="C5" s="264" t="s">
         <v>116</v>
       </c>
-      <c r="D5" s="266"/>
-      <c r="E5" s="266"/>
-      <c r="F5" s="266"/>
-      <c r="G5" s="266"/>
-      <c r="H5" s="266"/>
-      <c r="I5" s="266"/>
-      <c r="J5" s="266"/>
-      <c r="K5" s="266"/>
-      <c r="L5" s="266"/>
+      <c r="D5" s="264"/>
+      <c r="E5" s="264"/>
+      <c r="F5" s="264"/>
+      <c r="G5" s="264"/>
+      <c r="H5" s="264"/>
+      <c r="I5" s="264"/>
+      <c r="J5" s="264"/>
+      <c r="K5" s="264"/>
+      <c r="L5" s="264"/>
       <c r="P5" s="269"/>
       <c r="Q5" s="269"/>
       <c r="R5" s="269"/>
@@ -19747,18 +19718,18 @@
       <c r="N10" s="92"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="266" t="s">
+      <c r="C11" s="264" t="s">
         <v>136</v>
       </c>
-      <c r="D11" s="266"/>
-      <c r="E11" s="266"/>
-      <c r="F11" s="266"/>
-      <c r="G11" s="266"/>
-      <c r="H11" s="266"/>
-      <c r="I11" s="266"/>
-      <c r="J11" s="266"/>
-      <c r="K11" s="266"/>
-      <c r="L11" s="266"/>
+      <c r="D11" s="264"/>
+      <c r="E11" s="264"/>
+      <c r="F11" s="264"/>
+      <c r="G11" s="264"/>
+      <c r="H11" s="264"/>
+      <c r="I11" s="264"/>
+      <c r="J11" s="264"/>
+      <c r="K11" s="264"/>
+      <c r="L11" s="264"/>
       <c r="N11" s="92"/>
       <c r="P11" s="269"/>
       <c r="Q11" s="269"/>
@@ -20012,18 +19983,18 @@
       <c r="D16" s="24"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="266" t="s">
+      <c r="C18" s="264" t="s">
         <v>141</v>
       </c>
-      <c r="D18" s="266"/>
-      <c r="E18" s="266"/>
-      <c r="F18" s="266"/>
-      <c r="G18" s="266"/>
-      <c r="H18" s="266"/>
-      <c r="I18" s="266"/>
-      <c r="J18" s="266"/>
-      <c r="K18" s="266"/>
-      <c r="L18" s="266"/>
+      <c r="D18" s="264"/>
+      <c r="E18" s="264"/>
+      <c r="F18" s="264"/>
+      <c r="G18" s="264"/>
+      <c r="H18" s="264"/>
+      <c r="I18" s="264"/>
+      <c r="J18" s="264"/>
+      <c r="K18" s="264"/>
+      <c r="L18" s="264"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -20241,18 +20212,18 @@
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="111"/>
-      <c r="C26" s="266" t="s">
+      <c r="C26" s="264" t="s">
         <v>147</v>
       </c>
-      <c r="D26" s="266"/>
-      <c r="E26" s="266"/>
-      <c r="F26" s="266"/>
-      <c r="G26" s="266"/>
-      <c r="H26" s="266"/>
-      <c r="I26" s="266"/>
-      <c r="J26" s="266"/>
-      <c r="K26" s="266"/>
-      <c r="L26" s="266"/>
+      <c r="D26" s="264"/>
+      <c r="E26" s="264"/>
+      <c r="F26" s="264"/>
+      <c r="G26" s="264"/>
+      <c r="H26" s="264"/>
+      <c r="I26" s="264"/>
+      <c r="J26" s="264"/>
+      <c r="K26" s="264"/>
+      <c r="L26" s="264"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="16" t="s">
@@ -20444,18 +20415,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="111"/>
-      <c r="C33" s="266" t="s">
+      <c r="C33" s="264" t="s">
         <v>151</v>
       </c>
-      <c r="D33" s="266"/>
-      <c r="E33" s="266"/>
-      <c r="F33" s="266"/>
-      <c r="G33" s="266"/>
-      <c r="H33" s="266"/>
-      <c r="I33" s="266"/>
-      <c r="J33" s="266"/>
-      <c r="K33" s="266"/>
-      <c r="L33" s="266"/>
+      <c r="D33" s="264"/>
+      <c r="E33" s="264"/>
+      <c r="F33" s="264"/>
+      <c r="G33" s="264"/>
+      <c r="H33" s="264"/>
+      <c r="I33" s="264"/>
+      <c r="J33" s="264"/>
+      <c r="K33" s="264"/>
+      <c r="L33" s="264"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
@@ -20639,18 +20610,18 @@
       <c r="C39" s="127"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="266" t="s">
+      <c r="C40" s="264" t="s">
         <v>154</v>
       </c>
-      <c r="D40" s="266"/>
-      <c r="E40" s="266"/>
-      <c r="F40" s="266"/>
-      <c r="G40" s="266"/>
-      <c r="H40" s="266"/>
-      <c r="I40" s="266"/>
-      <c r="J40" s="266"/>
-      <c r="K40" s="266"/>
-      <c r="L40" s="266"/>
+      <c r="D40" s="264"/>
+      <c r="E40" s="264"/>
+      <c r="F40" s="264"/>
+      <c r="G40" s="264"/>
+      <c r="H40" s="264"/>
+      <c r="I40" s="264"/>
+      <c r="J40" s="264"/>
+      <c r="K40" s="264"/>
+      <c r="L40" s="264"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -20914,12 +20885,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -20927,6 +20892,12 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -20964,20 +20935,20 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="258" t="s">
+      <c r="C2" s="255" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="258"/>
-      <c r="E2" s="258"/>
-      <c r="F2" s="258"/>
-      <c r="G2" s="264"/>
-      <c r="H2" s="265" t="s">
+      <c r="D2" s="255"/>
+      <c r="E2" s="255"/>
+      <c r="F2" s="255"/>
+      <c r="G2" s="267"/>
+      <c r="H2" s="268" t="s">
         <v>114</v>
       </c>
-      <c r="I2" s="258"/>
-      <c r="J2" s="258"/>
-      <c r="K2" s="258"/>
-      <c r="L2" s="258"/>
+      <c r="I2" s="255"/>
+      <c r="J2" s="255"/>
+      <c r="K2" s="255"/>
+      <c r="L2" s="255"/>
       <c r="S2" s="269"/>
       <c r="T2" s="269"/>
       <c r="U2" s="269"/>
@@ -20995,18 +20966,18 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="266" t="s">
+      <c r="C4" s="264" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="266"/>
-      <c r="E4" s="266"/>
-      <c r="F4" s="266"/>
-      <c r="G4" s="266"/>
-      <c r="H4" s="266"/>
-      <c r="I4" s="266"/>
-      <c r="J4" s="266"/>
-      <c r="K4" s="266"/>
-      <c r="L4" s="266"/>
+      <c r="D4" s="264"/>
+      <c r="E4" s="264"/>
+      <c r="F4" s="264"/>
+      <c r="G4" s="264"/>
+      <c r="H4" s="264"/>
+      <c r="I4" s="264"/>
+      <c r="J4" s="264"/>
+      <c r="K4" s="264"/>
+      <c r="L4" s="264"/>
       <c r="S4" s="269"/>
       <c r="T4" s="269"/>
       <c r="U4" s="269"/>
@@ -21380,18 +21351,18 @@
       <c r="AE10" s="64"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="266" t="s">
+      <c r="C13" s="264" t="s">
         <v>162</v>
       </c>
-      <c r="D13" s="266"/>
-      <c r="E13" s="266"/>
-      <c r="F13" s="266"/>
-      <c r="G13" s="266"/>
-      <c r="H13" s="266"/>
-      <c r="I13" s="266"/>
-      <c r="J13" s="266"/>
-      <c r="K13" s="266"/>
-      <c r="L13" s="266"/>
+      <c r="D13" s="264"/>
+      <c r="E13" s="264"/>
+      <c r="F13" s="264"/>
+      <c r="G13" s="264"/>
+      <c r="H13" s="264"/>
+      <c r="I13" s="264"/>
+      <c r="J13" s="264"/>
+      <c r="K13" s="264"/>
+      <c r="L13" s="264"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="12">
@@ -21484,18 +21455,18 @@
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C18" s="266" t="s">
+      <c r="C18" s="264" t="s">
         <v>163</v>
       </c>
-      <c r="D18" s="266"/>
-      <c r="E18" s="266"/>
-      <c r="F18" s="266"/>
-      <c r="G18" s="266"/>
-      <c r="H18" s="266"/>
-      <c r="I18" s="266"/>
-      <c r="J18" s="266"/>
-      <c r="K18" s="266"/>
-      <c r="L18" s="266"/>
+      <c r="D18" s="264"/>
+      <c r="E18" s="264"/>
+      <c r="F18" s="264"/>
+      <c r="G18" s="264"/>
+      <c r="H18" s="264"/>
+      <c r="I18" s="264"/>
+      <c r="J18" s="264"/>
+      <c r="K18" s="264"/>
+      <c r="L18" s="264"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -21687,18 +21658,18 @@
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C25" s="266" t="s">
+      <c r="C25" s="264" t="s">
         <v>266</v>
       </c>
-      <c r="D25" s="266"/>
-      <c r="E25" s="266"/>
-      <c r="F25" s="266"/>
-      <c r="G25" s="266"/>
-      <c r="H25" s="266"/>
-      <c r="I25" s="266"/>
-      <c r="J25" s="266"/>
-      <c r="K25" s="266"/>
-      <c r="L25" s="266"/>
+      <c r="D25" s="264"/>
+      <c r="E25" s="264"/>
+      <c r="F25" s="264"/>
+      <c r="G25" s="264"/>
+      <c r="H25" s="264"/>
+      <c r="I25" s="264"/>
+      <c r="J25" s="264"/>
+      <c r="K25" s="264"/>
+      <c r="L25" s="264"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B26" s="16" t="s">
@@ -21836,18 +21807,18 @@
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C31" s="266" t="s">
+      <c r="C31" s="264" t="s">
         <v>78</v>
       </c>
-      <c r="D31" s="266"/>
-      <c r="E31" s="266"/>
-      <c r="F31" s="266"/>
-      <c r="G31" s="266"/>
-      <c r="H31" s="266"/>
-      <c r="I31" s="266"/>
-      <c r="J31" s="266"/>
-      <c r="K31" s="266"/>
-      <c r="L31" s="266"/>
+      <c r="D31" s="264"/>
+      <c r="E31" s="264"/>
+      <c r="F31" s="264"/>
+      <c r="G31" s="264"/>
+      <c r="H31" s="264"/>
+      <c r="I31" s="264"/>
+      <c r="J31" s="264"/>
+      <c r="K31" s="264"/>
+      <c r="L31" s="264"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="16" t="s">
@@ -21986,16 +21957,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C31:L31"/>
+    <mergeCell ref="C25:L25"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="S2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
     <mergeCell ref="C13:L13"/>
     <mergeCell ref="C18:L18"/>
-    <mergeCell ref="C31:L31"/>
-    <mergeCell ref="C25:L25"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="S2:Z2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -22058,10 +22029,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="258" t="s">
+      <c r="B4" s="255" t="s">
         <v>170</v>
       </c>
-      <c r="C4" s="258"/>
+      <c r="C4" s="255"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -22078,7 +22049,7 @@
       </c>
       <c r="C6" s="135">
         <f ca="1">Overview!C5</f>
-        <v>145.28</v>
+        <v>143.51</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22087,7 +22058,7 @@
       </c>
       <c r="C7" s="136">
         <f ca="1">C5*C6</f>
-        <v>7281724.1600000001</v>
+        <v>7193008.2199999997</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22146,10 +22117,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="258" t="s">
+      <c r="B15" s="255" t="s">
         <v>177</v>
       </c>
-      <c r="C15" s="258"/>
+      <c r="C15" s="255"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -22238,20 +22209,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="258" t="s">
+      <c r="C3" s="255" t="s">
         <v>113</v>
       </c>
-      <c r="D3" s="258"/>
-      <c r="E3" s="258"/>
-      <c r="F3" s="258"/>
-      <c r="G3" s="264"/>
-      <c r="H3" s="265" t="s">
+      <c r="D3" s="255"/>
+      <c r="E3" s="255"/>
+      <c r="F3" s="255"/>
+      <c r="G3" s="267"/>
+      <c r="H3" s="268" t="s">
         <v>114</v>
       </c>
-      <c r="I3" s="258"/>
-      <c r="J3" s="258"/>
-      <c r="K3" s="258"/>
-      <c r="L3" s="258"/>
+      <c r="I3" s="255"/>
+      <c r="J3" s="255"/>
+      <c r="K3" s="255"/>
+      <c r="L3" s="255"/>
       <c r="P3" s="269"/>
       <c r="Q3" s="269"/>
       <c r="R3" s="269"/>
@@ -22269,18 +22240,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="87"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="266" t="s">
+      <c r="C5" s="264" t="s">
         <v>184</v>
       </c>
-      <c r="D5" s="266"/>
-      <c r="E5" s="266"/>
-      <c r="F5" s="266"/>
-      <c r="G5" s="266"/>
-      <c r="H5" s="266"/>
-      <c r="I5" s="266"/>
-      <c r="J5" s="266"/>
-      <c r="K5" s="266"/>
-      <c r="L5" s="266"/>
+      <c r="D5" s="264"/>
+      <c r="E5" s="264"/>
+      <c r="F5" s="264"/>
+      <c r="G5" s="264"/>
+      <c r="H5" s="264"/>
+      <c r="I5" s="264"/>
+      <c r="J5" s="264"/>
+      <c r="K5" s="264"/>
+      <c r="L5" s="264"/>
       <c r="P5" s="269"/>
       <c r="Q5" s="269"/>
       <c r="R5" s="269"/>
@@ -22537,10 +22508,10 @@
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="258" t="s">
+      <c r="B13" s="255" t="s">
         <v>188</v>
       </c>
-      <c r="C13" s="258"/>
+      <c r="C13" s="255"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -22560,10 +22531,10 @@
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="258" t="s">
+      <c r="B18" s="255" t="s">
         <v>190</v>
       </c>
-      <c r="C18" s="258"/>
+      <c r="C18" s="255"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -22677,37 +22648,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="258" t="s">
+      <c r="C2" s="255" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="258"/>
-      <c r="E2" s="258"/>
-      <c r="F2" s="258"/>
-      <c r="G2" s="264"/>
-      <c r="H2" s="265" t="s">
+      <c r="D2" s="255"/>
+      <c r="E2" s="255"/>
+      <c r="F2" s="255"/>
+      <c r="G2" s="267"/>
+      <c r="H2" s="268" t="s">
         <v>114</v>
       </c>
-      <c r="I2" s="258"/>
-      <c r="J2" s="258"/>
-      <c r="K2" s="258"/>
-      <c r="L2" s="258"/>
+      <c r="I2" s="255"/>
+      <c r="J2" s="255"/>
+      <c r="K2" s="255"/>
+      <c r="L2" s="255"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="266" t="s">
+      <c r="C4" s="264" t="s">
         <v>198</v>
       </c>
-      <c r="D4" s="266"/>
-      <c r="E4" s="266"/>
-      <c r="F4" s="266"/>
-      <c r="G4" s="266"/>
-      <c r="H4" s="266"/>
-      <c r="I4" s="266"/>
-      <c r="J4" s="266"/>
-      <c r="K4" s="266"/>
-      <c r="L4" s="266"/>
+      <c r="D4" s="264"/>
+      <c r="E4" s="264"/>
+      <c r="F4" s="264"/>
+      <c r="G4" s="264"/>
+      <c r="H4" s="264"/>
+      <c r="I4" s="264"/>
+      <c r="J4" s="264"/>
+      <c r="K4" s="264"/>
+      <c r="L4" s="264"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -22927,18 +22898,18 @@
       <c r="N10" s="92"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C11" s="266" t="s">
+      <c r="C11" s="264" t="s">
         <v>122</v>
       </c>
-      <c r="D11" s="266"/>
-      <c r="E11" s="266"/>
-      <c r="F11" s="266"/>
-      <c r="G11" s="266"/>
-      <c r="H11" s="266"/>
-      <c r="I11" s="266"/>
-      <c r="J11" s="266"/>
-      <c r="K11" s="266"/>
-      <c r="L11" s="266"/>
+      <c r="D11" s="264"/>
+      <c r="E11" s="264"/>
+      <c r="F11" s="264"/>
+      <c r="G11" s="264"/>
+      <c r="H11" s="264"/>
+      <c r="I11" s="264"/>
+      <c r="J11" s="264"/>
+      <c r="K11" s="264"/>
+      <c r="L11" s="264"/>
       <c r="N11" s="92"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -23132,18 +23103,18 @@
       <c r="N16" s="92"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C17" s="266" t="s">
+      <c r="C17" s="264" t="s">
         <v>200</v>
       </c>
-      <c r="D17" s="266"/>
-      <c r="E17" s="266"/>
-      <c r="F17" s="266"/>
-      <c r="G17" s="266"/>
-      <c r="H17" s="266"/>
-      <c r="I17" s="266"/>
-      <c r="J17" s="266"/>
-      <c r="K17" s="266"/>
-      <c r="L17" s="266"/>
+      <c r="D17" s="264"/>
+      <c r="E17" s="264"/>
+      <c r="F17" s="264"/>
+      <c r="G17" s="264"/>
+      <c r="H17" s="264"/>
+      <c r="I17" s="264"/>
+      <c r="J17" s="264"/>
+      <c r="K17" s="264"/>
+      <c r="L17" s="264"/>
       <c r="N17" s="92"/>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
@@ -23277,18 +23248,18 @@
       <c r="N21" s="92"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C22" s="266" t="s">
+      <c r="C22" s="264" t="s">
         <v>203</v>
       </c>
-      <c r="D22" s="266"/>
-      <c r="E22" s="266"/>
-      <c r="F22" s="266"/>
-      <c r="G22" s="266"/>
-      <c r="H22" s="266"/>
-      <c r="I22" s="266"/>
-      <c r="J22" s="266"/>
-      <c r="K22" s="266"/>
-      <c r="L22" s="266"/>
+      <c r="D22" s="264"/>
+      <c r="E22" s="264"/>
+      <c r="F22" s="264"/>
+      <c r="G22" s="264"/>
+      <c r="H22" s="264"/>
+      <c r="I22" s="264"/>
+      <c r="J22" s="264"/>
+      <c r="K22" s="264"/>
+      <c r="L22" s="264"/>
       <c r="N22" s="92"/>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.2">
@@ -23372,18 +23343,18 @@
       <c r="N26" s="92"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C27" s="266" t="s">
+      <c r="C27" s="264" t="s">
         <v>204</v>
       </c>
-      <c r="D27" s="266"/>
-      <c r="E27" s="266"/>
-      <c r="F27" s="266"/>
-      <c r="G27" s="266"/>
-      <c r="H27" s="266"/>
-      <c r="I27" s="266"/>
-      <c r="J27" s="266"/>
-      <c r="K27" s="266"/>
-      <c r="L27" s="266"/>
+      <c r="D27" s="264"/>
+      <c r="E27" s="264"/>
+      <c r="F27" s="264"/>
+      <c r="G27" s="264"/>
+      <c r="H27" s="264"/>
+      <c r="I27" s="264"/>
+      <c r="J27" s="264"/>
+      <c r="K27" s="264"/>
+      <c r="L27" s="264"/>
       <c r="N27" s="92"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.2">
@@ -23653,10 +23624,10 @@
       <c r="N37" s="92"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B38" s="258" t="s">
+      <c r="B38" s="255" t="s">
         <v>209</v>
       </c>
-      <c r="C38" s="258"/>
+      <c r="C38" s="255"/>
       <c r="N38" s="92"/>
     </row>
     <row r="39" spans="2:14" x14ac:dyDescent="0.2">
@@ -23699,8 +23670,8 @@
         <v>430</v>
       </c>
       <c r="C43" s="24">
-        <f>C42/(1+C40)^5-G31+G32</f>
-        <v>8507877.9031145759</v>
+        <f>C42/(1+C40)^5</f>
+        <v>7232312.903114575</v>
       </c>
     </row>
     <row r="44" spans="2:14" x14ac:dyDescent="0.2">
@@ -23709,7 +23680,7 @@
       </c>
       <c r="C44" s="110">
         <f>SUM(H9:K9)+C43</f>
-        <v>9337453.9564038347</v>
+        <v>8061888.9564038347</v>
       </c>
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.2">
@@ -23736,7 +23707,7 @@
       </c>
       <c r="C47" s="110">
         <f>C44+C45-C46</f>
-        <v>10754012.956403835</v>
+        <v>9478447.9564038347</v>
       </c>
     </row>
     <row r="48" spans="2:14" x14ac:dyDescent="0.2">
@@ -23754,14 +23725,14 @@
       </c>
       <c r="C49" s="254">
         <f>C47/C48</f>
-        <v>214.55674068081549</v>
+        <v>189.1075367384349</v>
       </c>
     </row>
     <row r="51" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B51" s="258" t="s">
+      <c r="B51" s="255" t="s">
         <v>214</v>
       </c>
-      <c r="C51" s="258"/>
+      <c r="C51" s="255"/>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B52" s="1" t="s">
@@ -23817,10 +23788,10 @@
       </c>
     </row>
     <row r="59" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B59" s="258" t="s">
+      <c r="B59" s="255" t="s">
         <v>327</v>
       </c>
-      <c r="C59" s="258"/>
+      <c r="C59" s="255"/>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B60" s="1" t="s">
@@ -23862,8 +23833,8 @@
         <v>430</v>
       </c>
       <c r="C64" s="24">
-        <f>C63/(1+C61)^5-G31+G32</f>
-        <v>8769651.2362081893</v>
+        <f>C63/(1+C61)^5</f>
+        <v>7494086.2362081893</v>
       </c>
     </row>
     <row r="65" spans="2:3" x14ac:dyDescent="0.2">
@@ -23872,7 +23843,7 @@
       </c>
       <c r="C65" s="110">
         <f>SUM(H9:K9)+C64</f>
-        <v>9599227.2894974481</v>
+        <v>8323662.2894974491</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -23899,7 +23870,7 @@
       </c>
       <c r="C68" s="110">
         <f>C65+C66-C67</f>
-        <v>11015786.289497448</v>
+        <v>9740221.28949745</v>
       </c>
     </row>
     <row r="69" spans="2:3" x14ac:dyDescent="0.2">
@@ -23917,7 +23888,7 @@
       </c>
       <c r="C70" s="254">
         <f>C68/C69</f>
-        <v>219.77946389803776</v>
+        <v>194.3302599556572</v>
       </c>
     </row>
   </sheetData>
@@ -23969,10 +23940,10 @@
       <c r="N3" s="92"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="258" t="s">
+      <c r="B4" s="255" t="s">
         <v>218</v>
       </c>
-      <c r="C4" s="258"/>
+      <c r="C4" s="255"/>
       <c r="N4" s="92"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -23990,7 +23961,7 @@
       </c>
       <c r="C6" s="135">
         <f>Multiples!C49</f>
-        <v>214.55674068081549</v>
+        <v>189.1075367384349</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -24008,7 +23979,7 @@
       </c>
       <c r="C8" s="135">
         <f>Multiples!C70</f>
-        <v>219.77946389803776</v>
+        <v>194.3302599556572</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -24017,7 +23988,7 @@
       </c>
       <c r="C9" s="254">
         <f>AVERAGE(C5:C8)</f>
-        <v>176.8253439975197</v>
+        <v>164.10074202632939</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -24026,7 +23997,7 @@
       </c>
       <c r="C10" s="135">
         <f ca="1">Overview!C5</f>
-        <v>145.28</v>
+        <v>143.51</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -24035,7 +24006,7 @@
       </c>
       <c r="C11" s="154">
         <f ca="1">(C9-C10)/C10</f>
-        <v>0.21713480174504193</v>
+        <v>0.1434794929017448</v>
       </c>
     </row>
   </sheetData>
@@ -24091,37 +24062,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="258" t="s">
+      <c r="C2" s="255" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="258"/>
-      <c r="E2" s="258"/>
-      <c r="F2" s="258"/>
-      <c r="G2" s="264"/>
-      <c r="H2" s="265" t="s">
+      <c r="D2" s="255"/>
+      <c r="E2" s="255"/>
+      <c r="F2" s="255"/>
+      <c r="G2" s="267"/>
+      <c r="H2" s="268" t="s">
         <v>114</v>
       </c>
-      <c r="I2" s="258"/>
-      <c r="J2" s="258"/>
-      <c r="K2" s="258"/>
-      <c r="L2" s="258"/>
+      <c r="I2" s="255"/>
+      <c r="J2" s="255"/>
+      <c r="K2" s="255"/>
+      <c r="L2" s="255"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="266" t="s">
+      <c r="C4" s="264" t="s">
         <v>198</v>
       </c>
-      <c r="D4" s="266"/>
-      <c r="E4" s="266"/>
-      <c r="F4" s="266"/>
-      <c r="G4" s="266"/>
-      <c r="H4" s="266"/>
-      <c r="I4" s="266"/>
-      <c r="J4" s="266"/>
-      <c r="K4" s="266"/>
-      <c r="L4" s="266"/>
+      <c r="D4" s="264"/>
+      <c r="E4" s="264"/>
+      <c r="F4" s="264"/>
+      <c r="G4" s="264"/>
+      <c r="H4" s="264"/>
+      <c r="I4" s="264"/>
+      <c r="J4" s="264"/>
+      <c r="K4" s="264"/>
+      <c r="L4" s="264"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -24234,18 +24205,18 @@
       <c r="N8" s="92"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C9" s="266" t="s">
+      <c r="C9" s="264" t="s">
         <v>122</v>
       </c>
-      <c r="D9" s="266"/>
-      <c r="E9" s="266"/>
-      <c r="F9" s="266"/>
-      <c r="G9" s="266"/>
-      <c r="H9" s="266"/>
-      <c r="I9" s="266"/>
-      <c r="J9" s="266"/>
-      <c r="K9" s="266"/>
-      <c r="L9" s="266"/>
+      <c r="D9" s="264"/>
+      <c r="E9" s="264"/>
+      <c r="F9" s="264"/>
+      <c r="G9" s="264"/>
+      <c r="H9" s="264"/>
+      <c r="I9" s="264"/>
+      <c r="J9" s="264"/>
+      <c r="K9" s="264"/>
+      <c r="L9" s="264"/>
       <c r="N9" s="92"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -24366,18 +24337,18 @@
       <c r="N13" s="92"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C14" s="266" t="s">
+      <c r="C14" s="264" t="s">
         <v>413</v>
       </c>
-      <c r="D14" s="266"/>
-      <c r="E14" s="266"/>
-      <c r="F14" s="266"/>
-      <c r="G14" s="266"/>
-      <c r="H14" s="266"/>
-      <c r="I14" s="266"/>
-      <c r="J14" s="266"/>
-      <c r="K14" s="266"/>
-      <c r="L14" s="266"/>
+      <c r="D14" s="264"/>
+      <c r="E14" s="264"/>
+      <c r="F14" s="264"/>
+      <c r="G14" s="264"/>
+      <c r="H14" s="264"/>
+      <c r="I14" s="264"/>
+      <c r="J14" s="264"/>
+      <c r="K14" s="264"/>
+      <c r="L14" s="264"/>
       <c r="N14" s="92"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
@@ -24467,10 +24438,10 @@
       <c r="N19" s="92"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B20" s="258" t="s">
+      <c r="B20" s="255" t="s">
         <v>415</v>
       </c>
-      <c r="C20" s="258"/>
+      <c r="C20" s="255"/>
       <c r="N20" s="92"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
@@ -24572,20 +24543,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="258" t="s">
+      <c r="C3" s="255" t="s">
         <v>113</v>
       </c>
-      <c r="D3" s="258"/>
-      <c r="E3" s="258"/>
-      <c r="F3" s="258"/>
-      <c r="G3" s="264"/>
-      <c r="H3" s="265" t="s">
+      <c r="D3" s="255"/>
+      <c r="E3" s="255"/>
+      <c r="F3" s="255"/>
+      <c r="G3" s="267"/>
+      <c r="H3" s="268" t="s">
         <v>114</v>
       </c>
-      <c r="I3" s="258"/>
-      <c r="J3" s="258"/>
-      <c r="K3" s="258"/>
-      <c r="L3" s="258"/>
+      <c r="I3" s="255"/>
+      <c r="J3" s="255"/>
+      <c r="K3" s="255"/>
+      <c r="L3" s="255"/>
       <c r="P3" s="269"/>
       <c r="Q3" s="269"/>
       <c r="R3" s="269"/>
@@ -24603,18 +24574,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="87"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="266" t="s">
+      <c r="C5" s="264" t="s">
         <v>184</v>
       </c>
-      <c r="D5" s="266"/>
-      <c r="E5" s="266"/>
-      <c r="F5" s="266"/>
-      <c r="G5" s="266"/>
-      <c r="H5" s="266"/>
-      <c r="I5" s="266"/>
-      <c r="J5" s="266"/>
-      <c r="K5" s="266"/>
-      <c r="L5" s="266"/>
+      <c r="D5" s="264"/>
+      <c r="E5" s="264"/>
+      <c r="F5" s="264"/>
+      <c r="G5" s="264"/>
+      <c r="H5" s="264"/>
+      <c r="I5" s="264"/>
+      <c r="J5" s="264"/>
+      <c r="K5" s="264"/>
+      <c r="L5" s="264"/>
       <c r="P5" s="269"/>
       <c r="Q5" s="269"/>
       <c r="R5" s="269"/>
@@ -24865,7 +24836,7 @@
       </c>
       <c r="C15" s="156">
         <f ca="1">Overview!C5</f>
-        <v>145.28</v>
+        <v>143.51</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -24931,7 +24902,7 @@
       </c>
       <c r="C23" s="161">
         <f ca="1">C15*C22</f>
-        <v>6797070.0800000001</v>
+        <v>6714258.8599999994</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -24958,7 +24929,7 @@
       </c>
       <c r="C26" s="162">
         <f ca="1">C23+C25-C24</f>
-        <v>5380511.0800000001</v>
+        <v>5297699.8599999994</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -25042,16 +25013,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
     <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -31743,7 +31714,7 @@
       </c>
       <c r="AC116" s="63">
         <f ca="1">Overview!C5</f>
-        <v>145.28</v>
+        <v>143.51</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -31814,7 +31785,7 @@
       </c>
       <c r="AC117" s="65">
         <f ca="1">AC116/AC85</f>
-        <v>145.28</v>
+        <v>143.51</v>
       </c>
     </row>
     <row r="119" spans="1:31" x14ac:dyDescent="0.2">
@@ -32924,7 +32895,7 @@
       <c r="AA146" s="49"/>
       <c r="AC146" s="72">
         <f ca="1">AC117/Statement!AC26</f>
-        <v>46.258722122295872</v>
+        <v>45.695134992914923</v>
       </c>
     </row>
     <row r="147" spans="2:29" x14ac:dyDescent="0.2">
@@ -32961,7 +32932,7 @@
       <c r="AA147" s="49"/>
       <c r="AC147" s="72">
         <f ca="1">AC117/(Statement!AC5/Statement!AC22)</f>
-        <v>6.2389730368986323</v>
+        <v>6.1629613196952269</v>
       </c>
     </row>
     <row r="148" spans="2:29" x14ac:dyDescent="0.2">
@@ -33022,7 +32993,7 @@
       </c>
       <c r="AC148" s="72">
         <f ca="1">AC117/(Statement!AC49/Statement!AC75)</f>
-        <v>4.8214993098027872</v>
+        <v>4.7627571995443132</v>
       </c>
     </row>
     <row r="149" spans="2:29" x14ac:dyDescent="0.2">
@@ -33083,7 +33054,7 @@
       </c>
       <c r="AC149" s="143">
         <f ca="1">Statement!AC117*Statement!AC78</f>
-        <v>7281724.1600000001</v>
+        <v>7193008.2199999997</v>
       </c>
     </row>
     <row r="150" spans="2:29" x14ac:dyDescent="0.2">
@@ -33144,7 +33115,7 @@
       </c>
       <c r="AC150" s="143">
         <f ca="1">AC149+AC108-AC107+AC48+AC45</f>
-        <v>5865165.1600000001</v>
+        <v>5776449.2199999997</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -33181,7 +33152,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="182">
         <f ca="1">AC150/AC5</f>
-        <v>5.1224060394654334</v>
+        <v>5.0449250044978085</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -33218,7 +33189,7 @@
       <c r="AA152" s="49"/>
       <c r="AC152" s="182">
         <f ca="1">AC150/AC12</f>
-        <v>37.337525288856355</v>
+        <v>36.772761371232136</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -33353,7 +33324,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="72">
         <f t="shared" ref="AC155:AC156" ca="1" si="151">AC149/AC153</f>
-        <v>28.802009967565859</v>
+        <v>28.451104422118501</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -33390,7 +33361,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="72">
         <f t="shared" ca="1" si="151"/>
-        <v>35.177345682108275</v>
+        <v>34.645256439306252</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -33427,7 +33398,7 @@
       <c r="AA157" s="49"/>
       <c r="AC157" s="74">
         <f t="shared" ref="AC157" ca="1" si="154">AC153/AC149</f>
-        <v>3.4719799108677028E-2</v>
+        <v>3.514802044811232E-2</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
@@ -33464,7 +33435,7 @@
       <c r="AA158" s="49"/>
       <c r="AC158" s="74">
         <f ca="1">AC26/AC117</f>
-        <v>2.1617544846056564E-2</v>
+        <v>2.1884167759982566E-2</v>
       </c>
     </row>
     <row r="159" spans="2:29" x14ac:dyDescent="0.2">
@@ -33538,7 +33509,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="154">
         <f ca="1">-AC63/AC149</f>
-        <v>9.5585878386252963E-3</v>
+        <v>9.6764799748831655E-3</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -33575,7 +33546,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="154">
         <f ca="1">-(AC63+AC64)/AC149</f>
-        <v>9.5585878386252963E-3</v>
+        <v>9.6764799748831655E-3</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -34078,7 +34049,7 @@
       <c r="AA172" s="49"/>
       <c r="AC172" s="154">
         <f ca="1">(AC107-AC108)/AC149</f>
-        <v>0.19453620720508039</v>
+        <v>0.19693554583481346</v>
       </c>
     </row>
     <row r="173" spans="2:29" x14ac:dyDescent="0.2">
@@ -36000,15 +35971,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="258" t="s">
+      <c r="B4" s="255" t="s">
         <v>237</v>
       </c>
-      <c r="C4" s="258"/>
-      <c r="E4" s="258" t="s">
+      <c r="C4" s="255"/>
+      <c r="E4" s="255" t="s">
         <v>244</v>
       </c>
-      <c r="F4" s="258"/>
-      <c r="G4" s="258"/>
+      <c r="F4" s="255"/>
+      <c r="G4" s="255"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -36016,7 +35987,7 @@
       </c>
       <c r="C5" s="171">
         <f ca="1">Overview!C5</f>
-        <v>145.28</v>
+        <v>143.51</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="134" t="s">
@@ -36032,7 +36003,7 @@
       </c>
       <c r="C6" s="172">
         <f ca="1">Statement!AC149</f>
-        <v>7281724.1600000001</v>
+        <v>7193008.2199999997</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>20</v>
@@ -36052,7 +36023,7 @@
       </c>
       <c r="C7" s="172">
         <f ca="1">Statement!AC150</f>
-        <v>5865165.1600000001</v>
+        <v>5776449.2199999997</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>32</v>
@@ -36072,7 +36043,7 @@
       </c>
       <c r="C8" s="173">
         <f ca="1">Statement!AC146</f>
-        <v>46.258722122295872</v>
+        <v>45.695134992914923</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>247</v>
@@ -36092,7 +36063,7 @@
       </c>
       <c r="C9" s="173">
         <f ca="1">Statement!AC147</f>
-        <v>6.2389730368986323</v>
+        <v>6.1629613196952269</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>248</v>
@@ -36112,7 +36083,7 @@
       </c>
       <c r="C10" s="173">
         <f ca="1">Statement!AC148</f>
-        <v>4.8214993098027872</v>
+        <v>4.7627571995443132</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -36132,7 +36103,7 @@
       </c>
       <c r="C11" s="173">
         <f ca="1">Statement!AC151</f>
-        <v>5.1224060394654334</v>
+        <v>5.0449250044978085</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -36141,18 +36112,18 @@
       </c>
       <c r="C12" s="173">
         <f ca="1">Statement!AC152</f>
-        <v>37.337525288856355</v>
+        <v>36.772761371232136</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="258" t="s">
+      <c r="B15" s="255" t="s">
         <v>78</v>
       </c>
-      <c r="C15" s="258"/>
-      <c r="E15" s="258" t="s">
+      <c r="C15" s="255"/>
+      <c r="E15" s="255" t="s">
         <v>250</v>
       </c>
-      <c r="F15" s="258"/>
+      <c r="F15" s="255"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -36203,14 +36174,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="258" t="s">
+      <c r="B21" s="255" t="s">
         <v>249</v>
       </c>
-      <c r="C21" s="258"/>
-      <c r="E21" s="258" t="s">
+      <c r="C21" s="255"/>
+      <c r="E21" s="255" t="s">
         <v>253</v>
       </c>
-      <c r="F21" s="258"/>
+      <c r="F21" s="255"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -36279,14 +36250,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="258" t="s">
+      <c r="B29" s="255" t="s">
         <v>254</v>
       </c>
-      <c r="C29" s="258"/>
-      <c r="E29" s="258" t="s">
+      <c r="C29" s="255"/>
+      <c r="E29" s="255" t="s">
         <v>260</v>
       </c>
-      <c r="F29" s="258"/>
+      <c r="F29" s="255"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -36362,14 +36333,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="258" t="s">
+      <c r="B37" s="255" t="s">
         <v>272</v>
       </c>
-      <c r="C37" s="258"/>
-      <c r="E37" s="258" t="s">
+      <c r="C37" s="255"/>
+      <c r="E37" s="255" t="s">
         <v>275</v>
       </c>
-      <c r="F37" s="258"/>
+      <c r="F37" s="255"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -36377,7 +36348,7 @@
       </c>
       <c r="C38" s="174">
         <f ca="1">Statement!AC158</f>
-        <v>2.1617544846056564E-2</v>
+        <v>2.1884167759982566E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>274</v>
@@ -36393,7 +36364,7 @@
       </c>
       <c r="C39" s="214">
         <f ca="1">Statement!AC157</f>
-        <v>3.4719799108677028E-2</v>
+        <v>3.514802044811232E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>276</v>
@@ -36425,7 +36396,7 @@
       </c>
       <c r="C41" s="174">
         <f ca="1">Statement!AC160</f>
-        <v>9.5585878386252963E-3</v>
+        <v>9.6764799748831655E-3</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -36434,18 +36405,18 @@
       </c>
       <c r="C42" s="174">
         <f ca="1">Statement!AC161</f>
-        <v>9.5585878386252963E-3</v>
+        <v>9.6764799748831655E-3</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="258" t="s">
+      <c r="B45" s="255" t="s">
         <v>283</v>
       </c>
-      <c r="C45" s="258"/>
-      <c r="E45" s="258" t="s">
+      <c r="C45" s="255"/>
+      <c r="E45" s="255" t="s">
         <v>289</v>
       </c>
-      <c r="F45" s="258"/>
+      <c r="F45" s="255"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -36478,18 +36449,18 @@
       </c>
       <c r="F48" s="174">
         <f ca="1">Statement!AC172</f>
-        <v>0.19453620720508039</v>
+        <v>0.19693554583481346</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="258" t="s">
+      <c r="B51" s="255" t="s">
         <v>286</v>
       </c>
-      <c r="C51" s="258"/>
-      <c r="E51" s="258" t="s">
+      <c r="C51" s="255"/>
+      <c r="E51" s="255" t="s">
         <v>307</v>
       </c>
-      <c r="F51" s="258"/>
+      <c r="F51" s="255"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -36657,7 +36628,7 @@
       </c>
       <c r="I6" s="171">
         <f ca="1">Statement!AC116</f>
-        <v>145.28</v>
+        <v>143.51</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -36686,7 +36657,7 @@
       </c>
       <c r="I7" s="172">
         <f ca="1">Statement!AC149</f>
-        <v>7281724.1600000001</v>
+        <v>7193008.2199999997</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -36715,7 +36686,7 @@
       </c>
       <c r="I8" s="172">
         <f ca="1">Statement!AC150</f>
-        <v>5865165.1600000001</v>
+        <v>5776449.2199999997</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -36744,7 +36715,7 @@
       </c>
       <c r="I9" s="173">
         <f ca="1">Statement!AC146</f>
-        <v>46.258722122295872</v>
+        <v>45.695134992914923</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -36773,7 +36744,7 @@
       </c>
       <c r="I10" s="173">
         <f ca="1">Statement!AC147</f>
-        <v>6.2389730368986323</v>
+        <v>6.1629613196952269</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -36802,7 +36773,7 @@
       </c>
       <c r="I11" s="173">
         <f ca="1">Statement!AC148</f>
-        <v>4.8214993098027872</v>
+        <v>4.7627571995443132</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -36831,7 +36802,7 @@
       </c>
       <c r="I12" s="173">
         <f ca="1">Statement!AC151</f>
-        <v>5.1224060394654334</v>
+        <v>5.0449250044978085</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -36860,7 +36831,7 @@
       </c>
       <c r="I13" s="173">
         <f ca="1">Statement!AC152</f>
-        <v>37.337525288856355</v>
+        <v>36.772761371232136</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -37633,7 +37604,7 @@
       </c>
       <c r="I51" s="174">
         <f ca="1">Statement!AC158</f>
-        <v>2.1617544846056564E-2</v>
+        <v>2.1884167759982566E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -37662,7 +37633,7 @@
       </c>
       <c r="I52" s="174">
         <f ca="1">Statement!AC157</f>
-        <v>3.4719799108677028E-2</v>
+        <v>3.514802044811232E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -37720,7 +37691,7 @@
       </c>
       <c r="I54" s="174">
         <f ca="1">Statement!AC160</f>
-        <v>9.5585878386252963E-3</v>
+        <v>9.6764799748831655E-3</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -37749,7 +37720,7 @@
       </c>
       <c r="I55" s="174">
         <f ca="1">Statement!AC161</f>
-        <v>9.5585878386252963E-3</v>
+        <v>9.6764799748831655E-3</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -37985,7 +37956,7 @@
       </c>
       <c r="I68" s="195">
         <f ca="1">Statement!AC172</f>
-        <v>0.19453620720508039</v>
+        <v>0.19693554583481346</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -38528,14 +38499,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="261" t="s">
+      <c r="C3" s="259" t="s">
         <v>317</v>
       </c>
-      <c r="D3" s="262"/>
-      <c r="F3" s="263" t="s">
+      <c r="D3" s="260"/>
+      <c r="F3" s="261" t="s">
         <v>318</v>
       </c>
-      <c r="G3" s="262"/>
+      <c r="G3" s="260"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -38602,19 +38573,19 @@
       <c r="B7" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C7" s="259">
+      <c r="C7" s="262">
         <f>Statement!AA89</f>
         <v>2.2218264392893719E-2</v>
       </c>
-      <c r="D7" s="260"/>
-      <c r="F7" s="259">
+      <c r="D7" s="263"/>
+      <c r="F7" s="262">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.18309713991239371</v>
       </c>
-      <c r="G7" s="260"/>
+      <c r="G7" s="263"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="206" t="s">
@@ -38641,19 +38612,19 @@
       <c r="B9" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C9" s="259">
+      <c r="C9" s="262">
         <f>Statement!AA90</f>
         <v>3.6046202026093238E-2</v>
       </c>
-      <c r="D9" s="260"/>
-      <c r="F9" s="259">
+      <c r="D9" s="263"/>
+      <c r="F9" s="262">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.17263647322197348</v>
       </c>
-      <c r="G9" s="260"/>
+      <c r="G9" s="263"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="206" t="s">
@@ -38680,19 +38651,19 @@
       <c r="B11" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C11" s="259">
+      <c r="C11" s="262">
         <f>Statement!AA91</f>
         <v>1.710027405488606E-2</v>
       </c>
-      <c r="D11" s="260"/>
-      <c r="F11" s="259">
+      <c r="D11" s="263"/>
+      <c r="F11" s="262">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>0.1870895657269924</v>
       </c>
-      <c r="G11" s="260"/>
+      <c r="G11" s="263"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="206" t="s">
@@ -38719,19 +38690,19 @@
       <c r="B13" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C13" s="259">
+      <c r="C13" s="262">
         <f>Statement!AA95</f>
         <v>8.4392741251357012E-2</v>
       </c>
-      <c r="D13" s="260"/>
-      <c r="F13" s="259">
+      <c r="D13" s="263"/>
+      <c r="F13" s="262">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.22501976973287405</v>
       </c>
-      <c r="G13" s="260"/>
+      <c r="G13" s="263"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="206" t="s">
@@ -38758,19 +38729,19 @@
       <c r="B15" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C15" s="259">
+      <c r="C15" s="262">
         <f>Statement!AA96</f>
         <v>-0.23765355851505829</v>
       </c>
-      <c r="D15" s="260"/>
-      <c r="F15" s="259">
+      <c r="D15" s="263"/>
+      <c r="F15" s="262">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>1.7444474417768186E-2</v>
       </c>
-      <c r="G15" s="260"/>
+      <c r="G15" s="263"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="206" t="s">
@@ -38797,19 +38768,19 @@
       <c r="B17" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C17" s="259">
+      <c r="C17" s="262">
         <f>Statement!AA98</f>
         <v>-0.23704555913483663</v>
       </c>
-      <c r="D17" s="260"/>
-      <c r="F17" s="259">
+      <c r="D17" s="263"/>
+      <c r="F17" s="262">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>-0.25955204216073779</v>
       </c>
-      <c r="G17" s="260"/>
+      <c r="G17" s="263"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="206" t="s">
@@ -38836,22 +38807,22 @@
       <c r="B19" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C19" s="259">
+      <c r="C19" s="262">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>2.5565842762241744E-2</v>
       </c>
-      <c r="D19" s="260"/>
-      <c r="F19" s="259">
+      <c r="D19" s="263"/>
+      <c r="F19" s="262">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>2.5293753865182372E-2</v>
       </c>
-      <c r="G19" s="260"/>
+      <c r="G19" s="263"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="206" t="s">
@@ -38878,22 +38849,22 @@
       <c r="B21" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C21" s="259">
+      <c r="C21" s="262">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>-0.2584269662921348</v>
       </c>
-      <c r="D21" s="260"/>
-      <c r="F21" s="259">
+      <c r="D21" s="263"/>
+      <c r="F21" s="262">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>-0.27472527472527469</v>
       </c>
-      <c r="G21" s="260"/>
+      <c r="G21" s="263"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -38942,22 +38913,22 @@
       <c r="B25" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C25" s="259">
+      <c r="C25" s="262">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>2.840483364420425E-2</v>
       </c>
-      <c r="D25" s="260"/>
-      <c r="F25" s="259">
+      <c r="D25" s="263"/>
+      <c r="F25" s="262">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>0.22478379327694395</v>
       </c>
-      <c r="G25" s="260"/>
+      <c r="G25" s="263"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="str">
@@ -38985,22 +38956,22 @@
       <c r="B27" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C27" s="259">
+      <c r="C27" s="262">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>2.1247695740758708E-2</v>
       </c>
-      <c r="D27" s="260"/>
-      <c r="F27" s="259">
+      <c r="D27" s="263"/>
+      <c r="F27" s="262">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>2.1792942775323981E-2</v>
       </c>
-      <c r="G27" s="260"/>
+      <c r="G27" s="263"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="str">
@@ -39028,22 +38999,22 @@
       <c r="B29" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C29" s="259">
+      <c r="C29" s="262">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>-0.10674206945303526</v>
       </c>
-      <c r="D29" s="260"/>
-      <c r="F29" s="259">
+      <c r="D29" s="263"/>
+      <c r="F29" s="262">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>2.0816812053925456E-3</v>
       </c>
-      <c r="G29" s="260"/>
+      <c r="G29" s="263"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="str">
@@ -39071,22 +39042,22 @@
       <c r="B31" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C31" s="259">
+      <c r="C31" s="262">
         <f>IF(C30=0,
 IF(D30=0,0,IF(D30&gt;0,1,-1)),
 (D30-C30)/ABS(C30)
 )</f>
         <v>-5.2569263556713236E-2</v>
       </c>
-      <c r="D31" s="260"/>
-      <c r="F31" s="259">
+      <c r="D31" s="263"/>
+      <c r="F31" s="262">
         <f>IF(F30=0,
 IF(G30=0,0,IF(G30&gt;0,1,-1)),
 (G30-F30)/ABS(F30)
 )</f>
         <v>-0.22983638113570742</v>
       </c>
-      <c r="G31" s="260"/>
+      <c r="G31" s="263"/>
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B32" s="20" t="str">
@@ -39114,22 +39085,22 @@
       <c r="B33" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C33" s="259">
+      <c r="C33" s="262">
         <f>IF(C32=0,
 IF(D32=0,0,IF(D32&gt;0,1,-1)),
 (D32-C32)/ABS(C32)
 )</f>
         <v>0.84164222873900296</v>
       </c>
-      <c r="D33" s="260"/>
-      <c r="F33" s="259">
+      <c r="D33" s="263"/>
+      <c r="F33" s="262">
         <f>IF(F32=0,
 IF(G32=0,0,IF(G32&gt;0,1,-1)),
 (G32-F32)/ABS(F32)
 )</f>
         <v>1.482213438735178</v>
       </c>
-      <c r="G33" s="260"/>
+      <c r="G33" s="263"/>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B35" s="8" t="s">
@@ -39178,22 +39149,22 @@
       <c r="B37" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C37" s="259">
+      <c r="C37" s="262">
         <f>IF(C36=0,
 IF(D36=0,0,IF(D36&gt;0,1,-1)),
 (D36-C36)/ABS(C36)
 )</f>
         <v>3.8938053097345132E-2</v>
       </c>
-      <c r="D37" s="260"/>
-      <c r="F37" s="259">
+      <c r="D37" s="263"/>
+      <c r="F37" s="262">
         <f>IF(F36=0,
 IF(G36=0,0,IF(G36&gt;0,1,-1)),
 (G36-F36)/ABS(F36)
 )</f>
         <v>0.23060796645702306</v>
       </c>
-      <c r="G37" s="260"/>
+      <c r="G37" s="263"/>
     </row>
     <row r="38" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="str">
@@ -39221,22 +39192,22 @@
       <c r="B39" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C39" s="259">
+      <c r="C39" s="262">
         <f>IF(C38=0,
 IF(D38=0,0,IF(D38&gt;0,1,-1)),
 (D38-C38)/ABS(C38)
 )</f>
         <v>2.0319303338171262E-2</v>
       </c>
-      <c r="D39" s="260"/>
-      <c r="F39" s="259">
+      <c r="D39" s="263"/>
+      <c r="F39" s="262">
         <f>IF(F38=0,
 IF(G38=0,0,IF(G38&gt;0,1,-1)),
 (G38-F38)/ABS(F38)
 )</f>
         <v>9.5869056897895558E-2</v>
       </c>
-      <c r="G39" s="260"/>
+      <c r="G39" s="263"/>
     </row>
     <row r="40" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B40" s="20" t="str">
@@ -39264,22 +39235,22 @@
       <c r="B41" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C41" s="259">
+      <c r="C41" s="262">
         <f>IF(C40=0,
 IF(D40=0,0,IF(D40&gt;0,1,-1)),
 (D40-C40)/ABS(C40)
 )</f>
         <v>1.6E-2</v>
       </c>
-      <c r="D41" s="260"/>
-      <c r="F41" s="259">
+      <c r="D41" s="263"/>
+      <c r="F41" s="262">
         <f>IF(F40=0,
 IF(G40=0,0,IF(G40&gt;0,1,-1)),
 (G40-F40)/ABS(F40)
 )</f>
         <v>0.16513761467889909</v>
       </c>
-      <c r="G41" s="260"/>
+      <c r="G41" s="263"/>
     </row>
     <row r="42" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B42" s="20" t="str">
@@ -39307,22 +39278,22 @@
       <c r="B43" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C43" s="259">
+      <c r="C43" s="262">
         <f>IF(C42=0,
 IF(D42=0,0,IF(D42&gt;0,1,-1)),
 (D42-C42)/ABS(C42)
 )</f>
         <v>2.0750199521149242E-2</v>
       </c>
-      <c r="D43" s="260"/>
-      <c r="F43" s="259">
+      <c r="D43" s="263"/>
+      <c r="F43" s="262">
         <f>IF(F42=0,
 IF(G42=0,0,IF(G42&gt;0,1,-1)),
 (G42-F42)/ABS(F42)
 )</f>
         <v>8.9437819420783646E-2</v>
       </c>
-      <c r="G43" s="260"/>
+      <c r="G43" s="263"/>
     </row>
     <row r="44" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B44" s="20" t="str">
@@ -39350,22 +39321,22 @@
       <c r="B45" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C45" s="259">
+      <c r="C45" s="262">
         <f>IF(C44=0,
 IF(D44=0,0,IF(D44&gt;0,1,-1)),
 (D44-C44)/ABS(C44)
 )</f>
         <v>1.2209481933271921E-2</v>
       </c>
-      <c r="D45" s="260"/>
-      <c r="F45" s="259">
+      <c r="D45" s="263"/>
+      <c r="F45" s="262">
         <f>IF(F44=0,
 IF(G44=0,0,IF(G44&gt;0,1,-1)),
 (G44-F44)/ABS(F44)
 )</f>
         <v>5.119238950540856E-2</v>
       </c>
-      <c r="G45" s="260"/>
+      <c r="G45" s="263"/>
     </row>
     <row r="46" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="str">
@@ -39393,22 +39364,22 @@
       <c r="B47" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C47" s="259">
+      <c r="C47" s="262">
         <f>IF(C46=0,
 IF(D46=0,0,IF(D46&gt;0,1,-1)),
 (D46-C46)/ABS(C46)
 )</f>
         <v>1.8247963846473435E-2</v>
       </c>
-      <c r="D47" s="260"/>
-      <c r="F47" s="259">
+      <c r="D47" s="263"/>
+      <c r="F47" s="262">
         <f>IF(F46=0,
 IF(G46=0,0,IF(G46&gt;0,1,-1)),
 (G46-F46)/ABS(F46)
 )</f>
         <v>0.1229516507570132</v>
       </c>
-      <c r="G47" s="260"/>
+      <c r="G47" s="263"/>
     </row>
     <row r="48" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B48" s="20" t="str">
@@ -39436,22 +39407,22 @@
       <c r="B49" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C49" s="259">
+      <c r="C49" s="262">
         <f>IF(C48=0,
 IF(D48=0,0,IF(D48&gt;0,1,-1)),
 (D48-C48)/ABS(C48)
 )</f>
         <v>-4.2332859174963834E-3</v>
       </c>
-      <c r="D49" s="260"/>
-      <c r="F49" s="259">
+      <c r="D49" s="263"/>
+      <c r="F49" s="262">
         <f>IF(F48=0,
 IF(G48=0,0,IF(G48&gt;0,1,-1)),
 (G48-F48)/ABS(F48)
 )</f>
         <v>6.3208790635154666E-2</v>
       </c>
-      <c r="G49" s="260"/>
+      <c r="G49" s="263"/>
     </row>
     <row r="50" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B50" s="20" t="str">
@@ -39479,22 +39450,22 @@
       <c r="B51" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C51" s="259">
+      <c r="C51" s="262">
         <f>IF(C50=0,
 IF(D50=0,0,IF(D50&gt;0,1,-1)),
 (D50-C50)/ABS(C50)
 )</f>
         <v>4.8738292663854846E-4</v>
       </c>
-      <c r="D51" s="260"/>
-      <c r="F51" s="259">
+      <c r="D51" s="263"/>
+      <c r="F51" s="262">
         <f>IF(F50=0,
 IF(G50=0,0,IF(G50&gt;0,1,-1)),
 (G50-F50)/ABS(F50)
 )</f>
         <v>-6.2091544317255373E-2</v>
       </c>
-      <c r="G51" s="260"/>
+      <c r="G51" s="263"/>
     </row>
     <row r="52" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="str">
@@ -39522,43 +39493,39 @@
       <c r="B53" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C53" s="259">
+      <c r="C53" s="262">
         <f>IF(C52=0,
 IF(D52=0,0,IF(D52&gt;0,1,-1)),
 (D52-C52)/ABS(C52)
 )</f>
         <v>-8.8077740902117604E-2</v>
       </c>
-      <c r="D53" s="260"/>
-      <c r="F53" s="259">
+      <c r="D53" s="263"/>
+      <c r="F53" s="262">
         <f>IF(F52=0,
 IF(G52=0,0,IF(G52&gt;0,1,-1)),
 (G52-F52)/ABS(F52)
 )</f>
         <v>-0.37416005758387127</v>
       </c>
-      <c r="G53" s="260"/>
+      <c r="G53" s="263"/>
     </row>
   </sheetData>
   <mergeCells count="46">
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C53:D53"/>
+    <mergeCell ref="F53:G53"/>
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="F47:G47"/>
+    <mergeCell ref="C49:D49"/>
+    <mergeCell ref="F49:G49"/>
+    <mergeCell ref="C51:D51"/>
+    <mergeCell ref="F51:G51"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="F41:G41"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="F43:G43"/>
+    <mergeCell ref="C45:D45"/>
+    <mergeCell ref="F45:G45"/>
     <mergeCell ref="C37:D37"/>
     <mergeCell ref="F37:G37"/>
     <mergeCell ref="C39:D39"/>
@@ -39573,20 +39540,24 @@
     <mergeCell ref="F31:G31"/>
     <mergeCell ref="C33:D33"/>
     <mergeCell ref="F33:G33"/>
-    <mergeCell ref="C41:D41"/>
-    <mergeCell ref="F41:G41"/>
-    <mergeCell ref="C43:D43"/>
-    <mergeCell ref="F43:G43"/>
-    <mergeCell ref="C45:D45"/>
-    <mergeCell ref="F45:G45"/>
-    <mergeCell ref="C53:D53"/>
-    <mergeCell ref="F53:G53"/>
-    <mergeCell ref="C47:D47"/>
-    <mergeCell ref="F47:G47"/>
-    <mergeCell ref="C49:D49"/>
-    <mergeCell ref="F49:G49"/>
-    <mergeCell ref="C51:D51"/>
-    <mergeCell ref="F51:G51"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/DUOL.xlsx
+++ b/DUOL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91EF4B5E-7B2B-5F4C-A882-B42EE5CCAAEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8663E124-A23B-724E-ACBC-AAF9E2F276D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="7" activeTab="17" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -152,7 +152,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="838" uniqueCount="433">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="853" uniqueCount="438">
   <si>
     <t>Ticker</t>
   </si>
@@ -1451,6 +1451,21 @@
   </si>
   <si>
     <t>Year 5 FCFF</t>
+  </si>
+  <si>
+    <t>EV/Sales valuation</t>
+  </si>
+  <si>
+    <t>Year 5 Sales</t>
+  </si>
+  <si>
+    <t>Applied EV/Sales ratio</t>
+  </si>
+  <si>
+    <t>EV/Sales</t>
+  </si>
+  <si>
+    <t>Reverse DCF rate</t>
   </si>
 </sst>
 </file>
@@ -13142,11 +13157,11 @@
     <v>Powered by Refinitiv</v>
     <v>353</v>
     <v>87.89</v>
-    <v>1.0457000000000001</v>
+    <v>1.0463</v>
     <v>-4.24</v>
     <v>-2.8697E-2</v>
-    <v>0.49</v>
-    <v>3.4139999999999999E-3</v>
+    <v>0.46989999999999998</v>
+    <v>3.2740000000000004E-3</v>
     <v>USD</v>
     <v>Duolingo, Inc. is a technology company. The Company is engaged in offering a mobile learning platform, as well as a digital English language proficiency assessment exam. It operates a freemium business model, namely, the app and the Website are accessible free of charge, although Duolingo also offers premium services for a subscription fee. Its solutions consist of the Duolingo App, Super Duolingo, Duolingo Max, Duolingo English Test: AI-Driven Language Assessment, Duolingo for Schools, and Duolingo ABC. The Duolingo App offers courses in over 40 different languages, including Spanish, English, French, German, Italian, Portuguese, Japanese and Chinese. Duolingo can also be accessed on desktop computers via a Web browser. Its subscription offering, Super Duolingo, offers learners additional features to enhance their learning experience. The Duolingo English Test is an online, on-demand, high-stakes English proficiency assessment. It also operates an animation and motion design studio.</v>
     <v>900</v>
@@ -13157,21 +13172,21 @@
     <v>147.49</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46290.840662476563</v>
+    <v>46290.995045856253</v>
     <v>0</v>
     <v>142.16999999999999</v>
     <v>6714297607</v>
     <v>DUOLINGO, INC.</v>
     <v>DUOLINGO, INC.</v>
     <v>147.22</v>
-    <v>17.105899999999998</v>
+    <v>17.6113</v>
     <v>147.75</v>
     <v>143.51</v>
-    <v>144</v>
+    <v>143.97989999999999</v>
     <v>46786270</v>
     <v>DUOL</v>
     <v>DUOLINGO, INC. (XNAS:DUOL)</v>
-    <v>678956</v>
+    <v>680784</v>
     <v>1102655</v>
     <v>2011</v>
   </rv>
@@ -13194,19 +13209,19 @@
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>51.81</v>
+    <v>52.3</v>
     <v>39.47</v>
-    <v>0.48</v>
-    <v>9.3860000000000002E-3</v>
+    <v>0.22</v>
+    <v>4.2620000000000002E-3</v>
     <v>US</v>
-    <v>51.81</v>
+    <v>52.3</v>
     <v>Index</v>
     <v>3</v>
-    <v>50.87</v>
+    <v>51.62</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>51.21</v>
-    <v>51.14</v>
+    <v>51.86</v>
     <v>51.62</v>
+    <v>51.84</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -13428,9 +13443,9 @@
       <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq Last Sale</v>
+      <v>Source: Nasdaq</v>
       <v>GMT</v>
-      <v>Real-Time Nasdaq Last Sale</v>
+      <v>Delayed 15 minutes</v>
       <v>from close</v>
       <v>from close</v>
     </spb>
@@ -14034,8 +14049,8 @@
         <v>DCF price</v>
       </c>
       <c r="I3" s="210">
-        <f>'AVG target price'!C5</f>
-        <v>128.63343872974008</v>
+        <f ca="1">'AVG target price'!C5</f>
+        <v>144.76053918769324</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.2">
@@ -14058,8 +14073,8 @@
         <v>EV/EBIT price</v>
       </c>
       <c r="I4" s="210">
-        <f>'AVG target price'!C6</f>
-        <v>189.1075367384349</v>
+        <f ca="1">'AVG target price'!C6</f>
+        <v>196.97863823193862</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.2">
@@ -14082,8 +14097,8 @@
         <v>PS price</v>
       </c>
       <c r="I5" s="210">
-        <f>'AVG target price'!C7</f>
-        <v>144.33173268148542</v>
+        <f ca="1">'AVG target price'!C7</f>
+        <v>158.71378004179414</v>
       </c>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.2">
@@ -14092,7 +14107,7 @@
       </c>
       <c r="C6" s="207" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>144</v>
+        <v>143.97989999999999</v>
       </c>
       <c r="E6" s="184" t="s">
         <v>241</v>
@@ -14106,8 +14121,8 @@
         <v>EV/FCFF price</v>
       </c>
       <c r="I6" s="210">
-        <f>'AVG target price'!C8</f>
-        <v>194.3302599556572</v>
+        <f ca="1">'AVG target price'!C8</f>
+        <v>202.4699310308043</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -14125,13 +14140,13 @@
         <f ca="1">Statement!AC147</f>
         <v>6.1629613196952269</v>
       </c>
-      <c r="H7" s="183" t="str">
+      <c r="H7" s="184" t="str">
         <f>'AVG target price'!B9</f>
-        <v>AVG price</v>
-      </c>
-      <c r="I7" s="211">
-        <f>'AVG target price'!C9</f>
-        <v>164.10074202632939</v>
+        <v>EV/Sales</v>
+      </c>
+      <c r="I7" s="210">
+        <f ca="1">'AVG target price'!C9</f>
+        <v>202.88958346335514</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -14140,7 +14155,7 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>0.49</v>
+        <v>0.46989999999999998</v>
       </c>
       <c r="E8" s="184" t="s">
         <v>269</v>
@@ -14150,12 +14165,12 @@
         <v>3.514802044811232E-2</v>
       </c>
       <c r="H8" s="183" t="str">
-        <f>'AVG target price'!B11</f>
-        <v>Upside/Downside</v>
-      </c>
-      <c r="I8" s="212">
-        <f ca="1">'AVG target price'!C11</f>
-        <v>0.1434794929017448</v>
+        <f>'AVG target price'!B10</f>
+        <v>AVG price</v>
+      </c>
+      <c r="I8" s="211">
+        <f ca="1">'AVG target price'!C10</f>
+        <v>181.16249439111709</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -14173,6 +14188,14 @@
         <f ca="1">Statement!AC158</f>
         <v>2.1884167759982566E-2</v>
       </c>
+      <c r="H9" s="183" t="str">
+        <f>'AVG target price'!B12</f>
+        <v>Upside/Downside</v>
+      </c>
+      <c r="I9" s="212">
+        <f ca="1">'AVG target price'!C12</f>
+        <v>0.26236843698081741</v>
+      </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B10" s="184" t="s">
@@ -14180,7 +14203,7 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>3.4139999999999999E-3</v>
+        <v>3.2740000000000004E-3</v>
       </c>
       <c r="E10" s="184" t="s">
         <v>297</v>
@@ -14189,13 +14212,6 @@
         <f ca="1">Statement!AC160</f>
         <v>9.6764799748831655E-3</v>
       </c>
-      <c r="H10" s="183" t="s">
-        <v>420</v>
-      </c>
-      <c r="I10" s="211">
-        <f>DDM!C26</f>
-        <v>0</v>
-      </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B11" s="184" t="s">
@@ -14212,6 +14228,13 @@
         <f ca="1">Statement!AC159</f>
         <v>0</v>
       </c>
+      <c r="H11" s="183" t="s">
+        <v>420</v>
+      </c>
+      <c r="I11" s="211">
+        <f ca="1">DDM!C26</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B12" s="184" t="s">
@@ -14235,7 +14258,7 @@
       </c>
       <c r="C13" s="208" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>1.0457000000000001</v>
+        <v>1.0463</v>
       </c>
       <c r="E13" s="184" t="s">
         <v>104</v>
@@ -14244,6 +14267,13 @@
         <f>Statement!AC125</f>
         <v>0.10928737315054812</v>
       </c>
+      <c r="H13" s="183" t="s">
+        <v>437</v>
+      </c>
+      <c r="I13" s="212">
+        <f>'Reverse DCF'!C17</f>
+        <v>0.27</v>
+      </c>
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B14" s="185" t="s">
@@ -14306,7 +14336,6 @@
         <f>Statement!AC140</f>
         <v>22.829226659561293</v>
       </c>
-      <c r="I18" s="50"/>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B19" s="183" t="s">
@@ -14322,6 +14351,7 @@
         <f>Statement!AC142</f>
         <v>-1.00483563659166</v>
       </c>
+      <c r="I19" s="50"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="183" t="s">
@@ -14345,7 +14375,6 @@
       <c r="C21" s="69" t="s">
         <v>94</v>
       </c>
-      <c r="I21" s="50"/>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B22" s="183" t="s">
@@ -14354,6 +14383,7 @@
       <c r="C22" s="69" t="s">
         <v>94</v>
       </c>
+      <c r="I22" s="50"/>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B25" s="258" t="s">
@@ -14377,7 +14407,7 @@
       </c>
       <c r="F26" s="218" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>51.62</v>
+        <v>51.84</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -14392,7 +14422,7 @@
       </c>
       <c r="F27" s="219">
         <f ca="1">F26/1000</f>
-        <v>5.1619999999999999E-2</v>
+        <v>5.1840000000000004E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -14400,7 +14430,7 @@
         <v>348</v>
       </c>
       <c r="C28" s="220">
-        <v>0.11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
@@ -14408,19 +14438,19 @@
         <v>410</v>
       </c>
       <c r="C29" s="220">
-        <v>0.12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="255" t="s">
+      <c r="B33" s="134" t="s">
         <v>338</v>
       </c>
-      <c r="C33" s="255"/>
-      <c r="D33" s="255"/>
-      <c r="E33" s="255"/>
-      <c r="F33" s="255"/>
-      <c r="G33" s="255"/>
-      <c r="H33" s="255"/>
+      <c r="C33" s="134"/>
+      <c r="D33" s="134"/>
+      <c r="E33" s="134"/>
+      <c r="F33" s="134"/>
+      <c r="G33" s="134"/>
+      <c r="H33" s="134"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
@@ -14439,24 +14469,24 @@
       </c>
     </row>
     <row r="39" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="255"/>
-      <c r="C39" s="255"/>
-      <c r="D39" s="255"/>
-      <c r="E39" s="255"/>
-      <c r="F39" s="255"/>
-      <c r="G39" s="255"/>
-      <c r="H39" s="255"/>
+      <c r="B39" s="134"/>
+      <c r="C39" s="134"/>
+      <c r="D39" s="134"/>
+      <c r="E39" s="134"/>
+      <c r="F39" s="134"/>
+      <c r="G39" s="134"/>
+      <c r="H39" s="134"/>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B42" s="255" t="s">
+      <c r="B42" s="134" t="s">
         <v>341</v>
       </c>
-      <c r="C42" s="255"/>
-      <c r="D42" s="255"/>
-      <c r="E42" s="255"/>
-      <c r="F42" s="255"/>
-      <c r="G42" s="255"/>
-      <c r="H42" s="255"/>
+      <c r="C42" s="134"/>
+      <c r="D42" s="134"/>
+      <c r="E42" s="134"/>
+      <c r="F42" s="134"/>
+      <c r="G42" s="134"/>
+      <c r="H42" s="134"/>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="41" t="s">
@@ -14495,24 +14525,24 @@
       </c>
     </row>
     <row r="50" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B50" s="255"/>
-      <c r="C50" s="255"/>
-      <c r="D50" s="255"/>
-      <c r="E50" s="255"/>
-      <c r="F50" s="255"/>
-      <c r="G50" s="255"/>
-      <c r="H50" s="255"/>
+      <c r="B50" s="134"/>
+      <c r="C50" s="134"/>
+      <c r="D50" s="134"/>
+      <c r="E50" s="134"/>
+      <c r="F50" s="134"/>
+      <c r="G50" s="134"/>
+      <c r="H50" s="134"/>
     </row>
     <row r="53" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B53" s="255" t="s">
+      <c r="B53" s="134" t="s">
         <v>109</v>
       </c>
-      <c r="C53" s="255"/>
-      <c r="D53" s="255"/>
-      <c r="E53" s="255"/>
-      <c r="F53" s="255"/>
-      <c r="G53" s="255"/>
-      <c r="H53" s="255"/>
+      <c r="C53" s="134"/>
+      <c r="D53" s="134"/>
+      <c r="E53" s="134"/>
+      <c r="F53" s="134"/>
+      <c r="G53" s="134"/>
+      <c r="H53" s="134"/>
     </row>
     <row r="58" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B58" s="41" t="s">
@@ -14583,28 +14613,22 @@
       </c>
     </row>
     <row r="66" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B66" s="255"/>
-      <c r="C66" s="255"/>
-      <c r="D66" s="255"/>
-      <c r="E66" s="255"/>
-      <c r="F66" s="255"/>
-      <c r="G66" s="255"/>
-      <c r="H66" s="255"/>
+      <c r="B66" s="134"/>
+      <c r="C66" s="134"/>
+      <c r="D66" s="134"/>
+      <c r="E66" s="134"/>
+      <c r="F66" s="134"/>
+      <c r="G66" s="134"/>
+      <c r="H66" s="134"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="6">
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="E25:F25"/>
-    <mergeCell ref="B53:H53"/>
-    <mergeCell ref="B66:H66"/>
-    <mergeCell ref="B33:H33"/>
-    <mergeCell ref="B39:H39"/>
-    <mergeCell ref="B42:H42"/>
-    <mergeCell ref="B50:H50"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C10">
     <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
@@ -22076,7 +22100,7 @@
       </c>
       <c r="C9" s="137">
         <f ca="1">Overview!F27</f>
-        <v>5.1619999999999999E-2</v>
+        <v>5.1840000000000004E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22085,7 +22109,7 @@
       </c>
       <c r="C10" s="135">
         <f ca="1">Overview!C13</f>
-        <v>1.0457000000000001</v>
+        <v>1.0463</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22155,7 +22179,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>9.86765E-2</v>
+        <v>9.8923499999999998E-2</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22164,7 +22188,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>9.86765E-2</v>
+        <v>9.8923499999999998E-2</v>
       </c>
     </row>
   </sheetData>
@@ -22414,8 +22438,8 @@
         <v>0</v>
       </c>
       <c r="L8" s="128">
-        <f>L7*(1+C14)/(C15-C14)</f>
-        <v>6505318.4595415071</v>
+        <f ca="1">L7*(1+C14)/(C15-C14)</f>
+        <v>7418305.8450111272</v>
       </c>
       <c r="N8" s="92"/>
       <c r="O8" s="16"/>
@@ -22468,24 +22492,24 @@
       <c r="F10" s="139"/>
       <c r="G10" s="140"/>
       <c r="H10" s="128">
-        <f>H7/(1+$C$15)^H9</f>
-        <v>162858.71354166101</v>
+        <f ca="1">H7/(1+$C$15)^H9</f>
+        <v>164500.23321117781</v>
       </c>
       <c r="I10" s="128">
-        <f t="shared" ref="I10:L10" si="0">I7/(1+$C$15)^I9</f>
-        <v>195212.96795086376</v>
+        <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
+        <v>199168.06341362261</v>
       </c>
       <c r="J10" s="128">
-        <f t="shared" si="0"/>
-        <v>220446.8447918563</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>227180.1811763712</v>
       </c>
       <c r="K10" s="128">
-        <f t="shared" si="0"/>
-        <v>251057.5270048785</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>261333.64084099015</v>
       </c>
       <c r="L10" s="128">
-        <f t="shared" si="0"/>
-        <v>340640.28346400865</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>358157.12565835513</v>
       </c>
       <c r="N10" s="92"/>
     </row>
@@ -22503,8 +22527,8 @@
       <c r="J11" s="139"/>
       <c r="K11" s="139"/>
       <c r="L11" s="128">
-        <f>L8/(1+C15)^L9</f>
-        <v>3860589.879258764</v>
+        <f ca="1">L8/(1+C15)^L9</f>
+        <v>4628789.5008650431</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
@@ -22526,8 +22550,8 @@
         <v>169</v>
       </c>
       <c r="C15" s="137">
-        <f>IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.11</v>
+        <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
+        <v>9.8923499999999998E-2</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
@@ -22541,8 +22565,8 @@
         <v>191</v>
       </c>
       <c r="C19" s="64">
-        <f>SUM(H10:L10)</f>
-        <v>1170216.3367532683</v>
+        <f ca="1">SUM(H10:L10)</f>
+        <v>1210339.2443005168</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -22550,8 +22574,8 @@
         <v>187</v>
       </c>
       <c r="C20" s="64">
-        <f>L11</f>
-        <v>3860589.879258764</v>
+        <f ca="1">L11</f>
+        <v>4628789.5008650431</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -22559,8 +22583,8 @@
         <v>192</v>
       </c>
       <c r="C21" s="95">
-        <f>C19+C20</f>
-        <v>5030806.2160120327</v>
+        <f ca="1">C19+C20</f>
+        <v>5839128.7451655604</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -22586,8 +22610,8 @@
         <v>195</v>
       </c>
       <c r="C24" s="95">
-        <f>C21+C22-C23</f>
-        <v>6447365.2160120327</v>
+        <f ca="1">C21+C22-C23</f>
+        <v>7255687.7451655604</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -22604,8 +22628,8 @@
         <v>196</v>
       </c>
       <c r="C26" s="254">
-        <f>C24/C25</f>
-        <v>128.63343872974008</v>
+        <f ca="1">C24/C25</f>
+        <v>144.76053918769324</v>
       </c>
     </row>
   </sheetData>
@@ -22626,7 +22650,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2D33819-10E3-B843-9B8A-30FFCAB234A7}">
-  <dimension ref="A1:N70"/>
+  <dimension ref="A1:N84"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2" style="84" customWidth="1"/>
@@ -22873,24 +22897,24 @@
       <c r="F9" s="139"/>
       <c r="G9" s="140"/>
       <c r="H9" s="93">
-        <f>DCF!H10</f>
-        <v>162858.71354166101</v>
+        <f ca="1">DCF!H10</f>
+        <v>164500.23321117781</v>
       </c>
       <c r="I9" s="93">
-        <f>DCF!I10</f>
-        <v>195212.96795086376</v>
+        <f ca="1">DCF!I10</f>
+        <v>199168.06341362261</v>
       </c>
       <c r="J9" s="93">
-        <f>DCF!J10</f>
-        <v>220446.8447918563</v>
+        <f ca="1">DCF!J10</f>
+        <v>227180.1811763712</v>
       </c>
       <c r="K9" s="93">
-        <f>DCF!K10</f>
-        <v>251057.5270048785</v>
+        <f ca="1">DCF!K10</f>
+        <v>261333.64084099015</v>
       </c>
       <c r="L9" s="93">
-        <f>DCF!L10</f>
-        <v>340640.28346400865</v>
+        <f ca="1">DCF!L10</f>
+        <v>358157.12565835513</v>
       </c>
       <c r="N9" s="92"/>
     </row>
@@ -23618,291 +23642,427 @@
       <c r="N35" s="92"/>
     </row>
     <row r="36" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B36" s="16" t="s">
+        <v>436</v>
+      </c>
+      <c r="C36" s="149">
+        <f>C33/C6</f>
+        <v>8.1241093104493327</v>
+      </c>
+      <c r="D36" s="149">
+        <f t="shared" ref="D36:G36" si="14">D33/D6</f>
+        <v>5.9522350776059207</v>
+      </c>
+      <c r="E36" s="149">
+        <f t="shared" si="14"/>
+        <v>18.463075752811569</v>
+      </c>
+      <c r="F36" s="149">
+        <f t="shared" si="14"/>
+        <v>19.172256772509972</v>
+      </c>
+      <c r="G36" s="150">
+        <f t="shared" si="14"/>
+        <v>7.0192212429890013</v>
+      </c>
+      <c r="H36" s="139"/>
+      <c r="I36" s="139"/>
+      <c r="J36" s="139"/>
+      <c r="K36" s="139"/>
+      <c r="L36" s="139"/>
       <c r="N36" s="92"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="N37" s="92"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B38" s="255" t="s">
+      <c r="N38" s="92"/>
+    </row>
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B39" s="255" t="s">
         <v>209</v>
       </c>
-      <c r="C38" s="255"/>
-      <c r="N38" s="92"/>
-    </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B39" s="1" t="s">
+      <c r="C39" s="255"/>
+      <c r="N39" s="92"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B40" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C39" s="64">
+      <c r="C40" s="64">
         <f>L7</f>
         <v>487474.713505127</v>
       </c>
     </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B40" s="1" t="s">
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B41" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="C40" s="137">
-        <f>IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.11</v>
-      </c>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B41" s="39" t="s">
+      <c r="C41" s="137">
+        <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
+        <v>9.8923499999999998E-2</v>
+      </c>
+    </row>
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B42" s="39" t="s">
         <v>211</v>
       </c>
-      <c r="C41" s="106">
+      <c r="C42" s="106">
         <v>25</v>
-      </c>
-    </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B42" s="1" t="s">
-        <v>429</v>
-      </c>
-      <c r="C42" s="24">
-        <f>(C39*C41)</f>
-        <v>12186867.837628175</v>
       </c>
     </row>
     <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B43" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="C43" s="24">
+        <f>(C40*C42)</f>
+        <v>12186867.837628175</v>
+      </c>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B44" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="C43" s="24">
-        <f>C42/(1+C40)^5</f>
-        <v>7232312.903114575</v>
-      </c>
-    </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B44" s="16" t="s">
+      <c r="C44" s="24">
+        <f ca="1">C43/(1+C41)^5</f>
+        <v>7604222.1868190654</v>
+      </c>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B45" s="16" t="s">
         <v>431</v>
       </c>
-      <c r="C44" s="110">
-        <f>SUM(H9:K9)+C43</f>
-        <v>8061888.9564038347</v>
-      </c>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B45" s="1" t="s">
+      <c r="C45" s="110">
+        <f ca="1">SUM(H9:K9)+C44</f>
+        <v>8456404.3054612279</v>
+      </c>
+    </row>
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B46" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="C45" s="89">
+      <c r="C46" s="89">
         <f>Statement!AC107</f>
         <v>1416559</v>
       </c>
     </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B46" s="1" t="s">
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B47" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="C46" s="89">
+      <c r="C47" s="89">
         <f>Statement!AC108</f>
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B47" s="16" t="s">
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B48" s="16" t="s">
         <v>195</v>
       </c>
-      <c r="C47" s="110">
-        <f>C44+C45-C46</f>
-        <v>9478447.9564038347</v>
-      </c>
-    </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B48" s="1" t="s">
+      <c r="C48" s="110">
+        <f ca="1">C45+C46-C47</f>
+        <v>9872963.3054612279</v>
+      </c>
+    </row>
+    <row r="49" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B49" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C48" s="89">
+      <c r="C49" s="89">
         <f>Statement!AC78</f>
         <v>50122</v>
       </c>
     </row>
-    <row r="49" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B49" s="253" t="s">
+    <row r="50" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B50" s="253" t="s">
         <v>213</v>
       </c>
-      <c r="C49" s="254">
-        <f>C47/C48</f>
-        <v>189.1075367384349</v>
-      </c>
-    </row>
-    <row r="51" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B51" s="255" t="s">
+      <c r="C50" s="254">
+        <f ca="1">C48/C49</f>
+        <v>196.97863823193862</v>
+      </c>
+    </row>
+    <row r="52" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B52" s="255" t="s">
         <v>214</v>
       </c>
-      <c r="C51" s="255"/>
-    </row>
-    <row r="52" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B52" s="1" t="s">
+      <c r="C52" s="255"/>
+    </row>
+    <row r="53" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B53" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="C52" s="64">
+      <c r="C53" s="64">
         <f>L6</f>
         <v>3165420.2175657614</v>
       </c>
     </row>
-    <row r="53" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B53" s="1" t="s">
+    <row r="54" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B54" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="C53" s="137">
-        <f>IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="54" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B54" s="39" t="s">
+      <c r="C54" s="137">
+        <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
+        <v>9.8923499999999998E-2</v>
+      </c>
+    </row>
+    <row r="55" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B55" s="39" t="s">
         <v>216</v>
       </c>
-      <c r="C54" s="106">
+      <c r="C55" s="106">
         <v>4.5</v>
       </c>
     </row>
-    <row r="55" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B55" s="1" t="s">
+    <row r="56" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B56" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="C55" s="24">
+      <c r="C56" s="24">
         <f>L19</f>
         <v>56000.505465443181</v>
       </c>
     </row>
-    <row r="56" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B56" s="1" t="s">
+    <row r="57" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B57" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="C56" s="24">
-        <f>(C52*C54)/C55</f>
+      <c r="C57" s="24">
+        <f>(C53*C55)/C56</f>
         <v>254.36182871306156</v>
       </c>
     </row>
-    <row r="57" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B57" s="253" t="s">
+    <row r="58" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B58" s="253" t="s">
         <v>213</v>
       </c>
-      <c r="C57" s="254">
-        <f>C56/(1+C53)^5</f>
-        <v>144.33173268148542</v>
-      </c>
-    </row>
-    <row r="59" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B59" s="255" t="s">
+      <c r="C58" s="254">
+        <f ca="1">C57/(1+C54)^5</f>
+        <v>158.71378004179414</v>
+      </c>
+    </row>
+    <row r="60" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B60" s="255" t="s">
         <v>327</v>
       </c>
-      <c r="C59" s="255"/>
-    </row>
-    <row r="60" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B60" s="1" t="s">
+      <c r="C60" s="255"/>
+    </row>
+    <row r="61" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B61" s="1" t="s">
         <v>432</v>
       </c>
-      <c r="C60" s="64">
+      <c r="C61" s="64">
         <f>L8</f>
         <v>573998.68760660361</v>
       </c>
     </row>
-    <row r="61" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B61" s="1" t="s">
+    <row r="62" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B62" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="C61" s="137">
-        <f>IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.11</v>
-      </c>
-    </row>
-    <row r="62" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B62" s="39" t="s">
+      <c r="C62" s="137">
+        <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
+        <v>9.8923499999999998E-2</v>
+      </c>
+    </row>
+    <row r="63" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B63" s="39" t="s">
         <v>350</v>
       </c>
-      <c r="C62" s="106">
+      <c r="C63" s="106">
         <v>22</v>
-      </c>
-    </row>
-    <row r="63" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B63" s="1" t="s">
-        <v>429</v>
-      </c>
-      <c r="C63" s="24">
-        <f>(C60*C62)</f>
-        <v>12627971.127345279</v>
       </c>
     </row>
     <row r="64" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B64" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="C64" s="24">
+        <f>(C61*C63)</f>
+        <v>12627971.127345279</v>
+      </c>
+    </row>
+    <row r="65" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B65" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="C64" s="24">
-        <f>C63/(1+C61)^5</f>
-        <v>7494086.2362081893</v>
-      </c>
-    </row>
-    <row r="65" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B65" s="16" t="s">
+      <c r="C65" s="24">
+        <f ca="1">C64/(1+C62)^5</f>
+        <v>7879456.7644838123</v>
+      </c>
+    </row>
+    <row r="66" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B66" s="16" t="s">
         <v>431</v>
       </c>
-      <c r="C65" s="110">
-        <f>SUM(H9:K9)+C64</f>
-        <v>8323662.2894974491</v>
-      </c>
-    </row>
-    <row r="66" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B66" s="1" t="s">
+      <c r="C66" s="110">
+        <f ca="1">SUM(H9:K9)+C65</f>
+        <v>8731638.8831259739</v>
+      </c>
+    </row>
+    <row r="67" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B67" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="C66" s="89">
+      <c r="C67" s="89">
         <f>Statement!AC107</f>
         <v>1416559</v>
       </c>
     </row>
-    <row r="67" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B67" s="1" t="s">
+    <row r="68" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B68" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="C67" s="89">
+      <c r="C68" s="89">
         <f>Statement!AC108</f>
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B68" s="16" t="s">
+    <row r="69" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B69" s="16" t="s">
         <v>195</v>
       </c>
-      <c r="C68" s="110">
-        <f>C65+C66-C67</f>
-        <v>9740221.28949745</v>
-      </c>
-    </row>
-    <row r="69" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B69" s="1" t="s">
+      <c r="C69" s="110">
+        <f ca="1">C66+C67-C68</f>
+        <v>10148197.883125974</v>
+      </c>
+    </row>
+    <row r="70" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B70" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C69" s="89">
+      <c r="C70" s="89">
         <f>Statement!AC78</f>
         <v>50122</v>
       </c>
     </row>
-    <row r="70" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B70" s="253" t="s">
+    <row r="71" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B71" s="253" t="s">
         <v>213</v>
       </c>
-      <c r="C70" s="254">
-        <f>C68/C69</f>
-        <v>194.3302599556572</v>
+      <c r="C71" s="254">
+        <f ca="1">C69/C70</f>
+        <v>202.4699310308043</v>
+      </c>
+    </row>
+    <row r="73" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B73" s="255" t="s">
+        <v>433</v>
+      </c>
+      <c r="C73" s="255"/>
+    </row>
+    <row r="74" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B74" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="C74" s="64">
+        <f>L6</f>
+        <v>3165420.2175657614</v>
+      </c>
+    </row>
+    <row r="75" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B75" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="C75" s="137">
+        <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
+        <v>9.8923499999999998E-2</v>
+      </c>
+    </row>
+    <row r="76" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B76" s="39" t="s">
+        <v>435</v>
+      </c>
+      <c r="C76" s="106">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B77" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="C77" s="24">
+        <f>(C74*C76)</f>
+        <v>12661680.870263046</v>
+      </c>
+    </row>
+    <row r="78" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B78" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="C78" s="24">
+        <f ca="1">C77/(1+C75)^5</f>
+        <v>7900490.5837081242</v>
+      </c>
+    </row>
+    <row r="79" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B79" s="16" t="s">
+        <v>431</v>
+      </c>
+      <c r="C79" s="110">
+        <f ca="1">SUM(H9:K9)+C78</f>
+        <v>8752672.7023502868</v>
+      </c>
+    </row>
+    <row r="80" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B80" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="C80" s="89">
+        <f>Statement!AC107</f>
+        <v>1416559</v>
+      </c>
+    </row>
+    <row r="81" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B81" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="C81" s="89">
+        <f>Statement!AC108</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B82" s="16" t="s">
+        <v>195</v>
+      </c>
+      <c r="C82" s="110">
+        <f ca="1">C79+C80-C81</f>
+        <v>10169231.702350287</v>
+      </c>
+    </row>
+    <row r="83" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B83" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C83" s="89">
+        <f>Statement!AC78</f>
+        <v>50122</v>
+      </c>
+    </row>
+    <row r="84" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B84" s="253" t="s">
+        <v>213</v>
+      </c>
+      <c r="C84" s="254">
+        <f ca="1">C82/C83</f>
+        <v>202.88958346335514</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="C27:L27"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="B59:C59"/>
+  <mergeCells count="11">
+    <mergeCell ref="C22:L22"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="C17:L17"/>
-    <mergeCell ref="C22:L22"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="C27:L27"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B60:C60"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -23913,7 +24073,7 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69906138-34BE-DB43-85EE-BFBB58F201B2}">
-  <dimension ref="A1:N11"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2" style="84" customWidth="1"/>
@@ -23951,8 +24111,8 @@
         <v>219</v>
       </c>
       <c r="C5" s="135">
-        <f>DCF!C26</f>
-        <v>128.63343872974008</v>
+        <f ca="1">DCF!C26</f>
+        <v>144.76053918769324</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -23960,8 +24120,8 @@
         <v>220</v>
       </c>
       <c r="C6" s="135">
-        <f>Multiples!C49</f>
-        <v>189.1075367384349</v>
+        <f ca="1">Multiples!C50</f>
+        <v>196.97863823193862</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -23969,8 +24129,8 @@
         <v>221</v>
       </c>
       <c r="C7" s="135">
-        <f>Multiples!C57</f>
-        <v>144.33173268148542</v>
+        <f ca="1">Multiples!C58</f>
+        <v>158.71378004179414</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -23978,35 +24138,44 @@
         <v>328</v>
       </c>
       <c r="C8" s="135">
-        <f>Multiples!C70</f>
-        <v>194.3302599556572</v>
+        <f ca="1">Multiples!C71</f>
+        <v>202.4699310308043</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B9" s="253" t="s">
+      <c r="B9" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="C9" s="135">
+        <f ca="1">Multiples!C84</f>
+        <v>202.88958346335514</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B10" s="253" t="s">
         <v>222</v>
       </c>
-      <c r="C9" s="254">
-        <f>AVERAGE(C5:C8)</f>
-        <v>164.10074202632939</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B10" s="1" t="s">
+      <c r="C10" s="254">
+        <f ca="1">AVERAGE(C5:C9)</f>
+        <v>181.16249439111709</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B11" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="C10" s="135">
+      <c r="C11" s="135">
         <f ca="1">Overview!C5</f>
         <v>143.51</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B11" s="1" t="s">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B12" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="C11" s="154">
-        <f ca="1">(C9-C10)/C10</f>
-        <v>0.1434794929017448</v>
+      <c r="C12" s="154">
+        <f ca="1">(C10-C11)/C11</f>
+        <v>0.26236843698081741</v>
       </c>
     </row>
   </sheetData>
@@ -24475,8 +24644,8 @@
         <v>349</v>
       </c>
       <c r="C24" s="137">
-        <f>IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.12</v>
+        <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
+        <v>9.8923499999999998E-2</v>
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
@@ -24492,7 +24661,7 @@
         <v>213</v>
       </c>
       <c r="C26" s="254">
-        <f>C23/(C24-C25)</f>
+        <f ca="1">C23/(C24-C25)</f>
         <v>0</v>
       </c>
     </row>
@@ -24683,23 +24852,23 @@
       </c>
       <c r="H7" s="128">
         <f>G7*(1+$C$17)</f>
-        <v>201846.69050819584</v>
+        <v>194200.98253440054</v>
       </c>
       <c r="I7" s="128">
         <f t="shared" ref="I7:L7" si="0">H7*(1+$C$17)</f>
-        <v>266437.63147081854</v>
+        <v>246635.24781868869</v>
       </c>
       <c r="J7" s="128">
         <f t="shared" si="0"/>
-        <v>351697.6735414805</v>
+        <v>313226.76472973463</v>
       </c>
       <c r="K7" s="128">
         <f t="shared" si="0"/>
-        <v>464240.9290747543</v>
+        <v>397797.99120676296</v>
       </c>
       <c r="L7" s="128">
         <f t="shared" si="0"/>
-        <v>612798.02637867571</v>
+        <v>505203.44883258897</v>
       </c>
       <c r="N7" s="92"/>
       <c r="O7" s="16"/>
@@ -24730,8 +24899,8 @@
       <c r="J8" s="139"/>
       <c r="K8" s="139"/>
       <c r="L8" s="128">
-        <f>L7*(1+C20)/(C21-C20)</f>
-        <v>6945044.2989583248</v>
+        <f ca="1">L7*(1+C20)/(C21-C20)</f>
+        <v>6529202.5544893574</v>
       </c>
       <c r="N8" s="92"/>
       <c r="O8" s="16"/>
@@ -24784,24 +24953,24 @@
       <c r="F10" s="139"/>
       <c r="G10" s="140"/>
       <c r="H10" s="128">
-        <f>H7/(1+$C$21)^H9</f>
-        <v>181843.86532269893</v>
+        <f ca="1">H7/(1+$C$21)^H9</f>
+        <v>176719.29168354353</v>
       </c>
       <c r="I10" s="128">
-        <f t="shared" ref="I10:L10" si="1">I7/(1+$C$21)^I9</f>
-        <v>216246.75876212848</v>
+        <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
+        <v>204230.32216355397</v>
       </c>
       <c r="J10" s="128">
-        <f t="shared" si="1"/>
-        <v>257158.30771712578</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>236024.1719716737</v>
       </c>
       <c r="K10" s="128">
-        <f t="shared" si="1"/>
-        <v>305809.87944739283</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>272767.57518064324</v>
       </c>
       <c r="L10" s="128">
-        <f t="shared" si="1"/>
-        <v>363665.80258608877</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>315231.06065109809</v>
       </c>
       <c r="N10" s="92"/>
     </row>
@@ -24819,8 +24988,8 @@
       <c r="J11" s="139"/>
       <c r="K11" s="139"/>
       <c r="L11" s="128">
-        <f>L8/(1+C21)^L9</f>
-        <v>4121545.7626423393</v>
+        <f ca="1">L8/(1+C21)^L9</f>
+        <v>4074017.0147563154</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -24844,8 +25013,8 @@
         <v>228</v>
       </c>
       <c r="C16" s="156">
-        <f>C36</f>
-        <v>146.68553363138062</v>
+        <f ca="1">C36</f>
+        <v>143.11008499138265</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -24853,7 +25022,7 @@
         <v>329</v>
       </c>
       <c r="C17" s="158">
-        <v>0.32</v>
+        <v>0.27</v>
       </c>
       <c r="E17" s="272" t="s">
         <v>229</v>
@@ -24883,8 +25052,8 @@
         <v>169</v>
       </c>
       <c r="C21" s="221">
-        <f>IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.11</v>
+        <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
+        <v>9.8923499999999998E-2</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -24944,8 +25113,8 @@
         <v>191</v>
       </c>
       <c r="C29" s="161">
-        <f>SUM(H10:L10)</f>
-        <v>1324724.6138354349</v>
+        <f ca="1">SUM(H10:L10)</f>
+        <v>1204972.4216505126</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -24953,8 +25122,8 @@
         <v>187</v>
       </c>
       <c r="C30" s="161">
-        <f>L11</f>
-        <v>4121545.7626423393</v>
+        <f ca="1">L11</f>
+        <v>4074017.0147563154</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -24962,8 +25131,8 @@
         <v>192</v>
       </c>
       <c r="C31" s="164">
-        <f>C29+C30</f>
-        <v>5446270.3764777742</v>
+        <f ca="1">C29+C30</f>
+        <v>5278989.4364068285</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -24989,8 +25158,8 @@
         <v>195</v>
       </c>
       <c r="C34" s="164">
-        <f>C31+C32-C33</f>
-        <v>6862829.3764777742</v>
+        <f ca="1">C31+C32-C33</f>
+        <v>6695548.4364068285</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.2">
@@ -25007,8 +25176,8 @@
         <v>196</v>
       </c>
       <c r="C36" s="167">
-        <f>C34/C35</f>
-        <v>146.68553363138062</v>
+        <f ca="1">C34/C35</f>
+        <v>143.11008499138265</v>
       </c>
     </row>
   </sheetData>

--- a/DUOL.xlsx
+++ b/DUOL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8663E124-A23B-724E-ACBC-AAF9E2F276D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4860B105-9D3D-A84E-85C2-8859E89D4330}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -2409,9 +2409,6 @@
     <xf numFmtId="39" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="7" fillId="9" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2419,6 +2416,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2430,10 +2436,10 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2445,23 +2451,17 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -13157,11 +13157,11 @@
     <v>Powered by Refinitiv</v>
     <v>353</v>
     <v>87.89</v>
-    <v>1.0463</v>
-    <v>-4.24</v>
-    <v>-2.8697E-2</v>
-    <v>0.46989999999999998</v>
-    <v>3.2740000000000004E-3</v>
+    <v>1.054</v>
+    <v>8.32</v>
+    <v>6.1950999999999999E-2</v>
+    <v>-0.03</v>
+    <v>-2.1029999999999999E-4</v>
     <v>USD</v>
     <v>Duolingo, Inc. is a technology company. The Company is engaged in offering a mobile learning platform, as well as a digital English language proficiency assessment exam. It operates a freemium business model, namely, the app and the Website are accessible free of charge, although Duolingo also offers premium services for a subscription fee. Its solutions consist of the Duolingo App, Super Duolingo, Duolingo Max, Duolingo English Test: AI-Driven Language Assessment, Duolingo for Schools, and Duolingo ABC. The Duolingo App offers courses in over 40 different languages, including Spanish, English, French, German, Italian, Portuguese, Japanese and Chinese. Duolingo can also be accessed on desktop computers via a Web browser. Its subscription offering, Super Duolingo, offers learners additional features to enhance their learning experience. The Duolingo English Test is an online, on-demand, high-stakes English proficiency assessment. It also operates an animation and motion design studio.</v>
     <v>900</v>
@@ -13169,25 +13169,25 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>5900 PENN AVE, SECOND FLOOR, PITTSBURGH, PA, 15206 US</v>
-    <v>147.49</v>
+    <v>142.71</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46290.995045856253</v>
+    <v>46294.951956226563</v>
     <v>0</v>
-    <v>142.16999999999999</v>
-    <v>6714297607</v>
+    <v>134.31</v>
+    <v>6672657827</v>
     <v>DUOLINGO, INC.</v>
     <v>DUOLINGO, INC.</v>
-    <v>147.22</v>
-    <v>17.6113</v>
-    <v>147.75</v>
-    <v>143.51</v>
-    <v>143.97989999999999</v>
+    <v>134.44</v>
+    <v>16.008099999999999</v>
+    <v>134.30000000000001</v>
+    <v>142.62</v>
+    <v>142.59</v>
     <v>46786270</v>
     <v>DUOL</v>
     <v>DUOLINGO, INC. (XNAS:DUOL)</v>
-    <v>680784</v>
-    <v>1102655</v>
+    <v>1067735</v>
+    <v>1139488</v>
     <v>2011</v>
   </rv>
   <rv s="2">
@@ -13209,19 +13209,19 @@
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>52.3</v>
+    <v>52.74</v>
     <v>39.47</v>
-    <v>0.22</v>
-    <v>4.2620000000000002E-3</v>
+    <v>0.56000000000000005</v>
+    <v>1.0802000000000001E-2</v>
     <v>US</v>
-    <v>52.3</v>
+    <v>52.74</v>
     <v>Index</v>
     <v>3</v>
-    <v>51.62</v>
+    <v>52.05</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>51.86</v>
-    <v>51.62</v>
+    <v>52.09</v>
     <v>51.84</v>
+    <v>52.4</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -13443,9 +13443,9 @@
       <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq</v>
+      <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
-      <v>Delayed 15 minutes</v>
+      <v>Real-Time Nasdaq Last Sale</v>
       <v>from close</v>
       <v>from close</v>
     </spb>
@@ -14016,18 +14016,18 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="256" t="s">
+      <c r="B2" s="255" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="257"/>
-      <c r="E2" s="256" t="s">
+      <c r="C2" s="256"/>
+      <c r="E2" s="255" t="s">
         <v>291</v>
       </c>
-      <c r="F2" s="257"/>
-      <c r="H2" s="256" t="s">
+      <c r="F2" s="256"/>
+      <c r="H2" s="255" t="s">
         <v>330</v>
       </c>
-      <c r="I2" s="257"/>
+      <c r="I2" s="256"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="184" t="s">
@@ -14042,7 +14042,7 @@
       </c>
       <c r="F3" s="186">
         <f ca="1">Statement!AC149</f>
-        <v>7193008.2199999997</v>
+        <v>7148399.6400000006</v>
       </c>
       <c r="H3" s="184" t="str">
         <f>'AVG target price'!B5</f>
@@ -14050,7 +14050,7 @@
       </c>
       <c r="I3" s="210">
         <f ca="1">'AVG target price'!C5</f>
-        <v>144.76053918769324</v>
+        <v>143.26920240823023</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.2">
@@ -14066,7 +14066,7 @@
       </c>
       <c r="F4" s="187">
         <f ca="1">Statement!AC150</f>
-        <v>5776449.2199999997</v>
+        <v>5731840.6400000006</v>
       </c>
       <c r="H4" s="184" t="str">
         <f>'AVG target price'!B6</f>
@@ -14074,7 +14074,7 @@
       </c>
       <c r="I4" s="210">
         <f ca="1">'AVG target price'!C6</f>
-        <v>196.97863823193862</v>
+        <v>196.31682029546766</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.2">
@@ -14083,7 +14083,7 @@
       </c>
       <c r="C5" s="207" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>143.51</v>
+        <v>142.62</v>
       </c>
       <c r="E5" s="184" t="s">
         <v>247</v>
@@ -14098,7 +14098,7 @@
       </c>
       <c r="I5" s="210">
         <f ca="1">'AVG target price'!C7</f>
-        <v>158.71378004179414</v>
+        <v>158.06078335243151</v>
       </c>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.2">
@@ -14107,14 +14107,14 @@
       </c>
       <c r="C6" s="207" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>143.97989999999999</v>
+        <v>142.59</v>
       </c>
       <c r="E6" s="184" t="s">
         <v>241</v>
       </c>
       <c r="F6" s="189">
         <f ca="1">Statement!AC146</f>
-        <v>45.695134992914923</v>
+        <v>45.411749374186655</v>
       </c>
       <c r="H6" s="184" t="str">
         <f>'AVG target price'!B8</f>
@@ -14122,7 +14122,7 @@
       </c>
       <c r="I6" s="210">
         <f ca="1">'AVG target price'!C8</f>
-        <v>202.4699310308043</v>
+        <v>201.78552024816062</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -14131,14 +14131,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>-4.24</v>
+        <v>8.32</v>
       </c>
       <c r="E7" s="185" t="s">
         <v>205</v>
       </c>
       <c r="F7" s="190">
         <f ca="1">Statement!AC147</f>
-        <v>6.1629613196952269</v>
+        <v>6.1247407387285442</v>
       </c>
       <c r="H7" s="184" t="str">
         <f>'AVG target price'!B9</f>
@@ -14146,7 +14146,7 @@
       </c>
       <c r="I7" s="210">
         <f ca="1">'AVG target price'!C9</f>
-        <v>202.88958346335514</v>
+        <v>202.20344610316366</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -14155,14 +14155,14 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>0.46989999999999998</v>
+        <v>-0.03</v>
       </c>
       <c r="E8" s="184" t="s">
         <v>269</v>
       </c>
       <c r="F8" s="191">
         <f ca="1">Statement!AC157</f>
-        <v>3.514802044811232E-2</v>
+        <v>3.5367356713704938E-2</v>
       </c>
       <c r="H8" s="183" t="str">
         <f>'AVG target price'!B10</f>
@@ -14170,7 +14170,7 @@
       </c>
       <c r="I8" s="211">
         <f ca="1">'AVG target price'!C10</f>
-        <v>181.16249439111709</v>
+        <v>180.32715448149074</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -14179,14 +14179,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>-2.8697E-2</v>
+        <v>6.1950999999999999E-2</v>
       </c>
       <c r="E9" s="184" t="s">
         <v>292</v>
       </c>
       <c r="F9" s="191">
         <f ca="1">Statement!AC158</f>
-        <v>2.1884167759982566E-2</v>
+        <v>2.2020732823132085E-2</v>
       </c>
       <c r="H9" s="183" t="str">
         <f>'AVG target price'!B12</f>
@@ -14194,7 +14194,7 @@
       </c>
       <c r="I9" s="212">
         <f ca="1">'AVG target price'!C12</f>
-        <v>0.26236843698081741</v>
+        <v>0.26438896705574766</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -14203,14 +14203,14 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>3.2740000000000004E-3</v>
+        <v>-2.1029999999999999E-4</v>
       </c>
       <c r="E10" s="184" t="s">
         <v>297</v>
       </c>
       <c r="F10" s="191">
         <f ca="1">Statement!AC160</f>
-        <v>9.6764799748831655E-3</v>
+        <v>9.7368646837433948E-3</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -14258,7 +14258,7 @@
       </c>
       <c r="C13" s="208" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>1.0463</v>
+        <v>1.054</v>
       </c>
       <c r="E13" s="184" t="s">
         <v>104</v>
@@ -14281,7 +14281,7 @@
       </c>
       <c r="C14" s="209" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>1102655</v>
+        <v>1139488</v>
       </c>
       <c r="E14" s="185" t="s">
         <v>105</v>
@@ -14297,7 +14297,7 @@
       </c>
       <c r="F15" s="191">
         <f ca="1">Statement!AC172</f>
-        <v>0.19693554583481346</v>
+        <v>0.19816449433988276</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -14310,10 +14310,10 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="258" t="s">
+      <c r="B17" s="257" t="s">
         <v>90</v>
       </c>
-      <c r="C17" s="258"/>
+      <c r="C17" s="257"/>
       <c r="E17" s="183" t="s">
         <v>300</v>
       </c>
@@ -14386,14 +14386,14 @@
       <c r="I22" s="50"/>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="258" t="s">
+      <c r="B25" s="257" t="s">
         <v>107</v>
       </c>
-      <c r="C25" s="258"/>
-      <c r="E25" s="256" t="s">
+      <c r="C25" s="257"/>
+      <c r="E25" s="255" t="s">
         <v>343</v>
       </c>
-      <c r="F25" s="257"/>
+      <c r="F25" s="256"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="183" t="s">
@@ -14407,7 +14407,7 @@
       </c>
       <c r="F26" s="218" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>51.84</v>
+        <v>52.4</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -14422,7 +14422,7 @@
       </c>
       <c r="F27" s="219">
         <f ca="1">F26/1000</f>
-        <v>5.1840000000000004E-2</v>
+        <v>5.2399999999999995E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -14698,36 +14698,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="255" t="s">
+      <c r="C2" s="258" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="255"/>
-      <c r="E2" s="255"/>
-      <c r="F2" s="255"/>
-      <c r="G2" s="267"/>
-      <c r="H2" s="268" t="s">
+      <c r="D2" s="258"/>
+      <c r="E2" s="258"/>
+      <c r="F2" s="258"/>
+      <c r="G2" s="264"/>
+      <c r="H2" s="265" t="s">
         <v>114</v>
       </c>
-      <c r="I2" s="255"/>
-      <c r="J2" s="255"/>
-      <c r="K2" s="255"/>
-      <c r="L2" s="255"/>
+      <c r="I2" s="258"/>
+      <c r="J2" s="258"/>
+      <c r="K2" s="258"/>
+      <c r="L2" s="258"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="255" t="s">
+      <c r="S2" s="258" t="s">
         <v>113</v>
       </c>
-      <c r="T2" s="255"/>
-      <c r="U2" s="255"/>
-      <c r="V2" s="255"/>
-      <c r="W2" s="255"/>
-      <c r="X2" s="255"/>
-      <c r="Y2" s="255"/>
-      <c r="Z2" s="255"/>
-      <c r="AA2" s="255" t="s">
+      <c r="T2" s="258"/>
+      <c r="U2" s="258"/>
+      <c r="V2" s="258"/>
+      <c r="W2" s="258"/>
+      <c r="X2" s="258"/>
+      <c r="Y2" s="258"/>
+      <c r="Z2" s="258"/>
+      <c r="AA2" s="258" t="s">
         <v>114</v>
       </c>
-      <c r="AB2" s="255"/>
-      <c r="AC2" s="255"/>
+      <c r="AB2" s="258"/>
+      <c r="AC2" s="258"/>
       <c r="AE2" s="86" t="s">
         <v>85</v>
       </c>
@@ -14738,32 +14738,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="264" t="s">
+      <c r="C4" s="266" t="s">
         <v>116</v>
       </c>
-      <c r="D4" s="264"/>
-      <c r="E4" s="264"/>
-      <c r="F4" s="264"/>
-      <c r="G4" s="264"/>
-      <c r="H4" s="264"/>
-      <c r="I4" s="264"/>
-      <c r="J4" s="264"/>
-      <c r="K4" s="264"/>
-      <c r="L4" s="264"/>
+      <c r="D4" s="266"/>
+      <c r="E4" s="266"/>
+      <c r="F4" s="266"/>
+      <c r="G4" s="266"/>
+      <c r="H4" s="266"/>
+      <c r="I4" s="266"/>
+      <c r="J4" s="266"/>
+      <c r="K4" s="266"/>
+      <c r="L4" s="266"/>
       <c r="O4" s="5"/>
-      <c r="S4" s="265" t="s">
+      <c r="S4" s="267" t="s">
         <v>116</v>
       </c>
-      <c r="T4" s="266"/>
-      <c r="U4" s="266"/>
-      <c r="V4" s="266"/>
-      <c r="W4" s="266"/>
-      <c r="X4" s="266"/>
-      <c r="Y4" s="266"/>
-      <c r="Z4" s="266"/>
-      <c r="AA4" s="266"/>
-      <c r="AB4" s="266"/>
-      <c r="AC4" s="266"/>
+      <c r="T4" s="268"/>
+      <c r="U4" s="268"/>
+      <c r="V4" s="268"/>
+      <c r="W4" s="268"/>
+      <c r="X4" s="268"/>
+      <c r="Y4" s="268"/>
+      <c r="Z4" s="268"/>
+      <c r="AA4" s="268"/>
+      <c r="AB4" s="268"/>
+      <c r="AC4" s="268"/>
       <c r="AE4" s="88"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -15451,33 +15451,33 @@
       <c r="Q12" s="92"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="264" t="s">
+      <c r="C13" s="266" t="s">
         <v>122</v>
       </c>
-      <c r="D13" s="264"/>
-      <c r="E13" s="264"/>
-      <c r="F13" s="264"/>
-      <c r="G13" s="264"/>
-      <c r="H13" s="264"/>
-      <c r="I13" s="264"/>
-      <c r="J13" s="264"/>
-      <c r="K13" s="264"/>
-      <c r="L13" s="264"/>
+      <c r="D13" s="266"/>
+      <c r="E13" s="266"/>
+      <c r="F13" s="266"/>
+      <c r="G13" s="266"/>
+      <c r="H13" s="266"/>
+      <c r="I13" s="266"/>
+      <c r="J13" s="266"/>
+      <c r="K13" s="266"/>
+      <c r="L13" s="266"/>
       <c r="O13" s="5"/>
       <c r="Q13" s="92"/>
-      <c r="S13" s="265" t="s">
+      <c r="S13" s="267" t="s">
         <v>122</v>
       </c>
-      <c r="T13" s="266"/>
-      <c r="U13" s="266"/>
-      <c r="V13" s="266"/>
-      <c r="W13" s="266"/>
-      <c r="X13" s="266"/>
-      <c r="Y13" s="266"/>
-      <c r="Z13" s="266"/>
-      <c r="AA13" s="266"/>
-      <c r="AB13" s="266"/>
-      <c r="AC13" s="266"/>
+      <c r="T13" s="268"/>
+      <c r="U13" s="268"/>
+      <c r="V13" s="268"/>
+      <c r="W13" s="268"/>
+      <c r="X13" s="268"/>
+      <c r="Y13" s="268"/>
+      <c r="Z13" s="268"/>
+      <c r="AA13" s="268"/>
+      <c r="AB13" s="268"/>
+      <c r="AC13" s="268"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B14" s="16" t="s">
@@ -16086,33 +16086,33 @@
       <c r="Q22" s="92"/>
     </row>
     <row r="23" spans="2:31" x14ac:dyDescent="0.2">
-      <c r="C23" s="264" t="s">
+      <c r="C23" s="266" t="s">
         <v>124</v>
       </c>
-      <c r="D23" s="264"/>
-      <c r="E23" s="264"/>
-      <c r="F23" s="264"/>
-      <c r="G23" s="264"/>
-      <c r="H23" s="264"/>
-      <c r="I23" s="264"/>
-      <c r="J23" s="264"/>
-      <c r="K23" s="264"/>
-      <c r="L23" s="264"/>
+      <c r="D23" s="266"/>
+      <c r="E23" s="266"/>
+      <c r="F23" s="266"/>
+      <c r="G23" s="266"/>
+      <c r="H23" s="266"/>
+      <c r="I23" s="266"/>
+      <c r="J23" s="266"/>
+      <c r="K23" s="266"/>
+      <c r="L23" s="266"/>
       <c r="O23" s="5"/>
       <c r="Q23" s="92"/>
-      <c r="S23" s="265" t="s">
+      <c r="S23" s="267" t="s">
         <v>124</v>
       </c>
-      <c r="T23" s="266"/>
-      <c r="U23" s="266"/>
-      <c r="V23" s="266"/>
-      <c r="W23" s="266"/>
-      <c r="X23" s="266"/>
-      <c r="Y23" s="266"/>
-      <c r="Z23" s="266"/>
-      <c r="AA23" s="266"/>
-      <c r="AB23" s="266"/>
-      <c r="AC23" s="266"/>
+      <c r="T23" s="268"/>
+      <c r="U23" s="268"/>
+      <c r="V23" s="268"/>
+      <c r="W23" s="268"/>
+      <c r="X23" s="268"/>
+      <c r="Y23" s="268"/>
+      <c r="Z23" s="268"/>
+      <c r="AA23" s="268"/>
+      <c r="AB23" s="268"/>
+      <c r="AC23" s="268"/>
       <c r="AE23" s="88" t="str">
         <f>AE2</f>
         <v>TTM/YTD</v>
@@ -17431,32 +17431,32 @@
       <c r="O39" s="5"/>
     </row>
     <row r="40" spans="2:31" x14ac:dyDescent="0.2">
-      <c r="C40" s="264" t="s">
+      <c r="C40" s="266" t="s">
         <v>126</v>
       </c>
-      <c r="D40" s="264"/>
-      <c r="E40" s="264"/>
-      <c r="F40" s="264"/>
-      <c r="G40" s="264"/>
-      <c r="H40" s="264"/>
-      <c r="I40" s="264"/>
-      <c r="J40" s="264"/>
-      <c r="K40" s="264"/>
-      <c r="L40" s="264"/>
+      <c r="D40" s="266"/>
+      <c r="E40" s="266"/>
+      <c r="F40" s="266"/>
+      <c r="G40" s="266"/>
+      <c r="H40" s="266"/>
+      <c r="I40" s="266"/>
+      <c r="J40" s="266"/>
+      <c r="K40" s="266"/>
+      <c r="L40" s="266"/>
       <c r="O40" s="5"/>
-      <c r="S40" s="265" t="s">
+      <c r="S40" s="267" t="s">
         <v>126</v>
       </c>
-      <c r="T40" s="266"/>
-      <c r="U40" s="266"/>
-      <c r="V40" s="266"/>
-      <c r="W40" s="266"/>
-      <c r="X40" s="266"/>
-      <c r="Y40" s="266"/>
-      <c r="Z40" s="266"/>
-      <c r="AA40" s="266"/>
-      <c r="AB40" s="266"/>
-      <c r="AC40" s="266"/>
+      <c r="T40" s="268"/>
+      <c r="U40" s="268"/>
+      <c r="V40" s="268"/>
+      <c r="W40" s="268"/>
+      <c r="X40" s="268"/>
+      <c r="Y40" s="268"/>
+      <c r="Z40" s="268"/>
+      <c r="AA40" s="268"/>
+      <c r="AB40" s="268"/>
+      <c r="AC40" s="268"/>
     </row>
     <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -18023,18 +18023,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="C13:L13"/>
+    <mergeCell ref="S13:AC13"/>
+    <mergeCell ref="C23:L23"/>
+    <mergeCell ref="S23:AC23"/>
+    <mergeCell ref="C40:L40"/>
+    <mergeCell ref="S40:AC40"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="S2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
-    <mergeCell ref="C13:L13"/>
-    <mergeCell ref="S13:AC13"/>
-    <mergeCell ref="C23:L23"/>
-    <mergeCell ref="S23:AC23"/>
-    <mergeCell ref="C40:L40"/>
-    <mergeCell ref="S40:AC40"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -18068,35 +18068,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="255" t="s">
+      <c r="C2" s="258" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="255"/>
-      <c r="E2" s="255"/>
-      <c r="F2" s="255"/>
-      <c r="G2" s="267"/>
-      <c r="H2" s="268" t="s">
+      <c r="D2" s="258"/>
+      <c r="E2" s="258"/>
+      <c r="F2" s="258"/>
+      <c r="G2" s="264"/>
+      <c r="H2" s="265" t="s">
         <v>114</v>
       </c>
-      <c r="I2" s="255"/>
-      <c r="J2" s="255"/>
-      <c r="K2" s="255"/>
-      <c r="L2" s="255"/>
-      <c r="P2" s="255" t="s">
+      <c r="I2" s="258"/>
+      <c r="J2" s="258"/>
+      <c r="K2" s="258"/>
+      <c r="L2" s="258"/>
+      <c r="P2" s="258" t="s">
         <v>113</v>
       </c>
-      <c r="Q2" s="255"/>
-      <c r="R2" s="255"/>
-      <c r="S2" s="255"/>
-      <c r="T2" s="255"/>
-      <c r="U2" s="255"/>
-      <c r="V2" s="255"/>
-      <c r="W2" s="255"/>
-      <c r="X2" s="255" t="s">
+      <c r="Q2" s="258"/>
+      <c r="R2" s="258"/>
+      <c r="S2" s="258"/>
+      <c r="T2" s="258"/>
+      <c r="U2" s="258"/>
+      <c r="V2" s="258"/>
+      <c r="W2" s="258"/>
+      <c r="X2" s="258" t="s">
         <v>114</v>
       </c>
-      <c r="Y2" s="255"/>
-      <c r="Z2" s="255"/>
+      <c r="Y2" s="258"/>
+      <c r="Z2" s="258"/>
       <c r="AB2" s="86" t="s">
         <v>115</v>
       </c>
@@ -18105,31 +18105,31 @@
     <row r="4" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="264" t="s">
+      <c r="C4" s="266" t="s">
         <v>116</v>
       </c>
-      <c r="D4" s="264"/>
-      <c r="E4" s="264"/>
-      <c r="F4" s="264"/>
-      <c r="G4" s="264"/>
-      <c r="H4" s="264"/>
-      <c r="I4" s="264"/>
-      <c r="J4" s="264"/>
-      <c r="K4" s="264"/>
-      <c r="L4" s="264"/>
-      <c r="P4" s="266" t="s">
+      <c r="D4" s="266"/>
+      <c r="E4" s="266"/>
+      <c r="F4" s="266"/>
+      <c r="G4" s="266"/>
+      <c r="H4" s="266"/>
+      <c r="I4" s="266"/>
+      <c r="J4" s="266"/>
+      <c r="K4" s="266"/>
+      <c r="L4" s="266"/>
+      <c r="P4" s="268" t="s">
         <v>116</v>
       </c>
-      <c r="Q4" s="266"/>
-      <c r="R4" s="266"/>
-      <c r="S4" s="266"/>
-      <c r="T4" s="266"/>
-      <c r="U4" s="266"/>
-      <c r="V4" s="266"/>
-      <c r="W4" s="266"/>
-      <c r="X4" s="266"/>
-      <c r="Y4" s="266"/>
-      <c r="Z4" s="266"/>
+      <c r="Q4" s="268"/>
+      <c r="R4" s="268"/>
+      <c r="S4" s="268"/>
+      <c r="T4" s="268"/>
+      <c r="U4" s="268"/>
+      <c r="V4" s="268"/>
+      <c r="W4" s="268"/>
+      <c r="X4" s="268"/>
+      <c r="Y4" s="268"/>
+      <c r="Z4" s="268"/>
       <c r="AB4" s="88"/>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
@@ -18324,32 +18324,32 @@
       <c r="N8" s="92"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C9" s="264" t="s">
+      <c r="C9" s="266" t="s">
         <v>129</v>
       </c>
-      <c r="D9" s="264"/>
-      <c r="E9" s="264"/>
-      <c r="F9" s="264"/>
-      <c r="G9" s="264"/>
-      <c r="H9" s="264"/>
-      <c r="I9" s="264"/>
-      <c r="J9" s="264"/>
-      <c r="K9" s="264"/>
-      <c r="L9" s="264"/>
+      <c r="D9" s="266"/>
+      <c r="E9" s="266"/>
+      <c r="F9" s="266"/>
+      <c r="G9" s="266"/>
+      <c r="H9" s="266"/>
+      <c r="I9" s="266"/>
+      <c r="J9" s="266"/>
+      <c r="K9" s="266"/>
+      <c r="L9" s="266"/>
       <c r="N9" s="92"/>
-      <c r="P9" s="266" t="s">
+      <c r="P9" s="268" t="s">
         <v>130</v>
       </c>
-      <c r="Q9" s="266"/>
-      <c r="R9" s="266"/>
-      <c r="S9" s="266"/>
-      <c r="T9" s="266"/>
-      <c r="U9" s="266"/>
-      <c r="V9" s="266"/>
-      <c r="W9" s="266"/>
-      <c r="X9" s="266"/>
-      <c r="Y9" s="266"/>
-      <c r="Z9" s="266"/>
+      <c r="Q9" s="268"/>
+      <c r="R9" s="268"/>
+      <c r="S9" s="268"/>
+      <c r="T9" s="268"/>
+      <c r="U9" s="268"/>
+      <c r="V9" s="268"/>
+      <c r="W9" s="268"/>
+      <c r="X9" s="268"/>
+      <c r="Y9" s="268"/>
+      <c r="Z9" s="268"/>
       <c r="AB9" s="88">
         <f>AB4</f>
         <v>0</v>
@@ -18919,31 +18919,31 @@
       </c>
     </row>
     <row r="18" spans="2:26" x14ac:dyDescent="0.2">
-      <c r="C18" s="264" t="s">
+      <c r="C18" s="266" t="s">
         <v>132</v>
       </c>
-      <c r="D18" s="264"/>
-      <c r="E18" s="264"/>
-      <c r="F18" s="264"/>
-      <c r="G18" s="264"/>
-      <c r="H18" s="264"/>
-      <c r="I18" s="264"/>
-      <c r="J18" s="264"/>
-      <c r="K18" s="264"/>
-      <c r="L18" s="264"/>
-      <c r="P18" s="266" t="s">
+      <c r="D18" s="266"/>
+      <c r="E18" s="266"/>
+      <c r="F18" s="266"/>
+      <c r="G18" s="266"/>
+      <c r="H18" s="266"/>
+      <c r="I18" s="266"/>
+      <c r="J18" s="266"/>
+      <c r="K18" s="266"/>
+      <c r="L18" s="266"/>
+      <c r="P18" s="268" t="s">
         <v>132</v>
       </c>
-      <c r="Q18" s="266"/>
-      <c r="R18" s="266"/>
-      <c r="S18" s="266"/>
-      <c r="T18" s="266"/>
-      <c r="U18" s="266"/>
-      <c r="V18" s="266"/>
-      <c r="W18" s="266"/>
-      <c r="X18" s="266"/>
-      <c r="Y18" s="266"/>
-      <c r="Z18" s="266"/>
+      <c r="Q18" s="268"/>
+      <c r="R18" s="268"/>
+      <c r="S18" s="268"/>
+      <c r="T18" s="268"/>
+      <c r="U18" s="268"/>
+      <c r="V18" s="268"/>
+      <c r="W18" s="268"/>
+      <c r="X18" s="268"/>
+      <c r="Y18" s="268"/>
+      <c r="Z18" s="268"/>
     </row>
     <row r="19" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -19503,20 +19503,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="255" t="s">
+      <c r="C3" s="258" t="s">
         <v>113</v>
       </c>
-      <c r="D3" s="255"/>
-      <c r="E3" s="255"/>
-      <c r="F3" s="255"/>
-      <c r="G3" s="267"/>
-      <c r="H3" s="268" t="s">
+      <c r="D3" s="258"/>
+      <c r="E3" s="258"/>
+      <c r="F3" s="258"/>
+      <c r="G3" s="264"/>
+      <c r="H3" s="265" t="s">
         <v>114</v>
       </c>
-      <c r="I3" s="255"/>
-      <c r="J3" s="255"/>
-      <c r="K3" s="255"/>
-      <c r="L3" s="255"/>
+      <c r="I3" s="258"/>
+      <c r="J3" s="258"/>
+      <c r="K3" s="258"/>
+      <c r="L3" s="258"/>
       <c r="P3" s="269"/>
       <c r="Q3" s="269"/>
       <c r="R3" s="269"/>
@@ -19534,18 +19534,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="87"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="264" t="s">
+      <c r="C5" s="266" t="s">
         <v>116</v>
       </c>
-      <c r="D5" s="264"/>
-      <c r="E5" s="264"/>
-      <c r="F5" s="264"/>
-      <c r="G5" s="264"/>
-      <c r="H5" s="264"/>
-      <c r="I5" s="264"/>
-      <c r="J5" s="264"/>
-      <c r="K5" s="264"/>
-      <c r="L5" s="264"/>
+      <c r="D5" s="266"/>
+      <c r="E5" s="266"/>
+      <c r="F5" s="266"/>
+      <c r="G5" s="266"/>
+      <c r="H5" s="266"/>
+      <c r="I5" s="266"/>
+      <c r="J5" s="266"/>
+      <c r="K5" s="266"/>
+      <c r="L5" s="266"/>
       <c r="P5" s="269"/>
       <c r="Q5" s="269"/>
       <c r="R5" s="269"/>
@@ -19742,18 +19742,18 @@
       <c r="N10" s="92"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="264" t="s">
+      <c r="C11" s="266" t="s">
         <v>136</v>
       </c>
-      <c r="D11" s="264"/>
-      <c r="E11" s="264"/>
-      <c r="F11" s="264"/>
-      <c r="G11" s="264"/>
-      <c r="H11" s="264"/>
-      <c r="I11" s="264"/>
-      <c r="J11" s="264"/>
-      <c r="K11" s="264"/>
-      <c r="L11" s="264"/>
+      <c r="D11" s="266"/>
+      <c r="E11" s="266"/>
+      <c r="F11" s="266"/>
+      <c r="G11" s="266"/>
+      <c r="H11" s="266"/>
+      <c r="I11" s="266"/>
+      <c r="J11" s="266"/>
+      <c r="K11" s="266"/>
+      <c r="L11" s="266"/>
       <c r="N11" s="92"/>
       <c r="P11" s="269"/>
       <c r="Q11" s="269"/>
@@ -20007,18 +20007,18 @@
       <c r="D16" s="24"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="264" t="s">
+      <c r="C18" s="266" t="s">
         <v>141</v>
       </c>
-      <c r="D18" s="264"/>
-      <c r="E18" s="264"/>
-      <c r="F18" s="264"/>
-      <c r="G18" s="264"/>
-      <c r="H18" s="264"/>
-      <c r="I18" s="264"/>
-      <c r="J18" s="264"/>
-      <c r="K18" s="264"/>
-      <c r="L18" s="264"/>
+      <c r="D18" s="266"/>
+      <c r="E18" s="266"/>
+      <c r="F18" s="266"/>
+      <c r="G18" s="266"/>
+      <c r="H18" s="266"/>
+      <c r="I18" s="266"/>
+      <c r="J18" s="266"/>
+      <c r="K18" s="266"/>
+      <c r="L18" s="266"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -20236,18 +20236,18 @@
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="111"/>
-      <c r="C26" s="264" t="s">
+      <c r="C26" s="266" t="s">
         <v>147</v>
       </c>
-      <c r="D26" s="264"/>
-      <c r="E26" s="264"/>
-      <c r="F26" s="264"/>
-      <c r="G26" s="264"/>
-      <c r="H26" s="264"/>
-      <c r="I26" s="264"/>
-      <c r="J26" s="264"/>
-      <c r="K26" s="264"/>
-      <c r="L26" s="264"/>
+      <c r="D26" s="266"/>
+      <c r="E26" s="266"/>
+      <c r="F26" s="266"/>
+      <c r="G26" s="266"/>
+      <c r="H26" s="266"/>
+      <c r="I26" s="266"/>
+      <c r="J26" s="266"/>
+      <c r="K26" s="266"/>
+      <c r="L26" s="266"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="16" t="s">
@@ -20439,18 +20439,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="111"/>
-      <c r="C33" s="264" t="s">
+      <c r="C33" s="266" t="s">
         <v>151</v>
       </c>
-      <c r="D33" s="264"/>
-      <c r="E33" s="264"/>
-      <c r="F33" s="264"/>
-      <c r="G33" s="264"/>
-      <c r="H33" s="264"/>
-      <c r="I33" s="264"/>
-      <c r="J33" s="264"/>
-      <c r="K33" s="264"/>
-      <c r="L33" s="264"/>
+      <c r="D33" s="266"/>
+      <c r="E33" s="266"/>
+      <c r="F33" s="266"/>
+      <c r="G33" s="266"/>
+      <c r="H33" s="266"/>
+      <c r="I33" s="266"/>
+      <c r="J33" s="266"/>
+      <c r="K33" s="266"/>
+      <c r="L33" s="266"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
@@ -20634,18 +20634,18 @@
       <c r="C39" s="127"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="264" t="s">
+      <c r="C40" s="266" t="s">
         <v>154</v>
       </c>
-      <c r="D40" s="264"/>
-      <c r="E40" s="264"/>
-      <c r="F40" s="264"/>
-      <c r="G40" s="264"/>
-      <c r="H40" s="264"/>
-      <c r="I40" s="264"/>
-      <c r="J40" s="264"/>
-      <c r="K40" s="264"/>
-      <c r="L40" s="264"/>
+      <c r="D40" s="266"/>
+      <c r="E40" s="266"/>
+      <c r="F40" s="266"/>
+      <c r="G40" s="266"/>
+      <c r="H40" s="266"/>
+      <c r="I40" s="266"/>
+      <c r="J40" s="266"/>
+      <c r="K40" s="266"/>
+      <c r="L40" s="266"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -20909,6 +20909,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -20916,12 +20922,6 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -20959,20 +20959,20 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="255" t="s">
+      <c r="C2" s="258" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="255"/>
-      <c r="E2" s="255"/>
-      <c r="F2" s="255"/>
-      <c r="G2" s="267"/>
-      <c r="H2" s="268" t="s">
+      <c r="D2" s="258"/>
+      <c r="E2" s="258"/>
+      <c r="F2" s="258"/>
+      <c r="G2" s="264"/>
+      <c r="H2" s="265" t="s">
         <v>114</v>
       </c>
-      <c r="I2" s="255"/>
-      <c r="J2" s="255"/>
-      <c r="K2" s="255"/>
-      <c r="L2" s="255"/>
+      <c r="I2" s="258"/>
+      <c r="J2" s="258"/>
+      <c r="K2" s="258"/>
+      <c r="L2" s="258"/>
       <c r="S2" s="269"/>
       <c r="T2" s="269"/>
       <c r="U2" s="269"/>
@@ -20990,18 +20990,18 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="264" t="s">
+      <c r="C4" s="266" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="264"/>
-      <c r="E4" s="264"/>
-      <c r="F4" s="264"/>
-      <c r="G4" s="264"/>
-      <c r="H4" s="264"/>
-      <c r="I4" s="264"/>
-      <c r="J4" s="264"/>
-      <c r="K4" s="264"/>
-      <c r="L4" s="264"/>
+      <c r="D4" s="266"/>
+      <c r="E4" s="266"/>
+      <c r="F4" s="266"/>
+      <c r="G4" s="266"/>
+      <c r="H4" s="266"/>
+      <c r="I4" s="266"/>
+      <c r="J4" s="266"/>
+      <c r="K4" s="266"/>
+      <c r="L4" s="266"/>
       <c r="S4" s="269"/>
       <c r="T4" s="269"/>
       <c r="U4" s="269"/>
@@ -21375,18 +21375,18 @@
       <c r="AE10" s="64"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="264" t="s">
+      <c r="C13" s="266" t="s">
         <v>162</v>
       </c>
-      <c r="D13" s="264"/>
-      <c r="E13" s="264"/>
-      <c r="F13" s="264"/>
-      <c r="G13" s="264"/>
-      <c r="H13" s="264"/>
-      <c r="I13" s="264"/>
-      <c r="J13" s="264"/>
-      <c r="K13" s="264"/>
-      <c r="L13" s="264"/>
+      <c r="D13" s="266"/>
+      <c r="E13" s="266"/>
+      <c r="F13" s="266"/>
+      <c r="G13" s="266"/>
+      <c r="H13" s="266"/>
+      <c r="I13" s="266"/>
+      <c r="J13" s="266"/>
+      <c r="K13" s="266"/>
+      <c r="L13" s="266"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="12">
@@ -21479,18 +21479,18 @@
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C18" s="264" t="s">
+      <c r="C18" s="266" t="s">
         <v>163</v>
       </c>
-      <c r="D18" s="264"/>
-      <c r="E18" s="264"/>
-      <c r="F18" s="264"/>
-      <c r="G18" s="264"/>
-      <c r="H18" s="264"/>
-      <c r="I18" s="264"/>
-      <c r="J18" s="264"/>
-      <c r="K18" s="264"/>
-      <c r="L18" s="264"/>
+      <c r="D18" s="266"/>
+      <c r="E18" s="266"/>
+      <c r="F18" s="266"/>
+      <c r="G18" s="266"/>
+      <c r="H18" s="266"/>
+      <c r="I18" s="266"/>
+      <c r="J18" s="266"/>
+      <c r="K18" s="266"/>
+      <c r="L18" s="266"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -21682,18 +21682,18 @@
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C25" s="264" t="s">
+      <c r="C25" s="266" t="s">
         <v>266</v>
       </c>
-      <c r="D25" s="264"/>
-      <c r="E25" s="264"/>
-      <c r="F25" s="264"/>
-      <c r="G25" s="264"/>
-      <c r="H25" s="264"/>
-      <c r="I25" s="264"/>
-      <c r="J25" s="264"/>
-      <c r="K25" s="264"/>
-      <c r="L25" s="264"/>
+      <c r="D25" s="266"/>
+      <c r="E25" s="266"/>
+      <c r="F25" s="266"/>
+      <c r="G25" s="266"/>
+      <c r="H25" s="266"/>
+      <c r="I25" s="266"/>
+      <c r="J25" s="266"/>
+      <c r="K25" s="266"/>
+      <c r="L25" s="266"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B26" s="16" t="s">
@@ -21831,18 +21831,18 @@
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C31" s="264" t="s">
+      <c r="C31" s="266" t="s">
         <v>78</v>
       </c>
-      <c r="D31" s="264"/>
-      <c r="E31" s="264"/>
-      <c r="F31" s="264"/>
-      <c r="G31" s="264"/>
-      <c r="H31" s="264"/>
-      <c r="I31" s="264"/>
-      <c r="J31" s="264"/>
-      <c r="K31" s="264"/>
-      <c r="L31" s="264"/>
+      <c r="D31" s="266"/>
+      <c r="E31" s="266"/>
+      <c r="F31" s="266"/>
+      <c r="G31" s="266"/>
+      <c r="H31" s="266"/>
+      <c r="I31" s="266"/>
+      <c r="J31" s="266"/>
+      <c r="K31" s="266"/>
+      <c r="L31" s="266"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="16" t="s">
@@ -21981,16 +21981,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="S4:AC4"/>
+    <mergeCell ref="C13:L13"/>
+    <mergeCell ref="C18:L18"/>
     <mergeCell ref="C31:L31"/>
     <mergeCell ref="C25:L25"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="S2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="S4:AC4"/>
-    <mergeCell ref="C13:L13"/>
-    <mergeCell ref="C18:L18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -22053,10 +22053,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="255" t="s">
+      <c r="B4" s="258" t="s">
         <v>170</v>
       </c>
-      <c r="C4" s="255"/>
+      <c r="C4" s="258"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -22073,7 +22073,7 @@
       </c>
       <c r="C6" s="135">
         <f ca="1">Overview!C5</f>
-        <v>143.51</v>
+        <v>142.62</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22082,7 +22082,7 @@
       </c>
       <c r="C7" s="136">
         <f ca="1">C5*C6</f>
-        <v>7193008.2199999997</v>
+        <v>7148399.6400000006</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22100,7 +22100,7 @@
       </c>
       <c r="C9" s="137">
         <f ca="1">Overview!F27</f>
-        <v>5.1840000000000004E-2</v>
+        <v>5.2399999999999995E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22109,7 +22109,7 @@
       </c>
       <c r="C10" s="135">
         <f ca="1">Overview!C13</f>
-        <v>1.0463</v>
+        <v>1.054</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22141,10 +22141,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="255" t="s">
+      <c r="B15" s="258" t="s">
         <v>177</v>
       </c>
-      <c r="C15" s="255"/>
+      <c r="C15" s="258"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -22179,7 +22179,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>9.8923499999999998E-2</v>
+        <v>9.9830000000000002E-2</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22188,7 +22188,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>9.8923499999999998E-2</v>
+        <v>9.9830000000000002E-2</v>
       </c>
     </row>
   </sheetData>
@@ -22233,20 +22233,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="255" t="s">
+      <c r="C3" s="258" t="s">
         <v>113</v>
       </c>
-      <c r="D3" s="255"/>
-      <c r="E3" s="255"/>
-      <c r="F3" s="255"/>
-      <c r="G3" s="267"/>
-      <c r="H3" s="268" t="s">
+      <c r="D3" s="258"/>
+      <c r="E3" s="258"/>
+      <c r="F3" s="258"/>
+      <c r="G3" s="264"/>
+      <c r="H3" s="265" t="s">
         <v>114</v>
       </c>
-      <c r="I3" s="255"/>
-      <c r="J3" s="255"/>
-      <c r="K3" s="255"/>
-      <c r="L3" s="255"/>
+      <c r="I3" s="258"/>
+      <c r="J3" s="258"/>
+      <c r="K3" s="258"/>
+      <c r="L3" s="258"/>
       <c r="P3" s="269"/>
       <c r="Q3" s="269"/>
       <c r="R3" s="269"/>
@@ -22264,18 +22264,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="87"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="264" t="s">
+      <c r="C5" s="266" t="s">
         <v>184</v>
       </c>
-      <c r="D5" s="264"/>
-      <c r="E5" s="264"/>
-      <c r="F5" s="264"/>
-      <c r="G5" s="264"/>
-      <c r="H5" s="264"/>
-      <c r="I5" s="264"/>
-      <c r="J5" s="264"/>
-      <c r="K5" s="264"/>
-      <c r="L5" s="264"/>
+      <c r="D5" s="266"/>
+      <c r="E5" s="266"/>
+      <c r="F5" s="266"/>
+      <c r="G5" s="266"/>
+      <c r="H5" s="266"/>
+      <c r="I5" s="266"/>
+      <c r="J5" s="266"/>
+      <c r="K5" s="266"/>
+      <c r="L5" s="266"/>
       <c r="P5" s="269"/>
       <c r="Q5" s="269"/>
       <c r="R5" s="269"/>
@@ -22439,7 +22439,7 @@
       </c>
       <c r="L8" s="128">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>7418305.8450111272</v>
+        <v>7334068.1618280802</v>
       </c>
       <c r="N8" s="92"/>
       <c r="O8" s="16"/>
@@ -22493,23 +22493,23 @@
       <c r="G10" s="140"/>
       <c r="H10" s="128">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>164500.23321117781</v>
+        <v>164364.64911053865</v>
       </c>
       <c r="I10" s="128">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>199168.06341362261</v>
+        <v>198839.88279500158</v>
       </c>
       <c r="J10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>227180.1811763712</v>
+        <v>226618.90586386787</v>
       </c>
       <c r="K10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>261333.64084099015</v>
+        <v>260473.12159107611</v>
       </c>
       <c r="L10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>358157.12565835513</v>
+        <v>356683.55847808288</v>
       </c>
       <c r="N10" s="92"/>
     </row>
@@ -22528,14 +22528,14 @@
       <c r="K11" s="139"/>
       <c r="L11" s="128">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>4628789.5008650431</v>
+        <v>4557399.8452667482</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="255" t="s">
+      <c r="B13" s="258" t="s">
         <v>188</v>
       </c>
-      <c r="C13" s="255"/>
+      <c r="C13" s="258"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -22551,14 +22551,14 @@
       </c>
       <c r="C15" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>9.8923499999999998E-2</v>
+        <v>9.9830000000000002E-2</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="255" t="s">
+      <c r="B18" s="258" t="s">
         <v>190</v>
       </c>
-      <c r="C18" s="255"/>
+      <c r="C18" s="258"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -22566,7 +22566,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>1210339.2443005168</v>
+        <v>1206980.1178385671</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -22575,7 +22575,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>4628789.5008650431</v>
+        <v>4557399.8452667482</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -22584,7 +22584,7 @@
       </c>
       <c r="C21" s="95">
         <f ca="1">C19+C20</f>
-        <v>5839128.7451655604</v>
+        <v>5764379.9631053153</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -22611,7 +22611,7 @@
       </c>
       <c r="C24" s="95">
         <f ca="1">C21+C22-C23</f>
-        <v>7255687.7451655604</v>
+        <v>7180938.9631053153</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -22629,7 +22629,7 @@
       </c>
       <c r="C26" s="254">
         <f ca="1">C24/C25</f>
-        <v>144.76053918769324</v>
+        <v>143.26920240823023</v>
       </c>
     </row>
   </sheetData>
@@ -22672,37 +22672,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="255" t="s">
+      <c r="C2" s="258" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="255"/>
-      <c r="E2" s="255"/>
-      <c r="F2" s="255"/>
-      <c r="G2" s="267"/>
-      <c r="H2" s="268" t="s">
+      <c r="D2" s="258"/>
+      <c r="E2" s="258"/>
+      <c r="F2" s="258"/>
+      <c r="G2" s="264"/>
+      <c r="H2" s="265" t="s">
         <v>114</v>
       </c>
-      <c r="I2" s="255"/>
-      <c r="J2" s="255"/>
-      <c r="K2" s="255"/>
-      <c r="L2" s="255"/>
+      <c r="I2" s="258"/>
+      <c r="J2" s="258"/>
+      <c r="K2" s="258"/>
+      <c r="L2" s="258"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="264" t="s">
+      <c r="C4" s="266" t="s">
         <v>198</v>
       </c>
-      <c r="D4" s="264"/>
-      <c r="E4" s="264"/>
-      <c r="F4" s="264"/>
-      <c r="G4" s="264"/>
-      <c r="H4" s="264"/>
-      <c r="I4" s="264"/>
-      <c r="J4" s="264"/>
-      <c r="K4" s="264"/>
-      <c r="L4" s="264"/>
+      <c r="D4" s="266"/>
+      <c r="E4" s="266"/>
+      <c r="F4" s="266"/>
+      <c r="G4" s="266"/>
+      <c r="H4" s="266"/>
+      <c r="I4" s="266"/>
+      <c r="J4" s="266"/>
+      <c r="K4" s="266"/>
+      <c r="L4" s="266"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -22898,23 +22898,23 @@
       <c r="G9" s="140"/>
       <c r="H9" s="93">
         <f ca="1">DCF!H10</f>
-        <v>164500.23321117781</v>
+        <v>164364.64911053865</v>
       </c>
       <c r="I9" s="93">
         <f ca="1">DCF!I10</f>
-        <v>199168.06341362261</v>
+        <v>198839.88279500158</v>
       </c>
       <c r="J9" s="93">
         <f ca="1">DCF!J10</f>
-        <v>227180.1811763712</v>
+        <v>226618.90586386787</v>
       </c>
       <c r="K9" s="93">
         <f ca="1">DCF!K10</f>
-        <v>261333.64084099015</v>
+        <v>260473.12159107611</v>
       </c>
       <c r="L9" s="93">
         <f ca="1">DCF!L10</f>
-        <v>358157.12565835513</v>
+        <v>356683.55847808288</v>
       </c>
       <c r="N9" s="92"/>
     </row>
@@ -22922,18 +22922,18 @@
       <c r="N10" s="92"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C11" s="264" t="s">
+      <c r="C11" s="266" t="s">
         <v>122</v>
       </c>
-      <c r="D11" s="264"/>
-      <c r="E11" s="264"/>
-      <c r="F11" s="264"/>
-      <c r="G11" s="264"/>
-      <c r="H11" s="264"/>
-      <c r="I11" s="264"/>
-      <c r="J11" s="264"/>
-      <c r="K11" s="264"/>
-      <c r="L11" s="264"/>
+      <c r="D11" s="266"/>
+      <c r="E11" s="266"/>
+      <c r="F11" s="266"/>
+      <c r="G11" s="266"/>
+      <c r="H11" s="266"/>
+      <c r="I11" s="266"/>
+      <c r="J11" s="266"/>
+      <c r="K11" s="266"/>
+      <c r="L11" s="266"/>
       <c r="N11" s="92"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -23127,18 +23127,18 @@
       <c r="N16" s="92"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C17" s="264" t="s">
+      <c r="C17" s="266" t="s">
         <v>200</v>
       </c>
-      <c r="D17" s="264"/>
-      <c r="E17" s="264"/>
-      <c r="F17" s="264"/>
-      <c r="G17" s="264"/>
-      <c r="H17" s="264"/>
-      <c r="I17" s="264"/>
-      <c r="J17" s="264"/>
-      <c r="K17" s="264"/>
-      <c r="L17" s="264"/>
+      <c r="D17" s="266"/>
+      <c r="E17" s="266"/>
+      <c r="F17" s="266"/>
+      <c r="G17" s="266"/>
+      <c r="H17" s="266"/>
+      <c r="I17" s="266"/>
+      <c r="J17" s="266"/>
+      <c r="K17" s="266"/>
+      <c r="L17" s="266"/>
       <c r="N17" s="92"/>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
@@ -23272,18 +23272,18 @@
       <c r="N21" s="92"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C22" s="264" t="s">
+      <c r="C22" s="266" t="s">
         <v>203</v>
       </c>
-      <c r="D22" s="264"/>
-      <c r="E22" s="264"/>
-      <c r="F22" s="264"/>
-      <c r="G22" s="264"/>
-      <c r="H22" s="264"/>
-      <c r="I22" s="264"/>
-      <c r="J22" s="264"/>
-      <c r="K22" s="264"/>
-      <c r="L22" s="264"/>
+      <c r="D22" s="266"/>
+      <c r="E22" s="266"/>
+      <c r="F22" s="266"/>
+      <c r="G22" s="266"/>
+      <c r="H22" s="266"/>
+      <c r="I22" s="266"/>
+      <c r="J22" s="266"/>
+      <c r="K22" s="266"/>
+      <c r="L22" s="266"/>
       <c r="N22" s="92"/>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.2">
@@ -23367,18 +23367,18 @@
       <c r="N26" s="92"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C27" s="264" t="s">
+      <c r="C27" s="266" t="s">
         <v>204</v>
       </c>
-      <c r="D27" s="264"/>
-      <c r="E27" s="264"/>
-      <c r="F27" s="264"/>
-      <c r="G27" s="264"/>
-      <c r="H27" s="264"/>
-      <c r="I27" s="264"/>
-      <c r="J27" s="264"/>
-      <c r="K27" s="264"/>
-      <c r="L27" s="264"/>
+      <c r="D27" s="266"/>
+      <c r="E27" s="266"/>
+      <c r="F27" s="266"/>
+      <c r="G27" s="266"/>
+      <c r="H27" s="266"/>
+      <c r="I27" s="266"/>
+      <c r="J27" s="266"/>
+      <c r="K27" s="266"/>
+      <c r="L27" s="266"/>
       <c r="N27" s="92"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.2">
@@ -23679,10 +23679,10 @@
       <c r="N38" s="92"/>
     </row>
     <row r="39" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B39" s="255" t="s">
+      <c r="B39" s="258" t="s">
         <v>209</v>
       </c>
-      <c r="C39" s="255"/>
+      <c r="C39" s="258"/>
       <c r="N39" s="92"/>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -23700,7 +23700,7 @@
       </c>
       <c r="C41" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>9.8923499999999998E-2</v>
+        <v>9.9830000000000002E-2</v>
       </c>
     </row>
     <row r="42" spans="2:14" x14ac:dyDescent="0.2">
@@ -23726,7 +23726,7 @@
       </c>
       <c r="C44" s="24">
         <f ca="1">C43/(1+C41)^5</f>
-        <v>7604222.1868190654</v>
+        <v>7572936.1074889461</v>
       </c>
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.2">
@@ -23735,7 +23735,7 @@
       </c>
       <c r="C45" s="110">
         <f ca="1">SUM(H9:K9)+C44</f>
-        <v>8456404.3054612279</v>
+        <v>8423232.6668494307</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -23762,7 +23762,7 @@
       </c>
       <c r="C48" s="110">
         <f ca="1">C45+C46-C47</f>
-        <v>9872963.3054612279</v>
+        <v>9839791.6668494307</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
@@ -23780,14 +23780,14 @@
       </c>
       <c r="C50" s="254">
         <f ca="1">C48/C49</f>
-        <v>196.97863823193862</v>
+        <v>196.31682029546766</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B52" s="255" t="s">
+      <c r="B52" s="258" t="s">
         <v>214</v>
       </c>
-      <c r="C52" s="255"/>
+      <c r="C52" s="258"/>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B53" s="1" t="s">
@@ -23804,7 +23804,7 @@
       </c>
       <c r="C54" s="137">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>9.8923499999999998E-2</v>
+        <v>9.9830000000000002E-2</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
@@ -23839,14 +23839,14 @@
       </c>
       <c r="C58" s="254">
         <f ca="1">C57/(1+C54)^5</f>
-        <v>158.71378004179414</v>
+        <v>158.06078335243151</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B60" s="255" t="s">
+      <c r="B60" s="258" t="s">
         <v>327</v>
       </c>
-      <c r="C60" s="255"/>
+      <c r="C60" s="258"/>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B61" s="1" t="s">
@@ -23863,7 +23863,7 @@
       </c>
       <c r="C62" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>9.8923499999999998E-2</v>
+        <v>9.9830000000000002E-2</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
@@ -23889,7 +23889,7 @@
       </c>
       <c r="C65" s="24">
         <f ca="1">C64/(1+C62)^5</f>
-        <v>7879456.7644838123</v>
+        <v>7847038.2865178222</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -23898,7 +23898,7 @@
       </c>
       <c r="C66" s="110">
         <f ca="1">SUM(H9:K9)+C65</f>
-        <v>8731638.8831259739</v>
+        <v>8697334.8458783068</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.2">
@@ -23925,7 +23925,7 @@
       </c>
       <c r="C69" s="110">
         <f ca="1">C66+C67-C68</f>
-        <v>10148197.883125974</v>
+        <v>10113893.845878307</v>
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.2">
@@ -23943,14 +23943,14 @@
       </c>
       <c r="C71" s="254">
         <f ca="1">C69/C70</f>
-        <v>202.4699310308043</v>
+        <v>201.78552024816062</v>
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B73" s="255" t="s">
+      <c r="B73" s="258" t="s">
         <v>433</v>
       </c>
-      <c r="C73" s="255"/>
+      <c r="C73" s="258"/>
     </row>
     <row r="74" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B74" s="1" t="s">
@@ -23967,7 +23967,7 @@
       </c>
       <c r="C75" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>9.8923499999999998E-2</v>
+        <v>9.9830000000000002E-2</v>
       </c>
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.2">
@@ -23993,7 +23993,7 @@
       </c>
       <c r="C78" s="24">
         <f ca="1">C77/(1+C75)^5</f>
-        <v>7900490.5837081242</v>
+        <v>7867985.5662222859</v>
       </c>
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.2">
@@ -24002,7 +24002,7 @@
       </c>
       <c r="C79" s="110">
         <f ca="1">SUM(H9:K9)+C78</f>
-        <v>8752672.7023502868</v>
+        <v>8718282.1255827695</v>
       </c>
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.2">
@@ -24029,7 +24029,7 @@
       </c>
       <c r="C82" s="110">
         <f ca="1">C79+C80-C81</f>
-        <v>10169231.702350287</v>
+        <v>10134841.12558277</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.2">
@@ -24047,22 +24047,22 @@
       </c>
       <c r="C84" s="254">
         <f ca="1">C82/C83</f>
-        <v>202.88958346335514</v>
+        <v>202.20344610316366</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="C27:L27"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B60:C60"/>
     <mergeCell ref="C22:L22"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="C17:L17"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="C27:L27"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B60:C60"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -24100,10 +24100,10 @@
       <c r="N3" s="92"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="255" t="s">
+      <c r="B4" s="258" t="s">
         <v>218</v>
       </c>
-      <c r="C4" s="255"/>
+      <c r="C4" s="258"/>
       <c r="N4" s="92"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -24112,7 +24112,7 @@
       </c>
       <c r="C5" s="135">
         <f ca="1">DCF!C26</f>
-        <v>144.76053918769324</v>
+        <v>143.26920240823023</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -24121,7 +24121,7 @@
       </c>
       <c r="C6" s="135">
         <f ca="1">Multiples!C50</f>
-        <v>196.97863823193862</v>
+        <v>196.31682029546766</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -24130,7 +24130,7 @@
       </c>
       <c r="C7" s="135">
         <f ca="1">Multiples!C58</f>
-        <v>158.71378004179414</v>
+        <v>158.06078335243151</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -24139,7 +24139,7 @@
       </c>
       <c r="C8" s="135">
         <f ca="1">Multiples!C71</f>
-        <v>202.4699310308043</v>
+        <v>201.78552024816062</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -24148,7 +24148,7 @@
       </c>
       <c r="C9" s="135">
         <f ca="1">Multiples!C84</f>
-        <v>202.88958346335514</v>
+        <v>202.20344610316366</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -24157,7 +24157,7 @@
       </c>
       <c r="C10" s="254">
         <f ca="1">AVERAGE(C5:C9)</f>
-        <v>181.16249439111709</v>
+        <v>180.32715448149074</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -24166,7 +24166,7 @@
       </c>
       <c r="C11" s="135">
         <f ca="1">Overview!C5</f>
-        <v>143.51</v>
+        <v>142.62</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -24175,7 +24175,7 @@
       </c>
       <c r="C12" s="154">
         <f ca="1">(C10-C11)/C11</f>
-        <v>0.26236843698081741</v>
+        <v>0.26438896705574766</v>
       </c>
     </row>
   </sheetData>
@@ -24231,37 +24231,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="255" t="s">
+      <c r="C2" s="258" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="255"/>
-      <c r="E2" s="255"/>
-      <c r="F2" s="255"/>
-      <c r="G2" s="267"/>
-      <c r="H2" s="268" t="s">
+      <c r="D2" s="258"/>
+      <c r="E2" s="258"/>
+      <c r="F2" s="258"/>
+      <c r="G2" s="264"/>
+      <c r="H2" s="265" t="s">
         <v>114</v>
       </c>
-      <c r="I2" s="255"/>
-      <c r="J2" s="255"/>
-      <c r="K2" s="255"/>
-      <c r="L2" s="255"/>
+      <c r="I2" s="258"/>
+      <c r="J2" s="258"/>
+      <c r="K2" s="258"/>
+      <c r="L2" s="258"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="264" t="s">
+      <c r="C4" s="266" t="s">
         <v>198</v>
       </c>
-      <c r="D4" s="264"/>
-      <c r="E4" s="264"/>
-      <c r="F4" s="264"/>
-      <c r="G4" s="264"/>
-      <c r="H4" s="264"/>
-      <c r="I4" s="264"/>
-      <c r="J4" s="264"/>
-      <c r="K4" s="264"/>
-      <c r="L4" s="264"/>
+      <c r="D4" s="266"/>
+      <c r="E4" s="266"/>
+      <c r="F4" s="266"/>
+      <c r="G4" s="266"/>
+      <c r="H4" s="266"/>
+      <c r="I4" s="266"/>
+      <c r="J4" s="266"/>
+      <c r="K4" s="266"/>
+      <c r="L4" s="266"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -24374,18 +24374,18 @@
       <c r="N8" s="92"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C9" s="264" t="s">
+      <c r="C9" s="266" t="s">
         <v>122</v>
       </c>
-      <c r="D9" s="264"/>
-      <c r="E9" s="264"/>
-      <c r="F9" s="264"/>
-      <c r="G9" s="264"/>
-      <c r="H9" s="264"/>
-      <c r="I9" s="264"/>
-      <c r="J9" s="264"/>
-      <c r="K9" s="264"/>
-      <c r="L9" s="264"/>
+      <c r="D9" s="266"/>
+      <c r="E9" s="266"/>
+      <c r="F9" s="266"/>
+      <c r="G9" s="266"/>
+      <c r="H9" s="266"/>
+      <c r="I9" s="266"/>
+      <c r="J9" s="266"/>
+      <c r="K9" s="266"/>
+      <c r="L9" s="266"/>
       <c r="N9" s="92"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -24506,18 +24506,18 @@
       <c r="N13" s="92"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C14" s="264" t="s">
+      <c r="C14" s="266" t="s">
         <v>413</v>
       </c>
-      <c r="D14" s="264"/>
-      <c r="E14" s="264"/>
-      <c r="F14" s="264"/>
-      <c r="G14" s="264"/>
-      <c r="H14" s="264"/>
-      <c r="I14" s="264"/>
-      <c r="J14" s="264"/>
-      <c r="K14" s="264"/>
-      <c r="L14" s="264"/>
+      <c r="D14" s="266"/>
+      <c r="E14" s="266"/>
+      <c r="F14" s="266"/>
+      <c r="G14" s="266"/>
+      <c r="H14" s="266"/>
+      <c r="I14" s="266"/>
+      <c r="J14" s="266"/>
+      <c r="K14" s="266"/>
+      <c r="L14" s="266"/>
       <c r="N14" s="92"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
@@ -24607,10 +24607,10 @@
       <c r="N19" s="92"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B20" s="255" t="s">
+      <c r="B20" s="258" t="s">
         <v>415</v>
       </c>
-      <c r="C20" s="255"/>
+      <c r="C20" s="258"/>
       <c r="N20" s="92"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
@@ -24645,7 +24645,7 @@
       </c>
       <c r="C24" s="137">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>9.8923499999999998E-2</v>
+        <v>9.9830000000000002E-2</v>
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
@@ -24712,20 +24712,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="255" t="s">
+      <c r="C3" s="258" t="s">
         <v>113</v>
       </c>
-      <c r="D3" s="255"/>
-      <c r="E3" s="255"/>
-      <c r="F3" s="255"/>
-      <c r="G3" s="267"/>
-      <c r="H3" s="268" t="s">
+      <c r="D3" s="258"/>
+      <c r="E3" s="258"/>
+      <c r="F3" s="258"/>
+      <c r="G3" s="264"/>
+      <c r="H3" s="265" t="s">
         <v>114</v>
       </c>
-      <c r="I3" s="255"/>
-      <c r="J3" s="255"/>
-      <c r="K3" s="255"/>
-      <c r="L3" s="255"/>
+      <c r="I3" s="258"/>
+      <c r="J3" s="258"/>
+      <c r="K3" s="258"/>
+      <c r="L3" s="258"/>
       <c r="P3" s="269"/>
       <c r="Q3" s="269"/>
       <c r="R3" s="269"/>
@@ -24743,18 +24743,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="87"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="264" t="s">
+      <c r="C5" s="266" t="s">
         <v>184</v>
       </c>
-      <c r="D5" s="264"/>
-      <c r="E5" s="264"/>
-      <c r="F5" s="264"/>
-      <c r="G5" s="264"/>
-      <c r="H5" s="264"/>
-      <c r="I5" s="264"/>
-      <c r="J5" s="264"/>
-      <c r="K5" s="264"/>
-      <c r="L5" s="264"/>
+      <c r="D5" s="266"/>
+      <c r="E5" s="266"/>
+      <c r="F5" s="266"/>
+      <c r="G5" s="266"/>
+      <c r="H5" s="266"/>
+      <c r="I5" s="266"/>
+      <c r="J5" s="266"/>
+      <c r="K5" s="266"/>
+      <c r="L5" s="266"/>
       <c r="P5" s="269"/>
       <c r="Q5" s="269"/>
       <c r="R5" s="269"/>
@@ -24900,7 +24900,7 @@
       <c r="K8" s="139"/>
       <c r="L8" s="128">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>6529202.5544893574</v>
+        <v>6455060.9771920424</v>
       </c>
       <c r="N8" s="92"/>
       <c r="O8" s="16"/>
@@ -24954,23 +24954,23 @@
       <c r="G10" s="140"/>
       <c r="H10" s="128">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>176719.29168354353</v>
+        <v>176573.63641144588</v>
       </c>
       <c r="I10" s="128">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>204230.32216355397</v>
+        <v>203893.80017142306</v>
       </c>
       <c r="J10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>236024.1719716737</v>
+        <v>235441.04654147211</v>
       </c>
       <c r="K10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>272767.57518064324</v>
+        <v>271869.40627885179</v>
       </c>
       <c r="L10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>315231.06065109809</v>
+        <v>313934.10433807201</v>
       </c>
       <c r="N10" s="92"/>
     </row>
@@ -24989,15 +24989,15 @@
       <c r="K11" s="139"/>
       <c r="L11" s="128">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>4074017.0147563154</v>
+        <v>4011183.5954507506</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="270" t="s">
+      <c r="B14" s="271" t="s">
         <v>226</v>
       </c>
-      <c r="C14" s="271"/>
+      <c r="C14" s="272"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="155" t="s">
@@ -25005,7 +25005,7 @@
       </c>
       <c r="C15" s="156">
         <f ca="1">Overview!C5</f>
-        <v>143.51</v>
+        <v>142.62</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -25014,7 +25014,7 @@
       </c>
       <c r="C16" s="156">
         <f ca="1">C36</f>
-        <v>143.11008499138265</v>
+        <v>141.69740070089375</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -25024,20 +25024,20 @@
       <c r="C17" s="158">
         <v>0.27</v>
       </c>
-      <c r="E17" s="272" t="s">
+      <c r="E17" s="270" t="s">
         <v>229</v>
       </c>
-      <c r="F17" s="272"/>
-      <c r="G17" s="272"/>
-      <c r="H17" s="272"/>
-      <c r="I17" s="272"/>
+      <c r="F17" s="270"/>
+      <c r="G17" s="270"/>
+      <c r="H17" s="270"/>
+      <c r="I17" s="270"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="270" t="s">
+      <c r="B19" s="271" t="s">
         <v>188</v>
       </c>
-      <c r="C19" s="271"/>
+      <c r="C19" s="272"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="159" t="s">
@@ -25053,7 +25053,7 @@
       </c>
       <c r="C21" s="221">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>9.8923499999999998E-2</v>
+        <v>9.9830000000000002E-2</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -25071,7 +25071,7 @@
       </c>
       <c r="C23" s="161">
         <f ca="1">C15*C22</f>
-        <v>6714258.8599999994</v>
+        <v>6672619.3200000003</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -25098,15 +25098,15 @@
       </c>
       <c r="C26" s="162">
         <f ca="1">C23+C25-C24</f>
-        <v>5297699.8599999994</v>
+        <v>5256060.32</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="270" t="s">
+      <c r="B28" s="271" t="s">
         <v>190</v>
       </c>
-      <c r="C28" s="271"/>
+      <c r="C28" s="272"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="159" t="s">
@@ -25114,7 +25114,7 @@
       </c>
       <c r="C29" s="161">
         <f ca="1">SUM(H10:L10)</f>
-        <v>1204972.4216505126</v>
+        <v>1201711.9937412648</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -25123,7 +25123,7 @@
       </c>
       <c r="C30" s="161">
         <f ca="1">L11</f>
-        <v>4074017.0147563154</v>
+        <v>4011183.5954507506</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -25132,7 +25132,7 @@
       </c>
       <c r="C31" s="164">
         <f ca="1">C29+C30</f>
-        <v>5278989.4364068285</v>
+        <v>5212895.5891920151</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -25159,7 +25159,7 @@
       </c>
       <c r="C34" s="164">
         <f ca="1">C31+C32-C33</f>
-        <v>6695548.4364068285</v>
+        <v>6629454.5891920151</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.2">
@@ -25177,21 +25177,21 @@
       </c>
       <c r="C36" s="167">
         <f ca="1">C34/C35</f>
-        <v>143.11008499138265</v>
+        <v>141.69740070089375</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
+    <mergeCell ref="B14:C14"/>
     <mergeCell ref="E17:I17"/>
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
-    <mergeCell ref="B14:C14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -31883,7 +31883,7 @@
       </c>
       <c r="AC116" s="63">
         <f ca="1">Overview!C5</f>
-        <v>143.51</v>
+        <v>142.62</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -31954,7 +31954,7 @@
       </c>
       <c r="AC117" s="65">
         <f ca="1">AC116/AC85</f>
-        <v>143.51</v>
+        <v>142.62</v>
       </c>
     </row>
     <row r="119" spans="1:31" x14ac:dyDescent="0.2">
@@ -33064,7 +33064,7 @@
       <c r="AA146" s="49"/>
       <c r="AC146" s="72">
         <f ca="1">AC117/Statement!AC26</f>
-        <v>45.695134992914923</v>
+        <v>45.411749374186655</v>
       </c>
     </row>
     <row r="147" spans="2:29" x14ac:dyDescent="0.2">
@@ -33101,7 +33101,7 @@
       <c r="AA147" s="49"/>
       <c r="AC147" s="72">
         <f ca="1">AC117/(Statement!AC5/Statement!AC22)</f>
-        <v>6.1629613196952269</v>
+        <v>6.1247407387285442</v>
       </c>
     </row>
     <row r="148" spans="2:29" x14ac:dyDescent="0.2">
@@ -33162,7 +33162,7 @@
       </c>
       <c r="AC148" s="72">
         <f ca="1">AC117/(Statement!AC49/Statement!AC75)</f>
-        <v>4.7627571995443132</v>
+        <v>4.7332202062505058</v>
       </c>
     </row>
     <row r="149" spans="2:29" x14ac:dyDescent="0.2">
@@ -33223,7 +33223,7 @@
       </c>
       <c r="AC149" s="143">
         <f ca="1">Statement!AC117*Statement!AC78</f>
-        <v>7193008.2199999997</v>
+        <v>7148399.6400000006</v>
       </c>
     </row>
     <row r="150" spans="2:29" x14ac:dyDescent="0.2">
@@ -33284,7 +33284,7 @@
       </c>
       <c r="AC150" s="143">
         <f ca="1">AC149+AC108-AC107+AC48+AC45</f>
-        <v>5776449.2199999997</v>
+        <v>5731840.6400000006</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -33321,7 +33321,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="182">
         <f ca="1">AC150/AC5</f>
-        <v>5.0449250044978085</v>
+        <v>5.0059656140338626</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -33358,7 +33358,7 @@
       <c r="AA152" s="49"/>
       <c r="AC152" s="182">
         <f ca="1">AC150/AC12</f>
-        <v>36.772761371232136</v>
+        <v>36.488784034121657</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -33493,7 +33493,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="72">
         <f t="shared" ref="AC155:AC156" ca="1" si="151">AC149/AC153</f>
-        <v>28.451104422118501</v>
+        <v>28.274660390791869</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -33530,7 +33530,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="72">
         <f t="shared" ca="1" si="151"/>
-        <v>34.645256439306252</v>
+        <v>34.377708740948179</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -33567,7 +33567,7 @@
       <c r="AA157" s="49"/>
       <c r="AC157" s="74">
         <f t="shared" ref="AC157" ca="1" si="154">AC153/AC149</f>
-        <v>3.514802044811232E-2</v>
+        <v>3.5367356713704938E-2</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
@@ -33604,7 +33604,7 @@
       <c r="AA158" s="49"/>
       <c r="AC158" s="74">
         <f ca="1">AC26/AC117</f>
-        <v>2.1884167759982566E-2</v>
+        <v>2.2020732823132085E-2</v>
       </c>
     </row>
     <row r="159" spans="2:29" x14ac:dyDescent="0.2">
@@ -33678,7 +33678,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="154">
         <f ca="1">-AC63/AC149</f>
-        <v>9.6764799748831655E-3</v>
+        <v>9.7368646837433948E-3</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -33715,7 +33715,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="154">
         <f ca="1">-(AC63+AC64)/AC149</f>
-        <v>9.6764799748831655E-3</v>
+        <v>9.7368646837433948E-3</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -34218,7 +34218,7 @@
       <c r="AA172" s="49"/>
       <c r="AC172" s="154">
         <f ca="1">(AC107-AC108)/AC149</f>
-        <v>0.19693554583481346</v>
+        <v>0.19816449433988276</v>
       </c>
     </row>
     <row r="173" spans="2:29" x14ac:dyDescent="0.2">
@@ -36140,15 +36140,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="255" t="s">
+      <c r="B4" s="258" t="s">
         <v>237</v>
       </c>
-      <c r="C4" s="255"/>
-      <c r="E4" s="255" t="s">
+      <c r="C4" s="258"/>
+      <c r="E4" s="258" t="s">
         <v>244</v>
       </c>
-      <c r="F4" s="255"/>
-      <c r="G4" s="255"/>
+      <c r="F4" s="258"/>
+      <c r="G4" s="258"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -36156,7 +36156,7 @@
       </c>
       <c r="C5" s="171">
         <f ca="1">Overview!C5</f>
-        <v>143.51</v>
+        <v>142.62</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="134" t="s">
@@ -36172,7 +36172,7 @@
       </c>
       <c r="C6" s="172">
         <f ca="1">Statement!AC149</f>
-        <v>7193008.2199999997</v>
+        <v>7148399.6400000006</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>20</v>
@@ -36192,7 +36192,7 @@
       </c>
       <c r="C7" s="172">
         <f ca="1">Statement!AC150</f>
-        <v>5776449.2199999997</v>
+        <v>5731840.6400000006</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>32</v>
@@ -36212,7 +36212,7 @@
       </c>
       <c r="C8" s="173">
         <f ca="1">Statement!AC146</f>
-        <v>45.695134992914923</v>
+        <v>45.411749374186655</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>247</v>
@@ -36232,7 +36232,7 @@
       </c>
       <c r="C9" s="173">
         <f ca="1">Statement!AC147</f>
-        <v>6.1629613196952269</v>
+        <v>6.1247407387285442</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>248</v>
@@ -36252,7 +36252,7 @@
       </c>
       <c r="C10" s="173">
         <f ca="1">Statement!AC148</f>
-        <v>4.7627571995443132</v>
+        <v>4.7332202062505058</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -36272,7 +36272,7 @@
       </c>
       <c r="C11" s="173">
         <f ca="1">Statement!AC151</f>
-        <v>5.0449250044978085</v>
+        <v>5.0059656140338626</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -36281,18 +36281,18 @@
       </c>
       <c r="C12" s="173">
         <f ca="1">Statement!AC152</f>
-        <v>36.772761371232136</v>
+        <v>36.488784034121657</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="255" t="s">
+      <c r="B15" s="258" t="s">
         <v>78</v>
       </c>
-      <c r="C15" s="255"/>
-      <c r="E15" s="255" t="s">
+      <c r="C15" s="258"/>
+      <c r="E15" s="258" t="s">
         <v>250</v>
       </c>
-      <c r="F15" s="255"/>
+      <c r="F15" s="258"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -36343,14 +36343,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="255" t="s">
+      <c r="B21" s="258" t="s">
         <v>249</v>
       </c>
-      <c r="C21" s="255"/>
-      <c r="E21" s="255" t="s">
+      <c r="C21" s="258"/>
+      <c r="E21" s="258" t="s">
         <v>253</v>
       </c>
-      <c r="F21" s="255"/>
+      <c r="F21" s="258"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -36419,14 +36419,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="255" t="s">
+      <c r="B29" s="258" t="s">
         <v>254</v>
       </c>
-      <c r="C29" s="255"/>
-      <c r="E29" s="255" t="s">
+      <c r="C29" s="258"/>
+      <c r="E29" s="258" t="s">
         <v>260</v>
       </c>
-      <c r="F29" s="255"/>
+      <c r="F29" s="258"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -36502,14 +36502,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="255" t="s">
+      <c r="B37" s="258" t="s">
         <v>272</v>
       </c>
-      <c r="C37" s="255"/>
-      <c r="E37" s="255" t="s">
+      <c r="C37" s="258"/>
+      <c r="E37" s="258" t="s">
         <v>275</v>
       </c>
-      <c r="F37" s="255"/>
+      <c r="F37" s="258"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -36517,7 +36517,7 @@
       </c>
       <c r="C38" s="174">
         <f ca="1">Statement!AC158</f>
-        <v>2.1884167759982566E-2</v>
+        <v>2.2020732823132085E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>274</v>
@@ -36533,7 +36533,7 @@
       </c>
       <c r="C39" s="214">
         <f ca="1">Statement!AC157</f>
-        <v>3.514802044811232E-2</v>
+        <v>3.5367356713704938E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>276</v>
@@ -36565,7 +36565,7 @@
       </c>
       <c r="C41" s="174">
         <f ca="1">Statement!AC160</f>
-        <v>9.6764799748831655E-3</v>
+        <v>9.7368646837433948E-3</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -36574,18 +36574,18 @@
       </c>
       <c r="C42" s="174">
         <f ca="1">Statement!AC161</f>
-        <v>9.6764799748831655E-3</v>
+        <v>9.7368646837433948E-3</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="255" t="s">
+      <c r="B45" s="258" t="s">
         <v>283</v>
       </c>
-      <c r="C45" s="255"/>
-      <c r="E45" s="255" t="s">
+      <c r="C45" s="258"/>
+      <c r="E45" s="258" t="s">
         <v>289</v>
       </c>
-      <c r="F45" s="255"/>
+      <c r="F45" s="258"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -36618,18 +36618,18 @@
       </c>
       <c r="F48" s="174">
         <f ca="1">Statement!AC172</f>
-        <v>0.19693554583481346</v>
+        <v>0.19816449433988276</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="255" t="s">
+      <c r="B51" s="258" t="s">
         <v>286</v>
       </c>
-      <c r="C51" s="255"/>
-      <c r="E51" s="255" t="s">
+      <c r="C51" s="258"/>
+      <c r="E51" s="258" t="s">
         <v>307</v>
       </c>
-      <c r="F51" s="255"/>
+      <c r="F51" s="258"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -36797,7 +36797,7 @@
       </c>
       <c r="I6" s="171">
         <f ca="1">Statement!AC116</f>
-        <v>143.51</v>
+        <v>142.62</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -36826,7 +36826,7 @@
       </c>
       <c r="I7" s="172">
         <f ca="1">Statement!AC149</f>
-        <v>7193008.2199999997</v>
+        <v>7148399.6400000006</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -36855,7 +36855,7 @@
       </c>
       <c r="I8" s="172">
         <f ca="1">Statement!AC150</f>
-        <v>5776449.2199999997</v>
+        <v>5731840.6400000006</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -36884,7 +36884,7 @@
       </c>
       <c r="I9" s="173">
         <f ca="1">Statement!AC146</f>
-        <v>45.695134992914923</v>
+        <v>45.411749374186655</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -36913,7 +36913,7 @@
       </c>
       <c r="I10" s="173">
         <f ca="1">Statement!AC147</f>
-        <v>6.1629613196952269</v>
+        <v>6.1247407387285442</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -36942,7 +36942,7 @@
       </c>
       <c r="I11" s="173">
         <f ca="1">Statement!AC148</f>
-        <v>4.7627571995443132</v>
+        <v>4.7332202062505058</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -36971,7 +36971,7 @@
       </c>
       <c r="I12" s="173">
         <f ca="1">Statement!AC151</f>
-        <v>5.0449250044978085</v>
+        <v>5.0059656140338626</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -37000,7 +37000,7 @@
       </c>
       <c r="I13" s="173">
         <f ca="1">Statement!AC152</f>
-        <v>36.772761371232136</v>
+        <v>36.488784034121657</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -37773,7 +37773,7 @@
       </c>
       <c r="I51" s="174">
         <f ca="1">Statement!AC158</f>
-        <v>2.1884167759982566E-2</v>
+        <v>2.2020732823132085E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -37802,7 +37802,7 @@
       </c>
       <c r="I52" s="174">
         <f ca="1">Statement!AC157</f>
-        <v>3.514802044811232E-2</v>
+        <v>3.5367356713704938E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -37860,7 +37860,7 @@
       </c>
       <c r="I54" s="174">
         <f ca="1">Statement!AC160</f>
-        <v>9.6764799748831655E-3</v>
+        <v>9.7368646837433948E-3</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -37889,7 +37889,7 @@
       </c>
       <c r="I55" s="174">
         <f ca="1">Statement!AC161</f>
-        <v>9.6764799748831655E-3</v>
+        <v>9.7368646837433948E-3</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -38125,7 +38125,7 @@
       </c>
       <c r="I68" s="195">
         <f ca="1">Statement!AC172</f>
-        <v>0.19693554583481346</v>
+        <v>0.19816449433988276</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -38668,14 +38668,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="259" t="s">
+      <c r="C3" s="261" t="s">
         <v>317</v>
       </c>
-      <c r="D3" s="260"/>
-      <c r="F3" s="261" t="s">
+      <c r="D3" s="262"/>
+      <c r="F3" s="263" t="s">
         <v>318</v>
       </c>
-      <c r="G3" s="260"/>
+      <c r="G3" s="262"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -38742,19 +38742,19 @@
       <c r="B7" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C7" s="262">
+      <c r="C7" s="259">
         <f>Statement!AA89</f>
         <v>2.2218264392893719E-2</v>
       </c>
-      <c r="D7" s="263"/>
-      <c r="F7" s="262">
+      <c r="D7" s="260"/>
+      <c r="F7" s="259">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.18309713991239371</v>
       </c>
-      <c r="G7" s="263"/>
+      <c r="G7" s="260"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="206" t="s">
@@ -38781,19 +38781,19 @@
       <c r="B9" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C9" s="262">
+      <c r="C9" s="259">
         <f>Statement!AA90</f>
         <v>3.6046202026093238E-2</v>
       </c>
-      <c r="D9" s="263"/>
-      <c r="F9" s="262">
+      <c r="D9" s="260"/>
+      <c r="F9" s="259">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.17263647322197348</v>
       </c>
-      <c r="G9" s="263"/>
+      <c r="G9" s="260"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="206" t="s">
@@ -38820,19 +38820,19 @@
       <c r="B11" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C11" s="262">
+      <c r="C11" s="259">
         <f>Statement!AA91</f>
         <v>1.710027405488606E-2</v>
       </c>
-      <c r="D11" s="263"/>
-      <c r="F11" s="262">
+      <c r="D11" s="260"/>
+      <c r="F11" s="259">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>0.1870895657269924</v>
       </c>
-      <c r="G11" s="263"/>
+      <c r="G11" s="260"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="206" t="s">
@@ -38859,19 +38859,19 @@
       <c r="B13" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C13" s="262">
+      <c r="C13" s="259">
         <f>Statement!AA95</f>
         <v>8.4392741251357012E-2</v>
       </c>
-      <c r="D13" s="263"/>
-      <c r="F13" s="262">
+      <c r="D13" s="260"/>
+      <c r="F13" s="259">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.22501976973287405</v>
       </c>
-      <c r="G13" s="263"/>
+      <c r="G13" s="260"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="206" t="s">
@@ -38898,19 +38898,19 @@
       <c r="B15" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C15" s="262">
+      <c r="C15" s="259">
         <f>Statement!AA96</f>
         <v>-0.23765355851505829</v>
       </c>
-      <c r="D15" s="263"/>
-      <c r="F15" s="262">
+      <c r="D15" s="260"/>
+      <c r="F15" s="259">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>1.7444474417768186E-2</v>
       </c>
-      <c r="G15" s="263"/>
+      <c r="G15" s="260"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="206" t="s">
@@ -38937,19 +38937,19 @@
       <c r="B17" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C17" s="262">
+      <c r="C17" s="259">
         <f>Statement!AA98</f>
         <v>-0.23704555913483663</v>
       </c>
-      <c r="D17" s="263"/>
-      <c r="F17" s="262">
+      <c r="D17" s="260"/>
+      <c r="F17" s="259">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>-0.25955204216073779</v>
       </c>
-      <c r="G17" s="263"/>
+      <c r="G17" s="260"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="206" t="s">
@@ -38976,22 +38976,22 @@
       <c r="B19" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C19" s="262">
+      <c r="C19" s="259">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>2.5565842762241744E-2</v>
       </c>
-      <c r="D19" s="263"/>
-      <c r="F19" s="262">
+      <c r="D19" s="260"/>
+      <c r="F19" s="259">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>2.5293753865182372E-2</v>
       </c>
-      <c r="G19" s="263"/>
+      <c r="G19" s="260"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="206" t="s">
@@ -39018,22 +39018,22 @@
       <c r="B21" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C21" s="262">
+      <c r="C21" s="259">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>-0.2584269662921348</v>
       </c>
-      <c r="D21" s="263"/>
-      <c r="F21" s="262">
+      <c r="D21" s="260"/>
+      <c r="F21" s="259">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>-0.27472527472527469</v>
       </c>
-      <c r="G21" s="263"/>
+      <c r="G21" s="260"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -39082,22 +39082,22 @@
       <c r="B25" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C25" s="262">
+      <c r="C25" s="259">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>2.840483364420425E-2</v>
       </c>
-      <c r="D25" s="263"/>
-      <c r="F25" s="262">
+      <c r="D25" s="260"/>
+      <c r="F25" s="259">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>0.22478379327694395</v>
       </c>
-      <c r="G25" s="263"/>
+      <c r="G25" s="260"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="str">
@@ -39125,22 +39125,22 @@
       <c r="B27" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C27" s="262">
+      <c r="C27" s="259">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>2.1247695740758708E-2</v>
       </c>
-      <c r="D27" s="263"/>
-      <c r="F27" s="262">
+      <c r="D27" s="260"/>
+      <c r="F27" s="259">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>2.1792942775323981E-2</v>
       </c>
-      <c r="G27" s="263"/>
+      <c r="G27" s="260"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="str">
@@ -39168,22 +39168,22 @@
       <c r="B29" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C29" s="262">
+      <c r="C29" s="259">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>-0.10674206945303526</v>
       </c>
-      <c r="D29" s="263"/>
-      <c r="F29" s="262">
+      <c r="D29" s="260"/>
+      <c r="F29" s="259">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>2.0816812053925456E-3</v>
       </c>
-      <c r="G29" s="263"/>
+      <c r="G29" s="260"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="str">
@@ -39211,22 +39211,22 @@
       <c r="B31" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C31" s="262">
+      <c r="C31" s="259">
         <f>IF(C30=0,
 IF(D30=0,0,IF(D30&gt;0,1,-1)),
 (D30-C30)/ABS(C30)
 )</f>
         <v>-5.2569263556713236E-2</v>
       </c>
-      <c r="D31" s="263"/>
-      <c r="F31" s="262">
+      <c r="D31" s="260"/>
+      <c r="F31" s="259">
         <f>IF(F30=0,
 IF(G30=0,0,IF(G30&gt;0,1,-1)),
 (G30-F30)/ABS(F30)
 )</f>
         <v>-0.22983638113570742</v>
       </c>
-      <c r="G31" s="263"/>
+      <c r="G31" s="260"/>
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B32" s="20" t="str">
@@ -39254,22 +39254,22 @@
       <c r="B33" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C33" s="262">
+      <c r="C33" s="259">
         <f>IF(C32=0,
 IF(D32=0,0,IF(D32&gt;0,1,-1)),
 (D32-C32)/ABS(C32)
 )</f>
         <v>0.84164222873900296</v>
       </c>
-      <c r="D33" s="263"/>
-      <c r="F33" s="262">
+      <c r="D33" s="260"/>
+      <c r="F33" s="259">
         <f>IF(F32=0,
 IF(G32=0,0,IF(G32&gt;0,1,-1)),
 (G32-F32)/ABS(F32)
 )</f>
         <v>1.482213438735178</v>
       </c>
-      <c r="G33" s="263"/>
+      <c r="G33" s="260"/>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B35" s="8" t="s">
@@ -39318,22 +39318,22 @@
       <c r="B37" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C37" s="262">
+      <c r="C37" s="259">
         <f>IF(C36=0,
 IF(D36=0,0,IF(D36&gt;0,1,-1)),
 (D36-C36)/ABS(C36)
 )</f>
         <v>3.8938053097345132E-2</v>
       </c>
-      <c r="D37" s="263"/>
-      <c r="F37" s="262">
+      <c r="D37" s="260"/>
+      <c r="F37" s="259">
         <f>IF(F36=0,
 IF(G36=0,0,IF(G36&gt;0,1,-1)),
 (G36-F36)/ABS(F36)
 )</f>
         <v>0.23060796645702306</v>
       </c>
-      <c r="G37" s="263"/>
+      <c r="G37" s="260"/>
     </row>
     <row r="38" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="str">
@@ -39361,22 +39361,22 @@
       <c r="B39" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C39" s="262">
+      <c r="C39" s="259">
         <f>IF(C38=0,
 IF(D38=0,0,IF(D38&gt;0,1,-1)),
 (D38-C38)/ABS(C38)
 )</f>
         <v>2.0319303338171262E-2</v>
       </c>
-      <c r="D39" s="263"/>
-      <c r="F39" s="262">
+      <c r="D39" s="260"/>
+      <c r="F39" s="259">
         <f>IF(F38=0,
 IF(G38=0,0,IF(G38&gt;0,1,-1)),
 (G38-F38)/ABS(F38)
 )</f>
         <v>9.5869056897895558E-2</v>
       </c>
-      <c r="G39" s="263"/>
+      <c r="G39" s="260"/>
     </row>
     <row r="40" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B40" s="20" t="str">
@@ -39404,22 +39404,22 @@
       <c r="B41" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C41" s="262">
+      <c r="C41" s="259">
         <f>IF(C40=0,
 IF(D40=0,0,IF(D40&gt;0,1,-1)),
 (D40-C40)/ABS(C40)
 )</f>
         <v>1.6E-2</v>
       </c>
-      <c r="D41" s="263"/>
-      <c r="F41" s="262">
+      <c r="D41" s="260"/>
+      <c r="F41" s="259">
         <f>IF(F40=0,
 IF(G40=0,0,IF(G40&gt;0,1,-1)),
 (G40-F40)/ABS(F40)
 )</f>
         <v>0.16513761467889909</v>
       </c>
-      <c r="G41" s="263"/>
+      <c r="G41" s="260"/>
     </row>
     <row r="42" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B42" s="20" t="str">
@@ -39447,22 +39447,22 @@
       <c r="B43" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C43" s="262">
+      <c r="C43" s="259">
         <f>IF(C42=0,
 IF(D42=0,0,IF(D42&gt;0,1,-1)),
 (D42-C42)/ABS(C42)
 )</f>
         <v>2.0750199521149242E-2</v>
       </c>
-      <c r="D43" s="263"/>
-      <c r="F43" s="262">
+      <c r="D43" s="260"/>
+      <c r="F43" s="259">
         <f>IF(F42=0,
 IF(G42=0,0,IF(G42&gt;0,1,-1)),
 (G42-F42)/ABS(F42)
 )</f>
         <v>8.9437819420783646E-2</v>
       </c>
-      <c r="G43" s="263"/>
+      <c r="G43" s="260"/>
     </row>
     <row r="44" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B44" s="20" t="str">
@@ -39490,22 +39490,22 @@
       <c r="B45" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C45" s="262">
+      <c r="C45" s="259">
         <f>IF(C44=0,
 IF(D44=0,0,IF(D44&gt;0,1,-1)),
 (D44-C44)/ABS(C44)
 )</f>
         <v>1.2209481933271921E-2</v>
       </c>
-      <c r="D45" s="263"/>
-      <c r="F45" s="262">
+      <c r="D45" s="260"/>
+      <c r="F45" s="259">
         <f>IF(F44=0,
 IF(G44=0,0,IF(G44&gt;0,1,-1)),
 (G44-F44)/ABS(F44)
 )</f>
         <v>5.119238950540856E-2</v>
       </c>
-      <c r="G45" s="263"/>
+      <c r="G45" s="260"/>
     </row>
     <row r="46" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="str">
@@ -39533,22 +39533,22 @@
       <c r="B47" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C47" s="262">
+      <c r="C47" s="259">
         <f>IF(C46=0,
 IF(D46=0,0,IF(D46&gt;0,1,-1)),
 (D46-C46)/ABS(C46)
 )</f>
         <v>1.8247963846473435E-2</v>
       </c>
-      <c r="D47" s="263"/>
-      <c r="F47" s="262">
+      <c r="D47" s="260"/>
+      <c r="F47" s="259">
         <f>IF(F46=0,
 IF(G46=0,0,IF(G46&gt;0,1,-1)),
 (G46-F46)/ABS(F46)
 )</f>
         <v>0.1229516507570132</v>
       </c>
-      <c r="G47" s="263"/>
+      <c r="G47" s="260"/>
     </row>
     <row r="48" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B48" s="20" t="str">
@@ -39576,22 +39576,22 @@
       <c r="B49" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C49" s="262">
+      <c r="C49" s="259">
         <f>IF(C48=0,
 IF(D48=0,0,IF(D48&gt;0,1,-1)),
 (D48-C48)/ABS(C48)
 )</f>
         <v>-4.2332859174963834E-3</v>
       </c>
-      <c r="D49" s="263"/>
-      <c r="F49" s="262">
+      <c r="D49" s="260"/>
+      <c r="F49" s="259">
         <f>IF(F48=0,
 IF(G48=0,0,IF(G48&gt;0,1,-1)),
 (G48-F48)/ABS(F48)
 )</f>
         <v>6.3208790635154666E-2</v>
       </c>
-      <c r="G49" s="263"/>
+      <c r="G49" s="260"/>
     </row>
     <row r="50" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B50" s="20" t="str">
@@ -39619,22 +39619,22 @@
       <c r="B51" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C51" s="262">
+      <c r="C51" s="259">
         <f>IF(C50=0,
 IF(D50=0,0,IF(D50&gt;0,1,-1)),
 (D50-C50)/ABS(C50)
 )</f>
         <v>4.8738292663854846E-4</v>
       </c>
-      <c r="D51" s="263"/>
-      <c r="F51" s="262">
+      <c r="D51" s="260"/>
+      <c r="F51" s="259">
         <f>IF(F50=0,
 IF(G50=0,0,IF(G50&gt;0,1,-1)),
 (G50-F50)/ABS(F50)
 )</f>
         <v>-6.2091544317255373E-2</v>
       </c>
-      <c r="G51" s="263"/>
+      <c r="G51" s="260"/>
     </row>
     <row r="52" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="str">
@@ -39662,39 +39662,43 @@
       <c r="B53" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C53" s="262">
+      <c r="C53" s="259">
         <f>IF(C52=0,
 IF(D52=0,0,IF(D52&gt;0,1,-1)),
 (D52-C52)/ABS(C52)
 )</f>
         <v>-8.8077740902117604E-2</v>
       </c>
-      <c r="D53" s="263"/>
-      <c r="F53" s="262">
+      <c r="D53" s="260"/>
+      <c r="F53" s="259">
         <f>IF(F52=0,
 IF(G52=0,0,IF(G52&gt;0,1,-1)),
 (G52-F52)/ABS(F52)
 )</f>
         <v>-0.37416005758387127</v>
       </c>
-      <c r="G53" s="263"/>
+      <c r="G53" s="260"/>
     </row>
   </sheetData>
   <mergeCells count="46">
-    <mergeCell ref="C53:D53"/>
-    <mergeCell ref="F53:G53"/>
-    <mergeCell ref="C47:D47"/>
-    <mergeCell ref="F47:G47"/>
-    <mergeCell ref="C49:D49"/>
-    <mergeCell ref="F49:G49"/>
-    <mergeCell ref="C51:D51"/>
-    <mergeCell ref="F51:G51"/>
-    <mergeCell ref="C41:D41"/>
-    <mergeCell ref="F41:G41"/>
-    <mergeCell ref="C43:D43"/>
-    <mergeCell ref="F43:G43"/>
-    <mergeCell ref="C45:D45"/>
-    <mergeCell ref="F45:G45"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
     <mergeCell ref="C37:D37"/>
     <mergeCell ref="F37:G37"/>
     <mergeCell ref="C39:D39"/>
@@ -39709,24 +39713,20 @@
     <mergeCell ref="F31:G31"/>
     <mergeCell ref="C33:D33"/>
     <mergeCell ref="F33:G33"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="F41:G41"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="F43:G43"/>
+    <mergeCell ref="C45:D45"/>
+    <mergeCell ref="F45:G45"/>
+    <mergeCell ref="C53:D53"/>
+    <mergeCell ref="F53:G53"/>
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="F47:G47"/>
+    <mergeCell ref="C49:D49"/>
+    <mergeCell ref="F49:G49"/>
+    <mergeCell ref="C51:D51"/>
+    <mergeCell ref="F51:G51"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/DUOL.xlsx
+++ b/DUOL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4860B105-9D3D-A84E-85C2-8859E89D4330}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06D2F34A-7CAC-C44C-88A2-44D2F50F88AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" activeTab="2" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -2421,12 +2421,6 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2436,10 +2430,10 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2451,17 +2445,23 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -13157,11 +13157,11 @@
     <v>Powered by Refinitiv</v>
     <v>353</v>
     <v>87.89</v>
-    <v>1.054</v>
-    <v>8.32</v>
-    <v>6.1950999999999999E-2</v>
-    <v>-0.03</v>
-    <v>-2.1029999999999999E-4</v>
+    <v>1.0652999999999999</v>
+    <v>2.83</v>
+    <v>1.9616000000000001E-2</v>
+    <v>-0.6</v>
+    <v>-4.0790000000000002E-3</v>
     <v>USD</v>
     <v>Duolingo, Inc. is a technology company. The Company is engaged in offering a mobile learning platform, as well as a digital English language proficiency assessment exam. It operates a freemium business model, namely, the app and the Website are accessible free of charge, although Duolingo also offers premium services for a subscription fee. Its solutions consist of the Duolingo App, Super Duolingo, Duolingo Max, Duolingo English Test: AI-Driven Language Assessment, Duolingo for Schools, and Duolingo ABC. The Duolingo App offers courses in over 40 different languages, including Spanish, English, French, German, Italian, Portuguese, Japanese and Chinese. Duolingo can also be accessed on desktop computers via a Web browser. Its subscription offering, Super Duolingo, offers learners additional features to enhance their learning experience. The Duolingo English Test is an online, on-demand, high-stakes English proficiency assessment. It also operates an animation and motion design studio.</v>
     <v>900</v>
@@ -13169,25 +13169,25 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>5900 PENN AVE, SECOND FLOOR, PITTSBURGH, PA, 15206 US</v>
-    <v>142.71</v>
+    <v>147.75</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46294.951956226563</v>
+    <v>46300.888250821095</v>
     <v>0</v>
-    <v>134.31</v>
-    <v>6672657827</v>
+    <v>142.51</v>
+    <v>6882260317</v>
     <v>DUOLINGO, INC.</v>
     <v>DUOLINGO, INC.</v>
-    <v>134.44</v>
-    <v>16.008099999999999</v>
-    <v>134.30000000000001</v>
-    <v>142.62</v>
-    <v>142.59</v>
+    <v>144.11000000000001</v>
+    <v>17.1965</v>
+    <v>144.27000000000001</v>
+    <v>147.1</v>
+    <v>146.5</v>
     <v>46786270</v>
     <v>DUOL</v>
     <v>DUOLINGO, INC. (XNAS:DUOL)</v>
-    <v>1067735</v>
-    <v>1139488</v>
+    <v>841329</v>
+    <v>1139471</v>
     <v>2011</v>
   </rv>
   <rv s="2">
@@ -13209,19 +13209,19 @@
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>52.74</v>
+    <v>53.42</v>
     <v>39.47</v>
-    <v>0.56000000000000005</v>
-    <v>1.0802000000000001E-2</v>
+    <v>0.4</v>
+    <v>7.6380000000000007E-3</v>
     <v>US</v>
-    <v>52.74</v>
+    <v>52.98</v>
     <v>Index</v>
     <v>3</v>
-    <v>52.05</v>
+    <v>51.57</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>52.09</v>
-    <v>51.84</v>
-    <v>52.4</v>
+    <v>52.16</v>
+    <v>52.37</v>
+    <v>52.77</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -14042,7 +14042,7 @@
       </c>
       <c r="F3" s="186">
         <f ca="1">Statement!AC149</f>
-        <v>7148399.6400000006</v>
+        <v>7372946.1999999993</v>
       </c>
       <c r="H3" s="184" t="str">
         <f>'AVG target price'!B5</f>
@@ -14050,7 +14050,7 @@
       </c>
       <c r="I3" s="210">
         <f ca="1">'AVG target price'!C5</f>
-        <v>143.26920240823023</v>
+        <v>141.85646777088763</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.2">
@@ -14066,7 +14066,7 @@
       </c>
       <c r="F4" s="187">
         <f ca="1">Statement!AC150</f>
-        <v>5731840.6400000006</v>
+        <v>5956387.1999999993</v>
       </c>
       <c r="H4" s="184" t="str">
         <f>'AVG target price'!B6</f>
@@ -14074,7 +14074,7 @@
       </c>
       <c r="I4" s="210">
         <f ca="1">'AVG target price'!C6</f>
-        <v>196.31682029546766</v>
+        <v>195.67850504708815</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.2">
@@ -14083,7 +14083,7 @@
       </c>
       <c r="C5" s="207" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>142.62</v>
+        <v>147.1</v>
       </c>
       <c r="E5" s="184" t="s">
         <v>247</v>
@@ -14098,7 +14098,7 @@
       </c>
       <c r="I5" s="210">
         <f ca="1">'AVG target price'!C7</f>
-        <v>158.06078335243151</v>
+        <v>157.43103021510453</v>
       </c>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.2">
@@ -14107,14 +14107,14 @@
       </c>
       <c r="C6" s="207" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>142.59</v>
+        <v>146.5</v>
       </c>
       <c r="E6" s="184" t="s">
         <v>241</v>
       </c>
       <c r="F6" s="189">
         <f ca="1">Statement!AC146</f>
-        <v>45.411749374186655</v>
+        <v>46.838229792054811</v>
       </c>
       <c r="H6" s="184" t="str">
         <f>'AVG target price'!B8</f>
@@ -14122,7 +14122,7 @@
       </c>
       <c r="I6" s="210">
         <f ca="1">'AVG target price'!C8</f>
-        <v>201.78552024816062</v>
+        <v>201.12541635063448</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -14131,14 +14131,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>8.32</v>
+        <v>2.83</v>
       </c>
       <c r="E7" s="185" t="s">
         <v>205</v>
       </c>
       <c r="F7" s="190">
         <f ca="1">Statement!AC147</f>
-        <v>6.1247407387285442</v>
+        <v>6.31713197775185</v>
       </c>
       <c r="H7" s="184" t="str">
         <f>'AVG target price'!B9</f>
@@ -14146,7 +14146,7 @@
       </c>
       <c r="I7" s="210">
         <f ca="1">'AVG target price'!C9</f>
-        <v>202.20344610316366</v>
+        <v>201.54167708597421</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -14155,14 +14155,14 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>-0.03</v>
+        <v>-0.6</v>
       </c>
       <c r="E8" s="184" t="s">
         <v>269</v>
       </c>
       <c r="F8" s="191">
         <f ca="1">Statement!AC157</f>
-        <v>3.5367356713704938E-2</v>
+        <v>3.4290227155055059E-2</v>
       </c>
       <c r="H8" s="183" t="str">
         <f>'AVG target price'!B10</f>
@@ -14170,7 +14170,7 @@
       </c>
       <c r="I8" s="211">
         <f ca="1">'AVG target price'!C10</f>
-        <v>180.32715448149074</v>
+        <v>179.52661929393781</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -14179,14 +14179,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>6.1950999999999999E-2</v>
+        <v>1.9616000000000001E-2</v>
       </c>
       <c r="E9" s="184" t="s">
         <v>292</v>
       </c>
       <c r="F9" s="191">
         <f ca="1">Statement!AC158</f>
-        <v>2.2020732823132085E-2</v>
+        <v>2.1350081000918408E-2</v>
       </c>
       <c r="H9" s="183" t="str">
         <f>'AVG target price'!B12</f>
@@ -14194,7 +14194,7 @@
       </c>
       <c r="I9" s="212">
         <f ca="1">'AVG target price'!C12</f>
-        <v>0.26438896705574766</v>
+        <v>0.2204392881980817</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -14203,14 +14203,14 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>-2.1029999999999999E-4</v>
+        <v>-4.0790000000000002E-3</v>
       </c>
       <c r="E10" s="184" t="s">
         <v>297</v>
       </c>
       <c r="F10" s="191">
         <f ca="1">Statement!AC160</f>
-        <v>9.7368646837433948E-3</v>
+        <v>9.4403238694458404E-3</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -14258,7 +14258,7 @@
       </c>
       <c r="C13" s="208" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>1.054</v>
+        <v>1.0652999999999999</v>
       </c>
       <c r="E13" s="184" t="s">
         <v>104</v>
@@ -14281,7 +14281,7 @@
       </c>
       <c r="C14" s="209" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>1139488</v>
+        <v>1139471</v>
       </c>
       <c r="E14" s="185" t="s">
         <v>105</v>
@@ -14297,7 +14297,7 @@
       </c>
       <c r="F15" s="191">
         <f ca="1">Statement!AC172</f>
-        <v>0.19816449433988276</v>
+        <v>0.19212930103843701</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -14407,7 +14407,7 @@
       </c>
       <c r="F26" s="218" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>52.4</v>
+        <v>52.77</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -14422,7 +14422,7 @@
       </c>
       <c r="F27" s="219">
         <f ca="1">F26/1000</f>
-        <v>5.2399999999999995E-2</v>
+        <v>5.2770000000000004E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -14704,8 +14704,8 @@
       <c r="D2" s="258"/>
       <c r="E2" s="258"/>
       <c r="F2" s="258"/>
-      <c r="G2" s="264"/>
-      <c r="H2" s="265" t="s">
+      <c r="G2" s="267"/>
+      <c r="H2" s="268" t="s">
         <v>114</v>
       </c>
       <c r="I2" s="258"/>
@@ -14738,32 +14738,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="266" t="s">
+      <c r="C4" s="264" t="s">
         <v>116</v>
       </c>
-      <c r="D4" s="266"/>
-      <c r="E4" s="266"/>
-      <c r="F4" s="266"/>
-      <c r="G4" s="266"/>
-      <c r="H4" s="266"/>
-      <c r="I4" s="266"/>
-      <c r="J4" s="266"/>
-      <c r="K4" s="266"/>
-      <c r="L4" s="266"/>
+      <c r="D4" s="264"/>
+      <c r="E4" s="264"/>
+      <c r="F4" s="264"/>
+      <c r="G4" s="264"/>
+      <c r="H4" s="264"/>
+      <c r="I4" s="264"/>
+      <c r="J4" s="264"/>
+      <c r="K4" s="264"/>
+      <c r="L4" s="264"/>
       <c r="O4" s="5"/>
-      <c r="S4" s="267" t="s">
+      <c r="S4" s="265" t="s">
         <v>116</v>
       </c>
-      <c r="T4" s="268"/>
-      <c r="U4" s="268"/>
-      <c r="V4" s="268"/>
-      <c r="W4" s="268"/>
-      <c r="X4" s="268"/>
-      <c r="Y4" s="268"/>
-      <c r="Z4" s="268"/>
-      <c r="AA4" s="268"/>
-      <c r="AB4" s="268"/>
-      <c r="AC4" s="268"/>
+      <c r="T4" s="266"/>
+      <c r="U4" s="266"/>
+      <c r="V4" s="266"/>
+      <c r="W4" s="266"/>
+      <c r="X4" s="266"/>
+      <c r="Y4" s="266"/>
+      <c r="Z4" s="266"/>
+      <c r="AA4" s="266"/>
+      <c r="AB4" s="266"/>
+      <c r="AC4" s="266"/>
       <c r="AE4" s="88"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -15451,33 +15451,33 @@
       <c r="Q12" s="92"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="266" t="s">
+      <c r="C13" s="264" t="s">
         <v>122</v>
       </c>
-      <c r="D13" s="266"/>
-      <c r="E13" s="266"/>
-      <c r="F13" s="266"/>
-      <c r="G13" s="266"/>
-      <c r="H13" s="266"/>
-      <c r="I13" s="266"/>
-      <c r="J13" s="266"/>
-      <c r="K13" s="266"/>
-      <c r="L13" s="266"/>
+      <c r="D13" s="264"/>
+      <c r="E13" s="264"/>
+      <c r="F13" s="264"/>
+      <c r="G13" s="264"/>
+      <c r="H13" s="264"/>
+      <c r="I13" s="264"/>
+      <c r="J13" s="264"/>
+      <c r="K13" s="264"/>
+      <c r="L13" s="264"/>
       <c r="O13" s="5"/>
       <c r="Q13" s="92"/>
-      <c r="S13" s="267" t="s">
+      <c r="S13" s="265" t="s">
         <v>122</v>
       </c>
-      <c r="T13" s="268"/>
-      <c r="U13" s="268"/>
-      <c r="V13" s="268"/>
-      <c r="W13" s="268"/>
-      <c r="X13" s="268"/>
-      <c r="Y13" s="268"/>
-      <c r="Z13" s="268"/>
-      <c r="AA13" s="268"/>
-      <c r="AB13" s="268"/>
-      <c r="AC13" s="268"/>
+      <c r="T13" s="266"/>
+      <c r="U13" s="266"/>
+      <c r="V13" s="266"/>
+      <c r="W13" s="266"/>
+      <c r="X13" s="266"/>
+      <c r="Y13" s="266"/>
+      <c r="Z13" s="266"/>
+      <c r="AA13" s="266"/>
+      <c r="AB13" s="266"/>
+      <c r="AC13" s="266"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B14" s="16" t="s">
@@ -16086,33 +16086,33 @@
       <c r="Q22" s="92"/>
     </row>
     <row r="23" spans="2:31" x14ac:dyDescent="0.2">
-      <c r="C23" s="266" t="s">
+      <c r="C23" s="264" t="s">
         <v>124</v>
       </c>
-      <c r="D23" s="266"/>
-      <c r="E23" s="266"/>
-      <c r="F23" s="266"/>
-      <c r="G23" s="266"/>
-      <c r="H23" s="266"/>
-      <c r="I23" s="266"/>
-      <c r="J23" s="266"/>
-      <c r="K23" s="266"/>
-      <c r="L23" s="266"/>
+      <c r="D23" s="264"/>
+      <c r="E23" s="264"/>
+      <c r="F23" s="264"/>
+      <c r="G23" s="264"/>
+      <c r="H23" s="264"/>
+      <c r="I23" s="264"/>
+      <c r="J23" s="264"/>
+      <c r="K23" s="264"/>
+      <c r="L23" s="264"/>
       <c r="O23" s="5"/>
       <c r="Q23" s="92"/>
-      <c r="S23" s="267" t="s">
+      <c r="S23" s="265" t="s">
         <v>124</v>
       </c>
-      <c r="T23" s="268"/>
-      <c r="U23" s="268"/>
-      <c r="V23" s="268"/>
-      <c r="W23" s="268"/>
-      <c r="X23" s="268"/>
-      <c r="Y23" s="268"/>
-      <c r="Z23" s="268"/>
-      <c r="AA23" s="268"/>
-      <c r="AB23" s="268"/>
-      <c r="AC23" s="268"/>
+      <c r="T23" s="266"/>
+      <c r="U23" s="266"/>
+      <c r="V23" s="266"/>
+      <c r="W23" s="266"/>
+      <c r="X23" s="266"/>
+      <c r="Y23" s="266"/>
+      <c r="Z23" s="266"/>
+      <c r="AA23" s="266"/>
+      <c r="AB23" s="266"/>
+      <c r="AC23" s="266"/>
       <c r="AE23" s="88" t="str">
         <f>AE2</f>
         <v>TTM/YTD</v>
@@ -17431,32 +17431,32 @@
       <c r="O39" s="5"/>
     </row>
     <row r="40" spans="2:31" x14ac:dyDescent="0.2">
-      <c r="C40" s="266" t="s">
+      <c r="C40" s="264" t="s">
         <v>126</v>
       </c>
-      <c r="D40" s="266"/>
-      <c r="E40" s="266"/>
-      <c r="F40" s="266"/>
-      <c r="G40" s="266"/>
-      <c r="H40" s="266"/>
-      <c r="I40" s="266"/>
-      <c r="J40" s="266"/>
-      <c r="K40" s="266"/>
-      <c r="L40" s="266"/>
+      <c r="D40" s="264"/>
+      <c r="E40" s="264"/>
+      <c r="F40" s="264"/>
+      <c r="G40" s="264"/>
+      <c r="H40" s="264"/>
+      <c r="I40" s="264"/>
+      <c r="J40" s="264"/>
+      <c r="K40" s="264"/>
+      <c r="L40" s="264"/>
       <c r="O40" s="5"/>
-      <c r="S40" s="267" t="s">
+      <c r="S40" s="265" t="s">
         <v>126</v>
       </c>
-      <c r="T40" s="268"/>
-      <c r="U40" s="268"/>
-      <c r="V40" s="268"/>
-      <c r="W40" s="268"/>
-      <c r="X40" s="268"/>
-      <c r="Y40" s="268"/>
-      <c r="Z40" s="268"/>
-      <c r="AA40" s="268"/>
-      <c r="AB40" s="268"/>
-      <c r="AC40" s="268"/>
+      <c r="T40" s="266"/>
+      <c r="U40" s="266"/>
+      <c r="V40" s="266"/>
+      <c r="W40" s="266"/>
+      <c r="X40" s="266"/>
+      <c r="Y40" s="266"/>
+      <c r="Z40" s="266"/>
+      <c r="AA40" s="266"/>
+      <c r="AB40" s="266"/>
+      <c r="AC40" s="266"/>
     </row>
     <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -18023,18 +18023,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="S2:Z2"/>
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="S4:AC4"/>
     <mergeCell ref="C13:L13"/>
     <mergeCell ref="S13:AC13"/>
     <mergeCell ref="C23:L23"/>
     <mergeCell ref="S23:AC23"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="S40:AC40"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="S2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="S4:AC4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -18074,8 +18074,8 @@
       <c r="D2" s="258"/>
       <c r="E2" s="258"/>
       <c r="F2" s="258"/>
-      <c r="G2" s="264"/>
-      <c r="H2" s="265" t="s">
+      <c r="G2" s="267"/>
+      <c r="H2" s="268" t="s">
         <v>114</v>
       </c>
       <c r="I2" s="258"/>
@@ -18105,31 +18105,31 @@
     <row r="4" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="266" t="s">
+      <c r="C4" s="264" t="s">
         <v>116</v>
       </c>
-      <c r="D4" s="266"/>
-      <c r="E4" s="266"/>
-      <c r="F4" s="266"/>
-      <c r="G4" s="266"/>
-      <c r="H4" s="266"/>
-      <c r="I4" s="266"/>
-      <c r="J4" s="266"/>
-      <c r="K4" s="266"/>
-      <c r="L4" s="266"/>
-      <c r="P4" s="268" t="s">
+      <c r="D4" s="264"/>
+      <c r="E4" s="264"/>
+      <c r="F4" s="264"/>
+      <c r="G4" s="264"/>
+      <c r="H4" s="264"/>
+      <c r="I4" s="264"/>
+      <c r="J4" s="264"/>
+      <c r="K4" s="264"/>
+      <c r="L4" s="264"/>
+      <c r="P4" s="266" t="s">
         <v>116</v>
       </c>
-      <c r="Q4" s="268"/>
-      <c r="R4" s="268"/>
-      <c r="S4" s="268"/>
-      <c r="T4" s="268"/>
-      <c r="U4" s="268"/>
-      <c r="V4" s="268"/>
-      <c r="W4" s="268"/>
-      <c r="X4" s="268"/>
-      <c r="Y4" s="268"/>
-      <c r="Z4" s="268"/>
+      <c r="Q4" s="266"/>
+      <c r="R4" s="266"/>
+      <c r="S4" s="266"/>
+      <c r="T4" s="266"/>
+      <c r="U4" s="266"/>
+      <c r="V4" s="266"/>
+      <c r="W4" s="266"/>
+      <c r="X4" s="266"/>
+      <c r="Y4" s="266"/>
+      <c r="Z4" s="266"/>
       <c r="AB4" s="88"/>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
@@ -18324,32 +18324,32 @@
       <c r="N8" s="92"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C9" s="266" t="s">
+      <c r="C9" s="264" t="s">
         <v>129</v>
       </c>
-      <c r="D9" s="266"/>
-      <c r="E9" s="266"/>
-      <c r="F9" s="266"/>
-      <c r="G9" s="266"/>
-      <c r="H9" s="266"/>
-      <c r="I9" s="266"/>
-      <c r="J9" s="266"/>
-      <c r="K9" s="266"/>
-      <c r="L9" s="266"/>
+      <c r="D9" s="264"/>
+      <c r="E9" s="264"/>
+      <c r="F9" s="264"/>
+      <c r="G9" s="264"/>
+      <c r="H9" s="264"/>
+      <c r="I9" s="264"/>
+      <c r="J9" s="264"/>
+      <c r="K9" s="264"/>
+      <c r="L9" s="264"/>
       <c r="N9" s="92"/>
-      <c r="P9" s="268" t="s">
+      <c r="P9" s="266" t="s">
         <v>130</v>
       </c>
-      <c r="Q9" s="268"/>
-      <c r="R9" s="268"/>
-      <c r="S9" s="268"/>
-      <c r="T9" s="268"/>
-      <c r="U9" s="268"/>
-      <c r="V9" s="268"/>
-      <c r="W9" s="268"/>
-      <c r="X9" s="268"/>
-      <c r="Y9" s="268"/>
-      <c r="Z9" s="268"/>
+      <c r="Q9" s="266"/>
+      <c r="R9" s="266"/>
+      <c r="S9" s="266"/>
+      <c r="T9" s="266"/>
+      <c r="U9" s="266"/>
+      <c r="V9" s="266"/>
+      <c r="W9" s="266"/>
+      <c r="X9" s="266"/>
+      <c r="Y9" s="266"/>
+      <c r="Z9" s="266"/>
       <c r="AB9" s="88">
         <f>AB4</f>
         <v>0</v>
@@ -18919,31 +18919,31 @@
       </c>
     </row>
     <row r="18" spans="2:26" x14ac:dyDescent="0.2">
-      <c r="C18" s="266" t="s">
+      <c r="C18" s="264" t="s">
         <v>132</v>
       </c>
-      <c r="D18" s="266"/>
-      <c r="E18" s="266"/>
-      <c r="F18" s="266"/>
-      <c r="G18" s="266"/>
-      <c r="H18" s="266"/>
-      <c r="I18" s="266"/>
-      <c r="J18" s="266"/>
-      <c r="K18" s="266"/>
-      <c r="L18" s="266"/>
-      <c r="P18" s="268" t="s">
+      <c r="D18" s="264"/>
+      <c r="E18" s="264"/>
+      <c r="F18" s="264"/>
+      <c r="G18" s="264"/>
+      <c r="H18" s="264"/>
+      <c r="I18" s="264"/>
+      <c r="J18" s="264"/>
+      <c r="K18" s="264"/>
+      <c r="L18" s="264"/>
+      <c r="P18" s="266" t="s">
         <v>132</v>
       </c>
-      <c r="Q18" s="268"/>
-      <c r="R18" s="268"/>
-      <c r="S18" s="268"/>
-      <c r="T18" s="268"/>
-      <c r="U18" s="268"/>
-      <c r="V18" s="268"/>
-      <c r="W18" s="268"/>
-      <c r="X18" s="268"/>
-      <c r="Y18" s="268"/>
-      <c r="Z18" s="268"/>
+      <c r="Q18" s="266"/>
+      <c r="R18" s="266"/>
+      <c r="S18" s="266"/>
+      <c r="T18" s="266"/>
+      <c r="U18" s="266"/>
+      <c r="V18" s="266"/>
+      <c r="W18" s="266"/>
+      <c r="X18" s="266"/>
+      <c r="Y18" s="266"/>
+      <c r="Z18" s="266"/>
     </row>
     <row r="19" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -19509,8 +19509,8 @@
       <c r="D3" s="258"/>
       <c r="E3" s="258"/>
       <c r="F3" s="258"/>
-      <c r="G3" s="264"/>
-      <c r="H3" s="265" t="s">
+      <c r="G3" s="267"/>
+      <c r="H3" s="268" t="s">
         <v>114</v>
       </c>
       <c r="I3" s="258"/>
@@ -19534,18 +19534,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="87"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="266" t="s">
+      <c r="C5" s="264" t="s">
         <v>116</v>
       </c>
-      <c r="D5" s="266"/>
-      <c r="E5" s="266"/>
-      <c r="F5" s="266"/>
-      <c r="G5" s="266"/>
-      <c r="H5" s="266"/>
-      <c r="I5" s="266"/>
-      <c r="J5" s="266"/>
-      <c r="K5" s="266"/>
-      <c r="L5" s="266"/>
+      <c r="D5" s="264"/>
+      <c r="E5" s="264"/>
+      <c r="F5" s="264"/>
+      <c r="G5" s="264"/>
+      <c r="H5" s="264"/>
+      <c r="I5" s="264"/>
+      <c r="J5" s="264"/>
+      <c r="K5" s="264"/>
+      <c r="L5" s="264"/>
       <c r="P5" s="269"/>
       <c r="Q5" s="269"/>
       <c r="R5" s="269"/>
@@ -19742,18 +19742,18 @@
       <c r="N10" s="92"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="266" t="s">
+      <c r="C11" s="264" t="s">
         <v>136</v>
       </c>
-      <c r="D11" s="266"/>
-      <c r="E11" s="266"/>
-      <c r="F11" s="266"/>
-      <c r="G11" s="266"/>
-      <c r="H11" s="266"/>
-      <c r="I11" s="266"/>
-      <c r="J11" s="266"/>
-      <c r="K11" s="266"/>
-      <c r="L11" s="266"/>
+      <c r="D11" s="264"/>
+      <c r="E11" s="264"/>
+      <c r="F11" s="264"/>
+      <c r="G11" s="264"/>
+      <c r="H11" s="264"/>
+      <c r="I11" s="264"/>
+      <c r="J11" s="264"/>
+      <c r="K11" s="264"/>
+      <c r="L11" s="264"/>
       <c r="N11" s="92"/>
       <c r="P11" s="269"/>
       <c r="Q11" s="269"/>
@@ -20007,18 +20007,18 @@
       <c r="D16" s="24"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="266" t="s">
+      <c r="C18" s="264" t="s">
         <v>141</v>
       </c>
-      <c r="D18" s="266"/>
-      <c r="E18" s="266"/>
-      <c r="F18" s="266"/>
-      <c r="G18" s="266"/>
-      <c r="H18" s="266"/>
-      <c r="I18" s="266"/>
-      <c r="J18" s="266"/>
-      <c r="K18" s="266"/>
-      <c r="L18" s="266"/>
+      <c r="D18" s="264"/>
+      <c r="E18" s="264"/>
+      <c r="F18" s="264"/>
+      <c r="G18" s="264"/>
+      <c r="H18" s="264"/>
+      <c r="I18" s="264"/>
+      <c r="J18" s="264"/>
+      <c r="K18" s="264"/>
+      <c r="L18" s="264"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -20236,18 +20236,18 @@
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="111"/>
-      <c r="C26" s="266" t="s">
+      <c r="C26" s="264" t="s">
         <v>147</v>
       </c>
-      <c r="D26" s="266"/>
-      <c r="E26" s="266"/>
-      <c r="F26" s="266"/>
-      <c r="G26" s="266"/>
-      <c r="H26" s="266"/>
-      <c r="I26" s="266"/>
-      <c r="J26" s="266"/>
-      <c r="K26" s="266"/>
-      <c r="L26" s="266"/>
+      <c r="D26" s="264"/>
+      <c r="E26" s="264"/>
+      <c r="F26" s="264"/>
+      <c r="G26" s="264"/>
+      <c r="H26" s="264"/>
+      <c r="I26" s="264"/>
+      <c r="J26" s="264"/>
+      <c r="K26" s="264"/>
+      <c r="L26" s="264"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="16" t="s">
@@ -20439,18 +20439,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="111"/>
-      <c r="C33" s="266" t="s">
+      <c r="C33" s="264" t="s">
         <v>151</v>
       </c>
-      <c r="D33" s="266"/>
-      <c r="E33" s="266"/>
-      <c r="F33" s="266"/>
-      <c r="G33" s="266"/>
-      <c r="H33" s="266"/>
-      <c r="I33" s="266"/>
-      <c r="J33" s="266"/>
-      <c r="K33" s="266"/>
-      <c r="L33" s="266"/>
+      <c r="D33" s="264"/>
+      <c r="E33" s="264"/>
+      <c r="F33" s="264"/>
+      <c r="G33" s="264"/>
+      <c r="H33" s="264"/>
+      <c r="I33" s="264"/>
+      <c r="J33" s="264"/>
+      <c r="K33" s="264"/>
+      <c r="L33" s="264"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
@@ -20634,18 +20634,18 @@
       <c r="C39" s="127"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="266" t="s">
+      <c r="C40" s="264" t="s">
         <v>154</v>
       </c>
-      <c r="D40" s="266"/>
-      <c r="E40" s="266"/>
-      <c r="F40" s="266"/>
-      <c r="G40" s="266"/>
-      <c r="H40" s="266"/>
-      <c r="I40" s="266"/>
-      <c r="J40" s="266"/>
-      <c r="K40" s="266"/>
-      <c r="L40" s="266"/>
+      <c r="D40" s="264"/>
+      <c r="E40" s="264"/>
+      <c r="F40" s="264"/>
+      <c r="G40" s="264"/>
+      <c r="H40" s="264"/>
+      <c r="I40" s="264"/>
+      <c r="J40" s="264"/>
+      <c r="K40" s="264"/>
+      <c r="L40" s="264"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -20909,12 +20909,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -20922,6 +20916,12 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -20965,8 +20965,8 @@
       <c r="D2" s="258"/>
       <c r="E2" s="258"/>
       <c r="F2" s="258"/>
-      <c r="G2" s="264"/>
-      <c r="H2" s="265" t="s">
+      <c r="G2" s="267"/>
+      <c r="H2" s="268" t="s">
         <v>114</v>
       </c>
       <c r="I2" s="258"/>
@@ -20990,18 +20990,18 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="266" t="s">
+      <c r="C4" s="264" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="266"/>
-      <c r="E4" s="266"/>
-      <c r="F4" s="266"/>
-      <c r="G4" s="266"/>
-      <c r="H4" s="266"/>
-      <c r="I4" s="266"/>
-      <c r="J4" s="266"/>
-      <c r="K4" s="266"/>
-      <c r="L4" s="266"/>
+      <c r="D4" s="264"/>
+      <c r="E4" s="264"/>
+      <c r="F4" s="264"/>
+      <c r="G4" s="264"/>
+      <c r="H4" s="264"/>
+      <c r="I4" s="264"/>
+      <c r="J4" s="264"/>
+      <c r="K4" s="264"/>
+      <c r="L4" s="264"/>
       <c r="S4" s="269"/>
       <c r="T4" s="269"/>
       <c r="U4" s="269"/>
@@ -21375,18 +21375,18 @@
       <c r="AE10" s="64"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="266" t="s">
+      <c r="C13" s="264" t="s">
         <v>162</v>
       </c>
-      <c r="D13" s="266"/>
-      <c r="E13" s="266"/>
-      <c r="F13" s="266"/>
-      <c r="G13" s="266"/>
-      <c r="H13" s="266"/>
-      <c r="I13" s="266"/>
-      <c r="J13" s="266"/>
-      <c r="K13" s="266"/>
-      <c r="L13" s="266"/>
+      <c r="D13" s="264"/>
+      <c r="E13" s="264"/>
+      <c r="F13" s="264"/>
+      <c r="G13" s="264"/>
+      <c r="H13" s="264"/>
+      <c r="I13" s="264"/>
+      <c r="J13" s="264"/>
+      <c r="K13" s="264"/>
+      <c r="L13" s="264"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="12">
@@ -21479,18 +21479,18 @@
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C18" s="266" t="s">
+      <c r="C18" s="264" t="s">
         <v>163</v>
       </c>
-      <c r="D18" s="266"/>
-      <c r="E18" s="266"/>
-      <c r="F18" s="266"/>
-      <c r="G18" s="266"/>
-      <c r="H18" s="266"/>
-      <c r="I18" s="266"/>
-      <c r="J18" s="266"/>
-      <c r="K18" s="266"/>
-      <c r="L18" s="266"/>
+      <c r="D18" s="264"/>
+      <c r="E18" s="264"/>
+      <c r="F18" s="264"/>
+      <c r="G18" s="264"/>
+      <c r="H18" s="264"/>
+      <c r="I18" s="264"/>
+      <c r="J18" s="264"/>
+      <c r="K18" s="264"/>
+      <c r="L18" s="264"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -21682,18 +21682,18 @@
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C25" s="266" t="s">
+      <c r="C25" s="264" t="s">
         <v>266</v>
       </c>
-      <c r="D25" s="266"/>
-      <c r="E25" s="266"/>
-      <c r="F25" s="266"/>
-      <c r="G25" s="266"/>
-      <c r="H25" s="266"/>
-      <c r="I25" s="266"/>
-      <c r="J25" s="266"/>
-      <c r="K25" s="266"/>
-      <c r="L25" s="266"/>
+      <c r="D25" s="264"/>
+      <c r="E25" s="264"/>
+      <c r="F25" s="264"/>
+      <c r="G25" s="264"/>
+      <c r="H25" s="264"/>
+      <c r="I25" s="264"/>
+      <c r="J25" s="264"/>
+      <c r="K25" s="264"/>
+      <c r="L25" s="264"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B26" s="16" t="s">
@@ -21831,18 +21831,18 @@
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C31" s="266" t="s">
+      <c r="C31" s="264" t="s">
         <v>78</v>
       </c>
-      <c r="D31" s="266"/>
-      <c r="E31" s="266"/>
-      <c r="F31" s="266"/>
-      <c r="G31" s="266"/>
-      <c r="H31" s="266"/>
-      <c r="I31" s="266"/>
-      <c r="J31" s="266"/>
-      <c r="K31" s="266"/>
-      <c r="L31" s="266"/>
+      <c r="D31" s="264"/>
+      <c r="E31" s="264"/>
+      <c r="F31" s="264"/>
+      <c r="G31" s="264"/>
+      <c r="H31" s="264"/>
+      <c r="I31" s="264"/>
+      <c r="J31" s="264"/>
+      <c r="K31" s="264"/>
+      <c r="L31" s="264"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="16" t="s">
@@ -21981,16 +21981,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C31:L31"/>
+    <mergeCell ref="C25:L25"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="S2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
     <mergeCell ref="C13:L13"/>
     <mergeCell ref="C18:L18"/>
-    <mergeCell ref="C31:L31"/>
-    <mergeCell ref="C25:L25"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="S2:Z2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -22073,7 +22073,7 @@
       </c>
       <c r="C6" s="135">
         <f ca="1">Overview!C5</f>
-        <v>142.62</v>
+        <v>147.1</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22082,7 +22082,7 @@
       </c>
       <c r="C7" s="136">
         <f ca="1">C5*C6</f>
-        <v>7148399.6400000006</v>
+        <v>7372946.1999999993</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22100,7 +22100,7 @@
       </c>
       <c r="C9" s="137">
         <f ca="1">Overview!F27</f>
-        <v>5.2399999999999995E-2</v>
+        <v>5.2770000000000004E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22109,7 +22109,7 @@
       </c>
       <c r="C10" s="135">
         <f ca="1">Overview!C13</f>
-        <v>1.054</v>
+        <v>1.0652999999999999</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22179,7 +22179,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>9.9830000000000002E-2</v>
+        <v>0.10070850000000001</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22188,7 +22188,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>9.9830000000000002E-2</v>
+        <v>0.10070850000000001</v>
       </c>
     </row>
   </sheetData>
@@ -22239,8 +22239,8 @@
       <c r="D3" s="258"/>
       <c r="E3" s="258"/>
       <c r="F3" s="258"/>
-      <c r="G3" s="264"/>
-      <c r="H3" s="265" t="s">
+      <c r="G3" s="267"/>
+      <c r="H3" s="268" t="s">
         <v>114</v>
       </c>
       <c r="I3" s="258"/>
@@ -22264,18 +22264,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="87"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="266" t="s">
+      <c r="C5" s="264" t="s">
         <v>184</v>
       </c>
-      <c r="D5" s="266"/>
-      <c r="E5" s="266"/>
-      <c r="F5" s="266"/>
-      <c r="G5" s="266"/>
-      <c r="H5" s="266"/>
-      <c r="I5" s="266"/>
-      <c r="J5" s="266"/>
-      <c r="K5" s="266"/>
-      <c r="L5" s="266"/>
+      <c r="D5" s="264"/>
+      <c r="E5" s="264"/>
+      <c r="F5" s="264"/>
+      <c r="G5" s="264"/>
+      <c r="H5" s="264"/>
+      <c r="I5" s="264"/>
+      <c r="J5" s="264"/>
+      <c r="K5" s="264"/>
+      <c r="L5" s="264"/>
       <c r="P5" s="269"/>
       <c r="Q5" s="269"/>
       <c r="R5" s="269"/>
@@ -22439,7 +22439,7 @@
       </c>
       <c r="L8" s="128">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>7334068.1618280802</v>
+        <v>7254237.9223840814</v>
       </c>
       <c r="N8" s="92"/>
       <c r="O8" s="16"/>
@@ -22493,23 +22493,23 @@
       <c r="G10" s="140"/>
       <c r="H10" s="128">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>164364.64911053865</v>
+        <v>164233.46601869952</v>
       </c>
       <c r="I10" s="128">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>198839.88279500158</v>
+        <v>198522.61236654638</v>
       </c>
       <c r="J10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>226618.90586386787</v>
+        <v>226076.73000951245</v>
       </c>
       <c r="K10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>260473.12159107611</v>
+        <v>259642.55896060905</v>
       </c>
       <c r="L10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>356683.55847808288</v>
+        <v>355262.44322596065</v>
       </c>
       <c r="N10" s="92"/>
     </row>
@@ -22528,7 +22528,7 @@
       <c r="K11" s="139"/>
       <c r="L11" s="128">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>4557399.8452667482</v>
+        <v>4489833.0670311032</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
@@ -22551,7 +22551,7 @@
       </c>
       <c r="C15" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>9.9830000000000002E-2</v>
+        <v>0.10070850000000001</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
@@ -22566,7 +22566,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>1206980.1178385671</v>
+        <v>1203737.8105813279</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -22575,7 +22575,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>4557399.8452667482</v>
+        <v>4489833.0670311032</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -22584,7 +22584,7 @@
       </c>
       <c r="C21" s="95">
         <f ca="1">C19+C20</f>
-        <v>5764379.9631053153</v>
+        <v>5693570.8776124306</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -22611,7 +22611,7 @@
       </c>
       <c r="C24" s="95">
         <f ca="1">C21+C22-C23</f>
-        <v>7180938.9631053153</v>
+        <v>7110129.8776124306</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -22629,7 +22629,7 @@
       </c>
       <c r="C26" s="254">
         <f ca="1">C24/C25</f>
-        <v>143.26920240823023</v>
+        <v>141.85646777088763</v>
       </c>
     </row>
   </sheetData>
@@ -22678,8 +22678,8 @@
       <c r="D2" s="258"/>
       <c r="E2" s="258"/>
       <c r="F2" s="258"/>
-      <c r="G2" s="264"/>
-      <c r="H2" s="265" t="s">
+      <c r="G2" s="267"/>
+      <c r="H2" s="268" t="s">
         <v>114</v>
       </c>
       <c r="I2" s="258"/>
@@ -22691,18 +22691,18 @@
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="266" t="s">
+      <c r="C4" s="264" t="s">
         <v>198</v>
       </c>
-      <c r="D4" s="266"/>
-      <c r="E4" s="266"/>
-      <c r="F4" s="266"/>
-      <c r="G4" s="266"/>
-      <c r="H4" s="266"/>
-      <c r="I4" s="266"/>
-      <c r="J4" s="266"/>
-      <c r="K4" s="266"/>
-      <c r="L4" s="266"/>
+      <c r="D4" s="264"/>
+      <c r="E4" s="264"/>
+      <c r="F4" s="264"/>
+      <c r="G4" s="264"/>
+      <c r="H4" s="264"/>
+      <c r="I4" s="264"/>
+      <c r="J4" s="264"/>
+      <c r="K4" s="264"/>
+      <c r="L4" s="264"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -22898,23 +22898,23 @@
       <c r="G9" s="140"/>
       <c r="H9" s="93">
         <f ca="1">DCF!H10</f>
-        <v>164364.64911053865</v>
+        <v>164233.46601869952</v>
       </c>
       <c r="I9" s="93">
         <f ca="1">DCF!I10</f>
-        <v>198839.88279500158</v>
+        <v>198522.61236654638</v>
       </c>
       <c r="J9" s="93">
         <f ca="1">DCF!J10</f>
-        <v>226618.90586386787</v>
+        <v>226076.73000951245</v>
       </c>
       <c r="K9" s="93">
         <f ca="1">DCF!K10</f>
-        <v>260473.12159107611</v>
+        <v>259642.55896060905</v>
       </c>
       <c r="L9" s="93">
         <f ca="1">DCF!L10</f>
-        <v>356683.55847808288</v>
+        <v>355262.44322596065</v>
       </c>
       <c r="N9" s="92"/>
     </row>
@@ -22922,18 +22922,18 @@
       <c r="N10" s="92"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C11" s="266" t="s">
+      <c r="C11" s="264" t="s">
         <v>122</v>
       </c>
-      <c r="D11" s="266"/>
-      <c r="E11" s="266"/>
-      <c r="F11" s="266"/>
-      <c r="G11" s="266"/>
-      <c r="H11" s="266"/>
-      <c r="I11" s="266"/>
-      <c r="J11" s="266"/>
-      <c r="K11" s="266"/>
-      <c r="L11" s="266"/>
+      <c r="D11" s="264"/>
+      <c r="E11" s="264"/>
+      <c r="F11" s="264"/>
+      <c r="G11" s="264"/>
+      <c r="H11" s="264"/>
+      <c r="I11" s="264"/>
+      <c r="J11" s="264"/>
+      <c r="K11" s="264"/>
+      <c r="L11" s="264"/>
       <c r="N11" s="92"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -23127,18 +23127,18 @@
       <c r="N16" s="92"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C17" s="266" t="s">
+      <c r="C17" s="264" t="s">
         <v>200</v>
       </c>
-      <c r="D17" s="266"/>
-      <c r="E17" s="266"/>
-      <c r="F17" s="266"/>
-      <c r="G17" s="266"/>
-      <c r="H17" s="266"/>
-      <c r="I17" s="266"/>
-      <c r="J17" s="266"/>
-      <c r="K17" s="266"/>
-      <c r="L17" s="266"/>
+      <c r="D17" s="264"/>
+      <c r="E17" s="264"/>
+      <c r="F17" s="264"/>
+      <c r="G17" s="264"/>
+      <c r="H17" s="264"/>
+      <c r="I17" s="264"/>
+      <c r="J17" s="264"/>
+      <c r="K17" s="264"/>
+      <c r="L17" s="264"/>
       <c r="N17" s="92"/>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
@@ -23272,18 +23272,18 @@
       <c r="N21" s="92"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C22" s="266" t="s">
+      <c r="C22" s="264" t="s">
         <v>203</v>
       </c>
-      <c r="D22" s="266"/>
-      <c r="E22" s="266"/>
-      <c r="F22" s="266"/>
-      <c r="G22" s="266"/>
-      <c r="H22" s="266"/>
-      <c r="I22" s="266"/>
-      <c r="J22" s="266"/>
-      <c r="K22" s="266"/>
-      <c r="L22" s="266"/>
+      <c r="D22" s="264"/>
+      <c r="E22" s="264"/>
+      <c r="F22" s="264"/>
+      <c r="G22" s="264"/>
+      <c r="H22" s="264"/>
+      <c r="I22" s="264"/>
+      <c r="J22" s="264"/>
+      <c r="K22" s="264"/>
+      <c r="L22" s="264"/>
       <c r="N22" s="92"/>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.2">
@@ -23367,18 +23367,18 @@
       <c r="N26" s="92"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C27" s="266" t="s">
+      <c r="C27" s="264" t="s">
         <v>204</v>
       </c>
-      <c r="D27" s="266"/>
-      <c r="E27" s="266"/>
-      <c r="F27" s="266"/>
-      <c r="G27" s="266"/>
-      <c r="H27" s="266"/>
-      <c r="I27" s="266"/>
-      <c r="J27" s="266"/>
-      <c r="K27" s="266"/>
-      <c r="L27" s="266"/>
+      <c r="D27" s="264"/>
+      <c r="E27" s="264"/>
+      <c r="F27" s="264"/>
+      <c r="G27" s="264"/>
+      <c r="H27" s="264"/>
+      <c r="I27" s="264"/>
+      <c r="J27" s="264"/>
+      <c r="K27" s="264"/>
+      <c r="L27" s="264"/>
       <c r="N27" s="92"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.2">
@@ -23700,7 +23700,7 @@
       </c>
       <c r="C41" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>9.9830000000000002E-2</v>
+        <v>0.10070850000000001</v>
       </c>
     </row>
     <row r="42" spans="2:14" x14ac:dyDescent="0.2">
@@ -23726,7 +23726,7 @@
       </c>
       <c r="C44" s="24">
         <f ca="1">C43/(1+C41)^5</f>
-        <v>7572936.1074889461</v>
+        <v>7542763.6626147851</v>
       </c>
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.2">
@@ -23735,7 +23735,7 @@
       </c>
       <c r="C45" s="110">
         <f ca="1">SUM(H9:K9)+C44</f>
-        <v>8423232.6668494307</v>
+        <v>8391239.0299701523</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -23762,7 +23762,7 @@
       </c>
       <c r="C48" s="110">
         <f ca="1">C45+C46-C47</f>
-        <v>9839791.6668494307</v>
+        <v>9807798.0299701523</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
@@ -23780,7 +23780,7 @@
       </c>
       <c r="C50" s="254">
         <f ca="1">C48/C49</f>
-        <v>196.31682029546766</v>
+        <v>195.67850504708815</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
@@ -23804,7 +23804,7 @@
       </c>
       <c r="C54" s="137">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>9.9830000000000002E-2</v>
+        <v>0.10070850000000001</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
@@ -23839,7 +23839,7 @@
       </c>
       <c r="C58" s="254">
         <f ca="1">C57/(1+C54)^5</f>
-        <v>158.06078335243151</v>
+        <v>157.43103021510453</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
@@ -23863,7 +23863,7 @@
       </c>
       <c r="C62" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>9.9830000000000002E-2</v>
+        <v>0.10070850000000001</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
@@ -23889,7 +23889,7 @@
       </c>
       <c r="C65" s="24">
         <f ca="1">C64/(1+C62)^5</f>
-        <v>7847038.2865178222</v>
+        <v>7815773.7509711338</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -23898,7 +23898,7 @@
       </c>
       <c r="C66" s="110">
         <f ca="1">SUM(H9:K9)+C65</f>
-        <v>8697334.8458783068</v>
+        <v>8664249.1183265019</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.2">
@@ -23925,7 +23925,7 @@
       </c>
       <c r="C69" s="110">
         <f ca="1">C66+C67-C68</f>
-        <v>10113893.845878307</v>
+        <v>10080808.118326502</v>
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.2">
@@ -23943,7 +23943,7 @@
       </c>
       <c r="C71" s="254">
         <f ca="1">C69/C70</f>
-        <v>201.78552024816062</v>
+        <v>201.12541635063448</v>
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.2">
@@ -23967,7 +23967,7 @@
       </c>
       <c r="C75" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>9.9830000000000002E-2</v>
+        <v>0.10070850000000001</v>
       </c>
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.2">
@@ -23993,7 +23993,7 @@
       </c>
       <c r="C78" s="24">
         <f ca="1">C77/(1+C75)^5</f>
-        <v>7867985.5662222859</v>
+        <v>7836637.5715478323</v>
       </c>
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.2">
@@ -24002,7 +24002,7 @@
       </c>
       <c r="C79" s="110">
         <f ca="1">SUM(H9:K9)+C78</f>
-        <v>8718282.1255827695</v>
+        <v>8685112.9389031995</v>
       </c>
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.2">
@@ -24029,7 +24029,7 @@
       </c>
       <c r="C82" s="110">
         <f ca="1">C79+C80-C81</f>
-        <v>10134841.12558277</v>
+        <v>10101671.9389032</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.2">
@@ -24047,22 +24047,22 @@
       </c>
       <c r="C84" s="254">
         <f ca="1">C82/C83</f>
-        <v>202.20344610316366</v>
+        <v>201.54167708597421</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="C27:L27"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B60:C60"/>
     <mergeCell ref="C22:L22"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="C17:L17"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="C27:L27"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B60:C60"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -24112,7 +24112,7 @@
       </c>
       <c r="C5" s="135">
         <f ca="1">DCF!C26</f>
-        <v>143.26920240823023</v>
+        <v>141.85646777088763</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -24121,7 +24121,7 @@
       </c>
       <c r="C6" s="135">
         <f ca="1">Multiples!C50</f>
-        <v>196.31682029546766</v>
+        <v>195.67850504708815</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -24130,7 +24130,7 @@
       </c>
       <c r="C7" s="135">
         <f ca="1">Multiples!C58</f>
-        <v>158.06078335243151</v>
+        <v>157.43103021510453</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -24139,7 +24139,7 @@
       </c>
       <c r="C8" s="135">
         <f ca="1">Multiples!C71</f>
-        <v>201.78552024816062</v>
+        <v>201.12541635063448</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -24148,7 +24148,7 @@
       </c>
       <c r="C9" s="135">
         <f ca="1">Multiples!C84</f>
-        <v>202.20344610316366</v>
+        <v>201.54167708597421</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -24157,7 +24157,7 @@
       </c>
       <c r="C10" s="254">
         <f ca="1">AVERAGE(C5:C9)</f>
-        <v>180.32715448149074</v>
+        <v>179.52661929393781</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -24166,7 +24166,7 @@
       </c>
       <c r="C11" s="135">
         <f ca="1">Overview!C5</f>
-        <v>142.62</v>
+        <v>147.1</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -24175,7 +24175,7 @@
       </c>
       <c r="C12" s="154">
         <f ca="1">(C10-C11)/C11</f>
-        <v>0.26438896705574766</v>
+        <v>0.2204392881980817</v>
       </c>
     </row>
   </sheetData>
@@ -24237,8 +24237,8 @@
       <c r="D2" s="258"/>
       <c r="E2" s="258"/>
       <c r="F2" s="258"/>
-      <c r="G2" s="264"/>
-      <c r="H2" s="265" t="s">
+      <c r="G2" s="267"/>
+      <c r="H2" s="268" t="s">
         <v>114</v>
       </c>
       <c r="I2" s="258"/>
@@ -24250,18 +24250,18 @@
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="266" t="s">
+      <c r="C4" s="264" t="s">
         <v>198</v>
       </c>
-      <c r="D4" s="266"/>
-      <c r="E4" s="266"/>
-      <c r="F4" s="266"/>
-      <c r="G4" s="266"/>
-      <c r="H4" s="266"/>
-      <c r="I4" s="266"/>
-      <c r="J4" s="266"/>
-      <c r="K4" s="266"/>
-      <c r="L4" s="266"/>
+      <c r="D4" s="264"/>
+      <c r="E4" s="264"/>
+      <c r="F4" s="264"/>
+      <c r="G4" s="264"/>
+      <c r="H4" s="264"/>
+      <c r="I4" s="264"/>
+      <c r="J4" s="264"/>
+      <c r="K4" s="264"/>
+      <c r="L4" s="264"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -24374,18 +24374,18 @@
       <c r="N8" s="92"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C9" s="266" t="s">
+      <c r="C9" s="264" t="s">
         <v>122</v>
       </c>
-      <c r="D9" s="266"/>
-      <c r="E9" s="266"/>
-      <c r="F9" s="266"/>
-      <c r="G9" s="266"/>
-      <c r="H9" s="266"/>
-      <c r="I9" s="266"/>
-      <c r="J9" s="266"/>
-      <c r="K9" s="266"/>
-      <c r="L9" s="266"/>
+      <c r="D9" s="264"/>
+      <c r="E9" s="264"/>
+      <c r="F9" s="264"/>
+      <c r="G9" s="264"/>
+      <c r="H9" s="264"/>
+      <c r="I9" s="264"/>
+      <c r="J9" s="264"/>
+      <c r="K9" s="264"/>
+      <c r="L9" s="264"/>
       <c r="N9" s="92"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -24506,18 +24506,18 @@
       <c r="N13" s="92"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C14" s="266" t="s">
+      <c r="C14" s="264" t="s">
         <v>413</v>
       </c>
-      <c r="D14" s="266"/>
-      <c r="E14" s="266"/>
-      <c r="F14" s="266"/>
-      <c r="G14" s="266"/>
-      <c r="H14" s="266"/>
-      <c r="I14" s="266"/>
-      <c r="J14" s="266"/>
-      <c r="K14" s="266"/>
-      <c r="L14" s="266"/>
+      <c r="D14" s="264"/>
+      <c r="E14" s="264"/>
+      <c r="F14" s="264"/>
+      <c r="G14" s="264"/>
+      <c r="H14" s="264"/>
+      <c r="I14" s="264"/>
+      <c r="J14" s="264"/>
+      <c r="K14" s="264"/>
+      <c r="L14" s="264"/>
       <c r="N14" s="92"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
@@ -24645,7 +24645,7 @@
       </c>
       <c r="C24" s="137">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>9.9830000000000002E-2</v>
+        <v>0.10070850000000001</v>
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
@@ -24718,8 +24718,8 @@
       <c r="D3" s="258"/>
       <c r="E3" s="258"/>
       <c r="F3" s="258"/>
-      <c r="G3" s="264"/>
-      <c r="H3" s="265" t="s">
+      <c r="G3" s="267"/>
+      <c r="H3" s="268" t="s">
         <v>114</v>
       </c>
       <c r="I3" s="258"/>
@@ -24743,18 +24743,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="87"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="266" t="s">
+      <c r="C5" s="264" t="s">
         <v>184</v>
       </c>
-      <c r="D5" s="266"/>
-      <c r="E5" s="266"/>
-      <c r="F5" s="266"/>
-      <c r="G5" s="266"/>
-      <c r="H5" s="266"/>
-      <c r="I5" s="266"/>
-      <c r="J5" s="266"/>
-      <c r="K5" s="266"/>
-      <c r="L5" s="266"/>
+      <c r="D5" s="264"/>
+      <c r="E5" s="264"/>
+      <c r="F5" s="264"/>
+      <c r="G5" s="264"/>
+      <c r="H5" s="264"/>
+      <c r="I5" s="264"/>
+      <c r="J5" s="264"/>
+      <c r="K5" s="264"/>
+      <c r="L5" s="264"/>
       <c r="P5" s="269"/>
       <c r="Q5" s="269"/>
       <c r="R5" s="269"/>
@@ -24900,7 +24900,7 @@
       <c r="K8" s="139"/>
       <c r="L8" s="128">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>6455060.9771920424</v>
+        <v>6384798.6000141334</v>
       </c>
       <c r="N8" s="92"/>
       <c r="O8" s="16"/>
@@ -24954,23 +24954,23 @@
       <c r="G10" s="140"/>
       <c r="H10" s="128">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>176573.63641144588</v>
+        <v>176432.7090545776</v>
       </c>
       <c r="I10" s="128">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>203893.80017142306</v>
+        <v>203568.46567398502</v>
       </c>
       <c r="J10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>235441.04654147211</v>
+        <v>234877.76410008731</v>
       </c>
       <c r="K10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>271869.40627885179</v>
+        <v>271002.5046659591</v>
       </c>
       <c r="L10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>313934.10433807201</v>
+        <v>312683.31345289701</v>
       </c>
       <c r="N10" s="92"/>
     </row>
@@ -24989,15 +24989,15 @@
       <c r="K11" s="139"/>
       <c r="L11" s="128">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>4011183.5954507506</v>
+        <v>3951714.8716920139</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="271" t="s">
+      <c r="B14" s="270" t="s">
         <v>226</v>
       </c>
-      <c r="C14" s="272"/>
+      <c r="C14" s="271"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="155" t="s">
@@ -25005,7 +25005,7 @@
       </c>
       <c r="C15" s="156">
         <f ca="1">Overview!C5</f>
-        <v>142.62</v>
+        <v>147.1</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -25014,7 +25014,7 @@
       </c>
       <c r="C16" s="156">
         <f ca="1">C36</f>
-        <v>141.69740070089375</v>
+        <v>140.35905246525712</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -25024,20 +25024,20 @@
       <c r="C17" s="158">
         <v>0.27</v>
       </c>
-      <c r="E17" s="270" t="s">
+      <c r="E17" s="272" t="s">
         <v>229</v>
       </c>
-      <c r="F17" s="270"/>
-      <c r="G17" s="270"/>
-      <c r="H17" s="270"/>
-      <c r="I17" s="270"/>
+      <c r="F17" s="272"/>
+      <c r="G17" s="272"/>
+      <c r="H17" s="272"/>
+      <c r="I17" s="272"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="271" t="s">
+      <c r="B19" s="270" t="s">
         <v>188</v>
       </c>
-      <c r="C19" s="272"/>
+      <c r="C19" s="271"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="159" t="s">
@@ -25053,7 +25053,7 @@
       </c>
       <c r="C21" s="221">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>9.9830000000000002E-2</v>
+        <v>0.10070850000000001</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -25071,7 +25071,7 @@
       </c>
       <c r="C23" s="161">
         <f ca="1">C15*C22</f>
-        <v>6672619.3200000003</v>
+        <v>6882220.5999999996</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -25098,15 +25098,15 @@
       </c>
       <c r="C26" s="162">
         <f ca="1">C23+C25-C24</f>
-        <v>5256060.32</v>
+        <v>5465661.5999999996</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="271" t="s">
+      <c r="B28" s="270" t="s">
         <v>190</v>
       </c>
-      <c r="C28" s="272"/>
+      <c r="C28" s="271"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="159" t="s">
@@ -25114,7 +25114,7 @@
       </c>
       <c r="C29" s="161">
         <f ca="1">SUM(H10:L10)</f>
-        <v>1201711.9937412648</v>
+        <v>1198564.7569475062</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -25123,7 +25123,7 @@
       </c>
       <c r="C30" s="161">
         <f ca="1">L11</f>
-        <v>4011183.5954507506</v>
+        <v>3951714.8716920139</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -25132,7 +25132,7 @@
       </c>
       <c r="C31" s="164">
         <f ca="1">C29+C30</f>
-        <v>5212895.5891920151</v>
+        <v>5150279.6286395201</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -25159,7 +25159,7 @@
       </c>
       <c r="C34" s="164">
         <f ca="1">C31+C32-C33</f>
-        <v>6629454.5891920151</v>
+        <v>6566838.6286395201</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.2">
@@ -25177,21 +25177,21 @@
       </c>
       <c r="C36" s="167">
         <f ca="1">C34/C35</f>
-        <v>141.69740070089375</v>
+        <v>140.35905246525712</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
     <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -31883,7 +31883,7 @@
       </c>
       <c r="AC116" s="63">
         <f ca="1">Overview!C5</f>
-        <v>142.62</v>
+        <v>147.1</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -31954,7 +31954,7 @@
       </c>
       <c r="AC117" s="65">
         <f ca="1">AC116/AC85</f>
-        <v>142.62</v>
+        <v>147.1</v>
       </c>
     </row>
     <row r="119" spans="1:31" x14ac:dyDescent="0.2">
@@ -33064,7 +33064,7 @@
       <c r="AA146" s="49"/>
       <c r="AC146" s="72">
         <f ca="1">AC117/Statement!AC26</f>
-        <v>45.411749374186655</v>
+        <v>46.838229792054811</v>
       </c>
     </row>
     <row r="147" spans="2:29" x14ac:dyDescent="0.2">
@@ -33101,7 +33101,7 @@
       <c r="AA147" s="49"/>
       <c r="AC147" s="72">
         <f ca="1">AC117/(Statement!AC5/Statement!AC22)</f>
-        <v>6.1247407387285442</v>
+        <v>6.31713197775185</v>
       </c>
     </row>
     <row r="148" spans="2:29" x14ac:dyDescent="0.2">
@@ -33162,7 +33162,7 @@
       </c>
       <c r="AC148" s="72">
         <f ca="1">AC117/(Statement!AC49/Statement!AC75)</f>
-        <v>4.7332202062505058</v>
+        <v>4.8819008017069789</v>
       </c>
     </row>
     <row r="149" spans="2:29" x14ac:dyDescent="0.2">
@@ -33223,7 +33223,7 @@
       </c>
       <c r="AC149" s="143">
         <f ca="1">Statement!AC117*Statement!AC78</f>
-        <v>7148399.6400000006</v>
+        <v>7372946.1999999993</v>
       </c>
     </row>
     <row r="150" spans="2:29" x14ac:dyDescent="0.2">
@@ -33284,7 +33284,7 @@
       </c>
       <c r="AC150" s="143">
         <f ca="1">AC149+AC108-AC107+AC48+AC45</f>
-        <v>5731840.6400000006</v>
+        <v>5956387.1999999993</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -33321,7 +33321,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="182">
         <f ca="1">AC150/AC5</f>
-        <v>5.0059656140338626</v>
+        <v>5.2020758042344024</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -33358,7 +33358,7 @@
       <c r="AA152" s="49"/>
       <c r="AC152" s="182">
         <f ca="1">AC150/AC12</f>
-        <v>36.488784034121657</v>
+        <v>37.918242989464296</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -33455,7 +33455,7 @@
       <c r="Z154" s="49"/>
       <c r="AA154" s="49"/>
       <c r="AC154" s="64">
-        <f>AC109+AC53+AC110+AC55+AC57+AC58</f>
+        <f>AC109+AC53+AC110+AC55+AC57+AC58+AC56</f>
         <v>166731.31659797492</v>
       </c>
     </row>
@@ -33493,7 +33493,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="72">
         <f t="shared" ref="AC155:AC156" ca="1" si="151">AC149/AC153</f>
-        <v>28.274660390791869</v>
+        <v>29.162828099042795</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -33530,7 +33530,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="72">
         <f t="shared" ca="1" si="151"/>
-        <v>34.377708740948179</v>
+        <v>35.724465694480962</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -33567,7 +33567,7 @@
       <c r="AA157" s="49"/>
       <c r="AC157" s="74">
         <f t="shared" ref="AC157" ca="1" si="154">AC153/AC149</f>
-        <v>3.5367356713704938E-2</v>
+        <v>3.4290227155055059E-2</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
@@ -33604,7 +33604,7 @@
       <c r="AA158" s="49"/>
       <c r="AC158" s="74">
         <f ca="1">AC26/AC117</f>
-        <v>2.2020732823132085E-2</v>
+        <v>2.1350081000918408E-2</v>
       </c>
     </row>
     <row r="159" spans="2:29" x14ac:dyDescent="0.2">
@@ -33678,7 +33678,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="154">
         <f ca="1">-AC63/AC149</f>
-        <v>9.7368646837433948E-3</v>
+        <v>9.4403238694458404E-3</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -33715,7 +33715,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="154">
         <f ca="1">-(AC63+AC64)/AC149</f>
-        <v>9.7368646837433948E-3</v>
+        <v>9.4403238694458404E-3</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -34218,7 +34218,7 @@
       <c r="AA172" s="49"/>
       <c r="AC172" s="154">
         <f ca="1">(AC107-AC108)/AC149</f>
-        <v>0.19816449433988276</v>
+        <v>0.19212930103843701</v>
       </c>
     </row>
     <row r="173" spans="2:29" x14ac:dyDescent="0.2">
@@ -36156,7 +36156,7 @@
       </c>
       <c r="C5" s="171">
         <f ca="1">Overview!C5</f>
-        <v>142.62</v>
+        <v>147.1</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="134" t="s">
@@ -36172,7 +36172,7 @@
       </c>
       <c r="C6" s="172">
         <f ca="1">Statement!AC149</f>
-        <v>7148399.6400000006</v>
+        <v>7372946.1999999993</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>20</v>
@@ -36192,7 +36192,7 @@
       </c>
       <c r="C7" s="172">
         <f ca="1">Statement!AC150</f>
-        <v>5731840.6400000006</v>
+        <v>5956387.1999999993</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>32</v>
@@ -36212,7 +36212,7 @@
       </c>
       <c r="C8" s="173">
         <f ca="1">Statement!AC146</f>
-        <v>45.411749374186655</v>
+        <v>46.838229792054811</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>247</v>
@@ -36232,7 +36232,7 @@
       </c>
       <c r="C9" s="173">
         <f ca="1">Statement!AC147</f>
-        <v>6.1247407387285442</v>
+        <v>6.31713197775185</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>248</v>
@@ -36252,7 +36252,7 @@
       </c>
       <c r="C10" s="173">
         <f ca="1">Statement!AC148</f>
-        <v>4.7332202062505058</v>
+        <v>4.8819008017069789</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -36272,7 +36272,7 @@
       </c>
       <c r="C11" s="173">
         <f ca="1">Statement!AC151</f>
-        <v>5.0059656140338626</v>
+        <v>5.2020758042344024</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -36281,7 +36281,7 @@
       </c>
       <c r="C12" s="173">
         <f ca="1">Statement!AC152</f>
-        <v>36.488784034121657</v>
+        <v>37.918242989464296</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
@@ -36517,7 +36517,7 @@
       </c>
       <c r="C38" s="174">
         <f ca="1">Statement!AC158</f>
-        <v>2.2020732823132085E-2</v>
+        <v>2.1350081000918408E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>274</v>
@@ -36533,7 +36533,7 @@
       </c>
       <c r="C39" s="214">
         <f ca="1">Statement!AC157</f>
-        <v>3.5367356713704938E-2</v>
+        <v>3.4290227155055059E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>276</v>
@@ -36565,7 +36565,7 @@
       </c>
       <c r="C41" s="174">
         <f ca="1">Statement!AC160</f>
-        <v>9.7368646837433948E-3</v>
+        <v>9.4403238694458404E-3</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -36574,7 +36574,7 @@
       </c>
       <c r="C42" s="174">
         <f ca="1">Statement!AC161</f>
-        <v>9.7368646837433948E-3</v>
+        <v>9.4403238694458404E-3</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
@@ -36618,7 +36618,7 @@
       </c>
       <c r="F48" s="174">
         <f ca="1">Statement!AC172</f>
-        <v>0.19816449433988276</v>
+        <v>0.19212930103843701</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
@@ -36797,7 +36797,7 @@
       </c>
       <c r="I6" s="171">
         <f ca="1">Statement!AC116</f>
-        <v>142.62</v>
+        <v>147.1</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -36826,7 +36826,7 @@
       </c>
       <c r="I7" s="172">
         <f ca="1">Statement!AC149</f>
-        <v>7148399.6400000006</v>
+        <v>7372946.1999999993</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -36855,7 +36855,7 @@
       </c>
       <c r="I8" s="172">
         <f ca="1">Statement!AC150</f>
-        <v>5731840.6400000006</v>
+        <v>5956387.1999999993</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -36884,7 +36884,7 @@
       </c>
       <c r="I9" s="173">
         <f ca="1">Statement!AC146</f>
-        <v>45.411749374186655</v>
+        <v>46.838229792054811</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -36913,7 +36913,7 @@
       </c>
       <c r="I10" s="173">
         <f ca="1">Statement!AC147</f>
-        <v>6.1247407387285442</v>
+        <v>6.31713197775185</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -36942,7 +36942,7 @@
       </c>
       <c r="I11" s="173">
         <f ca="1">Statement!AC148</f>
-        <v>4.7332202062505058</v>
+        <v>4.8819008017069789</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -36971,7 +36971,7 @@
       </c>
       <c r="I12" s="173">
         <f ca="1">Statement!AC151</f>
-        <v>5.0059656140338626</v>
+        <v>5.2020758042344024</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -37000,7 +37000,7 @@
       </c>
       <c r="I13" s="173">
         <f ca="1">Statement!AC152</f>
-        <v>36.488784034121657</v>
+        <v>37.918242989464296</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -37773,7 +37773,7 @@
       </c>
       <c r="I51" s="174">
         <f ca="1">Statement!AC158</f>
-        <v>2.2020732823132085E-2</v>
+        <v>2.1350081000918408E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -37802,7 +37802,7 @@
       </c>
       <c r="I52" s="174">
         <f ca="1">Statement!AC157</f>
-        <v>3.5367356713704938E-2</v>
+        <v>3.4290227155055059E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -37860,7 +37860,7 @@
       </c>
       <c r="I54" s="174">
         <f ca="1">Statement!AC160</f>
-        <v>9.7368646837433948E-3</v>
+        <v>9.4403238694458404E-3</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -37889,7 +37889,7 @@
       </c>
       <c r="I55" s="174">
         <f ca="1">Statement!AC161</f>
-        <v>9.7368646837433948E-3</v>
+        <v>9.4403238694458404E-3</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -38125,7 +38125,7 @@
       </c>
       <c r="I68" s="195">
         <f ca="1">Statement!AC172</f>
-        <v>0.19816449433988276</v>
+        <v>0.19212930103843701</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -38668,14 +38668,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="261" t="s">
+      <c r="C3" s="259" t="s">
         <v>317</v>
       </c>
-      <c r="D3" s="262"/>
-      <c r="F3" s="263" t="s">
+      <c r="D3" s="260"/>
+      <c r="F3" s="261" t="s">
         <v>318</v>
       </c>
-      <c r="G3" s="262"/>
+      <c r="G3" s="260"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -38742,19 +38742,19 @@
       <c r="B7" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C7" s="259">
+      <c r="C7" s="262">
         <f>Statement!AA89</f>
         <v>2.2218264392893719E-2</v>
       </c>
-      <c r="D7" s="260"/>
-      <c r="F7" s="259">
+      <c r="D7" s="263"/>
+      <c r="F7" s="262">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.18309713991239371</v>
       </c>
-      <c r="G7" s="260"/>
+      <c r="G7" s="263"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="206" t="s">
@@ -38781,19 +38781,19 @@
       <c r="B9" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C9" s="259">
+      <c r="C9" s="262">
         <f>Statement!AA90</f>
         <v>3.6046202026093238E-2</v>
       </c>
-      <c r="D9" s="260"/>
-      <c r="F9" s="259">
+      <c r="D9" s="263"/>
+      <c r="F9" s="262">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.17263647322197348</v>
       </c>
-      <c r="G9" s="260"/>
+      <c r="G9" s="263"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="206" t="s">
@@ -38820,19 +38820,19 @@
       <c r="B11" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C11" s="259">
+      <c r="C11" s="262">
         <f>Statement!AA91</f>
         <v>1.710027405488606E-2</v>
       </c>
-      <c r="D11" s="260"/>
-      <c r="F11" s="259">
+      <c r="D11" s="263"/>
+      <c r="F11" s="262">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>0.1870895657269924</v>
       </c>
-      <c r="G11" s="260"/>
+      <c r="G11" s="263"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="206" t="s">
@@ -38859,19 +38859,19 @@
       <c r="B13" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C13" s="259">
+      <c r="C13" s="262">
         <f>Statement!AA95</f>
         <v>8.4392741251357012E-2</v>
       </c>
-      <c r="D13" s="260"/>
-      <c r="F13" s="259">
+      <c r="D13" s="263"/>
+      <c r="F13" s="262">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.22501976973287405</v>
       </c>
-      <c r="G13" s="260"/>
+      <c r="G13" s="263"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="206" t="s">
@@ -38898,19 +38898,19 @@
       <c r="B15" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C15" s="259">
+      <c r="C15" s="262">
         <f>Statement!AA96</f>
         <v>-0.23765355851505829</v>
       </c>
-      <c r="D15" s="260"/>
-      <c r="F15" s="259">
+      <c r="D15" s="263"/>
+      <c r="F15" s="262">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>1.7444474417768186E-2</v>
       </c>
-      <c r="G15" s="260"/>
+      <c r="G15" s="263"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="206" t="s">
@@ -38937,19 +38937,19 @@
       <c r="B17" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C17" s="259">
+      <c r="C17" s="262">
         <f>Statement!AA98</f>
         <v>-0.23704555913483663</v>
       </c>
-      <c r="D17" s="260"/>
-      <c r="F17" s="259">
+      <c r="D17" s="263"/>
+      <c r="F17" s="262">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>-0.25955204216073779</v>
       </c>
-      <c r="G17" s="260"/>
+      <c r="G17" s="263"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="206" t="s">
@@ -38976,22 +38976,22 @@
       <c r="B19" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C19" s="259">
+      <c r="C19" s="262">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>2.5565842762241744E-2</v>
       </c>
-      <c r="D19" s="260"/>
-      <c r="F19" s="259">
+      <c r="D19" s="263"/>
+      <c r="F19" s="262">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>2.5293753865182372E-2</v>
       </c>
-      <c r="G19" s="260"/>
+      <c r="G19" s="263"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="206" t="s">
@@ -39018,22 +39018,22 @@
       <c r="B21" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C21" s="259">
+      <c r="C21" s="262">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>-0.2584269662921348</v>
       </c>
-      <c r="D21" s="260"/>
-      <c r="F21" s="259">
+      <c r="D21" s="263"/>
+      <c r="F21" s="262">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>-0.27472527472527469</v>
       </c>
-      <c r="G21" s="260"/>
+      <c r="G21" s="263"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -39082,22 +39082,22 @@
       <c r="B25" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C25" s="259">
+      <c r="C25" s="262">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>2.840483364420425E-2</v>
       </c>
-      <c r="D25" s="260"/>
-      <c r="F25" s="259">
+      <c r="D25" s="263"/>
+      <c r="F25" s="262">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>0.22478379327694395</v>
       </c>
-      <c r="G25" s="260"/>
+      <c r="G25" s="263"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="str">
@@ -39125,22 +39125,22 @@
       <c r="B27" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C27" s="259">
+      <c r="C27" s="262">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>2.1247695740758708E-2</v>
       </c>
-      <c r="D27" s="260"/>
-      <c r="F27" s="259">
+      <c r="D27" s="263"/>
+      <c r="F27" s="262">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>2.1792942775323981E-2</v>
       </c>
-      <c r="G27" s="260"/>
+      <c r="G27" s="263"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="str">
@@ -39168,22 +39168,22 @@
       <c r="B29" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C29" s="259">
+      <c r="C29" s="262">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>-0.10674206945303526</v>
       </c>
-      <c r="D29" s="260"/>
-      <c r="F29" s="259">
+      <c r="D29" s="263"/>
+      <c r="F29" s="262">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>2.0816812053925456E-3</v>
       </c>
-      <c r="G29" s="260"/>
+      <c r="G29" s="263"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="str">
@@ -39211,22 +39211,22 @@
       <c r="B31" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C31" s="259">
+      <c r="C31" s="262">
         <f>IF(C30=0,
 IF(D30=0,0,IF(D30&gt;0,1,-1)),
 (D30-C30)/ABS(C30)
 )</f>
         <v>-5.2569263556713236E-2</v>
       </c>
-      <c r="D31" s="260"/>
-      <c r="F31" s="259">
+      <c r="D31" s="263"/>
+      <c r="F31" s="262">
         <f>IF(F30=0,
 IF(G30=0,0,IF(G30&gt;0,1,-1)),
 (G30-F30)/ABS(F30)
 )</f>
         <v>-0.22983638113570742</v>
       </c>
-      <c r="G31" s="260"/>
+      <c r="G31" s="263"/>
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B32" s="20" t="str">
@@ -39254,22 +39254,22 @@
       <c r="B33" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C33" s="259">
+      <c r="C33" s="262">
         <f>IF(C32=0,
 IF(D32=0,0,IF(D32&gt;0,1,-1)),
 (D32-C32)/ABS(C32)
 )</f>
         <v>0.84164222873900296</v>
       </c>
-      <c r="D33" s="260"/>
-      <c r="F33" s="259">
+      <c r="D33" s="263"/>
+      <c r="F33" s="262">
         <f>IF(F32=0,
 IF(G32=0,0,IF(G32&gt;0,1,-1)),
 (G32-F32)/ABS(F32)
 )</f>
         <v>1.482213438735178</v>
       </c>
-      <c r="G33" s="260"/>
+      <c r="G33" s="263"/>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B35" s="8" t="s">
@@ -39318,22 +39318,22 @@
       <c r="B37" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C37" s="259">
+      <c r="C37" s="262">
         <f>IF(C36=0,
 IF(D36=0,0,IF(D36&gt;0,1,-1)),
 (D36-C36)/ABS(C36)
 )</f>
         <v>3.8938053097345132E-2</v>
       </c>
-      <c r="D37" s="260"/>
-      <c r="F37" s="259">
+      <c r="D37" s="263"/>
+      <c r="F37" s="262">
         <f>IF(F36=0,
 IF(G36=0,0,IF(G36&gt;0,1,-1)),
 (G36-F36)/ABS(F36)
 )</f>
         <v>0.23060796645702306</v>
       </c>
-      <c r="G37" s="260"/>
+      <c r="G37" s="263"/>
     </row>
     <row r="38" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="str">
@@ -39361,22 +39361,22 @@
       <c r="B39" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C39" s="259">
+      <c r="C39" s="262">
         <f>IF(C38=0,
 IF(D38=0,0,IF(D38&gt;0,1,-1)),
 (D38-C38)/ABS(C38)
 )</f>
         <v>2.0319303338171262E-2</v>
       </c>
-      <c r="D39" s="260"/>
-      <c r="F39" s="259">
+      <c r="D39" s="263"/>
+      <c r="F39" s="262">
         <f>IF(F38=0,
 IF(G38=0,0,IF(G38&gt;0,1,-1)),
 (G38-F38)/ABS(F38)
 )</f>
         <v>9.5869056897895558E-2</v>
       </c>
-      <c r="G39" s="260"/>
+      <c r="G39" s="263"/>
     </row>
     <row r="40" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B40" s="20" t="str">
@@ -39404,22 +39404,22 @@
       <c r="B41" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C41" s="259">
+      <c r="C41" s="262">
         <f>IF(C40=0,
 IF(D40=0,0,IF(D40&gt;0,1,-1)),
 (D40-C40)/ABS(C40)
 )</f>
         <v>1.6E-2</v>
       </c>
-      <c r="D41" s="260"/>
-      <c r="F41" s="259">
+      <c r="D41" s="263"/>
+      <c r="F41" s="262">
         <f>IF(F40=0,
 IF(G40=0,0,IF(G40&gt;0,1,-1)),
 (G40-F40)/ABS(F40)
 )</f>
         <v>0.16513761467889909</v>
       </c>
-      <c r="G41" s="260"/>
+      <c r="G41" s="263"/>
     </row>
     <row r="42" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B42" s="20" t="str">
@@ -39447,22 +39447,22 @@
       <c r="B43" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C43" s="259">
+      <c r="C43" s="262">
         <f>IF(C42=0,
 IF(D42=0,0,IF(D42&gt;0,1,-1)),
 (D42-C42)/ABS(C42)
 )</f>
         <v>2.0750199521149242E-2</v>
       </c>
-      <c r="D43" s="260"/>
-      <c r="F43" s="259">
+      <c r="D43" s="263"/>
+      <c r="F43" s="262">
         <f>IF(F42=0,
 IF(G42=0,0,IF(G42&gt;0,1,-1)),
 (G42-F42)/ABS(F42)
 )</f>
         <v>8.9437819420783646E-2</v>
       </c>
-      <c r="G43" s="260"/>
+      <c r="G43" s="263"/>
     </row>
     <row r="44" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B44" s="20" t="str">
@@ -39490,22 +39490,22 @@
       <c r="B45" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C45" s="259">
+      <c r="C45" s="262">
         <f>IF(C44=0,
 IF(D44=0,0,IF(D44&gt;0,1,-1)),
 (D44-C44)/ABS(C44)
 )</f>
         <v>1.2209481933271921E-2</v>
       </c>
-      <c r="D45" s="260"/>
-      <c r="F45" s="259">
+      <c r="D45" s="263"/>
+      <c r="F45" s="262">
         <f>IF(F44=0,
 IF(G44=0,0,IF(G44&gt;0,1,-1)),
 (G44-F44)/ABS(F44)
 )</f>
         <v>5.119238950540856E-2</v>
       </c>
-      <c r="G45" s="260"/>
+      <c r="G45" s="263"/>
     </row>
     <row r="46" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="str">
@@ -39533,22 +39533,22 @@
       <c r="B47" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C47" s="259">
+      <c r="C47" s="262">
         <f>IF(C46=0,
 IF(D46=0,0,IF(D46&gt;0,1,-1)),
 (D46-C46)/ABS(C46)
 )</f>
         <v>1.8247963846473435E-2</v>
       </c>
-      <c r="D47" s="260"/>
-      <c r="F47" s="259">
+      <c r="D47" s="263"/>
+      <c r="F47" s="262">
         <f>IF(F46=0,
 IF(G46=0,0,IF(G46&gt;0,1,-1)),
 (G46-F46)/ABS(F46)
 )</f>
         <v>0.1229516507570132</v>
       </c>
-      <c r="G47" s="260"/>
+      <c r="G47" s="263"/>
     </row>
     <row r="48" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B48" s="20" t="str">
@@ -39576,22 +39576,22 @@
       <c r="B49" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C49" s="259">
+      <c r="C49" s="262">
         <f>IF(C48=0,
 IF(D48=0,0,IF(D48&gt;0,1,-1)),
 (D48-C48)/ABS(C48)
 )</f>
         <v>-4.2332859174963834E-3</v>
       </c>
-      <c r="D49" s="260"/>
-      <c r="F49" s="259">
+      <c r="D49" s="263"/>
+      <c r="F49" s="262">
         <f>IF(F48=0,
 IF(G48=0,0,IF(G48&gt;0,1,-1)),
 (G48-F48)/ABS(F48)
 )</f>
         <v>6.3208790635154666E-2</v>
       </c>
-      <c r="G49" s="260"/>
+      <c r="G49" s="263"/>
     </row>
     <row r="50" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B50" s="20" t="str">
@@ -39619,22 +39619,22 @@
       <c r="B51" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C51" s="259">
+      <c r="C51" s="262">
         <f>IF(C50=0,
 IF(D50=0,0,IF(D50&gt;0,1,-1)),
 (D50-C50)/ABS(C50)
 )</f>
         <v>4.8738292663854846E-4</v>
       </c>
-      <c r="D51" s="260"/>
-      <c r="F51" s="259">
+      <c r="D51" s="263"/>
+      <c r="F51" s="262">
         <f>IF(F50=0,
 IF(G50=0,0,IF(G50&gt;0,1,-1)),
 (G50-F50)/ABS(F50)
 )</f>
         <v>-6.2091544317255373E-2</v>
       </c>
-      <c r="G51" s="260"/>
+      <c r="G51" s="263"/>
     </row>
     <row r="52" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="str">
@@ -39662,43 +39662,39 @@
       <c r="B53" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C53" s="259">
+      <c r="C53" s="262">
         <f>IF(C52=0,
 IF(D52=0,0,IF(D52&gt;0,1,-1)),
 (D52-C52)/ABS(C52)
 )</f>
         <v>-8.8077740902117604E-2</v>
       </c>
-      <c r="D53" s="260"/>
-      <c r="F53" s="259">
+      <c r="D53" s="263"/>
+      <c r="F53" s="262">
         <f>IF(F52=0,
 IF(G52=0,0,IF(G52&gt;0,1,-1)),
 (G52-F52)/ABS(F52)
 )</f>
         <v>-0.37416005758387127</v>
       </c>
-      <c r="G53" s="260"/>
+      <c r="G53" s="263"/>
     </row>
   </sheetData>
   <mergeCells count="46">
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C53:D53"/>
+    <mergeCell ref="F53:G53"/>
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="F47:G47"/>
+    <mergeCell ref="C49:D49"/>
+    <mergeCell ref="F49:G49"/>
+    <mergeCell ref="C51:D51"/>
+    <mergeCell ref="F51:G51"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="F41:G41"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="F43:G43"/>
+    <mergeCell ref="C45:D45"/>
+    <mergeCell ref="F45:G45"/>
     <mergeCell ref="C37:D37"/>
     <mergeCell ref="F37:G37"/>
     <mergeCell ref="C39:D39"/>
@@ -39713,20 +39709,24 @@
     <mergeCell ref="F31:G31"/>
     <mergeCell ref="C33:D33"/>
     <mergeCell ref="F33:G33"/>
-    <mergeCell ref="C41:D41"/>
-    <mergeCell ref="F41:G41"/>
-    <mergeCell ref="C43:D43"/>
-    <mergeCell ref="F43:G43"/>
-    <mergeCell ref="C45:D45"/>
-    <mergeCell ref="F45:G45"/>
-    <mergeCell ref="C53:D53"/>
-    <mergeCell ref="F53:G53"/>
-    <mergeCell ref="C47:D47"/>
-    <mergeCell ref="F47:G47"/>
-    <mergeCell ref="C49:D49"/>
-    <mergeCell ref="F49:G49"/>
-    <mergeCell ref="C51:D51"/>
-    <mergeCell ref="F51:G51"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/DUOL.xlsx
+++ b/DUOL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11004"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06D2F34A-7CAC-C44C-88A2-44D2F50F88AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEBF78DB-FF24-7D4A-86EF-77FFA42CAC6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" activeTab="2" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="10" activeTab="20" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -2421,6 +2421,12 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2430,10 +2436,10 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2445,23 +2451,17 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -13155,13 +13155,13 @@
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>353</v>
+    <v>343.99799999999999</v>
     <v>87.89</v>
-    <v>1.0652999999999999</v>
-    <v>2.83</v>
-    <v>1.9616000000000001E-2</v>
-    <v>-0.6</v>
-    <v>-4.0790000000000002E-3</v>
+    <v>1.0680000000000001</v>
+    <v>-1.3</v>
+    <v>-8.5970000000000005E-3</v>
+    <v>-7.0000000000000007E-2</v>
+    <v>-4.6690000000000002E-4</v>
     <v>USD</v>
     <v>Duolingo, Inc. is a technology company. The Company is engaged in offering a mobile learning platform, as well as a digital English language proficiency assessment exam. It operates a freemium business model, namely, the app and the Website are accessible free of charge, although Duolingo also offers premium services for a subscription fee. Its solutions consist of the Duolingo App, Super Duolingo, Duolingo Max, Duolingo English Test: AI-Driven Language Assessment, Duolingo for Schools, and Duolingo ABC. The Duolingo App offers courses in over 40 different languages, including Spanish, English, French, German, Italian, Portuguese, Japanese and Chinese. Duolingo can also be accessed on desktop computers via a Web browser. Its subscription offering, Super Duolingo, offers learners additional features to enhance their learning experience. The Duolingo English Test is an online, on-demand, high-stakes English proficiency assessment. It also operates an animation and motion design studio.</v>
     <v>900</v>
@@ -13169,25 +13169,25 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>5900 PENN AVE, SECOND FLOOR, PITTSBURGH, PA, 15206 US</v>
-    <v>147.75</v>
+    <v>152.46</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46300.888250821095</v>
+    <v>46304.998811527345</v>
     <v>0</v>
-    <v>142.51</v>
-    <v>6882260317</v>
+    <v>148.52000000000001</v>
+    <v>7014197598</v>
     <v>DUOLINGO, INC.</v>
     <v>DUOLINGO, INC.</v>
-    <v>144.11000000000001</v>
-    <v>17.1965</v>
-    <v>144.27000000000001</v>
-    <v>147.1</v>
-    <v>146.5</v>
+    <v>150.61000000000001</v>
+    <v>18.024899999999999</v>
+    <v>151.22</v>
+    <v>149.91999999999999</v>
+    <v>149.85</v>
     <v>46786270</v>
     <v>DUOL</v>
     <v>DUOLINGO, INC. (XNAS:DUOL)</v>
-    <v>841329</v>
-    <v>1139471</v>
+    <v>621975</v>
+    <v>1063100</v>
     <v>2011</v>
   </rv>
   <rv s="2">
@@ -13209,19 +13209,19 @@
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>53.42</v>
+    <v>53.64</v>
     <v>39.47</v>
-    <v>0.4</v>
-    <v>7.6380000000000007E-3</v>
+    <v>0.13</v>
+    <v>2.4849999999999998E-3</v>
     <v>US</v>
-    <v>52.98</v>
+    <v>52.8</v>
     <v>Index</v>
     <v>3</v>
-    <v>51.57</v>
+    <v>52.34</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>52.16</v>
-    <v>52.37</v>
-    <v>52.77</v>
+    <v>52.36</v>
+    <v>52.31</v>
+    <v>52.44</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -13443,9 +13443,9 @@
       <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq Last Sale</v>
+      <v>Source: Nasdaq</v>
       <v>GMT</v>
-      <v>Real-Time Nasdaq Last Sale</v>
+      <v>Delayed 15 minutes</v>
       <v>from close</v>
       <v>from close</v>
     </spb>
@@ -14042,7 +14042,7 @@
       </c>
       <c r="F3" s="186">
         <f ca="1">Statement!AC149</f>
-        <v>7372946.1999999993</v>
+        <v>7514290.2399999993</v>
       </c>
       <c r="H3" s="184" t="str">
         <f>'AVG target price'!B5</f>
@@ -14050,7 +14050,7 @@
       </c>
       <c r="I3" s="210">
         <f ca="1">'AVG target price'!C5</f>
-        <v>141.85646777088763</v>
+        <v>142.18891938665595</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.2">
@@ -14066,7 +14066,7 @@
       </c>
       <c r="F4" s="187">
         <f ca="1">Statement!AC150</f>
-        <v>5956387.1999999993</v>
+        <v>6097731.2399999993</v>
       </c>
       <c r="H4" s="184" t="str">
         <f>'AVG target price'!B6</f>
@@ -14074,7 +14074,7 @@
       </c>
       <c r="I4" s="210">
         <f ca="1">'AVG target price'!C6</f>
-        <v>195.67850504708815</v>
+        <v>195.82972873595637</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.2">
@@ -14083,7 +14083,7 @@
       </c>
       <c r="C5" s="207" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>147.1</v>
+        <v>149.91999999999999</v>
       </c>
       <c r="E5" s="184" t="s">
         <v>247</v>
@@ -14098,7 +14098,7 @@
       </c>
       <c r="I5" s="210">
         <f ca="1">'AVG target price'!C7</f>
-        <v>157.43103021510453</v>
+        <v>157.58022062820396</v>
       </c>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.2">
@@ -14107,14 +14107,14 @@
       </c>
       <c r="C6" s="207" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>146.5</v>
+        <v>149.85</v>
       </c>
       <c r="E6" s="184" t="s">
         <v>241</v>
       </c>
       <c r="F6" s="189">
         <f ca="1">Statement!AC146</f>
-        <v>46.838229792054811</v>
+        <v>47.736148269373601</v>
       </c>
       <c r="H6" s="184" t="str">
         <f>'AVG target price'!B8</f>
@@ -14122,7 +14122,7 @@
       </c>
       <c r="I6" s="210">
         <f ca="1">'AVG target price'!C8</f>
-        <v>201.12541635063448</v>
+        <v>201.2818018360455</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -14131,14 +14131,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>2.83</v>
+        <v>-1.3</v>
       </c>
       <c r="E7" s="185" t="s">
         <v>205</v>
       </c>
       <c r="F7" s="190">
         <f ca="1">Statement!AC147</f>
-        <v>6.31713197775185</v>
+        <v>6.4382353916013413</v>
       </c>
       <c r="H7" s="184" t="str">
         <f>'AVG target price'!B9</f>
@@ -14146,7 +14146,7 @@
       </c>
       <c r="I7" s="210">
         <f ca="1">'AVG target price'!C9</f>
-        <v>201.54167708597421</v>
+        <v>201.69845704324368</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -14155,14 +14155,14 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>-0.6</v>
+        <v>-7.0000000000000007E-2</v>
       </c>
       <c r="E8" s="184" t="s">
         <v>269</v>
       </c>
       <c r="F8" s="191">
         <f ca="1">Statement!AC157</f>
-        <v>3.4290227155055059E-2</v>
+        <v>3.3645226884395675E-2</v>
       </c>
       <c r="H8" s="183" t="str">
         <f>'AVG target price'!B10</f>
@@ -14170,7 +14170,7 @@
       </c>
       <c r="I8" s="211">
         <f ca="1">'AVG target price'!C10</f>
-        <v>179.52661929393781</v>
+        <v>179.71582552602109</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -14179,14 +14179,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>1.9616000000000001E-2</v>
+        <v>-8.5970000000000005E-3</v>
       </c>
       <c r="E9" s="184" t="s">
         <v>292</v>
       </c>
       <c r="F9" s="191">
         <f ca="1">Statement!AC158</f>
-        <v>2.1350081000918408E-2</v>
+        <v>2.0948485293723975E-2</v>
       </c>
       <c r="H9" s="183" t="str">
         <f>'AVG target price'!B12</f>
@@ -14194,7 +14194,7 @@
       </c>
       <c r="I9" s="212">
         <f ca="1">'AVG target price'!C12</f>
-        <v>0.2204392881980817</v>
+        <v>0.19874483408498603</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -14203,14 +14203,14 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>-4.0790000000000002E-3</v>
+        <v>-4.6690000000000002E-4</v>
       </c>
       <c r="E10" s="184" t="s">
         <v>297</v>
       </c>
       <c r="F10" s="191">
         <f ca="1">Statement!AC160</f>
-        <v>9.4403238694458404E-3</v>
+        <v>9.2627510752099993E-3</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -14219,7 +14219,7 @@
       </c>
       <c r="C11" s="208" cm="1">
         <f t="array" aca="1" ref="C11" ca="1">_FV(C3,"52 week high",TRUE)</f>
-        <v>353</v>
+        <v>343.99799999999999</v>
       </c>
       <c r="E11" s="185" t="s">
         <v>293</v>
@@ -14258,7 +14258,7 @@
       </c>
       <c r="C13" s="208" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>1.0652999999999999</v>
+        <v>1.0680000000000001</v>
       </c>
       <c r="E13" s="184" t="s">
         <v>104</v>
@@ -14272,7 +14272,7 @@
       </c>
       <c r="I13" s="212">
         <f>'Reverse DCF'!C17</f>
-        <v>0.27</v>
+        <v>0.28999999999999998</v>
       </c>
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.2">
@@ -14281,7 +14281,7 @@
       </c>
       <c r="C14" s="209" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>1139471</v>
+        <v>1063100</v>
       </c>
       <c r="E14" s="185" t="s">
         <v>105</v>
@@ -14297,7 +14297,7 @@
       </c>
       <c r="F15" s="191">
         <f ca="1">Statement!AC172</f>
-        <v>0.19212930103843701</v>
+        <v>0.18851534273448561</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -14407,7 +14407,7 @@
       </c>
       <c r="F26" s="218" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>52.77</v>
+        <v>52.44</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -14422,7 +14422,7 @@
       </c>
       <c r="F27" s="219">
         <f ca="1">F26/1000</f>
-        <v>5.2770000000000004E-2</v>
+        <v>5.2440000000000001E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -14704,8 +14704,8 @@
       <c r="D2" s="258"/>
       <c r="E2" s="258"/>
       <c r="F2" s="258"/>
-      <c r="G2" s="267"/>
-      <c r="H2" s="268" t="s">
+      <c r="G2" s="264"/>
+      <c r="H2" s="265" t="s">
         <v>114</v>
       </c>
       <c r="I2" s="258"/>
@@ -14738,32 +14738,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="264" t="s">
+      <c r="C4" s="266" t="s">
         <v>116</v>
       </c>
-      <c r="D4" s="264"/>
-      <c r="E4" s="264"/>
-      <c r="F4" s="264"/>
-      <c r="G4" s="264"/>
-      <c r="H4" s="264"/>
-      <c r="I4" s="264"/>
-      <c r="J4" s="264"/>
-      <c r="K4" s="264"/>
-      <c r="L4" s="264"/>
+      <c r="D4" s="266"/>
+      <c r="E4" s="266"/>
+      <c r="F4" s="266"/>
+      <c r="G4" s="266"/>
+      <c r="H4" s="266"/>
+      <c r="I4" s="266"/>
+      <c r="J4" s="266"/>
+      <c r="K4" s="266"/>
+      <c r="L4" s="266"/>
       <c r="O4" s="5"/>
-      <c r="S4" s="265" t="s">
+      <c r="S4" s="267" t="s">
         <v>116</v>
       </c>
-      <c r="T4" s="266"/>
-      <c r="U4" s="266"/>
-      <c r="V4" s="266"/>
-      <c r="W4" s="266"/>
-      <c r="X4" s="266"/>
-      <c r="Y4" s="266"/>
-      <c r="Z4" s="266"/>
-      <c r="AA4" s="266"/>
-      <c r="AB4" s="266"/>
-      <c r="AC4" s="266"/>
+      <c r="T4" s="268"/>
+      <c r="U4" s="268"/>
+      <c r="V4" s="268"/>
+      <c r="W4" s="268"/>
+      <c r="X4" s="268"/>
+      <c r="Y4" s="268"/>
+      <c r="Z4" s="268"/>
+      <c r="AA4" s="268"/>
+      <c r="AB4" s="268"/>
+      <c r="AC4" s="268"/>
       <c r="AE4" s="88"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -15451,33 +15451,33 @@
       <c r="Q12" s="92"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="264" t="s">
+      <c r="C13" s="266" t="s">
         <v>122</v>
       </c>
-      <c r="D13" s="264"/>
-      <c r="E13" s="264"/>
-      <c r="F13" s="264"/>
-      <c r="G13" s="264"/>
-      <c r="H13" s="264"/>
-      <c r="I13" s="264"/>
-      <c r="J13" s="264"/>
-      <c r="K13" s="264"/>
-      <c r="L13" s="264"/>
+      <c r="D13" s="266"/>
+      <c r="E13" s="266"/>
+      <c r="F13" s="266"/>
+      <c r="G13" s="266"/>
+      <c r="H13" s="266"/>
+      <c r="I13" s="266"/>
+      <c r="J13" s="266"/>
+      <c r="K13" s="266"/>
+      <c r="L13" s="266"/>
       <c r="O13" s="5"/>
       <c r="Q13" s="92"/>
-      <c r="S13" s="265" t="s">
+      <c r="S13" s="267" t="s">
         <v>122</v>
       </c>
-      <c r="T13" s="266"/>
-      <c r="U13" s="266"/>
-      <c r="V13" s="266"/>
-      <c r="W13" s="266"/>
-      <c r="X13" s="266"/>
-      <c r="Y13" s="266"/>
-      <c r="Z13" s="266"/>
-      <c r="AA13" s="266"/>
-      <c r="AB13" s="266"/>
-      <c r="AC13" s="266"/>
+      <c r="T13" s="268"/>
+      <c r="U13" s="268"/>
+      <c r="V13" s="268"/>
+      <c r="W13" s="268"/>
+      <c r="X13" s="268"/>
+      <c r="Y13" s="268"/>
+      <c r="Z13" s="268"/>
+      <c r="AA13" s="268"/>
+      <c r="AB13" s="268"/>
+      <c r="AC13" s="268"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B14" s="16" t="s">
@@ -16086,33 +16086,33 @@
       <c r="Q22" s="92"/>
     </row>
     <row r="23" spans="2:31" x14ac:dyDescent="0.2">
-      <c r="C23" s="264" t="s">
+      <c r="C23" s="266" t="s">
         <v>124</v>
       </c>
-      <c r="D23" s="264"/>
-      <c r="E23" s="264"/>
-      <c r="F23" s="264"/>
-      <c r="G23" s="264"/>
-      <c r="H23" s="264"/>
-      <c r="I23" s="264"/>
-      <c r="J23" s="264"/>
-      <c r="K23" s="264"/>
-      <c r="L23" s="264"/>
+      <c r="D23" s="266"/>
+      <c r="E23" s="266"/>
+      <c r="F23" s="266"/>
+      <c r="G23" s="266"/>
+      <c r="H23" s="266"/>
+      <c r="I23" s="266"/>
+      <c r="J23" s="266"/>
+      <c r="K23" s="266"/>
+      <c r="L23" s="266"/>
       <c r="O23" s="5"/>
       <c r="Q23" s="92"/>
-      <c r="S23" s="265" t="s">
+      <c r="S23" s="267" t="s">
         <v>124</v>
       </c>
-      <c r="T23" s="266"/>
-      <c r="U23" s="266"/>
-      <c r="V23" s="266"/>
-      <c r="W23" s="266"/>
-      <c r="X23" s="266"/>
-      <c r="Y23" s="266"/>
-      <c r="Z23" s="266"/>
-      <c r="AA23" s="266"/>
-      <c r="AB23" s="266"/>
-      <c r="AC23" s="266"/>
+      <c r="T23" s="268"/>
+      <c r="U23" s="268"/>
+      <c r="V23" s="268"/>
+      <c r="W23" s="268"/>
+      <c r="X23" s="268"/>
+      <c r="Y23" s="268"/>
+      <c r="Z23" s="268"/>
+      <c r="AA23" s="268"/>
+      <c r="AB23" s="268"/>
+      <c r="AC23" s="268"/>
       <c r="AE23" s="88" t="str">
         <f>AE2</f>
         <v>TTM/YTD</v>
@@ -17431,32 +17431,32 @@
       <c r="O39" s="5"/>
     </row>
     <row r="40" spans="2:31" x14ac:dyDescent="0.2">
-      <c r="C40" s="264" t="s">
+      <c r="C40" s="266" t="s">
         <v>126</v>
       </c>
-      <c r="D40" s="264"/>
-      <c r="E40" s="264"/>
-      <c r="F40" s="264"/>
-      <c r="G40" s="264"/>
-      <c r="H40" s="264"/>
-      <c r="I40" s="264"/>
-      <c r="J40" s="264"/>
-      <c r="K40" s="264"/>
-      <c r="L40" s="264"/>
+      <c r="D40" s="266"/>
+      <c r="E40" s="266"/>
+      <c r="F40" s="266"/>
+      <c r="G40" s="266"/>
+      <c r="H40" s="266"/>
+      <c r="I40" s="266"/>
+      <c r="J40" s="266"/>
+      <c r="K40" s="266"/>
+      <c r="L40" s="266"/>
       <c r="O40" s="5"/>
-      <c r="S40" s="265" t="s">
+      <c r="S40" s="267" t="s">
         <v>126</v>
       </c>
-      <c r="T40" s="266"/>
-      <c r="U40" s="266"/>
-      <c r="V40" s="266"/>
-      <c r="W40" s="266"/>
-      <c r="X40" s="266"/>
-      <c r="Y40" s="266"/>
-      <c r="Z40" s="266"/>
-      <c r="AA40" s="266"/>
-      <c r="AB40" s="266"/>
-      <c r="AC40" s="266"/>
+      <c r="T40" s="268"/>
+      <c r="U40" s="268"/>
+      <c r="V40" s="268"/>
+      <c r="W40" s="268"/>
+      <c r="X40" s="268"/>
+      <c r="Y40" s="268"/>
+      <c r="Z40" s="268"/>
+      <c r="AA40" s="268"/>
+      <c r="AB40" s="268"/>
+      <c r="AC40" s="268"/>
     </row>
     <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -18023,18 +18023,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="C13:L13"/>
+    <mergeCell ref="S13:AC13"/>
+    <mergeCell ref="C23:L23"/>
+    <mergeCell ref="S23:AC23"/>
+    <mergeCell ref="C40:L40"/>
+    <mergeCell ref="S40:AC40"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="S2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
-    <mergeCell ref="C13:L13"/>
-    <mergeCell ref="S13:AC13"/>
-    <mergeCell ref="C23:L23"/>
-    <mergeCell ref="S23:AC23"/>
-    <mergeCell ref="C40:L40"/>
-    <mergeCell ref="S40:AC40"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -18074,8 +18074,8 @@
       <c r="D2" s="258"/>
       <c r="E2" s="258"/>
       <c r="F2" s="258"/>
-      <c r="G2" s="267"/>
-      <c r="H2" s="268" t="s">
+      <c r="G2" s="264"/>
+      <c r="H2" s="265" t="s">
         <v>114</v>
       </c>
       <c r="I2" s="258"/>
@@ -18105,31 +18105,31 @@
     <row r="4" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="264" t="s">
+      <c r="C4" s="266" t="s">
         <v>116</v>
       </c>
-      <c r="D4" s="264"/>
-      <c r="E4" s="264"/>
-      <c r="F4" s="264"/>
-      <c r="G4" s="264"/>
-      <c r="H4" s="264"/>
-      <c r="I4" s="264"/>
-      <c r="J4" s="264"/>
-      <c r="K4" s="264"/>
-      <c r="L4" s="264"/>
-      <c r="P4" s="266" t="s">
+      <c r="D4" s="266"/>
+      <c r="E4" s="266"/>
+      <c r="F4" s="266"/>
+      <c r="G4" s="266"/>
+      <c r="H4" s="266"/>
+      <c r="I4" s="266"/>
+      <c r="J4" s="266"/>
+      <c r="K4" s="266"/>
+      <c r="L4" s="266"/>
+      <c r="P4" s="268" t="s">
         <v>116</v>
       </c>
-      <c r="Q4" s="266"/>
-      <c r="R4" s="266"/>
-      <c r="S4" s="266"/>
-      <c r="T4" s="266"/>
-      <c r="U4" s="266"/>
-      <c r="V4" s="266"/>
-      <c r="W4" s="266"/>
-      <c r="X4" s="266"/>
-      <c r="Y4" s="266"/>
-      <c r="Z4" s="266"/>
+      <c r="Q4" s="268"/>
+      <c r="R4" s="268"/>
+      <c r="S4" s="268"/>
+      <c r="T4" s="268"/>
+      <c r="U4" s="268"/>
+      <c r="V4" s="268"/>
+      <c r="W4" s="268"/>
+      <c r="X4" s="268"/>
+      <c r="Y4" s="268"/>
+      <c r="Z4" s="268"/>
       <c r="AB4" s="88"/>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
@@ -18324,32 +18324,32 @@
       <c r="N8" s="92"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C9" s="264" t="s">
+      <c r="C9" s="266" t="s">
         <v>129</v>
       </c>
-      <c r="D9" s="264"/>
-      <c r="E9" s="264"/>
-      <c r="F9" s="264"/>
-      <c r="G9" s="264"/>
-      <c r="H9" s="264"/>
-      <c r="I9" s="264"/>
-      <c r="J9" s="264"/>
-      <c r="K9" s="264"/>
-      <c r="L9" s="264"/>
+      <c r="D9" s="266"/>
+      <c r="E9" s="266"/>
+      <c r="F9" s="266"/>
+      <c r="G9" s="266"/>
+      <c r="H9" s="266"/>
+      <c r="I9" s="266"/>
+      <c r="J9" s="266"/>
+      <c r="K9" s="266"/>
+      <c r="L9" s="266"/>
       <c r="N9" s="92"/>
-      <c r="P9" s="266" t="s">
+      <c r="P9" s="268" t="s">
         <v>130</v>
       </c>
-      <c r="Q9" s="266"/>
-      <c r="R9" s="266"/>
-      <c r="S9" s="266"/>
-      <c r="T9" s="266"/>
-      <c r="U9" s="266"/>
-      <c r="V9" s="266"/>
-      <c r="W9" s="266"/>
-      <c r="X9" s="266"/>
-      <c r="Y9" s="266"/>
-      <c r="Z9" s="266"/>
+      <c r="Q9" s="268"/>
+      <c r="R9" s="268"/>
+      <c r="S9" s="268"/>
+      <c r="T9" s="268"/>
+      <c r="U9" s="268"/>
+      <c r="V9" s="268"/>
+      <c r="W9" s="268"/>
+      <c r="X9" s="268"/>
+      <c r="Y9" s="268"/>
+      <c r="Z9" s="268"/>
       <c r="AB9" s="88">
         <f>AB4</f>
         <v>0</v>
@@ -18919,31 +18919,31 @@
       </c>
     </row>
     <row r="18" spans="2:26" x14ac:dyDescent="0.2">
-      <c r="C18" s="264" t="s">
+      <c r="C18" s="266" t="s">
         <v>132</v>
       </c>
-      <c r="D18" s="264"/>
-      <c r="E18" s="264"/>
-      <c r="F18" s="264"/>
-      <c r="G18" s="264"/>
-      <c r="H18" s="264"/>
-      <c r="I18" s="264"/>
-      <c r="J18" s="264"/>
-      <c r="K18" s="264"/>
-      <c r="L18" s="264"/>
-      <c r="P18" s="266" t="s">
+      <c r="D18" s="266"/>
+      <c r="E18" s="266"/>
+      <c r="F18" s="266"/>
+      <c r="G18" s="266"/>
+      <c r="H18" s="266"/>
+      <c r="I18" s="266"/>
+      <c r="J18" s="266"/>
+      <c r="K18" s="266"/>
+      <c r="L18" s="266"/>
+      <c r="P18" s="268" t="s">
         <v>132</v>
       </c>
-      <c r="Q18" s="266"/>
-      <c r="R18" s="266"/>
-      <c r="S18" s="266"/>
-      <c r="T18" s="266"/>
-      <c r="U18" s="266"/>
-      <c r="V18" s="266"/>
-      <c r="W18" s="266"/>
-      <c r="X18" s="266"/>
-      <c r="Y18" s="266"/>
-      <c r="Z18" s="266"/>
+      <c r="Q18" s="268"/>
+      <c r="R18" s="268"/>
+      <c r="S18" s="268"/>
+      <c r="T18" s="268"/>
+      <c r="U18" s="268"/>
+      <c r="V18" s="268"/>
+      <c r="W18" s="268"/>
+      <c r="X18" s="268"/>
+      <c r="Y18" s="268"/>
+      <c r="Z18" s="268"/>
     </row>
     <row r="19" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -19509,8 +19509,8 @@
       <c r="D3" s="258"/>
       <c r="E3" s="258"/>
       <c r="F3" s="258"/>
-      <c r="G3" s="267"/>
-      <c r="H3" s="268" t="s">
+      <c r="G3" s="264"/>
+      <c r="H3" s="265" t="s">
         <v>114</v>
       </c>
       <c r="I3" s="258"/>
@@ -19534,18 +19534,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="87"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="264" t="s">
+      <c r="C5" s="266" t="s">
         <v>116</v>
       </c>
-      <c r="D5" s="264"/>
-      <c r="E5" s="264"/>
-      <c r="F5" s="264"/>
-      <c r="G5" s="264"/>
-      <c r="H5" s="264"/>
-      <c r="I5" s="264"/>
-      <c r="J5" s="264"/>
-      <c r="K5" s="264"/>
-      <c r="L5" s="264"/>
+      <c r="D5" s="266"/>
+      <c r="E5" s="266"/>
+      <c r="F5" s="266"/>
+      <c r="G5" s="266"/>
+      <c r="H5" s="266"/>
+      <c r="I5" s="266"/>
+      <c r="J5" s="266"/>
+      <c r="K5" s="266"/>
+      <c r="L5" s="266"/>
       <c r="P5" s="269"/>
       <c r="Q5" s="269"/>
       <c r="R5" s="269"/>
@@ -19742,18 +19742,18 @@
       <c r="N10" s="92"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="264" t="s">
+      <c r="C11" s="266" t="s">
         <v>136</v>
       </c>
-      <c r="D11" s="264"/>
-      <c r="E11" s="264"/>
-      <c r="F11" s="264"/>
-      <c r="G11" s="264"/>
-      <c r="H11" s="264"/>
-      <c r="I11" s="264"/>
-      <c r="J11" s="264"/>
-      <c r="K11" s="264"/>
-      <c r="L11" s="264"/>
+      <c r="D11" s="266"/>
+      <c r="E11" s="266"/>
+      <c r="F11" s="266"/>
+      <c r="G11" s="266"/>
+      <c r="H11" s="266"/>
+      <c r="I11" s="266"/>
+      <c r="J11" s="266"/>
+      <c r="K11" s="266"/>
+      <c r="L11" s="266"/>
       <c r="N11" s="92"/>
       <c r="P11" s="269"/>
       <c r="Q11" s="269"/>
@@ -20007,18 +20007,18 @@
       <c r="D16" s="24"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="264" t="s">
+      <c r="C18" s="266" t="s">
         <v>141</v>
       </c>
-      <c r="D18" s="264"/>
-      <c r="E18" s="264"/>
-      <c r="F18" s="264"/>
-      <c r="G18" s="264"/>
-      <c r="H18" s="264"/>
-      <c r="I18" s="264"/>
-      <c r="J18" s="264"/>
-      <c r="K18" s="264"/>
-      <c r="L18" s="264"/>
+      <c r="D18" s="266"/>
+      <c r="E18" s="266"/>
+      <c r="F18" s="266"/>
+      <c r="G18" s="266"/>
+      <c r="H18" s="266"/>
+      <c r="I18" s="266"/>
+      <c r="J18" s="266"/>
+      <c r="K18" s="266"/>
+      <c r="L18" s="266"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -20236,18 +20236,18 @@
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="111"/>
-      <c r="C26" s="264" t="s">
+      <c r="C26" s="266" t="s">
         <v>147</v>
       </c>
-      <c r="D26" s="264"/>
-      <c r="E26" s="264"/>
-      <c r="F26" s="264"/>
-      <c r="G26" s="264"/>
-      <c r="H26" s="264"/>
-      <c r="I26" s="264"/>
-      <c r="J26" s="264"/>
-      <c r="K26" s="264"/>
-      <c r="L26" s="264"/>
+      <c r="D26" s="266"/>
+      <c r="E26" s="266"/>
+      <c r="F26" s="266"/>
+      <c r="G26" s="266"/>
+      <c r="H26" s="266"/>
+      <c r="I26" s="266"/>
+      <c r="J26" s="266"/>
+      <c r="K26" s="266"/>
+      <c r="L26" s="266"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="16" t="s">
@@ -20439,18 +20439,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="111"/>
-      <c r="C33" s="264" t="s">
+      <c r="C33" s="266" t="s">
         <v>151</v>
       </c>
-      <c r="D33" s="264"/>
-      <c r="E33" s="264"/>
-      <c r="F33" s="264"/>
-      <c r="G33" s="264"/>
-      <c r="H33" s="264"/>
-      <c r="I33" s="264"/>
-      <c r="J33" s="264"/>
-      <c r="K33" s="264"/>
-      <c r="L33" s="264"/>
+      <c r="D33" s="266"/>
+      <c r="E33" s="266"/>
+      <c r="F33" s="266"/>
+      <c r="G33" s="266"/>
+      <c r="H33" s="266"/>
+      <c r="I33" s="266"/>
+      <c r="J33" s="266"/>
+      <c r="K33" s="266"/>
+      <c r="L33" s="266"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
@@ -20634,18 +20634,18 @@
       <c r="C39" s="127"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="264" t="s">
+      <c r="C40" s="266" t="s">
         <v>154</v>
       </c>
-      <c r="D40" s="264"/>
-      <c r="E40" s="264"/>
-      <c r="F40" s="264"/>
-      <c r="G40" s="264"/>
-      <c r="H40" s="264"/>
-      <c r="I40" s="264"/>
-      <c r="J40" s="264"/>
-      <c r="K40" s="264"/>
-      <c r="L40" s="264"/>
+      <c r="D40" s="266"/>
+      <c r="E40" s="266"/>
+      <c r="F40" s="266"/>
+      <c r="G40" s="266"/>
+      <c r="H40" s="266"/>
+      <c r="I40" s="266"/>
+      <c r="J40" s="266"/>
+      <c r="K40" s="266"/>
+      <c r="L40" s="266"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -20909,6 +20909,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -20916,12 +20922,6 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -20965,8 +20965,8 @@
       <c r="D2" s="258"/>
       <c r="E2" s="258"/>
       <c r="F2" s="258"/>
-      <c r="G2" s="267"/>
-      <c r="H2" s="268" t="s">
+      <c r="G2" s="264"/>
+      <c r="H2" s="265" t="s">
         <v>114</v>
       </c>
       <c r="I2" s="258"/>
@@ -20990,18 +20990,18 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="264" t="s">
+      <c r="C4" s="266" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="264"/>
-      <c r="E4" s="264"/>
-      <c r="F4" s="264"/>
-      <c r="G4" s="264"/>
-      <c r="H4" s="264"/>
-      <c r="I4" s="264"/>
-      <c r="J4" s="264"/>
-      <c r="K4" s="264"/>
-      <c r="L4" s="264"/>
+      <c r="D4" s="266"/>
+      <c r="E4" s="266"/>
+      <c r="F4" s="266"/>
+      <c r="G4" s="266"/>
+      <c r="H4" s="266"/>
+      <c r="I4" s="266"/>
+      <c r="J4" s="266"/>
+      <c r="K4" s="266"/>
+      <c r="L4" s="266"/>
       <c r="S4" s="269"/>
       <c r="T4" s="269"/>
       <c r="U4" s="269"/>
@@ -21375,18 +21375,18 @@
       <c r="AE10" s="64"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="264" t="s">
+      <c r="C13" s="266" t="s">
         <v>162</v>
       </c>
-      <c r="D13" s="264"/>
-      <c r="E13" s="264"/>
-      <c r="F13" s="264"/>
-      <c r="G13" s="264"/>
-      <c r="H13" s="264"/>
-      <c r="I13" s="264"/>
-      <c r="J13" s="264"/>
-      <c r="K13" s="264"/>
-      <c r="L13" s="264"/>
+      <c r="D13" s="266"/>
+      <c r="E13" s="266"/>
+      <c r="F13" s="266"/>
+      <c r="G13" s="266"/>
+      <c r="H13" s="266"/>
+      <c r="I13" s="266"/>
+      <c r="J13" s="266"/>
+      <c r="K13" s="266"/>
+      <c r="L13" s="266"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="12">
@@ -21479,18 +21479,18 @@
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C18" s="264" t="s">
+      <c r="C18" s="266" t="s">
         <v>163</v>
       </c>
-      <c r="D18" s="264"/>
-      <c r="E18" s="264"/>
-      <c r="F18" s="264"/>
-      <c r="G18" s="264"/>
-      <c r="H18" s="264"/>
-      <c r="I18" s="264"/>
-      <c r="J18" s="264"/>
-      <c r="K18" s="264"/>
-      <c r="L18" s="264"/>
+      <c r="D18" s="266"/>
+      <c r="E18" s="266"/>
+      <c r="F18" s="266"/>
+      <c r="G18" s="266"/>
+      <c r="H18" s="266"/>
+      <c r="I18" s="266"/>
+      <c r="J18" s="266"/>
+      <c r="K18" s="266"/>
+      <c r="L18" s="266"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -21682,18 +21682,18 @@
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C25" s="264" t="s">
+      <c r="C25" s="266" t="s">
         <v>266</v>
       </c>
-      <c r="D25" s="264"/>
-      <c r="E25" s="264"/>
-      <c r="F25" s="264"/>
-      <c r="G25" s="264"/>
-      <c r="H25" s="264"/>
-      <c r="I25" s="264"/>
-      <c r="J25" s="264"/>
-      <c r="K25" s="264"/>
-      <c r="L25" s="264"/>
+      <c r="D25" s="266"/>
+      <c r="E25" s="266"/>
+      <c r="F25" s="266"/>
+      <c r="G25" s="266"/>
+      <c r="H25" s="266"/>
+      <c r="I25" s="266"/>
+      <c r="J25" s="266"/>
+      <c r="K25" s="266"/>
+      <c r="L25" s="266"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B26" s="16" t="s">
@@ -21831,18 +21831,18 @@
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C31" s="264" t="s">
+      <c r="C31" s="266" t="s">
         <v>78</v>
       </c>
-      <c r="D31" s="264"/>
-      <c r="E31" s="264"/>
-      <c r="F31" s="264"/>
-      <c r="G31" s="264"/>
-      <c r="H31" s="264"/>
-      <c r="I31" s="264"/>
-      <c r="J31" s="264"/>
-      <c r="K31" s="264"/>
-      <c r="L31" s="264"/>
+      <c r="D31" s="266"/>
+      <c r="E31" s="266"/>
+      <c r="F31" s="266"/>
+      <c r="G31" s="266"/>
+      <c r="H31" s="266"/>
+      <c r="I31" s="266"/>
+      <c r="J31" s="266"/>
+      <c r="K31" s="266"/>
+      <c r="L31" s="266"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="16" t="s">
@@ -21981,16 +21981,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="S4:AC4"/>
+    <mergeCell ref="C13:L13"/>
+    <mergeCell ref="C18:L18"/>
     <mergeCell ref="C31:L31"/>
     <mergeCell ref="C25:L25"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="S2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="S4:AC4"/>
-    <mergeCell ref="C13:L13"/>
-    <mergeCell ref="C18:L18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -22073,7 +22073,7 @@
       </c>
       <c r="C6" s="135">
         <f ca="1">Overview!C5</f>
-        <v>147.1</v>
+        <v>149.91999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22082,7 +22082,7 @@
       </c>
       <c r="C7" s="136">
         <f ca="1">C5*C6</f>
-        <v>7372946.1999999993</v>
+        <v>7514290.2399999993</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22100,7 +22100,7 @@
       </c>
       <c r="C9" s="137">
         <f ca="1">Overview!F27</f>
-        <v>5.2770000000000004E-2</v>
+        <v>5.2440000000000001E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22109,7 +22109,7 @@
       </c>
       <c r="C10" s="135">
         <f ca="1">Overview!C13</f>
-        <v>1.0652999999999999</v>
+        <v>1.0680000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22179,7 +22179,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.10070850000000001</v>
+        <v>0.10050000000000001</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22188,7 +22188,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.10070850000000001</v>
+        <v>0.10050000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -22239,8 +22239,8 @@
       <c r="D3" s="258"/>
       <c r="E3" s="258"/>
       <c r="F3" s="258"/>
-      <c r="G3" s="267"/>
-      <c r="H3" s="268" t="s">
+      <c r="G3" s="264"/>
+      <c r="H3" s="265" t="s">
         <v>114</v>
       </c>
       <c r="I3" s="258"/>
@@ -22264,18 +22264,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="87"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="264" t="s">
+      <c r="C5" s="266" t="s">
         <v>184</v>
       </c>
-      <c r="D5" s="264"/>
-      <c r="E5" s="264"/>
-      <c r="F5" s="264"/>
-      <c r="G5" s="264"/>
-      <c r="H5" s="264"/>
-      <c r="I5" s="264"/>
-      <c r="J5" s="264"/>
-      <c r="K5" s="264"/>
-      <c r="L5" s="264"/>
+      <c r="D5" s="266"/>
+      <c r="E5" s="266"/>
+      <c r="F5" s="266"/>
+      <c r="G5" s="266"/>
+      <c r="H5" s="266"/>
+      <c r="I5" s="266"/>
+      <c r="J5" s="266"/>
+      <c r="K5" s="266"/>
+      <c r="L5" s="266"/>
       <c r="P5" s="269"/>
       <c r="Q5" s="269"/>
       <c r="R5" s="269"/>
@@ -22439,7 +22439,7 @@
       </c>
       <c r="L8" s="128">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>7254237.9223840814</v>
+        <v>7273026.8491768399</v>
       </c>
       <c r="N8" s="92"/>
       <c r="O8" s="16"/>
@@ -22493,23 +22493,23 @@
       <c r="G10" s="140"/>
       <c r="H10" s="128">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>164233.46601869952</v>
+        <v>164264.58158222964</v>
       </c>
       <c r="I10" s="128">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>198522.61236654638</v>
+        <v>198597.84341738783</v>
       </c>
       <c r="J10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>226076.73000951245</v>
+        <v>226205.25139792333</v>
       </c>
       <c r="K10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>259642.55896060905</v>
+        <v>259839.38171460424</v>
       </c>
       <c r="L10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>355262.44322596065</v>
+        <v>355599.10970518761</v>
       </c>
       <c r="N10" s="92"/>
     </row>
@@ -22528,7 +22528,7 @@
       <c r="K11" s="139"/>
       <c r="L11" s="128">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>4489833.0670311032</v>
+        <v>4505727.849680637</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
@@ -22551,7 +22551,7 @@
       </c>
       <c r="C15" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.10070850000000001</v>
+        <v>0.10050000000000001</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
@@ -22566,7 +22566,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>1203737.8105813279</v>
+        <v>1204506.1678173328</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -22575,7 +22575,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>4489833.0670311032</v>
+        <v>4505727.849680637</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -22584,7 +22584,7 @@
       </c>
       <c r="C21" s="95">
         <f ca="1">C19+C20</f>
-        <v>5693570.8776124306</v>
+        <v>5710234.0174979698</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -22611,7 +22611,7 @@
       </c>
       <c r="C24" s="95">
         <f ca="1">C21+C22-C23</f>
-        <v>7110129.8776124306</v>
+        <v>7126793.0174979698</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -22629,7 +22629,7 @@
       </c>
       <c r="C26" s="254">
         <f ca="1">C24/C25</f>
-        <v>141.85646777088763</v>
+        <v>142.18891938665595</v>
       </c>
     </row>
   </sheetData>
@@ -22678,8 +22678,8 @@
       <c r="D2" s="258"/>
       <c r="E2" s="258"/>
       <c r="F2" s="258"/>
-      <c r="G2" s="267"/>
-      <c r="H2" s="268" t="s">
+      <c r="G2" s="264"/>
+      <c r="H2" s="265" t="s">
         <v>114</v>
       </c>
       <c r="I2" s="258"/>
@@ -22691,18 +22691,18 @@
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="264" t="s">
+      <c r="C4" s="266" t="s">
         <v>198</v>
       </c>
-      <c r="D4" s="264"/>
-      <c r="E4" s="264"/>
-      <c r="F4" s="264"/>
-      <c r="G4" s="264"/>
-      <c r="H4" s="264"/>
-      <c r="I4" s="264"/>
-      <c r="J4" s="264"/>
-      <c r="K4" s="264"/>
-      <c r="L4" s="264"/>
+      <c r="D4" s="266"/>
+      <c r="E4" s="266"/>
+      <c r="F4" s="266"/>
+      <c r="G4" s="266"/>
+      <c r="H4" s="266"/>
+      <c r="I4" s="266"/>
+      <c r="J4" s="266"/>
+      <c r="K4" s="266"/>
+      <c r="L4" s="266"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -22898,23 +22898,23 @@
       <c r="G9" s="140"/>
       <c r="H9" s="93">
         <f ca="1">DCF!H10</f>
-        <v>164233.46601869952</v>
+        <v>164264.58158222964</v>
       </c>
       <c r="I9" s="93">
         <f ca="1">DCF!I10</f>
-        <v>198522.61236654638</v>
+        <v>198597.84341738783</v>
       </c>
       <c r="J9" s="93">
         <f ca="1">DCF!J10</f>
-        <v>226076.73000951245</v>
+        <v>226205.25139792333</v>
       </c>
       <c r="K9" s="93">
         <f ca="1">DCF!K10</f>
-        <v>259642.55896060905</v>
+        <v>259839.38171460424</v>
       </c>
       <c r="L9" s="93">
         <f ca="1">DCF!L10</f>
-        <v>355262.44322596065</v>
+        <v>355599.10970518761</v>
       </c>
       <c r="N9" s="92"/>
     </row>
@@ -22922,18 +22922,18 @@
       <c r="N10" s="92"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C11" s="264" t="s">
+      <c r="C11" s="266" t="s">
         <v>122</v>
       </c>
-      <c r="D11" s="264"/>
-      <c r="E11" s="264"/>
-      <c r="F11" s="264"/>
-      <c r="G11" s="264"/>
-      <c r="H11" s="264"/>
-      <c r="I11" s="264"/>
-      <c r="J11" s="264"/>
-      <c r="K11" s="264"/>
-      <c r="L11" s="264"/>
+      <c r="D11" s="266"/>
+      <c r="E11" s="266"/>
+      <c r="F11" s="266"/>
+      <c r="G11" s="266"/>
+      <c r="H11" s="266"/>
+      <c r="I11" s="266"/>
+      <c r="J11" s="266"/>
+      <c r="K11" s="266"/>
+      <c r="L11" s="266"/>
       <c r="N11" s="92"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -23127,18 +23127,18 @@
       <c r="N16" s="92"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C17" s="264" t="s">
+      <c r="C17" s="266" t="s">
         <v>200</v>
       </c>
-      <c r="D17" s="264"/>
-      <c r="E17" s="264"/>
-      <c r="F17" s="264"/>
-      <c r="G17" s="264"/>
-      <c r="H17" s="264"/>
-      <c r="I17" s="264"/>
-      <c r="J17" s="264"/>
-      <c r="K17" s="264"/>
-      <c r="L17" s="264"/>
+      <c r="D17" s="266"/>
+      <c r="E17" s="266"/>
+      <c r="F17" s="266"/>
+      <c r="G17" s="266"/>
+      <c r="H17" s="266"/>
+      <c r="I17" s="266"/>
+      <c r="J17" s="266"/>
+      <c r="K17" s="266"/>
+      <c r="L17" s="266"/>
       <c r="N17" s="92"/>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
@@ -23272,18 +23272,18 @@
       <c r="N21" s="92"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C22" s="264" t="s">
+      <c r="C22" s="266" t="s">
         <v>203</v>
       </c>
-      <c r="D22" s="264"/>
-      <c r="E22" s="264"/>
-      <c r="F22" s="264"/>
-      <c r="G22" s="264"/>
-      <c r="H22" s="264"/>
-      <c r="I22" s="264"/>
-      <c r="J22" s="264"/>
-      <c r="K22" s="264"/>
-      <c r="L22" s="264"/>
+      <c r="D22" s="266"/>
+      <c r="E22" s="266"/>
+      <c r="F22" s="266"/>
+      <c r="G22" s="266"/>
+      <c r="H22" s="266"/>
+      <c r="I22" s="266"/>
+      <c r="J22" s="266"/>
+      <c r="K22" s="266"/>
+      <c r="L22" s="266"/>
       <c r="N22" s="92"/>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.2">
@@ -23367,18 +23367,18 @@
       <c r="N26" s="92"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C27" s="264" t="s">
+      <c r="C27" s="266" t="s">
         <v>204</v>
       </c>
-      <c r="D27" s="264"/>
-      <c r="E27" s="264"/>
-      <c r="F27" s="264"/>
-      <c r="G27" s="264"/>
-      <c r="H27" s="264"/>
-      <c r="I27" s="264"/>
-      <c r="J27" s="264"/>
-      <c r="K27" s="264"/>
-      <c r="L27" s="264"/>
+      <c r="D27" s="266"/>
+      <c r="E27" s="266"/>
+      <c r="F27" s="266"/>
+      <c r="G27" s="266"/>
+      <c r="H27" s="266"/>
+      <c r="I27" s="266"/>
+      <c r="J27" s="266"/>
+      <c r="K27" s="266"/>
+      <c r="L27" s="266"/>
       <c r="N27" s="92"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.2">
@@ -23700,7 +23700,7 @@
       </c>
       <c r="C41" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.10070850000000001</v>
+        <v>0.10050000000000001</v>
       </c>
     </row>
     <row r="42" spans="2:14" x14ac:dyDescent="0.2">
@@ -23726,7 +23726,7 @@
       </c>
       <c r="C44" s="24">
         <f ca="1">C43/(1+C41)^5</f>
-        <v>7542763.6626147851</v>
+        <v>7549911.6055914601</v>
       </c>
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.2">
@@ -23735,7 +23735,7 @@
       </c>
       <c r="C45" s="110">
         <f ca="1">SUM(H9:K9)+C44</f>
-        <v>8391239.0299701523</v>
+        <v>8398818.6637036055</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -23762,7 +23762,7 @@
       </c>
       <c r="C48" s="110">
         <f ca="1">C45+C46-C47</f>
-        <v>9807798.0299701523</v>
+        <v>9815377.6637036055</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
@@ -23780,7 +23780,7 @@
       </c>
       <c r="C50" s="254">
         <f ca="1">C48/C49</f>
-        <v>195.67850504708815</v>
+        <v>195.82972873595637</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
@@ -23804,7 +23804,7 @@
       </c>
       <c r="C54" s="137">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.10070850000000001</v>
+        <v>0.10050000000000001</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
@@ -23839,7 +23839,7 @@
       </c>
       <c r="C58" s="254">
         <f ca="1">C57/(1+C54)^5</f>
-        <v>157.43103021510453</v>
+        <v>157.58022062820396</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
@@ -23863,7 +23863,7 @@
       </c>
       <c r="C62" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.10070850000000001</v>
+        <v>0.10050000000000001</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
@@ -23889,7 +23889,7 @@
       </c>
       <c r="C65" s="24">
         <f ca="1">C64/(1+C62)^5</f>
-        <v>7815773.7509711338</v>
+        <v>7823180.413514127</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -23898,7 +23898,7 @@
       </c>
       <c r="C66" s="110">
         <f ca="1">SUM(H9:K9)+C65</f>
-        <v>8664249.1183265019</v>
+        <v>8672087.4716262724</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.2">
@@ -23925,7 +23925,7 @@
       </c>
       <c r="C69" s="110">
         <f ca="1">C66+C67-C68</f>
-        <v>10080808.118326502</v>
+        <v>10088646.471626272</v>
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.2">
@@ -23943,7 +23943,7 @@
       </c>
       <c r="C71" s="254">
         <f ca="1">C69/C70</f>
-        <v>201.12541635063448</v>
+        <v>201.2818018360455</v>
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.2">
@@ -23967,7 +23967,7 @@
       </c>
       <c r="C75" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.10070850000000001</v>
+        <v>0.10050000000000001</v>
       </c>
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.2">
@@ -23993,7 +23993,7 @@
       </c>
       <c r="C78" s="24">
         <f ca="1">C77/(1+C75)^5</f>
-        <v>7836637.5715478323</v>
+        <v>7844064.0058093136</v>
       </c>
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.2">
@@ -24002,7 +24002,7 @@
       </c>
       <c r="C79" s="110">
         <f ca="1">SUM(H9:K9)+C78</f>
-        <v>8685112.9389031995</v>
+        <v>8692971.063921459</v>
       </c>
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.2">
@@ -24029,7 +24029,7 @@
       </c>
       <c r="C82" s="110">
         <f ca="1">C79+C80-C81</f>
-        <v>10101671.9389032</v>
+        <v>10109530.063921459</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.2">
@@ -24047,22 +24047,22 @@
       </c>
       <c r="C84" s="254">
         <f ca="1">C82/C83</f>
-        <v>201.54167708597421</v>
+        <v>201.69845704324368</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="C27:L27"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B60:C60"/>
     <mergeCell ref="C22:L22"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="C17:L17"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="C27:L27"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B60:C60"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -24112,7 +24112,7 @@
       </c>
       <c r="C5" s="135">
         <f ca="1">DCF!C26</f>
-        <v>141.85646777088763</v>
+        <v>142.18891938665595</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -24121,7 +24121,7 @@
       </c>
       <c r="C6" s="135">
         <f ca="1">Multiples!C50</f>
-        <v>195.67850504708815</v>
+        <v>195.82972873595637</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -24130,7 +24130,7 @@
       </c>
       <c r="C7" s="135">
         <f ca="1">Multiples!C58</f>
-        <v>157.43103021510453</v>
+        <v>157.58022062820396</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -24139,7 +24139,7 @@
       </c>
       <c r="C8" s="135">
         <f ca="1">Multiples!C71</f>
-        <v>201.12541635063448</v>
+        <v>201.2818018360455</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -24148,7 +24148,7 @@
       </c>
       <c r="C9" s="135">
         <f ca="1">Multiples!C84</f>
-        <v>201.54167708597421</v>
+        <v>201.69845704324368</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -24157,7 +24157,7 @@
       </c>
       <c r="C10" s="254">
         <f ca="1">AVERAGE(C5:C9)</f>
-        <v>179.52661929393781</v>
+        <v>179.71582552602109</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -24166,7 +24166,7 @@
       </c>
       <c r="C11" s="135">
         <f ca="1">Overview!C5</f>
-        <v>147.1</v>
+        <v>149.91999999999999</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -24175,7 +24175,7 @@
       </c>
       <c r="C12" s="154">
         <f ca="1">(C10-C11)/C11</f>
-        <v>0.2204392881980817</v>
+        <v>0.19874483408498603</v>
       </c>
     </row>
   </sheetData>
@@ -24237,8 +24237,8 @@
       <c r="D2" s="258"/>
       <c r="E2" s="258"/>
       <c r="F2" s="258"/>
-      <c r="G2" s="267"/>
-      <c r="H2" s="268" t="s">
+      <c r="G2" s="264"/>
+      <c r="H2" s="265" t="s">
         <v>114</v>
       </c>
       <c r="I2" s="258"/>
@@ -24250,18 +24250,18 @@
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="264" t="s">
+      <c r="C4" s="266" t="s">
         <v>198</v>
       </c>
-      <c r="D4" s="264"/>
-      <c r="E4" s="264"/>
-      <c r="F4" s="264"/>
-      <c r="G4" s="264"/>
-      <c r="H4" s="264"/>
-      <c r="I4" s="264"/>
-      <c r="J4" s="264"/>
-      <c r="K4" s="264"/>
-      <c r="L4" s="264"/>
+      <c r="D4" s="266"/>
+      <c r="E4" s="266"/>
+      <c r="F4" s="266"/>
+      <c r="G4" s="266"/>
+      <c r="H4" s="266"/>
+      <c r="I4" s="266"/>
+      <c r="J4" s="266"/>
+      <c r="K4" s="266"/>
+      <c r="L4" s="266"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -24374,18 +24374,18 @@
       <c r="N8" s="92"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C9" s="264" t="s">
+      <c r="C9" s="266" t="s">
         <v>122</v>
       </c>
-      <c r="D9" s="264"/>
-      <c r="E9" s="264"/>
-      <c r="F9" s="264"/>
-      <c r="G9" s="264"/>
-      <c r="H9" s="264"/>
-      <c r="I9" s="264"/>
-      <c r="J9" s="264"/>
-      <c r="K9" s="264"/>
-      <c r="L9" s="264"/>
+      <c r="D9" s="266"/>
+      <c r="E9" s="266"/>
+      <c r="F9" s="266"/>
+      <c r="G9" s="266"/>
+      <c r="H9" s="266"/>
+      <c r="I9" s="266"/>
+      <c r="J9" s="266"/>
+      <c r="K9" s="266"/>
+      <c r="L9" s="266"/>
       <c r="N9" s="92"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -24506,18 +24506,18 @@
       <c r="N13" s="92"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C14" s="264" t="s">
+      <c r="C14" s="266" t="s">
         <v>413</v>
       </c>
-      <c r="D14" s="264"/>
-      <c r="E14" s="264"/>
-      <c r="F14" s="264"/>
-      <c r="G14" s="264"/>
-      <c r="H14" s="264"/>
-      <c r="I14" s="264"/>
-      <c r="J14" s="264"/>
-      <c r="K14" s="264"/>
-      <c r="L14" s="264"/>
+      <c r="D14" s="266"/>
+      <c r="E14" s="266"/>
+      <c r="F14" s="266"/>
+      <c r="G14" s="266"/>
+      <c r="H14" s="266"/>
+      <c r="I14" s="266"/>
+      <c r="J14" s="266"/>
+      <c r="K14" s="266"/>
+      <c r="L14" s="266"/>
       <c r="N14" s="92"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
@@ -24645,7 +24645,7 @@
       </c>
       <c r="C24" s="137">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.10070850000000001</v>
+        <v>0.10050000000000001</v>
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
@@ -24718,8 +24718,8 @@
       <c r="D3" s="258"/>
       <c r="E3" s="258"/>
       <c r="F3" s="258"/>
-      <c r="G3" s="267"/>
-      <c r="H3" s="268" t="s">
+      <c r="G3" s="264"/>
+      <c r="H3" s="265" t="s">
         <v>114</v>
       </c>
       <c r="I3" s="258"/>
@@ -24743,18 +24743,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="87"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="264" t="s">
+      <c r="C5" s="266" t="s">
         <v>184</v>
       </c>
-      <c r="D5" s="264"/>
-      <c r="E5" s="264"/>
-      <c r="F5" s="264"/>
-      <c r="G5" s="264"/>
-      <c r="H5" s="264"/>
-      <c r="I5" s="264"/>
-      <c r="J5" s="264"/>
-      <c r="K5" s="264"/>
-      <c r="L5" s="264"/>
+      <c r="D5" s="266"/>
+      <c r="E5" s="266"/>
+      <c r="F5" s="266"/>
+      <c r="G5" s="266"/>
+      <c r="H5" s="266"/>
+      <c r="I5" s="266"/>
+      <c r="J5" s="266"/>
+      <c r="K5" s="266"/>
+      <c r="L5" s="266"/>
       <c r="P5" s="269"/>
       <c r="Q5" s="269"/>
       <c r="R5" s="269"/>
@@ -24852,23 +24852,23 @@
       </c>
       <c r="H7" s="128">
         <f>G7*(1+$C$17)</f>
-        <v>194200.98253440054</v>
+        <v>197259.26572391865</v>
       </c>
       <c r="I7" s="128">
         <f t="shared" ref="I7:L7" si="0">H7*(1+$C$17)</f>
-        <v>246635.24781868869</v>
+        <v>254464.45278385506</v>
       </c>
       <c r="J7" s="128">
         <f t="shared" si="0"/>
-        <v>313226.76472973463</v>
+        <v>328259.14409117302</v>
       </c>
       <c r="K7" s="128">
         <f t="shared" si="0"/>
-        <v>397797.99120676296</v>
+        <v>423454.29587761319</v>
       </c>
       <c r="L7" s="128">
         <f t="shared" si="0"/>
-        <v>505203.44883258897</v>
+        <v>546256.04168212099</v>
       </c>
       <c r="N7" s="92"/>
       <c r="O7" s="16"/>
@@ -24900,7 +24900,7 @@
       <c r="K8" s="139"/>
       <c r="L8" s="128">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>6384798.6000141334</v>
+        <v>6921505.124419421</v>
       </c>
       <c r="N8" s="92"/>
       <c r="O8" s="16"/>
@@ -24954,23 +24954,23 @@
       <c r="G10" s="140"/>
       <c r="H10" s="128">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>176432.7090545776</v>
+        <v>179245.13014440585</v>
       </c>
       <c r="I10" s="128">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>203568.46567398502</v>
+        <v>210110.14801116177</v>
       </c>
       <c r="J10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>234877.76410008731</v>
+        <v>246289.95087178436</v>
       </c>
       <c r="K10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>271002.5046659591</v>
+        <v>288699.7152427095</v>
       </c>
       <c r="L10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>312683.31345289701</v>
+        <v>338412.20596373943</v>
       </c>
       <c r="N10" s="92"/>
     </row>
@@ -24989,15 +24989,15 @@
       <c r="K11" s="139"/>
       <c r="L11" s="128">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>3951714.8716920139</v>
+        <v>4287955.9016523501</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="270" t="s">
+      <c r="B14" s="271" t="s">
         <v>226</v>
       </c>
-      <c r="C14" s="271"/>
+      <c r="C14" s="272"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="155" t="s">
@@ -25005,7 +25005,7 @@
       </c>
       <c r="C15" s="156">
         <f ca="1">Overview!C5</f>
-        <v>147.1</v>
+        <v>149.91999999999999</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -25014,7 +25014,7 @@
       </c>
       <c r="C16" s="156">
         <f ca="1">C36</f>
-        <v>140.35905246525712</v>
+        <v>148.91788252652825</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -25022,22 +25022,22 @@
         <v>329</v>
       </c>
       <c r="C17" s="158">
-        <v>0.27</v>
-      </c>
-      <c r="E17" s="272" t="s">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="E17" s="270" t="s">
         <v>229</v>
       </c>
-      <c r="F17" s="272"/>
-      <c r="G17" s="272"/>
-      <c r="H17" s="272"/>
-      <c r="I17" s="272"/>
+      <c r="F17" s="270"/>
+      <c r="G17" s="270"/>
+      <c r="H17" s="270"/>
+      <c r="I17" s="270"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="270" t="s">
+      <c r="B19" s="271" t="s">
         <v>188</v>
       </c>
-      <c r="C19" s="271"/>
+      <c r="C19" s="272"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="159" t="s">
@@ -25053,7 +25053,7 @@
       </c>
       <c r="C21" s="221">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.10070850000000001</v>
+        <v>0.10050000000000001</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -25071,7 +25071,7 @@
       </c>
       <c r="C23" s="161">
         <f ca="1">C15*C22</f>
-        <v>6882220.5999999996</v>
+        <v>7014157.1199999992</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -25098,15 +25098,15 @@
       </c>
       <c r="C26" s="162">
         <f ca="1">C23+C25-C24</f>
-        <v>5465661.5999999996</v>
+        <v>5597598.1199999992</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="270" t="s">
+      <c r="B28" s="271" t="s">
         <v>190</v>
       </c>
-      <c r="C28" s="271"/>
+      <c r="C28" s="272"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="159" t="s">
@@ -25114,7 +25114,7 @@
       </c>
       <c r="C29" s="161">
         <f ca="1">SUM(H10:L10)</f>
-        <v>1198564.7569475062</v>
+        <v>1262757.150233801</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -25123,7 +25123,7 @@
       </c>
       <c r="C30" s="161">
         <f ca="1">L11</f>
-        <v>3951714.8716920139</v>
+        <v>4287955.9016523501</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -25132,7 +25132,7 @@
       </c>
       <c r="C31" s="164">
         <f ca="1">C29+C30</f>
-        <v>5150279.6286395201</v>
+        <v>5550713.0518861506</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -25159,7 +25159,7 @@
       </c>
       <c r="C34" s="164">
         <f ca="1">C31+C32-C33</f>
-        <v>6566838.6286395201</v>
+        <v>6967272.0518861506</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.2">
@@ -25177,21 +25177,21 @@
       </c>
       <c r="C36" s="167">
         <f ca="1">C34/C35</f>
-        <v>140.35905246525712</v>
+        <v>148.91788252652825</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
+    <mergeCell ref="B14:C14"/>
     <mergeCell ref="E17:I17"/>
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
-    <mergeCell ref="B14:C14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -31883,7 +31883,7 @@
       </c>
       <c r="AC116" s="63">
         <f ca="1">Overview!C5</f>
-        <v>147.1</v>
+        <v>149.91999999999999</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -31954,7 +31954,7 @@
       </c>
       <c r="AC117" s="65">
         <f ca="1">AC116/AC85</f>
-        <v>147.1</v>
+        <v>149.91999999999999</v>
       </c>
     </row>
     <row r="119" spans="1:31" x14ac:dyDescent="0.2">
@@ -33064,7 +33064,7 @@
       <c r="AA146" s="49"/>
       <c r="AC146" s="72">
         <f ca="1">AC117/Statement!AC26</f>
-        <v>46.838229792054811</v>
+        <v>47.736148269373601</v>
       </c>
     </row>
     <row r="147" spans="2:29" x14ac:dyDescent="0.2">
@@ -33101,7 +33101,7 @@
       <c r="AA147" s="49"/>
       <c r="AC147" s="72">
         <f ca="1">AC117/(Statement!AC5/Statement!AC22)</f>
-        <v>6.31713197775185</v>
+        <v>6.4382353916013413</v>
       </c>
     </row>
     <row r="148" spans="2:29" x14ac:dyDescent="0.2">
@@ -33162,7 +33162,7 @@
       </c>
       <c r="AC148" s="72">
         <f ca="1">AC117/(Statement!AC49/Statement!AC75)</f>
-        <v>4.8819008017069789</v>
+        <v>4.9754899265255625</v>
       </c>
     </row>
     <row r="149" spans="2:29" x14ac:dyDescent="0.2">
@@ -33223,7 +33223,7 @@
       </c>
       <c r="AC149" s="143">
         <f ca="1">Statement!AC117*Statement!AC78</f>
-        <v>7372946.1999999993</v>
+        <v>7514290.2399999993</v>
       </c>
     </row>
     <row r="150" spans="2:29" x14ac:dyDescent="0.2">
@@ -33284,7 +33284,7 @@
       </c>
       <c r="AC150" s="143">
         <f ca="1">AC149+AC108-AC107+AC48+AC45</f>
-        <v>5956387.1999999993</v>
+        <v>6097731.2399999993</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -33321,7 +33321,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="182">
         <f ca="1">AC150/AC5</f>
-        <v>5.2020758042344024</v>
+        <v>5.3255201650302784</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -33358,7 +33358,7 @@
       <c r="AA152" s="49"/>
       <c r="AC152" s="182">
         <f ca="1">AC150/AC12</f>
-        <v>37.918242989464296</v>
+        <v>38.818036349746947</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -33493,7 +33493,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="72">
         <f t="shared" ref="AC155:AC156" ca="1" si="151">AC149/AC153</f>
-        <v>29.162828099042795</v>
+        <v>29.721897951111458</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -33530,7 +33530,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="72">
         <f t="shared" ca="1" si="151"/>
-        <v>35.724465694480962</v>
+        <v>36.572201098267229</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -33567,7 +33567,7 @@
       <c r="AA157" s="49"/>
       <c r="AC157" s="74">
         <f t="shared" ref="AC157" ca="1" si="154">AC153/AC149</f>
-        <v>3.4290227155055059E-2</v>
+        <v>3.3645226884395675E-2</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
@@ -33604,7 +33604,7 @@
       <c r="AA158" s="49"/>
       <c r="AC158" s="74">
         <f ca="1">AC26/AC117</f>
-        <v>2.1350081000918408E-2</v>
+        <v>2.0948485293723975E-2</v>
       </c>
     </row>
     <row r="159" spans="2:29" x14ac:dyDescent="0.2">
@@ -33678,7 +33678,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="154">
         <f ca="1">-AC63/AC149</f>
-        <v>9.4403238694458404E-3</v>
+        <v>9.2627510752099993E-3</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -33715,7 +33715,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="154">
         <f ca="1">-(AC63+AC64)/AC149</f>
-        <v>9.4403238694458404E-3</v>
+        <v>9.2627510752099993E-3</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -34218,7 +34218,7 @@
       <c r="AA172" s="49"/>
       <c r="AC172" s="154">
         <f ca="1">(AC107-AC108)/AC149</f>
-        <v>0.19212930103843701</v>
+        <v>0.18851534273448561</v>
       </c>
     </row>
     <row r="173" spans="2:29" x14ac:dyDescent="0.2">
@@ -36156,7 +36156,7 @@
       </c>
       <c r="C5" s="171">
         <f ca="1">Overview!C5</f>
-        <v>147.1</v>
+        <v>149.91999999999999</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="134" t="s">
@@ -36172,7 +36172,7 @@
       </c>
       <c r="C6" s="172">
         <f ca="1">Statement!AC149</f>
-        <v>7372946.1999999993</v>
+        <v>7514290.2399999993</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>20</v>
@@ -36192,7 +36192,7 @@
       </c>
       <c r="C7" s="172">
         <f ca="1">Statement!AC150</f>
-        <v>5956387.1999999993</v>
+        <v>6097731.2399999993</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>32</v>
@@ -36212,7 +36212,7 @@
       </c>
       <c r="C8" s="173">
         <f ca="1">Statement!AC146</f>
-        <v>46.838229792054811</v>
+        <v>47.736148269373601</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>247</v>
@@ -36232,7 +36232,7 @@
       </c>
       <c r="C9" s="173">
         <f ca="1">Statement!AC147</f>
-        <v>6.31713197775185</v>
+        <v>6.4382353916013413</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>248</v>
@@ -36252,7 +36252,7 @@
       </c>
       <c r="C10" s="173">
         <f ca="1">Statement!AC148</f>
-        <v>4.8819008017069789</v>
+        <v>4.9754899265255625</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -36272,7 +36272,7 @@
       </c>
       <c r="C11" s="173">
         <f ca="1">Statement!AC151</f>
-        <v>5.2020758042344024</v>
+        <v>5.3255201650302784</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -36281,7 +36281,7 @@
       </c>
       <c r="C12" s="173">
         <f ca="1">Statement!AC152</f>
-        <v>37.918242989464296</v>
+        <v>38.818036349746947</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
@@ -36517,7 +36517,7 @@
       </c>
       <c r="C38" s="174">
         <f ca="1">Statement!AC158</f>
-        <v>2.1350081000918408E-2</v>
+        <v>2.0948485293723975E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>274</v>
@@ -36533,7 +36533,7 @@
       </c>
       <c r="C39" s="214">
         <f ca="1">Statement!AC157</f>
-        <v>3.4290227155055059E-2</v>
+        <v>3.3645226884395675E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>276</v>
@@ -36565,7 +36565,7 @@
       </c>
       <c r="C41" s="174">
         <f ca="1">Statement!AC160</f>
-        <v>9.4403238694458404E-3</v>
+        <v>9.2627510752099993E-3</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -36574,7 +36574,7 @@
       </c>
       <c r="C42" s="174">
         <f ca="1">Statement!AC161</f>
-        <v>9.4403238694458404E-3</v>
+        <v>9.2627510752099993E-3</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
@@ -36618,7 +36618,7 @@
       </c>
       <c r="F48" s="174">
         <f ca="1">Statement!AC172</f>
-        <v>0.19212930103843701</v>
+        <v>0.18851534273448561</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
@@ -36797,7 +36797,7 @@
       </c>
       <c r="I6" s="171">
         <f ca="1">Statement!AC116</f>
-        <v>147.1</v>
+        <v>149.91999999999999</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -36826,7 +36826,7 @@
       </c>
       <c r="I7" s="172">
         <f ca="1">Statement!AC149</f>
-        <v>7372946.1999999993</v>
+        <v>7514290.2399999993</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -36855,7 +36855,7 @@
       </c>
       <c r="I8" s="172">
         <f ca="1">Statement!AC150</f>
-        <v>5956387.1999999993</v>
+        <v>6097731.2399999993</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -36884,7 +36884,7 @@
       </c>
       <c r="I9" s="173">
         <f ca="1">Statement!AC146</f>
-        <v>46.838229792054811</v>
+        <v>47.736148269373601</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -36913,7 +36913,7 @@
       </c>
       <c r="I10" s="173">
         <f ca="1">Statement!AC147</f>
-        <v>6.31713197775185</v>
+        <v>6.4382353916013413</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -36942,7 +36942,7 @@
       </c>
       <c r="I11" s="173">
         <f ca="1">Statement!AC148</f>
-        <v>4.8819008017069789</v>
+        <v>4.9754899265255625</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -36971,7 +36971,7 @@
       </c>
       <c r="I12" s="173">
         <f ca="1">Statement!AC151</f>
-        <v>5.2020758042344024</v>
+        <v>5.3255201650302784</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -37000,7 +37000,7 @@
       </c>
       <c r="I13" s="173">
         <f ca="1">Statement!AC152</f>
-        <v>37.918242989464296</v>
+        <v>38.818036349746947</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -37773,7 +37773,7 @@
       </c>
       <c r="I51" s="174">
         <f ca="1">Statement!AC158</f>
-        <v>2.1350081000918408E-2</v>
+        <v>2.0948485293723975E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -37802,7 +37802,7 @@
       </c>
       <c r="I52" s="174">
         <f ca="1">Statement!AC157</f>
-        <v>3.4290227155055059E-2</v>
+        <v>3.3645226884395675E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -37860,7 +37860,7 @@
       </c>
       <c r="I54" s="174">
         <f ca="1">Statement!AC160</f>
-        <v>9.4403238694458404E-3</v>
+        <v>9.2627510752099993E-3</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -37889,7 +37889,7 @@
       </c>
       <c r="I55" s="174">
         <f ca="1">Statement!AC161</f>
-        <v>9.4403238694458404E-3</v>
+        <v>9.2627510752099993E-3</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -38125,7 +38125,7 @@
       </c>
       <c r="I68" s="195">
         <f ca="1">Statement!AC172</f>
-        <v>0.19212930103843701</v>
+        <v>0.18851534273448561</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -38668,14 +38668,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="259" t="s">
+      <c r="C3" s="261" t="s">
         <v>317</v>
       </c>
-      <c r="D3" s="260"/>
-      <c r="F3" s="261" t="s">
+      <c r="D3" s="262"/>
+      <c r="F3" s="263" t="s">
         <v>318</v>
       </c>
-      <c r="G3" s="260"/>
+      <c r="G3" s="262"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -38742,19 +38742,19 @@
       <c r="B7" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C7" s="262">
+      <c r="C7" s="259">
         <f>Statement!AA89</f>
         <v>2.2218264392893719E-2</v>
       </c>
-      <c r="D7" s="263"/>
-      <c r="F7" s="262">
+      <c r="D7" s="260"/>
+      <c r="F7" s="259">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.18309713991239371</v>
       </c>
-      <c r="G7" s="263"/>
+      <c r="G7" s="260"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="206" t="s">
@@ -38781,19 +38781,19 @@
       <c r="B9" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C9" s="262">
+      <c r="C9" s="259">
         <f>Statement!AA90</f>
         <v>3.6046202026093238E-2</v>
       </c>
-      <c r="D9" s="263"/>
-      <c r="F9" s="262">
+      <c r="D9" s="260"/>
+      <c r="F9" s="259">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.17263647322197348</v>
       </c>
-      <c r="G9" s="263"/>
+      <c r="G9" s="260"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="206" t="s">
@@ -38820,19 +38820,19 @@
       <c r="B11" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C11" s="262">
+      <c r="C11" s="259">
         <f>Statement!AA91</f>
         <v>1.710027405488606E-2</v>
       </c>
-      <c r="D11" s="263"/>
-      <c r="F11" s="262">
+      <c r="D11" s="260"/>
+      <c r="F11" s="259">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>0.1870895657269924</v>
       </c>
-      <c r="G11" s="263"/>
+      <c r="G11" s="260"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="206" t="s">
@@ -38859,19 +38859,19 @@
       <c r="B13" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C13" s="262">
+      <c r="C13" s="259">
         <f>Statement!AA95</f>
         <v>8.4392741251357012E-2</v>
       </c>
-      <c r="D13" s="263"/>
-      <c r="F13" s="262">
+      <c r="D13" s="260"/>
+      <c r="F13" s="259">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.22501976973287405</v>
       </c>
-      <c r="G13" s="263"/>
+      <c r="G13" s="260"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="206" t="s">
@@ -38898,19 +38898,19 @@
       <c r="B15" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C15" s="262">
+      <c r="C15" s="259">
         <f>Statement!AA96</f>
         <v>-0.23765355851505829</v>
       </c>
-      <c r="D15" s="263"/>
-      <c r="F15" s="262">
+      <c r="D15" s="260"/>
+      <c r="F15" s="259">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>1.7444474417768186E-2</v>
       </c>
-      <c r="G15" s="263"/>
+      <c r="G15" s="260"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="206" t="s">
@@ -38937,19 +38937,19 @@
       <c r="B17" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C17" s="262">
+      <c r="C17" s="259">
         <f>Statement!AA98</f>
         <v>-0.23704555913483663</v>
       </c>
-      <c r="D17" s="263"/>
-      <c r="F17" s="262">
+      <c r="D17" s="260"/>
+      <c r="F17" s="259">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>-0.25955204216073779</v>
       </c>
-      <c r="G17" s="263"/>
+      <c r="G17" s="260"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="206" t="s">
@@ -38976,22 +38976,22 @@
       <c r="B19" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C19" s="262">
+      <c r="C19" s="259">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>2.5565842762241744E-2</v>
       </c>
-      <c r="D19" s="263"/>
-      <c r="F19" s="262">
+      <c r="D19" s="260"/>
+      <c r="F19" s="259">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>2.5293753865182372E-2</v>
       </c>
-      <c r="G19" s="263"/>
+      <c r="G19" s="260"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="206" t="s">
@@ -39018,22 +39018,22 @@
       <c r="B21" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C21" s="262">
+      <c r="C21" s="259">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>-0.2584269662921348</v>
       </c>
-      <c r="D21" s="263"/>
-      <c r="F21" s="262">
+      <c r="D21" s="260"/>
+      <c r="F21" s="259">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>-0.27472527472527469</v>
       </c>
-      <c r="G21" s="263"/>
+      <c r="G21" s="260"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -39082,22 +39082,22 @@
       <c r="B25" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C25" s="262">
+      <c r="C25" s="259">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>2.840483364420425E-2</v>
       </c>
-      <c r="D25" s="263"/>
-      <c r="F25" s="262">
+      <c r="D25" s="260"/>
+      <c r="F25" s="259">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>0.22478379327694395</v>
       </c>
-      <c r="G25" s="263"/>
+      <c r="G25" s="260"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="str">
@@ -39125,22 +39125,22 @@
       <c r="B27" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C27" s="262">
+      <c r="C27" s="259">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>2.1247695740758708E-2</v>
       </c>
-      <c r="D27" s="263"/>
-      <c r="F27" s="262">
+      <c r="D27" s="260"/>
+      <c r="F27" s="259">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>2.1792942775323981E-2</v>
       </c>
-      <c r="G27" s="263"/>
+      <c r="G27" s="260"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="str">
@@ -39168,22 +39168,22 @@
       <c r="B29" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C29" s="262">
+      <c r="C29" s="259">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>-0.10674206945303526</v>
       </c>
-      <c r="D29" s="263"/>
-      <c r="F29" s="262">
+      <c r="D29" s="260"/>
+      <c r="F29" s="259">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>2.0816812053925456E-3</v>
       </c>
-      <c r="G29" s="263"/>
+      <c r="G29" s="260"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="str">
@@ -39211,22 +39211,22 @@
       <c r="B31" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C31" s="262">
+      <c r="C31" s="259">
         <f>IF(C30=0,
 IF(D30=0,0,IF(D30&gt;0,1,-1)),
 (D30-C30)/ABS(C30)
 )</f>
         <v>-5.2569263556713236E-2</v>
       </c>
-      <c r="D31" s="263"/>
-      <c r="F31" s="262">
+      <c r="D31" s="260"/>
+      <c r="F31" s="259">
         <f>IF(F30=0,
 IF(G30=0,0,IF(G30&gt;0,1,-1)),
 (G30-F30)/ABS(F30)
 )</f>
         <v>-0.22983638113570742</v>
       </c>
-      <c r="G31" s="263"/>
+      <c r="G31" s="260"/>
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B32" s="20" t="str">
@@ -39254,22 +39254,22 @@
       <c r="B33" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C33" s="262">
+      <c r="C33" s="259">
         <f>IF(C32=0,
 IF(D32=0,0,IF(D32&gt;0,1,-1)),
 (D32-C32)/ABS(C32)
 )</f>
         <v>0.84164222873900296</v>
       </c>
-      <c r="D33" s="263"/>
-      <c r="F33" s="262">
+      <c r="D33" s="260"/>
+      <c r="F33" s="259">
         <f>IF(F32=0,
 IF(G32=0,0,IF(G32&gt;0,1,-1)),
 (G32-F32)/ABS(F32)
 )</f>
         <v>1.482213438735178</v>
       </c>
-      <c r="G33" s="263"/>
+      <c r="G33" s="260"/>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B35" s="8" t="s">
@@ -39318,22 +39318,22 @@
       <c r="B37" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C37" s="262">
+      <c r="C37" s="259">
         <f>IF(C36=0,
 IF(D36=0,0,IF(D36&gt;0,1,-1)),
 (D36-C36)/ABS(C36)
 )</f>
         <v>3.8938053097345132E-2</v>
       </c>
-      <c r="D37" s="263"/>
-      <c r="F37" s="262">
+      <c r="D37" s="260"/>
+      <c r="F37" s="259">
         <f>IF(F36=0,
 IF(G36=0,0,IF(G36&gt;0,1,-1)),
 (G36-F36)/ABS(F36)
 )</f>
         <v>0.23060796645702306</v>
       </c>
-      <c r="G37" s="263"/>
+      <c r="G37" s="260"/>
     </row>
     <row r="38" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="str">
@@ -39361,22 +39361,22 @@
       <c r="B39" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C39" s="262">
+      <c r="C39" s="259">
         <f>IF(C38=0,
 IF(D38=0,0,IF(D38&gt;0,1,-1)),
 (D38-C38)/ABS(C38)
 )</f>
         <v>2.0319303338171262E-2</v>
       </c>
-      <c r="D39" s="263"/>
-      <c r="F39" s="262">
+      <c r="D39" s="260"/>
+      <c r="F39" s="259">
         <f>IF(F38=0,
 IF(G38=0,0,IF(G38&gt;0,1,-1)),
 (G38-F38)/ABS(F38)
 )</f>
         <v>9.5869056897895558E-2</v>
       </c>
-      <c r="G39" s="263"/>
+      <c r="G39" s="260"/>
     </row>
     <row r="40" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B40" s="20" t="str">
@@ -39404,22 +39404,22 @@
       <c r="B41" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C41" s="262">
+      <c r="C41" s="259">
         <f>IF(C40=0,
 IF(D40=0,0,IF(D40&gt;0,1,-1)),
 (D40-C40)/ABS(C40)
 )</f>
         <v>1.6E-2</v>
       </c>
-      <c r="D41" s="263"/>
-      <c r="F41" s="262">
+      <c r="D41" s="260"/>
+      <c r="F41" s="259">
         <f>IF(F40=0,
 IF(G40=0,0,IF(G40&gt;0,1,-1)),
 (G40-F40)/ABS(F40)
 )</f>
         <v>0.16513761467889909</v>
       </c>
-      <c r="G41" s="263"/>
+      <c r="G41" s="260"/>
     </row>
     <row r="42" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B42" s="20" t="str">
@@ -39447,22 +39447,22 @@
       <c r="B43" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C43" s="262">
+      <c r="C43" s="259">
         <f>IF(C42=0,
 IF(D42=0,0,IF(D42&gt;0,1,-1)),
 (D42-C42)/ABS(C42)
 )</f>
         <v>2.0750199521149242E-2</v>
       </c>
-      <c r="D43" s="263"/>
-      <c r="F43" s="262">
+      <c r="D43" s="260"/>
+      <c r="F43" s="259">
         <f>IF(F42=0,
 IF(G42=0,0,IF(G42&gt;0,1,-1)),
 (G42-F42)/ABS(F42)
 )</f>
         <v>8.9437819420783646E-2</v>
       </c>
-      <c r="G43" s="263"/>
+      <c r="G43" s="260"/>
     </row>
     <row r="44" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B44" s="20" t="str">
@@ -39490,22 +39490,22 @@
       <c r="B45" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C45" s="262">
+      <c r="C45" s="259">
         <f>IF(C44=0,
 IF(D44=0,0,IF(D44&gt;0,1,-1)),
 (D44-C44)/ABS(C44)
 )</f>
         <v>1.2209481933271921E-2</v>
       </c>
-      <c r="D45" s="263"/>
-      <c r="F45" s="262">
+      <c r="D45" s="260"/>
+      <c r="F45" s="259">
         <f>IF(F44=0,
 IF(G44=0,0,IF(G44&gt;0,1,-1)),
 (G44-F44)/ABS(F44)
 )</f>
         <v>5.119238950540856E-2</v>
       </c>
-      <c r="G45" s="263"/>
+      <c r="G45" s="260"/>
     </row>
     <row r="46" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="str">
@@ -39533,22 +39533,22 @@
       <c r="B47" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C47" s="262">
+      <c r="C47" s="259">
         <f>IF(C46=0,
 IF(D46=0,0,IF(D46&gt;0,1,-1)),
 (D46-C46)/ABS(C46)
 )</f>
         <v>1.8247963846473435E-2</v>
       </c>
-      <c r="D47" s="263"/>
-      <c r="F47" s="262">
+      <c r="D47" s="260"/>
+      <c r="F47" s="259">
         <f>IF(F46=0,
 IF(G46=0,0,IF(G46&gt;0,1,-1)),
 (G46-F46)/ABS(F46)
 )</f>
         <v>0.1229516507570132</v>
       </c>
-      <c r="G47" s="263"/>
+      <c r="G47" s="260"/>
     </row>
     <row r="48" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B48" s="20" t="str">
@@ -39576,22 +39576,22 @@
       <c r="B49" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C49" s="262">
+      <c r="C49" s="259">
         <f>IF(C48=0,
 IF(D48=0,0,IF(D48&gt;0,1,-1)),
 (D48-C48)/ABS(C48)
 )</f>
         <v>-4.2332859174963834E-3</v>
       </c>
-      <c r="D49" s="263"/>
-      <c r="F49" s="262">
+      <c r="D49" s="260"/>
+      <c r="F49" s="259">
         <f>IF(F48=0,
 IF(G48=0,0,IF(G48&gt;0,1,-1)),
 (G48-F48)/ABS(F48)
 )</f>
         <v>6.3208790635154666E-2</v>
       </c>
-      <c r="G49" s="263"/>
+      <c r="G49" s="260"/>
     </row>
     <row r="50" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B50" s="20" t="str">
@@ -39619,22 +39619,22 @@
       <c r="B51" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C51" s="262">
+      <c r="C51" s="259">
         <f>IF(C50=0,
 IF(D50=0,0,IF(D50&gt;0,1,-1)),
 (D50-C50)/ABS(C50)
 )</f>
         <v>4.8738292663854846E-4</v>
       </c>
-      <c r="D51" s="263"/>
-      <c r="F51" s="262">
+      <c r="D51" s="260"/>
+      <c r="F51" s="259">
         <f>IF(F50=0,
 IF(G50=0,0,IF(G50&gt;0,1,-1)),
 (G50-F50)/ABS(F50)
 )</f>
         <v>-6.2091544317255373E-2</v>
       </c>
-      <c r="G51" s="263"/>
+      <c r="G51" s="260"/>
     </row>
     <row r="52" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="str">
@@ -39662,39 +39662,43 @@
       <c r="B53" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C53" s="262">
+      <c r="C53" s="259">
         <f>IF(C52=0,
 IF(D52=0,0,IF(D52&gt;0,1,-1)),
 (D52-C52)/ABS(C52)
 )</f>
         <v>-8.8077740902117604E-2</v>
       </c>
-      <c r="D53" s="263"/>
-      <c r="F53" s="262">
+      <c r="D53" s="260"/>
+      <c r="F53" s="259">
         <f>IF(F52=0,
 IF(G52=0,0,IF(G52&gt;0,1,-1)),
 (G52-F52)/ABS(F52)
 )</f>
         <v>-0.37416005758387127</v>
       </c>
-      <c r="G53" s="263"/>
+      <c r="G53" s="260"/>
     </row>
   </sheetData>
   <mergeCells count="46">
-    <mergeCell ref="C53:D53"/>
-    <mergeCell ref="F53:G53"/>
-    <mergeCell ref="C47:D47"/>
-    <mergeCell ref="F47:G47"/>
-    <mergeCell ref="C49:D49"/>
-    <mergeCell ref="F49:G49"/>
-    <mergeCell ref="C51:D51"/>
-    <mergeCell ref="F51:G51"/>
-    <mergeCell ref="C41:D41"/>
-    <mergeCell ref="F41:G41"/>
-    <mergeCell ref="C43:D43"/>
-    <mergeCell ref="F43:G43"/>
-    <mergeCell ref="C45:D45"/>
-    <mergeCell ref="F45:G45"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
     <mergeCell ref="C37:D37"/>
     <mergeCell ref="F37:G37"/>
     <mergeCell ref="C39:D39"/>
@@ -39709,24 +39713,20 @@
     <mergeCell ref="F31:G31"/>
     <mergeCell ref="C33:D33"/>
     <mergeCell ref="F33:G33"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="F41:G41"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="F43:G43"/>
+    <mergeCell ref="C45:D45"/>
+    <mergeCell ref="F45:G45"/>
+    <mergeCell ref="C53:D53"/>
+    <mergeCell ref="F53:G53"/>
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="F47:G47"/>
+    <mergeCell ref="C49:D49"/>
+    <mergeCell ref="F49:G49"/>
+    <mergeCell ref="C51:D51"/>
+    <mergeCell ref="F51:G51"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/DUOL.xlsx
+++ b/DUOL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEBF78DB-FF24-7D4A-86EF-77FFA42CAC6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E78C6BE-9772-D545-836B-B0728589AB63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="10" activeTab="20" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -152,7 +152,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="853" uniqueCount="438">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="885" uniqueCount="446">
   <si>
     <t>Ticker</t>
   </si>
@@ -1466,6 +1466,30 @@
   </si>
   <si>
     <t>Reverse DCF rate</t>
+  </si>
+  <si>
+    <t>Discount rates used</t>
+  </si>
+  <si>
+    <t>Cost of Equity</t>
+  </si>
+  <si>
+    <t>Links</t>
+  </si>
+  <si>
+    <t>Financials -&gt;'!B13</t>
+  </si>
+  <si>
+    <t>Analysis -&gt;'!B13</t>
+  </si>
+  <si>
+    <t>Forecast -&gt;'!B13</t>
+  </si>
+  <si>
+    <t>Valuation -&gt;'!B13</t>
+  </si>
+  <si>
+    <t>Overview'!B3</t>
   </si>
 </sst>
 </file>
@@ -1484,7 +1508,7 @@
     <numFmt numFmtId="171" formatCode="0.0_);\(0.0\)"/>
     <numFmt numFmtId="172" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="24" x14ac:knownFonts="1">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1650,6 +1674,14 @@
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -2073,11 +2105,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="273">
+  <cellXfs count="277">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
@@ -2409,6 +2442,14 @@
     <xf numFmtId="39" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="7" fillId="9" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="0" fillId="17" borderId="25" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="0" fillId="17" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="25" xfId="2" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="26" xfId="2" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2421,12 +2462,6 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2436,10 +2471,10 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2451,11 +2486,14 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2463,8 +2501,12 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
@@ -13158,10 +13200,10 @@
     <v>343.99799999999999</v>
     <v>87.89</v>
     <v>1.0680000000000001</v>
-    <v>-1.3</v>
-    <v>-8.5970000000000005E-3</v>
-    <v>-7.0000000000000007E-2</v>
-    <v>-4.6690000000000002E-4</v>
+    <v>-2.1800000000000002</v>
+    <v>-1.4541E-2</v>
+    <v>0.26</v>
+    <v>1.7599999999999998E-3</v>
     <v>USD</v>
     <v>Duolingo, Inc. is a technology company. The Company is engaged in offering a mobile learning platform, as well as a digital English language proficiency assessment exam. It operates a freemium business model, namely, the app and the Website are accessible free of charge, although Duolingo also offers premium services for a subscription fee. Its solutions consist of the Duolingo App, Super Duolingo, Duolingo Max, Duolingo English Test: AI-Driven Language Assessment, Duolingo for Schools, and Duolingo ABC. The Duolingo App offers courses in over 40 different languages, including Spanish, English, French, German, Italian, Portuguese, Japanese and Chinese. Duolingo can also be accessed on desktop computers via a Web browser. Its subscription offering, Super Duolingo, offers learners additional features to enhance their learning experience. The Duolingo English Test is an online, on-demand, high-stakes English proficiency assessment. It also operates an animation and motion design studio.</v>
     <v>900</v>
@@ -13169,25 +13211,25 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>5900 PENN AVE, SECOND FLOOR, PITTSBURGH, PA, 15206 US</v>
-    <v>152.46</v>
+    <v>150.495</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46304.998811527345</v>
+    <v>46307.853151226562</v>
     <v>0</v>
-    <v>148.52000000000001</v>
-    <v>7014197598</v>
+    <v>147.5001</v>
+    <v>6912203529</v>
     <v>DUOLINGO, INC.</v>
     <v>DUOLINGO, INC.</v>
-    <v>150.61000000000001</v>
-    <v>18.024899999999999</v>
-    <v>151.22</v>
+    <v>149.85</v>
+    <v>17.610099999999999</v>
     <v>149.91999999999999</v>
-    <v>149.85</v>
+    <v>147.74</v>
+    <v>148</v>
     <v>46786270</v>
     <v>DUOL</v>
     <v>DUOLINGO, INC. (XNAS:DUOL)</v>
-    <v>621975</v>
-    <v>1063100</v>
+    <v>783499</v>
+    <v>1030227</v>
     <v>2011</v>
   </rv>
   <rv s="2">
@@ -13443,9 +13485,9 @@
       <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq</v>
+      <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
-      <v>Delayed 15 minutes</v>
+      <v>Real-Time Nasdaq Last Sale</v>
       <v>from close</v>
       <v>from close</v>
     </spb>
@@ -13999,7 +14041,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{825B172E-7ADE-4B4A-B533-F037BCFCDCB0}">
-  <dimension ref="B1:I66"/>
+  <dimension ref="B1:K66"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2" style="1" customWidth="1"/>
@@ -14011,25 +14053,30 @@
     <col min="7" max="7" width="1.6640625" style="1" customWidth="1"/>
     <col min="8" max="8" width="15.1640625" style="1" customWidth="1"/>
     <col min="9" max="9" width="8.6640625" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="10.83203125" style="1"/>
+    <col min="10" max="10" width="2" style="1" customWidth="1"/>
+    <col min="11" max="11" width="16.5" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="255" t="s">
+    <row r="1" spans="2:11" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="2" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B2" s="259" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="256"/>
-      <c r="E2" s="255" t="s">
+      <c r="C2" s="260"/>
+      <c r="E2" s="259" t="s">
         <v>291</v>
       </c>
-      <c r="F2" s="256"/>
-      <c r="H2" s="255" t="s">
+      <c r="F2" s="260"/>
+      <c r="H2" s="259" t="s">
         <v>330</v>
       </c>
-      <c r="I2" s="256"/>
-    </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="I2" s="260"/>
+      <c r="K2" s="134" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="3" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B3" s="184" t="s">
         <v>11</v>
       </c>
@@ -14042,7 +14089,7 @@
       </c>
       <c r="F3" s="186">
         <f ca="1">Statement!AC149</f>
-        <v>7514290.2399999993</v>
+        <v>7405024.2800000003</v>
       </c>
       <c r="H3" s="184" t="str">
         <f>'AVG target price'!B5</f>
@@ -14052,8 +14099,11 @@
         <f ca="1">'AVG target price'!C5</f>
         <v>142.18891938665595</v>
       </c>
-    </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K3" s="257" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="4" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B4" s="184" t="s">
         <v>0</v>
       </c>
@@ -14066,7 +14116,7 @@
       </c>
       <c r="F4" s="187">
         <f ca="1">Statement!AC150</f>
-        <v>6097731.2399999993</v>
+        <v>5988465.2800000003</v>
       </c>
       <c r="H4" s="184" t="str">
         <f>'AVG target price'!B6</f>
@@ -14076,14 +14126,17 @@
         <f ca="1">'AVG target price'!C6</f>
         <v>195.82972873595637</v>
       </c>
-    </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K4" s="257" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="5" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B5" s="184" t="s">
         <v>1</v>
       </c>
       <c r="C5" s="207" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>149.91999999999999</v>
+        <v>147.74</v>
       </c>
       <c r="E5" s="184" t="s">
         <v>247</v>
@@ -14100,21 +14153,24 @@
         <f ca="1">'AVG target price'!C7</f>
         <v>157.58022062820396</v>
       </c>
-    </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K5" s="257" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="6" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B6" s="184" t="s">
         <v>2</v>
       </c>
       <c r="C6" s="207" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>149.85</v>
+        <v>148</v>
       </c>
       <c r="E6" s="184" t="s">
         <v>241</v>
       </c>
       <c r="F6" s="189">
         <f ca="1">Statement!AC146</f>
-        <v>47.736148269373601</v>
+        <v>47.042012708893125</v>
       </c>
       <c r="H6" s="184" t="str">
         <f>'AVG target price'!B8</f>
@@ -14124,21 +14180,24 @@
         <f ca="1">'AVG target price'!C8</f>
         <v>201.2818018360455</v>
       </c>
-    </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K6" s="258" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="7" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B7" s="184" t="s">
         <v>3</v>
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>-1.3</v>
+        <v>-2.1800000000000002</v>
       </c>
       <c r="E7" s="185" t="s">
         <v>205</v>
       </c>
       <c r="F7" s="190">
         <f ca="1">Statement!AC147</f>
-        <v>6.4382353916013413</v>
+        <v>6.3446164404694656</v>
       </c>
       <c r="H7" s="184" t="str">
         <f>'AVG target price'!B9</f>
@@ -14149,20 +14208,20 @@
         <v>201.69845704324368</v>
       </c>
     </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B8" s="184" t="s">
         <v>4</v>
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>-7.0000000000000007E-2</v>
+        <v>0.26</v>
       </c>
       <c r="E8" s="184" t="s">
         <v>269</v>
       </c>
       <c r="F8" s="191">
         <f ca="1">Statement!AC157</f>
-        <v>3.3645226884395675E-2</v>
+        <v>3.4141684137732498E-2</v>
       </c>
       <c r="H8" s="183" t="str">
         <f>'AVG target price'!B10</f>
@@ -14173,20 +14232,20 @@
         <v>179.71582552602109</v>
       </c>
     </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B9" s="184" t="s">
         <v>5</v>
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>-8.5970000000000005E-3</v>
+        <v>-1.4541E-2</v>
       </c>
       <c r="E9" s="184" t="s">
         <v>292</v>
       </c>
       <c r="F9" s="191">
         <f ca="1">Statement!AC158</f>
-        <v>2.0948485293723975E-2</v>
+        <v>2.1257593848890602E-2</v>
       </c>
       <c r="H9" s="183" t="str">
         <f>'AVG target price'!B12</f>
@@ -14194,26 +14253,26 @@
       </c>
       <c r="I9" s="212">
         <f ca="1">'AVG target price'!C12</f>
-        <v>0.19874483408498603</v>
-      </c>
-    </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.2">
+        <v>0.21643309547868608</v>
+      </c>
+    </row>
+    <row r="10" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B10" s="184" t="s">
         <v>6</v>
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>-4.6690000000000002E-4</v>
+        <v>1.7599999999999998E-3</v>
       </c>
       <c r="E10" s="184" t="s">
         <v>297</v>
       </c>
       <c r="F10" s="191">
         <f ca="1">Statement!AC160</f>
-        <v>9.2627510752099993E-3</v>
-      </c>
-    </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.2">
+        <v>9.3994290049782252E-3</v>
+      </c>
+    </row>
+    <row r="11" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B11" s="184" t="s">
         <v>7</v>
       </c>
@@ -14236,7 +14295,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B12" s="184" t="s">
         <v>8</v>
       </c>
@@ -14252,7 +14311,7 @@
         <v>7.428664005404173E-2</v>
       </c>
     </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B13" s="184" t="s">
         <v>9</v>
       </c>
@@ -14275,13 +14334,13 @@
         <v>0.28999999999999998</v>
       </c>
     </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B14" s="185" t="s">
         <v>10</v>
       </c>
       <c r="C14" s="209" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>1063100</v>
+        <v>1030227</v>
       </c>
       <c r="E14" s="185" t="s">
         <v>105</v>
@@ -14291,16 +14350,16 @@
         <v>-17.586668123511064</v>
       </c>
     </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:11" x14ac:dyDescent="0.2">
       <c r="E15" s="184" t="s">
         <v>294</v>
       </c>
       <c r="F15" s="191">
         <f ca="1">Statement!AC172</f>
-        <v>0.18851534273448561</v>
-      </c>
-    </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.2">
+        <v>0.19129700949474807</v>
+      </c>
+    </row>
+    <row r="16" spans="2:11" x14ac:dyDescent="0.2">
       <c r="E16" s="185" t="s">
         <v>299</v>
       </c>
@@ -14308,12 +14367,16 @@
         <f>Statement!AC171</f>
         <v>30.277412046338647</v>
       </c>
+      <c r="H16" s="259" t="s">
+        <v>438</v>
+      </c>
+      <c r="I16" s="260"/>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="257" t="s">
+      <c r="B17" s="261" t="s">
         <v>90</v>
       </c>
-      <c r="C17" s="257"/>
+      <c r="C17" s="261"/>
       <c r="E17" s="183" t="s">
         <v>300</v>
       </c>
@@ -14321,6 +14384,13 @@
         <f>Statement!AC167</f>
         <v>0.14520569809664419</v>
       </c>
+      <c r="H17" s="184" t="s">
+        <v>169</v>
+      </c>
+      <c r="I17" s="255">
+        <f ca="1">DCF!C15</f>
+        <v>0.10050000000000001</v>
+      </c>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B18" s="183" t="s">
@@ -14336,6 +14406,13 @@
         <f>Statement!AC140</f>
         <v>22.829226659561293</v>
       </c>
+      <c r="H18" s="185" t="s">
+        <v>439</v>
+      </c>
+      <c r="I18" s="256">
+        <f ca="1">Multiples!C54</f>
+        <v>0.10050000000000001</v>
+      </c>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B19" s="183" t="s">
@@ -14386,14 +14463,14 @@
       <c r="I22" s="50"/>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="257" t="s">
+      <c r="B25" s="261" t="s">
         <v>107</v>
       </c>
-      <c r="C25" s="257"/>
-      <c r="E25" s="255" t="s">
+      <c r="C25" s="261"/>
+      <c r="E25" s="259" t="s">
         <v>343</v>
       </c>
-      <c r="F25" s="256"/>
+      <c r="F25" s="260"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="183" t="s">
@@ -14622,13 +14699,14 @@
       <c r="H66" s="134"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="E25:F25"/>
+    <mergeCell ref="H16:I16"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C10">
     <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
@@ -14641,6 +14719,12 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
+  <hyperlinks>
+    <hyperlink ref="K3" location="'Financials -&gt;'!B13" display="'Financials -&gt;'!B13" xr:uid="{832F424A-8F06-9F4F-AF97-7DA683ACB5AB}"/>
+    <hyperlink ref="K4" location="'Analysis -&gt;'!B13" display="'Analysis -&gt;'!B13" xr:uid="{2EE05D4C-B9FB-F441-979B-3D7F89BD8BD7}"/>
+    <hyperlink ref="K5" location="'Forecast -&gt;'!B13" display="'Forecast -&gt;'!B13" xr:uid="{40305C7F-453F-A74B-872A-0E9BE5931076}"/>
+    <hyperlink ref="K6" location="'Valuation -&gt;'!B13" display="'Valuation -&gt;'!B13" xr:uid="{B5F2AFC3-E8B4-0A4D-BF18-F9C84ACE33D6}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -14650,18 +14734,57 @@
   <sheetPr>
     <tabColor theme="6" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="B13"/>
+  <dimension ref="B5:H13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="10.83203125" style="1"/>
+    <col min="1" max="7" width="10.83203125" style="1"/>
+    <col min="8" max="8" width="16.1640625" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="13" spans="2:2" s="4" customFormat="1" ht="49" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H5" s="134" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H6" s="257" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H7" s="257" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H8" s="257" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H9" s="257" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H10" s="258" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" s="4" customFormat="1" ht="49" x14ac:dyDescent="0.2">
       <c r="B13" s="3" t="s">
         <v>111</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="H6" location="Overview!B3" display="Overview'!B3" xr:uid="{2FE79ECC-FE2D-DE4D-9B1D-17B797FDC517}"/>
+    <hyperlink ref="H8" location="'Analysis -&gt;'!B13" display="'Analysis -&gt;'!B13" xr:uid="{6565A3E3-EAEF-E24A-BD88-AB11899D5D29}"/>
+    <hyperlink ref="H9" location="'Forecast -&gt;'!B13" display="'Forecast -&gt;'!B13" xr:uid="{5E4C62ED-FAC3-424A-9651-3EEA2A78A5C5}"/>
+    <hyperlink ref="H10" location="'Valuation -&gt;'!B13" display="'Valuation -&gt;'!B13" xr:uid="{A5ED8842-F42F-7342-8F39-C785B981FA4B}"/>
+    <hyperlink ref="H7" location="'Financials -&gt;'!B13" display="'Financials -&gt;'!B13" xr:uid="{03D9F6FE-D077-FB4B-B548-AE8A5DC91DC0}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -14698,36 +14821,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="258" t="s">
+      <c r="C2" s="262" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="258"/>
-      <c r="E2" s="258"/>
-      <c r="F2" s="258"/>
-      <c r="G2" s="264"/>
-      <c r="H2" s="265" t="s">
+      <c r="D2" s="262"/>
+      <c r="E2" s="262"/>
+      <c r="F2" s="262"/>
+      <c r="G2" s="271"/>
+      <c r="H2" s="272" t="s">
         <v>114</v>
       </c>
-      <c r="I2" s="258"/>
-      <c r="J2" s="258"/>
-      <c r="K2" s="258"/>
-      <c r="L2" s="258"/>
+      <c r="I2" s="262"/>
+      <c r="J2" s="262"/>
+      <c r="K2" s="262"/>
+      <c r="L2" s="262"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="258" t="s">
+      <c r="S2" s="262" t="s">
         <v>113</v>
       </c>
-      <c r="T2" s="258"/>
-      <c r="U2" s="258"/>
-      <c r="V2" s="258"/>
-      <c r="W2" s="258"/>
-      <c r="X2" s="258"/>
-      <c r="Y2" s="258"/>
-      <c r="Z2" s="258"/>
-      <c r="AA2" s="258" t="s">
+      <c r="T2" s="262"/>
+      <c r="U2" s="262"/>
+      <c r="V2" s="262"/>
+      <c r="W2" s="262"/>
+      <c r="X2" s="262"/>
+      <c r="Y2" s="262"/>
+      <c r="Z2" s="262"/>
+      <c r="AA2" s="262" t="s">
         <v>114</v>
       </c>
-      <c r="AB2" s="258"/>
-      <c r="AC2" s="258"/>
+      <c r="AB2" s="262"/>
+      <c r="AC2" s="262"/>
       <c r="AE2" s="86" t="s">
         <v>85</v>
       </c>
@@ -14738,32 +14861,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="266" t="s">
+      <c r="C4" s="268" t="s">
         <v>116</v>
       </c>
-      <c r="D4" s="266"/>
-      <c r="E4" s="266"/>
-      <c r="F4" s="266"/>
-      <c r="G4" s="266"/>
-      <c r="H4" s="266"/>
-      <c r="I4" s="266"/>
-      <c r="J4" s="266"/>
-      <c r="K4" s="266"/>
-      <c r="L4" s="266"/>
+      <c r="D4" s="268"/>
+      <c r="E4" s="268"/>
+      <c r="F4" s="268"/>
+      <c r="G4" s="268"/>
+      <c r="H4" s="268"/>
+      <c r="I4" s="268"/>
+      <c r="J4" s="268"/>
+      <c r="K4" s="268"/>
+      <c r="L4" s="268"/>
       <c r="O4" s="5"/>
-      <c r="S4" s="267" t="s">
+      <c r="S4" s="269" t="s">
         <v>116</v>
       </c>
-      <c r="T4" s="268"/>
-      <c r="U4" s="268"/>
-      <c r="V4" s="268"/>
-      <c r="W4" s="268"/>
-      <c r="X4" s="268"/>
-      <c r="Y4" s="268"/>
-      <c r="Z4" s="268"/>
-      <c r="AA4" s="268"/>
-      <c r="AB4" s="268"/>
-      <c r="AC4" s="268"/>
+      <c r="T4" s="270"/>
+      <c r="U4" s="270"/>
+      <c r="V4" s="270"/>
+      <c r="W4" s="270"/>
+      <c r="X4" s="270"/>
+      <c r="Y4" s="270"/>
+      <c r="Z4" s="270"/>
+      <c r="AA4" s="270"/>
+      <c r="AB4" s="270"/>
+      <c r="AC4" s="270"/>
       <c r="AE4" s="88"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -15451,33 +15574,33 @@
       <c r="Q12" s="92"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="266" t="s">
+      <c r="C13" s="268" t="s">
         <v>122</v>
       </c>
-      <c r="D13" s="266"/>
-      <c r="E13" s="266"/>
-      <c r="F13" s="266"/>
-      <c r="G13" s="266"/>
-      <c r="H13" s="266"/>
-      <c r="I13" s="266"/>
-      <c r="J13" s="266"/>
-      <c r="K13" s="266"/>
-      <c r="L13" s="266"/>
+      <c r="D13" s="268"/>
+      <c r="E13" s="268"/>
+      <c r="F13" s="268"/>
+      <c r="G13" s="268"/>
+      <c r="H13" s="268"/>
+      <c r="I13" s="268"/>
+      <c r="J13" s="268"/>
+      <c r="K13" s="268"/>
+      <c r="L13" s="268"/>
       <c r="O13" s="5"/>
       <c r="Q13" s="92"/>
-      <c r="S13" s="267" t="s">
+      <c r="S13" s="269" t="s">
         <v>122</v>
       </c>
-      <c r="T13" s="268"/>
-      <c r="U13" s="268"/>
-      <c r="V13" s="268"/>
-      <c r="W13" s="268"/>
-      <c r="X13" s="268"/>
-      <c r="Y13" s="268"/>
-      <c r="Z13" s="268"/>
-      <c r="AA13" s="268"/>
-      <c r="AB13" s="268"/>
-      <c r="AC13" s="268"/>
+      <c r="T13" s="270"/>
+      <c r="U13" s="270"/>
+      <c r="V13" s="270"/>
+      <c r="W13" s="270"/>
+      <c r="X13" s="270"/>
+      <c r="Y13" s="270"/>
+      <c r="Z13" s="270"/>
+      <c r="AA13" s="270"/>
+      <c r="AB13" s="270"/>
+      <c r="AC13" s="270"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B14" s="16" t="s">
@@ -16086,33 +16209,33 @@
       <c r="Q22" s="92"/>
     </row>
     <row r="23" spans="2:31" x14ac:dyDescent="0.2">
-      <c r="C23" s="266" t="s">
+      <c r="C23" s="268" t="s">
         <v>124</v>
       </c>
-      <c r="D23" s="266"/>
-      <c r="E23" s="266"/>
-      <c r="F23" s="266"/>
-      <c r="G23" s="266"/>
-      <c r="H23" s="266"/>
-      <c r="I23" s="266"/>
-      <c r="J23" s="266"/>
-      <c r="K23" s="266"/>
-      <c r="L23" s="266"/>
+      <c r="D23" s="268"/>
+      <c r="E23" s="268"/>
+      <c r="F23" s="268"/>
+      <c r="G23" s="268"/>
+      <c r="H23" s="268"/>
+      <c r="I23" s="268"/>
+      <c r="J23" s="268"/>
+      <c r="K23" s="268"/>
+      <c r="L23" s="268"/>
       <c r="O23" s="5"/>
       <c r="Q23" s="92"/>
-      <c r="S23" s="267" t="s">
+      <c r="S23" s="269" t="s">
         <v>124</v>
       </c>
-      <c r="T23" s="268"/>
-      <c r="U23" s="268"/>
-      <c r="V23" s="268"/>
-      <c r="W23" s="268"/>
-      <c r="X23" s="268"/>
-      <c r="Y23" s="268"/>
-      <c r="Z23" s="268"/>
-      <c r="AA23" s="268"/>
-      <c r="AB23" s="268"/>
-      <c r="AC23" s="268"/>
+      <c r="T23" s="270"/>
+      <c r="U23" s="270"/>
+      <c r="V23" s="270"/>
+      <c r="W23" s="270"/>
+      <c r="X23" s="270"/>
+      <c r="Y23" s="270"/>
+      <c r="Z23" s="270"/>
+      <c r="AA23" s="270"/>
+      <c r="AB23" s="270"/>
+      <c r="AC23" s="270"/>
       <c r="AE23" s="88" t="str">
         <f>AE2</f>
         <v>TTM/YTD</v>
@@ -17431,32 +17554,32 @@
       <c r="O39" s="5"/>
     </row>
     <row r="40" spans="2:31" x14ac:dyDescent="0.2">
-      <c r="C40" s="266" t="s">
+      <c r="C40" s="268" t="s">
         <v>126</v>
       </c>
-      <c r="D40" s="266"/>
-      <c r="E40" s="266"/>
-      <c r="F40" s="266"/>
-      <c r="G40" s="266"/>
-      <c r="H40" s="266"/>
-      <c r="I40" s="266"/>
-      <c r="J40" s="266"/>
-      <c r="K40" s="266"/>
-      <c r="L40" s="266"/>
+      <c r="D40" s="268"/>
+      <c r="E40" s="268"/>
+      <c r="F40" s="268"/>
+      <c r="G40" s="268"/>
+      <c r="H40" s="268"/>
+      <c r="I40" s="268"/>
+      <c r="J40" s="268"/>
+      <c r="K40" s="268"/>
+      <c r="L40" s="268"/>
       <c r="O40" s="5"/>
-      <c r="S40" s="267" t="s">
+      <c r="S40" s="269" t="s">
         <v>126</v>
       </c>
-      <c r="T40" s="268"/>
-      <c r="U40" s="268"/>
-      <c r="V40" s="268"/>
-      <c r="W40" s="268"/>
-      <c r="X40" s="268"/>
-      <c r="Y40" s="268"/>
-      <c r="Z40" s="268"/>
-      <c r="AA40" s="268"/>
-      <c r="AB40" s="268"/>
-      <c r="AC40" s="268"/>
+      <c r="T40" s="270"/>
+      <c r="U40" s="270"/>
+      <c r="V40" s="270"/>
+      <c r="W40" s="270"/>
+      <c r="X40" s="270"/>
+      <c r="Y40" s="270"/>
+      <c r="Z40" s="270"/>
+      <c r="AA40" s="270"/>
+      <c r="AB40" s="270"/>
+      <c r="AC40" s="270"/>
     </row>
     <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -18023,18 +18146,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="S2:Z2"/>
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="S4:AC4"/>
     <mergeCell ref="C13:L13"/>
     <mergeCell ref="S13:AC13"/>
     <mergeCell ref="C23:L23"/>
     <mergeCell ref="S23:AC23"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="S40:AC40"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="S2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="S4:AC4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -18068,35 +18191,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="258" t="s">
+      <c r="C2" s="262" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="258"/>
-      <c r="E2" s="258"/>
-      <c r="F2" s="258"/>
-      <c r="G2" s="264"/>
-      <c r="H2" s="265" t="s">
+      <c r="D2" s="262"/>
+      <c r="E2" s="262"/>
+      <c r="F2" s="262"/>
+      <c r="G2" s="271"/>
+      <c r="H2" s="272" t="s">
         <v>114</v>
       </c>
-      <c r="I2" s="258"/>
-      <c r="J2" s="258"/>
-      <c r="K2" s="258"/>
-      <c r="L2" s="258"/>
-      <c r="P2" s="258" t="s">
+      <c r="I2" s="262"/>
+      <c r="J2" s="262"/>
+      <c r="K2" s="262"/>
+      <c r="L2" s="262"/>
+      <c r="P2" s="262" t="s">
         <v>113</v>
       </c>
-      <c r="Q2" s="258"/>
-      <c r="R2" s="258"/>
-      <c r="S2" s="258"/>
-      <c r="T2" s="258"/>
-      <c r="U2" s="258"/>
-      <c r="V2" s="258"/>
-      <c r="W2" s="258"/>
-      <c r="X2" s="258" t="s">
+      <c r="Q2" s="262"/>
+      <c r="R2" s="262"/>
+      <c r="S2" s="262"/>
+      <c r="T2" s="262"/>
+      <c r="U2" s="262"/>
+      <c r="V2" s="262"/>
+      <c r="W2" s="262"/>
+      <c r="X2" s="262" t="s">
         <v>114</v>
       </c>
-      <c r="Y2" s="258"/>
-      <c r="Z2" s="258"/>
+      <c r="Y2" s="262"/>
+      <c r="Z2" s="262"/>
       <c r="AB2" s="86" t="s">
         <v>115</v>
       </c>
@@ -18105,31 +18228,31 @@
     <row r="4" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="266" t="s">
+      <c r="C4" s="268" t="s">
         <v>116</v>
       </c>
-      <c r="D4" s="266"/>
-      <c r="E4" s="266"/>
-      <c r="F4" s="266"/>
-      <c r="G4" s="266"/>
-      <c r="H4" s="266"/>
-      <c r="I4" s="266"/>
-      <c r="J4" s="266"/>
-      <c r="K4" s="266"/>
-      <c r="L4" s="266"/>
-      <c r="P4" s="268" t="s">
+      <c r="D4" s="268"/>
+      <c r="E4" s="268"/>
+      <c r="F4" s="268"/>
+      <c r="G4" s="268"/>
+      <c r="H4" s="268"/>
+      <c r="I4" s="268"/>
+      <c r="J4" s="268"/>
+      <c r="K4" s="268"/>
+      <c r="L4" s="268"/>
+      <c r="P4" s="270" t="s">
         <v>116</v>
       </c>
-      <c r="Q4" s="268"/>
-      <c r="R4" s="268"/>
-      <c r="S4" s="268"/>
-      <c r="T4" s="268"/>
-      <c r="U4" s="268"/>
-      <c r="V4" s="268"/>
-      <c r="W4" s="268"/>
-      <c r="X4" s="268"/>
-      <c r="Y4" s="268"/>
-      <c r="Z4" s="268"/>
+      <c r="Q4" s="270"/>
+      <c r="R4" s="270"/>
+      <c r="S4" s="270"/>
+      <c r="T4" s="270"/>
+      <c r="U4" s="270"/>
+      <c r="V4" s="270"/>
+      <c r="W4" s="270"/>
+      <c r="X4" s="270"/>
+      <c r="Y4" s="270"/>
+      <c r="Z4" s="270"/>
       <c r="AB4" s="88"/>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
@@ -18324,32 +18447,32 @@
       <c r="N8" s="92"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C9" s="266" t="s">
+      <c r="C9" s="268" t="s">
         <v>129</v>
       </c>
-      <c r="D9" s="266"/>
-      <c r="E9" s="266"/>
-      <c r="F9" s="266"/>
-      <c r="G9" s="266"/>
-      <c r="H9" s="266"/>
-      <c r="I9" s="266"/>
-      <c r="J9" s="266"/>
-      <c r="K9" s="266"/>
-      <c r="L9" s="266"/>
+      <c r="D9" s="268"/>
+      <c r="E9" s="268"/>
+      <c r="F9" s="268"/>
+      <c r="G9" s="268"/>
+      <c r="H9" s="268"/>
+      <c r="I9" s="268"/>
+      <c r="J9" s="268"/>
+      <c r="K9" s="268"/>
+      <c r="L9" s="268"/>
       <c r="N9" s="92"/>
-      <c r="P9" s="268" t="s">
+      <c r="P9" s="270" t="s">
         <v>130</v>
       </c>
-      <c r="Q9" s="268"/>
-      <c r="R9" s="268"/>
-      <c r="S9" s="268"/>
-      <c r="T9" s="268"/>
-      <c r="U9" s="268"/>
-      <c r="V9" s="268"/>
-      <c r="W9" s="268"/>
-      <c r="X9" s="268"/>
-      <c r="Y9" s="268"/>
-      <c r="Z9" s="268"/>
+      <c r="Q9" s="270"/>
+      <c r="R9" s="270"/>
+      <c r="S9" s="270"/>
+      <c r="T9" s="270"/>
+      <c r="U9" s="270"/>
+      <c r="V9" s="270"/>
+      <c r="W9" s="270"/>
+      <c r="X9" s="270"/>
+      <c r="Y9" s="270"/>
+      <c r="Z9" s="270"/>
       <c r="AB9" s="88">
         <f>AB4</f>
         <v>0</v>
@@ -18919,31 +19042,31 @@
       </c>
     </row>
     <row r="18" spans="2:26" x14ac:dyDescent="0.2">
-      <c r="C18" s="266" t="s">
+      <c r="C18" s="268" t="s">
         <v>132</v>
       </c>
-      <c r="D18" s="266"/>
-      <c r="E18" s="266"/>
-      <c r="F18" s="266"/>
-      <c r="G18" s="266"/>
-      <c r="H18" s="266"/>
-      <c r="I18" s="266"/>
-      <c r="J18" s="266"/>
-      <c r="K18" s="266"/>
-      <c r="L18" s="266"/>
-      <c r="P18" s="268" t="s">
+      <c r="D18" s="268"/>
+      <c r="E18" s="268"/>
+      <c r="F18" s="268"/>
+      <c r="G18" s="268"/>
+      <c r="H18" s="268"/>
+      <c r="I18" s="268"/>
+      <c r="J18" s="268"/>
+      <c r="K18" s="268"/>
+      <c r="L18" s="268"/>
+      <c r="P18" s="270" t="s">
         <v>132</v>
       </c>
-      <c r="Q18" s="268"/>
-      <c r="R18" s="268"/>
-      <c r="S18" s="268"/>
-      <c r="T18" s="268"/>
-      <c r="U18" s="268"/>
-      <c r="V18" s="268"/>
-      <c r="W18" s="268"/>
-      <c r="X18" s="268"/>
-      <c r="Y18" s="268"/>
-      <c r="Z18" s="268"/>
+      <c r="Q18" s="270"/>
+      <c r="R18" s="270"/>
+      <c r="S18" s="270"/>
+      <c r="T18" s="270"/>
+      <c r="U18" s="270"/>
+      <c r="V18" s="270"/>
+      <c r="W18" s="270"/>
+      <c r="X18" s="270"/>
+      <c r="Y18" s="270"/>
+      <c r="Z18" s="270"/>
     </row>
     <row r="19" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -19503,60 +19626,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="258" t="s">
+      <c r="C3" s="262" t="s">
         <v>113</v>
       </c>
-      <c r="D3" s="258"/>
-      <c r="E3" s="258"/>
-      <c r="F3" s="258"/>
-      <c r="G3" s="264"/>
-      <c r="H3" s="265" t="s">
+      <c r="D3" s="262"/>
+      <c r="E3" s="262"/>
+      <c r="F3" s="262"/>
+      <c r="G3" s="271"/>
+      <c r="H3" s="272" t="s">
         <v>114</v>
       </c>
-      <c r="I3" s="258"/>
-      <c r="J3" s="258"/>
-      <c r="K3" s="258"/>
-      <c r="L3" s="258"/>
-      <c r="P3" s="269"/>
-      <c r="Q3" s="269"/>
-      <c r="R3" s="269"/>
-      <c r="S3" s="269"/>
-      <c r="T3" s="269"/>
-      <c r="U3" s="269"/>
-      <c r="V3" s="269"/>
-      <c r="W3" s="269"/>
-      <c r="X3" s="269"/>
-      <c r="Y3" s="269"/>
-      <c r="Z3" s="269"/>
+      <c r="I3" s="262"/>
+      <c r="J3" s="262"/>
+      <c r="K3" s="262"/>
+      <c r="L3" s="262"/>
+      <c r="P3" s="273"/>
+      <c r="Q3" s="273"/>
+      <c r="R3" s="273"/>
+      <c r="S3" s="273"/>
+      <c r="T3" s="273"/>
+      <c r="U3" s="273"/>
+      <c r="V3" s="273"/>
+      <c r="W3" s="273"/>
+      <c r="X3" s="273"/>
+      <c r="Y3" s="273"/>
+      <c r="Z3" s="273"/>
       <c r="AB3" s="111"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="87"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="266" t="s">
+      <c r="C5" s="268" t="s">
         <v>116</v>
       </c>
-      <c r="D5" s="266"/>
-      <c r="E5" s="266"/>
-      <c r="F5" s="266"/>
-      <c r="G5" s="266"/>
-      <c r="H5" s="266"/>
-      <c r="I5" s="266"/>
-      <c r="J5" s="266"/>
-      <c r="K5" s="266"/>
-      <c r="L5" s="266"/>
-      <c r="P5" s="269"/>
-      <c r="Q5" s="269"/>
-      <c r="R5" s="269"/>
-      <c r="S5" s="269"/>
-      <c r="T5" s="269"/>
-      <c r="U5" s="269"/>
-      <c r="V5" s="269"/>
-      <c r="W5" s="269"/>
-      <c r="X5" s="269"/>
-      <c r="Y5" s="269"/>
-      <c r="Z5" s="269"/>
+      <c r="D5" s="268"/>
+      <c r="E5" s="268"/>
+      <c r="F5" s="268"/>
+      <c r="G5" s="268"/>
+      <c r="H5" s="268"/>
+      <c r="I5" s="268"/>
+      <c r="J5" s="268"/>
+      <c r="K5" s="268"/>
+      <c r="L5" s="268"/>
+      <c r="P5" s="273"/>
+      <c r="Q5" s="273"/>
+      <c r="R5" s="273"/>
+      <c r="S5" s="273"/>
+      <c r="T5" s="273"/>
+      <c r="U5" s="273"/>
+      <c r="V5" s="273"/>
+      <c r="W5" s="273"/>
+      <c r="X5" s="273"/>
+      <c r="Y5" s="273"/>
+      <c r="Z5" s="273"/>
       <c r="AB5" s="112"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -19742,30 +19865,30 @@
       <c r="N10" s="92"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="266" t="s">
+      <c r="C11" s="268" t="s">
         <v>136</v>
       </c>
-      <c r="D11" s="266"/>
-      <c r="E11" s="266"/>
-      <c r="F11" s="266"/>
-      <c r="G11" s="266"/>
-      <c r="H11" s="266"/>
-      <c r="I11" s="266"/>
-      <c r="J11" s="266"/>
-      <c r="K11" s="266"/>
-      <c r="L11" s="266"/>
+      <c r="D11" s="268"/>
+      <c r="E11" s="268"/>
+      <c r="F11" s="268"/>
+      <c r="G11" s="268"/>
+      <c r="H11" s="268"/>
+      <c r="I11" s="268"/>
+      <c r="J11" s="268"/>
+      <c r="K11" s="268"/>
+      <c r="L11" s="268"/>
       <c r="N11" s="92"/>
-      <c r="P11" s="269"/>
-      <c r="Q11" s="269"/>
-      <c r="R11" s="269"/>
-      <c r="S11" s="269"/>
-      <c r="T11" s="269"/>
-      <c r="U11" s="269"/>
-      <c r="V11" s="269"/>
-      <c r="W11" s="269"/>
-      <c r="X11" s="269"/>
-      <c r="Y11" s="269"/>
-      <c r="Z11" s="269"/>
+      <c r="P11" s="273"/>
+      <c r="Q11" s="273"/>
+      <c r="R11" s="273"/>
+      <c r="S11" s="273"/>
+      <c r="T11" s="273"/>
+      <c r="U11" s="273"/>
+      <c r="V11" s="273"/>
+      <c r="W11" s="273"/>
+      <c r="X11" s="273"/>
+      <c r="Y11" s="273"/>
+      <c r="Z11" s="273"/>
       <c r="AB11" s="112"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.2">
@@ -20007,18 +20130,18 @@
       <c r="D16" s="24"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="266" t="s">
+      <c r="C18" s="268" t="s">
         <v>141</v>
       </c>
-      <c r="D18" s="266"/>
-      <c r="E18" s="266"/>
-      <c r="F18" s="266"/>
-      <c r="G18" s="266"/>
-      <c r="H18" s="266"/>
-      <c r="I18" s="266"/>
-      <c r="J18" s="266"/>
-      <c r="K18" s="266"/>
-      <c r="L18" s="266"/>
+      <c r="D18" s="268"/>
+      <c r="E18" s="268"/>
+      <c r="F18" s="268"/>
+      <c r="G18" s="268"/>
+      <c r="H18" s="268"/>
+      <c r="I18" s="268"/>
+      <c r="J18" s="268"/>
+      <c r="K18" s="268"/>
+      <c r="L18" s="268"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -20231,23 +20354,23 @@
       </c>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B25" s="269"/>
-      <c r="C25" s="269"/>
+      <c r="B25" s="273"/>
+      <c r="C25" s="273"/>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="111"/>
-      <c r="C26" s="266" t="s">
+      <c r="C26" s="268" t="s">
         <v>147</v>
       </c>
-      <c r="D26" s="266"/>
-      <c r="E26" s="266"/>
-      <c r="F26" s="266"/>
-      <c r="G26" s="266"/>
-      <c r="H26" s="266"/>
-      <c r="I26" s="266"/>
-      <c r="J26" s="266"/>
-      <c r="K26" s="266"/>
-      <c r="L26" s="266"/>
+      <c r="D26" s="268"/>
+      <c r="E26" s="268"/>
+      <c r="F26" s="268"/>
+      <c r="G26" s="268"/>
+      <c r="H26" s="268"/>
+      <c r="I26" s="268"/>
+      <c r="J26" s="268"/>
+      <c r="K26" s="268"/>
+      <c r="L26" s="268"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="16" t="s">
@@ -20439,18 +20562,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="111"/>
-      <c r="C33" s="266" t="s">
+      <c r="C33" s="268" t="s">
         <v>151</v>
       </c>
-      <c r="D33" s="266"/>
-      <c r="E33" s="266"/>
-      <c r="F33" s="266"/>
-      <c r="G33" s="266"/>
-      <c r="H33" s="266"/>
-      <c r="I33" s="266"/>
-      <c r="J33" s="266"/>
-      <c r="K33" s="266"/>
-      <c r="L33" s="266"/>
+      <c r="D33" s="268"/>
+      <c r="E33" s="268"/>
+      <c r="F33" s="268"/>
+      <c r="G33" s="268"/>
+      <c r="H33" s="268"/>
+      <c r="I33" s="268"/>
+      <c r="J33" s="268"/>
+      <c r="K33" s="268"/>
+      <c r="L33" s="268"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
@@ -20634,18 +20757,18 @@
       <c r="C39" s="127"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="266" t="s">
+      <c r="C40" s="268" t="s">
         <v>154</v>
       </c>
-      <c r="D40" s="266"/>
-      <c r="E40" s="266"/>
-      <c r="F40" s="266"/>
-      <c r="G40" s="266"/>
-      <c r="H40" s="266"/>
-      <c r="I40" s="266"/>
-      <c r="J40" s="266"/>
-      <c r="K40" s="266"/>
-      <c r="L40" s="266"/>
+      <c r="D40" s="268"/>
+      <c r="E40" s="268"/>
+      <c r="F40" s="268"/>
+      <c r="G40" s="268"/>
+      <c r="H40" s="268"/>
+      <c r="I40" s="268"/>
+      <c r="J40" s="268"/>
+      <c r="K40" s="268"/>
+      <c r="L40" s="268"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -20909,12 +21032,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -20922,6 +21039,12 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -20959,60 +21082,60 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="258" t="s">
+      <c r="C2" s="262" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="258"/>
-      <c r="E2" s="258"/>
-      <c r="F2" s="258"/>
-      <c r="G2" s="264"/>
-      <c r="H2" s="265" t="s">
+      <c r="D2" s="262"/>
+      <c r="E2" s="262"/>
+      <c r="F2" s="262"/>
+      <c r="G2" s="271"/>
+      <c r="H2" s="272" t="s">
         <v>114</v>
       </c>
-      <c r="I2" s="258"/>
-      <c r="J2" s="258"/>
-      <c r="K2" s="258"/>
-      <c r="L2" s="258"/>
-      <c r="S2" s="269"/>
-      <c r="T2" s="269"/>
-      <c r="U2" s="269"/>
-      <c r="V2" s="269"/>
-      <c r="W2" s="269"/>
-      <c r="X2" s="269"/>
-      <c r="Y2" s="269"/>
-      <c r="Z2" s="269"/>
-      <c r="AA2" s="269"/>
-      <c r="AB2" s="269"/>
-      <c r="AC2" s="269"/>
+      <c r="I2" s="262"/>
+      <c r="J2" s="262"/>
+      <c r="K2" s="262"/>
+      <c r="L2" s="262"/>
+      <c r="S2" s="273"/>
+      <c r="T2" s="273"/>
+      <c r="U2" s="273"/>
+      <c r="V2" s="273"/>
+      <c r="W2" s="273"/>
+      <c r="X2" s="273"/>
+      <c r="Y2" s="273"/>
+      <c r="Z2" s="273"/>
+      <c r="AA2" s="273"/>
+      <c r="AB2" s="273"/>
+      <c r="AC2" s="273"/>
       <c r="AE2" s="111"/>
     </row>
     <row r="3" spans="1:31" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="266" t="s">
+      <c r="C4" s="268" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="266"/>
-      <c r="E4" s="266"/>
-      <c r="F4" s="266"/>
-      <c r="G4" s="266"/>
-      <c r="H4" s="266"/>
-      <c r="I4" s="266"/>
-      <c r="J4" s="266"/>
-      <c r="K4" s="266"/>
-      <c r="L4" s="266"/>
-      <c r="S4" s="269"/>
-      <c r="T4" s="269"/>
-      <c r="U4" s="269"/>
-      <c r="V4" s="269"/>
-      <c r="W4" s="269"/>
-      <c r="X4" s="269"/>
-      <c r="Y4" s="269"/>
-      <c r="Z4" s="269"/>
-      <c r="AA4" s="269"/>
-      <c r="AB4" s="269"/>
-      <c r="AC4" s="269"/>
+      <c r="D4" s="268"/>
+      <c r="E4" s="268"/>
+      <c r="F4" s="268"/>
+      <c r="G4" s="268"/>
+      <c r="H4" s="268"/>
+      <c r="I4" s="268"/>
+      <c r="J4" s="268"/>
+      <c r="K4" s="268"/>
+      <c r="L4" s="268"/>
+      <c r="S4" s="273"/>
+      <c r="T4" s="273"/>
+      <c r="U4" s="273"/>
+      <c r="V4" s="273"/>
+      <c r="W4" s="273"/>
+      <c r="X4" s="273"/>
+      <c r="Y4" s="273"/>
+      <c r="Z4" s="273"/>
+      <c r="AA4" s="273"/>
+      <c r="AB4" s="273"/>
+      <c r="AC4" s="273"/>
       <c r="AE4" s="112"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -21375,18 +21498,18 @@
       <c r="AE10" s="64"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="266" t="s">
+      <c r="C13" s="268" t="s">
         <v>162</v>
       </c>
-      <c r="D13" s="266"/>
-      <c r="E13" s="266"/>
-      <c r="F13" s="266"/>
-      <c r="G13" s="266"/>
-      <c r="H13" s="266"/>
-      <c r="I13" s="266"/>
-      <c r="J13" s="266"/>
-      <c r="K13" s="266"/>
-      <c r="L13" s="266"/>
+      <c r="D13" s="268"/>
+      <c r="E13" s="268"/>
+      <c r="F13" s="268"/>
+      <c r="G13" s="268"/>
+      <c r="H13" s="268"/>
+      <c r="I13" s="268"/>
+      <c r="J13" s="268"/>
+      <c r="K13" s="268"/>
+      <c r="L13" s="268"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="12">
@@ -21479,18 +21602,18 @@
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C18" s="266" t="s">
+      <c r="C18" s="268" t="s">
         <v>163</v>
       </c>
-      <c r="D18" s="266"/>
-      <c r="E18" s="266"/>
-      <c r="F18" s="266"/>
-      <c r="G18" s="266"/>
-      <c r="H18" s="266"/>
-      <c r="I18" s="266"/>
-      <c r="J18" s="266"/>
-      <c r="K18" s="266"/>
-      <c r="L18" s="266"/>
+      <c r="D18" s="268"/>
+      <c r="E18" s="268"/>
+      <c r="F18" s="268"/>
+      <c r="G18" s="268"/>
+      <c r="H18" s="268"/>
+      <c r="I18" s="268"/>
+      <c r="J18" s="268"/>
+      <c r="K18" s="268"/>
+      <c r="L18" s="268"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -21682,18 +21805,18 @@
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C25" s="266" t="s">
+      <c r="C25" s="268" t="s">
         <v>266</v>
       </c>
-      <c r="D25" s="266"/>
-      <c r="E25" s="266"/>
-      <c r="F25" s="266"/>
-      <c r="G25" s="266"/>
-      <c r="H25" s="266"/>
-      <c r="I25" s="266"/>
-      <c r="J25" s="266"/>
-      <c r="K25" s="266"/>
-      <c r="L25" s="266"/>
+      <c r="D25" s="268"/>
+      <c r="E25" s="268"/>
+      <c r="F25" s="268"/>
+      <c r="G25" s="268"/>
+      <c r="H25" s="268"/>
+      <c r="I25" s="268"/>
+      <c r="J25" s="268"/>
+      <c r="K25" s="268"/>
+      <c r="L25" s="268"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B26" s="16" t="s">
@@ -21831,18 +21954,18 @@
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C31" s="266" t="s">
+      <c r="C31" s="268" t="s">
         <v>78</v>
       </c>
-      <c r="D31" s="266"/>
-      <c r="E31" s="266"/>
-      <c r="F31" s="266"/>
-      <c r="G31" s="266"/>
-      <c r="H31" s="266"/>
-      <c r="I31" s="266"/>
-      <c r="J31" s="266"/>
-      <c r="K31" s="266"/>
-      <c r="L31" s="266"/>
+      <c r="D31" s="268"/>
+      <c r="E31" s="268"/>
+      <c r="F31" s="268"/>
+      <c r="G31" s="268"/>
+      <c r="H31" s="268"/>
+      <c r="I31" s="268"/>
+      <c r="J31" s="268"/>
+      <c r="K31" s="268"/>
+      <c r="L31" s="268"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="16" t="s">
@@ -21981,16 +22104,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C31:L31"/>
+    <mergeCell ref="C25:L25"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="S2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
     <mergeCell ref="C13:L13"/>
     <mergeCell ref="C18:L18"/>
-    <mergeCell ref="C31:L31"/>
-    <mergeCell ref="C25:L25"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="S2:Z2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -22004,18 +22127,57 @@
   <sheetPr>
     <tabColor theme="6" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="B13"/>
+  <dimension ref="B5:H13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="10.83203125" style="1"/>
+    <col min="1" max="7" width="10.83203125" style="1"/>
+    <col min="8" max="8" width="17.33203125" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="13" spans="2:2" s="4" customFormat="1" ht="49" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H5" s="134" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H6" s="257" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H7" s="257" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H8" s="257" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H9" s="257" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H10" s="258" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" s="4" customFormat="1" ht="49" x14ac:dyDescent="0.2">
       <c r="B13" s="3" t="s">
         <v>168</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="H6" location="Overview!B3" display="Overview'!B3" xr:uid="{BD4BBD1D-850C-C04D-9BCC-AF07CB5BD671}"/>
+    <hyperlink ref="H8" location="'Analysis -&gt;'!B13" display="'Analysis -&gt;'!B13" xr:uid="{E2C5673D-D268-9E48-A2FB-31DB6DD94B6A}"/>
+    <hyperlink ref="H9" location="'Forecast -&gt;'!B13" display="'Forecast -&gt;'!B13" xr:uid="{385C5B83-2040-6A4E-959F-22FA9A190462}"/>
+    <hyperlink ref="H10" location="'Valuation -&gt;'!B13" display="'Valuation -&gt;'!B13" xr:uid="{9CC1EBF3-31DF-3540-A9CC-5B8E246ED24F}"/>
+    <hyperlink ref="H7" location="'Financials -&gt;'!B13" display="'Financials -&gt;'!B13" xr:uid="{54A00459-1C54-A141-837E-D62AA2660345}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -22053,10 +22215,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="258" t="s">
+      <c r="B4" s="262" t="s">
         <v>170</v>
       </c>
-      <c r="C4" s="258"/>
+      <c r="C4" s="262"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -22073,7 +22235,7 @@
       </c>
       <c r="C6" s="135">
         <f ca="1">Overview!C5</f>
-        <v>149.91999999999999</v>
+        <v>147.74</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22082,7 +22244,7 @@
       </c>
       <c r="C7" s="136">
         <f ca="1">C5*C6</f>
-        <v>7514290.2399999993</v>
+        <v>7405024.2800000003</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22141,10 +22303,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="258" t="s">
+      <c r="B15" s="262" t="s">
         <v>177</v>
       </c>
-      <c r="C15" s="258"/>
+      <c r="C15" s="262"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -22233,60 +22395,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="258" t="s">
+      <c r="C3" s="262" t="s">
         <v>113</v>
       </c>
-      <c r="D3" s="258"/>
-      <c r="E3" s="258"/>
-      <c r="F3" s="258"/>
-      <c r="G3" s="264"/>
-      <c r="H3" s="265" t="s">
+      <c r="D3" s="262"/>
+      <c r="E3" s="262"/>
+      <c r="F3" s="262"/>
+      <c r="G3" s="271"/>
+      <c r="H3" s="272" t="s">
         <v>114</v>
       </c>
-      <c r="I3" s="258"/>
-      <c r="J3" s="258"/>
-      <c r="K3" s="258"/>
-      <c r="L3" s="258"/>
-      <c r="P3" s="269"/>
-      <c r="Q3" s="269"/>
-      <c r="R3" s="269"/>
-      <c r="S3" s="269"/>
-      <c r="T3" s="269"/>
-      <c r="U3" s="269"/>
-      <c r="V3" s="269"/>
-      <c r="W3" s="269"/>
-      <c r="X3" s="269"/>
-      <c r="Y3" s="269"/>
-      <c r="Z3" s="269"/>
+      <c r="I3" s="262"/>
+      <c r="J3" s="262"/>
+      <c r="K3" s="262"/>
+      <c r="L3" s="262"/>
+      <c r="P3" s="273"/>
+      <c r="Q3" s="273"/>
+      <c r="R3" s="273"/>
+      <c r="S3" s="273"/>
+      <c r="T3" s="273"/>
+      <c r="U3" s="273"/>
+      <c r="V3" s="273"/>
+      <c r="W3" s="273"/>
+      <c r="X3" s="273"/>
+      <c r="Y3" s="273"/>
+      <c r="Z3" s="273"/>
       <c r="AB3" s="111"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="87"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="266" t="s">
+      <c r="C5" s="268" t="s">
         <v>184</v>
       </c>
-      <c r="D5" s="266"/>
-      <c r="E5" s="266"/>
-      <c r="F5" s="266"/>
-      <c r="G5" s="266"/>
-      <c r="H5" s="266"/>
-      <c r="I5" s="266"/>
-      <c r="J5" s="266"/>
-      <c r="K5" s="266"/>
-      <c r="L5" s="266"/>
-      <c r="P5" s="269"/>
-      <c r="Q5" s="269"/>
-      <c r="R5" s="269"/>
-      <c r="S5" s="269"/>
-      <c r="T5" s="269"/>
-      <c r="U5" s="269"/>
-      <c r="V5" s="269"/>
-      <c r="W5" s="269"/>
-      <c r="X5" s="269"/>
-      <c r="Y5" s="269"/>
-      <c r="Z5" s="269"/>
+      <c r="D5" s="268"/>
+      <c r="E5" s="268"/>
+      <c r="F5" s="268"/>
+      <c r="G5" s="268"/>
+      <c r="H5" s="268"/>
+      <c r="I5" s="268"/>
+      <c r="J5" s="268"/>
+      <c r="K5" s="268"/>
+      <c r="L5" s="268"/>
+      <c r="P5" s="273"/>
+      <c r="Q5" s="273"/>
+      <c r="R5" s="273"/>
+      <c r="S5" s="273"/>
+      <c r="T5" s="273"/>
+      <c r="U5" s="273"/>
+      <c r="V5" s="273"/>
+      <c r="W5" s="273"/>
+      <c r="X5" s="273"/>
+      <c r="Y5" s="273"/>
+      <c r="Z5" s="273"/>
       <c r="AB5" s="112"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -22532,10 +22694,10 @@
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="258" t="s">
+      <c r="B13" s="262" t="s">
         <v>188</v>
       </c>
-      <c r="C13" s="258"/>
+      <c r="C13" s="262"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -22555,10 +22717,10 @@
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="258" t="s">
+      <c r="B18" s="262" t="s">
         <v>190</v>
       </c>
-      <c r="C18" s="258"/>
+      <c r="C18" s="262"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -22672,37 +22834,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="258" t="s">
+      <c r="C2" s="262" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="258"/>
-      <c r="E2" s="258"/>
-      <c r="F2" s="258"/>
-      <c r="G2" s="264"/>
-      <c r="H2" s="265" t="s">
+      <c r="D2" s="262"/>
+      <c r="E2" s="262"/>
+      <c r="F2" s="262"/>
+      <c r="G2" s="271"/>
+      <c r="H2" s="272" t="s">
         <v>114</v>
       </c>
-      <c r="I2" s="258"/>
-      <c r="J2" s="258"/>
-      <c r="K2" s="258"/>
-      <c r="L2" s="258"/>
+      <c r="I2" s="262"/>
+      <c r="J2" s="262"/>
+      <c r="K2" s="262"/>
+      <c r="L2" s="262"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="266" t="s">
+      <c r="C4" s="268" t="s">
         <v>198</v>
       </c>
-      <c r="D4" s="266"/>
-      <c r="E4" s="266"/>
-      <c r="F4" s="266"/>
-      <c r="G4" s="266"/>
-      <c r="H4" s="266"/>
-      <c r="I4" s="266"/>
-      <c r="J4" s="266"/>
-      <c r="K4" s="266"/>
-      <c r="L4" s="266"/>
+      <c r="D4" s="268"/>
+      <c r="E4" s="268"/>
+      <c r="F4" s="268"/>
+      <c r="G4" s="268"/>
+      <c r="H4" s="268"/>
+      <c r="I4" s="268"/>
+      <c r="J4" s="268"/>
+      <c r="K4" s="268"/>
+      <c r="L4" s="268"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -22922,18 +23084,18 @@
       <c r="N10" s="92"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C11" s="266" t="s">
+      <c r="C11" s="268" t="s">
         <v>122</v>
       </c>
-      <c r="D11" s="266"/>
-      <c r="E11" s="266"/>
-      <c r="F11" s="266"/>
-      <c r="G11" s="266"/>
-      <c r="H11" s="266"/>
-      <c r="I11" s="266"/>
-      <c r="J11" s="266"/>
-      <c r="K11" s="266"/>
-      <c r="L11" s="266"/>
+      <c r="D11" s="268"/>
+      <c r="E11" s="268"/>
+      <c r="F11" s="268"/>
+      <c r="G11" s="268"/>
+      <c r="H11" s="268"/>
+      <c r="I11" s="268"/>
+      <c r="J11" s="268"/>
+      <c r="K11" s="268"/>
+      <c r="L11" s="268"/>
       <c r="N11" s="92"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -23127,18 +23289,18 @@
       <c r="N16" s="92"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C17" s="266" t="s">
+      <c r="C17" s="268" t="s">
         <v>200</v>
       </c>
-      <c r="D17" s="266"/>
-      <c r="E17" s="266"/>
-      <c r="F17" s="266"/>
-      <c r="G17" s="266"/>
-      <c r="H17" s="266"/>
-      <c r="I17" s="266"/>
-      <c r="J17" s="266"/>
-      <c r="K17" s="266"/>
-      <c r="L17" s="266"/>
+      <c r="D17" s="268"/>
+      <c r="E17" s="268"/>
+      <c r="F17" s="268"/>
+      <c r="G17" s="268"/>
+      <c r="H17" s="268"/>
+      <c r="I17" s="268"/>
+      <c r="J17" s="268"/>
+      <c r="K17" s="268"/>
+      <c r="L17" s="268"/>
       <c r="N17" s="92"/>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
@@ -23272,18 +23434,18 @@
       <c r="N21" s="92"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C22" s="266" t="s">
+      <c r="C22" s="268" t="s">
         <v>203</v>
       </c>
-      <c r="D22" s="266"/>
-      <c r="E22" s="266"/>
-      <c r="F22" s="266"/>
-      <c r="G22" s="266"/>
-      <c r="H22" s="266"/>
-      <c r="I22" s="266"/>
-      <c r="J22" s="266"/>
-      <c r="K22" s="266"/>
-      <c r="L22" s="266"/>
+      <c r="D22" s="268"/>
+      <c r="E22" s="268"/>
+      <c r="F22" s="268"/>
+      <c r="G22" s="268"/>
+      <c r="H22" s="268"/>
+      <c r="I22" s="268"/>
+      <c r="J22" s="268"/>
+      <c r="K22" s="268"/>
+      <c r="L22" s="268"/>
       <c r="N22" s="92"/>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.2">
@@ -23367,18 +23529,18 @@
       <c r="N26" s="92"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C27" s="266" t="s">
+      <c r="C27" s="268" t="s">
         <v>204</v>
       </c>
-      <c r="D27" s="266"/>
-      <c r="E27" s="266"/>
-      <c r="F27" s="266"/>
-      <c r="G27" s="266"/>
-      <c r="H27" s="266"/>
-      <c r="I27" s="266"/>
-      <c r="J27" s="266"/>
-      <c r="K27" s="266"/>
-      <c r="L27" s="266"/>
+      <c r="D27" s="268"/>
+      <c r="E27" s="268"/>
+      <c r="F27" s="268"/>
+      <c r="G27" s="268"/>
+      <c r="H27" s="268"/>
+      <c r="I27" s="268"/>
+      <c r="J27" s="268"/>
+      <c r="K27" s="268"/>
+      <c r="L27" s="268"/>
       <c r="N27" s="92"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.2">
@@ -23679,10 +23841,10 @@
       <c r="N38" s="92"/>
     </row>
     <row r="39" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B39" s="258" t="s">
+      <c r="B39" s="262" t="s">
         <v>209</v>
       </c>
-      <c r="C39" s="258"/>
+      <c r="C39" s="262"/>
       <c r="N39" s="92"/>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -23784,10 +23946,10 @@
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B52" s="258" t="s">
+      <c r="B52" s="262" t="s">
         <v>214</v>
       </c>
-      <c r="C52" s="258"/>
+      <c r="C52" s="262"/>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B53" s="1" t="s">
@@ -23843,10 +24005,10 @@
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B60" s="258" t="s">
+      <c r="B60" s="262" t="s">
         <v>327</v>
       </c>
-      <c r="C60" s="258"/>
+      <c r="C60" s="262"/>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B61" s="1" t="s">
@@ -23947,10 +24109,10 @@
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B73" s="258" t="s">
+      <c r="B73" s="262" t="s">
         <v>433</v>
       </c>
-      <c r="C73" s="258"/>
+      <c r="C73" s="262"/>
     </row>
     <row r="74" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B74" s="1" t="s">
@@ -24052,17 +24214,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="C27:L27"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B60:C60"/>
     <mergeCell ref="C22:L22"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="C17:L17"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="C27:L27"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B60:C60"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -24100,10 +24262,10 @@
       <c r="N3" s="92"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="258" t="s">
+      <c r="B4" s="262" t="s">
         <v>218</v>
       </c>
-      <c r="C4" s="258"/>
+      <c r="C4" s="262"/>
       <c r="N4" s="92"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -24166,7 +24328,7 @@
       </c>
       <c r="C11" s="135">
         <f ca="1">Overview!C5</f>
-        <v>149.91999999999999</v>
+        <v>147.74</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -24175,7 +24337,7 @@
       </c>
       <c r="C12" s="154">
         <f ca="1">(C10-C11)/C11</f>
-        <v>0.19874483408498603</v>
+        <v>0.21643309547868608</v>
       </c>
     </row>
   </sheetData>
@@ -24191,18 +24353,57 @@
   <sheetPr>
     <tabColor theme="6" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="B13"/>
+  <dimension ref="B5:H13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="10.83203125" style="1"/>
+    <col min="1" max="7" width="10.83203125" style="1"/>
+    <col min="8" max="8" width="16.6640625" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="13" spans="2:2" s="4" customFormat="1" ht="49" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H5" s="134" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H6" s="257" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H7" s="257" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H8" s="257" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H9" s="257" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H10" s="258" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" s="4" customFormat="1" ht="49" x14ac:dyDescent="0.2">
       <c r="B13" s="3" t="s">
         <v>15</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="H6" location="Overview!B3" display="Overview'!B3" xr:uid="{43F92576-E081-3349-8041-1D0736C4387B}"/>
+    <hyperlink ref="H8" location="'Analysis -&gt;'!B13" display="'Analysis -&gt;'!B13" xr:uid="{768BAAB0-4CD5-A74A-B3E4-FE7E6B235C16}"/>
+    <hyperlink ref="H9" location="'Forecast -&gt;'!B13" display="'Forecast -&gt;'!B13" xr:uid="{BDE6F3E7-1153-FF42-8B67-759D125896AC}"/>
+    <hyperlink ref="H10" location="'Valuation -&gt;'!B13" display="'Valuation -&gt;'!B13" xr:uid="{DB907F2A-DF85-0D46-8BFA-53745129BEB9}"/>
+    <hyperlink ref="H7" location="'Financials -&gt;'!B13" display="'Financials -&gt;'!B13" xr:uid="{B45ACB67-5258-0F4A-9418-8851277B2A40}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -24231,37 +24432,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="258" t="s">
+      <c r="C2" s="262" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="258"/>
-      <c r="E2" s="258"/>
-      <c r="F2" s="258"/>
-      <c r="G2" s="264"/>
-      <c r="H2" s="265" t="s">
+      <c r="D2" s="262"/>
+      <c r="E2" s="262"/>
+      <c r="F2" s="262"/>
+      <c r="G2" s="271"/>
+      <c r="H2" s="272" t="s">
         <v>114</v>
       </c>
-      <c r="I2" s="258"/>
-      <c r="J2" s="258"/>
-      <c r="K2" s="258"/>
-      <c r="L2" s="258"/>
+      <c r="I2" s="262"/>
+      <c r="J2" s="262"/>
+      <c r="K2" s="262"/>
+      <c r="L2" s="262"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="266" t="s">
+      <c r="C4" s="268" t="s">
         <v>198</v>
       </c>
-      <c r="D4" s="266"/>
-      <c r="E4" s="266"/>
-      <c r="F4" s="266"/>
-      <c r="G4" s="266"/>
-      <c r="H4" s="266"/>
-      <c r="I4" s="266"/>
-      <c r="J4" s="266"/>
-      <c r="K4" s="266"/>
-      <c r="L4" s="266"/>
+      <c r="D4" s="268"/>
+      <c r="E4" s="268"/>
+      <c r="F4" s="268"/>
+      <c r="G4" s="268"/>
+      <c r="H4" s="268"/>
+      <c r="I4" s="268"/>
+      <c r="J4" s="268"/>
+      <c r="K4" s="268"/>
+      <c r="L4" s="268"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -24374,18 +24575,18 @@
       <c r="N8" s="92"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C9" s="266" t="s">
+      <c r="C9" s="268" t="s">
         <v>122</v>
       </c>
-      <c r="D9" s="266"/>
-      <c r="E9" s="266"/>
-      <c r="F9" s="266"/>
-      <c r="G9" s="266"/>
-      <c r="H9" s="266"/>
-      <c r="I9" s="266"/>
-      <c r="J9" s="266"/>
-      <c r="K9" s="266"/>
-      <c r="L9" s="266"/>
+      <c r="D9" s="268"/>
+      <c r="E9" s="268"/>
+      <c r="F9" s="268"/>
+      <c r="G9" s="268"/>
+      <c r="H9" s="268"/>
+      <c r="I9" s="268"/>
+      <c r="J9" s="268"/>
+      <c r="K9" s="268"/>
+      <c r="L9" s="268"/>
       <c r="N9" s="92"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -24506,18 +24707,18 @@
       <c r="N13" s="92"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C14" s="266" t="s">
+      <c r="C14" s="268" t="s">
         <v>413</v>
       </c>
-      <c r="D14" s="266"/>
-      <c r="E14" s="266"/>
-      <c r="F14" s="266"/>
-      <c r="G14" s="266"/>
-      <c r="H14" s="266"/>
-      <c r="I14" s="266"/>
-      <c r="J14" s="266"/>
-      <c r="K14" s="266"/>
-      <c r="L14" s="266"/>
+      <c r="D14" s="268"/>
+      <c r="E14" s="268"/>
+      <c r="F14" s="268"/>
+      <c r="G14" s="268"/>
+      <c r="H14" s="268"/>
+      <c r="I14" s="268"/>
+      <c r="J14" s="268"/>
+      <c r="K14" s="268"/>
+      <c r="L14" s="268"/>
       <c r="N14" s="92"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
@@ -24607,10 +24808,10 @@
       <c r="N19" s="92"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B20" s="258" t="s">
+      <c r="B20" s="262" t="s">
         <v>415</v>
       </c>
-      <c r="C20" s="258"/>
+      <c r="C20" s="262"/>
       <c r="N20" s="92"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
@@ -24712,60 +24913,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="258" t="s">
+      <c r="C3" s="262" t="s">
         <v>113</v>
       </c>
-      <c r="D3" s="258"/>
-      <c r="E3" s="258"/>
-      <c r="F3" s="258"/>
-      <c r="G3" s="264"/>
-      <c r="H3" s="265" t="s">
+      <c r="D3" s="262"/>
+      <c r="E3" s="262"/>
+      <c r="F3" s="262"/>
+      <c r="G3" s="271"/>
+      <c r="H3" s="272" t="s">
         <v>114</v>
       </c>
-      <c r="I3" s="258"/>
-      <c r="J3" s="258"/>
-      <c r="K3" s="258"/>
-      <c r="L3" s="258"/>
-      <c r="P3" s="269"/>
-      <c r="Q3" s="269"/>
-      <c r="R3" s="269"/>
-      <c r="S3" s="269"/>
-      <c r="T3" s="269"/>
-      <c r="U3" s="269"/>
-      <c r="V3" s="269"/>
-      <c r="W3" s="269"/>
-      <c r="X3" s="269"/>
-      <c r="Y3" s="269"/>
-      <c r="Z3" s="269"/>
+      <c r="I3" s="262"/>
+      <c r="J3" s="262"/>
+      <c r="K3" s="262"/>
+      <c r="L3" s="262"/>
+      <c r="P3" s="273"/>
+      <c r="Q3" s="273"/>
+      <c r="R3" s="273"/>
+      <c r="S3" s="273"/>
+      <c r="T3" s="273"/>
+      <c r="U3" s="273"/>
+      <c r="V3" s="273"/>
+      <c r="W3" s="273"/>
+      <c r="X3" s="273"/>
+      <c r="Y3" s="273"/>
+      <c r="Z3" s="273"/>
       <c r="AB3" s="111"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="87"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="266" t="s">
+      <c r="C5" s="268" t="s">
         <v>184</v>
       </c>
-      <c r="D5" s="266"/>
-      <c r="E5" s="266"/>
-      <c r="F5" s="266"/>
-      <c r="G5" s="266"/>
-      <c r="H5" s="266"/>
-      <c r="I5" s="266"/>
-      <c r="J5" s="266"/>
-      <c r="K5" s="266"/>
-      <c r="L5" s="266"/>
-      <c r="P5" s="269"/>
-      <c r="Q5" s="269"/>
-      <c r="R5" s="269"/>
-      <c r="S5" s="269"/>
-      <c r="T5" s="269"/>
-      <c r="U5" s="269"/>
-      <c r="V5" s="269"/>
-      <c r="W5" s="269"/>
-      <c r="X5" s="269"/>
-      <c r="Y5" s="269"/>
-      <c r="Z5" s="269"/>
+      <c r="D5" s="268"/>
+      <c r="E5" s="268"/>
+      <c r="F5" s="268"/>
+      <c r="G5" s="268"/>
+      <c r="H5" s="268"/>
+      <c r="I5" s="268"/>
+      <c r="J5" s="268"/>
+      <c r="K5" s="268"/>
+      <c r="L5" s="268"/>
+      <c r="P5" s="273"/>
+      <c r="Q5" s="273"/>
+      <c r="R5" s="273"/>
+      <c r="S5" s="273"/>
+      <c r="T5" s="273"/>
+      <c r="U5" s="273"/>
+      <c r="V5" s="273"/>
+      <c r="W5" s="273"/>
+      <c r="X5" s="273"/>
+      <c r="Y5" s="273"/>
+      <c r="Z5" s="273"/>
       <c r="AB5" s="112"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -24994,10 +25195,10 @@
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="271" t="s">
+      <c r="B14" s="274" t="s">
         <v>226</v>
       </c>
-      <c r="C14" s="272"/>
+      <c r="C14" s="275"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="155" t="s">
@@ -25005,7 +25206,7 @@
       </c>
       <c r="C15" s="156">
         <f ca="1">Overview!C5</f>
-        <v>149.91999999999999</v>
+        <v>147.74</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -25024,20 +25225,20 @@
       <c r="C17" s="158">
         <v>0.28999999999999998</v>
       </c>
-      <c r="E17" s="270" t="s">
+      <c r="E17" s="276" t="s">
         <v>229</v>
       </c>
-      <c r="F17" s="270"/>
-      <c r="G17" s="270"/>
-      <c r="H17" s="270"/>
-      <c r="I17" s="270"/>
+      <c r="F17" s="276"/>
+      <c r="G17" s="276"/>
+      <c r="H17" s="276"/>
+      <c r="I17" s="276"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="271" t="s">
+      <c r="B19" s="274" t="s">
         <v>188</v>
       </c>
-      <c r="C19" s="272"/>
+      <c r="C19" s="275"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="159" t="s">
@@ -25071,7 +25272,7 @@
       </c>
       <c r="C23" s="161">
         <f ca="1">C15*C22</f>
-        <v>7014157.1199999992</v>
+        <v>6912163.6400000006</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -25098,15 +25299,15 @@
       </c>
       <c r="C26" s="162">
         <f ca="1">C23+C25-C24</f>
-        <v>5597598.1199999992</v>
+        <v>5495604.6400000006</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="271" t="s">
+      <c r="B28" s="274" t="s">
         <v>190</v>
       </c>
-      <c r="C28" s="272"/>
+      <c r="C28" s="275"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="159" t="s">
@@ -25182,16 +25383,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
     <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -31883,7 +32084,7 @@
       </c>
       <c r="AC116" s="63">
         <f ca="1">Overview!C5</f>
-        <v>149.91999999999999</v>
+        <v>147.74</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -31954,7 +32155,7 @@
       </c>
       <c r="AC117" s="65">
         <f ca="1">AC116/AC85</f>
-        <v>149.91999999999999</v>
+        <v>147.74</v>
       </c>
     </row>
     <row r="119" spans="1:31" x14ac:dyDescent="0.2">
@@ -33064,7 +33265,7 @@
       <c r="AA146" s="49"/>
       <c r="AC146" s="72">
         <f ca="1">AC117/Statement!AC26</f>
-        <v>47.736148269373601</v>
+        <v>47.042012708893125</v>
       </c>
     </row>
     <row r="147" spans="2:29" x14ac:dyDescent="0.2">
@@ -33101,7 +33302,7 @@
       <c r="AA147" s="49"/>
       <c r="AC147" s="72">
         <f ca="1">AC117/(Statement!AC5/Statement!AC22)</f>
-        <v>6.4382353916013413</v>
+        <v>6.3446164404694656</v>
       </c>
     </row>
     <row r="148" spans="2:29" x14ac:dyDescent="0.2">
@@ -33162,7 +33363,7 @@
       </c>
       <c r="AC148" s="72">
         <f ca="1">AC117/(Statement!AC49/Statement!AC75)</f>
-        <v>4.9754899265255625</v>
+        <v>4.9031408867721904</v>
       </c>
     </row>
     <row r="149" spans="2:29" x14ac:dyDescent="0.2">
@@ -33223,7 +33424,7 @@
       </c>
       <c r="AC149" s="143">
         <f ca="1">Statement!AC117*Statement!AC78</f>
-        <v>7514290.2399999993</v>
+        <v>7405024.2800000003</v>
       </c>
     </row>
     <row r="150" spans="2:29" x14ac:dyDescent="0.2">
@@ -33284,7 +33485,7 @@
       </c>
       <c r="AC150" s="143">
         <f ca="1">AC149+AC108-AC107+AC48+AC45</f>
-        <v>6097731.2399999993</v>
+        <v>5988465.2800000003</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -33321,7 +33522,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="182">
         <f ca="1">AC150/AC5</f>
-        <v>5.3255201650302784</v>
+        <v>5.2300915456916233</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -33358,7 +33559,7 @@
       <c r="AA152" s="49"/>
       <c r="AC152" s="182">
         <f ca="1">AC150/AC12</f>
-        <v>38.818036349746947</v>
+        <v>38.122451411656108</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -33493,7 +33694,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="72">
         <f t="shared" ref="AC155:AC156" ca="1" si="151">AC149/AC153</f>
-        <v>29.721897951111458</v>
+        <v>29.289709200221502</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -33530,7 +33731,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="72">
         <f t="shared" ca="1" si="151"/>
-        <v>36.572201098267229</v>
+        <v>35.916859544985655</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -33567,7 +33768,7 @@
       <c r="AA157" s="49"/>
       <c r="AC157" s="74">
         <f t="shared" ref="AC157" ca="1" si="154">AC153/AC149</f>
-        <v>3.3645226884395675E-2</v>
+        <v>3.4141684137732498E-2</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
@@ -33604,7 +33805,7 @@
       <c r="AA158" s="49"/>
       <c r="AC158" s="74">
         <f ca="1">AC26/AC117</f>
-        <v>2.0948485293723975E-2</v>
+        <v>2.1257593848890602E-2</v>
       </c>
     </row>
     <row r="159" spans="2:29" x14ac:dyDescent="0.2">
@@ -33678,7 +33879,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="154">
         <f ca="1">-AC63/AC149</f>
-        <v>9.2627510752099993E-3</v>
+        <v>9.3994290049782252E-3</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -33715,7 +33916,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="154">
         <f ca="1">-(AC63+AC64)/AC149</f>
-        <v>9.2627510752099993E-3</v>
+        <v>9.3994290049782252E-3</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -34218,7 +34419,7 @@
       <c r="AA172" s="49"/>
       <c r="AC172" s="154">
         <f ca="1">(AC107-AC108)/AC149</f>
-        <v>0.18851534273448561</v>
+        <v>0.19129700949474807</v>
       </c>
     </row>
     <row r="173" spans="2:29" x14ac:dyDescent="0.2">
@@ -36105,18 +36306,57 @@
   <sheetPr>
     <tabColor theme="6" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="B13"/>
+  <dimension ref="B5:H13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="10.83203125" style="1"/>
+    <col min="1" max="7" width="10.83203125" style="1"/>
+    <col min="8" max="8" width="17.83203125" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="13" spans="2:2" s="4" customFormat="1" ht="49" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H5" s="134" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H6" s="257" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H7" s="257" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H8" s="257" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H9" s="257" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H10" s="258" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" s="4" customFormat="1" ht="49" x14ac:dyDescent="0.2">
       <c r="B13" s="3" t="s">
         <v>236</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="H6" location="Overview!B3" display="Overview'!B3" xr:uid="{49108935-869E-9741-8C9B-DC045F5EF96E}"/>
+    <hyperlink ref="H8" location="'Analysis -&gt;'!B13" display="'Analysis -&gt;'!B13" xr:uid="{3A5D5632-C1EB-BF40-A3F8-475D826AEA93}"/>
+    <hyperlink ref="H9" location="'Forecast -&gt;'!B13" display="'Forecast -&gt;'!B13" xr:uid="{9EECD199-A3EA-4C47-AC14-DC5149ED784C}"/>
+    <hyperlink ref="H10" location="'Valuation -&gt;'!B13" display="'Valuation -&gt;'!B13" xr:uid="{F0189B84-9339-1F46-92C6-E9D205DC39D7}"/>
+    <hyperlink ref="H7" location="'Financials -&gt;'!B13" display="'Financials -&gt;'!B13" xr:uid="{420C8526-7E34-634E-9935-64B927AAC9AA}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -36140,15 +36380,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="258" t="s">
+      <c r="B4" s="262" t="s">
         <v>237</v>
       </c>
-      <c r="C4" s="258"/>
-      <c r="E4" s="258" t="s">
+      <c r="C4" s="262"/>
+      <c r="E4" s="262" t="s">
         <v>244</v>
       </c>
-      <c r="F4" s="258"/>
-      <c r="G4" s="258"/>
+      <c r="F4" s="262"/>
+      <c r="G4" s="262"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -36156,7 +36396,7 @@
       </c>
       <c r="C5" s="171">
         <f ca="1">Overview!C5</f>
-        <v>149.91999999999999</v>
+        <v>147.74</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="134" t="s">
@@ -36172,7 +36412,7 @@
       </c>
       <c r="C6" s="172">
         <f ca="1">Statement!AC149</f>
-        <v>7514290.2399999993</v>
+        <v>7405024.2800000003</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>20</v>
@@ -36192,7 +36432,7 @@
       </c>
       <c r="C7" s="172">
         <f ca="1">Statement!AC150</f>
-        <v>6097731.2399999993</v>
+        <v>5988465.2800000003</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>32</v>
@@ -36212,7 +36452,7 @@
       </c>
       <c r="C8" s="173">
         <f ca="1">Statement!AC146</f>
-        <v>47.736148269373601</v>
+        <v>47.042012708893125</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>247</v>
@@ -36232,7 +36472,7 @@
       </c>
       <c r="C9" s="173">
         <f ca="1">Statement!AC147</f>
-        <v>6.4382353916013413</v>
+        <v>6.3446164404694656</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>248</v>
@@ -36252,7 +36492,7 @@
       </c>
       <c r="C10" s="173">
         <f ca="1">Statement!AC148</f>
-        <v>4.9754899265255625</v>
+        <v>4.9031408867721904</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -36272,7 +36512,7 @@
       </c>
       <c r="C11" s="173">
         <f ca="1">Statement!AC151</f>
-        <v>5.3255201650302784</v>
+        <v>5.2300915456916233</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -36281,18 +36521,18 @@
       </c>
       <c r="C12" s="173">
         <f ca="1">Statement!AC152</f>
-        <v>38.818036349746947</v>
+        <v>38.122451411656108</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="258" t="s">
+      <c r="B15" s="262" t="s">
         <v>78</v>
       </c>
-      <c r="C15" s="258"/>
-      <c r="E15" s="258" t="s">
+      <c r="C15" s="262"/>
+      <c r="E15" s="262" t="s">
         <v>250</v>
       </c>
-      <c r="F15" s="258"/>
+      <c r="F15" s="262"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -36343,14 +36583,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="258" t="s">
+      <c r="B21" s="262" t="s">
         <v>249</v>
       </c>
-      <c r="C21" s="258"/>
-      <c r="E21" s="258" t="s">
+      <c r="C21" s="262"/>
+      <c r="E21" s="262" t="s">
         <v>253</v>
       </c>
-      <c r="F21" s="258"/>
+      <c r="F21" s="262"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -36419,14 +36659,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="258" t="s">
+      <c r="B29" s="262" t="s">
         <v>254</v>
       </c>
-      <c r="C29" s="258"/>
-      <c r="E29" s="258" t="s">
+      <c r="C29" s="262"/>
+      <c r="E29" s="262" t="s">
         <v>260</v>
       </c>
-      <c r="F29" s="258"/>
+      <c r="F29" s="262"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -36502,14 +36742,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="258" t="s">
+      <c r="B37" s="262" t="s">
         <v>272</v>
       </c>
-      <c r="C37" s="258"/>
-      <c r="E37" s="258" t="s">
+      <c r="C37" s="262"/>
+      <c r="E37" s="262" t="s">
         <v>275</v>
       </c>
-      <c r="F37" s="258"/>
+      <c r="F37" s="262"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -36517,7 +36757,7 @@
       </c>
       <c r="C38" s="174">
         <f ca="1">Statement!AC158</f>
-        <v>2.0948485293723975E-2</v>
+        <v>2.1257593848890602E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>274</v>
@@ -36533,7 +36773,7 @@
       </c>
       <c r="C39" s="214">
         <f ca="1">Statement!AC157</f>
-        <v>3.3645226884395675E-2</v>
+        <v>3.4141684137732498E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>276</v>
@@ -36565,7 +36805,7 @@
       </c>
       <c r="C41" s="174">
         <f ca="1">Statement!AC160</f>
-        <v>9.2627510752099993E-3</v>
+        <v>9.3994290049782252E-3</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -36574,18 +36814,18 @@
       </c>
       <c r="C42" s="174">
         <f ca="1">Statement!AC161</f>
-        <v>9.2627510752099993E-3</v>
+        <v>9.3994290049782252E-3</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="258" t="s">
+      <c r="B45" s="262" t="s">
         <v>283</v>
       </c>
-      <c r="C45" s="258"/>
-      <c r="E45" s="258" t="s">
+      <c r="C45" s="262"/>
+      <c r="E45" s="262" t="s">
         <v>289</v>
       </c>
-      <c r="F45" s="258"/>
+      <c r="F45" s="262"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -36618,18 +36858,18 @@
       </c>
       <c r="F48" s="174">
         <f ca="1">Statement!AC172</f>
-        <v>0.18851534273448561</v>
+        <v>0.19129700949474807</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="258" t="s">
+      <c r="B51" s="262" t="s">
         <v>286</v>
       </c>
-      <c r="C51" s="258"/>
-      <c r="E51" s="258" t="s">
+      <c r="C51" s="262"/>
+      <c r="E51" s="262" t="s">
         <v>307</v>
       </c>
-      <c r="F51" s="258"/>
+      <c r="F51" s="262"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -36797,7 +37037,7 @@
       </c>
       <c r="I6" s="171">
         <f ca="1">Statement!AC116</f>
-        <v>149.91999999999999</v>
+        <v>147.74</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -36826,7 +37066,7 @@
       </c>
       <c r="I7" s="172">
         <f ca="1">Statement!AC149</f>
-        <v>7514290.2399999993</v>
+        <v>7405024.2800000003</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -36855,7 +37095,7 @@
       </c>
       <c r="I8" s="172">
         <f ca="1">Statement!AC150</f>
-        <v>6097731.2399999993</v>
+        <v>5988465.2800000003</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -36884,7 +37124,7 @@
       </c>
       <c r="I9" s="173">
         <f ca="1">Statement!AC146</f>
-        <v>47.736148269373601</v>
+        <v>47.042012708893125</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -36913,7 +37153,7 @@
       </c>
       <c r="I10" s="173">
         <f ca="1">Statement!AC147</f>
-        <v>6.4382353916013413</v>
+        <v>6.3446164404694656</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -36942,7 +37182,7 @@
       </c>
       <c r="I11" s="173">
         <f ca="1">Statement!AC148</f>
-        <v>4.9754899265255625</v>
+        <v>4.9031408867721904</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -36971,7 +37211,7 @@
       </c>
       <c r="I12" s="173">
         <f ca="1">Statement!AC151</f>
-        <v>5.3255201650302784</v>
+        <v>5.2300915456916233</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -37000,7 +37240,7 @@
       </c>
       <c r="I13" s="173">
         <f ca="1">Statement!AC152</f>
-        <v>38.818036349746947</v>
+        <v>38.122451411656108</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -37773,7 +38013,7 @@
       </c>
       <c r="I51" s="174">
         <f ca="1">Statement!AC158</f>
-        <v>2.0948485293723975E-2</v>
+        <v>2.1257593848890602E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -37802,7 +38042,7 @@
       </c>
       <c r="I52" s="174">
         <f ca="1">Statement!AC157</f>
-        <v>3.3645226884395675E-2</v>
+        <v>3.4141684137732498E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -37860,7 +38100,7 @@
       </c>
       <c r="I54" s="174">
         <f ca="1">Statement!AC160</f>
-        <v>9.2627510752099993E-3</v>
+        <v>9.3994290049782252E-3</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -37889,7 +38129,7 @@
       </c>
       <c r="I55" s="174">
         <f ca="1">Statement!AC161</f>
-        <v>9.2627510752099993E-3</v>
+        <v>9.3994290049782252E-3</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -38125,7 +38365,7 @@
       </c>
       <c r="I68" s="195">
         <f ca="1">Statement!AC172</f>
-        <v>0.18851534273448561</v>
+        <v>0.19129700949474807</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -38668,14 +38908,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="261" t="s">
+      <c r="C3" s="263" t="s">
         <v>317</v>
       </c>
-      <c r="D3" s="262"/>
-      <c r="F3" s="263" t="s">
+      <c r="D3" s="264"/>
+      <c r="F3" s="265" t="s">
         <v>318</v>
       </c>
-      <c r="G3" s="262"/>
+      <c r="G3" s="264"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -38742,19 +38982,19 @@
       <c r="B7" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C7" s="259">
+      <c r="C7" s="266">
         <f>Statement!AA89</f>
         <v>2.2218264392893719E-2</v>
       </c>
-      <c r="D7" s="260"/>
-      <c r="F7" s="259">
+      <c r="D7" s="267"/>
+      <c r="F7" s="266">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.18309713991239371</v>
       </c>
-      <c r="G7" s="260"/>
+      <c r="G7" s="267"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="206" t="s">
@@ -38781,19 +39021,19 @@
       <c r="B9" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C9" s="259">
+      <c r="C9" s="266">
         <f>Statement!AA90</f>
         <v>3.6046202026093238E-2</v>
       </c>
-      <c r="D9" s="260"/>
-      <c r="F9" s="259">
+      <c r="D9" s="267"/>
+      <c r="F9" s="266">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.17263647322197348</v>
       </c>
-      <c r="G9" s="260"/>
+      <c r="G9" s="267"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="206" t="s">
@@ -38820,19 +39060,19 @@
       <c r="B11" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C11" s="259">
+      <c r="C11" s="266">
         <f>Statement!AA91</f>
         <v>1.710027405488606E-2</v>
       </c>
-      <c r="D11" s="260"/>
-      <c r="F11" s="259">
+      <c r="D11" s="267"/>
+      <c r="F11" s="266">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>0.1870895657269924</v>
       </c>
-      <c r="G11" s="260"/>
+      <c r="G11" s="267"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="206" t="s">
@@ -38859,19 +39099,19 @@
       <c r="B13" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C13" s="259">
+      <c r="C13" s="266">
         <f>Statement!AA95</f>
         <v>8.4392741251357012E-2</v>
       </c>
-      <c r="D13" s="260"/>
-      <c r="F13" s="259">
+      <c r="D13" s="267"/>
+      <c r="F13" s="266">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.22501976973287405</v>
       </c>
-      <c r="G13" s="260"/>
+      <c r="G13" s="267"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="206" t="s">
@@ -38898,19 +39138,19 @@
       <c r="B15" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C15" s="259">
+      <c r="C15" s="266">
         <f>Statement!AA96</f>
         <v>-0.23765355851505829</v>
       </c>
-      <c r="D15" s="260"/>
-      <c r="F15" s="259">
+      <c r="D15" s="267"/>
+      <c r="F15" s="266">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>1.7444474417768186E-2</v>
       </c>
-      <c r="G15" s="260"/>
+      <c r="G15" s="267"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="206" t="s">
@@ -38937,19 +39177,19 @@
       <c r="B17" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C17" s="259">
+      <c r="C17" s="266">
         <f>Statement!AA98</f>
         <v>-0.23704555913483663</v>
       </c>
-      <c r="D17" s="260"/>
-      <c r="F17" s="259">
+      <c r="D17" s="267"/>
+      <c r="F17" s="266">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>-0.25955204216073779</v>
       </c>
-      <c r="G17" s="260"/>
+      <c r="G17" s="267"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="206" t="s">
@@ -38976,22 +39216,22 @@
       <c r="B19" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C19" s="259">
+      <c r="C19" s="266">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>2.5565842762241744E-2</v>
       </c>
-      <c r="D19" s="260"/>
-      <c r="F19" s="259">
+      <c r="D19" s="267"/>
+      <c r="F19" s="266">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>2.5293753865182372E-2</v>
       </c>
-      <c r="G19" s="260"/>
+      <c r="G19" s="267"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="206" t="s">
@@ -39018,22 +39258,22 @@
       <c r="B21" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C21" s="259">
+      <c r="C21" s="266">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>-0.2584269662921348</v>
       </c>
-      <c r="D21" s="260"/>
-      <c r="F21" s="259">
+      <c r="D21" s="267"/>
+      <c r="F21" s="266">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>-0.27472527472527469</v>
       </c>
-      <c r="G21" s="260"/>
+      <c r="G21" s="267"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -39082,22 +39322,22 @@
       <c r="B25" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C25" s="259">
+      <c r="C25" s="266">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>2.840483364420425E-2</v>
       </c>
-      <c r="D25" s="260"/>
-      <c r="F25" s="259">
+      <c r="D25" s="267"/>
+      <c r="F25" s="266">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>0.22478379327694395</v>
       </c>
-      <c r="G25" s="260"/>
+      <c r="G25" s="267"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="str">
@@ -39125,22 +39365,22 @@
       <c r="B27" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C27" s="259">
+      <c r="C27" s="266">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>2.1247695740758708E-2</v>
       </c>
-      <c r="D27" s="260"/>
-      <c r="F27" s="259">
+      <c r="D27" s="267"/>
+      <c r="F27" s="266">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>2.1792942775323981E-2</v>
       </c>
-      <c r="G27" s="260"/>
+      <c r="G27" s="267"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="str">
@@ -39168,22 +39408,22 @@
       <c r="B29" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C29" s="259">
+      <c r="C29" s="266">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>-0.10674206945303526</v>
       </c>
-      <c r="D29" s="260"/>
-      <c r="F29" s="259">
+      <c r="D29" s="267"/>
+      <c r="F29" s="266">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>2.0816812053925456E-3</v>
       </c>
-      <c r="G29" s="260"/>
+      <c r="G29" s="267"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="str">
@@ -39211,22 +39451,22 @@
       <c r="B31" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C31" s="259">
+      <c r="C31" s="266">
         <f>IF(C30=0,
 IF(D30=0,0,IF(D30&gt;0,1,-1)),
 (D30-C30)/ABS(C30)
 )</f>
         <v>-5.2569263556713236E-2</v>
       </c>
-      <c r="D31" s="260"/>
-      <c r="F31" s="259">
+      <c r="D31" s="267"/>
+      <c r="F31" s="266">
         <f>IF(F30=0,
 IF(G30=0,0,IF(G30&gt;0,1,-1)),
 (G30-F30)/ABS(F30)
 )</f>
         <v>-0.22983638113570742</v>
       </c>
-      <c r="G31" s="260"/>
+      <c r="G31" s="267"/>
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B32" s="20" t="str">
@@ -39254,22 +39494,22 @@
       <c r="B33" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C33" s="259">
+      <c r="C33" s="266">
         <f>IF(C32=0,
 IF(D32=0,0,IF(D32&gt;0,1,-1)),
 (D32-C32)/ABS(C32)
 )</f>
         <v>0.84164222873900296</v>
       </c>
-      <c r="D33" s="260"/>
-      <c r="F33" s="259">
+      <c r="D33" s="267"/>
+      <c r="F33" s="266">
         <f>IF(F32=0,
 IF(G32=0,0,IF(G32&gt;0,1,-1)),
 (G32-F32)/ABS(F32)
 )</f>
         <v>1.482213438735178</v>
       </c>
-      <c r="G33" s="260"/>
+      <c r="G33" s="267"/>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B35" s="8" t="s">
@@ -39318,22 +39558,22 @@
       <c r="B37" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C37" s="259">
+      <c r="C37" s="266">
         <f>IF(C36=0,
 IF(D36=0,0,IF(D36&gt;0,1,-1)),
 (D36-C36)/ABS(C36)
 )</f>
         <v>3.8938053097345132E-2</v>
       </c>
-      <c r="D37" s="260"/>
-      <c r="F37" s="259">
+      <c r="D37" s="267"/>
+      <c r="F37" s="266">
         <f>IF(F36=0,
 IF(G36=0,0,IF(G36&gt;0,1,-1)),
 (G36-F36)/ABS(F36)
 )</f>
         <v>0.23060796645702306</v>
       </c>
-      <c r="G37" s="260"/>
+      <c r="G37" s="267"/>
     </row>
     <row r="38" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="str">
@@ -39361,22 +39601,22 @@
       <c r="B39" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C39" s="259">
+      <c r="C39" s="266">
         <f>IF(C38=0,
 IF(D38=0,0,IF(D38&gt;0,1,-1)),
 (D38-C38)/ABS(C38)
 )</f>
         <v>2.0319303338171262E-2</v>
       </c>
-      <c r="D39" s="260"/>
-      <c r="F39" s="259">
+      <c r="D39" s="267"/>
+      <c r="F39" s="266">
         <f>IF(F38=0,
 IF(G38=0,0,IF(G38&gt;0,1,-1)),
 (G38-F38)/ABS(F38)
 )</f>
         <v>9.5869056897895558E-2</v>
       </c>
-      <c r="G39" s="260"/>
+      <c r="G39" s="267"/>
     </row>
     <row r="40" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B40" s="20" t="str">
@@ -39404,22 +39644,22 @@
       <c r="B41" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C41" s="259">
+      <c r="C41" s="266">
         <f>IF(C40=0,
 IF(D40=0,0,IF(D40&gt;0,1,-1)),
 (D40-C40)/ABS(C40)
 )</f>
         <v>1.6E-2</v>
       </c>
-      <c r="D41" s="260"/>
-      <c r="F41" s="259">
+      <c r="D41" s="267"/>
+      <c r="F41" s="266">
         <f>IF(F40=0,
 IF(G40=0,0,IF(G40&gt;0,1,-1)),
 (G40-F40)/ABS(F40)
 )</f>
         <v>0.16513761467889909</v>
       </c>
-      <c r="G41" s="260"/>
+      <c r="G41" s="267"/>
     </row>
     <row r="42" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B42" s="20" t="str">
@@ -39447,22 +39687,22 @@
       <c r="B43" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C43" s="259">
+      <c r="C43" s="266">
         <f>IF(C42=0,
 IF(D42=0,0,IF(D42&gt;0,1,-1)),
 (D42-C42)/ABS(C42)
 )</f>
         <v>2.0750199521149242E-2</v>
       </c>
-      <c r="D43" s="260"/>
-      <c r="F43" s="259">
+      <c r="D43" s="267"/>
+      <c r="F43" s="266">
         <f>IF(F42=0,
 IF(G42=0,0,IF(G42&gt;0,1,-1)),
 (G42-F42)/ABS(F42)
 )</f>
         <v>8.9437819420783646E-2</v>
       </c>
-      <c r="G43" s="260"/>
+      <c r="G43" s="267"/>
     </row>
     <row r="44" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B44" s="20" t="str">
@@ -39490,22 +39730,22 @@
       <c r="B45" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C45" s="259">
+      <c r="C45" s="266">
         <f>IF(C44=0,
 IF(D44=0,0,IF(D44&gt;0,1,-1)),
 (D44-C44)/ABS(C44)
 )</f>
         <v>1.2209481933271921E-2</v>
       </c>
-      <c r="D45" s="260"/>
-      <c r="F45" s="259">
+      <c r="D45" s="267"/>
+      <c r="F45" s="266">
         <f>IF(F44=0,
 IF(G44=0,0,IF(G44&gt;0,1,-1)),
 (G44-F44)/ABS(F44)
 )</f>
         <v>5.119238950540856E-2</v>
       </c>
-      <c r="G45" s="260"/>
+      <c r="G45" s="267"/>
     </row>
     <row r="46" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="str">
@@ -39533,22 +39773,22 @@
       <c r="B47" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C47" s="259">
+      <c r="C47" s="266">
         <f>IF(C46=0,
 IF(D46=0,0,IF(D46&gt;0,1,-1)),
 (D46-C46)/ABS(C46)
 )</f>
         <v>1.8247963846473435E-2</v>
       </c>
-      <c r="D47" s="260"/>
-      <c r="F47" s="259">
+      <c r="D47" s="267"/>
+      <c r="F47" s="266">
         <f>IF(F46=0,
 IF(G46=0,0,IF(G46&gt;0,1,-1)),
 (G46-F46)/ABS(F46)
 )</f>
         <v>0.1229516507570132</v>
       </c>
-      <c r="G47" s="260"/>
+      <c r="G47" s="267"/>
     </row>
     <row r="48" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B48" s="20" t="str">
@@ -39576,22 +39816,22 @@
       <c r="B49" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C49" s="259">
+      <c r="C49" s="266">
         <f>IF(C48=0,
 IF(D48=0,0,IF(D48&gt;0,1,-1)),
 (D48-C48)/ABS(C48)
 )</f>
         <v>-4.2332859174963834E-3</v>
       </c>
-      <c r="D49" s="260"/>
-      <c r="F49" s="259">
+      <c r="D49" s="267"/>
+      <c r="F49" s="266">
         <f>IF(F48=0,
 IF(G48=0,0,IF(G48&gt;0,1,-1)),
 (G48-F48)/ABS(F48)
 )</f>
         <v>6.3208790635154666E-2</v>
       </c>
-      <c r="G49" s="260"/>
+      <c r="G49" s="267"/>
     </row>
     <row r="50" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B50" s="20" t="str">
@@ -39619,22 +39859,22 @@
       <c r="B51" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C51" s="259">
+      <c r="C51" s="266">
         <f>IF(C50=0,
 IF(D50=0,0,IF(D50&gt;0,1,-1)),
 (D50-C50)/ABS(C50)
 )</f>
         <v>4.8738292663854846E-4</v>
       </c>
-      <c r="D51" s="260"/>
-      <c r="F51" s="259">
+      <c r="D51" s="267"/>
+      <c r="F51" s="266">
         <f>IF(F50=0,
 IF(G50=0,0,IF(G50&gt;0,1,-1)),
 (G50-F50)/ABS(F50)
 )</f>
         <v>-6.2091544317255373E-2</v>
       </c>
-      <c r="G51" s="260"/>
+      <c r="G51" s="267"/>
     </row>
     <row r="52" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="str">
@@ -39662,43 +39902,39 @@
       <c r="B53" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C53" s="259">
+      <c r="C53" s="266">
         <f>IF(C52=0,
 IF(D52=0,0,IF(D52&gt;0,1,-1)),
 (D52-C52)/ABS(C52)
 )</f>
         <v>-8.8077740902117604E-2</v>
       </c>
-      <c r="D53" s="260"/>
-      <c r="F53" s="259">
+      <c r="D53" s="267"/>
+      <c r="F53" s="266">
         <f>IF(F52=0,
 IF(G52=0,0,IF(G52&gt;0,1,-1)),
 (G52-F52)/ABS(F52)
 )</f>
         <v>-0.37416005758387127</v>
       </c>
-      <c r="G53" s="260"/>
+      <c r="G53" s="267"/>
     </row>
   </sheetData>
   <mergeCells count="46">
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C53:D53"/>
+    <mergeCell ref="F53:G53"/>
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="F47:G47"/>
+    <mergeCell ref="C49:D49"/>
+    <mergeCell ref="F49:G49"/>
+    <mergeCell ref="C51:D51"/>
+    <mergeCell ref="F51:G51"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="F41:G41"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="F43:G43"/>
+    <mergeCell ref="C45:D45"/>
+    <mergeCell ref="F45:G45"/>
     <mergeCell ref="C37:D37"/>
     <mergeCell ref="F37:G37"/>
     <mergeCell ref="C39:D39"/>
@@ -39713,20 +39949,24 @@
     <mergeCell ref="F31:G31"/>
     <mergeCell ref="C33:D33"/>
     <mergeCell ref="F33:G33"/>
-    <mergeCell ref="C41:D41"/>
-    <mergeCell ref="F41:G41"/>
-    <mergeCell ref="C43:D43"/>
-    <mergeCell ref="F43:G43"/>
-    <mergeCell ref="C45:D45"/>
-    <mergeCell ref="F45:G45"/>
-    <mergeCell ref="C53:D53"/>
-    <mergeCell ref="F53:G53"/>
-    <mergeCell ref="C47:D47"/>
-    <mergeCell ref="F47:G47"/>
-    <mergeCell ref="C49:D49"/>
-    <mergeCell ref="F49:G49"/>
-    <mergeCell ref="C51:D51"/>
-    <mergeCell ref="F51:G51"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/DUOL.xlsx
+++ b/DUOL.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11004"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E78C6BE-9772-D545-836B-B0728589AB63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E8748A2-072B-024A-8C86-875BD281AC8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -13199,11 +13199,11 @@
     <v>Powered by Refinitiv</v>
     <v>343.99799999999999</v>
     <v>87.89</v>
-    <v>1.0680000000000001</v>
-    <v>-2.1800000000000002</v>
-    <v>-1.4541E-2</v>
-    <v>0.26</v>
-    <v>1.7599999999999998E-3</v>
+    <v>1.0654999999999999</v>
+    <v>9.1999999999999993</v>
+    <v>6.5840999999999997E-2</v>
+    <v>-0.16</v>
+    <v>-1.0739999999999999E-3</v>
     <v>USD</v>
     <v>Duolingo, Inc. is a technology company. The Company is engaged in offering a mobile learning platform, as well as a digital English language proficiency assessment exam. It operates a freemium business model, namely, the app and the Website are accessible free of charge, although Duolingo also offers premium services for a subscription fee. Its solutions consist of the Duolingo App, Super Duolingo, Duolingo Max, Duolingo English Test: AI-Driven Language Assessment, Duolingo for Schools, and Duolingo ABC. The Duolingo App offers courses in over 40 different languages, including Spanish, English, French, German, Italian, Portuguese, Japanese and Chinese. Duolingo can also be accessed on desktop computers via a Web browser. Its subscription offering, Super Duolingo, offers learners additional features to enhance their learning experience. The Duolingo English Test is an online, on-demand, high-stakes English proficiency assessment. It also operates an animation and motion design studio.</v>
     <v>900</v>
@@ -13211,25 +13211,25 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>5900 PENN AVE, SECOND FLOOR, PITTSBURGH, PA, 15206 US</v>
-    <v>150.495</v>
+    <v>150.22999999999999</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46307.853151226562</v>
+    <v>46310.901905740626</v>
     <v>0</v>
-    <v>147.5001</v>
-    <v>6912203529</v>
+    <v>138.2525</v>
+    <v>6967879191</v>
     <v>DUOLINGO, INC.</v>
     <v>DUOLINGO, INC.</v>
-    <v>149.85</v>
-    <v>17.610099999999999</v>
-    <v>149.91999999999999</v>
-    <v>147.74</v>
-    <v>148</v>
+    <v>138.85</v>
+    <v>17.751999999999999</v>
+    <v>139.72999999999999</v>
+    <v>148.93</v>
+    <v>148.77000000000001</v>
     <v>46786270</v>
     <v>DUOL</v>
     <v>DUOLINGO, INC. (XNAS:DUOL)</v>
-    <v>783499</v>
-    <v>1030227</v>
+    <v>1516461</v>
+    <v>987806</v>
     <v>2011</v>
   </rv>
   <rv s="2">
@@ -13253,17 +13253,17 @@
     <v>Powered by Refinitiv</v>
     <v>53.64</v>
     <v>39.47</v>
-    <v>0.13</v>
-    <v>2.4849999999999998E-3</v>
+    <v>-0.27</v>
+    <v>-5.1749999999999999E-3</v>
     <v>US</v>
-    <v>52.8</v>
+    <v>53.29</v>
     <v>Index</v>
     <v>3</v>
-    <v>52.34</v>
+    <v>51.77</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>52.36</v>
-    <v>52.31</v>
-    <v>52.44</v>
+    <v>51.96</v>
+    <v>52.17</v>
+    <v>51.9</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -14089,7 +14089,7 @@
       </c>
       <c r="F3" s="186">
         <f ca="1">Statement!AC149</f>
-        <v>7405024.2800000003</v>
+        <v>7464669.46</v>
       </c>
       <c r="H3" s="184" t="str">
         <f>'AVG target price'!B5</f>
@@ -14097,7 +14097,7 @@
       </c>
       <c r="I3" s="210">
         <f ca="1">'AVG target price'!C5</f>
-        <v>142.18891938665595</v>
+        <v>143.24075126818636</v>
       </c>
       <c r="K3" s="257" t="s">
         <v>441</v>
@@ -14116,7 +14116,7 @@
       </c>
       <c r="F4" s="187">
         <f ca="1">Statement!AC150</f>
-        <v>5988465.2800000003</v>
+        <v>6048110.46</v>
       </c>
       <c r="H4" s="184" t="str">
         <f>'AVG target price'!B6</f>
@@ -14124,7 +14124,7 @@
       </c>
       <c r="I4" s="210">
         <f ca="1">'AVG target price'!C6</f>
-        <v>195.82972873595637</v>
+        <v>196.3040755028031</v>
       </c>
       <c r="K4" s="257" t="s">
         <v>442</v>
@@ -14136,7 +14136,7 @@
       </c>
       <c r="C5" s="207" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>147.74</v>
+        <v>148.93</v>
       </c>
       <c r="E5" s="184" t="s">
         <v>247</v>
@@ -14151,7 +14151,7 @@
       </c>
       <c r="I5" s="210">
         <f ca="1">'AVG target price'!C7</f>
-        <v>157.58022062820396</v>
+        <v>158.04820899241003</v>
       </c>
       <c r="K5" s="257" t="s">
         <v>443</v>
@@ -14163,14 +14163,14 @@
       </c>
       <c r="C6" s="207" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>148</v>
+        <v>148.77000000000001</v>
       </c>
       <c r="E6" s="184" t="s">
         <v>241</v>
       </c>
       <c r="F6" s="189">
         <f ca="1">Statement!AC146</f>
-        <v>47.042012708893125</v>
+        <v>47.420921569889352</v>
       </c>
       <c r="H6" s="184" t="str">
         <f>'AVG target price'!B8</f>
@@ -14178,7 +14178,7 @@
       </c>
       <c r="I6" s="210">
         <f ca="1">'AVG target price'!C8</f>
-        <v>201.2818018360455</v>
+        <v>201.77234039880079</v>
       </c>
       <c r="K6" s="258" t="s">
         <v>444</v>
@@ -14190,14 +14190,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>-2.1800000000000002</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="E7" s="185" t="s">
         <v>205</v>
       </c>
       <c r="F7" s="190">
         <f ca="1">Statement!AC147</f>
-        <v>6.3446164404694656</v>
+        <v>6.3957203633350312</v>
       </c>
       <c r="H7" s="184" t="str">
         <f>'AVG target price'!B9</f>
@@ -14205,7 +14205,7 @@
       </c>
       <c r="I7" s="210">
         <f ca="1">'AVG target price'!C9</f>
-        <v>201.69845704324368</v>
+        <v>202.19023300615032</v>
       </c>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.2">
@@ -14214,14 +14214,14 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>0.26</v>
+        <v>-0.16</v>
       </c>
       <c r="E8" s="184" t="s">
         <v>269</v>
       </c>
       <c r="F8" s="191">
         <f ca="1">Statement!AC157</f>
-        <v>3.4141684137732498E-2</v>
+        <v>3.386888077961861E-2</v>
       </c>
       <c r="H8" s="183" t="str">
         <f>'AVG target price'!B10</f>
@@ -14229,7 +14229,7 @@
       </c>
       <c r="I8" s="211">
         <f ca="1">'AVG target price'!C10</f>
-        <v>179.71582552602109</v>
+        <v>180.31112183367014</v>
       </c>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.2">
@@ -14238,14 +14238,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>-1.4541E-2</v>
+        <v>6.5840999999999997E-2</v>
       </c>
       <c r="E9" s="184" t="s">
         <v>292</v>
       </c>
       <c r="F9" s="191">
         <f ca="1">Statement!AC158</f>
-        <v>2.1257593848890602E-2</v>
+        <v>2.1087738637179197E-2</v>
       </c>
       <c r="H9" s="183" t="str">
         <f>'AVG target price'!B12</f>
@@ -14253,7 +14253,7 @@
       </c>
       <c r="I9" s="212">
         <f ca="1">'AVG target price'!C12</f>
-        <v>0.21643309547868608</v>
+        <v>0.21071054746303722</v>
       </c>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.2">
@@ -14262,14 +14262,14 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>1.7599999999999998E-3</v>
+        <v>-1.0739999999999999E-3</v>
       </c>
       <c r="E10" s="184" t="s">
         <v>297</v>
       </c>
       <c r="F10" s="191">
         <f ca="1">Statement!AC160</f>
-        <v>9.3994290049782252E-3</v>
+        <v>9.3243244557542678E-3</v>
       </c>
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.2">
@@ -14317,7 +14317,7 @@
       </c>
       <c r="C13" s="208" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>1.0680000000000001</v>
+        <v>1.0654999999999999</v>
       </c>
       <c r="E13" s="184" t="s">
         <v>104</v>
@@ -14340,7 +14340,7 @@
       </c>
       <c r="C14" s="209" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>1030227</v>
+        <v>987806</v>
       </c>
       <c r="E14" s="185" t="s">
         <v>105</v>
@@ -14356,7 +14356,7 @@
       </c>
       <c r="F15" s="191">
         <f ca="1">Statement!AC172</f>
-        <v>0.19129700949474807</v>
+        <v>0.18976848306421862</v>
       </c>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.2">
@@ -14389,7 +14389,7 @@
       </c>
       <c r="I17" s="255">
         <f ca="1">DCF!C15</f>
-        <v>0.10050000000000001</v>
+        <v>9.9847499999999992E-2</v>
       </c>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.2">
@@ -14411,7 +14411,7 @@
       </c>
       <c r="I18" s="256">
         <f ca="1">Multiples!C54</f>
-        <v>0.10050000000000001</v>
+        <v>9.9847499999999992E-2</v>
       </c>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
@@ -14484,7 +14484,7 @@
       </c>
       <c r="F26" s="218" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>52.44</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -14499,7 +14499,7 @@
       </c>
       <c r="F27" s="219">
         <f ca="1">F26/1000</f>
-        <v>5.2440000000000001E-2</v>
+        <v>5.1900000000000002E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -22235,7 +22235,7 @@
       </c>
       <c r="C6" s="135">
         <f ca="1">Overview!C5</f>
-        <v>147.74</v>
+        <v>148.93</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22244,7 +22244,7 @@
       </c>
       <c r="C7" s="136">
         <f ca="1">C5*C6</f>
-        <v>7405024.2800000003</v>
+        <v>7464669.46</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22262,7 +22262,7 @@
       </c>
       <c r="C9" s="137">
         <f ca="1">Overview!F27</f>
-        <v>5.2440000000000001E-2</v>
+        <v>5.1900000000000002E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22271,7 +22271,7 @@
       </c>
       <c r="C10" s="135">
         <f ca="1">Overview!C13</f>
-        <v>1.0680000000000001</v>
+        <v>1.0654999999999999</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22341,7 +22341,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.10050000000000001</v>
+        <v>9.9847499999999992E-2</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22350,7 +22350,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.10050000000000001</v>
+        <v>9.9847499999999992E-2</v>
       </c>
     </row>
   </sheetData>
@@ -22601,7 +22601,7 @@
       </c>
       <c r="L8" s="128">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>7273026.8491768399</v>
+        <v>7332460.7703276332</v>
       </c>
       <c r="N8" s="92"/>
       <c r="O8" s="16"/>
@@ -22655,23 +22655,23 @@
       <c r="G10" s="140"/>
       <c r="H10" s="128">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>164264.58158222964</v>
+        <v>164362.03385582429</v>
       </c>
       <c r="I10" s="128">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>198597.84341738783</v>
+        <v>198833.55524456274</v>
       </c>
       <c r="J10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>226205.25139792333</v>
+        <v>226608.08863397525</v>
       </c>
       <c r="K10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>259839.38171460424</v>
+        <v>260456.54412615745</v>
       </c>
       <c r="L10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>355599.10970518761</v>
+        <v>356655.18289128062</v>
       </c>
       <c r="N10" s="92"/>
     </row>
@@ -22690,7 +22690,7 @@
       <c r="K11" s="139"/>
       <c r="L11" s="128">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>4505727.849680637</v>
+        <v>4556038.5303122355</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
@@ -22713,7 +22713,7 @@
       </c>
       <c r="C15" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.10050000000000001</v>
+        <v>9.9847499999999992E-2</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
@@ -22728,7 +22728,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>1204506.1678173328</v>
+        <v>1206915.4047518005</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -22737,7 +22737,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>4505727.849680637</v>
+        <v>4556038.5303122355</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -22746,7 +22746,7 @@
       </c>
       <c r="C21" s="95">
         <f ca="1">C19+C20</f>
-        <v>5710234.0174979698</v>
+        <v>5762953.9350640364</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -22773,7 +22773,7 @@
       </c>
       <c r="C24" s="95">
         <f ca="1">C21+C22-C23</f>
-        <v>7126793.0174979698</v>
+        <v>7179512.9350640364</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -22791,7 +22791,7 @@
       </c>
       <c r="C26" s="254">
         <f ca="1">C24/C25</f>
-        <v>142.18891938665595</v>
+        <v>143.24075126818636</v>
       </c>
     </row>
   </sheetData>
@@ -23060,23 +23060,23 @@
       <c r="G9" s="140"/>
       <c r="H9" s="93">
         <f ca="1">DCF!H10</f>
-        <v>164264.58158222964</v>
+        <v>164362.03385582429</v>
       </c>
       <c r="I9" s="93">
         <f ca="1">DCF!I10</f>
-        <v>198597.84341738783</v>
+        <v>198833.55524456274</v>
       </c>
       <c r="J9" s="93">
         <f ca="1">DCF!J10</f>
-        <v>226205.25139792333</v>
+        <v>226608.08863397525</v>
       </c>
       <c r="K9" s="93">
         <f ca="1">DCF!K10</f>
-        <v>259839.38171460424</v>
+        <v>260456.54412615745</v>
       </c>
       <c r="L9" s="93">
         <f ca="1">DCF!L10</f>
-        <v>355599.10970518761</v>
+        <v>356655.18289128062</v>
       </c>
       <c r="N9" s="92"/>
     </row>
@@ -23862,7 +23862,7 @@
       </c>
       <c r="C41" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.10050000000000001</v>
+        <v>9.9847499999999992E-2</v>
       </c>
     </row>
     <row r="42" spans="2:14" x14ac:dyDescent="0.2">
@@ -23888,7 +23888,7 @@
       </c>
       <c r="C44" s="24">
         <f ca="1">C43/(1+C41)^5</f>
-        <v>7549911.6055914601</v>
+        <v>7572333.6504909769</v>
       </c>
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.2">
@@ -23897,7 +23897,7 @@
       </c>
       <c r="C45" s="110">
         <f ca="1">SUM(H9:K9)+C44</f>
-        <v>8398818.6637036055</v>
+        <v>8422593.8723514974</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -23924,7 +23924,7 @@
       </c>
       <c r="C48" s="110">
         <f ca="1">C45+C46-C47</f>
-        <v>9815377.6637036055</v>
+        <v>9839152.8723514974</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
@@ -23942,7 +23942,7 @@
       </c>
       <c r="C50" s="254">
         <f ca="1">C48/C49</f>
-        <v>195.82972873595637</v>
+        <v>196.3040755028031</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
@@ -23966,7 +23966,7 @@
       </c>
       <c r="C54" s="137">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.10050000000000001</v>
+        <v>9.9847499999999992E-2</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
@@ -24001,7 +24001,7 @@
       </c>
       <c r="C58" s="254">
         <f ca="1">C57/(1+C54)^5</f>
-        <v>157.58022062820396</v>
+        <v>158.04820899241003</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
@@ -24025,7 +24025,7 @@
       </c>
       <c r="C62" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.10050000000000001</v>
+        <v>9.9847499999999992E-2</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
@@ -24051,7 +24051,7 @@
       </c>
       <c r="C65" s="24">
         <f ca="1">C64/(1+C62)^5</f>
-        <v>7823180.413514127</v>
+        <v>7846414.0236081732</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -24060,7 +24060,7 @@
       </c>
       <c r="C66" s="110">
         <f ca="1">SUM(H9:K9)+C65</f>
-        <v>8672087.4716262724</v>
+        <v>8696674.2454686929</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.2">
@@ -24087,7 +24087,7 @@
       </c>
       <c r="C69" s="110">
         <f ca="1">C66+C67-C68</f>
-        <v>10088646.471626272</v>
+        <v>10113233.245468693</v>
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.2">
@@ -24105,7 +24105,7 @@
       </c>
       <c r="C71" s="254">
         <f ca="1">C69/C70</f>
-        <v>201.2818018360455</v>
+        <v>201.77234039880079</v>
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.2">
@@ -24129,7 +24129,7 @@
       </c>
       <c r="C75" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.10050000000000001</v>
+        <v>9.9847499999999992E-2</v>
       </c>
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.2">
@@ -24155,7 +24155,7 @@
       </c>
       <c r="C78" s="24">
         <f ca="1">C77/(1+C75)^5</f>
-        <v>7844064.0058093136</v>
+        <v>7867359.6368737463</v>
       </c>
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.2">
@@ -24164,7 +24164,7 @@
       </c>
       <c r="C79" s="110">
         <f ca="1">SUM(H9:K9)+C78</f>
-        <v>8692971.063921459</v>
+        <v>8717619.8587342668</v>
       </c>
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.2">
@@ -24191,7 +24191,7 @@
       </c>
       <c r="C82" s="110">
         <f ca="1">C79+C80-C81</f>
-        <v>10109530.063921459</v>
+        <v>10134178.858734267</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.2">
@@ -24209,7 +24209,7 @@
       </c>
       <c r="C84" s="254">
         <f ca="1">C82/C83</f>
-        <v>201.69845704324368</v>
+        <v>202.19023300615032</v>
       </c>
     </row>
   </sheetData>
@@ -24274,7 +24274,7 @@
       </c>
       <c r="C5" s="135">
         <f ca="1">DCF!C26</f>
-        <v>142.18891938665595</v>
+        <v>143.24075126818636</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -24283,7 +24283,7 @@
       </c>
       <c r="C6" s="135">
         <f ca="1">Multiples!C50</f>
-        <v>195.82972873595637</v>
+        <v>196.3040755028031</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -24292,7 +24292,7 @@
       </c>
       <c r="C7" s="135">
         <f ca="1">Multiples!C58</f>
-        <v>157.58022062820396</v>
+        <v>158.04820899241003</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -24301,7 +24301,7 @@
       </c>
       <c r="C8" s="135">
         <f ca="1">Multiples!C71</f>
-        <v>201.2818018360455</v>
+        <v>201.77234039880079</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -24310,7 +24310,7 @@
       </c>
       <c r="C9" s="135">
         <f ca="1">Multiples!C84</f>
-        <v>201.69845704324368</v>
+        <v>202.19023300615032</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -24319,7 +24319,7 @@
       </c>
       <c r="C10" s="254">
         <f ca="1">AVERAGE(C5:C9)</f>
-        <v>179.71582552602109</v>
+        <v>180.31112183367014</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -24328,7 +24328,7 @@
       </c>
       <c r="C11" s="135">
         <f ca="1">Overview!C5</f>
-        <v>147.74</v>
+        <v>148.93</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -24337,7 +24337,7 @@
       </c>
       <c r="C12" s="154">
         <f ca="1">(C10-C11)/C11</f>
-        <v>0.21643309547868608</v>
+        <v>0.21071054746303722</v>
       </c>
     </row>
   </sheetData>
@@ -24846,7 +24846,7 @@
       </c>
       <c r="C24" s="137">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.10050000000000001</v>
+        <v>9.9847499999999992E-2</v>
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
@@ -25101,7 +25101,7 @@
       <c r="K8" s="139"/>
       <c r="L8" s="128">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>6921505.124419421</v>
+        <v>6978066.470656733</v>
       </c>
       <c r="N8" s="92"/>
       <c r="O8" s="16"/>
@@ -25155,23 +25155,23 @@
       <c r="G10" s="140"/>
       <c r="H10" s="128">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>179245.13014440585</v>
+        <v>179351.46983915372</v>
       </c>
       <c r="I10" s="128">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>210110.14801116177</v>
+        <v>210359.52356350157</v>
       </c>
       <c r="J10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>246289.95087178436</v>
+        <v>246728.55591063033</v>
       </c>
       <c r="K10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>288699.7152427095</v>
+        <v>289385.42582013697</v>
       </c>
       <c r="L10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>338412.20596373943</v>
+        <v>339417.23676052969</v>
       </c>
       <c r="N10" s="92"/>
     </row>
@@ -25190,7 +25190,7 @@
       <c r="K11" s="139"/>
       <c r="L11" s="128">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>4287955.9016523501</v>
+        <v>4335834.9540779646</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -25206,7 +25206,7 @@
       </c>
       <c r="C15" s="156">
         <f ca="1">Overview!C5</f>
-        <v>147.74</v>
+        <v>148.93</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -25215,7 +25215,7 @@
       </c>
       <c r="C16" s="156">
         <f ca="1">C36</f>
-        <v>148.91788252652825</v>
+        <v>149.99436083383742</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -25254,7 +25254,7 @@
       </c>
       <c r="C21" s="221">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.10050000000000001</v>
+        <v>9.9847499999999992E-2</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -25272,7 +25272,7 @@
       </c>
       <c r="C23" s="161">
         <f ca="1">C15*C22</f>
-        <v>6912163.6400000006</v>
+        <v>6967838.9800000004</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -25299,7 +25299,7 @@
       </c>
       <c r="C26" s="162">
         <f ca="1">C23+C25-C24</f>
-        <v>5495604.6400000006</v>
+        <v>5551279.9800000004</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -25315,7 +25315,7 @@
       </c>
       <c r="C29" s="161">
         <f ca="1">SUM(H10:L10)</f>
-        <v>1262757.150233801</v>
+        <v>1265242.2118939522</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -25324,7 +25324,7 @@
       </c>
       <c r="C30" s="161">
         <f ca="1">L11</f>
-        <v>4287955.9016523501</v>
+        <v>4335834.9540779646</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -25333,7 +25333,7 @@
       </c>
       <c r="C31" s="164">
         <f ca="1">C29+C30</f>
-        <v>5550713.0518861506</v>
+        <v>5601077.1659719171</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -25360,7 +25360,7 @@
       </c>
       <c r="C34" s="164">
         <f ca="1">C31+C32-C33</f>
-        <v>6967272.0518861506</v>
+        <v>7017636.1659719171</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.2">
@@ -25378,7 +25378,7 @@
       </c>
       <c r="C36" s="167">
         <f ca="1">C34/C35</f>
-        <v>148.91788252652825</v>
+        <v>149.99436083383742</v>
       </c>
     </row>
   </sheetData>
@@ -32084,7 +32084,7 @@
       </c>
       <c r="AC116" s="63">
         <f ca="1">Overview!C5</f>
-        <v>147.74</v>
+        <v>148.93</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -32155,7 +32155,7 @@
       </c>
       <c r="AC117" s="65">
         <f ca="1">AC116/AC85</f>
-        <v>147.74</v>
+        <v>148.93</v>
       </c>
     </row>
     <row r="119" spans="1:31" x14ac:dyDescent="0.2">
@@ -33265,7 +33265,7 @@
       <c r="AA146" s="49"/>
       <c r="AC146" s="72">
         <f ca="1">AC117/Statement!AC26</f>
-        <v>47.042012708893125</v>
+        <v>47.420921569889352</v>
       </c>
     </row>
     <row r="147" spans="2:29" x14ac:dyDescent="0.2">
@@ -33302,7 +33302,7 @@
       <c r="AA147" s="49"/>
       <c r="AC147" s="72">
         <f ca="1">AC117/(Statement!AC5/Statement!AC22)</f>
-        <v>6.3446164404694656</v>
+        <v>6.3957203633350312</v>
       </c>
     </row>
     <row r="148" spans="2:29" x14ac:dyDescent="0.2">
@@ -33363,7 +33363,7 @@
       </c>
       <c r="AC148" s="72">
         <f ca="1">AC117/(Statement!AC49/Statement!AC75)</f>
-        <v>4.9031408867721904</v>
+        <v>4.942634169940316</v>
       </c>
     </row>
     <row r="149" spans="2:29" x14ac:dyDescent="0.2">
@@ -33424,7 +33424,7 @@
       </c>
       <c r="AC149" s="143">
         <f ca="1">Statement!AC117*Statement!AC78</f>
-        <v>7405024.2800000003</v>
+        <v>7464669.46</v>
       </c>
     </row>
     <row r="150" spans="2:29" x14ac:dyDescent="0.2">
@@ -33485,7 +33485,7 @@
       </c>
       <c r="AC150" s="143">
         <f ca="1">AC149+AC108-AC107+AC48+AC45</f>
-        <v>5988465.2800000003</v>
+        <v>6048110.46</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -33522,7 +33522,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="182">
         <f ca="1">AC150/AC5</f>
-        <v>5.2300915456916233</v>
+        <v>5.2821833149636417</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -33559,7 +33559,7 @@
       <c r="AA152" s="49"/>
       <c r="AC152" s="182">
         <f ca="1">AC150/AC12</f>
-        <v>38.122451411656108</v>
+        <v>38.502151446669004</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -33694,7 +33694,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="72">
         <f t="shared" ref="AC155:AC156" ca="1" si="151">AC149/AC153</f>
-        <v>29.289709200221502</v>
+        <v>29.525628747725655</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -33731,7 +33731,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="72">
         <f t="shared" ca="1" si="151"/>
-        <v>35.916859544985655</v>
+        <v>36.274591860767799</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -33768,7 +33768,7 @@
       <c r="AA157" s="49"/>
       <c r="AC157" s="74">
         <f t="shared" ref="AC157" ca="1" si="154">AC153/AC149</f>
-        <v>3.4141684137732498E-2</v>
+        <v>3.386888077961861E-2</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
@@ -33805,7 +33805,7 @@
       <c r="AA158" s="49"/>
       <c r="AC158" s="74">
         <f ca="1">AC26/AC117</f>
-        <v>2.1257593848890602E-2</v>
+        <v>2.1087738637179197E-2</v>
       </c>
     </row>
     <row r="159" spans="2:29" x14ac:dyDescent="0.2">
@@ -33879,7 +33879,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="154">
         <f ca="1">-AC63/AC149</f>
-        <v>9.3994290049782252E-3</v>
+        <v>9.3243244557542678E-3</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -33916,7 +33916,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="154">
         <f ca="1">-(AC63+AC64)/AC149</f>
-        <v>9.3994290049782252E-3</v>
+        <v>9.3243244557542678E-3</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -34419,7 +34419,7 @@
       <c r="AA172" s="49"/>
       <c r="AC172" s="154">
         <f ca="1">(AC107-AC108)/AC149</f>
-        <v>0.19129700949474807</v>
+        <v>0.18976848306421862</v>
       </c>
     </row>
     <row r="173" spans="2:29" x14ac:dyDescent="0.2">
@@ -36396,7 +36396,7 @@
       </c>
       <c r="C5" s="171">
         <f ca="1">Overview!C5</f>
-        <v>147.74</v>
+        <v>148.93</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="134" t="s">
@@ -36412,7 +36412,7 @@
       </c>
       <c r="C6" s="172">
         <f ca="1">Statement!AC149</f>
-        <v>7405024.2800000003</v>
+        <v>7464669.46</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>20</v>
@@ -36432,7 +36432,7 @@
       </c>
       <c r="C7" s="172">
         <f ca="1">Statement!AC150</f>
-        <v>5988465.2800000003</v>
+        <v>6048110.46</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>32</v>
@@ -36452,7 +36452,7 @@
       </c>
       <c r="C8" s="173">
         <f ca="1">Statement!AC146</f>
-        <v>47.042012708893125</v>
+        <v>47.420921569889352</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>247</v>
@@ -36472,7 +36472,7 @@
       </c>
       <c r="C9" s="173">
         <f ca="1">Statement!AC147</f>
-        <v>6.3446164404694656</v>
+        <v>6.3957203633350312</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>248</v>
@@ -36492,7 +36492,7 @@
       </c>
       <c r="C10" s="173">
         <f ca="1">Statement!AC148</f>
-        <v>4.9031408867721904</v>
+        <v>4.942634169940316</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -36512,7 +36512,7 @@
       </c>
       <c r="C11" s="173">
         <f ca="1">Statement!AC151</f>
-        <v>5.2300915456916233</v>
+        <v>5.2821833149636417</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -36521,7 +36521,7 @@
       </c>
       <c r="C12" s="173">
         <f ca="1">Statement!AC152</f>
-        <v>38.122451411656108</v>
+        <v>38.502151446669004</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
@@ -36757,7 +36757,7 @@
       </c>
       <c r="C38" s="174">
         <f ca="1">Statement!AC158</f>
-        <v>2.1257593848890602E-2</v>
+        <v>2.1087738637179197E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>274</v>
@@ -36773,7 +36773,7 @@
       </c>
       <c r="C39" s="214">
         <f ca="1">Statement!AC157</f>
-        <v>3.4141684137732498E-2</v>
+        <v>3.386888077961861E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>276</v>
@@ -36805,7 +36805,7 @@
       </c>
       <c r="C41" s="174">
         <f ca="1">Statement!AC160</f>
-        <v>9.3994290049782252E-3</v>
+        <v>9.3243244557542678E-3</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -36814,7 +36814,7 @@
       </c>
       <c r="C42" s="174">
         <f ca="1">Statement!AC161</f>
-        <v>9.3994290049782252E-3</v>
+        <v>9.3243244557542678E-3</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
@@ -36858,7 +36858,7 @@
       </c>
       <c r="F48" s="174">
         <f ca="1">Statement!AC172</f>
-        <v>0.19129700949474807</v>
+        <v>0.18976848306421862</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
@@ -37037,7 +37037,7 @@
       </c>
       <c r="I6" s="171">
         <f ca="1">Statement!AC116</f>
-        <v>147.74</v>
+        <v>148.93</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -37066,7 +37066,7 @@
       </c>
       <c r="I7" s="172">
         <f ca="1">Statement!AC149</f>
-        <v>7405024.2800000003</v>
+        <v>7464669.46</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -37095,7 +37095,7 @@
       </c>
       <c r="I8" s="172">
         <f ca="1">Statement!AC150</f>
-        <v>5988465.2800000003</v>
+        <v>6048110.46</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -37124,7 +37124,7 @@
       </c>
       <c r="I9" s="173">
         <f ca="1">Statement!AC146</f>
-        <v>47.042012708893125</v>
+        <v>47.420921569889352</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -37153,7 +37153,7 @@
       </c>
       <c r="I10" s="173">
         <f ca="1">Statement!AC147</f>
-        <v>6.3446164404694656</v>
+        <v>6.3957203633350312</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -37182,7 +37182,7 @@
       </c>
       <c r="I11" s="173">
         <f ca="1">Statement!AC148</f>
-        <v>4.9031408867721904</v>
+        <v>4.942634169940316</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -37211,7 +37211,7 @@
       </c>
       <c r="I12" s="173">
         <f ca="1">Statement!AC151</f>
-        <v>5.2300915456916233</v>
+        <v>5.2821833149636417</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -37240,7 +37240,7 @@
       </c>
       <c r="I13" s="173">
         <f ca="1">Statement!AC152</f>
-        <v>38.122451411656108</v>
+        <v>38.502151446669004</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -38013,7 +38013,7 @@
       </c>
       <c r="I51" s="174">
         <f ca="1">Statement!AC158</f>
-        <v>2.1257593848890602E-2</v>
+        <v>2.1087738637179197E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -38042,7 +38042,7 @@
       </c>
       <c r="I52" s="174">
         <f ca="1">Statement!AC157</f>
-        <v>3.4141684137732498E-2</v>
+        <v>3.386888077961861E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -38100,7 +38100,7 @@
       </c>
       <c r="I54" s="174">
         <f ca="1">Statement!AC160</f>
-        <v>9.3994290049782252E-3</v>
+        <v>9.3243244557542678E-3</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -38129,7 +38129,7 @@
       </c>
       <c r="I55" s="174">
         <f ca="1">Statement!AC161</f>
-        <v>9.3994290049782252E-3</v>
+        <v>9.3243244557542678E-3</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -38365,7 +38365,7 @@
       </c>
       <c r="I68" s="195">
         <f ca="1">Statement!AC172</f>
-        <v>0.19129700949474807</v>
+        <v>0.18976848306421862</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">

--- a/DUOL.xlsx
+++ b/DUOL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E8748A2-072B-024A-8C86-875BD281AC8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F261F7F-F31F-E947-933B-8B409F2DDE2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -119,7 +119,7 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="2">
+  <futureMetadata name="XLRICHVALUE" count="5">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -130,7 +130,28 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="3"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="4"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="5"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="8"/>
         </ext>
       </extLst>
     </bk>
@@ -140,19 +161,28 @@
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="2">
+  <valueMetadata count="5">
     <bk>
       <rc t="2" v="0"/>
     </bk>
     <bk>
       <rc t="2" v="1"/>
     </bk>
+    <bk>
+      <rc t="2" v="2"/>
+    </bk>
+    <bk>
+      <rc t="2" v="3"/>
+    </bk>
+    <bk>
+      <rc t="2" v="4"/>
+    </bk>
   </valueMetadata>
 </metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="885" uniqueCount="446">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="886" uniqueCount="447">
   <si>
     <t>Ticker</t>
   </si>
@@ -1490,6 +1520,9 @@
   </si>
   <si>
     <t>Overview'!B3</t>
+  </si>
+  <si>
+    <t>Reverse DCF price</t>
   </si>
 </sst>
 </file>
@@ -2110,7 +2143,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="277">
+  <cellXfs count="280">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
@@ -2462,6 +2495,12 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2471,10 +2510,10 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2486,14 +2525,11 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2501,9 +2537,9 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="168" fontId="0" fillId="17" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="27" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -13180,7 +13216,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="6">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="9">
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=c2mtim&amp;q=XNAS%3aDUOL&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
@@ -13197,13 +13233,11 @@
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>343.99799999999999</v>
+    <v>328.53</v>
     <v>87.89</v>
-    <v>1.0654999999999999</v>
-    <v>9.1999999999999993</v>
-    <v>6.5840999999999997E-2</v>
-    <v>-0.16</v>
-    <v>-1.0739999999999999E-3</v>
+    <v>1.0656000000000001</v>
+    <v>-0.18</v>
+    <v>-1.2670000000000001E-3</v>
     <v>USD</v>
     <v>Duolingo, Inc. is a technology company. The Company is engaged in offering a mobile learning platform, as well as a digital English language proficiency assessment exam. It operates a freemium business model, namely, the app and the Website are accessible free of charge, although Duolingo also offers premium services for a subscription fee. Its solutions consist of the Duolingo App, Super Duolingo, Duolingo Max, Duolingo English Test: AI-Driven Language Assessment, Duolingo for Schools, and Duolingo ABC. The Duolingo App offers courses in over 40 different languages, including Spanish, English, French, German, Italian, Portuguese, Japanese and Chinese. Duolingo can also be accessed on desktop computers via a Web browser. Its subscription offering, Super Duolingo, offers learners additional features to enhance their learning experience. The Duolingo English Test is an online, on-demand, high-stakes English proficiency assessment. It also operates an animation and motion design studio.</v>
     <v>900</v>
@@ -13211,35 +13245,49 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>5900 PENN AVE, SECOND FLOOR, PITTSBURGH, PA, 15206 US</v>
-    <v>150.22999999999999</v>
+    <v>143.33000000000001</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46310.901905740626</v>
+    <v>46315.717072221873</v>
     <v>0</v>
-    <v>138.2525</v>
-    <v>6967879191</v>
+    <v>139.6</v>
+    <v>6640375301</v>
     <v>DUOLINGO, INC.</v>
     <v>DUOLINGO, INC.</v>
-    <v>138.85</v>
-    <v>17.751999999999999</v>
-    <v>139.72999999999999</v>
-    <v>148.93</v>
-    <v>148.77000000000001</v>
+    <v>141.97999999999999</v>
+    <v>16.9176</v>
+    <v>142.11000000000001</v>
+    <v>141.93</v>
     <v>46786270</v>
     <v>DUOL</v>
     <v>DUOLINGO, INC. (XNAS:DUOL)</v>
-    <v>1516461</v>
-    <v>987806</v>
+    <v>190895</v>
+    <v>969450</v>
     <v>2011</v>
   </rv>
   <rv s="2">
     <v>1</v>
   </rv>
+  <rv s="3">
+    <v>12</v>
+    <v>Price (Extended hours)</v>
+    <v>0</v>
+  </rv>
+  <rv s="3">
+    <v>12</v>
+    <v>Change (extended hours)</v>
+    <v>0</v>
+  </rv>
+  <rv s="3">
+    <v>12</v>
+    <v>Change % (extended hours)</v>
+    <v>0</v>
+  </rv>
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a33knm&amp;q=10+Y+TSY+YLD+NDX&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="3">
+  <rv s="4">
     <v>5</v>
     <v>10 Y TSY YLD NDX</v>
     <v>6</v>
@@ -13253,28 +13301,28 @@
     <v>Powered by Refinitiv</v>
     <v>53.64</v>
     <v>39.47</v>
-    <v>-0.27</v>
-    <v>-5.1749999999999999E-3</v>
+    <v>0.38</v>
+    <v>7.4539999999999997E-3</v>
     <v>US</v>
-    <v>53.29</v>
+    <v>51.5</v>
     <v>Index</v>
-    <v>3</v>
-    <v>51.77</v>
+    <v>6</v>
+    <v>50.9</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>51.96</v>
-    <v>52.17</v>
-    <v>51.9</v>
+    <v>50.9</v>
+    <v>50.98</v>
+    <v>51.36</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
   <rv s="2">
-    <v>4</v>
+    <v>7</v>
   </rv>
 </rvData>
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="4">
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="5">
   <s t="_hyperlink">
     <k n="Address" t="s"/>
     <k n="Text" t="s"/>
@@ -13296,8 +13344,6 @@
     <k n="Beta"/>
     <k n="Change"/>
     <k n="Change (%)"/>
-    <k n="Change (Extended hours)"/>
-    <k n="Change % (Extended hours)"/>
     <k n="Currency" t="s"/>
     <k n="Description" t="s"/>
     <k n="Employees"/>
@@ -13318,7 +13364,6 @@
     <k n="P/E"/>
     <k n="Previous close"/>
     <k n="Price"/>
-    <k n="Price (Extended hours)"/>
     <k n="Shares outstanding"/>
     <k n="Ticker symbol" t="s"/>
     <k n="UniqueName" t="s"/>
@@ -13328,6 +13373,11 @@
   </s>
   <s t="_linkedentity">
     <k n="%cvi" t="r"/>
+  </s>
+  <s t="_error">
+    <k n="errorType" t="i"/>
+    <k n="field" t="s"/>
+    <k n="subType" t="i"/>
   </s>
   <s t="_linkedentitycore">
     <k n="_Display" t="spb"/>
@@ -13363,7 +13413,7 @@
 <file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
 <supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
   <spbArrays count="2">
-    <a count="45">
+    <a count="42">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%IsRefreshable</v>
@@ -13374,16 +13424,13 @@
       <v t="s">Name</v>
       <v t="s">_SubLabel</v>
       <v t="s">Price</v>
-      <v t="s">Price (Extended hours)</v>
       <v t="s">Exchange</v>
       <v t="s">Official name</v>
       <v t="s">Last trade time</v>
       <v t="s">Ticker symbol</v>
       <v t="s">Exchange abbreviation</v>
       <v t="s">Change</v>
-      <v t="s">Change (Extended hours)</v>
       <v t="s">Change (%)</v>
-      <v t="s">Change % (Extended hours)</v>
       <v t="s">Currency</v>
       <v t="s">Previous close</v>
       <v t="s">Open</v>
@@ -13477,19 +13524,13 @@
       <v>8</v>
       <v>9</v>
       <v>4</v>
-      <v>1</v>
-      <v>1</v>
-      <v>5</v>
     </spb>
     <spb s="4">
-      <v>at close</v>
+      <v>Real-Time Nasdaq Last Sale</v>
       <v>from previous close</v>
       <v>from previous close</v>
       <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
-      <v>Real-Time Nasdaq Last Sale</v>
-      <v>from close</v>
-      <v>from close</v>
     </spb>
     <spb s="0">
       <v>1</v>
@@ -13561,9 +13602,6 @@
     <k n="Year incorporated" t="i"/>
     <k n="`%EntityServiceId" t="i"/>
     <k n="Shares outstanding" t="i"/>
-    <k n="Price (Extended hours)" t="i"/>
-    <k n="Change (Extended hours)" t="i"/>
-    <k n="Change % (Extended hours)" t="i"/>
   </s>
   <s>
     <k n="Price" t="s"/>
@@ -13571,9 +13609,6 @@
     <k n="Change (%)" t="s"/>
     <k n="ExchangeID" t="s"/>
     <k n="Last trade time" t="s"/>
-    <k n="Price (Extended hours)" t="s"/>
-    <k n="Change (Extended hours)" t="s"/>
-    <k n="Change % (Extended hours)" t="s"/>
   </s>
   <s>
     <k n="UniqueName" t="spb"/>
@@ -14051,7 +14086,7 @@
     <col min="5" max="5" width="19.1640625" style="1" customWidth="1"/>
     <col min="6" max="6" width="14.5" style="1" customWidth="1"/>
     <col min="7" max="7" width="1.6640625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="15.1640625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="15.83203125" style="1" customWidth="1"/>
     <col min="9" max="9" width="8.6640625" style="1" customWidth="1"/>
     <col min="10" max="10" width="2" style="1" customWidth="1"/>
     <col min="11" max="11" width="16.5" style="1" customWidth="1"/>
@@ -14089,7 +14124,7 @@
       </c>
       <c r="F3" s="186">
         <f ca="1">Statement!AC149</f>
-        <v>7464669.46</v>
+        <v>7113815.46</v>
       </c>
       <c r="H3" s="184" t="str">
         <f>'AVG target price'!B5</f>
@@ -14097,7 +14132,7 @@
       </c>
       <c r="I3" s="210">
         <f ca="1">'AVG target price'!C5</f>
-        <v>143.24075126818636</v>
+        <v>144.11714547052802</v>
       </c>
       <c r="K3" s="257" t="s">
         <v>441</v>
@@ -14116,7 +14151,7 @@
       </c>
       <c r="F4" s="187">
         <f ca="1">Statement!AC150</f>
-        <v>6048110.46</v>
+        <v>5697256.46</v>
       </c>
       <c r="H4" s="184" t="str">
         <f>'AVG target price'!B6</f>
@@ -14124,7 +14159,7 @@
       </c>
       <c r="I4" s="210">
         <f ca="1">'AVG target price'!C6</f>
-        <v>196.3040755028031</v>
+        <v>196.69460806261617</v>
       </c>
       <c r="K4" s="257" t="s">
         <v>442</v>
@@ -14136,7 +14171,7 @@
       </c>
       <c r="C5" s="207" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>148.93</v>
+        <v>141.93</v>
       </c>
       <c r="E5" s="184" t="s">
         <v>247</v>
@@ -14151,7 +14186,7 @@
       </c>
       <c r="I5" s="210">
         <f ca="1">'AVG target price'!C7</f>
-        <v>158.04820899241003</v>
+        <v>158.43352867962039</v>
       </c>
       <c r="K5" s="257" t="s">
         <v>443</v>
@@ -14161,16 +14196,16 @@
       <c r="B6" s="184" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="207" cm="1">
-        <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>148.77000000000001</v>
+      <c r="C6" s="207" t="e" cm="1" vm="2">
+        <f t="array" ref="C6">_FV(C3,"Price (Extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E6" s="184" t="s">
         <v>241</v>
       </c>
       <c r="F6" s="189">
         <f ca="1">Statement!AC146</f>
-        <v>47.420921569889352</v>
+        <v>45.192045916970358</v>
       </c>
       <c r="H6" s="184" t="str">
         <f>'AVG target price'!B8</f>
@@ -14178,7 +14213,7 @@
       </c>
       <c r="I6" s="210">
         <f ca="1">'AVG target price'!C8</f>
-        <v>201.77234039880079</v>
+        <v>202.17620452455026</v>
       </c>
       <c r="K6" s="258" t="s">
         <v>444</v>
@@ -14190,14 +14225,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>9.1999999999999993</v>
+        <v>-0.18</v>
       </c>
       <c r="E7" s="185" t="s">
         <v>205</v>
       </c>
       <c r="F7" s="190">
         <f ca="1">Statement!AC147</f>
-        <v>6.3957203633350312</v>
+        <v>6.0951090523611153</v>
       </c>
       <c r="H7" s="184" t="str">
         <f>'AVG target price'!B9</f>
@@ -14205,23 +14240,23 @@
       </c>
       <c r="I7" s="210">
         <f ca="1">'AVG target price'!C9</f>
-        <v>202.19023300615032</v>
+        <v>202.59511594919471</v>
       </c>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B8" s="184" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="6" cm="1">
-        <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>-0.16</v>
+      <c r="C8" s="6" t="e" cm="1" vm="3">
+        <f t="array" ref="C8">_FV(C3,"Change (extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E8" s="184" t="s">
         <v>269</v>
       </c>
       <c r="F8" s="191">
         <f ca="1">Statement!AC157</f>
-        <v>3.386888077961861E-2</v>
+        <v>3.5539296938692309E-2</v>
       </c>
       <c r="H8" s="183" t="str">
         <f>'AVG target price'!B10</f>
@@ -14229,7 +14264,7 @@
       </c>
       <c r="I8" s="211">
         <f ca="1">'AVG target price'!C10</f>
-        <v>180.31112183367014</v>
+        <v>180.80332053730189</v>
       </c>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.2">
@@ -14238,14 +14273,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>6.5840999999999997E-2</v>
+        <v>-1.2670000000000001E-3</v>
       </c>
       <c r="E9" s="184" t="s">
         <v>292</v>
       </c>
       <c r="F9" s="191">
         <f ca="1">Statement!AC158</f>
-        <v>2.1087738637179197E-2</v>
+        <v>2.2127787749137588E-2</v>
       </c>
       <c r="H9" s="183" t="str">
         <f>'AVG target price'!B12</f>
@@ -14253,23 +14288,23 @@
       </c>
       <c r="I9" s="212">
         <f ca="1">'AVG target price'!C12</f>
-        <v>0.21071054746303722</v>
+        <v>0.27389079502079811</v>
       </c>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B10" s="184" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="73" cm="1">
-        <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>-1.0739999999999999E-3</v>
+      <c r="C10" s="73" t="e" cm="1" vm="4">
+        <f t="array" ref="C10">_FV(C3,"Change % (extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E10" s="184" t="s">
         <v>297</v>
       </c>
       <c r="F10" s="191">
         <f ca="1">Statement!AC160</f>
-        <v>9.3243244557542678E-3</v>
+        <v>9.7842009525504342E-3</v>
       </c>
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.2">
@@ -14278,7 +14313,7 @@
       </c>
       <c r="C11" s="208" cm="1">
         <f t="array" aca="1" ref="C11" ca="1">_FV(C3,"52 week high",TRUE)</f>
-        <v>343.99799999999999</v>
+        <v>328.53</v>
       </c>
       <c r="E11" s="185" t="s">
         <v>293</v>
@@ -14317,7 +14352,7 @@
       </c>
       <c r="C13" s="208" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>1.0654999999999999</v>
+        <v>1.0656000000000001</v>
       </c>
       <c r="E13" s="184" t="s">
         <v>104</v>
@@ -14326,10 +14361,10 @@
         <f>Statement!AC125</f>
         <v>0.10928737315054812</v>
       </c>
-      <c r="H13" s="183" t="s">
+      <c r="H13" s="279" t="s">
         <v>437</v>
       </c>
-      <c r="I13" s="212">
+      <c r="I13" s="277">
         <f>'Reverse DCF'!C17</f>
         <v>0.28999999999999998</v>
       </c>
@@ -14340,7 +14375,7 @@
       </c>
       <c r="C14" s="209" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>987806</v>
+        <v>969450</v>
       </c>
       <c r="E14" s="185" t="s">
         <v>105</v>
@@ -14349,6 +14384,13 @@
         <f>Statement!AC136</f>
         <v>-17.586668123511064</v>
       </c>
+      <c r="H14" s="185" t="s">
+        <v>446</v>
+      </c>
+      <c r="I14" s="278">
+        <f ca="1">'Reverse DCF'!C16</f>
+        <v>150.89124691191896</v>
+      </c>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.2">
       <c r="E15" s="184" t="s">
@@ -14356,7 +14398,7 @@
       </c>
       <c r="F15" s="191">
         <f ca="1">Statement!AC172</f>
-        <v>0.18976848306421862</v>
+        <v>0.19912788122845121</v>
       </c>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.2">
@@ -14389,7 +14431,7 @@
       </c>
       <c r="I17" s="255">
         <f ca="1">DCF!C15</f>
-        <v>9.9847499999999992E-2</v>
+        <v>9.9312000000000011E-2</v>
       </c>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.2">
@@ -14411,7 +14453,7 @@
       </c>
       <c r="I18" s="256">
         <f ca="1">Multiples!C54</f>
-        <v>9.9847499999999992E-2</v>
+        <v>9.9312000000000011E-2</v>
       </c>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
@@ -14479,12 +14521,12 @@
       <c r="C26" s="169">
         <v>0.21</v>
       </c>
-      <c r="E26" s="184" t="e" vm="2">
+      <c r="E26" s="184" t="e" vm="5">
         <v>#VALUE!</v>
       </c>
       <c r="F26" s="218" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>51.9</v>
+        <v>51.36</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -14499,7 +14541,7 @@
       </c>
       <c r="F27" s="219">
         <f ca="1">F26/1000</f>
-        <v>5.1900000000000002E-2</v>
+        <v>5.1360000000000003E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -14827,8 +14869,8 @@
       <c r="D2" s="262"/>
       <c r="E2" s="262"/>
       <c r="F2" s="262"/>
-      <c r="G2" s="271"/>
-      <c r="H2" s="272" t="s">
+      <c r="G2" s="268"/>
+      <c r="H2" s="269" t="s">
         <v>114</v>
       </c>
       <c r="I2" s="262"/>
@@ -14861,32 +14903,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="268" t="s">
+      <c r="C4" s="270" t="s">
         <v>116</v>
       </c>
-      <c r="D4" s="268"/>
-      <c r="E4" s="268"/>
-      <c r="F4" s="268"/>
-      <c r="G4" s="268"/>
-      <c r="H4" s="268"/>
-      <c r="I4" s="268"/>
-      <c r="J4" s="268"/>
-      <c r="K4" s="268"/>
-      <c r="L4" s="268"/>
+      <c r="D4" s="270"/>
+      <c r="E4" s="270"/>
+      <c r="F4" s="270"/>
+      <c r="G4" s="270"/>
+      <c r="H4" s="270"/>
+      <c r="I4" s="270"/>
+      <c r="J4" s="270"/>
+      <c r="K4" s="270"/>
+      <c r="L4" s="270"/>
       <c r="O4" s="5"/>
-      <c r="S4" s="269" t="s">
+      <c r="S4" s="271" t="s">
         <v>116</v>
       </c>
-      <c r="T4" s="270"/>
-      <c r="U4" s="270"/>
-      <c r="V4" s="270"/>
-      <c r="W4" s="270"/>
-      <c r="X4" s="270"/>
-      <c r="Y4" s="270"/>
-      <c r="Z4" s="270"/>
-      <c r="AA4" s="270"/>
-      <c r="AB4" s="270"/>
-      <c r="AC4" s="270"/>
+      <c r="T4" s="272"/>
+      <c r="U4" s="272"/>
+      <c r="V4" s="272"/>
+      <c r="W4" s="272"/>
+      <c r="X4" s="272"/>
+      <c r="Y4" s="272"/>
+      <c r="Z4" s="272"/>
+      <c r="AA4" s="272"/>
+      <c r="AB4" s="272"/>
+      <c r="AC4" s="272"/>
       <c r="AE4" s="88"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -15574,33 +15616,33 @@
       <c r="Q12" s="92"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="268" t="s">
+      <c r="C13" s="270" t="s">
         <v>122</v>
       </c>
-      <c r="D13" s="268"/>
-      <c r="E13" s="268"/>
-      <c r="F13" s="268"/>
-      <c r="G13" s="268"/>
-      <c r="H13" s="268"/>
-      <c r="I13" s="268"/>
-      <c r="J13" s="268"/>
-      <c r="K13" s="268"/>
-      <c r="L13" s="268"/>
+      <c r="D13" s="270"/>
+      <c r="E13" s="270"/>
+      <c r="F13" s="270"/>
+      <c r="G13" s="270"/>
+      <c r="H13" s="270"/>
+      <c r="I13" s="270"/>
+      <c r="J13" s="270"/>
+      <c r="K13" s="270"/>
+      <c r="L13" s="270"/>
       <c r="O13" s="5"/>
       <c r="Q13" s="92"/>
-      <c r="S13" s="269" t="s">
+      <c r="S13" s="271" t="s">
         <v>122</v>
       </c>
-      <c r="T13" s="270"/>
-      <c r="U13" s="270"/>
-      <c r="V13" s="270"/>
-      <c r="W13" s="270"/>
-      <c r="X13" s="270"/>
-      <c r="Y13" s="270"/>
-      <c r="Z13" s="270"/>
-      <c r="AA13" s="270"/>
-      <c r="AB13" s="270"/>
-      <c r="AC13" s="270"/>
+      <c r="T13" s="272"/>
+      <c r="U13" s="272"/>
+      <c r="V13" s="272"/>
+      <c r="W13" s="272"/>
+      <c r="X13" s="272"/>
+      <c r="Y13" s="272"/>
+      <c r="Z13" s="272"/>
+      <c r="AA13" s="272"/>
+      <c r="AB13" s="272"/>
+      <c r="AC13" s="272"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B14" s="16" t="s">
@@ -16209,33 +16251,33 @@
       <c r="Q22" s="92"/>
     </row>
     <row r="23" spans="2:31" x14ac:dyDescent="0.2">
-      <c r="C23" s="268" t="s">
+      <c r="C23" s="270" t="s">
         <v>124</v>
       </c>
-      <c r="D23" s="268"/>
-      <c r="E23" s="268"/>
-      <c r="F23" s="268"/>
-      <c r="G23" s="268"/>
-      <c r="H23" s="268"/>
-      <c r="I23" s="268"/>
-      <c r="J23" s="268"/>
-      <c r="K23" s="268"/>
-      <c r="L23" s="268"/>
+      <c r="D23" s="270"/>
+      <c r="E23" s="270"/>
+      <c r="F23" s="270"/>
+      <c r="G23" s="270"/>
+      <c r="H23" s="270"/>
+      <c r="I23" s="270"/>
+      <c r="J23" s="270"/>
+      <c r="K23" s="270"/>
+      <c r="L23" s="270"/>
       <c r="O23" s="5"/>
       <c r="Q23" s="92"/>
-      <c r="S23" s="269" t="s">
+      <c r="S23" s="271" t="s">
         <v>124</v>
       </c>
-      <c r="T23" s="270"/>
-      <c r="U23" s="270"/>
-      <c r="V23" s="270"/>
-      <c r="W23" s="270"/>
-      <c r="X23" s="270"/>
-      <c r="Y23" s="270"/>
-      <c r="Z23" s="270"/>
-      <c r="AA23" s="270"/>
-      <c r="AB23" s="270"/>
-      <c r="AC23" s="270"/>
+      <c r="T23" s="272"/>
+      <c r="U23" s="272"/>
+      <c r="V23" s="272"/>
+      <c r="W23" s="272"/>
+      <c r="X23" s="272"/>
+      <c r="Y23" s="272"/>
+      <c r="Z23" s="272"/>
+      <c r="AA23" s="272"/>
+      <c r="AB23" s="272"/>
+      <c r="AC23" s="272"/>
       <c r="AE23" s="88" t="str">
         <f>AE2</f>
         <v>TTM/YTD</v>
@@ -17554,32 +17596,32 @@
       <c r="O39" s="5"/>
     </row>
     <row r="40" spans="2:31" x14ac:dyDescent="0.2">
-      <c r="C40" s="268" t="s">
+      <c r="C40" s="270" t="s">
         <v>126</v>
       </c>
-      <c r="D40" s="268"/>
-      <c r="E40" s="268"/>
-      <c r="F40" s="268"/>
-      <c r="G40" s="268"/>
-      <c r="H40" s="268"/>
-      <c r="I40" s="268"/>
-      <c r="J40" s="268"/>
-      <c r="K40" s="268"/>
-      <c r="L40" s="268"/>
+      <c r="D40" s="270"/>
+      <c r="E40" s="270"/>
+      <c r="F40" s="270"/>
+      <c r="G40" s="270"/>
+      <c r="H40" s="270"/>
+      <c r="I40" s="270"/>
+      <c r="J40" s="270"/>
+      <c r="K40" s="270"/>
+      <c r="L40" s="270"/>
       <c r="O40" s="5"/>
-      <c r="S40" s="269" t="s">
+      <c r="S40" s="271" t="s">
         <v>126</v>
       </c>
-      <c r="T40" s="270"/>
-      <c r="U40" s="270"/>
-      <c r="V40" s="270"/>
-      <c r="W40" s="270"/>
-      <c r="X40" s="270"/>
-      <c r="Y40" s="270"/>
-      <c r="Z40" s="270"/>
-      <c r="AA40" s="270"/>
-      <c r="AB40" s="270"/>
-      <c r="AC40" s="270"/>
+      <c r="T40" s="272"/>
+      <c r="U40" s="272"/>
+      <c r="V40" s="272"/>
+      <c r="W40" s="272"/>
+      <c r="X40" s="272"/>
+      <c r="Y40" s="272"/>
+      <c r="Z40" s="272"/>
+      <c r="AA40" s="272"/>
+      <c r="AB40" s="272"/>
+      <c r="AC40" s="272"/>
     </row>
     <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -18146,18 +18188,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="C13:L13"/>
+    <mergeCell ref="S13:AC13"/>
+    <mergeCell ref="C23:L23"/>
+    <mergeCell ref="S23:AC23"/>
+    <mergeCell ref="C40:L40"/>
+    <mergeCell ref="S40:AC40"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="S2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
-    <mergeCell ref="C13:L13"/>
-    <mergeCell ref="S13:AC13"/>
-    <mergeCell ref="C23:L23"/>
-    <mergeCell ref="S23:AC23"/>
-    <mergeCell ref="C40:L40"/>
-    <mergeCell ref="S40:AC40"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -18197,8 +18239,8 @@
       <c r="D2" s="262"/>
       <c r="E2" s="262"/>
       <c r="F2" s="262"/>
-      <c r="G2" s="271"/>
-      <c r="H2" s="272" t="s">
+      <c r="G2" s="268"/>
+      <c r="H2" s="269" t="s">
         <v>114</v>
       </c>
       <c r="I2" s="262"/>
@@ -18228,31 +18270,31 @@
     <row r="4" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="268" t="s">
+      <c r="C4" s="270" t="s">
         <v>116</v>
       </c>
-      <c r="D4" s="268"/>
-      <c r="E4" s="268"/>
-      <c r="F4" s="268"/>
-      <c r="G4" s="268"/>
-      <c r="H4" s="268"/>
-      <c r="I4" s="268"/>
-      <c r="J4" s="268"/>
-      <c r="K4" s="268"/>
-      <c r="L4" s="268"/>
-      <c r="P4" s="270" t="s">
+      <c r="D4" s="270"/>
+      <c r="E4" s="270"/>
+      <c r="F4" s="270"/>
+      <c r="G4" s="270"/>
+      <c r="H4" s="270"/>
+      <c r="I4" s="270"/>
+      <c r="J4" s="270"/>
+      <c r="K4" s="270"/>
+      <c r="L4" s="270"/>
+      <c r="P4" s="272" t="s">
         <v>116</v>
       </c>
-      <c r="Q4" s="270"/>
-      <c r="R4" s="270"/>
-      <c r="S4" s="270"/>
-      <c r="T4" s="270"/>
-      <c r="U4" s="270"/>
-      <c r="V4" s="270"/>
-      <c r="W4" s="270"/>
-      <c r="X4" s="270"/>
-      <c r="Y4" s="270"/>
-      <c r="Z4" s="270"/>
+      <c r="Q4" s="272"/>
+      <c r="R4" s="272"/>
+      <c r="S4" s="272"/>
+      <c r="T4" s="272"/>
+      <c r="U4" s="272"/>
+      <c r="V4" s="272"/>
+      <c r="W4" s="272"/>
+      <c r="X4" s="272"/>
+      <c r="Y4" s="272"/>
+      <c r="Z4" s="272"/>
       <c r="AB4" s="88"/>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
@@ -18447,32 +18489,32 @@
       <c r="N8" s="92"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C9" s="268" t="s">
+      <c r="C9" s="270" t="s">
         <v>129</v>
       </c>
-      <c r="D9" s="268"/>
-      <c r="E9" s="268"/>
-      <c r="F9" s="268"/>
-      <c r="G9" s="268"/>
-      <c r="H9" s="268"/>
-      <c r="I9" s="268"/>
-      <c r="J9" s="268"/>
-      <c r="K9" s="268"/>
-      <c r="L9" s="268"/>
+      <c r="D9" s="270"/>
+      <c r="E9" s="270"/>
+      <c r="F9" s="270"/>
+      <c r="G9" s="270"/>
+      <c r="H9" s="270"/>
+      <c r="I9" s="270"/>
+      <c r="J9" s="270"/>
+      <c r="K9" s="270"/>
+      <c r="L9" s="270"/>
       <c r="N9" s="92"/>
-      <c r="P9" s="270" t="s">
+      <c r="P9" s="272" t="s">
         <v>130</v>
       </c>
-      <c r="Q9" s="270"/>
-      <c r="R9" s="270"/>
-      <c r="S9" s="270"/>
-      <c r="T9" s="270"/>
-      <c r="U9" s="270"/>
-      <c r="V9" s="270"/>
-      <c r="W9" s="270"/>
-      <c r="X9" s="270"/>
-      <c r="Y9" s="270"/>
-      <c r="Z9" s="270"/>
+      <c r="Q9" s="272"/>
+      <c r="R9" s="272"/>
+      <c r="S9" s="272"/>
+      <c r="T9" s="272"/>
+      <c r="U9" s="272"/>
+      <c r="V9" s="272"/>
+      <c r="W9" s="272"/>
+      <c r="X9" s="272"/>
+      <c r="Y9" s="272"/>
+      <c r="Z9" s="272"/>
       <c r="AB9" s="88">
         <f>AB4</f>
         <v>0</v>
@@ -19042,31 +19084,31 @@
       </c>
     </row>
     <row r="18" spans="2:26" x14ac:dyDescent="0.2">
-      <c r="C18" s="268" t="s">
+      <c r="C18" s="270" t="s">
         <v>132</v>
       </c>
-      <c r="D18" s="268"/>
-      <c r="E18" s="268"/>
-      <c r="F18" s="268"/>
-      <c r="G18" s="268"/>
-      <c r="H18" s="268"/>
-      <c r="I18" s="268"/>
-      <c r="J18" s="268"/>
-      <c r="K18" s="268"/>
-      <c r="L18" s="268"/>
-      <c r="P18" s="270" t="s">
+      <c r="D18" s="270"/>
+      <c r="E18" s="270"/>
+      <c r="F18" s="270"/>
+      <c r="G18" s="270"/>
+      <c r="H18" s="270"/>
+      <c r="I18" s="270"/>
+      <c r="J18" s="270"/>
+      <c r="K18" s="270"/>
+      <c r="L18" s="270"/>
+      <c r="P18" s="272" t="s">
         <v>132</v>
       </c>
-      <c r="Q18" s="270"/>
-      <c r="R18" s="270"/>
-      <c r="S18" s="270"/>
-      <c r="T18" s="270"/>
-      <c r="U18" s="270"/>
-      <c r="V18" s="270"/>
-      <c r="W18" s="270"/>
-      <c r="X18" s="270"/>
-      <c r="Y18" s="270"/>
-      <c r="Z18" s="270"/>
+      <c r="Q18" s="272"/>
+      <c r="R18" s="272"/>
+      <c r="S18" s="272"/>
+      <c r="T18" s="272"/>
+      <c r="U18" s="272"/>
+      <c r="V18" s="272"/>
+      <c r="W18" s="272"/>
+      <c r="X18" s="272"/>
+      <c r="Y18" s="272"/>
+      <c r="Z18" s="272"/>
     </row>
     <row r="19" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -19632,8 +19674,8 @@
       <c r="D3" s="262"/>
       <c r="E3" s="262"/>
       <c r="F3" s="262"/>
-      <c r="G3" s="271"/>
-      <c r="H3" s="272" t="s">
+      <c r="G3" s="268"/>
+      <c r="H3" s="269" t="s">
         <v>114</v>
       </c>
       <c r="I3" s="262"/>
@@ -19657,18 +19699,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="87"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="268" t="s">
+      <c r="C5" s="270" t="s">
         <v>116</v>
       </c>
-      <c r="D5" s="268"/>
-      <c r="E5" s="268"/>
-      <c r="F5" s="268"/>
-      <c r="G5" s="268"/>
-      <c r="H5" s="268"/>
-      <c r="I5" s="268"/>
-      <c r="J5" s="268"/>
-      <c r="K5" s="268"/>
-      <c r="L5" s="268"/>
+      <c r="D5" s="270"/>
+      <c r="E5" s="270"/>
+      <c r="F5" s="270"/>
+      <c r="G5" s="270"/>
+      <c r="H5" s="270"/>
+      <c r="I5" s="270"/>
+      <c r="J5" s="270"/>
+      <c r="K5" s="270"/>
+      <c r="L5" s="270"/>
       <c r="P5" s="273"/>
       <c r="Q5" s="273"/>
       <c r="R5" s="273"/>
@@ -19865,18 +19907,18 @@
       <c r="N10" s="92"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="268" t="s">
+      <c r="C11" s="270" t="s">
         <v>136</v>
       </c>
-      <c r="D11" s="268"/>
-      <c r="E11" s="268"/>
-      <c r="F11" s="268"/>
-      <c r="G11" s="268"/>
-      <c r="H11" s="268"/>
-      <c r="I11" s="268"/>
-      <c r="J11" s="268"/>
-      <c r="K11" s="268"/>
-      <c r="L11" s="268"/>
+      <c r="D11" s="270"/>
+      <c r="E11" s="270"/>
+      <c r="F11" s="270"/>
+      <c r="G11" s="270"/>
+      <c r="H11" s="270"/>
+      <c r="I11" s="270"/>
+      <c r="J11" s="270"/>
+      <c r="K11" s="270"/>
+      <c r="L11" s="270"/>
       <c r="N11" s="92"/>
       <c r="P11" s="273"/>
       <c r="Q11" s="273"/>
@@ -20130,18 +20172,18 @@
       <c r="D16" s="24"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="268" t="s">
+      <c r="C18" s="270" t="s">
         <v>141</v>
       </c>
-      <c r="D18" s="268"/>
-      <c r="E18" s="268"/>
-      <c r="F18" s="268"/>
-      <c r="G18" s="268"/>
-      <c r="H18" s="268"/>
-      <c r="I18" s="268"/>
-      <c r="J18" s="268"/>
-      <c r="K18" s="268"/>
-      <c r="L18" s="268"/>
+      <c r="D18" s="270"/>
+      <c r="E18" s="270"/>
+      <c r="F18" s="270"/>
+      <c r="G18" s="270"/>
+      <c r="H18" s="270"/>
+      <c r="I18" s="270"/>
+      <c r="J18" s="270"/>
+      <c r="K18" s="270"/>
+      <c r="L18" s="270"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -20359,18 +20401,18 @@
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="111"/>
-      <c r="C26" s="268" t="s">
+      <c r="C26" s="270" t="s">
         <v>147</v>
       </c>
-      <c r="D26" s="268"/>
-      <c r="E26" s="268"/>
-      <c r="F26" s="268"/>
-      <c r="G26" s="268"/>
-      <c r="H26" s="268"/>
-      <c r="I26" s="268"/>
-      <c r="J26" s="268"/>
-      <c r="K26" s="268"/>
-      <c r="L26" s="268"/>
+      <c r="D26" s="270"/>
+      <c r="E26" s="270"/>
+      <c r="F26" s="270"/>
+      <c r="G26" s="270"/>
+      <c r="H26" s="270"/>
+      <c r="I26" s="270"/>
+      <c r="J26" s="270"/>
+      <c r="K26" s="270"/>
+      <c r="L26" s="270"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="16" t="s">
@@ -20562,18 +20604,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="111"/>
-      <c r="C33" s="268" t="s">
+      <c r="C33" s="270" t="s">
         <v>151</v>
       </c>
-      <c r="D33" s="268"/>
-      <c r="E33" s="268"/>
-      <c r="F33" s="268"/>
-      <c r="G33" s="268"/>
-      <c r="H33" s="268"/>
-      <c r="I33" s="268"/>
-      <c r="J33" s="268"/>
-      <c r="K33" s="268"/>
-      <c r="L33" s="268"/>
+      <c r="D33" s="270"/>
+      <c r="E33" s="270"/>
+      <c r="F33" s="270"/>
+      <c r="G33" s="270"/>
+      <c r="H33" s="270"/>
+      <c r="I33" s="270"/>
+      <c r="J33" s="270"/>
+      <c r="K33" s="270"/>
+      <c r="L33" s="270"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
@@ -20757,18 +20799,18 @@
       <c r="C39" s="127"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="268" t="s">
+      <c r="C40" s="270" t="s">
         <v>154</v>
       </c>
-      <c r="D40" s="268"/>
-      <c r="E40" s="268"/>
-      <c r="F40" s="268"/>
-      <c r="G40" s="268"/>
-      <c r="H40" s="268"/>
-      <c r="I40" s="268"/>
-      <c r="J40" s="268"/>
-      <c r="K40" s="268"/>
-      <c r="L40" s="268"/>
+      <c r="D40" s="270"/>
+      <c r="E40" s="270"/>
+      <c r="F40" s="270"/>
+      <c r="G40" s="270"/>
+      <c r="H40" s="270"/>
+      <c r="I40" s="270"/>
+      <c r="J40" s="270"/>
+      <c r="K40" s="270"/>
+      <c r="L40" s="270"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -21032,6 +21074,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -21039,12 +21087,6 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -21088,8 +21130,8 @@
       <c r="D2" s="262"/>
       <c r="E2" s="262"/>
       <c r="F2" s="262"/>
-      <c r="G2" s="271"/>
-      <c r="H2" s="272" t="s">
+      <c r="G2" s="268"/>
+      <c r="H2" s="269" t="s">
         <v>114</v>
       </c>
       <c r="I2" s="262"/>
@@ -21113,18 +21155,18 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="268" t="s">
+      <c r="C4" s="270" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="268"/>
-      <c r="E4" s="268"/>
-      <c r="F4" s="268"/>
-      <c r="G4" s="268"/>
-      <c r="H4" s="268"/>
-      <c r="I4" s="268"/>
-      <c r="J4" s="268"/>
-      <c r="K4" s="268"/>
-      <c r="L4" s="268"/>
+      <c r="D4" s="270"/>
+      <c r="E4" s="270"/>
+      <c r="F4" s="270"/>
+      <c r="G4" s="270"/>
+      <c r="H4" s="270"/>
+      <c r="I4" s="270"/>
+      <c r="J4" s="270"/>
+      <c r="K4" s="270"/>
+      <c r="L4" s="270"/>
       <c r="S4" s="273"/>
       <c r="T4" s="273"/>
       <c r="U4" s="273"/>
@@ -21498,18 +21540,18 @@
       <c r="AE10" s="64"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="268" t="s">
+      <c r="C13" s="270" t="s">
         <v>162</v>
       </c>
-      <c r="D13" s="268"/>
-      <c r="E13" s="268"/>
-      <c r="F13" s="268"/>
-      <c r="G13" s="268"/>
-      <c r="H13" s="268"/>
-      <c r="I13" s="268"/>
-      <c r="J13" s="268"/>
-      <c r="K13" s="268"/>
-      <c r="L13" s="268"/>
+      <c r="D13" s="270"/>
+      <c r="E13" s="270"/>
+      <c r="F13" s="270"/>
+      <c r="G13" s="270"/>
+      <c r="H13" s="270"/>
+      <c r="I13" s="270"/>
+      <c r="J13" s="270"/>
+      <c r="K13" s="270"/>
+      <c r="L13" s="270"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="12">
@@ -21602,18 +21644,18 @@
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C18" s="268" t="s">
+      <c r="C18" s="270" t="s">
         <v>163</v>
       </c>
-      <c r="D18" s="268"/>
-      <c r="E18" s="268"/>
-      <c r="F18" s="268"/>
-      <c r="G18" s="268"/>
-      <c r="H18" s="268"/>
-      <c r="I18" s="268"/>
-      <c r="J18" s="268"/>
-      <c r="K18" s="268"/>
-      <c r="L18" s="268"/>
+      <c r="D18" s="270"/>
+      <c r="E18" s="270"/>
+      <c r="F18" s="270"/>
+      <c r="G18" s="270"/>
+      <c r="H18" s="270"/>
+      <c r="I18" s="270"/>
+      <c r="J18" s="270"/>
+      <c r="K18" s="270"/>
+      <c r="L18" s="270"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -21805,18 +21847,18 @@
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C25" s="268" t="s">
+      <c r="C25" s="270" t="s">
         <v>266</v>
       </c>
-      <c r="D25" s="268"/>
-      <c r="E25" s="268"/>
-      <c r="F25" s="268"/>
-      <c r="G25" s="268"/>
-      <c r="H25" s="268"/>
-      <c r="I25" s="268"/>
-      <c r="J25" s="268"/>
-      <c r="K25" s="268"/>
-      <c r="L25" s="268"/>
+      <c r="D25" s="270"/>
+      <c r="E25" s="270"/>
+      <c r="F25" s="270"/>
+      <c r="G25" s="270"/>
+      <c r="H25" s="270"/>
+      <c r="I25" s="270"/>
+      <c r="J25" s="270"/>
+      <c r="K25" s="270"/>
+      <c r="L25" s="270"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B26" s="16" t="s">
@@ -21954,18 +21996,18 @@
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C31" s="268" t="s">
+      <c r="C31" s="270" t="s">
         <v>78</v>
       </c>
-      <c r="D31" s="268"/>
-      <c r="E31" s="268"/>
-      <c r="F31" s="268"/>
-      <c r="G31" s="268"/>
-      <c r="H31" s="268"/>
-      <c r="I31" s="268"/>
-      <c r="J31" s="268"/>
-      <c r="K31" s="268"/>
-      <c r="L31" s="268"/>
+      <c r="D31" s="270"/>
+      <c r="E31" s="270"/>
+      <c r="F31" s="270"/>
+      <c r="G31" s="270"/>
+      <c r="H31" s="270"/>
+      <c r="I31" s="270"/>
+      <c r="J31" s="270"/>
+      <c r="K31" s="270"/>
+      <c r="L31" s="270"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="16" t="s">
@@ -22104,16 +22146,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="S4:AC4"/>
+    <mergeCell ref="C13:L13"/>
+    <mergeCell ref="C18:L18"/>
     <mergeCell ref="C31:L31"/>
     <mergeCell ref="C25:L25"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="S2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="S4:AC4"/>
-    <mergeCell ref="C13:L13"/>
-    <mergeCell ref="C18:L18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -22235,7 +22277,7 @@
       </c>
       <c r="C6" s="135">
         <f ca="1">Overview!C5</f>
-        <v>148.93</v>
+        <v>141.93</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22244,7 +22286,7 @@
       </c>
       <c r="C7" s="136">
         <f ca="1">C5*C6</f>
-        <v>7464669.46</v>
+        <v>7113815.46</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22262,7 +22304,7 @@
       </c>
       <c r="C9" s="137">
         <f ca="1">Overview!F27</f>
-        <v>5.1900000000000002E-2</v>
+        <v>5.1360000000000003E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22271,7 +22313,7 @@
       </c>
       <c r="C10" s="135">
         <f ca="1">Overview!C13</f>
-        <v>1.0654999999999999</v>
+        <v>1.0656000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22341,7 +22383,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>9.9847499999999992E-2</v>
+        <v>9.9312000000000011E-2</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22350,7 +22392,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>9.9847499999999992E-2</v>
+        <v>9.9312000000000011E-2</v>
       </c>
     </row>
   </sheetData>
@@ -22401,8 +22443,8 @@
       <c r="D3" s="262"/>
       <c r="E3" s="262"/>
       <c r="F3" s="262"/>
-      <c r="G3" s="271"/>
-      <c r="H3" s="272" t="s">
+      <c r="G3" s="268"/>
+      <c r="H3" s="269" t="s">
         <v>114</v>
       </c>
       <c r="I3" s="262"/>
@@ -22426,18 +22468,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="87"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="268" t="s">
+      <c r="C5" s="270" t="s">
         <v>184</v>
       </c>
-      <c r="D5" s="268"/>
-      <c r="E5" s="268"/>
-      <c r="F5" s="268"/>
-      <c r="G5" s="268"/>
-      <c r="H5" s="268"/>
-      <c r="I5" s="268"/>
-      <c r="J5" s="268"/>
-      <c r="K5" s="268"/>
-      <c r="L5" s="268"/>
+      <c r="D5" s="270"/>
+      <c r="E5" s="270"/>
+      <c r="F5" s="270"/>
+      <c r="G5" s="270"/>
+      <c r="H5" s="270"/>
+      <c r="I5" s="270"/>
+      <c r="J5" s="270"/>
+      <c r="K5" s="270"/>
+      <c r="L5" s="270"/>
       <c r="P5" s="273"/>
       <c r="Q5" s="273"/>
       <c r="R5" s="273"/>
@@ -22601,7 +22643,7 @@
       </c>
       <c r="L8" s="128">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>7332460.7703276332</v>
+        <v>7381968.193447846</v>
       </c>
       <c r="N8" s="92"/>
       <c r="O8" s="16"/>
@@ -22655,23 +22697,23 @@
       <c r="G10" s="140"/>
       <c r="H10" s="128">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>164362.03385582429</v>
+        <v>164442.09835901338</v>
       </c>
       <c r="I10" s="128">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>198833.55524456274</v>
+        <v>199027.31516372363</v>
       </c>
       <c r="J10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>226608.08863397525</v>
+        <v>226939.40791208789</v>
       </c>
       <c r="K10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>260456.54412615745</v>
+        <v>260964.41240846203</v>
       </c>
       <c r="L10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>356655.18289128062</v>
+        <v>357524.70406073733</v>
       </c>
       <c r="N10" s="92"/>
     </row>
@@ -22690,7 +22732,7 @@
       <c r="K11" s="139"/>
       <c r="L11" s="128">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>4556038.5303122355</v>
+        <v>4597982.6273697801</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
@@ -22713,7 +22755,7 @@
       </c>
       <c r="C15" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>9.9847499999999992E-2</v>
+        <v>9.9312000000000011E-2</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
@@ -22728,7 +22770,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>1206915.4047518005</v>
+        <v>1208897.9379040243</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -22737,7 +22779,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>4556038.5303122355</v>
+        <v>4597982.6273697801</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -22746,7 +22788,7 @@
       </c>
       <c r="C21" s="95">
         <f ca="1">C19+C20</f>
-        <v>5762953.9350640364</v>
+        <v>5806880.5652738046</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -22773,7 +22815,7 @@
       </c>
       <c r="C24" s="95">
         <f ca="1">C21+C22-C23</f>
-        <v>7179512.9350640364</v>
+        <v>7223439.5652738046</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -22791,7 +22833,7 @@
       </c>
       <c r="C26" s="254">
         <f ca="1">C24/C25</f>
-        <v>143.24075126818636</v>
+        <v>144.11714547052802</v>
       </c>
     </row>
   </sheetData>
@@ -22840,8 +22882,8 @@
       <c r="D2" s="262"/>
       <c r="E2" s="262"/>
       <c r="F2" s="262"/>
-      <c r="G2" s="271"/>
-      <c r="H2" s="272" t="s">
+      <c r="G2" s="268"/>
+      <c r="H2" s="269" t="s">
         <v>114</v>
       </c>
       <c r="I2" s="262"/>
@@ -22853,18 +22895,18 @@
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="268" t="s">
+      <c r="C4" s="270" t="s">
         <v>198</v>
       </c>
-      <c r="D4" s="268"/>
-      <c r="E4" s="268"/>
-      <c r="F4" s="268"/>
-      <c r="G4" s="268"/>
-      <c r="H4" s="268"/>
-      <c r="I4" s="268"/>
-      <c r="J4" s="268"/>
-      <c r="K4" s="268"/>
-      <c r="L4" s="268"/>
+      <c r="D4" s="270"/>
+      <c r="E4" s="270"/>
+      <c r="F4" s="270"/>
+      <c r="G4" s="270"/>
+      <c r="H4" s="270"/>
+      <c r="I4" s="270"/>
+      <c r="J4" s="270"/>
+      <c r="K4" s="270"/>
+      <c r="L4" s="270"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -23060,23 +23102,23 @@
       <c r="G9" s="140"/>
       <c r="H9" s="93">
         <f ca="1">DCF!H10</f>
-        <v>164362.03385582429</v>
+        <v>164442.09835901338</v>
       </c>
       <c r="I9" s="93">
         <f ca="1">DCF!I10</f>
-        <v>198833.55524456274</v>
+        <v>199027.31516372363</v>
       </c>
       <c r="J9" s="93">
         <f ca="1">DCF!J10</f>
-        <v>226608.08863397525</v>
+        <v>226939.40791208789</v>
       </c>
       <c r="K9" s="93">
         <f ca="1">DCF!K10</f>
-        <v>260456.54412615745</v>
+        <v>260964.41240846203</v>
       </c>
       <c r="L9" s="93">
         <f ca="1">DCF!L10</f>
-        <v>356655.18289128062</v>
+        <v>357524.70406073733</v>
       </c>
       <c r="N9" s="92"/>
     </row>
@@ -23084,18 +23126,18 @@
       <c r="N10" s="92"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C11" s="268" t="s">
+      <c r="C11" s="270" t="s">
         <v>122</v>
       </c>
-      <c r="D11" s="268"/>
-      <c r="E11" s="268"/>
-      <c r="F11" s="268"/>
-      <c r="G11" s="268"/>
-      <c r="H11" s="268"/>
-      <c r="I11" s="268"/>
-      <c r="J11" s="268"/>
-      <c r="K11" s="268"/>
-      <c r="L11" s="268"/>
+      <c r="D11" s="270"/>
+      <c r="E11" s="270"/>
+      <c r="F11" s="270"/>
+      <c r="G11" s="270"/>
+      <c r="H11" s="270"/>
+      <c r="I11" s="270"/>
+      <c r="J11" s="270"/>
+      <c r="K11" s="270"/>
+      <c r="L11" s="270"/>
       <c r="N11" s="92"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -23289,18 +23331,18 @@
       <c r="N16" s="92"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C17" s="268" t="s">
+      <c r="C17" s="270" t="s">
         <v>200</v>
       </c>
-      <c r="D17" s="268"/>
-      <c r="E17" s="268"/>
-      <c r="F17" s="268"/>
-      <c r="G17" s="268"/>
-      <c r="H17" s="268"/>
-      <c r="I17" s="268"/>
-      <c r="J17" s="268"/>
-      <c r="K17" s="268"/>
-      <c r="L17" s="268"/>
+      <c r="D17" s="270"/>
+      <c r="E17" s="270"/>
+      <c r="F17" s="270"/>
+      <c r="G17" s="270"/>
+      <c r="H17" s="270"/>
+      <c r="I17" s="270"/>
+      <c r="J17" s="270"/>
+      <c r="K17" s="270"/>
+      <c r="L17" s="270"/>
       <c r="N17" s="92"/>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
@@ -23434,18 +23476,18 @@
       <c r="N21" s="92"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C22" s="268" t="s">
+      <c r="C22" s="270" t="s">
         <v>203</v>
       </c>
-      <c r="D22" s="268"/>
-      <c r="E22" s="268"/>
-      <c r="F22" s="268"/>
-      <c r="G22" s="268"/>
-      <c r="H22" s="268"/>
-      <c r="I22" s="268"/>
-      <c r="J22" s="268"/>
-      <c r="K22" s="268"/>
-      <c r="L22" s="268"/>
+      <c r="D22" s="270"/>
+      <c r="E22" s="270"/>
+      <c r="F22" s="270"/>
+      <c r="G22" s="270"/>
+      <c r="H22" s="270"/>
+      <c r="I22" s="270"/>
+      <c r="J22" s="270"/>
+      <c r="K22" s="270"/>
+      <c r="L22" s="270"/>
       <c r="N22" s="92"/>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.2">
@@ -23529,18 +23571,18 @@
       <c r="N26" s="92"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C27" s="268" t="s">
+      <c r="C27" s="270" t="s">
         <v>204</v>
       </c>
-      <c r="D27" s="268"/>
-      <c r="E27" s="268"/>
-      <c r="F27" s="268"/>
-      <c r="G27" s="268"/>
-      <c r="H27" s="268"/>
-      <c r="I27" s="268"/>
-      <c r="J27" s="268"/>
-      <c r="K27" s="268"/>
-      <c r="L27" s="268"/>
+      <c r="D27" s="270"/>
+      <c r="E27" s="270"/>
+      <c r="F27" s="270"/>
+      <c r="G27" s="270"/>
+      <c r="H27" s="270"/>
+      <c r="I27" s="270"/>
+      <c r="J27" s="270"/>
+      <c r="K27" s="270"/>
+      <c r="L27" s="270"/>
       <c r="N27" s="92"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.2">
@@ -23862,7 +23904,7 @@
       </c>
       <c r="C41" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>9.9847499999999992E-2</v>
+        <v>9.9312000000000011E-2</v>
       </c>
     </row>
     <row r="42" spans="2:14" x14ac:dyDescent="0.2">
@@ -23888,7 +23930,7 @@
       </c>
       <c r="C44" s="24">
         <f ca="1">C43/(1+C41)^5</f>
-        <v>7572333.6504909769</v>
+        <v>7590794.9114711611</v>
       </c>
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.2">
@@ -23897,7 +23939,7 @@
       </c>
       <c r="C45" s="110">
         <f ca="1">SUM(H9:K9)+C44</f>
-        <v>8422593.8723514974</v>
+        <v>8442168.1453144476</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -23924,7 +23966,7 @@
       </c>
       <c r="C48" s="110">
         <f ca="1">C45+C46-C47</f>
-        <v>9839152.8723514974</v>
+        <v>9858727.1453144476</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
@@ -23942,7 +23984,7 @@
       </c>
       <c r="C50" s="254">
         <f ca="1">C48/C49</f>
-        <v>196.3040755028031</v>
+        <v>196.69460806261617</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
@@ -23966,7 +24008,7 @@
       </c>
       <c r="C54" s="137">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>9.9847499999999992E-2</v>
+        <v>9.9312000000000011E-2</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
@@ -24001,7 +24043,7 @@
       </c>
       <c r="C58" s="254">
         <f ca="1">C57/(1+C54)^5</f>
-        <v>158.04820899241003</v>
+        <v>158.43352867962039</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
@@ -24025,7 +24067,7 @@
       </c>
       <c r="C62" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>9.9847499999999992E-2</v>
+        <v>9.9312000000000011E-2</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
@@ -24051,7 +24093,7 @@
       </c>
       <c r="C65" s="24">
         <f ca="1">C64/(1+C62)^5</f>
-        <v>7846414.0236081732</v>
+        <v>7865543.4893362215</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -24060,7 +24102,7 @@
       </c>
       <c r="C66" s="110">
         <f ca="1">SUM(H9:K9)+C65</f>
-        <v>8696674.2454686929</v>
+        <v>8716916.723179508</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.2">
@@ -24087,7 +24129,7 @@
       </c>
       <c r="C69" s="110">
         <f ca="1">C66+C67-C68</f>
-        <v>10113233.245468693</v>
+        <v>10133475.723179508</v>
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.2">
@@ -24105,7 +24147,7 @@
       </c>
       <c r="C71" s="254">
         <f ca="1">C69/C70</f>
-        <v>201.77234039880079</v>
+        <v>202.17620452455026</v>
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.2">
@@ -24129,7 +24171,7 @@
       </c>
       <c r="C75" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>9.9847499999999992E-2</v>
+        <v>9.9312000000000011E-2</v>
       </c>
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.2">
@@ -24155,7 +24197,7 @@
       </c>
       <c r="C78" s="24">
         <f ca="1">C77/(1+C75)^5</f>
-        <v>7867359.6368737463</v>
+        <v>7886540.1677622497</v>
       </c>
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.2">
@@ -24164,7 +24206,7 @@
       </c>
       <c r="C79" s="110">
         <f ca="1">SUM(H9:K9)+C78</f>
-        <v>8717619.8587342668</v>
+        <v>8737913.4016055372</v>
       </c>
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.2">
@@ -24191,7 +24233,7 @@
       </c>
       <c r="C82" s="110">
         <f ca="1">C79+C80-C81</f>
-        <v>10134178.858734267</v>
+        <v>10154472.401605537</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.2">
@@ -24209,22 +24251,22 @@
       </c>
       <c r="C84" s="254">
         <f ca="1">C82/C83</f>
-        <v>202.19023300615032</v>
+        <v>202.59511594919471</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="C27:L27"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B60:C60"/>
     <mergeCell ref="C22:L22"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="C17:L17"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="C27:L27"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B60:C60"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -24274,7 +24316,7 @@
       </c>
       <c r="C5" s="135">
         <f ca="1">DCF!C26</f>
-        <v>143.24075126818636</v>
+        <v>144.11714547052802</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -24283,7 +24325,7 @@
       </c>
       <c r="C6" s="135">
         <f ca="1">Multiples!C50</f>
-        <v>196.3040755028031</v>
+        <v>196.69460806261617</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -24292,7 +24334,7 @@
       </c>
       <c r="C7" s="135">
         <f ca="1">Multiples!C58</f>
-        <v>158.04820899241003</v>
+        <v>158.43352867962039</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -24301,7 +24343,7 @@
       </c>
       <c r="C8" s="135">
         <f ca="1">Multiples!C71</f>
-        <v>201.77234039880079</v>
+        <v>202.17620452455026</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -24310,7 +24352,7 @@
       </c>
       <c r="C9" s="135">
         <f ca="1">Multiples!C84</f>
-        <v>202.19023300615032</v>
+        <v>202.59511594919471</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -24319,7 +24361,7 @@
       </c>
       <c r="C10" s="254">
         <f ca="1">AVERAGE(C5:C9)</f>
-        <v>180.31112183367014</v>
+        <v>180.80332053730189</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -24328,7 +24370,7 @@
       </c>
       <c r="C11" s="135">
         <f ca="1">Overview!C5</f>
-        <v>148.93</v>
+        <v>141.93</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -24337,7 +24379,7 @@
       </c>
       <c r="C12" s="154">
         <f ca="1">(C10-C11)/C11</f>
-        <v>0.21071054746303722</v>
+        <v>0.27389079502079811</v>
       </c>
     </row>
   </sheetData>
@@ -24438,8 +24480,8 @@
       <c r="D2" s="262"/>
       <c r="E2" s="262"/>
       <c r="F2" s="262"/>
-      <c r="G2" s="271"/>
-      <c r="H2" s="272" t="s">
+      <c r="G2" s="268"/>
+      <c r="H2" s="269" t="s">
         <v>114</v>
       </c>
       <c r="I2" s="262"/>
@@ -24451,18 +24493,18 @@
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="268" t="s">
+      <c r="C4" s="270" t="s">
         <v>198</v>
       </c>
-      <c r="D4" s="268"/>
-      <c r="E4" s="268"/>
-      <c r="F4" s="268"/>
-      <c r="G4" s="268"/>
-      <c r="H4" s="268"/>
-      <c r="I4" s="268"/>
-      <c r="J4" s="268"/>
-      <c r="K4" s="268"/>
-      <c r="L4" s="268"/>
+      <c r="D4" s="270"/>
+      <c r="E4" s="270"/>
+      <c r="F4" s="270"/>
+      <c r="G4" s="270"/>
+      <c r="H4" s="270"/>
+      <c r="I4" s="270"/>
+      <c r="J4" s="270"/>
+      <c r="K4" s="270"/>
+      <c r="L4" s="270"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -24575,18 +24617,18 @@
       <c r="N8" s="92"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C9" s="268" t="s">
+      <c r="C9" s="270" t="s">
         <v>122</v>
       </c>
-      <c r="D9" s="268"/>
-      <c r="E9" s="268"/>
-      <c r="F9" s="268"/>
-      <c r="G9" s="268"/>
-      <c r="H9" s="268"/>
-      <c r="I9" s="268"/>
-      <c r="J9" s="268"/>
-      <c r="K9" s="268"/>
-      <c r="L9" s="268"/>
+      <c r="D9" s="270"/>
+      <c r="E9" s="270"/>
+      <c r="F9" s="270"/>
+      <c r="G9" s="270"/>
+      <c r="H9" s="270"/>
+      <c r="I9" s="270"/>
+      <c r="J9" s="270"/>
+      <c r="K9" s="270"/>
+      <c r="L9" s="270"/>
       <c r="N9" s="92"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -24707,18 +24749,18 @@
       <c r="N13" s="92"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C14" s="268" t="s">
+      <c r="C14" s="270" t="s">
         <v>413</v>
       </c>
-      <c r="D14" s="268"/>
-      <c r="E14" s="268"/>
-      <c r="F14" s="268"/>
-      <c r="G14" s="268"/>
-      <c r="H14" s="268"/>
-      <c r="I14" s="268"/>
-      <c r="J14" s="268"/>
-      <c r="K14" s="268"/>
-      <c r="L14" s="268"/>
+      <c r="D14" s="270"/>
+      <c r="E14" s="270"/>
+      <c r="F14" s="270"/>
+      <c r="G14" s="270"/>
+      <c r="H14" s="270"/>
+      <c r="I14" s="270"/>
+      <c r="J14" s="270"/>
+      <c r="K14" s="270"/>
+      <c r="L14" s="270"/>
       <c r="N14" s="92"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
@@ -24846,7 +24888,7 @@
       </c>
       <c r="C24" s="137">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>9.9847499999999992E-2</v>
+        <v>9.9312000000000011E-2</v>
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
@@ -24919,8 +24961,8 @@
       <c r="D3" s="262"/>
       <c r="E3" s="262"/>
       <c r="F3" s="262"/>
-      <c r="G3" s="271"/>
-      <c r="H3" s="272" t="s">
+      <c r="G3" s="268"/>
+      <c r="H3" s="269" t="s">
         <v>114</v>
       </c>
       <c r="I3" s="262"/>
@@ -24944,18 +24986,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="87"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="268" t="s">
+      <c r="C5" s="270" t="s">
         <v>184</v>
       </c>
-      <c r="D5" s="268"/>
-      <c r="E5" s="268"/>
-      <c r="F5" s="268"/>
-      <c r="G5" s="268"/>
-      <c r="H5" s="268"/>
-      <c r="I5" s="268"/>
-      <c r="J5" s="268"/>
-      <c r="K5" s="268"/>
-      <c r="L5" s="268"/>
+      <c r="D5" s="270"/>
+      <c r="E5" s="270"/>
+      <c r="F5" s="270"/>
+      <c r="G5" s="270"/>
+      <c r="H5" s="270"/>
+      <c r="I5" s="270"/>
+      <c r="J5" s="270"/>
+      <c r="K5" s="270"/>
+      <c r="L5" s="270"/>
       <c r="P5" s="273"/>
       <c r="Q5" s="273"/>
       <c r="R5" s="273"/>
@@ -25101,7 +25143,7 @@
       <c r="K8" s="139"/>
       <c r="L8" s="128">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>6978066.470656733</v>
+        <v>7025181.0888108155</v>
       </c>
       <c r="N8" s="92"/>
       <c r="O8" s="16"/>
@@ -25155,23 +25197,23 @@
       <c r="G10" s="140"/>
       <c r="H10" s="128">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>179351.46983915372</v>
+        <v>179438.8360391942</v>
       </c>
       <c r="I10" s="128">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>210359.52356350157</v>
+        <v>210564.51534283304</v>
       </c>
       <c r="J10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>246728.55591063033</v>
+        <v>247089.29293253834</v>
       </c>
       <c r="K10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>289385.42582013697</v>
+        <v>289949.70298056828</v>
       </c>
       <c r="L10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>339417.23676052969</v>
+        <v>340244.73201869265</v>
       </c>
       <c r="N10" s="92"/>
     </row>
@@ -25190,15 +25232,15 @@
       <c r="K11" s="139"/>
       <c r="L11" s="128">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>4335834.9540779646</v>
+        <v>4375751.7987072133</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="274" t="s">
+      <c r="B14" s="275" t="s">
         <v>226</v>
       </c>
-      <c r="C14" s="275"/>
+      <c r="C14" s="276"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="155" t="s">
@@ -25206,7 +25248,7 @@
       </c>
       <c r="C15" s="156">
         <f ca="1">Overview!C5</f>
-        <v>148.93</v>
+        <v>141.93</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -25215,7 +25257,7 @@
       </c>
       <c r="C16" s="156">
         <f ca="1">C36</f>
-        <v>149.99436083383742</v>
+        <v>150.89124691191896</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -25225,20 +25267,20 @@
       <c r="C17" s="158">
         <v>0.28999999999999998</v>
       </c>
-      <c r="E17" s="276" t="s">
+      <c r="E17" s="274" t="s">
         <v>229</v>
       </c>
-      <c r="F17" s="276"/>
-      <c r="G17" s="276"/>
-      <c r="H17" s="276"/>
-      <c r="I17" s="276"/>
+      <c r="F17" s="274"/>
+      <c r="G17" s="274"/>
+      <c r="H17" s="274"/>
+      <c r="I17" s="274"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="274" t="s">
+      <c r="B19" s="275" t="s">
         <v>188</v>
       </c>
-      <c r="C19" s="275"/>
+      <c r="C19" s="276"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="159" t="s">
@@ -25254,7 +25296,7 @@
       </c>
       <c r="C21" s="221">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>9.9847499999999992E-2</v>
+        <v>9.9312000000000011E-2</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -25272,7 +25314,7 @@
       </c>
       <c r="C23" s="161">
         <f ca="1">C15*C22</f>
-        <v>6967838.9800000004</v>
+        <v>6640336.9800000004</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -25299,15 +25341,15 @@
       </c>
       <c r="C26" s="162">
         <f ca="1">C23+C25-C24</f>
-        <v>5551279.9800000004</v>
+        <v>5223777.9800000004</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="274" t="s">
+      <c r="B28" s="275" t="s">
         <v>190</v>
       </c>
-      <c r="C28" s="275"/>
+      <c r="C28" s="276"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="159" t="s">
@@ -25315,7 +25357,7 @@
       </c>
       <c r="C29" s="161">
         <f ca="1">SUM(H10:L10)</f>
-        <v>1265242.2118939522</v>
+        <v>1267287.0793138265</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -25324,7 +25366,7 @@
       </c>
       <c r="C30" s="161">
         <f ca="1">L11</f>
-        <v>4335834.9540779646</v>
+        <v>4375751.7987072133</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -25333,7 +25375,7 @@
       </c>
       <c r="C31" s="164">
         <f ca="1">C29+C30</f>
-        <v>5601077.1659719171</v>
+        <v>5643038.87802104</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -25360,7 +25402,7 @@
       </c>
       <c r="C34" s="164">
         <f ca="1">C31+C32-C33</f>
-        <v>7017636.1659719171</v>
+        <v>7059597.87802104</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.2">
@@ -25378,21 +25420,21 @@
       </c>
       <c r="C36" s="167">
         <f ca="1">C34/C35</f>
-        <v>149.99436083383742</v>
+        <v>150.89124691191896</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
+    <mergeCell ref="B14:C14"/>
     <mergeCell ref="E17:I17"/>
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
-    <mergeCell ref="B14:C14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -32084,7 +32126,7 @@
       </c>
       <c r="AC116" s="63">
         <f ca="1">Overview!C5</f>
-        <v>148.93</v>
+        <v>141.93</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -32155,7 +32197,7 @@
       </c>
       <c r="AC117" s="65">
         <f ca="1">AC116/AC85</f>
-        <v>148.93</v>
+        <v>141.93</v>
       </c>
     </row>
     <row r="119" spans="1:31" x14ac:dyDescent="0.2">
@@ -33265,7 +33307,7 @@
       <c r="AA146" s="49"/>
       <c r="AC146" s="72">
         <f ca="1">AC117/Statement!AC26</f>
-        <v>47.420921569889352</v>
+        <v>45.192045916970358</v>
       </c>
     </row>
     <row r="147" spans="2:29" x14ac:dyDescent="0.2">
@@ -33302,7 +33344,7 @@
       <c r="AA147" s="49"/>
       <c r="AC147" s="72">
         <f ca="1">AC117/(Statement!AC5/Statement!AC22)</f>
-        <v>6.3957203633350312</v>
+        <v>6.0951090523611153</v>
       </c>
     </row>
     <row r="148" spans="2:29" x14ac:dyDescent="0.2">
@@ -33363,7 +33405,7 @@
       </c>
       <c r="AC148" s="72">
         <f ca="1">AC117/(Statement!AC49/Statement!AC75)</f>
-        <v>4.942634169940316</v>
+        <v>4.7103207395395756</v>
       </c>
     </row>
     <row r="149" spans="2:29" x14ac:dyDescent="0.2">
@@ -33424,7 +33466,7 @@
       </c>
       <c r="AC149" s="143">
         <f ca="1">Statement!AC117*Statement!AC78</f>
-        <v>7464669.46</v>
+        <v>7113815.46</v>
       </c>
     </row>
     <row r="150" spans="2:29" x14ac:dyDescent="0.2">
@@ -33485,7 +33527,7 @@
       </c>
       <c r="AC150" s="143">
         <f ca="1">AC149+AC108-AC107+AC48+AC45</f>
-        <v>6048110.46</v>
+        <v>5697256.46</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -33522,7 +33564,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="182">
         <f ca="1">AC150/AC5</f>
-        <v>5.2821833149636417</v>
+        <v>4.9757611427752968</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -33559,7 +33601,7 @@
       <c r="AA152" s="49"/>
       <c r="AC152" s="182">
         <f ca="1">AC150/AC12</f>
-        <v>38.502151446669004</v>
+        <v>36.26862182894611</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -33694,7 +33736,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="72">
         <f t="shared" ref="AC155:AC156" ca="1" si="151">AC149/AC153</f>
-        <v>29.525628747725655</v>
+        <v>28.137866703583576</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -33731,7 +33773,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="72">
         <f t="shared" ca="1" si="151"/>
-        <v>36.274591860767799</v>
+        <v>34.170284120872815</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -33768,7 +33810,7 @@
       <c r="AA157" s="49"/>
       <c r="AC157" s="74">
         <f t="shared" ref="AC157" ca="1" si="154">AC153/AC149</f>
-        <v>3.386888077961861E-2</v>
+        <v>3.5539296938692309E-2</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
@@ -33805,7 +33847,7 @@
       <c r="AA158" s="49"/>
       <c r="AC158" s="74">
         <f ca="1">AC26/AC117</f>
-        <v>2.1087738637179197E-2</v>
+        <v>2.2127787749137588E-2</v>
       </c>
     </row>
     <row r="159" spans="2:29" x14ac:dyDescent="0.2">
@@ -33879,7 +33921,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="154">
         <f ca="1">-AC63/AC149</f>
-        <v>9.3243244557542678E-3</v>
+        <v>9.7842009525504342E-3</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -33916,7 +33958,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="154">
         <f ca="1">-(AC63+AC64)/AC149</f>
-        <v>9.3243244557542678E-3</v>
+        <v>9.7842009525504342E-3</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -34419,7 +34461,7 @@
       <c r="AA172" s="49"/>
       <c r="AC172" s="154">
         <f ca="1">(AC107-AC108)/AC149</f>
-        <v>0.18976848306421862</v>
+        <v>0.19912788122845121</v>
       </c>
     </row>
     <row r="173" spans="2:29" x14ac:dyDescent="0.2">
@@ -36396,7 +36438,7 @@
       </c>
       <c r="C5" s="171">
         <f ca="1">Overview!C5</f>
-        <v>148.93</v>
+        <v>141.93</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="134" t="s">
@@ -36412,7 +36454,7 @@
       </c>
       <c r="C6" s="172">
         <f ca="1">Statement!AC149</f>
-        <v>7464669.46</v>
+        <v>7113815.46</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>20</v>
@@ -36432,7 +36474,7 @@
       </c>
       <c r="C7" s="172">
         <f ca="1">Statement!AC150</f>
-        <v>6048110.46</v>
+        <v>5697256.46</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>32</v>
@@ -36452,7 +36494,7 @@
       </c>
       <c r="C8" s="173">
         <f ca="1">Statement!AC146</f>
-        <v>47.420921569889352</v>
+        <v>45.192045916970358</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>247</v>
@@ -36472,7 +36514,7 @@
       </c>
       <c r="C9" s="173">
         <f ca="1">Statement!AC147</f>
-        <v>6.3957203633350312</v>
+        <v>6.0951090523611153</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>248</v>
@@ -36492,7 +36534,7 @@
       </c>
       <c r="C10" s="173">
         <f ca="1">Statement!AC148</f>
-        <v>4.942634169940316</v>
+        <v>4.7103207395395756</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -36512,7 +36554,7 @@
       </c>
       <c r="C11" s="173">
         <f ca="1">Statement!AC151</f>
-        <v>5.2821833149636417</v>
+        <v>4.9757611427752968</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -36521,7 +36563,7 @@
       </c>
       <c r="C12" s="173">
         <f ca="1">Statement!AC152</f>
-        <v>38.502151446669004</v>
+        <v>36.26862182894611</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
@@ -36757,7 +36799,7 @@
       </c>
       <c r="C38" s="174">
         <f ca="1">Statement!AC158</f>
-        <v>2.1087738637179197E-2</v>
+        <v>2.2127787749137588E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>274</v>
@@ -36773,7 +36815,7 @@
       </c>
       <c r="C39" s="214">
         <f ca="1">Statement!AC157</f>
-        <v>3.386888077961861E-2</v>
+        <v>3.5539296938692309E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>276</v>
@@ -36805,7 +36847,7 @@
       </c>
       <c r="C41" s="174">
         <f ca="1">Statement!AC160</f>
-        <v>9.3243244557542678E-3</v>
+        <v>9.7842009525504342E-3</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -36814,7 +36856,7 @@
       </c>
       <c r="C42" s="174">
         <f ca="1">Statement!AC161</f>
-        <v>9.3243244557542678E-3</v>
+        <v>9.7842009525504342E-3</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
@@ -36858,7 +36900,7 @@
       </c>
       <c r="F48" s="174">
         <f ca="1">Statement!AC172</f>
-        <v>0.18976848306421862</v>
+        <v>0.19912788122845121</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
@@ -37037,7 +37079,7 @@
       </c>
       <c r="I6" s="171">
         <f ca="1">Statement!AC116</f>
-        <v>148.93</v>
+        <v>141.93</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -37066,7 +37108,7 @@
       </c>
       <c r="I7" s="172">
         <f ca="1">Statement!AC149</f>
-        <v>7464669.46</v>
+        <v>7113815.46</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -37095,7 +37137,7 @@
       </c>
       <c r="I8" s="172">
         <f ca="1">Statement!AC150</f>
-        <v>6048110.46</v>
+        <v>5697256.46</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -37124,7 +37166,7 @@
       </c>
       <c r="I9" s="173">
         <f ca="1">Statement!AC146</f>
-        <v>47.420921569889352</v>
+        <v>45.192045916970358</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -37153,7 +37195,7 @@
       </c>
       <c r="I10" s="173">
         <f ca="1">Statement!AC147</f>
-        <v>6.3957203633350312</v>
+        <v>6.0951090523611153</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -37182,7 +37224,7 @@
       </c>
       <c r="I11" s="173">
         <f ca="1">Statement!AC148</f>
-        <v>4.942634169940316</v>
+        <v>4.7103207395395756</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -37211,7 +37253,7 @@
       </c>
       <c r="I12" s="173">
         <f ca="1">Statement!AC151</f>
-        <v>5.2821833149636417</v>
+        <v>4.9757611427752968</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -37240,7 +37282,7 @@
       </c>
       <c r="I13" s="173">
         <f ca="1">Statement!AC152</f>
-        <v>38.502151446669004</v>
+        <v>36.26862182894611</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -38013,7 +38055,7 @@
       </c>
       <c r="I51" s="174">
         <f ca="1">Statement!AC158</f>
-        <v>2.1087738637179197E-2</v>
+        <v>2.2127787749137588E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -38042,7 +38084,7 @@
       </c>
       <c r="I52" s="174">
         <f ca="1">Statement!AC157</f>
-        <v>3.386888077961861E-2</v>
+        <v>3.5539296938692309E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -38100,7 +38142,7 @@
       </c>
       <c r="I54" s="174">
         <f ca="1">Statement!AC160</f>
-        <v>9.3243244557542678E-3</v>
+        <v>9.7842009525504342E-3</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -38129,7 +38171,7 @@
       </c>
       <c r="I55" s="174">
         <f ca="1">Statement!AC161</f>
-        <v>9.3243244557542678E-3</v>
+        <v>9.7842009525504342E-3</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -38365,7 +38407,7 @@
       </c>
       <c r="I68" s="195">
         <f ca="1">Statement!AC172</f>
-        <v>0.18976848306421862</v>
+        <v>0.19912788122845121</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -38908,14 +38950,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="263" t="s">
+      <c r="C3" s="265" t="s">
         <v>317</v>
       </c>
-      <c r="D3" s="264"/>
-      <c r="F3" s="265" t="s">
+      <c r="D3" s="266"/>
+      <c r="F3" s="267" t="s">
         <v>318</v>
       </c>
-      <c r="G3" s="264"/>
+      <c r="G3" s="266"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -38982,19 +39024,19 @@
       <c r="B7" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C7" s="266">
+      <c r="C7" s="263">
         <f>Statement!AA89</f>
         <v>2.2218264392893719E-2</v>
       </c>
-      <c r="D7" s="267"/>
-      <c r="F7" s="266">
+      <c r="D7" s="264"/>
+      <c r="F7" s="263">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.18309713991239371</v>
       </c>
-      <c r="G7" s="267"/>
+      <c r="G7" s="264"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="206" t="s">
@@ -39021,19 +39063,19 @@
       <c r="B9" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C9" s="266">
+      <c r="C9" s="263">
         <f>Statement!AA90</f>
         <v>3.6046202026093238E-2</v>
       </c>
-      <c r="D9" s="267"/>
-      <c r="F9" s="266">
+      <c r="D9" s="264"/>
+      <c r="F9" s="263">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.17263647322197348</v>
       </c>
-      <c r="G9" s="267"/>
+      <c r="G9" s="264"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="206" t="s">
@@ -39060,19 +39102,19 @@
       <c r="B11" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C11" s="266">
+      <c r="C11" s="263">
         <f>Statement!AA91</f>
         <v>1.710027405488606E-2</v>
       </c>
-      <c r="D11" s="267"/>
-      <c r="F11" s="266">
+      <c r="D11" s="264"/>
+      <c r="F11" s="263">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>0.1870895657269924</v>
       </c>
-      <c r="G11" s="267"/>
+      <c r="G11" s="264"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="206" t="s">
@@ -39099,19 +39141,19 @@
       <c r="B13" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C13" s="266">
+      <c r="C13" s="263">
         <f>Statement!AA95</f>
         <v>8.4392741251357012E-2</v>
       </c>
-      <c r="D13" s="267"/>
-      <c r="F13" s="266">
+      <c r="D13" s="264"/>
+      <c r="F13" s="263">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.22501976973287405</v>
       </c>
-      <c r="G13" s="267"/>
+      <c r="G13" s="264"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="206" t="s">
@@ -39138,19 +39180,19 @@
       <c r="B15" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C15" s="266">
+      <c r="C15" s="263">
         <f>Statement!AA96</f>
         <v>-0.23765355851505829</v>
       </c>
-      <c r="D15" s="267"/>
-      <c r="F15" s="266">
+      <c r="D15" s="264"/>
+      <c r="F15" s="263">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>1.7444474417768186E-2</v>
       </c>
-      <c r="G15" s="267"/>
+      <c r="G15" s="264"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="206" t="s">
@@ -39177,19 +39219,19 @@
       <c r="B17" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C17" s="266">
+      <c r="C17" s="263">
         <f>Statement!AA98</f>
         <v>-0.23704555913483663</v>
       </c>
-      <c r="D17" s="267"/>
-      <c r="F17" s="266">
+      <c r="D17" s="264"/>
+      <c r="F17" s="263">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>-0.25955204216073779</v>
       </c>
-      <c r="G17" s="267"/>
+      <c r="G17" s="264"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="206" t="s">
@@ -39216,22 +39258,22 @@
       <c r="B19" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C19" s="266">
+      <c r="C19" s="263">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>2.5565842762241744E-2</v>
       </c>
-      <c r="D19" s="267"/>
-      <c r="F19" s="266">
+      <c r="D19" s="264"/>
+      <c r="F19" s="263">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>2.5293753865182372E-2</v>
       </c>
-      <c r="G19" s="267"/>
+      <c r="G19" s="264"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="206" t="s">
@@ -39258,22 +39300,22 @@
       <c r="B21" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C21" s="266">
+      <c r="C21" s="263">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>-0.2584269662921348</v>
       </c>
-      <c r="D21" s="267"/>
-      <c r="F21" s="266">
+      <c r="D21" s="264"/>
+      <c r="F21" s="263">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>-0.27472527472527469</v>
       </c>
-      <c r="G21" s="267"/>
+      <c r="G21" s="264"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -39322,22 +39364,22 @@
       <c r="B25" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C25" s="266">
+      <c r="C25" s="263">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>2.840483364420425E-2</v>
       </c>
-      <c r="D25" s="267"/>
-      <c r="F25" s="266">
+      <c r="D25" s="264"/>
+      <c r="F25" s="263">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>0.22478379327694395</v>
       </c>
-      <c r="G25" s="267"/>
+      <c r="G25" s="264"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="str">
@@ -39365,22 +39407,22 @@
       <c r="B27" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C27" s="266">
+      <c r="C27" s="263">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>2.1247695740758708E-2</v>
       </c>
-      <c r="D27" s="267"/>
-      <c r="F27" s="266">
+      <c r="D27" s="264"/>
+      <c r="F27" s="263">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>2.1792942775323981E-2</v>
       </c>
-      <c r="G27" s="267"/>
+      <c r="G27" s="264"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="str">
@@ -39408,22 +39450,22 @@
       <c r="B29" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C29" s="266">
+      <c r="C29" s="263">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>-0.10674206945303526</v>
       </c>
-      <c r="D29" s="267"/>
-      <c r="F29" s="266">
+      <c r="D29" s="264"/>
+      <c r="F29" s="263">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>2.0816812053925456E-3</v>
       </c>
-      <c r="G29" s="267"/>
+      <c r="G29" s="264"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="str">
@@ -39451,22 +39493,22 @@
       <c r="B31" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C31" s="266">
+      <c r="C31" s="263">
         <f>IF(C30=0,
 IF(D30=0,0,IF(D30&gt;0,1,-1)),
 (D30-C30)/ABS(C30)
 )</f>
         <v>-5.2569263556713236E-2</v>
       </c>
-      <c r="D31" s="267"/>
-      <c r="F31" s="266">
+      <c r="D31" s="264"/>
+      <c r="F31" s="263">
         <f>IF(F30=0,
 IF(G30=0,0,IF(G30&gt;0,1,-1)),
 (G30-F30)/ABS(F30)
 )</f>
         <v>-0.22983638113570742</v>
       </c>
-      <c r="G31" s="267"/>
+      <c r="G31" s="264"/>
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B32" s="20" t="str">
@@ -39494,22 +39536,22 @@
       <c r="B33" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C33" s="266">
+      <c r="C33" s="263">
         <f>IF(C32=0,
 IF(D32=0,0,IF(D32&gt;0,1,-1)),
 (D32-C32)/ABS(C32)
 )</f>
         <v>0.84164222873900296</v>
       </c>
-      <c r="D33" s="267"/>
-      <c r="F33" s="266">
+      <c r="D33" s="264"/>
+      <c r="F33" s="263">
         <f>IF(F32=0,
 IF(G32=0,0,IF(G32&gt;0,1,-1)),
 (G32-F32)/ABS(F32)
 )</f>
         <v>1.482213438735178</v>
       </c>
-      <c r="G33" s="267"/>
+      <c r="G33" s="264"/>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B35" s="8" t="s">
@@ -39558,22 +39600,22 @@
       <c r="B37" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C37" s="266">
+      <c r="C37" s="263">
         <f>IF(C36=0,
 IF(D36=0,0,IF(D36&gt;0,1,-1)),
 (D36-C36)/ABS(C36)
 )</f>
         <v>3.8938053097345132E-2</v>
       </c>
-      <c r="D37" s="267"/>
-      <c r="F37" s="266">
+      <c r="D37" s="264"/>
+      <c r="F37" s="263">
         <f>IF(F36=0,
 IF(G36=0,0,IF(G36&gt;0,1,-1)),
 (G36-F36)/ABS(F36)
 )</f>
         <v>0.23060796645702306</v>
       </c>
-      <c r="G37" s="267"/>
+      <c r="G37" s="264"/>
     </row>
     <row r="38" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="str">
@@ -39601,22 +39643,22 @@
       <c r="B39" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C39" s="266">
+      <c r="C39" s="263">
         <f>IF(C38=0,
 IF(D38=0,0,IF(D38&gt;0,1,-1)),
 (D38-C38)/ABS(C38)
 )</f>
         <v>2.0319303338171262E-2</v>
       </c>
-      <c r="D39" s="267"/>
-      <c r="F39" s="266">
+      <c r="D39" s="264"/>
+      <c r="F39" s="263">
         <f>IF(F38=0,
 IF(G38=0,0,IF(G38&gt;0,1,-1)),
 (G38-F38)/ABS(F38)
 )</f>
         <v>9.5869056897895558E-2</v>
       </c>
-      <c r="G39" s="267"/>
+      <c r="G39" s="264"/>
     </row>
     <row r="40" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B40" s="20" t="str">
@@ -39644,22 +39686,22 @@
       <c r="B41" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C41" s="266">
+      <c r="C41" s="263">
         <f>IF(C40=0,
 IF(D40=0,0,IF(D40&gt;0,1,-1)),
 (D40-C40)/ABS(C40)
 )</f>
         <v>1.6E-2</v>
       </c>
-      <c r="D41" s="267"/>
-      <c r="F41" s="266">
+      <c r="D41" s="264"/>
+      <c r="F41" s="263">
         <f>IF(F40=0,
 IF(G40=0,0,IF(G40&gt;0,1,-1)),
 (G40-F40)/ABS(F40)
 )</f>
         <v>0.16513761467889909</v>
       </c>
-      <c r="G41" s="267"/>
+      <c r="G41" s="264"/>
     </row>
     <row r="42" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B42" s="20" t="str">
@@ -39687,22 +39729,22 @@
       <c r="B43" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C43" s="266">
+      <c r="C43" s="263">
         <f>IF(C42=0,
 IF(D42=0,0,IF(D42&gt;0,1,-1)),
 (D42-C42)/ABS(C42)
 )</f>
         <v>2.0750199521149242E-2</v>
       </c>
-      <c r="D43" s="267"/>
-      <c r="F43" s="266">
+      <c r="D43" s="264"/>
+      <c r="F43" s="263">
         <f>IF(F42=0,
 IF(G42=0,0,IF(G42&gt;0,1,-1)),
 (G42-F42)/ABS(F42)
 )</f>
         <v>8.9437819420783646E-2</v>
       </c>
-      <c r="G43" s="267"/>
+      <c r="G43" s="264"/>
     </row>
     <row r="44" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B44" s="20" t="str">
@@ -39730,22 +39772,22 @@
       <c r="B45" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C45" s="266">
+      <c r="C45" s="263">
         <f>IF(C44=0,
 IF(D44=0,0,IF(D44&gt;0,1,-1)),
 (D44-C44)/ABS(C44)
 )</f>
         <v>1.2209481933271921E-2</v>
       </c>
-      <c r="D45" s="267"/>
-      <c r="F45" s="266">
+      <c r="D45" s="264"/>
+      <c r="F45" s="263">
         <f>IF(F44=0,
 IF(G44=0,0,IF(G44&gt;0,1,-1)),
 (G44-F44)/ABS(F44)
 )</f>
         <v>5.119238950540856E-2</v>
       </c>
-      <c r="G45" s="267"/>
+      <c r="G45" s="264"/>
     </row>
     <row r="46" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="str">
@@ -39773,22 +39815,22 @@
       <c r="B47" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C47" s="266">
+      <c r="C47" s="263">
         <f>IF(C46=0,
 IF(D46=0,0,IF(D46&gt;0,1,-1)),
 (D46-C46)/ABS(C46)
 )</f>
         <v>1.8247963846473435E-2</v>
       </c>
-      <c r="D47" s="267"/>
-      <c r="F47" s="266">
+      <c r="D47" s="264"/>
+      <c r="F47" s="263">
         <f>IF(F46=0,
 IF(G46=0,0,IF(G46&gt;0,1,-1)),
 (G46-F46)/ABS(F46)
 )</f>
         <v>0.1229516507570132</v>
       </c>
-      <c r="G47" s="267"/>
+      <c r="G47" s="264"/>
     </row>
     <row r="48" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B48" s="20" t="str">
@@ -39816,22 +39858,22 @@
       <c r="B49" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C49" s="266">
+      <c r="C49" s="263">
         <f>IF(C48=0,
 IF(D48=0,0,IF(D48&gt;0,1,-1)),
 (D48-C48)/ABS(C48)
 )</f>
         <v>-4.2332859174963834E-3</v>
       </c>
-      <c r="D49" s="267"/>
-      <c r="F49" s="266">
+      <c r="D49" s="264"/>
+      <c r="F49" s="263">
         <f>IF(F48=0,
 IF(G48=0,0,IF(G48&gt;0,1,-1)),
 (G48-F48)/ABS(F48)
 )</f>
         <v>6.3208790635154666E-2</v>
       </c>
-      <c r="G49" s="267"/>
+      <c r="G49" s="264"/>
     </row>
     <row r="50" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B50" s="20" t="str">
@@ -39859,22 +39901,22 @@
       <c r="B51" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C51" s="266">
+      <c r="C51" s="263">
         <f>IF(C50=0,
 IF(D50=0,0,IF(D50&gt;0,1,-1)),
 (D50-C50)/ABS(C50)
 )</f>
         <v>4.8738292663854846E-4</v>
       </c>
-      <c r="D51" s="267"/>
-      <c r="F51" s="266">
+      <c r="D51" s="264"/>
+      <c r="F51" s="263">
         <f>IF(F50=0,
 IF(G50=0,0,IF(G50&gt;0,1,-1)),
 (G50-F50)/ABS(F50)
 )</f>
         <v>-6.2091544317255373E-2</v>
       </c>
-      <c r="G51" s="267"/>
+      <c r="G51" s="264"/>
     </row>
     <row r="52" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="str">
@@ -39902,39 +39944,43 @@
       <c r="B53" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C53" s="266">
+      <c r="C53" s="263">
         <f>IF(C52=0,
 IF(D52=0,0,IF(D52&gt;0,1,-1)),
 (D52-C52)/ABS(C52)
 )</f>
         <v>-8.8077740902117604E-2</v>
       </c>
-      <c r="D53" s="267"/>
-      <c r="F53" s="266">
+      <c r="D53" s="264"/>
+      <c r="F53" s="263">
         <f>IF(F52=0,
 IF(G52=0,0,IF(G52&gt;0,1,-1)),
 (G52-F52)/ABS(F52)
 )</f>
         <v>-0.37416005758387127</v>
       </c>
-      <c r="G53" s="267"/>
+      <c r="G53" s="264"/>
     </row>
   </sheetData>
   <mergeCells count="46">
-    <mergeCell ref="C53:D53"/>
-    <mergeCell ref="F53:G53"/>
-    <mergeCell ref="C47:D47"/>
-    <mergeCell ref="F47:G47"/>
-    <mergeCell ref="C49:D49"/>
-    <mergeCell ref="F49:G49"/>
-    <mergeCell ref="C51:D51"/>
-    <mergeCell ref="F51:G51"/>
-    <mergeCell ref="C41:D41"/>
-    <mergeCell ref="F41:G41"/>
-    <mergeCell ref="C43:D43"/>
-    <mergeCell ref="F43:G43"/>
-    <mergeCell ref="C45:D45"/>
-    <mergeCell ref="F45:G45"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
     <mergeCell ref="C37:D37"/>
     <mergeCell ref="F37:G37"/>
     <mergeCell ref="C39:D39"/>
@@ -39949,24 +39995,20 @@
     <mergeCell ref="F31:G31"/>
     <mergeCell ref="C33:D33"/>
     <mergeCell ref="F33:G33"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="F41:G41"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="F43:G43"/>
+    <mergeCell ref="C45:D45"/>
+    <mergeCell ref="F45:G45"/>
+    <mergeCell ref="C53:D53"/>
+    <mergeCell ref="F53:G53"/>
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="F47:G47"/>
+    <mergeCell ref="C49:D49"/>
+    <mergeCell ref="F49:G49"/>
+    <mergeCell ref="C51:D51"/>
+    <mergeCell ref="F51:G51"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/DUOL.xlsx
+++ b/DUOL.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11020"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F261F7F-F31F-E947-933B-8B409F2DDE2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40EBE32F-47B2-BA4A-A0A8-72332994F270}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -119,7 +119,7 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="5">
+  <futureMetadata name="XLRICHVALUE" count="2">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -130,28 +130,7 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="3"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="4"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="5"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="8"/>
         </ext>
       </extLst>
     </bk>
@@ -161,21 +140,12 @@
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="5">
+  <valueMetadata count="2">
     <bk>
       <rc t="2" v="0"/>
     </bk>
     <bk>
       <rc t="2" v="1"/>
-    </bk>
-    <bk>
-      <rc t="2" v="2"/>
-    </bk>
-    <bk>
-      <rc t="2" v="3"/>
-    </bk>
-    <bk>
-      <rc t="2" v="4"/>
     </bk>
   </valueMetadata>
 </metadata>
@@ -2483,6 +2453,9 @@
     <xf numFmtId="0" fontId="24" fillId="8" borderId="26" xfId="2" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="168" fontId="0" fillId="17" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="27" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2495,12 +2468,6 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2510,10 +2477,10 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2525,11 +2492,14 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2537,9 +2507,9 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="17" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="27" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -13216,7 +13186,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="9">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="6">
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=c2mtim&amp;q=XNAS%3aDUOL&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
@@ -13233,11 +13203,13 @@
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>328.53</v>
+    <v>322.08999999999997</v>
     <v>87.89</v>
-    <v>1.0656000000000001</v>
-    <v>-0.18</v>
-    <v>-1.2670000000000001E-3</v>
+    <v>1.0660000000000001</v>
+    <v>1.65</v>
+    <v>1.167E-2</v>
+    <v>-0.35</v>
+    <v>-2.447E-3</v>
     <v>USD</v>
     <v>Duolingo, Inc. is a technology company. The Company is engaged in offering a mobile learning platform, as well as a digital English language proficiency assessment exam. It operates a freemium business model, namely, the app and the Website are accessible free of charge, although Duolingo also offers premium services for a subscription fee. Its solutions consist of the Duolingo App, Super Duolingo, Duolingo Max, Duolingo English Test: AI-Driven Language Assessment, Duolingo for Schools, and Duolingo ABC. The Duolingo App offers courses in over 40 different languages, including Spanish, English, French, German, Italian, Portuguese, Japanese and Chinese. Duolingo can also be accessed on desktop computers via a Web browser. Its subscription offering, Super Duolingo, offers learners additional features to enhance their learning experience. The Duolingo English Test is an online, on-demand, high-stakes English proficiency assessment. It also operates an animation and motion design studio.</v>
     <v>900</v>
@@ -13245,49 +13217,35 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>5900 PENN AVE, SECOND FLOOR, PITTSBURGH, PA, 15206 US</v>
-    <v>143.33000000000001</v>
+    <v>146</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46315.717072221873</v>
+    <v>46318.946449560157</v>
     <v>0</v>
-    <v>139.6</v>
-    <v>6640375301</v>
+    <v>137.86000000000001</v>
+    <v>6692308060</v>
     <v>DUOLINGO, INC.</v>
     <v>DUOLINGO, INC.</v>
-    <v>141.97999999999999</v>
-    <v>16.9176</v>
-    <v>142.11000000000001</v>
-    <v>141.93</v>
+    <v>139.5</v>
+    <v>16.853200000000001</v>
+    <v>141.38999999999999</v>
+    <v>143.04</v>
+    <v>142.69</v>
     <v>46786270</v>
     <v>DUOL</v>
     <v>DUOLINGO, INC. (XNAS:DUOL)</v>
-    <v>190895</v>
-    <v>969450</v>
+    <v>763587</v>
+    <v>930380</v>
     <v>2011</v>
   </rv>
   <rv s="2">
     <v>1</v>
   </rv>
-  <rv s="3">
-    <v>12</v>
-    <v>Price (Extended hours)</v>
-    <v>0</v>
-  </rv>
-  <rv s="3">
-    <v>12</v>
-    <v>Change (extended hours)</v>
-    <v>0</v>
-  </rv>
-  <rv s="3">
-    <v>12</v>
-    <v>Change % (extended hours)</v>
-    <v>0</v>
-  </rv>
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a33knm&amp;q=10+Y+TSY+YLD+NDX&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="4">
+  <rv s="3">
     <v>5</v>
     <v>10 Y TSY YLD NDX</v>
     <v>6</v>
@@ -13301,28 +13259,28 @@
     <v>Powered by Refinitiv</v>
     <v>53.64</v>
     <v>39.47</v>
-    <v>0.38</v>
-    <v>7.4539999999999997E-3</v>
+    <v>-1.93</v>
+    <v>-3.7505000000000004E-2</v>
     <v>US</v>
-    <v>51.5</v>
+    <v>50.54</v>
     <v>Index</v>
-    <v>6</v>
-    <v>50.9</v>
+    <v>3</v>
+    <v>49.39</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>50.9</v>
-    <v>50.98</v>
-    <v>51.36</v>
+    <v>50.4</v>
+    <v>51.46</v>
+    <v>49.53</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
   <rv s="2">
-    <v>7</v>
+    <v>4</v>
   </rv>
 </rvData>
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="5">
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="4">
   <s t="_hyperlink">
     <k n="Address" t="s"/>
     <k n="Text" t="s"/>
@@ -13344,6 +13302,8 @@
     <k n="Beta"/>
     <k n="Change"/>
     <k n="Change (%)"/>
+    <k n="Change (Extended hours)"/>
+    <k n="Change % (Extended hours)"/>
     <k n="Currency" t="s"/>
     <k n="Description" t="s"/>
     <k n="Employees"/>
@@ -13364,6 +13324,7 @@
     <k n="P/E"/>
     <k n="Previous close"/>
     <k n="Price"/>
+    <k n="Price (Extended hours)"/>
     <k n="Shares outstanding"/>
     <k n="Ticker symbol" t="s"/>
     <k n="UniqueName" t="s"/>
@@ -13373,11 +13334,6 @@
   </s>
   <s t="_linkedentity">
     <k n="%cvi" t="r"/>
-  </s>
-  <s t="_error">
-    <k n="errorType" t="i"/>
-    <k n="field" t="s"/>
-    <k n="subType" t="i"/>
   </s>
   <s t="_linkedentitycore">
     <k n="_Display" t="spb"/>
@@ -13413,7 +13369,7 @@
 <file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
 <supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
   <spbArrays count="2">
-    <a count="42">
+    <a count="45">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%IsRefreshable</v>
@@ -13424,13 +13380,16 @@
       <v t="s">Name</v>
       <v t="s">_SubLabel</v>
       <v t="s">Price</v>
+      <v t="s">Price (Extended hours)</v>
       <v t="s">Exchange</v>
       <v t="s">Official name</v>
       <v t="s">Last trade time</v>
       <v t="s">Ticker symbol</v>
       <v t="s">Exchange abbreviation</v>
       <v t="s">Change</v>
+      <v t="s">Change (Extended hours)</v>
       <v t="s">Change (%)</v>
+      <v t="s">Change % (Extended hours)</v>
       <v t="s">Currency</v>
       <v t="s">Previous close</v>
       <v t="s">Open</v>
@@ -13524,13 +13483,19 @@
       <v>8</v>
       <v>9</v>
       <v>4</v>
+      <v>1</v>
+      <v>1</v>
+      <v>5</v>
     </spb>
     <spb s="4">
-      <v>Real-Time Nasdaq Last Sale</v>
+      <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
       <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
+      <v>Real-Time Nasdaq Last Sale</v>
+      <v>from close</v>
+      <v>from close</v>
     </spb>
     <spb s="0">
       <v>1</v>
@@ -13602,6 +13567,9 @@
     <k n="Year incorporated" t="i"/>
     <k n="`%EntityServiceId" t="i"/>
     <k n="Shares outstanding" t="i"/>
+    <k n="Price (Extended hours)" t="i"/>
+    <k n="Change (Extended hours)" t="i"/>
+    <k n="Change % (Extended hours)" t="i"/>
   </s>
   <s>
     <k n="Price" t="s"/>
@@ -13609,6 +13577,9 @@
     <k n="Change (%)" t="s"/>
     <k n="ExchangeID" t="s"/>
     <k n="Last trade time" t="s"/>
+    <k n="Price (Extended hours)" t="s"/>
+    <k n="Change (Extended hours)" t="s"/>
+    <k n="Change % (Extended hours)" t="s"/>
   </s>
   <s>
     <k n="UniqueName" t="spb"/>
@@ -14095,18 +14066,18 @@
   <sheetData>
     <row r="1" spans="2:11" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B2" s="259" t="s">
+      <c r="B2" s="262" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="260"/>
-      <c r="E2" s="259" t="s">
+      <c r="C2" s="263"/>
+      <c r="E2" s="262" t="s">
         <v>291</v>
       </c>
-      <c r="F2" s="260"/>
-      <c r="H2" s="259" t="s">
+      <c r="F2" s="263"/>
+      <c r="H2" s="262" t="s">
         <v>330</v>
       </c>
-      <c r="I2" s="260"/>
+      <c r="I2" s="263"/>
       <c r="K2" s="134" t="s">
         <v>440</v>
       </c>
@@ -14124,7 +14095,7 @@
       </c>
       <c r="F3" s="186">
         <f ca="1">Statement!AC149</f>
-        <v>7113815.46</v>
+        <v>7169450.8799999999</v>
       </c>
       <c r="H3" s="184" t="str">
         <f>'AVG target price'!B5</f>
@@ -14132,7 +14103,7 @@
       </c>
       <c r="I3" s="210">
         <f ca="1">'AVG target price'!C5</f>
-        <v>144.11714547052802</v>
+        <v>147.17410015769124</v>
       </c>
       <c r="K3" s="257" t="s">
         <v>441</v>
@@ -14151,7 +14122,7 @@
       </c>
       <c r="F4" s="187">
         <f ca="1">Statement!AC150</f>
-        <v>5697256.46</v>
+        <v>5752891.8799999999</v>
       </c>
       <c r="H4" s="184" t="str">
         <f>'AVG target price'!B6</f>
@@ -14159,7 +14130,7 @@
       </c>
       <c r="I4" s="210">
         <f ca="1">'AVG target price'!C6</f>
-        <v>196.69460806261617</v>
+        <v>198.02442476307402</v>
       </c>
       <c r="K4" s="257" t="s">
         <v>442</v>
@@ -14171,7 +14142,7 @@
       </c>
       <c r="C5" s="207" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>141.93</v>
+        <v>143.04</v>
       </c>
       <c r="E5" s="184" t="s">
         <v>247</v>
@@ -14186,7 +14157,7 @@
       </c>
       <c r="I5" s="210">
         <f ca="1">'AVG target price'!C7</f>
-        <v>158.43352867962039</v>
+        <v>159.74574315816156</v>
       </c>
       <c r="K5" s="257" t="s">
         <v>443</v>
@@ -14196,16 +14167,16 @@
       <c r="B6" s="184" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="207" t="e" cm="1" vm="2">
-        <f t="array" ref="C6">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C6" s="207" cm="1">
+        <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
+        <v>142.69</v>
       </c>
       <c r="E6" s="184" t="s">
         <v>241</v>
       </c>
       <c r="F6" s="189">
         <f ca="1">Statement!AC146</f>
-        <v>45.192045916970358</v>
+        <v>45.54548191336179</v>
       </c>
       <c r="H6" s="184" t="str">
         <f>'AVG target price'!B8</f>
@@ -14213,7 +14184,7 @@
       </c>
       <c r="I6" s="210">
         <f ca="1">'AVG target price'!C8</f>
-        <v>202.17620452455026</v>
+        <v>203.55142215941146</v>
       </c>
       <c r="K6" s="258" t="s">
         <v>444</v>
@@ -14225,14 +14196,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>-0.18</v>
+        <v>1.65</v>
       </c>
       <c r="E7" s="185" t="s">
         <v>205</v>
       </c>
       <c r="F7" s="190">
         <f ca="1">Statement!AC147</f>
-        <v>6.0951090523611153</v>
+        <v>6.1427774173869789</v>
       </c>
       <c r="H7" s="184" t="str">
         <f>'AVG target price'!B9</f>
@@ -14240,23 +14211,23 @@
       </c>
       <c r="I7" s="210">
         <f ca="1">'AVG target price'!C9</f>
-        <v>202.59511594919471</v>
+        <v>203.97380318825662</v>
       </c>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B8" s="184" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="6" t="e" cm="1" vm="3">
-        <f t="array" ref="C8">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C8" s="6" cm="1">
+        <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
+        <v>-0.35</v>
       </c>
       <c r="E8" s="184" t="s">
         <v>269</v>
       </c>
       <c r="F8" s="191">
         <f ca="1">Statement!AC157</f>
-        <v>3.5539296938692309E-2</v>
+        <v>3.5263509609260342E-2</v>
       </c>
       <c r="H8" s="183" t="str">
         <f>'AVG target price'!B10</f>
@@ -14264,7 +14235,7 @@
       </c>
       <c r="I8" s="211">
         <f ca="1">'AVG target price'!C10</f>
-        <v>180.80332053730189</v>
+        <v>182.49389868531898</v>
       </c>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.2">
@@ -14273,14 +14244,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>-1.2670000000000001E-3</v>
+        <v>1.167E-2</v>
       </c>
       <c r="E9" s="184" t="s">
         <v>292</v>
       </c>
       <c r="F9" s="191">
         <f ca="1">Statement!AC158</f>
-        <v>2.2127787749137588E-2</v>
+        <v>2.1956074631117855E-2</v>
       </c>
       <c r="H9" s="183" t="str">
         <f>'AVG target price'!B12</f>
@@ -14288,23 +14259,23 @@
       </c>
       <c r="I9" s="212">
         <f ca="1">'AVG target price'!C12</f>
-        <v>0.27389079502079811</v>
+        <v>0.27582423577544041</v>
       </c>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B10" s="184" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="73" t="e" cm="1" vm="4">
-        <f t="array" ref="C10">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C10" s="73" cm="1">
+        <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
+        <v>-2.447E-3</v>
       </c>
       <c r="E10" s="184" t="s">
         <v>297</v>
       </c>
       <c r="F10" s="191">
         <f ca="1">Statement!AC160</f>
-        <v>9.7842009525504342E-3</v>
+        <v>9.7082748965008608E-3</v>
       </c>
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.2">
@@ -14313,7 +14284,7 @@
       </c>
       <c r="C11" s="208" cm="1">
         <f t="array" aca="1" ref="C11" ca="1">_FV(C3,"52 week high",TRUE)</f>
-        <v>328.53</v>
+        <v>322.08999999999997</v>
       </c>
       <c r="E11" s="185" t="s">
         <v>293</v>
@@ -14352,7 +14323,7 @@
       </c>
       <c r="C13" s="208" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>1.0656000000000001</v>
+        <v>1.0660000000000001</v>
       </c>
       <c r="E13" s="184" t="s">
         <v>104</v>
@@ -14361,10 +14332,10 @@
         <f>Statement!AC125</f>
         <v>0.10928737315054812</v>
       </c>
-      <c r="H13" s="279" t="s">
+      <c r="H13" s="261" t="s">
         <v>437</v>
       </c>
-      <c r="I13" s="277">
+      <c r="I13" s="259">
         <f>'Reverse DCF'!C17</f>
         <v>0.28999999999999998</v>
       </c>
@@ -14375,7 +14346,7 @@
       </c>
       <c r="C14" s="209" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>969450</v>
+        <v>930380</v>
       </c>
       <c r="E14" s="185" t="s">
         <v>105</v>
@@ -14387,9 +14358,9 @@
       <c r="H14" s="185" t="s">
         <v>446</v>
       </c>
-      <c r="I14" s="278">
+      <c r="I14" s="260">
         <f ca="1">'Reverse DCF'!C16</f>
-        <v>150.89124691191896</v>
+        <v>154.01937861223695</v>
       </c>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.2">
@@ -14398,7 +14369,7 @@
       </c>
       <c r="F15" s="191">
         <f ca="1">Statement!AC172</f>
-        <v>0.19912788122845121</v>
+        <v>0.19758263550583111</v>
       </c>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.2">
@@ -14409,16 +14380,16 @@
         <f>Statement!AC171</f>
         <v>30.277412046338647</v>
       </c>
-      <c r="H16" s="259" t="s">
+      <c r="H16" s="262" t="s">
         <v>438</v>
       </c>
-      <c r="I16" s="260"/>
+      <c r="I16" s="263"/>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="261" t="s">
+      <c r="B17" s="264" t="s">
         <v>90</v>
       </c>
-      <c r="C17" s="261"/>
+      <c r="C17" s="264"/>
       <c r="E17" s="183" t="s">
         <v>300</v>
       </c>
@@ -14431,7 +14402,7 @@
       </c>
       <c r="I17" s="255">
         <f ca="1">DCF!C15</f>
-        <v>9.9312000000000011E-2</v>
+        <v>9.7500000000000003E-2</v>
       </c>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.2">
@@ -14453,7 +14424,7 @@
       </c>
       <c r="I18" s="256">
         <f ca="1">Multiples!C54</f>
-        <v>9.9312000000000011E-2</v>
+        <v>9.7500000000000003E-2</v>
       </c>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
@@ -14505,14 +14476,14 @@
       <c r="I22" s="50"/>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="261" t="s">
+      <c r="B25" s="264" t="s">
         <v>107</v>
       </c>
-      <c r="C25" s="261"/>
-      <c r="E25" s="259" t="s">
+      <c r="C25" s="264"/>
+      <c r="E25" s="262" t="s">
         <v>343</v>
       </c>
-      <c r="F25" s="260"/>
+      <c r="F25" s="263"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="183" t="s">
@@ -14521,12 +14492,12 @@
       <c r="C26" s="169">
         <v>0.21</v>
       </c>
-      <c r="E26" s="184" t="e" vm="5">
+      <c r="E26" s="184" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
       <c r="F26" s="218" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>51.36</v>
+        <v>49.53</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -14541,7 +14512,7 @@
       </c>
       <c r="F27" s="219">
         <f ca="1">F26/1000</f>
-        <v>5.1360000000000003E-2</v>
+        <v>4.9530000000000005E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -14863,36 +14834,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="262" t="s">
+      <c r="C2" s="265" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="262"/>
-      <c r="E2" s="262"/>
-      <c r="F2" s="262"/>
-      <c r="G2" s="268"/>
-      <c r="H2" s="269" t="s">
+      <c r="D2" s="265"/>
+      <c r="E2" s="265"/>
+      <c r="F2" s="265"/>
+      <c r="G2" s="274"/>
+      <c r="H2" s="275" t="s">
         <v>114</v>
       </c>
-      <c r="I2" s="262"/>
-      <c r="J2" s="262"/>
-      <c r="K2" s="262"/>
-      <c r="L2" s="262"/>
+      <c r="I2" s="265"/>
+      <c r="J2" s="265"/>
+      <c r="K2" s="265"/>
+      <c r="L2" s="265"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="262" t="s">
+      <c r="S2" s="265" t="s">
         <v>113</v>
       </c>
-      <c r="T2" s="262"/>
-      <c r="U2" s="262"/>
-      <c r="V2" s="262"/>
-      <c r="W2" s="262"/>
-      <c r="X2" s="262"/>
-      <c r="Y2" s="262"/>
-      <c r="Z2" s="262"/>
-      <c r="AA2" s="262" t="s">
+      <c r="T2" s="265"/>
+      <c r="U2" s="265"/>
+      <c r="V2" s="265"/>
+      <c r="W2" s="265"/>
+      <c r="X2" s="265"/>
+      <c r="Y2" s="265"/>
+      <c r="Z2" s="265"/>
+      <c r="AA2" s="265" t="s">
         <v>114</v>
       </c>
-      <c r="AB2" s="262"/>
-      <c r="AC2" s="262"/>
+      <c r="AB2" s="265"/>
+      <c r="AC2" s="265"/>
       <c r="AE2" s="86" t="s">
         <v>85</v>
       </c>
@@ -14903,32 +14874,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="270" t="s">
+      <c r="C4" s="271" t="s">
         <v>116</v>
       </c>
-      <c r="D4" s="270"/>
-      <c r="E4" s="270"/>
-      <c r="F4" s="270"/>
-      <c r="G4" s="270"/>
-      <c r="H4" s="270"/>
-      <c r="I4" s="270"/>
-      <c r="J4" s="270"/>
-      <c r="K4" s="270"/>
-      <c r="L4" s="270"/>
+      <c r="D4" s="271"/>
+      <c r="E4" s="271"/>
+      <c r="F4" s="271"/>
+      <c r="G4" s="271"/>
+      <c r="H4" s="271"/>
+      <c r="I4" s="271"/>
+      <c r="J4" s="271"/>
+      <c r="K4" s="271"/>
+      <c r="L4" s="271"/>
       <c r="O4" s="5"/>
-      <c r="S4" s="271" t="s">
+      <c r="S4" s="272" t="s">
         <v>116</v>
       </c>
-      <c r="T4" s="272"/>
-      <c r="U4" s="272"/>
-      <c r="V4" s="272"/>
-      <c r="W4" s="272"/>
-      <c r="X4" s="272"/>
-      <c r="Y4" s="272"/>
-      <c r="Z4" s="272"/>
-      <c r="AA4" s="272"/>
-      <c r="AB4" s="272"/>
-      <c r="AC4" s="272"/>
+      <c r="T4" s="273"/>
+      <c r="U4" s="273"/>
+      <c r="V4" s="273"/>
+      <c r="W4" s="273"/>
+      <c r="X4" s="273"/>
+      <c r="Y4" s="273"/>
+      <c r="Z4" s="273"/>
+      <c r="AA4" s="273"/>
+      <c r="AB4" s="273"/>
+      <c r="AC4" s="273"/>
       <c r="AE4" s="88"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -15616,33 +15587,33 @@
       <c r="Q12" s="92"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="270" t="s">
+      <c r="C13" s="271" t="s">
         <v>122</v>
       </c>
-      <c r="D13" s="270"/>
-      <c r="E13" s="270"/>
-      <c r="F13" s="270"/>
-      <c r="G13" s="270"/>
-      <c r="H13" s="270"/>
-      <c r="I13" s="270"/>
-      <c r="J13" s="270"/>
-      <c r="K13" s="270"/>
-      <c r="L13" s="270"/>
+      <c r="D13" s="271"/>
+      <c r="E13" s="271"/>
+      <c r="F13" s="271"/>
+      <c r="G13" s="271"/>
+      <c r="H13" s="271"/>
+      <c r="I13" s="271"/>
+      <c r="J13" s="271"/>
+      <c r="K13" s="271"/>
+      <c r="L13" s="271"/>
       <c r="O13" s="5"/>
       <c r="Q13" s="92"/>
-      <c r="S13" s="271" t="s">
+      <c r="S13" s="272" t="s">
         <v>122</v>
       </c>
-      <c r="T13" s="272"/>
-      <c r="U13" s="272"/>
-      <c r="V13" s="272"/>
-      <c r="W13" s="272"/>
-      <c r="X13" s="272"/>
-      <c r="Y13" s="272"/>
-      <c r="Z13" s="272"/>
-      <c r="AA13" s="272"/>
-      <c r="AB13" s="272"/>
-      <c r="AC13" s="272"/>
+      <c r="T13" s="273"/>
+      <c r="U13" s="273"/>
+      <c r="V13" s="273"/>
+      <c r="W13" s="273"/>
+      <c r="X13" s="273"/>
+      <c r="Y13" s="273"/>
+      <c r="Z13" s="273"/>
+      <c r="AA13" s="273"/>
+      <c r="AB13" s="273"/>
+      <c r="AC13" s="273"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B14" s="16" t="s">
@@ -16251,33 +16222,33 @@
       <c r="Q22" s="92"/>
     </row>
     <row r="23" spans="2:31" x14ac:dyDescent="0.2">
-      <c r="C23" s="270" t="s">
+      <c r="C23" s="271" t="s">
         <v>124</v>
       </c>
-      <c r="D23" s="270"/>
-      <c r="E23" s="270"/>
-      <c r="F23" s="270"/>
-      <c r="G23" s="270"/>
-      <c r="H23" s="270"/>
-      <c r="I23" s="270"/>
-      <c r="J23" s="270"/>
-      <c r="K23" s="270"/>
-      <c r="L23" s="270"/>
+      <c r="D23" s="271"/>
+      <c r="E23" s="271"/>
+      <c r="F23" s="271"/>
+      <c r="G23" s="271"/>
+      <c r="H23" s="271"/>
+      <c r="I23" s="271"/>
+      <c r="J23" s="271"/>
+      <c r="K23" s="271"/>
+      <c r="L23" s="271"/>
       <c r="O23" s="5"/>
       <c r="Q23" s="92"/>
-      <c r="S23" s="271" t="s">
+      <c r="S23" s="272" t="s">
         <v>124</v>
       </c>
-      <c r="T23" s="272"/>
-      <c r="U23" s="272"/>
-      <c r="V23" s="272"/>
-      <c r="W23" s="272"/>
-      <c r="X23" s="272"/>
-      <c r="Y23" s="272"/>
-      <c r="Z23" s="272"/>
-      <c r="AA23" s="272"/>
-      <c r="AB23" s="272"/>
-      <c r="AC23" s="272"/>
+      <c r="T23" s="273"/>
+      <c r="U23" s="273"/>
+      <c r="V23" s="273"/>
+      <c r="W23" s="273"/>
+      <c r="X23" s="273"/>
+      <c r="Y23" s="273"/>
+      <c r="Z23" s="273"/>
+      <c r="AA23" s="273"/>
+      <c r="AB23" s="273"/>
+      <c r="AC23" s="273"/>
       <c r="AE23" s="88" t="str">
         <f>AE2</f>
         <v>TTM/YTD</v>
@@ -17596,32 +17567,32 @@
       <c r="O39" s="5"/>
     </row>
     <row r="40" spans="2:31" x14ac:dyDescent="0.2">
-      <c r="C40" s="270" t="s">
+      <c r="C40" s="271" t="s">
         <v>126</v>
       </c>
-      <c r="D40" s="270"/>
-      <c r="E40" s="270"/>
-      <c r="F40" s="270"/>
-      <c r="G40" s="270"/>
-      <c r="H40" s="270"/>
-      <c r="I40" s="270"/>
-      <c r="J40" s="270"/>
-      <c r="K40" s="270"/>
-      <c r="L40" s="270"/>
+      <c r="D40" s="271"/>
+      <c r="E40" s="271"/>
+      <c r="F40" s="271"/>
+      <c r="G40" s="271"/>
+      <c r="H40" s="271"/>
+      <c r="I40" s="271"/>
+      <c r="J40" s="271"/>
+      <c r="K40" s="271"/>
+      <c r="L40" s="271"/>
       <c r="O40" s="5"/>
-      <c r="S40" s="271" t="s">
+      <c r="S40" s="272" t="s">
         <v>126</v>
       </c>
-      <c r="T40" s="272"/>
-      <c r="U40" s="272"/>
-      <c r="V40" s="272"/>
-      <c r="W40" s="272"/>
-      <c r="X40" s="272"/>
-      <c r="Y40" s="272"/>
-      <c r="Z40" s="272"/>
-      <c r="AA40" s="272"/>
-      <c r="AB40" s="272"/>
-      <c r="AC40" s="272"/>
+      <c r="T40" s="273"/>
+      <c r="U40" s="273"/>
+      <c r="V40" s="273"/>
+      <c r="W40" s="273"/>
+      <c r="X40" s="273"/>
+      <c r="Y40" s="273"/>
+      <c r="Z40" s="273"/>
+      <c r="AA40" s="273"/>
+      <c r="AB40" s="273"/>
+      <c r="AC40" s="273"/>
     </row>
     <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -18188,18 +18159,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="S2:Z2"/>
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="S4:AC4"/>
     <mergeCell ref="C13:L13"/>
     <mergeCell ref="S13:AC13"/>
     <mergeCell ref="C23:L23"/>
     <mergeCell ref="S23:AC23"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="S40:AC40"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="S2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="S4:AC4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -18233,35 +18204,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="262" t="s">
+      <c r="C2" s="265" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="262"/>
-      <c r="E2" s="262"/>
-      <c r="F2" s="262"/>
-      <c r="G2" s="268"/>
-      <c r="H2" s="269" t="s">
+      <c r="D2" s="265"/>
+      <c r="E2" s="265"/>
+      <c r="F2" s="265"/>
+      <c r="G2" s="274"/>
+      <c r="H2" s="275" t="s">
         <v>114</v>
       </c>
-      <c r="I2" s="262"/>
-      <c r="J2" s="262"/>
-      <c r="K2" s="262"/>
-      <c r="L2" s="262"/>
-      <c r="P2" s="262" t="s">
+      <c r="I2" s="265"/>
+      <c r="J2" s="265"/>
+      <c r="K2" s="265"/>
+      <c r="L2" s="265"/>
+      <c r="P2" s="265" t="s">
         <v>113</v>
       </c>
-      <c r="Q2" s="262"/>
-      <c r="R2" s="262"/>
-      <c r="S2" s="262"/>
-      <c r="T2" s="262"/>
-      <c r="U2" s="262"/>
-      <c r="V2" s="262"/>
-      <c r="W2" s="262"/>
-      <c r="X2" s="262" t="s">
+      <c r="Q2" s="265"/>
+      <c r="R2" s="265"/>
+      <c r="S2" s="265"/>
+      <c r="T2" s="265"/>
+      <c r="U2" s="265"/>
+      <c r="V2" s="265"/>
+      <c r="W2" s="265"/>
+      <c r="X2" s="265" t="s">
         <v>114</v>
       </c>
-      <c r="Y2" s="262"/>
-      <c r="Z2" s="262"/>
+      <c r="Y2" s="265"/>
+      <c r="Z2" s="265"/>
       <c r="AB2" s="86" t="s">
         <v>115</v>
       </c>
@@ -18270,31 +18241,31 @@
     <row r="4" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="270" t="s">
+      <c r="C4" s="271" t="s">
         <v>116</v>
       </c>
-      <c r="D4" s="270"/>
-      <c r="E4" s="270"/>
-      <c r="F4" s="270"/>
-      <c r="G4" s="270"/>
-      <c r="H4" s="270"/>
-      <c r="I4" s="270"/>
-      <c r="J4" s="270"/>
-      <c r="K4" s="270"/>
-      <c r="L4" s="270"/>
-      <c r="P4" s="272" t="s">
+      <c r="D4" s="271"/>
+      <c r="E4" s="271"/>
+      <c r="F4" s="271"/>
+      <c r="G4" s="271"/>
+      <c r="H4" s="271"/>
+      <c r="I4" s="271"/>
+      <c r="J4" s="271"/>
+      <c r="K4" s="271"/>
+      <c r="L4" s="271"/>
+      <c r="P4" s="273" t="s">
         <v>116</v>
       </c>
-      <c r="Q4" s="272"/>
-      <c r="R4" s="272"/>
-      <c r="S4" s="272"/>
-      <c r="T4" s="272"/>
-      <c r="U4" s="272"/>
-      <c r="V4" s="272"/>
-      <c r="W4" s="272"/>
-      <c r="X4" s="272"/>
-      <c r="Y4" s="272"/>
-      <c r="Z4" s="272"/>
+      <c r="Q4" s="273"/>
+      <c r="R4" s="273"/>
+      <c r="S4" s="273"/>
+      <c r="T4" s="273"/>
+      <c r="U4" s="273"/>
+      <c r="V4" s="273"/>
+      <c r="W4" s="273"/>
+      <c r="X4" s="273"/>
+      <c r="Y4" s="273"/>
+      <c r="Z4" s="273"/>
       <c r="AB4" s="88"/>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
@@ -18489,32 +18460,32 @@
       <c r="N8" s="92"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C9" s="270" t="s">
+      <c r="C9" s="271" t="s">
         <v>129</v>
       </c>
-      <c r="D9" s="270"/>
-      <c r="E9" s="270"/>
-      <c r="F9" s="270"/>
-      <c r="G9" s="270"/>
-      <c r="H9" s="270"/>
-      <c r="I9" s="270"/>
-      <c r="J9" s="270"/>
-      <c r="K9" s="270"/>
-      <c r="L9" s="270"/>
+      <c r="D9" s="271"/>
+      <c r="E9" s="271"/>
+      <c r="F9" s="271"/>
+      <c r="G9" s="271"/>
+      <c r="H9" s="271"/>
+      <c r="I9" s="271"/>
+      <c r="J9" s="271"/>
+      <c r="K9" s="271"/>
+      <c r="L9" s="271"/>
       <c r="N9" s="92"/>
-      <c r="P9" s="272" t="s">
+      <c r="P9" s="273" t="s">
         <v>130</v>
       </c>
-      <c r="Q9" s="272"/>
-      <c r="R9" s="272"/>
-      <c r="S9" s="272"/>
-      <c r="T9" s="272"/>
-      <c r="U9" s="272"/>
-      <c r="V9" s="272"/>
-      <c r="W9" s="272"/>
-      <c r="X9" s="272"/>
-      <c r="Y9" s="272"/>
-      <c r="Z9" s="272"/>
+      <c r="Q9" s="273"/>
+      <c r="R9" s="273"/>
+      <c r="S9" s="273"/>
+      <c r="T9" s="273"/>
+      <c r="U9" s="273"/>
+      <c r="V9" s="273"/>
+      <c r="W9" s="273"/>
+      <c r="X9" s="273"/>
+      <c r="Y9" s="273"/>
+      <c r="Z9" s="273"/>
       <c r="AB9" s="88">
         <f>AB4</f>
         <v>0</v>
@@ -19084,31 +19055,31 @@
       </c>
     </row>
     <row r="18" spans="2:26" x14ac:dyDescent="0.2">
-      <c r="C18" s="270" t="s">
+      <c r="C18" s="271" t="s">
         <v>132</v>
       </c>
-      <c r="D18" s="270"/>
-      <c r="E18" s="270"/>
-      <c r="F18" s="270"/>
-      <c r="G18" s="270"/>
-      <c r="H18" s="270"/>
-      <c r="I18" s="270"/>
-      <c r="J18" s="270"/>
-      <c r="K18" s="270"/>
-      <c r="L18" s="270"/>
-      <c r="P18" s="272" t="s">
+      <c r="D18" s="271"/>
+      <c r="E18" s="271"/>
+      <c r="F18" s="271"/>
+      <c r="G18" s="271"/>
+      <c r="H18" s="271"/>
+      <c r="I18" s="271"/>
+      <c r="J18" s="271"/>
+      <c r="K18" s="271"/>
+      <c r="L18" s="271"/>
+      <c r="P18" s="273" t="s">
         <v>132</v>
       </c>
-      <c r="Q18" s="272"/>
-      <c r="R18" s="272"/>
-      <c r="S18" s="272"/>
-      <c r="T18" s="272"/>
-      <c r="U18" s="272"/>
-      <c r="V18" s="272"/>
-      <c r="W18" s="272"/>
-      <c r="X18" s="272"/>
-      <c r="Y18" s="272"/>
-      <c r="Z18" s="272"/>
+      <c r="Q18" s="273"/>
+      <c r="R18" s="273"/>
+      <c r="S18" s="273"/>
+      <c r="T18" s="273"/>
+      <c r="U18" s="273"/>
+      <c r="V18" s="273"/>
+      <c r="W18" s="273"/>
+      <c r="X18" s="273"/>
+      <c r="Y18" s="273"/>
+      <c r="Z18" s="273"/>
     </row>
     <row r="19" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -19668,60 +19639,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="262" t="s">
+      <c r="C3" s="265" t="s">
         <v>113</v>
       </c>
-      <c r="D3" s="262"/>
-      <c r="E3" s="262"/>
-      <c r="F3" s="262"/>
-      <c r="G3" s="268"/>
-      <c r="H3" s="269" t="s">
+      <c r="D3" s="265"/>
+      <c r="E3" s="265"/>
+      <c r="F3" s="265"/>
+      <c r="G3" s="274"/>
+      <c r="H3" s="275" t="s">
         <v>114</v>
       </c>
-      <c r="I3" s="262"/>
-      <c r="J3" s="262"/>
-      <c r="K3" s="262"/>
-      <c r="L3" s="262"/>
-      <c r="P3" s="273"/>
-      <c r="Q3" s="273"/>
-      <c r="R3" s="273"/>
-      <c r="S3" s="273"/>
-      <c r="T3" s="273"/>
-      <c r="U3" s="273"/>
-      <c r="V3" s="273"/>
-      <c r="W3" s="273"/>
-      <c r="X3" s="273"/>
-      <c r="Y3" s="273"/>
-      <c r="Z3" s="273"/>
+      <c r="I3" s="265"/>
+      <c r="J3" s="265"/>
+      <c r="K3" s="265"/>
+      <c r="L3" s="265"/>
+      <c r="P3" s="276"/>
+      <c r="Q3" s="276"/>
+      <c r="R3" s="276"/>
+      <c r="S3" s="276"/>
+      <c r="T3" s="276"/>
+      <c r="U3" s="276"/>
+      <c r="V3" s="276"/>
+      <c r="W3" s="276"/>
+      <c r="X3" s="276"/>
+      <c r="Y3" s="276"/>
+      <c r="Z3" s="276"/>
       <c r="AB3" s="111"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="87"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="270" t="s">
+      <c r="C5" s="271" t="s">
         <v>116</v>
       </c>
-      <c r="D5" s="270"/>
-      <c r="E5" s="270"/>
-      <c r="F5" s="270"/>
-      <c r="G5" s="270"/>
-      <c r="H5" s="270"/>
-      <c r="I5" s="270"/>
-      <c r="J5" s="270"/>
-      <c r="K5" s="270"/>
-      <c r="L5" s="270"/>
-      <c r="P5" s="273"/>
-      <c r="Q5" s="273"/>
-      <c r="R5" s="273"/>
-      <c r="S5" s="273"/>
-      <c r="T5" s="273"/>
-      <c r="U5" s="273"/>
-      <c r="V5" s="273"/>
-      <c r="W5" s="273"/>
-      <c r="X5" s="273"/>
-      <c r="Y5" s="273"/>
-      <c r="Z5" s="273"/>
+      <c r="D5" s="271"/>
+      <c r="E5" s="271"/>
+      <c r="F5" s="271"/>
+      <c r="G5" s="271"/>
+      <c r="H5" s="271"/>
+      <c r="I5" s="271"/>
+      <c r="J5" s="271"/>
+      <c r="K5" s="271"/>
+      <c r="L5" s="271"/>
+      <c r="P5" s="276"/>
+      <c r="Q5" s="276"/>
+      <c r="R5" s="276"/>
+      <c r="S5" s="276"/>
+      <c r="T5" s="276"/>
+      <c r="U5" s="276"/>
+      <c r="V5" s="276"/>
+      <c r="W5" s="276"/>
+      <c r="X5" s="276"/>
+      <c r="Y5" s="276"/>
+      <c r="Z5" s="276"/>
       <c r="AB5" s="112"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -19907,30 +19878,30 @@
       <c r="N10" s="92"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="270" t="s">
+      <c r="C11" s="271" t="s">
         <v>136</v>
       </c>
-      <c r="D11" s="270"/>
-      <c r="E11" s="270"/>
-      <c r="F11" s="270"/>
-      <c r="G11" s="270"/>
-      <c r="H11" s="270"/>
-      <c r="I11" s="270"/>
-      <c r="J11" s="270"/>
-      <c r="K11" s="270"/>
-      <c r="L11" s="270"/>
+      <c r="D11" s="271"/>
+      <c r="E11" s="271"/>
+      <c r="F11" s="271"/>
+      <c r="G11" s="271"/>
+      <c r="H11" s="271"/>
+      <c r="I11" s="271"/>
+      <c r="J11" s="271"/>
+      <c r="K11" s="271"/>
+      <c r="L11" s="271"/>
       <c r="N11" s="92"/>
-      <c r="P11" s="273"/>
-      <c r="Q11" s="273"/>
-      <c r="R11" s="273"/>
-      <c r="S11" s="273"/>
-      <c r="T11" s="273"/>
-      <c r="U11" s="273"/>
-      <c r="V11" s="273"/>
-      <c r="W11" s="273"/>
-      <c r="X11" s="273"/>
-      <c r="Y11" s="273"/>
-      <c r="Z11" s="273"/>
+      <c r="P11" s="276"/>
+      <c r="Q11" s="276"/>
+      <c r="R11" s="276"/>
+      <c r="S11" s="276"/>
+      <c r="T11" s="276"/>
+      <c r="U11" s="276"/>
+      <c r="V11" s="276"/>
+      <c r="W11" s="276"/>
+      <c r="X11" s="276"/>
+      <c r="Y11" s="276"/>
+      <c r="Z11" s="276"/>
       <c r="AB11" s="112"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.2">
@@ -20172,18 +20143,18 @@
       <c r="D16" s="24"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="270" t="s">
+      <c r="C18" s="271" t="s">
         <v>141</v>
       </c>
-      <c r="D18" s="270"/>
-      <c r="E18" s="270"/>
-      <c r="F18" s="270"/>
-      <c r="G18" s="270"/>
-      <c r="H18" s="270"/>
-      <c r="I18" s="270"/>
-      <c r="J18" s="270"/>
-      <c r="K18" s="270"/>
-      <c r="L18" s="270"/>
+      <c r="D18" s="271"/>
+      <c r="E18" s="271"/>
+      <c r="F18" s="271"/>
+      <c r="G18" s="271"/>
+      <c r="H18" s="271"/>
+      <c r="I18" s="271"/>
+      <c r="J18" s="271"/>
+      <c r="K18" s="271"/>
+      <c r="L18" s="271"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -20396,23 +20367,23 @@
       </c>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B25" s="273"/>
-      <c r="C25" s="273"/>
+      <c r="B25" s="276"/>
+      <c r="C25" s="276"/>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="111"/>
-      <c r="C26" s="270" t="s">
+      <c r="C26" s="271" t="s">
         <v>147</v>
       </c>
-      <c r="D26" s="270"/>
-      <c r="E26" s="270"/>
-      <c r="F26" s="270"/>
-      <c r="G26" s="270"/>
-      <c r="H26" s="270"/>
-      <c r="I26" s="270"/>
-      <c r="J26" s="270"/>
-      <c r="K26" s="270"/>
-      <c r="L26" s="270"/>
+      <c r="D26" s="271"/>
+      <c r="E26" s="271"/>
+      <c r="F26" s="271"/>
+      <c r="G26" s="271"/>
+      <c r="H26" s="271"/>
+      <c r="I26" s="271"/>
+      <c r="J26" s="271"/>
+      <c r="K26" s="271"/>
+      <c r="L26" s="271"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="16" t="s">
@@ -20604,18 +20575,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="111"/>
-      <c r="C33" s="270" t="s">
+      <c r="C33" s="271" t="s">
         <v>151</v>
       </c>
-      <c r="D33" s="270"/>
-      <c r="E33" s="270"/>
-      <c r="F33" s="270"/>
-      <c r="G33" s="270"/>
-      <c r="H33" s="270"/>
-      <c r="I33" s="270"/>
-      <c r="J33" s="270"/>
-      <c r="K33" s="270"/>
-      <c r="L33" s="270"/>
+      <c r="D33" s="271"/>
+      <c r="E33" s="271"/>
+      <c r="F33" s="271"/>
+      <c r="G33" s="271"/>
+      <c r="H33" s="271"/>
+      <c r="I33" s="271"/>
+      <c r="J33" s="271"/>
+      <c r="K33" s="271"/>
+      <c r="L33" s="271"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
@@ -20799,18 +20770,18 @@
       <c r="C39" s="127"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="270" t="s">
+      <c r="C40" s="271" t="s">
         <v>154</v>
       </c>
-      <c r="D40" s="270"/>
-      <c r="E40" s="270"/>
-      <c r="F40" s="270"/>
-      <c r="G40" s="270"/>
-      <c r="H40" s="270"/>
-      <c r="I40" s="270"/>
-      <c r="J40" s="270"/>
-      <c r="K40" s="270"/>
-      <c r="L40" s="270"/>
+      <c r="D40" s="271"/>
+      <c r="E40" s="271"/>
+      <c r="F40" s="271"/>
+      <c r="G40" s="271"/>
+      <c r="H40" s="271"/>
+      <c r="I40" s="271"/>
+      <c r="J40" s="271"/>
+      <c r="K40" s="271"/>
+      <c r="L40" s="271"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -21074,12 +21045,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -21087,6 +21052,12 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -21124,60 +21095,60 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="262" t="s">
+      <c r="C2" s="265" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="262"/>
-      <c r="E2" s="262"/>
-      <c r="F2" s="262"/>
-      <c r="G2" s="268"/>
-      <c r="H2" s="269" t="s">
+      <c r="D2" s="265"/>
+      <c r="E2" s="265"/>
+      <c r="F2" s="265"/>
+      <c r="G2" s="274"/>
+      <c r="H2" s="275" t="s">
         <v>114</v>
       </c>
-      <c r="I2" s="262"/>
-      <c r="J2" s="262"/>
-      <c r="K2" s="262"/>
-      <c r="L2" s="262"/>
-      <c r="S2" s="273"/>
-      <c r="T2" s="273"/>
-      <c r="U2" s="273"/>
-      <c r="V2" s="273"/>
-      <c r="W2" s="273"/>
-      <c r="X2" s="273"/>
-      <c r="Y2" s="273"/>
-      <c r="Z2" s="273"/>
-      <c r="AA2" s="273"/>
-      <c r="AB2" s="273"/>
-      <c r="AC2" s="273"/>
+      <c r="I2" s="265"/>
+      <c r="J2" s="265"/>
+      <c r="K2" s="265"/>
+      <c r="L2" s="265"/>
+      <c r="S2" s="276"/>
+      <c r="T2" s="276"/>
+      <c r="U2" s="276"/>
+      <c r="V2" s="276"/>
+      <c r="W2" s="276"/>
+      <c r="X2" s="276"/>
+      <c r="Y2" s="276"/>
+      <c r="Z2" s="276"/>
+      <c r="AA2" s="276"/>
+      <c r="AB2" s="276"/>
+      <c r="AC2" s="276"/>
       <c r="AE2" s="111"/>
     </row>
     <row r="3" spans="1:31" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="270" t="s">
+      <c r="C4" s="271" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="270"/>
-      <c r="E4" s="270"/>
-      <c r="F4" s="270"/>
-      <c r="G4" s="270"/>
-      <c r="H4" s="270"/>
-      <c r="I4" s="270"/>
-      <c r="J4" s="270"/>
-      <c r="K4" s="270"/>
-      <c r="L4" s="270"/>
-      <c r="S4" s="273"/>
-      <c r="T4" s="273"/>
-      <c r="U4" s="273"/>
-      <c r="V4" s="273"/>
-      <c r="W4" s="273"/>
-      <c r="X4" s="273"/>
-      <c r="Y4" s="273"/>
-      <c r="Z4" s="273"/>
-      <c r="AA4" s="273"/>
-      <c r="AB4" s="273"/>
-      <c r="AC4" s="273"/>
+      <c r="D4" s="271"/>
+      <c r="E4" s="271"/>
+      <c r="F4" s="271"/>
+      <c r="G4" s="271"/>
+      <c r="H4" s="271"/>
+      <c r="I4" s="271"/>
+      <c r="J4" s="271"/>
+      <c r="K4" s="271"/>
+      <c r="L4" s="271"/>
+      <c r="S4" s="276"/>
+      <c r="T4" s="276"/>
+      <c r="U4" s="276"/>
+      <c r="V4" s="276"/>
+      <c r="W4" s="276"/>
+      <c r="X4" s="276"/>
+      <c r="Y4" s="276"/>
+      <c r="Z4" s="276"/>
+      <c r="AA4" s="276"/>
+      <c r="AB4" s="276"/>
+      <c r="AC4" s="276"/>
       <c r="AE4" s="112"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -21540,18 +21511,18 @@
       <c r="AE10" s="64"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="270" t="s">
+      <c r="C13" s="271" t="s">
         <v>162</v>
       </c>
-      <c r="D13" s="270"/>
-      <c r="E13" s="270"/>
-      <c r="F13" s="270"/>
-      <c r="G13" s="270"/>
-      <c r="H13" s="270"/>
-      <c r="I13" s="270"/>
-      <c r="J13" s="270"/>
-      <c r="K13" s="270"/>
-      <c r="L13" s="270"/>
+      <c r="D13" s="271"/>
+      <c r="E13" s="271"/>
+      <c r="F13" s="271"/>
+      <c r="G13" s="271"/>
+      <c r="H13" s="271"/>
+      <c r="I13" s="271"/>
+      <c r="J13" s="271"/>
+      <c r="K13" s="271"/>
+      <c r="L13" s="271"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="12">
@@ -21644,18 +21615,18 @@
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C18" s="270" t="s">
+      <c r="C18" s="271" t="s">
         <v>163</v>
       </c>
-      <c r="D18" s="270"/>
-      <c r="E18" s="270"/>
-      <c r="F18" s="270"/>
-      <c r="G18" s="270"/>
-      <c r="H18" s="270"/>
-      <c r="I18" s="270"/>
-      <c r="J18" s="270"/>
-      <c r="K18" s="270"/>
-      <c r="L18" s="270"/>
+      <c r="D18" s="271"/>
+      <c r="E18" s="271"/>
+      <c r="F18" s="271"/>
+      <c r="G18" s="271"/>
+      <c r="H18" s="271"/>
+      <c r="I18" s="271"/>
+      <c r="J18" s="271"/>
+      <c r="K18" s="271"/>
+      <c r="L18" s="271"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -21847,18 +21818,18 @@
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C25" s="270" t="s">
+      <c r="C25" s="271" t="s">
         <v>266</v>
       </c>
-      <c r="D25" s="270"/>
-      <c r="E25" s="270"/>
-      <c r="F25" s="270"/>
-      <c r="G25" s="270"/>
-      <c r="H25" s="270"/>
-      <c r="I25" s="270"/>
-      <c r="J25" s="270"/>
-      <c r="K25" s="270"/>
-      <c r="L25" s="270"/>
+      <c r="D25" s="271"/>
+      <c r="E25" s="271"/>
+      <c r="F25" s="271"/>
+      <c r="G25" s="271"/>
+      <c r="H25" s="271"/>
+      <c r="I25" s="271"/>
+      <c r="J25" s="271"/>
+      <c r="K25" s="271"/>
+      <c r="L25" s="271"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B26" s="16" t="s">
@@ -21996,18 +21967,18 @@
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C31" s="270" t="s">
+      <c r="C31" s="271" t="s">
         <v>78</v>
       </c>
-      <c r="D31" s="270"/>
-      <c r="E31" s="270"/>
-      <c r="F31" s="270"/>
-      <c r="G31" s="270"/>
-      <c r="H31" s="270"/>
-      <c r="I31" s="270"/>
-      <c r="J31" s="270"/>
-      <c r="K31" s="270"/>
-      <c r="L31" s="270"/>
+      <c r="D31" s="271"/>
+      <c r="E31" s="271"/>
+      <c r="F31" s="271"/>
+      <c r="G31" s="271"/>
+      <c r="H31" s="271"/>
+      <c r="I31" s="271"/>
+      <c r="J31" s="271"/>
+      <c r="K31" s="271"/>
+      <c r="L31" s="271"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="16" t="s">
@@ -22146,16 +22117,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C31:L31"/>
+    <mergeCell ref="C25:L25"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="S2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
     <mergeCell ref="C13:L13"/>
     <mergeCell ref="C18:L18"/>
-    <mergeCell ref="C31:L31"/>
-    <mergeCell ref="C25:L25"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="S2:Z2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -22257,10 +22228,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="262" t="s">
+      <c r="B4" s="265" t="s">
         <v>170</v>
       </c>
-      <c r="C4" s="262"/>
+      <c r="C4" s="265"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -22277,7 +22248,7 @@
       </c>
       <c r="C6" s="135">
         <f ca="1">Overview!C5</f>
-        <v>141.93</v>
+        <v>143.04</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22286,7 +22257,7 @@
       </c>
       <c r="C7" s="136">
         <f ca="1">C5*C6</f>
-        <v>7113815.46</v>
+        <v>7169450.8799999999</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22304,7 +22275,7 @@
       </c>
       <c r="C9" s="137">
         <f ca="1">Overview!F27</f>
-        <v>5.1360000000000003E-2</v>
+        <v>4.9530000000000005E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22313,7 +22284,7 @@
       </c>
       <c r="C10" s="135">
         <f ca="1">Overview!C13</f>
-        <v>1.0656000000000001</v>
+        <v>1.0660000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22345,10 +22316,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="262" t="s">
+      <c r="B15" s="265" t="s">
         <v>177</v>
       </c>
-      <c r="C15" s="262"/>
+      <c r="C15" s="265"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -22383,7 +22354,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>9.9312000000000011E-2</v>
+        <v>9.7500000000000003E-2</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22392,7 +22363,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>9.9312000000000011E-2</v>
+        <v>9.7500000000000003E-2</v>
       </c>
     </row>
   </sheetData>
@@ -22437,60 +22408,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="262" t="s">
+      <c r="C3" s="265" t="s">
         <v>113</v>
       </c>
-      <c r="D3" s="262"/>
-      <c r="E3" s="262"/>
-      <c r="F3" s="262"/>
-      <c r="G3" s="268"/>
-      <c r="H3" s="269" t="s">
+      <c r="D3" s="265"/>
+      <c r="E3" s="265"/>
+      <c r="F3" s="265"/>
+      <c r="G3" s="274"/>
+      <c r="H3" s="275" t="s">
         <v>114</v>
       </c>
-      <c r="I3" s="262"/>
-      <c r="J3" s="262"/>
-      <c r="K3" s="262"/>
-      <c r="L3" s="262"/>
-      <c r="P3" s="273"/>
-      <c r="Q3" s="273"/>
-      <c r="R3" s="273"/>
-      <c r="S3" s="273"/>
-      <c r="T3" s="273"/>
-      <c r="U3" s="273"/>
-      <c r="V3" s="273"/>
-      <c r="W3" s="273"/>
-      <c r="X3" s="273"/>
-      <c r="Y3" s="273"/>
-      <c r="Z3" s="273"/>
+      <c r="I3" s="265"/>
+      <c r="J3" s="265"/>
+      <c r="K3" s="265"/>
+      <c r="L3" s="265"/>
+      <c r="P3" s="276"/>
+      <c r="Q3" s="276"/>
+      <c r="R3" s="276"/>
+      <c r="S3" s="276"/>
+      <c r="T3" s="276"/>
+      <c r="U3" s="276"/>
+      <c r="V3" s="276"/>
+      <c r="W3" s="276"/>
+      <c r="X3" s="276"/>
+      <c r="Y3" s="276"/>
+      <c r="Z3" s="276"/>
       <c r="AB3" s="111"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="87"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="270" t="s">
+      <c r="C5" s="271" t="s">
         <v>184</v>
       </c>
-      <c r="D5" s="270"/>
-      <c r="E5" s="270"/>
-      <c r="F5" s="270"/>
-      <c r="G5" s="270"/>
-      <c r="H5" s="270"/>
-      <c r="I5" s="270"/>
-      <c r="J5" s="270"/>
-      <c r="K5" s="270"/>
-      <c r="L5" s="270"/>
-      <c r="P5" s="273"/>
-      <c r="Q5" s="273"/>
-      <c r="R5" s="273"/>
-      <c r="S5" s="273"/>
-      <c r="T5" s="273"/>
-      <c r="U5" s="273"/>
-      <c r="V5" s="273"/>
-      <c r="W5" s="273"/>
-      <c r="X5" s="273"/>
-      <c r="Y5" s="273"/>
-      <c r="Z5" s="273"/>
+      <c r="D5" s="271"/>
+      <c r="E5" s="271"/>
+      <c r="F5" s="271"/>
+      <c r="G5" s="271"/>
+      <c r="H5" s="271"/>
+      <c r="I5" s="271"/>
+      <c r="J5" s="271"/>
+      <c r="K5" s="271"/>
+      <c r="L5" s="271"/>
+      <c r="P5" s="276"/>
+      <c r="Q5" s="276"/>
+      <c r="R5" s="276"/>
+      <c r="S5" s="276"/>
+      <c r="T5" s="276"/>
+      <c r="U5" s="276"/>
+      <c r="V5" s="276"/>
+      <c r="W5" s="276"/>
+      <c r="X5" s="276"/>
+      <c r="Y5" s="276"/>
+      <c r="Z5" s="276"/>
       <c r="AB5" s="112"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -22643,7 +22614,7 @@
       </c>
       <c r="L8" s="128">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>7381968.193447846</v>
+        <v>7554563.3723707823</v>
       </c>
       <c r="N8" s="92"/>
       <c r="O8" s="16"/>
@@ -22697,23 +22668,23 @@
       <c r="G10" s="140"/>
       <c r="H10" s="128">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>164442.09835901338</v>
+        <v>164713.59638382119</v>
       </c>
       <c r="I10" s="128">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>199027.31516372363</v>
+        <v>199685.05585775024</v>
       </c>
       <c r="J10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>226939.40791208789</v>
+        <v>228065.31271136957</v>
       </c>
       <c r="K10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>260964.41240846203</v>
+        <v>262692.12039560592</v>
       </c>
       <c r="L10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>357524.70406073733</v>
+        <v>360485.87709661247</v>
       </c>
       <c r="N10" s="92"/>
     </row>
@@ -22732,14 +22703,14 @@
       <c r="K11" s="139"/>
       <c r="L11" s="128">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>4597982.6273697801</v>
+        <v>4744459.2856586417</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="262" t="s">
+      <c r="B13" s="265" t="s">
         <v>188</v>
       </c>
-      <c r="C13" s="262"/>
+      <c r="C13" s="265"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -22755,14 +22726,14 @@
       </c>
       <c r="C15" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>9.9312000000000011E-2</v>
+        <v>9.7500000000000003E-2</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="262" t="s">
+      <c r="B18" s="265" t="s">
         <v>190</v>
       </c>
-      <c r="C18" s="262"/>
+      <c r="C18" s="265"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -22770,7 +22741,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>1208897.9379040243</v>
+        <v>1215641.9624451594</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -22779,7 +22750,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>4597982.6273697801</v>
+        <v>4744459.2856586417</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -22788,7 +22759,7 @@
       </c>
       <c r="C21" s="95">
         <f ca="1">C19+C20</f>
-        <v>5806880.5652738046</v>
+        <v>5960101.2481038012</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -22815,7 +22786,7 @@
       </c>
       <c r="C24" s="95">
         <f ca="1">C21+C22-C23</f>
-        <v>7223439.5652738046</v>
+        <v>7376660.2481038012</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -22833,7 +22804,7 @@
       </c>
       <c r="C26" s="254">
         <f ca="1">C24/C25</f>
-        <v>144.11714547052802</v>
+        <v>147.17410015769124</v>
       </c>
     </row>
   </sheetData>
@@ -22876,37 +22847,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="262" t="s">
+      <c r="C2" s="265" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="262"/>
-      <c r="E2" s="262"/>
-      <c r="F2" s="262"/>
-      <c r="G2" s="268"/>
-      <c r="H2" s="269" t="s">
+      <c r="D2" s="265"/>
+      <c r="E2" s="265"/>
+      <c r="F2" s="265"/>
+      <c r="G2" s="274"/>
+      <c r="H2" s="275" t="s">
         <v>114</v>
       </c>
-      <c r="I2" s="262"/>
-      <c r="J2" s="262"/>
-      <c r="K2" s="262"/>
-      <c r="L2" s="262"/>
+      <c r="I2" s="265"/>
+      <c r="J2" s="265"/>
+      <c r="K2" s="265"/>
+      <c r="L2" s="265"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="270" t="s">
+      <c r="C4" s="271" t="s">
         <v>198</v>
       </c>
-      <c r="D4" s="270"/>
-      <c r="E4" s="270"/>
-      <c r="F4" s="270"/>
-      <c r="G4" s="270"/>
-      <c r="H4" s="270"/>
-      <c r="I4" s="270"/>
-      <c r="J4" s="270"/>
-      <c r="K4" s="270"/>
-      <c r="L4" s="270"/>
+      <c r="D4" s="271"/>
+      <c r="E4" s="271"/>
+      <c r="F4" s="271"/>
+      <c r="G4" s="271"/>
+      <c r="H4" s="271"/>
+      <c r="I4" s="271"/>
+      <c r="J4" s="271"/>
+      <c r="K4" s="271"/>
+      <c r="L4" s="271"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -23102,23 +23073,23 @@
       <c r="G9" s="140"/>
       <c r="H9" s="93">
         <f ca="1">DCF!H10</f>
-        <v>164442.09835901338</v>
+        <v>164713.59638382119</v>
       </c>
       <c r="I9" s="93">
         <f ca="1">DCF!I10</f>
-        <v>199027.31516372363</v>
+        <v>199685.05585775024</v>
       </c>
       <c r="J9" s="93">
         <f ca="1">DCF!J10</f>
-        <v>226939.40791208789</v>
+        <v>228065.31271136957</v>
       </c>
       <c r="K9" s="93">
         <f ca="1">DCF!K10</f>
-        <v>260964.41240846203</v>
+        <v>262692.12039560592</v>
       </c>
       <c r="L9" s="93">
         <f ca="1">DCF!L10</f>
-        <v>357524.70406073733</v>
+        <v>360485.87709661247</v>
       </c>
       <c r="N9" s="92"/>
     </row>
@@ -23126,18 +23097,18 @@
       <c r="N10" s="92"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C11" s="270" t="s">
+      <c r="C11" s="271" t="s">
         <v>122</v>
       </c>
-      <c r="D11" s="270"/>
-      <c r="E11" s="270"/>
-      <c r="F11" s="270"/>
-      <c r="G11" s="270"/>
-      <c r="H11" s="270"/>
-      <c r="I11" s="270"/>
-      <c r="J11" s="270"/>
-      <c r="K11" s="270"/>
-      <c r="L11" s="270"/>
+      <c r="D11" s="271"/>
+      <c r="E11" s="271"/>
+      <c r="F11" s="271"/>
+      <c r="G11" s="271"/>
+      <c r="H11" s="271"/>
+      <c r="I11" s="271"/>
+      <c r="J11" s="271"/>
+      <c r="K11" s="271"/>
+      <c r="L11" s="271"/>
       <c r="N11" s="92"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -23331,18 +23302,18 @@
       <c r="N16" s="92"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C17" s="270" t="s">
+      <c r="C17" s="271" t="s">
         <v>200</v>
       </c>
-      <c r="D17" s="270"/>
-      <c r="E17" s="270"/>
-      <c r="F17" s="270"/>
-      <c r="G17" s="270"/>
-      <c r="H17" s="270"/>
-      <c r="I17" s="270"/>
-      <c r="J17" s="270"/>
-      <c r="K17" s="270"/>
-      <c r="L17" s="270"/>
+      <c r="D17" s="271"/>
+      <c r="E17" s="271"/>
+      <c r="F17" s="271"/>
+      <c r="G17" s="271"/>
+      <c r="H17" s="271"/>
+      <c r="I17" s="271"/>
+      <c r="J17" s="271"/>
+      <c r="K17" s="271"/>
+      <c r="L17" s="271"/>
       <c r="N17" s="92"/>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
@@ -23476,18 +23447,18 @@
       <c r="N21" s="92"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C22" s="270" t="s">
+      <c r="C22" s="271" t="s">
         <v>203</v>
       </c>
-      <c r="D22" s="270"/>
-      <c r="E22" s="270"/>
-      <c r="F22" s="270"/>
-      <c r="G22" s="270"/>
-      <c r="H22" s="270"/>
-      <c r="I22" s="270"/>
-      <c r="J22" s="270"/>
-      <c r="K22" s="270"/>
-      <c r="L22" s="270"/>
+      <c r="D22" s="271"/>
+      <c r="E22" s="271"/>
+      <c r="F22" s="271"/>
+      <c r="G22" s="271"/>
+      <c r="H22" s="271"/>
+      <c r="I22" s="271"/>
+      <c r="J22" s="271"/>
+      <c r="K22" s="271"/>
+      <c r="L22" s="271"/>
       <c r="N22" s="92"/>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.2">
@@ -23571,18 +23542,18 @@
       <c r="N26" s="92"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C27" s="270" t="s">
+      <c r="C27" s="271" t="s">
         <v>204</v>
       </c>
-      <c r="D27" s="270"/>
-      <c r="E27" s="270"/>
-      <c r="F27" s="270"/>
-      <c r="G27" s="270"/>
-      <c r="H27" s="270"/>
-      <c r="I27" s="270"/>
-      <c r="J27" s="270"/>
-      <c r="K27" s="270"/>
-      <c r="L27" s="270"/>
+      <c r="D27" s="271"/>
+      <c r="E27" s="271"/>
+      <c r="F27" s="271"/>
+      <c r="G27" s="271"/>
+      <c r="H27" s="271"/>
+      <c r="I27" s="271"/>
+      <c r="J27" s="271"/>
+      <c r="K27" s="271"/>
+      <c r="L27" s="271"/>
       <c r="N27" s="92"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.2">
@@ -23883,10 +23854,10 @@
       <c r="N38" s="92"/>
     </row>
     <row r="39" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B39" s="262" t="s">
+      <c r="B39" s="265" t="s">
         <v>209</v>
       </c>
-      <c r="C39" s="262"/>
+      <c r="C39" s="265"/>
       <c r="N39" s="92"/>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -23904,7 +23875,7 @@
       </c>
       <c r="C41" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>9.9312000000000011E-2</v>
+        <v>9.7500000000000003E-2</v>
       </c>
     </row>
     <row r="42" spans="2:14" x14ac:dyDescent="0.2">
@@ -23930,7 +23901,7 @@
       </c>
       <c r="C44" s="24">
         <f ca="1">C43/(1+C41)^5</f>
-        <v>7590794.9114711611</v>
+        <v>7653665.1326262504</v>
       </c>
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.2">
@@ -23939,7 +23910,7 @@
       </c>
       <c r="C45" s="110">
         <f ca="1">SUM(H9:K9)+C44</f>
-        <v>8442168.1453144476</v>
+        <v>8508821.2179747969</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -23966,7 +23937,7 @@
       </c>
       <c r="C48" s="110">
         <f ca="1">C45+C46-C47</f>
-        <v>9858727.1453144476</v>
+        <v>9925380.2179747969</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
@@ -23984,14 +23955,14 @@
       </c>
       <c r="C50" s="254">
         <f ca="1">C48/C49</f>
-        <v>196.69460806261617</v>
+        <v>198.02442476307402</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B52" s="262" t="s">
+      <c r="B52" s="265" t="s">
         <v>214</v>
       </c>
-      <c r="C52" s="262"/>
+      <c r="C52" s="265"/>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B53" s="1" t="s">
@@ -24008,7 +23979,7 @@
       </c>
       <c r="C54" s="137">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>9.9312000000000011E-2</v>
+        <v>9.7500000000000003E-2</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
@@ -24043,14 +24014,14 @@
       </c>
       <c r="C58" s="254">
         <f ca="1">C57/(1+C54)^5</f>
-        <v>158.43352867962039</v>
+        <v>159.74574315816156</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B60" s="262" t="s">
+      <c r="B60" s="265" t="s">
         <v>327</v>
       </c>
-      <c r="C60" s="262"/>
+      <c r="C60" s="265"/>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B61" s="1" t="s">
@@ -24067,7 +24038,7 @@
       </c>
       <c r="C62" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>9.9312000000000011E-2</v>
+        <v>9.7500000000000003E-2</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
@@ -24093,7 +24064,7 @@
       </c>
       <c r="C65" s="24">
         <f ca="1">C64/(1+C62)^5</f>
-        <v>7865543.4893362215</v>
+        <v>7930689.2961254744</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -24102,7 +24073,7 @@
       </c>
       <c r="C66" s="110">
         <f ca="1">SUM(H9:K9)+C65</f>
-        <v>8716916.723179508</v>
+        <v>8785845.3814740218</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.2">
@@ -24129,7 +24100,7 @@
       </c>
       <c r="C69" s="110">
         <f ca="1">C66+C67-C68</f>
-        <v>10133475.723179508</v>
+        <v>10202404.381474022</v>
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.2">
@@ -24147,14 +24118,14 @@
       </c>
       <c r="C71" s="254">
         <f ca="1">C69/C70</f>
-        <v>202.17620452455026</v>
+        <v>203.55142215941146</v>
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B73" s="262" t="s">
+      <c r="B73" s="265" t="s">
         <v>433</v>
       </c>
-      <c r="C73" s="262"/>
+      <c r="C73" s="265"/>
     </row>
     <row r="74" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B74" s="1" t="s">
@@ -24171,7 +24142,7 @@
       </c>
       <c r="C75" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>9.9312000000000011E-2</v>
+        <v>9.7500000000000003E-2</v>
       </c>
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.2">
@@ -24197,7 +24168,7 @@
       </c>
       <c r="C78" s="24">
         <f ca="1">C77/(1+C75)^5</f>
-        <v>7886540.1677622497</v>
+        <v>7951859.8780532517</v>
       </c>
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.2">
@@ -24206,7 +24177,7 @@
       </c>
       <c r="C79" s="110">
         <f ca="1">SUM(H9:K9)+C78</f>
-        <v>8737913.4016055372</v>
+        <v>8807015.9634017982</v>
       </c>
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.2">
@@ -24233,7 +24204,7 @@
       </c>
       <c r="C82" s="110">
         <f ca="1">C79+C80-C81</f>
-        <v>10154472.401605537</v>
+        <v>10223574.963401798</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.2">
@@ -24251,22 +24222,22 @@
       </c>
       <c r="C84" s="254">
         <f ca="1">C82/C83</f>
-        <v>202.59511594919471</v>
+        <v>203.97380318825662</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="C27:L27"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B60:C60"/>
     <mergeCell ref="C22:L22"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="C17:L17"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="C27:L27"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B60:C60"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -24304,10 +24275,10 @@
       <c r="N3" s="92"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="262" t="s">
+      <c r="B4" s="265" t="s">
         <v>218</v>
       </c>
-      <c r="C4" s="262"/>
+      <c r="C4" s="265"/>
       <c r="N4" s="92"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -24316,7 +24287,7 @@
       </c>
       <c r="C5" s="135">
         <f ca="1">DCF!C26</f>
-        <v>144.11714547052802</v>
+        <v>147.17410015769124</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -24325,7 +24296,7 @@
       </c>
       <c r="C6" s="135">
         <f ca="1">Multiples!C50</f>
-        <v>196.69460806261617</v>
+        <v>198.02442476307402</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -24334,7 +24305,7 @@
       </c>
       <c r="C7" s="135">
         <f ca="1">Multiples!C58</f>
-        <v>158.43352867962039</v>
+        <v>159.74574315816156</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -24343,7 +24314,7 @@
       </c>
       <c r="C8" s="135">
         <f ca="1">Multiples!C71</f>
-        <v>202.17620452455026</v>
+        <v>203.55142215941146</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -24352,7 +24323,7 @@
       </c>
       <c r="C9" s="135">
         <f ca="1">Multiples!C84</f>
-        <v>202.59511594919471</v>
+        <v>203.97380318825662</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -24361,7 +24332,7 @@
       </c>
       <c r="C10" s="254">
         <f ca="1">AVERAGE(C5:C9)</f>
-        <v>180.80332053730189</v>
+        <v>182.49389868531898</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -24370,7 +24341,7 @@
       </c>
       <c r="C11" s="135">
         <f ca="1">Overview!C5</f>
-        <v>141.93</v>
+        <v>143.04</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -24379,7 +24350,7 @@
       </c>
       <c r="C12" s="154">
         <f ca="1">(C10-C11)/C11</f>
-        <v>0.27389079502079811</v>
+        <v>0.27582423577544041</v>
       </c>
     </row>
   </sheetData>
@@ -24474,37 +24445,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="262" t="s">
+      <c r="C2" s="265" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="262"/>
-      <c r="E2" s="262"/>
-      <c r="F2" s="262"/>
-      <c r="G2" s="268"/>
-      <c r="H2" s="269" t="s">
+      <c r="D2" s="265"/>
+      <c r="E2" s="265"/>
+      <c r="F2" s="265"/>
+      <c r="G2" s="274"/>
+      <c r="H2" s="275" t="s">
         <v>114</v>
       </c>
-      <c r="I2" s="262"/>
-      <c r="J2" s="262"/>
-      <c r="K2" s="262"/>
-      <c r="L2" s="262"/>
+      <c r="I2" s="265"/>
+      <c r="J2" s="265"/>
+      <c r="K2" s="265"/>
+      <c r="L2" s="265"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="270" t="s">
+      <c r="C4" s="271" t="s">
         <v>198</v>
       </c>
-      <c r="D4" s="270"/>
-      <c r="E4" s="270"/>
-      <c r="F4" s="270"/>
-      <c r="G4" s="270"/>
-      <c r="H4" s="270"/>
-      <c r="I4" s="270"/>
-      <c r="J4" s="270"/>
-      <c r="K4" s="270"/>
-      <c r="L4" s="270"/>
+      <c r="D4" s="271"/>
+      <c r="E4" s="271"/>
+      <c r="F4" s="271"/>
+      <c r="G4" s="271"/>
+      <c r="H4" s="271"/>
+      <c r="I4" s="271"/>
+      <c r="J4" s="271"/>
+      <c r="K4" s="271"/>
+      <c r="L4" s="271"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -24617,18 +24588,18 @@
       <c r="N8" s="92"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C9" s="270" t="s">
+      <c r="C9" s="271" t="s">
         <v>122</v>
       </c>
-      <c r="D9" s="270"/>
-      <c r="E9" s="270"/>
-      <c r="F9" s="270"/>
-      <c r="G9" s="270"/>
-      <c r="H9" s="270"/>
-      <c r="I9" s="270"/>
-      <c r="J9" s="270"/>
-      <c r="K9" s="270"/>
-      <c r="L9" s="270"/>
+      <c r="D9" s="271"/>
+      <c r="E9" s="271"/>
+      <c r="F9" s="271"/>
+      <c r="G9" s="271"/>
+      <c r="H9" s="271"/>
+      <c r="I9" s="271"/>
+      <c r="J9" s="271"/>
+      <c r="K9" s="271"/>
+      <c r="L9" s="271"/>
       <c r="N9" s="92"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -24749,18 +24720,18 @@
       <c r="N13" s="92"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C14" s="270" t="s">
+      <c r="C14" s="271" t="s">
         <v>413</v>
       </c>
-      <c r="D14" s="270"/>
-      <c r="E14" s="270"/>
-      <c r="F14" s="270"/>
-      <c r="G14" s="270"/>
-      <c r="H14" s="270"/>
-      <c r="I14" s="270"/>
-      <c r="J14" s="270"/>
-      <c r="K14" s="270"/>
-      <c r="L14" s="270"/>
+      <c r="D14" s="271"/>
+      <c r="E14" s="271"/>
+      <c r="F14" s="271"/>
+      <c r="G14" s="271"/>
+      <c r="H14" s="271"/>
+      <c r="I14" s="271"/>
+      <c r="J14" s="271"/>
+      <c r="K14" s="271"/>
+      <c r="L14" s="271"/>
       <c r="N14" s="92"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
@@ -24850,10 +24821,10 @@
       <c r="N19" s="92"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B20" s="262" t="s">
+      <c r="B20" s="265" t="s">
         <v>415</v>
       </c>
-      <c r="C20" s="262"/>
+      <c r="C20" s="265"/>
       <c r="N20" s="92"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
@@ -24888,7 +24859,7 @@
       </c>
       <c r="C24" s="137">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>9.9312000000000011E-2</v>
+        <v>9.7500000000000003E-2</v>
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
@@ -24955,60 +24926,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="262" t="s">
+      <c r="C3" s="265" t="s">
         <v>113</v>
       </c>
-      <c r="D3" s="262"/>
-      <c r="E3" s="262"/>
-      <c r="F3" s="262"/>
-      <c r="G3" s="268"/>
-      <c r="H3" s="269" t="s">
+      <c r="D3" s="265"/>
+      <c r="E3" s="265"/>
+      <c r="F3" s="265"/>
+      <c r="G3" s="274"/>
+      <c r="H3" s="275" t="s">
         <v>114</v>
       </c>
-      <c r="I3" s="262"/>
-      <c r="J3" s="262"/>
-      <c r="K3" s="262"/>
-      <c r="L3" s="262"/>
-      <c r="P3" s="273"/>
-      <c r="Q3" s="273"/>
-      <c r="R3" s="273"/>
-      <c r="S3" s="273"/>
-      <c r="T3" s="273"/>
-      <c r="U3" s="273"/>
-      <c r="V3" s="273"/>
-      <c r="W3" s="273"/>
-      <c r="X3" s="273"/>
-      <c r="Y3" s="273"/>
-      <c r="Z3" s="273"/>
+      <c r="I3" s="265"/>
+      <c r="J3" s="265"/>
+      <c r="K3" s="265"/>
+      <c r="L3" s="265"/>
+      <c r="P3" s="276"/>
+      <c r="Q3" s="276"/>
+      <c r="R3" s="276"/>
+      <c r="S3" s="276"/>
+      <c r="T3" s="276"/>
+      <c r="U3" s="276"/>
+      <c r="V3" s="276"/>
+      <c r="W3" s="276"/>
+      <c r="X3" s="276"/>
+      <c r="Y3" s="276"/>
+      <c r="Z3" s="276"/>
       <c r="AB3" s="111"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="87"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="270" t="s">
+      <c r="C5" s="271" t="s">
         <v>184</v>
       </c>
-      <c r="D5" s="270"/>
-      <c r="E5" s="270"/>
-      <c r="F5" s="270"/>
-      <c r="G5" s="270"/>
-      <c r="H5" s="270"/>
-      <c r="I5" s="270"/>
-      <c r="J5" s="270"/>
-      <c r="K5" s="270"/>
-      <c r="L5" s="270"/>
-      <c r="P5" s="273"/>
-      <c r="Q5" s="273"/>
-      <c r="R5" s="273"/>
-      <c r="S5" s="273"/>
-      <c r="T5" s="273"/>
-      <c r="U5" s="273"/>
-      <c r="V5" s="273"/>
-      <c r="W5" s="273"/>
-      <c r="X5" s="273"/>
-      <c r="Y5" s="273"/>
-      <c r="Z5" s="273"/>
+      <c r="D5" s="271"/>
+      <c r="E5" s="271"/>
+      <c r="F5" s="271"/>
+      <c r="G5" s="271"/>
+      <c r="H5" s="271"/>
+      <c r="I5" s="271"/>
+      <c r="J5" s="271"/>
+      <c r="K5" s="271"/>
+      <c r="L5" s="271"/>
+      <c r="P5" s="276"/>
+      <c r="Q5" s="276"/>
+      <c r="R5" s="276"/>
+      <c r="S5" s="276"/>
+      <c r="T5" s="276"/>
+      <c r="U5" s="276"/>
+      <c r="V5" s="276"/>
+      <c r="W5" s="276"/>
+      <c r="X5" s="276"/>
+      <c r="Y5" s="276"/>
+      <c r="Z5" s="276"/>
       <c r="AB5" s="112"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -25143,7 +25114,7 @@
       <c r="K8" s="139"/>
       <c r="L8" s="128">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>7025181.0888108155</v>
+        <v>7189434.3550421083</v>
       </c>
       <c r="N8" s="92"/>
       <c r="O8" s="16"/>
@@ -25197,23 +25168,23 @@
       <c r="G10" s="140"/>
       <c r="H10" s="128">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>179438.8360391942</v>
+        <v>179735.09405368444</v>
       </c>
       <c r="I10" s="128">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>210564.51534283304</v>
+        <v>211260.38389909151</v>
       </c>
       <c r="J10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>247089.29293253834</v>
+        <v>248315.16649642648</v>
       </c>
       <c r="K10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>289949.70298056828</v>
+        <v>291869.30731698417</v>
       </c>
       <c r="L10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>340244.73201869265</v>
+        <v>343062.78491016821</v>
       </c>
       <c r="N10" s="92"/>
     </row>
@@ -25232,15 +25203,15 @@
       <c r="K11" s="139"/>
       <c r="L11" s="128">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>4375751.7987072133</v>
+        <v>4515148.9110757625</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="275" t="s">
+      <c r="B14" s="277" t="s">
         <v>226</v>
       </c>
-      <c r="C14" s="276"/>
+      <c r="C14" s="278"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="155" t="s">
@@ -25248,7 +25219,7 @@
       </c>
       <c r="C15" s="156">
         <f ca="1">Overview!C5</f>
-        <v>141.93</v>
+        <v>143.04</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -25257,7 +25228,7 @@
       </c>
       <c r="C16" s="156">
         <f ca="1">C36</f>
-        <v>150.89124691191896</v>
+        <v>154.01937861223695</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -25267,20 +25238,20 @@
       <c r="C17" s="158">
         <v>0.28999999999999998</v>
       </c>
-      <c r="E17" s="274" t="s">
+      <c r="E17" s="279" t="s">
         <v>229</v>
       </c>
-      <c r="F17" s="274"/>
-      <c r="G17" s="274"/>
-      <c r="H17" s="274"/>
-      <c r="I17" s="274"/>
+      <c r="F17" s="279"/>
+      <c r="G17" s="279"/>
+      <c r="H17" s="279"/>
+      <c r="I17" s="279"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="275" t="s">
+      <c r="B19" s="277" t="s">
         <v>188</v>
       </c>
-      <c r="C19" s="276"/>
+      <c r="C19" s="278"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="159" t="s">
@@ -25296,7 +25267,7 @@
       </c>
       <c r="C21" s="221">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>9.9312000000000011E-2</v>
+        <v>9.7500000000000003E-2</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -25314,7 +25285,7 @@
       </c>
       <c r="C23" s="161">
         <f ca="1">C15*C22</f>
-        <v>6640336.9800000004</v>
+        <v>6692269.4399999995</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -25341,15 +25312,15 @@
       </c>
       <c r="C26" s="162">
         <f ca="1">C23+C25-C24</f>
-        <v>5223777.9800000004</v>
+        <v>5275710.4399999995</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="275" t="s">
+      <c r="B28" s="277" t="s">
         <v>190</v>
       </c>
-      <c r="C28" s="276"/>
+      <c r="C28" s="278"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="159" t="s">
@@ -25357,7 +25328,7 @@
       </c>
       <c r="C29" s="161">
         <f ca="1">SUM(H10:L10)</f>
-        <v>1267287.0793138265</v>
+        <v>1274242.7366763549</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -25366,7 +25337,7 @@
       </c>
       <c r="C30" s="161">
         <f ca="1">L11</f>
-        <v>4375751.7987072133</v>
+        <v>4515148.9110757625</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -25375,7 +25346,7 @@
       </c>
       <c r="C31" s="164">
         <f ca="1">C29+C30</f>
-        <v>5643038.87802104</v>
+        <v>5789391.6477521174</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -25402,7 +25373,7 @@
       </c>
       <c r="C34" s="164">
         <f ca="1">C31+C32-C33</f>
-        <v>7059597.87802104</v>
+        <v>7205950.6477521174</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.2">
@@ -25420,21 +25391,21 @@
       </c>
       <c r="C36" s="167">
         <f ca="1">C34/C35</f>
-        <v>150.89124691191896</v>
+        <v>154.01937861223695</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
     <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -32126,7 +32097,7 @@
       </c>
       <c r="AC116" s="63">
         <f ca="1">Overview!C5</f>
-        <v>141.93</v>
+        <v>143.04</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -32197,7 +32168,7 @@
       </c>
       <c r="AC117" s="65">
         <f ca="1">AC116/AC85</f>
-        <v>141.93</v>
+        <v>143.04</v>
       </c>
     </row>
     <row r="119" spans="1:31" x14ac:dyDescent="0.2">
@@ -33307,7 +33278,7 @@
       <c r="AA146" s="49"/>
       <c r="AC146" s="72">
         <f ca="1">AC117/Statement!AC26</f>
-        <v>45.192045916970358</v>
+        <v>45.54548191336179</v>
       </c>
     </row>
     <row r="147" spans="2:29" x14ac:dyDescent="0.2">
@@ -33344,7 +33315,7 @@
       <c r="AA147" s="49"/>
       <c r="AC147" s="72">
         <f ca="1">AC117/(Statement!AC5/Statement!AC22)</f>
-        <v>6.0951090523611153</v>
+        <v>6.1427774173869789</v>
       </c>
     </row>
     <row r="148" spans="2:29" x14ac:dyDescent="0.2">
@@ -33405,7 +33376,7 @@
       </c>
       <c r="AC148" s="72">
         <f ca="1">AC117/(Statement!AC49/Statement!AC75)</f>
-        <v>4.7103207395395756</v>
+        <v>4.7471590120745493</v>
       </c>
     </row>
     <row r="149" spans="2:29" x14ac:dyDescent="0.2">
@@ -33466,7 +33437,7 @@
       </c>
       <c r="AC149" s="143">
         <f ca="1">Statement!AC117*Statement!AC78</f>
-        <v>7113815.46</v>
+        <v>7169450.8799999999</v>
       </c>
     </row>
     <row r="150" spans="2:29" x14ac:dyDescent="0.2">
@@ -33527,7 +33498,7 @@
       </c>
       <c r="AC150" s="143">
         <f ca="1">AC149+AC108-AC107+AC48+AC45</f>
-        <v>5697256.46</v>
+        <v>5752891.8799999999</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -33564,7 +33535,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="182">
         <f ca="1">AC150/AC5</f>
-        <v>4.9757611427752968</v>
+        <v>5.0243509443651622</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -33601,7 +33572,7 @@
       <c r="AA152" s="49"/>
       <c r="AC152" s="182">
         <f ca="1">AC150/AC12</f>
-        <v>36.26862182894611</v>
+        <v>36.622795811185028</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -33736,7 +33707,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="72">
         <f t="shared" ref="AC155:AC156" ca="1" si="151">AC149/AC153</f>
-        <v>28.137866703583576</v>
+        <v>28.357926113440392</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -33773,7 +33744,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="72">
         <f t="shared" ca="1" si="151"/>
-        <v>34.170284120872815</v>
+        <v>34.503967205341873</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -33810,7 +33781,7 @@
       <c r="AA157" s="49"/>
       <c r="AC157" s="74">
         <f t="shared" ref="AC157" ca="1" si="154">AC153/AC149</f>
-        <v>3.5539296938692309E-2</v>
+        <v>3.5263509609260342E-2</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
@@ -33847,7 +33818,7 @@
       <c r="AA158" s="49"/>
       <c r="AC158" s="74">
         <f ca="1">AC26/AC117</f>
-        <v>2.2127787749137588E-2</v>
+        <v>2.1956074631117855E-2</v>
       </c>
     </row>
     <row r="159" spans="2:29" x14ac:dyDescent="0.2">
@@ -33921,7 +33892,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="154">
         <f ca="1">-AC63/AC149</f>
-        <v>9.7842009525504342E-3</v>
+        <v>9.7082748965008608E-3</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -33958,7 +33929,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="154">
         <f ca="1">-(AC63+AC64)/AC149</f>
-        <v>9.7842009525504342E-3</v>
+        <v>9.7082748965008608E-3</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -34461,7 +34432,7 @@
       <c r="AA172" s="49"/>
       <c r="AC172" s="154">
         <f ca="1">(AC107-AC108)/AC149</f>
-        <v>0.19912788122845121</v>
+        <v>0.19758263550583111</v>
       </c>
     </row>
     <row r="173" spans="2:29" x14ac:dyDescent="0.2">
@@ -36422,15 +36393,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="262" t="s">
+      <c r="B4" s="265" t="s">
         <v>237</v>
       </c>
-      <c r="C4" s="262"/>
-      <c r="E4" s="262" t="s">
+      <c r="C4" s="265"/>
+      <c r="E4" s="265" t="s">
         <v>244</v>
       </c>
-      <c r="F4" s="262"/>
-      <c r="G4" s="262"/>
+      <c r="F4" s="265"/>
+      <c r="G4" s="265"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -36438,7 +36409,7 @@
       </c>
       <c r="C5" s="171">
         <f ca="1">Overview!C5</f>
-        <v>141.93</v>
+        <v>143.04</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="134" t="s">
@@ -36454,7 +36425,7 @@
       </c>
       <c r="C6" s="172">
         <f ca="1">Statement!AC149</f>
-        <v>7113815.46</v>
+        <v>7169450.8799999999</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>20</v>
@@ -36474,7 +36445,7 @@
       </c>
       <c r="C7" s="172">
         <f ca="1">Statement!AC150</f>
-        <v>5697256.46</v>
+        <v>5752891.8799999999</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>32</v>
@@ -36494,7 +36465,7 @@
       </c>
       <c r="C8" s="173">
         <f ca="1">Statement!AC146</f>
-        <v>45.192045916970358</v>
+        <v>45.54548191336179</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>247</v>
@@ -36514,7 +36485,7 @@
       </c>
       <c r="C9" s="173">
         <f ca="1">Statement!AC147</f>
-        <v>6.0951090523611153</v>
+        <v>6.1427774173869789</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>248</v>
@@ -36534,7 +36505,7 @@
       </c>
       <c r="C10" s="173">
         <f ca="1">Statement!AC148</f>
-        <v>4.7103207395395756</v>
+        <v>4.7471590120745493</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -36554,7 +36525,7 @@
       </c>
       <c r="C11" s="173">
         <f ca="1">Statement!AC151</f>
-        <v>4.9757611427752968</v>
+        <v>5.0243509443651622</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -36563,18 +36534,18 @@
       </c>
       <c r="C12" s="173">
         <f ca="1">Statement!AC152</f>
-        <v>36.26862182894611</v>
+        <v>36.622795811185028</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="262" t="s">
+      <c r="B15" s="265" t="s">
         <v>78</v>
       </c>
-      <c r="C15" s="262"/>
-      <c r="E15" s="262" t="s">
+      <c r="C15" s="265"/>
+      <c r="E15" s="265" t="s">
         <v>250</v>
       </c>
-      <c r="F15" s="262"/>
+      <c r="F15" s="265"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -36625,14 +36596,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="262" t="s">
+      <c r="B21" s="265" t="s">
         <v>249</v>
       </c>
-      <c r="C21" s="262"/>
-      <c r="E21" s="262" t="s">
+      <c r="C21" s="265"/>
+      <c r="E21" s="265" t="s">
         <v>253</v>
       </c>
-      <c r="F21" s="262"/>
+      <c r="F21" s="265"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -36701,14 +36672,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="262" t="s">
+      <c r="B29" s="265" t="s">
         <v>254</v>
       </c>
-      <c r="C29" s="262"/>
-      <c r="E29" s="262" t="s">
+      <c r="C29" s="265"/>
+      <c r="E29" s="265" t="s">
         <v>260</v>
       </c>
-      <c r="F29" s="262"/>
+      <c r="F29" s="265"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -36784,14 +36755,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="262" t="s">
+      <c r="B37" s="265" t="s">
         <v>272</v>
       </c>
-      <c r="C37" s="262"/>
-      <c r="E37" s="262" t="s">
+      <c r="C37" s="265"/>
+      <c r="E37" s="265" t="s">
         <v>275</v>
       </c>
-      <c r="F37" s="262"/>
+      <c r="F37" s="265"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -36799,7 +36770,7 @@
       </c>
       <c r="C38" s="174">
         <f ca="1">Statement!AC158</f>
-        <v>2.2127787749137588E-2</v>
+        <v>2.1956074631117855E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>274</v>
@@ -36815,7 +36786,7 @@
       </c>
       <c r="C39" s="214">
         <f ca="1">Statement!AC157</f>
-        <v>3.5539296938692309E-2</v>
+        <v>3.5263509609260342E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>276</v>
@@ -36847,7 +36818,7 @@
       </c>
       <c r="C41" s="174">
         <f ca="1">Statement!AC160</f>
-        <v>9.7842009525504342E-3</v>
+        <v>9.7082748965008608E-3</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -36856,18 +36827,18 @@
       </c>
       <c r="C42" s="174">
         <f ca="1">Statement!AC161</f>
-        <v>9.7842009525504342E-3</v>
+        <v>9.7082748965008608E-3</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="262" t="s">
+      <c r="B45" s="265" t="s">
         <v>283</v>
       </c>
-      <c r="C45" s="262"/>
-      <c r="E45" s="262" t="s">
+      <c r="C45" s="265"/>
+      <c r="E45" s="265" t="s">
         <v>289</v>
       </c>
-      <c r="F45" s="262"/>
+      <c r="F45" s="265"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -36900,18 +36871,18 @@
       </c>
       <c r="F48" s="174">
         <f ca="1">Statement!AC172</f>
-        <v>0.19912788122845121</v>
+        <v>0.19758263550583111</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="262" t="s">
+      <c r="B51" s="265" t="s">
         <v>286</v>
       </c>
-      <c r="C51" s="262"/>
-      <c r="E51" s="262" t="s">
+      <c r="C51" s="265"/>
+      <c r="E51" s="265" t="s">
         <v>307</v>
       </c>
-      <c r="F51" s="262"/>
+      <c r="F51" s="265"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -37079,7 +37050,7 @@
       </c>
       <c r="I6" s="171">
         <f ca="1">Statement!AC116</f>
-        <v>141.93</v>
+        <v>143.04</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -37108,7 +37079,7 @@
       </c>
       <c r="I7" s="172">
         <f ca="1">Statement!AC149</f>
-        <v>7113815.46</v>
+        <v>7169450.8799999999</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -37137,7 +37108,7 @@
       </c>
       <c r="I8" s="172">
         <f ca="1">Statement!AC150</f>
-        <v>5697256.46</v>
+        <v>5752891.8799999999</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -37166,7 +37137,7 @@
       </c>
       <c r="I9" s="173">
         <f ca="1">Statement!AC146</f>
-        <v>45.192045916970358</v>
+        <v>45.54548191336179</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -37195,7 +37166,7 @@
       </c>
       <c r="I10" s="173">
         <f ca="1">Statement!AC147</f>
-        <v>6.0951090523611153</v>
+        <v>6.1427774173869789</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -37224,7 +37195,7 @@
       </c>
       <c r="I11" s="173">
         <f ca="1">Statement!AC148</f>
-        <v>4.7103207395395756</v>
+        <v>4.7471590120745493</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -37253,7 +37224,7 @@
       </c>
       <c r="I12" s="173">
         <f ca="1">Statement!AC151</f>
-        <v>4.9757611427752968</v>
+        <v>5.0243509443651622</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -37282,7 +37253,7 @@
       </c>
       <c r="I13" s="173">
         <f ca="1">Statement!AC152</f>
-        <v>36.26862182894611</v>
+        <v>36.622795811185028</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -38055,7 +38026,7 @@
       </c>
       <c r="I51" s="174">
         <f ca="1">Statement!AC158</f>
-        <v>2.2127787749137588E-2</v>
+        <v>2.1956074631117855E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -38084,7 +38055,7 @@
       </c>
       <c r="I52" s="174">
         <f ca="1">Statement!AC157</f>
-        <v>3.5539296938692309E-2</v>
+        <v>3.5263509609260342E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -38142,7 +38113,7 @@
       </c>
       <c r="I54" s="174">
         <f ca="1">Statement!AC160</f>
-        <v>9.7842009525504342E-3</v>
+        <v>9.7082748965008608E-3</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -38171,7 +38142,7 @@
       </c>
       <c r="I55" s="174">
         <f ca="1">Statement!AC161</f>
-        <v>9.7842009525504342E-3</v>
+        <v>9.7082748965008608E-3</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -38407,7 +38378,7 @@
       </c>
       <c r="I68" s="195">
         <f ca="1">Statement!AC172</f>
-        <v>0.19912788122845121</v>
+        <v>0.19758263550583111</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -38950,14 +38921,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="265" t="s">
+      <c r="C3" s="266" t="s">
         <v>317</v>
       </c>
-      <c r="D3" s="266"/>
-      <c r="F3" s="267" t="s">
+      <c r="D3" s="267"/>
+      <c r="F3" s="268" t="s">
         <v>318</v>
       </c>
-      <c r="G3" s="266"/>
+      <c r="G3" s="267"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -39024,19 +38995,19 @@
       <c r="B7" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C7" s="263">
+      <c r="C7" s="269">
         <f>Statement!AA89</f>
         <v>2.2218264392893719E-2</v>
       </c>
-      <c r="D7" s="264"/>
-      <c r="F7" s="263">
+      <c r="D7" s="270"/>
+      <c r="F7" s="269">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.18309713991239371</v>
       </c>
-      <c r="G7" s="264"/>
+      <c r="G7" s="270"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="206" t="s">
@@ -39063,19 +39034,19 @@
       <c r="B9" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C9" s="263">
+      <c r="C9" s="269">
         <f>Statement!AA90</f>
         <v>3.6046202026093238E-2</v>
       </c>
-      <c r="D9" s="264"/>
-      <c r="F9" s="263">
+      <c r="D9" s="270"/>
+      <c r="F9" s="269">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.17263647322197348</v>
       </c>
-      <c r="G9" s="264"/>
+      <c r="G9" s="270"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="206" t="s">
@@ -39102,19 +39073,19 @@
       <c r="B11" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C11" s="263">
+      <c r="C11" s="269">
         <f>Statement!AA91</f>
         <v>1.710027405488606E-2</v>
       </c>
-      <c r="D11" s="264"/>
-      <c r="F11" s="263">
+      <c r="D11" s="270"/>
+      <c r="F11" s="269">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>0.1870895657269924</v>
       </c>
-      <c r="G11" s="264"/>
+      <c r="G11" s="270"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="206" t="s">
@@ -39141,19 +39112,19 @@
       <c r="B13" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C13" s="263">
+      <c r="C13" s="269">
         <f>Statement!AA95</f>
         <v>8.4392741251357012E-2</v>
       </c>
-      <c r="D13" s="264"/>
-      <c r="F13" s="263">
+      <c r="D13" s="270"/>
+      <c r="F13" s="269">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.22501976973287405</v>
       </c>
-      <c r="G13" s="264"/>
+      <c r="G13" s="270"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="206" t="s">
@@ -39180,19 +39151,19 @@
       <c r="B15" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C15" s="263">
+      <c r="C15" s="269">
         <f>Statement!AA96</f>
         <v>-0.23765355851505829</v>
       </c>
-      <c r="D15" s="264"/>
-      <c r="F15" s="263">
+      <c r="D15" s="270"/>
+      <c r="F15" s="269">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>1.7444474417768186E-2</v>
       </c>
-      <c r="G15" s="264"/>
+      <c r="G15" s="270"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="206" t="s">
@@ -39219,19 +39190,19 @@
       <c r="B17" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C17" s="263">
+      <c r="C17" s="269">
         <f>Statement!AA98</f>
         <v>-0.23704555913483663</v>
       </c>
-      <c r="D17" s="264"/>
-      <c r="F17" s="263">
+      <c r="D17" s="270"/>
+      <c r="F17" s="269">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>-0.25955204216073779</v>
       </c>
-      <c r="G17" s="264"/>
+      <c r="G17" s="270"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="206" t="s">
@@ -39258,22 +39229,22 @@
       <c r="B19" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C19" s="263">
+      <c r="C19" s="269">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>2.5565842762241744E-2</v>
       </c>
-      <c r="D19" s="264"/>
-      <c r="F19" s="263">
+      <c r="D19" s="270"/>
+      <c r="F19" s="269">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>2.5293753865182372E-2</v>
       </c>
-      <c r="G19" s="264"/>
+      <c r="G19" s="270"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="206" t="s">
@@ -39300,22 +39271,22 @@
       <c r="B21" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C21" s="263">
+      <c r="C21" s="269">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>-0.2584269662921348</v>
       </c>
-      <c r="D21" s="264"/>
-      <c r="F21" s="263">
+      <c r="D21" s="270"/>
+      <c r="F21" s="269">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>-0.27472527472527469</v>
       </c>
-      <c r="G21" s="264"/>
+      <c r="G21" s="270"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -39364,22 +39335,22 @@
       <c r="B25" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C25" s="263">
+      <c r="C25" s="269">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>2.840483364420425E-2</v>
       </c>
-      <c r="D25" s="264"/>
-      <c r="F25" s="263">
+      <c r="D25" s="270"/>
+      <c r="F25" s="269">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>0.22478379327694395</v>
       </c>
-      <c r="G25" s="264"/>
+      <c r="G25" s="270"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="str">
@@ -39407,22 +39378,22 @@
       <c r="B27" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C27" s="263">
+      <c r="C27" s="269">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>2.1247695740758708E-2</v>
       </c>
-      <c r="D27" s="264"/>
-      <c r="F27" s="263">
+      <c r="D27" s="270"/>
+      <c r="F27" s="269">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>2.1792942775323981E-2</v>
       </c>
-      <c r="G27" s="264"/>
+      <c r="G27" s="270"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="str">
@@ -39450,22 +39421,22 @@
       <c r="B29" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C29" s="263">
+      <c r="C29" s="269">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>-0.10674206945303526</v>
       </c>
-      <c r="D29" s="264"/>
-      <c r="F29" s="263">
+      <c r="D29" s="270"/>
+      <c r="F29" s="269">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>2.0816812053925456E-3</v>
       </c>
-      <c r="G29" s="264"/>
+      <c r="G29" s="270"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="str">
@@ -39493,22 +39464,22 @@
       <c r="B31" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C31" s="263">
+      <c r="C31" s="269">
         <f>IF(C30=0,
 IF(D30=0,0,IF(D30&gt;0,1,-1)),
 (D30-C30)/ABS(C30)
 )</f>
         <v>-5.2569263556713236E-2</v>
       </c>
-      <c r="D31" s="264"/>
-      <c r="F31" s="263">
+      <c r="D31" s="270"/>
+      <c r="F31" s="269">
         <f>IF(F30=0,
 IF(G30=0,0,IF(G30&gt;0,1,-1)),
 (G30-F30)/ABS(F30)
 )</f>
         <v>-0.22983638113570742</v>
       </c>
-      <c r="G31" s="264"/>
+      <c r="G31" s="270"/>
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B32" s="20" t="str">
@@ -39536,22 +39507,22 @@
       <c r="B33" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C33" s="263">
+      <c r="C33" s="269">
         <f>IF(C32=0,
 IF(D32=0,0,IF(D32&gt;0,1,-1)),
 (D32-C32)/ABS(C32)
 )</f>
         <v>0.84164222873900296</v>
       </c>
-      <c r="D33" s="264"/>
-      <c r="F33" s="263">
+      <c r="D33" s="270"/>
+      <c r="F33" s="269">
         <f>IF(F32=0,
 IF(G32=0,0,IF(G32&gt;0,1,-1)),
 (G32-F32)/ABS(F32)
 )</f>
         <v>1.482213438735178</v>
       </c>
-      <c r="G33" s="264"/>
+      <c r="G33" s="270"/>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B35" s="8" t="s">
@@ -39600,22 +39571,22 @@
       <c r="B37" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C37" s="263">
+      <c r="C37" s="269">
         <f>IF(C36=0,
 IF(D36=0,0,IF(D36&gt;0,1,-1)),
 (D36-C36)/ABS(C36)
 )</f>
         <v>3.8938053097345132E-2</v>
       </c>
-      <c r="D37" s="264"/>
-      <c r="F37" s="263">
+      <c r="D37" s="270"/>
+      <c r="F37" s="269">
         <f>IF(F36=0,
 IF(G36=0,0,IF(G36&gt;0,1,-1)),
 (G36-F36)/ABS(F36)
 )</f>
         <v>0.23060796645702306</v>
       </c>
-      <c r="G37" s="264"/>
+      <c r="G37" s="270"/>
     </row>
     <row r="38" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="str">
@@ -39643,22 +39614,22 @@
       <c r="B39" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C39" s="263">
+      <c r="C39" s="269">
         <f>IF(C38=0,
 IF(D38=0,0,IF(D38&gt;0,1,-1)),
 (D38-C38)/ABS(C38)
 )</f>
         <v>2.0319303338171262E-2</v>
       </c>
-      <c r="D39" s="264"/>
-      <c r="F39" s="263">
+      <c r="D39" s="270"/>
+      <c r="F39" s="269">
         <f>IF(F38=0,
 IF(G38=0,0,IF(G38&gt;0,1,-1)),
 (G38-F38)/ABS(F38)
 )</f>
         <v>9.5869056897895558E-2</v>
       </c>
-      <c r="G39" s="264"/>
+      <c r="G39" s="270"/>
     </row>
     <row r="40" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B40" s="20" t="str">
@@ -39686,22 +39657,22 @@
       <c r="B41" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C41" s="263">
+      <c r="C41" s="269">
         <f>IF(C40=0,
 IF(D40=0,0,IF(D40&gt;0,1,-1)),
 (D40-C40)/ABS(C40)
 )</f>
         <v>1.6E-2</v>
       </c>
-      <c r="D41" s="264"/>
-      <c r="F41" s="263">
+      <c r="D41" s="270"/>
+      <c r="F41" s="269">
         <f>IF(F40=0,
 IF(G40=0,0,IF(G40&gt;0,1,-1)),
 (G40-F40)/ABS(F40)
 )</f>
         <v>0.16513761467889909</v>
       </c>
-      <c r="G41" s="264"/>
+      <c r="G41" s="270"/>
     </row>
     <row r="42" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B42" s="20" t="str">
@@ -39729,22 +39700,22 @@
       <c r="B43" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C43" s="263">
+      <c r="C43" s="269">
         <f>IF(C42=0,
 IF(D42=0,0,IF(D42&gt;0,1,-1)),
 (D42-C42)/ABS(C42)
 )</f>
         <v>2.0750199521149242E-2</v>
       </c>
-      <c r="D43" s="264"/>
-      <c r="F43" s="263">
+      <c r="D43" s="270"/>
+      <c r="F43" s="269">
         <f>IF(F42=0,
 IF(G42=0,0,IF(G42&gt;0,1,-1)),
 (G42-F42)/ABS(F42)
 )</f>
         <v>8.9437819420783646E-2</v>
       </c>
-      <c r="G43" s="264"/>
+      <c r="G43" s="270"/>
     </row>
     <row r="44" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B44" s="20" t="str">
@@ -39772,22 +39743,22 @@
       <c r="B45" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C45" s="263">
+      <c r="C45" s="269">
         <f>IF(C44=0,
 IF(D44=0,0,IF(D44&gt;0,1,-1)),
 (D44-C44)/ABS(C44)
 )</f>
         <v>1.2209481933271921E-2</v>
       </c>
-      <c r="D45" s="264"/>
-      <c r="F45" s="263">
+      <c r="D45" s="270"/>
+      <c r="F45" s="269">
         <f>IF(F44=0,
 IF(G44=0,0,IF(G44&gt;0,1,-1)),
 (G44-F44)/ABS(F44)
 )</f>
         <v>5.119238950540856E-2</v>
       </c>
-      <c r="G45" s="264"/>
+      <c r="G45" s="270"/>
     </row>
     <row r="46" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="str">
@@ -39815,22 +39786,22 @@
       <c r="B47" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C47" s="263">
+      <c r="C47" s="269">
         <f>IF(C46=0,
 IF(D46=0,0,IF(D46&gt;0,1,-1)),
 (D46-C46)/ABS(C46)
 )</f>
         <v>1.8247963846473435E-2</v>
       </c>
-      <c r="D47" s="264"/>
-      <c r="F47" s="263">
+      <c r="D47" s="270"/>
+      <c r="F47" s="269">
         <f>IF(F46=0,
 IF(G46=0,0,IF(G46&gt;0,1,-1)),
 (G46-F46)/ABS(F46)
 )</f>
         <v>0.1229516507570132</v>
       </c>
-      <c r="G47" s="264"/>
+      <c r="G47" s="270"/>
     </row>
     <row r="48" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B48" s="20" t="str">
@@ -39858,22 +39829,22 @@
       <c r="B49" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C49" s="263">
+      <c r="C49" s="269">
         <f>IF(C48=0,
 IF(D48=0,0,IF(D48&gt;0,1,-1)),
 (D48-C48)/ABS(C48)
 )</f>
         <v>-4.2332859174963834E-3</v>
       </c>
-      <c r="D49" s="264"/>
-      <c r="F49" s="263">
+      <c r="D49" s="270"/>
+      <c r="F49" s="269">
         <f>IF(F48=0,
 IF(G48=0,0,IF(G48&gt;0,1,-1)),
 (G48-F48)/ABS(F48)
 )</f>
         <v>6.3208790635154666E-2</v>
       </c>
-      <c r="G49" s="264"/>
+      <c r="G49" s="270"/>
     </row>
     <row r="50" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B50" s="20" t="str">
@@ -39901,22 +39872,22 @@
       <c r="B51" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C51" s="263">
+      <c r="C51" s="269">
         <f>IF(C50=0,
 IF(D50=0,0,IF(D50&gt;0,1,-1)),
 (D50-C50)/ABS(C50)
 )</f>
         <v>4.8738292663854846E-4</v>
       </c>
-      <c r="D51" s="264"/>
-      <c r="F51" s="263">
+      <c r="D51" s="270"/>
+      <c r="F51" s="269">
         <f>IF(F50=0,
 IF(G50=0,0,IF(G50&gt;0,1,-1)),
 (G50-F50)/ABS(F50)
 )</f>
         <v>-6.2091544317255373E-2</v>
       </c>
-      <c r="G51" s="264"/>
+      <c r="G51" s="270"/>
     </row>
     <row r="52" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="str">
@@ -39944,43 +39915,39 @@
       <c r="B53" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C53" s="263">
+      <c r="C53" s="269">
         <f>IF(C52=0,
 IF(D52=0,0,IF(D52&gt;0,1,-1)),
 (D52-C52)/ABS(C52)
 )</f>
         <v>-8.8077740902117604E-2</v>
       </c>
-      <c r="D53" s="264"/>
-      <c r="F53" s="263">
+      <c r="D53" s="270"/>
+      <c r="F53" s="269">
         <f>IF(F52=0,
 IF(G52=0,0,IF(G52&gt;0,1,-1)),
 (G52-F52)/ABS(F52)
 )</f>
         <v>-0.37416005758387127</v>
       </c>
-      <c r="G53" s="264"/>
+      <c r="G53" s="270"/>
     </row>
   </sheetData>
   <mergeCells count="46">
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C53:D53"/>
+    <mergeCell ref="F53:G53"/>
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="F47:G47"/>
+    <mergeCell ref="C49:D49"/>
+    <mergeCell ref="F49:G49"/>
+    <mergeCell ref="C51:D51"/>
+    <mergeCell ref="F51:G51"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="F41:G41"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="F43:G43"/>
+    <mergeCell ref="C45:D45"/>
+    <mergeCell ref="F45:G45"/>
     <mergeCell ref="C37:D37"/>
     <mergeCell ref="F37:G37"/>
     <mergeCell ref="C39:D39"/>
@@ -39995,20 +39962,24 @@
     <mergeCell ref="F31:G31"/>
     <mergeCell ref="C33:D33"/>
     <mergeCell ref="F33:G33"/>
-    <mergeCell ref="C41:D41"/>
-    <mergeCell ref="F41:G41"/>
-    <mergeCell ref="C43:D43"/>
-    <mergeCell ref="F43:G43"/>
-    <mergeCell ref="C45:D45"/>
-    <mergeCell ref="F45:G45"/>
-    <mergeCell ref="C53:D53"/>
-    <mergeCell ref="F53:G53"/>
-    <mergeCell ref="C47:D47"/>
-    <mergeCell ref="F47:G47"/>
-    <mergeCell ref="C49:D49"/>
-    <mergeCell ref="F49:G49"/>
-    <mergeCell ref="C51:D51"/>
-    <mergeCell ref="F51:G51"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/DUOL.xlsx
+++ b/DUOL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40EBE32F-47B2-BA4A-A0A8-72332994F270}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E68D4584-8393-4645-A012-C78C4068655A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -2468,6 +2468,12 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2477,10 +2483,10 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2492,23 +2498,17 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -13203,13 +13203,13 @@
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>322.08999999999997</v>
+    <v>318.83999999999997</v>
     <v>87.89</v>
-    <v>1.0660000000000001</v>
-    <v>1.65</v>
-    <v>1.167E-2</v>
-    <v>-0.35</v>
-    <v>-2.447E-3</v>
+    <v>1.0646</v>
+    <v>-4.4400000000000004</v>
+    <v>-3.1040000000000002E-2</v>
+    <v>-3.1300000000000001E-2</v>
+    <v>-2.2579999999999999E-4</v>
     <v>USD</v>
     <v>Duolingo, Inc. is a technology company. The Company is engaged in offering a mobile learning platform, as well as a digital English language proficiency assessment exam. It operates a freemium business model, namely, the app and the Website are accessible free of charge, although Duolingo also offers premium services for a subscription fee. Its solutions consist of the Duolingo App, Super Duolingo, Duolingo Max, Duolingo English Test: AI-Driven Language Assessment, Duolingo for Schools, and Duolingo ABC. The Duolingo App offers courses in over 40 different languages, including Spanish, English, French, German, Italian, Portuguese, Japanese and Chinese. Duolingo can also be accessed on desktop computers via a Web browser. Its subscription offering, Super Duolingo, offers learners additional features to enhance their learning experience. The Duolingo English Test is an online, on-demand, high-stakes English proficiency assessment. It also operates an animation and motion design studio.</v>
     <v>900</v>
@@ -13217,25 +13217,25 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>5900 PENN AVE, SECOND FLOOR, PITTSBURGH, PA, 15206 US</v>
-    <v>146</v>
+    <v>141.5</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46318.946449560157</v>
+    <v>46321.851466666405</v>
     <v>0</v>
-    <v>137.86000000000001</v>
-    <v>6692308060</v>
+    <v>134.53</v>
+    <v>6484577022</v>
     <v>DUOLINGO, INC.</v>
     <v>DUOLINGO, INC.</v>
-    <v>139.5</v>
-    <v>16.853200000000001</v>
-    <v>141.38999999999999</v>
+    <v>140.72</v>
+    <v>16.520700000000001</v>
     <v>143.04</v>
-    <v>142.69</v>
+    <v>138.6</v>
+    <v>138.56870000000001</v>
     <v>46786270</v>
     <v>DUOL</v>
     <v>DUOLINGO, INC. (XNAS:DUOL)</v>
-    <v>763587</v>
-    <v>930380</v>
+    <v>1145639</v>
+    <v>905489</v>
     <v>2011</v>
   </rv>
   <rv s="2">
@@ -13259,17 +13259,17 @@
     <v>Powered by Refinitiv</v>
     <v>53.64</v>
     <v>39.47</v>
-    <v>-1.93</v>
-    <v>-3.7505000000000004E-2</v>
+    <v>0.35</v>
+    <v>7.0660000000000002E-3</v>
     <v>US</v>
-    <v>50.54</v>
+    <v>50.03</v>
     <v>Index</v>
     <v>3</v>
-    <v>49.39</v>
+    <v>49.55</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>50.4</v>
-    <v>51.46</v>
+    <v>49.92</v>
     <v>49.53</v>
+    <v>49.88</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -14095,7 +14095,7 @@
       </c>
       <c r="F3" s="186">
         <f ca="1">Statement!AC149</f>
-        <v>7169450.8799999999</v>
+        <v>6946909.1999999993</v>
       </c>
       <c r="H3" s="184" t="str">
         <f>'AVG target price'!B5</f>
@@ -14103,7 +14103,7 @@
       </c>
       <c r="I3" s="210">
         <f ca="1">'AVG target price'!C5</f>
-        <v>147.17410015769124</v>
+        <v>146.68025389330302</v>
       </c>
       <c r="K3" s="257" t="s">
         <v>441</v>
@@ -14122,7 +14122,7 @@
       </c>
       <c r="F4" s="187">
         <f ca="1">Statement!AC150</f>
-        <v>5752891.8799999999</v>
+        <v>5530350.1999999993</v>
       </c>
       <c r="H4" s="184" t="str">
         <f>'AVG target price'!B6</f>
@@ -14130,7 +14130,7 @@
       </c>
       <c r="I4" s="210">
         <f ca="1">'AVG target price'!C6</f>
-        <v>198.02442476307402</v>
+        <v>197.8129340897973</v>
       </c>
       <c r="K4" s="257" t="s">
         <v>442</v>
@@ -14142,7 +14142,7 @@
       </c>
       <c r="C5" s="207" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>143.04</v>
+        <v>138.6</v>
       </c>
       <c r="E5" s="184" t="s">
         <v>247</v>
@@ -14157,7 +14157,7 @@
       </c>
       <c r="I5" s="210">
         <f ca="1">'AVG target price'!C7</f>
-        <v>159.74574315816156</v>
+        <v>159.53703663079153</v>
       </c>
       <c r="K5" s="257" t="s">
         <v>443</v>
@@ -14169,14 +14169,14 @@
       </c>
       <c r="C6" s="207" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>142.69</v>
+        <v>138.56870000000001</v>
       </c>
       <c r="E6" s="184" t="s">
         <v>241</v>
       </c>
       <c r="F6" s="189">
         <f ca="1">Statement!AC146</f>
-        <v>45.54548191336179</v>
+        <v>44.131737927796031</v>
       </c>
       <c r="H6" s="184" t="str">
         <f>'AVG target price'!B8</f>
@@ -14184,7 +14184,7 @@
       </c>
       <c r="I6" s="210">
         <f ca="1">'AVG target price'!C8</f>
-        <v>203.55142215941146</v>
+        <v>203.33271050853264</v>
       </c>
       <c r="K6" s="258" t="s">
         <v>444</v>
@@ -14196,14 +14196,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>1.65</v>
+        <v>-4.4400000000000004</v>
       </c>
       <c r="E7" s="185" t="s">
         <v>205</v>
       </c>
       <c r="F7" s="190">
         <f ca="1">Statement!AC147</f>
-        <v>6.1427774173869789</v>
+        <v>5.9521039572835237</v>
       </c>
       <c r="H7" s="184" t="str">
         <f>'AVG target price'!B9</f>
@@ -14211,7 +14211,7 @@
       </c>
       <c r="I7" s="210">
         <f ca="1">'AVG target price'!C9</f>
-        <v>203.97380318825662</v>
+        <v>203.75453969996408</v>
       </c>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.2">
@@ -14220,14 +14220,14 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>-0.35</v>
+        <v>-3.1300000000000001E-2</v>
       </c>
       <c r="E8" s="184" t="s">
         <v>269</v>
       </c>
       <c r="F8" s="191">
         <f ca="1">Statement!AC157</f>
-        <v>3.5263509609260342E-2</v>
+        <v>3.6393163163842709E-2</v>
       </c>
       <c r="H8" s="183" t="str">
         <f>'AVG target price'!B10</f>
@@ -14235,7 +14235,7 @@
       </c>
       <c r="I8" s="211">
         <f ca="1">'AVG target price'!C10</f>
-        <v>182.49389868531898</v>
+        <v>182.22349496447771</v>
       </c>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.2">
@@ -14244,14 +14244,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>1.167E-2</v>
+        <v>-3.1040000000000002E-2</v>
       </c>
       <c r="E9" s="184" t="s">
         <v>292</v>
       </c>
       <c r="F9" s="191">
         <f ca="1">Statement!AC158</f>
-        <v>2.1956074631117855E-2</v>
+        <v>2.2659429402850637E-2</v>
       </c>
       <c r="H9" s="183" t="str">
         <f>'AVG target price'!B12</f>
@@ -14259,7 +14259,7 @@
       </c>
       <c r="I9" s="212">
         <f ca="1">'AVG target price'!C12</f>
-        <v>0.27582423577544041</v>
+        <v>0.31474383091253766</v>
       </c>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.2">
@@ -14268,14 +14268,14 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>-2.447E-3</v>
+        <v>-2.2579999999999999E-4</v>
       </c>
       <c r="E10" s="184" t="s">
         <v>297</v>
       </c>
       <c r="F10" s="191">
         <f ca="1">Statement!AC160</f>
-        <v>9.7082748965008608E-3</v>
+        <v>1.0019275910501321E-2</v>
       </c>
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.2">
@@ -14284,7 +14284,7 @@
       </c>
       <c r="C11" s="208" cm="1">
         <f t="array" aca="1" ref="C11" ca="1">_FV(C3,"52 week high",TRUE)</f>
-        <v>322.08999999999997</v>
+        <v>318.83999999999997</v>
       </c>
       <c r="E11" s="185" t="s">
         <v>293</v>
@@ -14323,7 +14323,7 @@
       </c>
       <c r="C13" s="208" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>1.0660000000000001</v>
+        <v>1.0646</v>
       </c>
       <c r="E13" s="184" t="s">
         <v>104</v>
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C14" s="209" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>930380</v>
+        <v>905489</v>
       </c>
       <c r="E14" s="185" t="s">
         <v>105</v>
@@ -14360,7 +14360,7 @@
       </c>
       <c r="I14" s="260">
         <f ca="1">'Reverse DCF'!C16</f>
-        <v>154.01937861223695</v>
+        <v>153.51406475701702</v>
       </c>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.2">
@@ -14369,7 +14369,7 @@
       </c>
       <c r="F15" s="191">
         <f ca="1">Statement!AC172</f>
-        <v>0.19758263550583111</v>
+        <v>0.20391212253069324</v>
       </c>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.2">
@@ -14402,7 +14402,7 @@
       </c>
       <c r="I17" s="255">
         <f ca="1">DCF!C15</f>
-        <v>9.7500000000000003E-2</v>
+        <v>9.7786999999999999E-2</v>
       </c>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.2">
@@ -14424,7 +14424,7 @@
       </c>
       <c r="I18" s="256">
         <f ca="1">Multiples!C54</f>
-        <v>9.7500000000000003E-2</v>
+        <v>9.7786999999999999E-2</v>
       </c>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
@@ -14497,7 +14497,7 @@
       </c>
       <c r="F26" s="218" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>49.53</v>
+        <v>49.88</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -14512,7 +14512,7 @@
       </c>
       <c r="F27" s="219">
         <f ca="1">F26/1000</f>
-        <v>4.9530000000000005E-2</v>
+        <v>4.9880000000000001E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -14840,8 +14840,8 @@
       <c r="D2" s="265"/>
       <c r="E2" s="265"/>
       <c r="F2" s="265"/>
-      <c r="G2" s="274"/>
-      <c r="H2" s="275" t="s">
+      <c r="G2" s="271"/>
+      <c r="H2" s="272" t="s">
         <v>114</v>
       </c>
       <c r="I2" s="265"/>
@@ -14874,32 +14874,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="271" t="s">
+      <c r="C4" s="273" t="s">
         <v>116</v>
       </c>
-      <c r="D4" s="271"/>
-      <c r="E4" s="271"/>
-      <c r="F4" s="271"/>
-      <c r="G4" s="271"/>
-      <c r="H4" s="271"/>
-      <c r="I4" s="271"/>
-      <c r="J4" s="271"/>
-      <c r="K4" s="271"/>
-      <c r="L4" s="271"/>
+      <c r="D4" s="273"/>
+      <c r="E4" s="273"/>
+      <c r="F4" s="273"/>
+      <c r="G4" s="273"/>
+      <c r="H4" s="273"/>
+      <c r="I4" s="273"/>
+      <c r="J4" s="273"/>
+      <c r="K4" s="273"/>
+      <c r="L4" s="273"/>
       <c r="O4" s="5"/>
-      <c r="S4" s="272" t="s">
+      <c r="S4" s="274" t="s">
         <v>116</v>
       </c>
-      <c r="T4" s="273"/>
-      <c r="U4" s="273"/>
-      <c r="V4" s="273"/>
-      <c r="W4" s="273"/>
-      <c r="X4" s="273"/>
-      <c r="Y4" s="273"/>
-      <c r="Z4" s="273"/>
-      <c r="AA4" s="273"/>
-      <c r="AB4" s="273"/>
-      <c r="AC4" s="273"/>
+      <c r="T4" s="275"/>
+      <c r="U4" s="275"/>
+      <c r="V4" s="275"/>
+      <c r="W4" s="275"/>
+      <c r="X4" s="275"/>
+      <c r="Y4" s="275"/>
+      <c r="Z4" s="275"/>
+      <c r="AA4" s="275"/>
+      <c r="AB4" s="275"/>
+      <c r="AC4" s="275"/>
       <c r="AE4" s="88"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -15587,33 +15587,33 @@
       <c r="Q12" s="92"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="271" t="s">
+      <c r="C13" s="273" t="s">
         <v>122</v>
       </c>
-      <c r="D13" s="271"/>
-      <c r="E13" s="271"/>
-      <c r="F13" s="271"/>
-      <c r="G13" s="271"/>
-      <c r="H13" s="271"/>
-      <c r="I13" s="271"/>
-      <c r="J13" s="271"/>
-      <c r="K13" s="271"/>
-      <c r="L13" s="271"/>
+      <c r="D13" s="273"/>
+      <c r="E13" s="273"/>
+      <c r="F13" s="273"/>
+      <c r="G13" s="273"/>
+      <c r="H13" s="273"/>
+      <c r="I13" s="273"/>
+      <c r="J13" s="273"/>
+      <c r="K13" s="273"/>
+      <c r="L13" s="273"/>
       <c r="O13" s="5"/>
       <c r="Q13" s="92"/>
-      <c r="S13" s="272" t="s">
+      <c r="S13" s="274" t="s">
         <v>122</v>
       </c>
-      <c r="T13" s="273"/>
-      <c r="U13" s="273"/>
-      <c r="V13" s="273"/>
-      <c r="W13" s="273"/>
-      <c r="X13" s="273"/>
-      <c r="Y13" s="273"/>
-      <c r="Z13" s="273"/>
-      <c r="AA13" s="273"/>
-      <c r="AB13" s="273"/>
-      <c r="AC13" s="273"/>
+      <c r="T13" s="275"/>
+      <c r="U13" s="275"/>
+      <c r="V13" s="275"/>
+      <c r="W13" s="275"/>
+      <c r="X13" s="275"/>
+      <c r="Y13" s="275"/>
+      <c r="Z13" s="275"/>
+      <c r="AA13" s="275"/>
+      <c r="AB13" s="275"/>
+      <c r="AC13" s="275"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B14" s="16" t="s">
@@ -16222,33 +16222,33 @@
       <c r="Q22" s="92"/>
     </row>
     <row r="23" spans="2:31" x14ac:dyDescent="0.2">
-      <c r="C23" s="271" t="s">
+      <c r="C23" s="273" t="s">
         <v>124</v>
       </c>
-      <c r="D23" s="271"/>
-      <c r="E23" s="271"/>
-      <c r="F23" s="271"/>
-      <c r="G23" s="271"/>
-      <c r="H23" s="271"/>
-      <c r="I23" s="271"/>
-      <c r="J23" s="271"/>
-      <c r="K23" s="271"/>
-      <c r="L23" s="271"/>
+      <c r="D23" s="273"/>
+      <c r="E23" s="273"/>
+      <c r="F23" s="273"/>
+      <c r="G23" s="273"/>
+      <c r="H23" s="273"/>
+      <c r="I23" s="273"/>
+      <c r="J23" s="273"/>
+      <c r="K23" s="273"/>
+      <c r="L23" s="273"/>
       <c r="O23" s="5"/>
       <c r="Q23" s="92"/>
-      <c r="S23" s="272" t="s">
+      <c r="S23" s="274" t="s">
         <v>124</v>
       </c>
-      <c r="T23" s="273"/>
-      <c r="U23" s="273"/>
-      <c r="V23" s="273"/>
-      <c r="W23" s="273"/>
-      <c r="X23" s="273"/>
-      <c r="Y23" s="273"/>
-      <c r="Z23" s="273"/>
-      <c r="AA23" s="273"/>
-      <c r="AB23" s="273"/>
-      <c r="AC23" s="273"/>
+      <c r="T23" s="275"/>
+      <c r="U23" s="275"/>
+      <c r="V23" s="275"/>
+      <c r="W23" s="275"/>
+      <c r="X23" s="275"/>
+      <c r="Y23" s="275"/>
+      <c r="Z23" s="275"/>
+      <c r="AA23" s="275"/>
+      <c r="AB23" s="275"/>
+      <c r="AC23" s="275"/>
       <c r="AE23" s="88" t="str">
         <f>AE2</f>
         <v>TTM/YTD</v>
@@ -17567,32 +17567,32 @@
       <c r="O39" s="5"/>
     </row>
     <row r="40" spans="2:31" x14ac:dyDescent="0.2">
-      <c r="C40" s="271" t="s">
+      <c r="C40" s="273" t="s">
         <v>126</v>
       </c>
-      <c r="D40" s="271"/>
-      <c r="E40" s="271"/>
-      <c r="F40" s="271"/>
-      <c r="G40" s="271"/>
-      <c r="H40" s="271"/>
-      <c r="I40" s="271"/>
-      <c r="J40" s="271"/>
-      <c r="K40" s="271"/>
-      <c r="L40" s="271"/>
+      <c r="D40" s="273"/>
+      <c r="E40" s="273"/>
+      <c r="F40" s="273"/>
+      <c r="G40" s="273"/>
+      <c r="H40" s="273"/>
+      <c r="I40" s="273"/>
+      <c r="J40" s="273"/>
+      <c r="K40" s="273"/>
+      <c r="L40" s="273"/>
       <c r="O40" s="5"/>
-      <c r="S40" s="272" t="s">
+      <c r="S40" s="274" t="s">
         <v>126</v>
       </c>
-      <c r="T40" s="273"/>
-      <c r="U40" s="273"/>
-      <c r="V40" s="273"/>
-      <c r="W40" s="273"/>
-      <c r="X40" s="273"/>
-      <c r="Y40" s="273"/>
-      <c r="Z40" s="273"/>
-      <c r="AA40" s="273"/>
-      <c r="AB40" s="273"/>
-      <c r="AC40" s="273"/>
+      <c r="T40" s="275"/>
+      <c r="U40" s="275"/>
+      <c r="V40" s="275"/>
+      <c r="W40" s="275"/>
+      <c r="X40" s="275"/>
+      <c r="Y40" s="275"/>
+      <c r="Z40" s="275"/>
+      <c r="AA40" s="275"/>
+      <c r="AB40" s="275"/>
+      <c r="AC40" s="275"/>
     </row>
     <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -18159,18 +18159,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="C13:L13"/>
+    <mergeCell ref="S13:AC13"/>
+    <mergeCell ref="C23:L23"/>
+    <mergeCell ref="S23:AC23"/>
+    <mergeCell ref="C40:L40"/>
+    <mergeCell ref="S40:AC40"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="S2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
-    <mergeCell ref="C13:L13"/>
-    <mergeCell ref="S13:AC13"/>
-    <mergeCell ref="C23:L23"/>
-    <mergeCell ref="S23:AC23"/>
-    <mergeCell ref="C40:L40"/>
-    <mergeCell ref="S40:AC40"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -18210,8 +18210,8 @@
       <c r="D2" s="265"/>
       <c r="E2" s="265"/>
       <c r="F2" s="265"/>
-      <c r="G2" s="274"/>
-      <c r="H2" s="275" t="s">
+      <c r="G2" s="271"/>
+      <c r="H2" s="272" t="s">
         <v>114</v>
       </c>
       <c r="I2" s="265"/>
@@ -18241,31 +18241,31 @@
     <row r="4" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="271" t="s">
+      <c r="C4" s="273" t="s">
         <v>116</v>
       </c>
-      <c r="D4" s="271"/>
-      <c r="E4" s="271"/>
-      <c r="F4" s="271"/>
-      <c r="G4" s="271"/>
-      <c r="H4" s="271"/>
-      <c r="I4" s="271"/>
-      <c r="J4" s="271"/>
-      <c r="K4" s="271"/>
-      <c r="L4" s="271"/>
-      <c r="P4" s="273" t="s">
+      <c r="D4" s="273"/>
+      <c r="E4" s="273"/>
+      <c r="F4" s="273"/>
+      <c r="G4" s="273"/>
+      <c r="H4" s="273"/>
+      <c r="I4" s="273"/>
+      <c r="J4" s="273"/>
+      <c r="K4" s="273"/>
+      <c r="L4" s="273"/>
+      <c r="P4" s="275" t="s">
         <v>116</v>
       </c>
-      <c r="Q4" s="273"/>
-      <c r="R4" s="273"/>
-      <c r="S4" s="273"/>
-      <c r="T4" s="273"/>
-      <c r="U4" s="273"/>
-      <c r="V4" s="273"/>
-      <c r="W4" s="273"/>
-      <c r="X4" s="273"/>
-      <c r="Y4" s="273"/>
-      <c r="Z4" s="273"/>
+      <c r="Q4" s="275"/>
+      <c r="R4" s="275"/>
+      <c r="S4" s="275"/>
+      <c r="T4" s="275"/>
+      <c r="U4" s="275"/>
+      <c r="V4" s="275"/>
+      <c r="W4" s="275"/>
+      <c r="X4" s="275"/>
+      <c r="Y4" s="275"/>
+      <c r="Z4" s="275"/>
       <c r="AB4" s="88"/>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
@@ -18460,32 +18460,32 @@
       <c r="N8" s="92"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C9" s="271" t="s">
+      <c r="C9" s="273" t="s">
         <v>129</v>
       </c>
-      <c r="D9" s="271"/>
-      <c r="E9" s="271"/>
-      <c r="F9" s="271"/>
-      <c r="G9" s="271"/>
-      <c r="H9" s="271"/>
-      <c r="I9" s="271"/>
-      <c r="J9" s="271"/>
-      <c r="K9" s="271"/>
-      <c r="L9" s="271"/>
+      <c r="D9" s="273"/>
+      <c r="E9" s="273"/>
+      <c r="F9" s="273"/>
+      <c r="G9" s="273"/>
+      <c r="H9" s="273"/>
+      <c r="I9" s="273"/>
+      <c r="J9" s="273"/>
+      <c r="K9" s="273"/>
+      <c r="L9" s="273"/>
       <c r="N9" s="92"/>
-      <c r="P9" s="273" t="s">
+      <c r="P9" s="275" t="s">
         <v>130</v>
       </c>
-      <c r="Q9" s="273"/>
-      <c r="R9" s="273"/>
-      <c r="S9" s="273"/>
-      <c r="T9" s="273"/>
-      <c r="U9" s="273"/>
-      <c r="V9" s="273"/>
-      <c r="W9" s="273"/>
-      <c r="X9" s="273"/>
-      <c r="Y9" s="273"/>
-      <c r="Z9" s="273"/>
+      <c r="Q9" s="275"/>
+      <c r="R9" s="275"/>
+      <c r="S9" s="275"/>
+      <c r="T9" s="275"/>
+      <c r="U9" s="275"/>
+      <c r="V9" s="275"/>
+      <c r="W9" s="275"/>
+      <c r="X9" s="275"/>
+      <c r="Y9" s="275"/>
+      <c r="Z9" s="275"/>
       <c r="AB9" s="88">
         <f>AB4</f>
         <v>0</v>
@@ -19055,31 +19055,31 @@
       </c>
     </row>
     <row r="18" spans="2:26" x14ac:dyDescent="0.2">
-      <c r="C18" s="271" t="s">
+      <c r="C18" s="273" t="s">
         <v>132</v>
       </c>
-      <c r="D18" s="271"/>
-      <c r="E18" s="271"/>
-      <c r="F18" s="271"/>
-      <c r="G18" s="271"/>
-      <c r="H18" s="271"/>
-      <c r="I18" s="271"/>
-      <c r="J18" s="271"/>
-      <c r="K18" s="271"/>
-      <c r="L18" s="271"/>
-      <c r="P18" s="273" t="s">
+      <c r="D18" s="273"/>
+      <c r="E18" s="273"/>
+      <c r="F18" s="273"/>
+      <c r="G18" s="273"/>
+      <c r="H18" s="273"/>
+      <c r="I18" s="273"/>
+      <c r="J18" s="273"/>
+      <c r="K18" s="273"/>
+      <c r="L18" s="273"/>
+      <c r="P18" s="275" t="s">
         <v>132</v>
       </c>
-      <c r="Q18" s="273"/>
-      <c r="R18" s="273"/>
-      <c r="S18" s="273"/>
-      <c r="T18" s="273"/>
-      <c r="U18" s="273"/>
-      <c r="V18" s="273"/>
-      <c r="W18" s="273"/>
-      <c r="X18" s="273"/>
-      <c r="Y18" s="273"/>
-      <c r="Z18" s="273"/>
+      <c r="Q18" s="275"/>
+      <c r="R18" s="275"/>
+      <c r="S18" s="275"/>
+      <c r="T18" s="275"/>
+      <c r="U18" s="275"/>
+      <c r="V18" s="275"/>
+      <c r="W18" s="275"/>
+      <c r="X18" s="275"/>
+      <c r="Y18" s="275"/>
+      <c r="Z18" s="275"/>
     </row>
     <row r="19" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -19645,8 +19645,8 @@
       <c r="D3" s="265"/>
       <c r="E3" s="265"/>
       <c r="F3" s="265"/>
-      <c r="G3" s="274"/>
-      <c r="H3" s="275" t="s">
+      <c r="G3" s="271"/>
+      <c r="H3" s="272" t="s">
         <v>114</v>
       </c>
       <c r="I3" s="265"/>
@@ -19670,18 +19670,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="87"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="271" t="s">
+      <c r="C5" s="273" t="s">
         <v>116</v>
       </c>
-      <c r="D5" s="271"/>
-      <c r="E5" s="271"/>
-      <c r="F5" s="271"/>
-      <c r="G5" s="271"/>
-      <c r="H5" s="271"/>
-      <c r="I5" s="271"/>
-      <c r="J5" s="271"/>
-      <c r="K5" s="271"/>
-      <c r="L5" s="271"/>
+      <c r="D5" s="273"/>
+      <c r="E5" s="273"/>
+      <c r="F5" s="273"/>
+      <c r="G5" s="273"/>
+      <c r="H5" s="273"/>
+      <c r="I5" s="273"/>
+      <c r="J5" s="273"/>
+      <c r="K5" s="273"/>
+      <c r="L5" s="273"/>
       <c r="P5" s="276"/>
       <c r="Q5" s="276"/>
       <c r="R5" s="276"/>
@@ -19878,18 +19878,18 @@
       <c r="N10" s="92"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="271" t="s">
+      <c r="C11" s="273" t="s">
         <v>136</v>
       </c>
-      <c r="D11" s="271"/>
-      <c r="E11" s="271"/>
-      <c r="F11" s="271"/>
-      <c r="G11" s="271"/>
-      <c r="H11" s="271"/>
-      <c r="I11" s="271"/>
-      <c r="J11" s="271"/>
-      <c r="K11" s="271"/>
-      <c r="L11" s="271"/>
+      <c r="D11" s="273"/>
+      <c r="E11" s="273"/>
+      <c r="F11" s="273"/>
+      <c r="G11" s="273"/>
+      <c r="H11" s="273"/>
+      <c r="I11" s="273"/>
+      <c r="J11" s="273"/>
+      <c r="K11" s="273"/>
+      <c r="L11" s="273"/>
       <c r="N11" s="92"/>
       <c r="P11" s="276"/>
       <c r="Q11" s="276"/>
@@ -20143,18 +20143,18 @@
       <c r="D16" s="24"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="271" t="s">
+      <c r="C18" s="273" t="s">
         <v>141</v>
       </c>
-      <c r="D18" s="271"/>
-      <c r="E18" s="271"/>
-      <c r="F18" s="271"/>
-      <c r="G18" s="271"/>
-      <c r="H18" s="271"/>
-      <c r="I18" s="271"/>
-      <c r="J18" s="271"/>
-      <c r="K18" s="271"/>
-      <c r="L18" s="271"/>
+      <c r="D18" s="273"/>
+      <c r="E18" s="273"/>
+      <c r="F18" s="273"/>
+      <c r="G18" s="273"/>
+      <c r="H18" s="273"/>
+      <c r="I18" s="273"/>
+      <c r="J18" s="273"/>
+      <c r="K18" s="273"/>
+      <c r="L18" s="273"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -20372,18 +20372,18 @@
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="111"/>
-      <c r="C26" s="271" t="s">
+      <c r="C26" s="273" t="s">
         <v>147</v>
       </c>
-      <c r="D26" s="271"/>
-      <c r="E26" s="271"/>
-      <c r="F26" s="271"/>
-      <c r="G26" s="271"/>
-      <c r="H26" s="271"/>
-      <c r="I26" s="271"/>
-      <c r="J26" s="271"/>
-      <c r="K26" s="271"/>
-      <c r="L26" s="271"/>
+      <c r="D26" s="273"/>
+      <c r="E26" s="273"/>
+      <c r="F26" s="273"/>
+      <c r="G26" s="273"/>
+      <c r="H26" s="273"/>
+      <c r="I26" s="273"/>
+      <c r="J26" s="273"/>
+      <c r="K26" s="273"/>
+      <c r="L26" s="273"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="16" t="s">
@@ -20575,18 +20575,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="111"/>
-      <c r="C33" s="271" t="s">
+      <c r="C33" s="273" t="s">
         <v>151</v>
       </c>
-      <c r="D33" s="271"/>
-      <c r="E33" s="271"/>
-      <c r="F33" s="271"/>
-      <c r="G33" s="271"/>
-      <c r="H33" s="271"/>
-      <c r="I33" s="271"/>
-      <c r="J33" s="271"/>
-      <c r="K33" s="271"/>
-      <c r="L33" s="271"/>
+      <c r="D33" s="273"/>
+      <c r="E33" s="273"/>
+      <c r="F33" s="273"/>
+      <c r="G33" s="273"/>
+      <c r="H33" s="273"/>
+      <c r="I33" s="273"/>
+      <c r="J33" s="273"/>
+      <c r="K33" s="273"/>
+      <c r="L33" s="273"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
@@ -20770,18 +20770,18 @@
       <c r="C39" s="127"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="271" t="s">
+      <c r="C40" s="273" t="s">
         <v>154</v>
       </c>
-      <c r="D40" s="271"/>
-      <c r="E40" s="271"/>
-      <c r="F40" s="271"/>
-      <c r="G40" s="271"/>
-      <c r="H40" s="271"/>
-      <c r="I40" s="271"/>
-      <c r="J40" s="271"/>
-      <c r="K40" s="271"/>
-      <c r="L40" s="271"/>
+      <c r="D40" s="273"/>
+      <c r="E40" s="273"/>
+      <c r="F40" s="273"/>
+      <c r="G40" s="273"/>
+      <c r="H40" s="273"/>
+      <c r="I40" s="273"/>
+      <c r="J40" s="273"/>
+      <c r="K40" s="273"/>
+      <c r="L40" s="273"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -21045,6 +21045,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -21052,12 +21058,6 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -21101,8 +21101,8 @@
       <c r="D2" s="265"/>
       <c r="E2" s="265"/>
       <c r="F2" s="265"/>
-      <c r="G2" s="274"/>
-      <c r="H2" s="275" t="s">
+      <c r="G2" s="271"/>
+      <c r="H2" s="272" t="s">
         <v>114</v>
       </c>
       <c r="I2" s="265"/>
@@ -21126,18 +21126,18 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="271" t="s">
+      <c r="C4" s="273" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="271"/>
-      <c r="E4" s="271"/>
-      <c r="F4" s="271"/>
-      <c r="G4" s="271"/>
-      <c r="H4" s="271"/>
-      <c r="I4" s="271"/>
-      <c r="J4" s="271"/>
-      <c r="K4" s="271"/>
-      <c r="L4" s="271"/>
+      <c r="D4" s="273"/>
+      <c r="E4" s="273"/>
+      <c r="F4" s="273"/>
+      <c r="G4" s="273"/>
+      <c r="H4" s="273"/>
+      <c r="I4" s="273"/>
+      <c r="J4" s="273"/>
+      <c r="K4" s="273"/>
+      <c r="L4" s="273"/>
       <c r="S4" s="276"/>
       <c r="T4" s="276"/>
       <c r="U4" s="276"/>
@@ -21511,18 +21511,18 @@
       <c r="AE10" s="64"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="271" t="s">
+      <c r="C13" s="273" t="s">
         <v>162</v>
       </c>
-      <c r="D13" s="271"/>
-      <c r="E13" s="271"/>
-      <c r="F13" s="271"/>
-      <c r="G13" s="271"/>
-      <c r="H13" s="271"/>
-      <c r="I13" s="271"/>
-      <c r="J13" s="271"/>
-      <c r="K13" s="271"/>
-      <c r="L13" s="271"/>
+      <c r="D13" s="273"/>
+      <c r="E13" s="273"/>
+      <c r="F13" s="273"/>
+      <c r="G13" s="273"/>
+      <c r="H13" s="273"/>
+      <c r="I13" s="273"/>
+      <c r="J13" s="273"/>
+      <c r="K13" s="273"/>
+      <c r="L13" s="273"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="12">
@@ -21615,18 +21615,18 @@
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C18" s="271" t="s">
+      <c r="C18" s="273" t="s">
         <v>163</v>
       </c>
-      <c r="D18" s="271"/>
-      <c r="E18" s="271"/>
-      <c r="F18" s="271"/>
-      <c r="G18" s="271"/>
-      <c r="H18" s="271"/>
-      <c r="I18" s="271"/>
-      <c r="J18" s="271"/>
-      <c r="K18" s="271"/>
-      <c r="L18" s="271"/>
+      <c r="D18" s="273"/>
+      <c r="E18" s="273"/>
+      <c r="F18" s="273"/>
+      <c r="G18" s="273"/>
+      <c r="H18" s="273"/>
+      <c r="I18" s="273"/>
+      <c r="J18" s="273"/>
+      <c r="K18" s="273"/>
+      <c r="L18" s="273"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -21818,18 +21818,18 @@
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C25" s="271" t="s">
+      <c r="C25" s="273" t="s">
         <v>266</v>
       </c>
-      <c r="D25" s="271"/>
-      <c r="E25" s="271"/>
-      <c r="F25" s="271"/>
-      <c r="G25" s="271"/>
-      <c r="H25" s="271"/>
-      <c r="I25" s="271"/>
-      <c r="J25" s="271"/>
-      <c r="K25" s="271"/>
-      <c r="L25" s="271"/>
+      <c r="D25" s="273"/>
+      <c r="E25" s="273"/>
+      <c r="F25" s="273"/>
+      <c r="G25" s="273"/>
+      <c r="H25" s="273"/>
+      <c r="I25" s="273"/>
+      <c r="J25" s="273"/>
+      <c r="K25" s="273"/>
+      <c r="L25" s="273"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B26" s="16" t="s">
@@ -21967,18 +21967,18 @@
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C31" s="271" t="s">
+      <c r="C31" s="273" t="s">
         <v>78</v>
       </c>
-      <c r="D31" s="271"/>
-      <c r="E31" s="271"/>
-      <c r="F31" s="271"/>
-      <c r="G31" s="271"/>
-      <c r="H31" s="271"/>
-      <c r="I31" s="271"/>
-      <c r="J31" s="271"/>
-      <c r="K31" s="271"/>
-      <c r="L31" s="271"/>
+      <c r="D31" s="273"/>
+      <c r="E31" s="273"/>
+      <c r="F31" s="273"/>
+      <c r="G31" s="273"/>
+      <c r="H31" s="273"/>
+      <c r="I31" s="273"/>
+      <c r="J31" s="273"/>
+      <c r="K31" s="273"/>
+      <c r="L31" s="273"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="16" t="s">
@@ -22117,16 +22117,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="S4:AC4"/>
+    <mergeCell ref="C13:L13"/>
+    <mergeCell ref="C18:L18"/>
     <mergeCell ref="C31:L31"/>
     <mergeCell ref="C25:L25"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="S2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="S4:AC4"/>
-    <mergeCell ref="C13:L13"/>
-    <mergeCell ref="C18:L18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -22248,7 +22248,7 @@
       </c>
       <c r="C6" s="135">
         <f ca="1">Overview!C5</f>
-        <v>143.04</v>
+        <v>138.6</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22257,7 +22257,7 @@
       </c>
       <c r="C7" s="136">
         <f ca="1">C5*C6</f>
-        <v>7169450.8799999999</v>
+        <v>6946909.1999999993</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22275,7 +22275,7 @@
       </c>
       <c r="C9" s="137">
         <f ca="1">Overview!F27</f>
-        <v>4.9530000000000005E-2</v>
+        <v>4.9880000000000001E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22284,7 +22284,7 @@
       </c>
       <c r="C10" s="135">
         <f ca="1">Overview!C13</f>
-        <v>1.0660000000000001</v>
+        <v>1.0646</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22354,7 +22354,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>9.7500000000000003E-2</v>
+        <v>9.7786999999999999E-2</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22363,7 +22363,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>9.7500000000000003E-2</v>
+        <v>9.7786999999999999E-2</v>
       </c>
     </row>
   </sheetData>
@@ -22414,8 +22414,8 @@
       <c r="D3" s="265"/>
       <c r="E3" s="265"/>
       <c r="F3" s="265"/>
-      <c r="G3" s="274"/>
-      <c r="H3" s="275" t="s">
+      <c r="G3" s="271"/>
+      <c r="H3" s="272" t="s">
         <v>114</v>
       </c>
       <c r="I3" s="265"/>
@@ -22439,18 +22439,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="87"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="271" t="s">
+      <c r="C5" s="273" t="s">
         <v>184</v>
       </c>
-      <c r="D5" s="271"/>
-      <c r="E5" s="271"/>
-      <c r="F5" s="271"/>
-      <c r="G5" s="271"/>
-      <c r="H5" s="271"/>
-      <c r="I5" s="271"/>
-      <c r="J5" s="271"/>
-      <c r="K5" s="271"/>
-      <c r="L5" s="271"/>
+      <c r="D5" s="273"/>
+      <c r="E5" s="273"/>
+      <c r="F5" s="273"/>
+      <c r="G5" s="273"/>
+      <c r="H5" s="273"/>
+      <c r="I5" s="273"/>
+      <c r="J5" s="273"/>
+      <c r="K5" s="273"/>
+      <c r="L5" s="273"/>
       <c r="P5" s="276"/>
       <c r="Q5" s="276"/>
       <c r="R5" s="276"/>
@@ -22614,7 +22614,7 @@
       </c>
       <c r="L8" s="128">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>7554563.3723707823</v>
+        <v>7526690.3384721829</v>
       </c>
       <c r="N8" s="92"/>
       <c r="O8" s="16"/>
@@ -22668,23 +22668,23 @@
       <c r="G10" s="140"/>
       <c r="H10" s="128">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>164713.59638382119</v>
+        <v>164670.5344764</v>
       </c>
       <c r="I10" s="128">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>199685.05585775024</v>
+        <v>199580.66016047809</v>
       </c>
       <c r="J10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>228065.31271136957</v>
+        <v>227886.48667114065</v>
       </c>
       <c r="K10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>262692.12039560592</v>
+        <v>262417.52039291413</v>
       </c>
       <c r="L10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>360485.87709661247</v>
+        <v>360014.90520035184</v>
       </c>
       <c r="N10" s="92"/>
     </row>
@@ -22703,7 +22703,7 @@
       <c r="K11" s="139"/>
       <c r="L11" s="128">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>4744459.2856586417</v>
+        <v>4720778.5787388496</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
@@ -22726,7 +22726,7 @@
       </c>
       <c r="C15" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>9.7500000000000003E-2</v>
+        <v>9.7786999999999999E-2</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
@@ -22741,7 +22741,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>1215641.9624451594</v>
+        <v>1214570.1069012848</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -22750,7 +22750,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>4744459.2856586417</v>
+        <v>4720778.5787388496</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -22759,7 +22759,7 @@
       </c>
       <c r="C21" s="95">
         <f ca="1">C19+C20</f>
-        <v>5960101.2481038012</v>
+        <v>5935348.6856401339</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -22786,7 +22786,7 @@
       </c>
       <c r="C24" s="95">
         <f ca="1">C21+C22-C23</f>
-        <v>7376660.2481038012</v>
+        <v>7351907.6856401339</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -22804,7 +22804,7 @@
       </c>
       <c r="C26" s="254">
         <f ca="1">C24/C25</f>
-        <v>147.17410015769124</v>
+        <v>146.68025389330302</v>
       </c>
     </row>
   </sheetData>
@@ -22853,8 +22853,8 @@
       <c r="D2" s="265"/>
       <c r="E2" s="265"/>
       <c r="F2" s="265"/>
-      <c r="G2" s="274"/>
-      <c r="H2" s="275" t="s">
+      <c r="G2" s="271"/>
+      <c r="H2" s="272" t="s">
         <v>114</v>
       </c>
       <c r="I2" s="265"/>
@@ -22866,18 +22866,18 @@
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="271" t="s">
+      <c r="C4" s="273" t="s">
         <v>198</v>
       </c>
-      <c r="D4" s="271"/>
-      <c r="E4" s="271"/>
-      <c r="F4" s="271"/>
-      <c r="G4" s="271"/>
-      <c r="H4" s="271"/>
-      <c r="I4" s="271"/>
-      <c r="J4" s="271"/>
-      <c r="K4" s="271"/>
-      <c r="L4" s="271"/>
+      <c r="D4" s="273"/>
+      <c r="E4" s="273"/>
+      <c r="F4" s="273"/>
+      <c r="G4" s="273"/>
+      <c r="H4" s="273"/>
+      <c r="I4" s="273"/>
+      <c r="J4" s="273"/>
+      <c r="K4" s="273"/>
+      <c r="L4" s="273"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -23073,23 +23073,23 @@
       <c r="G9" s="140"/>
       <c r="H9" s="93">
         <f ca="1">DCF!H10</f>
-        <v>164713.59638382119</v>
+        <v>164670.5344764</v>
       </c>
       <c r="I9" s="93">
         <f ca="1">DCF!I10</f>
-        <v>199685.05585775024</v>
+        <v>199580.66016047809</v>
       </c>
       <c r="J9" s="93">
         <f ca="1">DCF!J10</f>
-        <v>228065.31271136957</v>
+        <v>227886.48667114065</v>
       </c>
       <c r="K9" s="93">
         <f ca="1">DCF!K10</f>
-        <v>262692.12039560592</v>
+        <v>262417.52039291413</v>
       </c>
       <c r="L9" s="93">
         <f ca="1">DCF!L10</f>
-        <v>360485.87709661247</v>
+        <v>360014.90520035184</v>
       </c>
       <c r="N9" s="92"/>
     </row>
@@ -23097,18 +23097,18 @@
       <c r="N10" s="92"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C11" s="271" t="s">
+      <c r="C11" s="273" t="s">
         <v>122</v>
       </c>
-      <c r="D11" s="271"/>
-      <c r="E11" s="271"/>
-      <c r="F11" s="271"/>
-      <c r="G11" s="271"/>
-      <c r="H11" s="271"/>
-      <c r="I11" s="271"/>
-      <c r="J11" s="271"/>
-      <c r="K11" s="271"/>
-      <c r="L11" s="271"/>
+      <c r="D11" s="273"/>
+      <c r="E11" s="273"/>
+      <c r="F11" s="273"/>
+      <c r="G11" s="273"/>
+      <c r="H11" s="273"/>
+      <c r="I11" s="273"/>
+      <c r="J11" s="273"/>
+      <c r="K11" s="273"/>
+      <c r="L11" s="273"/>
       <c r="N11" s="92"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -23302,18 +23302,18 @@
       <c r="N16" s="92"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C17" s="271" t="s">
+      <c r="C17" s="273" t="s">
         <v>200</v>
       </c>
-      <c r="D17" s="271"/>
-      <c r="E17" s="271"/>
-      <c r="F17" s="271"/>
-      <c r="G17" s="271"/>
-      <c r="H17" s="271"/>
-      <c r="I17" s="271"/>
-      <c r="J17" s="271"/>
-      <c r="K17" s="271"/>
-      <c r="L17" s="271"/>
+      <c r="D17" s="273"/>
+      <c r="E17" s="273"/>
+      <c r="F17" s="273"/>
+      <c r="G17" s="273"/>
+      <c r="H17" s="273"/>
+      <c r="I17" s="273"/>
+      <c r="J17" s="273"/>
+      <c r="K17" s="273"/>
+      <c r="L17" s="273"/>
       <c r="N17" s="92"/>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
@@ -23447,18 +23447,18 @@
       <c r="N21" s="92"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C22" s="271" t="s">
+      <c r="C22" s="273" t="s">
         <v>203</v>
       </c>
-      <c r="D22" s="271"/>
-      <c r="E22" s="271"/>
-      <c r="F22" s="271"/>
-      <c r="G22" s="271"/>
-      <c r="H22" s="271"/>
-      <c r="I22" s="271"/>
-      <c r="J22" s="271"/>
-      <c r="K22" s="271"/>
-      <c r="L22" s="271"/>
+      <c r="D22" s="273"/>
+      <c r="E22" s="273"/>
+      <c r="F22" s="273"/>
+      <c r="G22" s="273"/>
+      <c r="H22" s="273"/>
+      <c r="I22" s="273"/>
+      <c r="J22" s="273"/>
+      <c r="K22" s="273"/>
+      <c r="L22" s="273"/>
       <c r="N22" s="92"/>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.2">
@@ -23542,18 +23542,18 @@
       <c r="N26" s="92"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C27" s="271" t="s">
+      <c r="C27" s="273" t="s">
         <v>204</v>
       </c>
-      <c r="D27" s="271"/>
-      <c r="E27" s="271"/>
-      <c r="F27" s="271"/>
-      <c r="G27" s="271"/>
-      <c r="H27" s="271"/>
-      <c r="I27" s="271"/>
-      <c r="J27" s="271"/>
-      <c r="K27" s="271"/>
-      <c r="L27" s="271"/>
+      <c r="D27" s="273"/>
+      <c r="E27" s="273"/>
+      <c r="F27" s="273"/>
+      <c r="G27" s="273"/>
+      <c r="H27" s="273"/>
+      <c r="I27" s="273"/>
+      <c r="J27" s="273"/>
+      <c r="K27" s="273"/>
+      <c r="L27" s="273"/>
       <c r="N27" s="92"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.2">
@@ -23875,7 +23875,7 @@
       </c>
       <c r="C41" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>9.7500000000000003E-2</v>
+        <v>9.7786999999999999E-2</v>
       </c>
     </row>
     <row r="42" spans="2:14" x14ac:dyDescent="0.2">
@@ -23901,7 +23901,7 @@
       </c>
       <c r="C44" s="24">
         <f ca="1">C43/(1+C41)^5</f>
-        <v>7653665.1326262504</v>
+        <v>7643665.6807478881</v>
       </c>
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.2">
@@ -23910,7 +23910,7 @@
       </c>
       <c r="C45" s="110">
         <f ca="1">SUM(H9:K9)+C44</f>
-        <v>8508821.2179747969</v>
+        <v>8498220.8824488204</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -23937,7 +23937,7 @@
       </c>
       <c r="C48" s="110">
         <f ca="1">C45+C46-C47</f>
-        <v>9925380.2179747969</v>
+        <v>9914779.8824488204</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
@@ -23955,7 +23955,7 @@
       </c>
       <c r="C50" s="254">
         <f ca="1">C48/C49</f>
-        <v>198.02442476307402</v>
+        <v>197.8129340897973</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
@@ -23979,7 +23979,7 @@
       </c>
       <c r="C54" s="137">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>9.7500000000000003E-2</v>
+        <v>9.7786999999999999E-2</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
@@ -24014,7 +24014,7 @@
       </c>
       <c r="C58" s="254">
         <f ca="1">C57/(1+C54)^5</f>
-        <v>159.74574315816156</v>
+        <v>159.53703663079153</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
@@ -24038,7 +24038,7 @@
       </c>
       <c r="C62" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>9.7500000000000003E-2</v>
+        <v>9.7786999999999999E-2</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
@@ -24064,7 +24064,7 @@
       </c>
       <c r="C65" s="24">
         <f ca="1">C64/(1+C62)^5</f>
-        <v>7930689.2961254744</v>
+        <v>7920327.9144077403</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -24073,7 +24073,7 @@
       </c>
       <c r="C66" s="110">
         <f ca="1">SUM(H9:K9)+C65</f>
-        <v>8785845.3814740218</v>
+        <v>8774883.1161086727</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.2">
@@ -24100,7 +24100,7 @@
       </c>
       <c r="C69" s="110">
         <f ca="1">C66+C67-C68</f>
-        <v>10202404.381474022</v>
+        <v>10191442.116108673</v>
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.2">
@@ -24118,7 +24118,7 @@
       </c>
       <c r="C71" s="254">
         <f ca="1">C69/C70</f>
-        <v>203.55142215941146</v>
+        <v>203.33271050853264</v>
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.2">
@@ -24142,7 +24142,7 @@
       </c>
       <c r="C75" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>9.7500000000000003E-2</v>
+        <v>9.7786999999999999E-2</v>
       </c>
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.2">
@@ -24168,7 +24168,7 @@
       </c>
       <c r="C78" s="24">
         <f ca="1">C77/(1+C75)^5</f>
-        <v>7951859.8780532517</v>
+        <v>7941470.8371406673</v>
       </c>
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.2">
@@ -24177,7 +24177,7 @@
       </c>
       <c r="C79" s="110">
         <f ca="1">SUM(H9:K9)+C78</f>
-        <v>8807015.9634017982</v>
+        <v>8796026.0388415996</v>
       </c>
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.2">
@@ -24204,7 +24204,7 @@
       </c>
       <c r="C82" s="110">
         <f ca="1">C79+C80-C81</f>
-        <v>10223574.963401798</v>
+        <v>10212585.0388416</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.2">
@@ -24222,22 +24222,22 @@
       </c>
       <c r="C84" s="254">
         <f ca="1">C82/C83</f>
-        <v>203.97380318825662</v>
+        <v>203.75453969996408</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="C27:L27"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B60:C60"/>
     <mergeCell ref="C22:L22"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="C17:L17"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="C27:L27"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B60:C60"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -24287,7 +24287,7 @@
       </c>
       <c r="C5" s="135">
         <f ca="1">DCF!C26</f>
-        <v>147.17410015769124</v>
+        <v>146.68025389330302</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -24296,7 +24296,7 @@
       </c>
       <c r="C6" s="135">
         <f ca="1">Multiples!C50</f>
-        <v>198.02442476307402</v>
+        <v>197.8129340897973</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -24305,7 +24305,7 @@
       </c>
       <c r="C7" s="135">
         <f ca="1">Multiples!C58</f>
-        <v>159.74574315816156</v>
+        <v>159.53703663079153</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -24314,7 +24314,7 @@
       </c>
       <c r="C8" s="135">
         <f ca="1">Multiples!C71</f>
-        <v>203.55142215941146</v>
+        <v>203.33271050853264</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -24323,7 +24323,7 @@
       </c>
       <c r="C9" s="135">
         <f ca="1">Multiples!C84</f>
-        <v>203.97380318825662</v>
+        <v>203.75453969996408</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -24332,7 +24332,7 @@
       </c>
       <c r="C10" s="254">
         <f ca="1">AVERAGE(C5:C9)</f>
-        <v>182.49389868531898</v>
+        <v>182.22349496447771</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -24341,7 +24341,7 @@
       </c>
       <c r="C11" s="135">
         <f ca="1">Overview!C5</f>
-        <v>143.04</v>
+        <v>138.6</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -24350,7 +24350,7 @@
       </c>
       <c r="C12" s="154">
         <f ca="1">(C10-C11)/C11</f>
-        <v>0.27582423577544041</v>
+        <v>0.31474383091253766</v>
       </c>
     </row>
   </sheetData>
@@ -24451,8 +24451,8 @@
       <c r="D2" s="265"/>
       <c r="E2" s="265"/>
       <c r="F2" s="265"/>
-      <c r="G2" s="274"/>
-      <c r="H2" s="275" t="s">
+      <c r="G2" s="271"/>
+      <c r="H2" s="272" t="s">
         <v>114</v>
       </c>
       <c r="I2" s="265"/>
@@ -24464,18 +24464,18 @@
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="271" t="s">
+      <c r="C4" s="273" t="s">
         <v>198</v>
       </c>
-      <c r="D4" s="271"/>
-      <c r="E4" s="271"/>
-      <c r="F4" s="271"/>
-      <c r="G4" s="271"/>
-      <c r="H4" s="271"/>
-      <c r="I4" s="271"/>
-      <c r="J4" s="271"/>
-      <c r="K4" s="271"/>
-      <c r="L4" s="271"/>
+      <c r="D4" s="273"/>
+      <c r="E4" s="273"/>
+      <c r="F4" s="273"/>
+      <c r="G4" s="273"/>
+      <c r="H4" s="273"/>
+      <c r="I4" s="273"/>
+      <c r="J4" s="273"/>
+      <c r="K4" s="273"/>
+      <c r="L4" s="273"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -24588,18 +24588,18 @@
       <c r="N8" s="92"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C9" s="271" t="s">
+      <c r="C9" s="273" t="s">
         <v>122</v>
       </c>
-      <c r="D9" s="271"/>
-      <c r="E9" s="271"/>
-      <c r="F9" s="271"/>
-      <c r="G9" s="271"/>
-      <c r="H9" s="271"/>
-      <c r="I9" s="271"/>
-      <c r="J9" s="271"/>
-      <c r="K9" s="271"/>
-      <c r="L9" s="271"/>
+      <c r="D9" s="273"/>
+      <c r="E9" s="273"/>
+      <c r="F9" s="273"/>
+      <c r="G9" s="273"/>
+      <c r="H9" s="273"/>
+      <c r="I9" s="273"/>
+      <c r="J9" s="273"/>
+      <c r="K9" s="273"/>
+      <c r="L9" s="273"/>
       <c r="N9" s="92"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -24720,18 +24720,18 @@
       <c r="N13" s="92"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C14" s="271" t="s">
+      <c r="C14" s="273" t="s">
         <v>413</v>
       </c>
-      <c r="D14" s="271"/>
-      <c r="E14" s="271"/>
-      <c r="F14" s="271"/>
-      <c r="G14" s="271"/>
-      <c r="H14" s="271"/>
-      <c r="I14" s="271"/>
-      <c r="J14" s="271"/>
-      <c r="K14" s="271"/>
-      <c r="L14" s="271"/>
+      <c r="D14" s="273"/>
+      <c r="E14" s="273"/>
+      <c r="F14" s="273"/>
+      <c r="G14" s="273"/>
+      <c r="H14" s="273"/>
+      <c r="I14" s="273"/>
+      <c r="J14" s="273"/>
+      <c r="K14" s="273"/>
+      <c r="L14" s="273"/>
       <c r="N14" s="92"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
@@ -24859,7 +24859,7 @@
       </c>
       <c r="C24" s="137">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>9.7500000000000003E-2</v>
+        <v>9.7786999999999999E-2</v>
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
@@ -24932,8 +24932,8 @@
       <c r="D3" s="265"/>
       <c r="E3" s="265"/>
       <c r="F3" s="265"/>
-      <c r="G3" s="274"/>
-      <c r="H3" s="275" t="s">
+      <c r="G3" s="271"/>
+      <c r="H3" s="272" t="s">
         <v>114</v>
       </c>
       <c r="I3" s="265"/>
@@ -24957,18 +24957,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="87"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="271" t="s">
+      <c r="C5" s="273" t="s">
         <v>184</v>
       </c>
-      <c r="D5" s="271"/>
-      <c r="E5" s="271"/>
-      <c r="F5" s="271"/>
-      <c r="G5" s="271"/>
-      <c r="H5" s="271"/>
-      <c r="I5" s="271"/>
-      <c r="J5" s="271"/>
-      <c r="K5" s="271"/>
-      <c r="L5" s="271"/>
+      <c r="D5" s="273"/>
+      <c r="E5" s="273"/>
+      <c r="F5" s="273"/>
+      <c r="G5" s="273"/>
+      <c r="H5" s="273"/>
+      <c r="I5" s="273"/>
+      <c r="J5" s="273"/>
+      <c r="K5" s="273"/>
+      <c r="L5" s="273"/>
       <c r="P5" s="276"/>
       <c r="Q5" s="276"/>
       <c r="R5" s="276"/>
@@ -25114,7 +25114,7 @@
       <c r="K8" s="139"/>
       <c r="L8" s="128">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>7189434.3550421083</v>
+        <v>7162908.4874820141</v>
       </c>
       <c r="N8" s="92"/>
       <c r="O8" s="16"/>
@@ -25168,23 +25168,23 @@
       <c r="G10" s="140"/>
       <c r="H10" s="128">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>179735.09405368444</v>
+        <v>179688.10500025837</v>
       </c>
       <c r="I10" s="128">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>211260.38389909151</v>
+        <v>211149.9366000265</v>
       </c>
       <c r="J10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>248315.16649642648</v>
+        <v>248120.46254331135</v>
       </c>
       <c r="K10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>291869.30731698417</v>
+        <v>291564.20752010337</v>
       </c>
       <c r="L10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>343062.78491016821</v>
+        <v>342614.57614358095</v>
       </c>
       <c r="N10" s="92"/>
     </row>
@@ -25203,15 +25203,15 @@
       <c r="K11" s="139"/>
       <c r="L11" s="128">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>4515148.9110757625</v>
+        <v>4492612.7459145179</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="277" t="s">
+      <c r="B14" s="278" t="s">
         <v>226</v>
       </c>
-      <c r="C14" s="278"/>
+      <c r="C14" s="279"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="155" t="s">
@@ -25219,7 +25219,7 @@
       </c>
       <c r="C15" s="156">
         <f ca="1">Overview!C5</f>
-        <v>143.04</v>
+        <v>138.6</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -25228,7 +25228,7 @@
       </c>
       <c r="C16" s="156">
         <f ca="1">C36</f>
-        <v>154.01937861223695</v>
+        <v>153.51406475701702</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -25238,20 +25238,20 @@
       <c r="C17" s="158">
         <v>0.28999999999999998</v>
       </c>
-      <c r="E17" s="279" t="s">
+      <c r="E17" s="277" t="s">
         <v>229</v>
       </c>
-      <c r="F17" s="279"/>
-      <c r="G17" s="279"/>
-      <c r="H17" s="279"/>
-      <c r="I17" s="279"/>
+      <c r="F17" s="277"/>
+      <c r="G17" s="277"/>
+      <c r="H17" s="277"/>
+      <c r="I17" s="277"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="277" t="s">
+      <c r="B19" s="278" t="s">
         <v>188</v>
       </c>
-      <c r="C19" s="278"/>
+      <c r="C19" s="279"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="159" t="s">
@@ -25267,7 +25267,7 @@
       </c>
       <c r="C21" s="221">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>9.7500000000000003E-2</v>
+        <v>9.7786999999999999E-2</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -25285,7 +25285,7 @@
       </c>
       <c r="C23" s="161">
         <f ca="1">C15*C22</f>
-        <v>6692269.4399999995</v>
+        <v>6484539.5999999996</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -25312,15 +25312,15 @@
       </c>
       <c r="C26" s="162">
         <f ca="1">C23+C25-C24</f>
-        <v>5275710.4399999995</v>
+        <v>5067980.5999999996</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="277" t="s">
+      <c r="B28" s="278" t="s">
         <v>190</v>
       </c>
-      <c r="C28" s="278"/>
+      <c r="C28" s="279"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="159" t="s">
@@ -25328,7 +25328,7 @@
       </c>
       <c r="C29" s="161">
         <f ca="1">SUM(H10:L10)</f>
-        <v>1274242.7366763549</v>
+        <v>1273137.2878072804</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -25337,7 +25337,7 @@
       </c>
       <c r="C30" s="161">
         <f ca="1">L11</f>
-        <v>4515148.9110757625</v>
+        <v>4492612.7459145179</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -25346,7 +25346,7 @@
       </c>
       <c r="C31" s="164">
         <f ca="1">C29+C30</f>
-        <v>5789391.6477521174</v>
+        <v>5765750.0337217981</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -25373,7 +25373,7 @@
       </c>
       <c r="C34" s="164">
         <f ca="1">C31+C32-C33</f>
-        <v>7205950.6477521174</v>
+        <v>7182309.0337217981</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.2">
@@ -25391,21 +25391,21 @@
       </c>
       <c r="C36" s="167">
         <f ca="1">C34/C35</f>
-        <v>154.01937861223695</v>
+        <v>153.51406475701702</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
+    <mergeCell ref="B14:C14"/>
     <mergeCell ref="E17:I17"/>
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
-    <mergeCell ref="B14:C14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -32097,7 +32097,7 @@
       </c>
       <c r="AC116" s="63">
         <f ca="1">Overview!C5</f>
-        <v>143.04</v>
+        <v>138.6</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -32168,7 +32168,7 @@
       </c>
       <c r="AC117" s="65">
         <f ca="1">AC116/AC85</f>
-        <v>143.04</v>
+        <v>138.6</v>
       </c>
     </row>
     <row r="119" spans="1:31" x14ac:dyDescent="0.2">
@@ -33278,7 +33278,7 @@
       <c r="AA146" s="49"/>
       <c r="AC146" s="72">
         <f ca="1">AC117/Statement!AC26</f>
-        <v>45.54548191336179</v>
+        <v>44.131737927796031</v>
       </c>
     </row>
     <row r="147" spans="2:29" x14ac:dyDescent="0.2">
@@ -33315,7 +33315,7 @@
       <c r="AA147" s="49"/>
       <c r="AC147" s="72">
         <f ca="1">AC117/(Statement!AC5/Statement!AC22)</f>
-        <v>6.1427774173869789</v>
+        <v>5.9521039572835237</v>
       </c>
     </row>
     <row r="148" spans="2:29" x14ac:dyDescent="0.2">
@@ -33376,7 +33376,7 @@
       </c>
       <c r="AC148" s="72">
         <f ca="1">AC117/(Statement!AC49/Statement!AC75)</f>
-        <v>4.7471590120745493</v>
+        <v>4.5998059219346521</v>
       </c>
     </row>
     <row r="149" spans="2:29" x14ac:dyDescent="0.2">
@@ -33437,7 +33437,7 @@
       </c>
       <c r="AC149" s="143">
         <f ca="1">Statement!AC117*Statement!AC78</f>
-        <v>7169450.8799999999</v>
+        <v>6946909.1999999993</v>
       </c>
     </row>
     <row r="150" spans="2:29" x14ac:dyDescent="0.2">
@@ -33498,7 +33498,7 @@
       </c>
       <c r="AC150" s="143">
         <f ca="1">AC149+AC108-AC107+AC48+AC45</f>
-        <v>5752891.8799999999</v>
+        <v>5530350.1999999993</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -33535,7 +33535,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="182">
         <f ca="1">AC150/AC5</f>
-        <v>5.0243509443651622</v>
+        <v>4.8299917380056971</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -33572,7 +33572,7 @@
       <c r="AA152" s="49"/>
       <c r="AC152" s="182">
         <f ca="1">AC150/AC12</f>
-        <v>36.622795811185028</v>
+        <v>35.20609988222936</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -33707,7 +33707,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="72">
         <f t="shared" ref="AC155:AC156" ca="1" si="151">AC149/AC153</f>
-        <v>28.357926113440392</v>
+        <v>27.477688474013128</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -33744,7 +33744,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="72">
         <f t="shared" ca="1" si="151"/>
-        <v>34.503967205341873</v>
+        <v>33.169234867465619</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -33781,7 +33781,7 @@
       <c r="AA157" s="49"/>
       <c r="AC157" s="74">
         <f t="shared" ref="AC157" ca="1" si="154">AC153/AC149</f>
-        <v>3.5263509609260342E-2</v>
+        <v>3.6393163163842709E-2</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
@@ -33818,7 +33818,7 @@
       <c r="AA158" s="49"/>
       <c r="AC158" s="74">
         <f ca="1">AC26/AC117</f>
-        <v>2.1956074631117855E-2</v>
+        <v>2.2659429402850637E-2</v>
       </c>
     </row>
     <row r="159" spans="2:29" x14ac:dyDescent="0.2">
@@ -33892,7 +33892,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="154">
         <f ca="1">-AC63/AC149</f>
-        <v>9.7082748965008608E-3</v>
+        <v>1.0019275910501321E-2</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -33929,7 +33929,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="154">
         <f ca="1">-(AC63+AC64)/AC149</f>
-        <v>9.7082748965008608E-3</v>
+        <v>1.0019275910501321E-2</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -34432,7 +34432,7 @@
       <c r="AA172" s="49"/>
       <c r="AC172" s="154">
         <f ca="1">(AC107-AC108)/AC149</f>
-        <v>0.19758263550583111</v>
+        <v>0.20391212253069324</v>
       </c>
     </row>
     <row r="173" spans="2:29" x14ac:dyDescent="0.2">
@@ -36409,7 +36409,7 @@
       </c>
       <c r="C5" s="171">
         <f ca="1">Overview!C5</f>
-        <v>143.04</v>
+        <v>138.6</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="134" t="s">
@@ -36425,7 +36425,7 @@
       </c>
       <c r="C6" s="172">
         <f ca="1">Statement!AC149</f>
-        <v>7169450.8799999999</v>
+        <v>6946909.1999999993</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>20</v>
@@ -36445,7 +36445,7 @@
       </c>
       <c r="C7" s="172">
         <f ca="1">Statement!AC150</f>
-        <v>5752891.8799999999</v>
+        <v>5530350.1999999993</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>32</v>
@@ -36465,7 +36465,7 @@
       </c>
       <c r="C8" s="173">
         <f ca="1">Statement!AC146</f>
-        <v>45.54548191336179</v>
+        <v>44.131737927796031</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>247</v>
@@ -36485,7 +36485,7 @@
       </c>
       <c r="C9" s="173">
         <f ca="1">Statement!AC147</f>
-        <v>6.1427774173869789</v>
+        <v>5.9521039572835237</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>248</v>
@@ -36505,7 +36505,7 @@
       </c>
       <c r="C10" s="173">
         <f ca="1">Statement!AC148</f>
-        <v>4.7471590120745493</v>
+        <v>4.5998059219346521</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -36525,7 +36525,7 @@
       </c>
       <c r="C11" s="173">
         <f ca="1">Statement!AC151</f>
-        <v>5.0243509443651622</v>
+        <v>4.8299917380056971</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -36534,7 +36534,7 @@
       </c>
       <c r="C12" s="173">
         <f ca="1">Statement!AC152</f>
-        <v>36.622795811185028</v>
+        <v>35.20609988222936</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
@@ -36770,7 +36770,7 @@
       </c>
       <c r="C38" s="174">
         <f ca="1">Statement!AC158</f>
-        <v>2.1956074631117855E-2</v>
+        <v>2.2659429402850637E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>274</v>
@@ -36786,7 +36786,7 @@
       </c>
       <c r="C39" s="214">
         <f ca="1">Statement!AC157</f>
-        <v>3.5263509609260342E-2</v>
+        <v>3.6393163163842709E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>276</v>
@@ -36818,7 +36818,7 @@
       </c>
       <c r="C41" s="174">
         <f ca="1">Statement!AC160</f>
-        <v>9.7082748965008608E-3</v>
+        <v>1.0019275910501321E-2</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -36827,7 +36827,7 @@
       </c>
       <c r="C42" s="174">
         <f ca="1">Statement!AC161</f>
-        <v>9.7082748965008608E-3</v>
+        <v>1.0019275910501321E-2</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
@@ -36871,7 +36871,7 @@
       </c>
       <c r="F48" s="174">
         <f ca="1">Statement!AC172</f>
-        <v>0.19758263550583111</v>
+        <v>0.20391212253069324</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
@@ -37050,7 +37050,7 @@
       </c>
       <c r="I6" s="171">
         <f ca="1">Statement!AC116</f>
-        <v>143.04</v>
+        <v>138.6</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -37079,7 +37079,7 @@
       </c>
       <c r="I7" s="172">
         <f ca="1">Statement!AC149</f>
-        <v>7169450.8799999999</v>
+        <v>6946909.1999999993</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -37108,7 +37108,7 @@
       </c>
       <c r="I8" s="172">
         <f ca="1">Statement!AC150</f>
-        <v>5752891.8799999999</v>
+        <v>5530350.1999999993</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -37137,7 +37137,7 @@
       </c>
       <c r="I9" s="173">
         <f ca="1">Statement!AC146</f>
-        <v>45.54548191336179</v>
+        <v>44.131737927796031</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -37166,7 +37166,7 @@
       </c>
       <c r="I10" s="173">
         <f ca="1">Statement!AC147</f>
-        <v>6.1427774173869789</v>
+        <v>5.9521039572835237</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -37195,7 +37195,7 @@
       </c>
       <c r="I11" s="173">
         <f ca="1">Statement!AC148</f>
-        <v>4.7471590120745493</v>
+        <v>4.5998059219346521</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -37224,7 +37224,7 @@
       </c>
       <c r="I12" s="173">
         <f ca="1">Statement!AC151</f>
-        <v>5.0243509443651622</v>
+        <v>4.8299917380056971</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -37253,7 +37253,7 @@
       </c>
       <c r="I13" s="173">
         <f ca="1">Statement!AC152</f>
-        <v>36.622795811185028</v>
+        <v>35.20609988222936</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -38026,7 +38026,7 @@
       </c>
       <c r="I51" s="174">
         <f ca="1">Statement!AC158</f>
-        <v>2.1956074631117855E-2</v>
+        <v>2.2659429402850637E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -38055,7 +38055,7 @@
       </c>
       <c r="I52" s="174">
         <f ca="1">Statement!AC157</f>
-        <v>3.5263509609260342E-2</v>
+        <v>3.6393163163842709E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -38113,7 +38113,7 @@
       </c>
       <c r="I54" s="174">
         <f ca="1">Statement!AC160</f>
-        <v>9.7082748965008608E-3</v>
+        <v>1.0019275910501321E-2</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -38142,7 +38142,7 @@
       </c>
       <c r="I55" s="174">
         <f ca="1">Statement!AC161</f>
-        <v>9.7082748965008608E-3</v>
+        <v>1.0019275910501321E-2</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -38378,7 +38378,7 @@
       </c>
       <c r="I68" s="195">
         <f ca="1">Statement!AC172</f>
-        <v>0.19758263550583111</v>
+        <v>0.20391212253069324</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -38921,14 +38921,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="266" t="s">
+      <c r="C3" s="268" t="s">
         <v>317</v>
       </c>
-      <c r="D3" s="267"/>
-      <c r="F3" s="268" t="s">
+      <c r="D3" s="269"/>
+      <c r="F3" s="270" t="s">
         <v>318</v>
       </c>
-      <c r="G3" s="267"/>
+      <c r="G3" s="269"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -38995,19 +38995,19 @@
       <c r="B7" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C7" s="269">
+      <c r="C7" s="266">
         <f>Statement!AA89</f>
         <v>2.2218264392893719E-2</v>
       </c>
-      <c r="D7" s="270"/>
-      <c r="F7" s="269">
+      <c r="D7" s="267"/>
+      <c r="F7" s="266">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.18309713991239371</v>
       </c>
-      <c r="G7" s="270"/>
+      <c r="G7" s="267"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="206" t="s">
@@ -39034,19 +39034,19 @@
       <c r="B9" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C9" s="269">
+      <c r="C9" s="266">
         <f>Statement!AA90</f>
         <v>3.6046202026093238E-2</v>
       </c>
-      <c r="D9" s="270"/>
-      <c r="F9" s="269">
+      <c r="D9" s="267"/>
+      <c r="F9" s="266">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.17263647322197348</v>
       </c>
-      <c r="G9" s="270"/>
+      <c r="G9" s="267"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="206" t="s">
@@ -39073,19 +39073,19 @@
       <c r="B11" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C11" s="269">
+      <c r="C11" s="266">
         <f>Statement!AA91</f>
         <v>1.710027405488606E-2</v>
       </c>
-      <c r="D11" s="270"/>
-      <c r="F11" s="269">
+      <c r="D11" s="267"/>
+      <c r="F11" s="266">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>0.1870895657269924</v>
       </c>
-      <c r="G11" s="270"/>
+      <c r="G11" s="267"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="206" t="s">
@@ -39112,19 +39112,19 @@
       <c r="B13" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C13" s="269">
+      <c r="C13" s="266">
         <f>Statement!AA95</f>
         <v>8.4392741251357012E-2</v>
       </c>
-      <c r="D13" s="270"/>
-      <c r="F13" s="269">
+      <c r="D13" s="267"/>
+      <c r="F13" s="266">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.22501976973287405</v>
       </c>
-      <c r="G13" s="270"/>
+      <c r="G13" s="267"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="206" t="s">
@@ -39151,19 +39151,19 @@
       <c r="B15" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C15" s="269">
+      <c r="C15" s="266">
         <f>Statement!AA96</f>
         <v>-0.23765355851505829</v>
       </c>
-      <c r="D15" s="270"/>
-      <c r="F15" s="269">
+      <c r="D15" s="267"/>
+      <c r="F15" s="266">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>1.7444474417768186E-2</v>
       </c>
-      <c r="G15" s="270"/>
+      <c r="G15" s="267"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="206" t="s">
@@ -39190,19 +39190,19 @@
       <c r="B17" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C17" s="269">
+      <c r="C17" s="266">
         <f>Statement!AA98</f>
         <v>-0.23704555913483663</v>
       </c>
-      <c r="D17" s="270"/>
-      <c r="F17" s="269">
+      <c r="D17" s="267"/>
+      <c r="F17" s="266">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>-0.25955204216073779</v>
       </c>
-      <c r="G17" s="270"/>
+      <c r="G17" s="267"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="206" t="s">
@@ -39229,22 +39229,22 @@
       <c r="B19" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C19" s="269">
+      <c r="C19" s="266">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>2.5565842762241744E-2</v>
       </c>
-      <c r="D19" s="270"/>
-      <c r="F19" s="269">
+      <c r="D19" s="267"/>
+      <c r="F19" s="266">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>2.5293753865182372E-2</v>
       </c>
-      <c r="G19" s="270"/>
+      <c r="G19" s="267"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="206" t="s">
@@ -39271,22 +39271,22 @@
       <c r="B21" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C21" s="269">
+      <c r="C21" s="266">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>-0.2584269662921348</v>
       </c>
-      <c r="D21" s="270"/>
-      <c r="F21" s="269">
+      <c r="D21" s="267"/>
+      <c r="F21" s="266">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>-0.27472527472527469</v>
       </c>
-      <c r="G21" s="270"/>
+      <c r="G21" s="267"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -39335,22 +39335,22 @@
       <c r="B25" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C25" s="269">
+      <c r="C25" s="266">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>2.840483364420425E-2</v>
       </c>
-      <c r="D25" s="270"/>
-      <c r="F25" s="269">
+      <c r="D25" s="267"/>
+      <c r="F25" s="266">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>0.22478379327694395</v>
       </c>
-      <c r="G25" s="270"/>
+      <c r="G25" s="267"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="str">
@@ -39378,22 +39378,22 @@
       <c r="B27" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C27" s="269">
+      <c r="C27" s="266">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>2.1247695740758708E-2</v>
       </c>
-      <c r="D27" s="270"/>
-      <c r="F27" s="269">
+      <c r="D27" s="267"/>
+      <c r="F27" s="266">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>2.1792942775323981E-2</v>
       </c>
-      <c r="G27" s="270"/>
+      <c r="G27" s="267"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="str">
@@ -39421,22 +39421,22 @@
       <c r="B29" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C29" s="269">
+      <c r="C29" s="266">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>-0.10674206945303526</v>
       </c>
-      <c r="D29" s="270"/>
-      <c r="F29" s="269">
+      <c r="D29" s="267"/>
+      <c r="F29" s="266">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>2.0816812053925456E-3</v>
       </c>
-      <c r="G29" s="270"/>
+      <c r="G29" s="267"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="str">
@@ -39464,22 +39464,22 @@
       <c r="B31" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C31" s="269">
+      <c r="C31" s="266">
         <f>IF(C30=0,
 IF(D30=0,0,IF(D30&gt;0,1,-1)),
 (D30-C30)/ABS(C30)
 )</f>
         <v>-5.2569263556713236E-2</v>
       </c>
-      <c r="D31" s="270"/>
-      <c r="F31" s="269">
+      <c r="D31" s="267"/>
+      <c r="F31" s="266">
         <f>IF(F30=0,
 IF(G30=0,0,IF(G30&gt;0,1,-1)),
 (G30-F30)/ABS(F30)
 )</f>
         <v>-0.22983638113570742</v>
       </c>
-      <c r="G31" s="270"/>
+      <c r="G31" s="267"/>
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B32" s="20" t="str">
@@ -39507,22 +39507,22 @@
       <c r="B33" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C33" s="269">
+      <c r="C33" s="266">
         <f>IF(C32=0,
 IF(D32=0,0,IF(D32&gt;0,1,-1)),
 (D32-C32)/ABS(C32)
 )</f>
         <v>0.84164222873900296</v>
       </c>
-      <c r="D33" s="270"/>
-      <c r="F33" s="269">
+      <c r="D33" s="267"/>
+      <c r="F33" s="266">
         <f>IF(F32=0,
 IF(G32=0,0,IF(G32&gt;0,1,-1)),
 (G32-F32)/ABS(F32)
 )</f>
         <v>1.482213438735178</v>
       </c>
-      <c r="G33" s="270"/>
+      <c r="G33" s="267"/>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B35" s="8" t="s">
@@ -39571,22 +39571,22 @@
       <c r="B37" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C37" s="269">
+      <c r="C37" s="266">
         <f>IF(C36=0,
 IF(D36=0,0,IF(D36&gt;0,1,-1)),
 (D36-C36)/ABS(C36)
 )</f>
         <v>3.8938053097345132E-2</v>
       </c>
-      <c r="D37" s="270"/>
-      <c r="F37" s="269">
+      <c r="D37" s="267"/>
+      <c r="F37" s="266">
         <f>IF(F36=0,
 IF(G36=0,0,IF(G36&gt;0,1,-1)),
 (G36-F36)/ABS(F36)
 )</f>
         <v>0.23060796645702306</v>
       </c>
-      <c r="G37" s="270"/>
+      <c r="G37" s="267"/>
     </row>
     <row r="38" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="str">
@@ -39614,22 +39614,22 @@
       <c r="B39" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C39" s="269">
+      <c r="C39" s="266">
         <f>IF(C38=0,
 IF(D38=0,0,IF(D38&gt;0,1,-1)),
 (D38-C38)/ABS(C38)
 )</f>
         <v>2.0319303338171262E-2</v>
       </c>
-      <c r="D39" s="270"/>
-      <c r="F39" s="269">
+      <c r="D39" s="267"/>
+      <c r="F39" s="266">
         <f>IF(F38=0,
 IF(G38=0,0,IF(G38&gt;0,1,-1)),
 (G38-F38)/ABS(F38)
 )</f>
         <v>9.5869056897895558E-2</v>
       </c>
-      <c r="G39" s="270"/>
+      <c r="G39" s="267"/>
     </row>
     <row r="40" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B40" s="20" t="str">
@@ -39657,22 +39657,22 @@
       <c r="B41" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C41" s="269">
+      <c r="C41" s="266">
         <f>IF(C40=0,
 IF(D40=0,0,IF(D40&gt;0,1,-1)),
 (D40-C40)/ABS(C40)
 )</f>
         <v>1.6E-2</v>
       </c>
-      <c r="D41" s="270"/>
-      <c r="F41" s="269">
+      <c r="D41" s="267"/>
+      <c r="F41" s="266">
         <f>IF(F40=0,
 IF(G40=0,0,IF(G40&gt;0,1,-1)),
 (G40-F40)/ABS(F40)
 )</f>
         <v>0.16513761467889909</v>
       </c>
-      <c r="G41" s="270"/>
+      <c r="G41" s="267"/>
     </row>
     <row r="42" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B42" s="20" t="str">
@@ -39700,22 +39700,22 @@
       <c r="B43" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C43" s="269">
+      <c r="C43" s="266">
         <f>IF(C42=0,
 IF(D42=0,0,IF(D42&gt;0,1,-1)),
 (D42-C42)/ABS(C42)
 )</f>
         <v>2.0750199521149242E-2</v>
       </c>
-      <c r="D43" s="270"/>
-      <c r="F43" s="269">
+      <c r="D43" s="267"/>
+      <c r="F43" s="266">
         <f>IF(F42=0,
 IF(G42=0,0,IF(G42&gt;0,1,-1)),
 (G42-F42)/ABS(F42)
 )</f>
         <v>8.9437819420783646E-2</v>
       </c>
-      <c r="G43" s="270"/>
+      <c r="G43" s="267"/>
     </row>
     <row r="44" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B44" s="20" t="str">
@@ -39743,22 +39743,22 @@
       <c r="B45" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C45" s="269">
+      <c r="C45" s="266">
         <f>IF(C44=0,
 IF(D44=0,0,IF(D44&gt;0,1,-1)),
 (D44-C44)/ABS(C44)
 )</f>
         <v>1.2209481933271921E-2</v>
       </c>
-      <c r="D45" s="270"/>
-      <c r="F45" s="269">
+      <c r="D45" s="267"/>
+      <c r="F45" s="266">
         <f>IF(F44=0,
 IF(G44=0,0,IF(G44&gt;0,1,-1)),
 (G44-F44)/ABS(F44)
 )</f>
         <v>5.119238950540856E-2</v>
       </c>
-      <c r="G45" s="270"/>
+      <c r="G45" s="267"/>
     </row>
     <row r="46" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="str">
@@ -39786,22 +39786,22 @@
       <c r="B47" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C47" s="269">
+      <c r="C47" s="266">
         <f>IF(C46=0,
 IF(D46=0,0,IF(D46&gt;0,1,-1)),
 (D46-C46)/ABS(C46)
 )</f>
         <v>1.8247963846473435E-2</v>
       </c>
-      <c r="D47" s="270"/>
-      <c r="F47" s="269">
+      <c r="D47" s="267"/>
+      <c r="F47" s="266">
         <f>IF(F46=0,
 IF(G46=0,0,IF(G46&gt;0,1,-1)),
 (G46-F46)/ABS(F46)
 )</f>
         <v>0.1229516507570132</v>
       </c>
-      <c r="G47" s="270"/>
+      <c r="G47" s="267"/>
     </row>
     <row r="48" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B48" s="20" t="str">
@@ -39829,22 +39829,22 @@
       <c r="B49" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C49" s="269">
+      <c r="C49" s="266">
         <f>IF(C48=0,
 IF(D48=0,0,IF(D48&gt;0,1,-1)),
 (D48-C48)/ABS(C48)
 )</f>
         <v>-4.2332859174963834E-3</v>
       </c>
-      <c r="D49" s="270"/>
-      <c r="F49" s="269">
+      <c r="D49" s="267"/>
+      <c r="F49" s="266">
         <f>IF(F48=0,
 IF(G48=0,0,IF(G48&gt;0,1,-1)),
 (G48-F48)/ABS(F48)
 )</f>
         <v>6.3208790635154666E-2</v>
       </c>
-      <c r="G49" s="270"/>
+      <c r="G49" s="267"/>
     </row>
     <row r="50" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B50" s="20" t="str">
@@ -39872,22 +39872,22 @@
       <c r="B51" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C51" s="269">
+      <c r="C51" s="266">
         <f>IF(C50=0,
 IF(D50=0,0,IF(D50&gt;0,1,-1)),
 (D50-C50)/ABS(C50)
 )</f>
         <v>4.8738292663854846E-4</v>
       </c>
-      <c r="D51" s="270"/>
-      <c r="F51" s="269">
+      <c r="D51" s="267"/>
+      <c r="F51" s="266">
         <f>IF(F50=0,
 IF(G50=0,0,IF(G50&gt;0,1,-1)),
 (G50-F50)/ABS(F50)
 )</f>
         <v>-6.2091544317255373E-2</v>
       </c>
-      <c r="G51" s="270"/>
+      <c r="G51" s="267"/>
     </row>
     <row r="52" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="str">
@@ -39915,39 +39915,43 @@
       <c r="B53" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C53" s="269">
+      <c r="C53" s="266">
         <f>IF(C52=0,
 IF(D52=0,0,IF(D52&gt;0,1,-1)),
 (D52-C52)/ABS(C52)
 )</f>
         <v>-8.8077740902117604E-2</v>
       </c>
-      <c r="D53" s="270"/>
-      <c r="F53" s="269">
+      <c r="D53" s="267"/>
+      <c r="F53" s="266">
         <f>IF(F52=0,
 IF(G52=0,0,IF(G52&gt;0,1,-1)),
 (G52-F52)/ABS(F52)
 )</f>
         <v>-0.37416005758387127</v>
       </c>
-      <c r="G53" s="270"/>
+      <c r="G53" s="267"/>
     </row>
   </sheetData>
   <mergeCells count="46">
-    <mergeCell ref="C53:D53"/>
-    <mergeCell ref="F53:G53"/>
-    <mergeCell ref="C47:D47"/>
-    <mergeCell ref="F47:G47"/>
-    <mergeCell ref="C49:D49"/>
-    <mergeCell ref="F49:G49"/>
-    <mergeCell ref="C51:D51"/>
-    <mergeCell ref="F51:G51"/>
-    <mergeCell ref="C41:D41"/>
-    <mergeCell ref="F41:G41"/>
-    <mergeCell ref="C43:D43"/>
-    <mergeCell ref="F43:G43"/>
-    <mergeCell ref="C45:D45"/>
-    <mergeCell ref="F45:G45"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
     <mergeCell ref="C37:D37"/>
     <mergeCell ref="F37:G37"/>
     <mergeCell ref="C39:D39"/>
@@ -39962,24 +39966,20 @@
     <mergeCell ref="F31:G31"/>
     <mergeCell ref="C33:D33"/>
     <mergeCell ref="F33:G33"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="F41:G41"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="F43:G43"/>
+    <mergeCell ref="C45:D45"/>
+    <mergeCell ref="F45:G45"/>
+    <mergeCell ref="C53:D53"/>
+    <mergeCell ref="F53:G53"/>
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="F47:G47"/>
+    <mergeCell ref="C49:D49"/>
+    <mergeCell ref="F49:G49"/>
+    <mergeCell ref="C51:D51"/>
+    <mergeCell ref="F51:G51"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/DUOL.xlsx
+++ b/DUOL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E68D4584-8393-4645-A012-C78C4068655A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15F947DB-3AB4-7741-BC94-65A87E72FE35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -152,7 +152,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="886" uniqueCount="447">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="896" uniqueCount="451">
   <si>
     <t>Ticker</t>
   </si>
@@ -1493,6 +1493,18 @@
   </si>
   <si>
     <t>Reverse DCF price</t>
+  </si>
+  <si>
+    <t>FCF ratios</t>
+  </si>
+  <si>
+    <t>FCFF/Sales</t>
+  </si>
+  <si>
+    <t>FCFE/Sales</t>
+  </si>
+  <si>
+    <t>Other standard growth rates</t>
   </si>
 </sst>
 </file>
@@ -2468,12 +2480,6 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2483,10 +2489,10 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2498,17 +2504,23 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -13205,11 +13217,11 @@
     <v>Powered by Refinitiv</v>
     <v>318.83999999999997</v>
     <v>87.89</v>
-    <v>1.0646</v>
-    <v>-4.4400000000000004</v>
-    <v>-3.1040000000000002E-2</v>
-    <v>-3.1300000000000001E-2</v>
-    <v>-2.2579999999999999E-4</v>
+    <v>1.0669999999999999</v>
+    <v>2.71</v>
+    <v>1.9553000000000001E-2</v>
+    <v>0.47620000000000001</v>
+    <v>3.3700000000000002E-3</v>
     <v>USD</v>
     <v>Duolingo, Inc. is a technology company. The Company is engaged in offering a mobile learning platform, as well as a digital English language proficiency assessment exam. It operates a freemium business model, namely, the app and the Website are accessible free of charge, although Duolingo also offers premium services for a subscription fee. Its solutions consist of the Duolingo App, Super Duolingo, Duolingo Max, Duolingo English Test: AI-Driven Language Assessment, Duolingo for Schools, and Duolingo ABC. The Duolingo App offers courses in over 40 different languages, including Spanish, English, French, German, Italian, Portuguese, Japanese and Chinese. Duolingo can also be accessed on desktop computers via a Web browser. Its subscription offering, Super Duolingo, offers learners additional features to enhance their learning experience. The Duolingo English Test is an online, on-demand, high-stakes English proficiency assessment. It also operates an animation and motion design studio.</v>
     <v>900</v>
@@ -13217,25 +13229,25 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>5900 PENN AVE, SECOND FLOOR, PITTSBURGH, PA, 15206 US</v>
-    <v>141.5</v>
+    <v>142.52000000000001</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46321.851466666405</v>
+    <v>46322.89167665469</v>
     <v>0</v>
-    <v>134.53</v>
-    <v>6484577022</v>
+    <v>136.51</v>
+    <v>6611367813</v>
     <v>DUOLINGO, INC.</v>
     <v>DUOLINGO, INC.</v>
-    <v>140.72</v>
-    <v>16.520700000000001</v>
-    <v>143.04</v>
+    <v>137.29</v>
+    <v>16.843699999999998</v>
     <v>138.6</v>
-    <v>138.56870000000001</v>
+    <v>141.31</v>
+    <v>141.78620000000001</v>
     <v>46786270</v>
     <v>DUOL</v>
     <v>DUOLINGO, INC. (XNAS:DUOL)</v>
-    <v>1145639</v>
-    <v>905489</v>
+    <v>803479</v>
+    <v>901532</v>
     <v>2011</v>
   </rv>
   <rv s="2">
@@ -13259,17 +13271,17 @@
     <v>Powered by Refinitiv</v>
     <v>53.64</v>
     <v>39.47</v>
-    <v>0.35</v>
-    <v>7.0660000000000002E-3</v>
+    <v>-0.02</v>
+    <v>-4.0099999999999999E-4</v>
     <v>US</v>
     <v>50.03</v>
     <v>Index</v>
     <v>3</v>
-    <v>49.55</v>
+    <v>49.61</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>49.92</v>
-    <v>49.53</v>
+    <v>50.03</v>
     <v>49.88</v>
+    <v>49.86</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -13491,9 +13503,9 @@
       <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq Last Sale</v>
+      <v>Source: Nasdaq</v>
       <v>GMT</v>
-      <v>Real-Time Nasdaq Last Sale</v>
+      <v>Delayed 15 minutes</v>
       <v>from close</v>
       <v>from close</v>
     </spb>
@@ -14095,7 +14107,7 @@
       </c>
       <c r="F3" s="186">
         <f ca="1">Statement!AC149</f>
-        <v>6946909.1999999993</v>
+        <v>7082739.8200000003</v>
       </c>
       <c r="H3" s="184" t="str">
         <f>'AVG target price'!B5</f>
@@ -14103,7 +14115,7 @@
       </c>
       <c r="I3" s="210">
         <f ca="1">'AVG target price'!C5</f>
-        <v>146.68025389330302</v>
+        <v>146.52957244723353</v>
       </c>
       <c r="K3" s="257" t="s">
         <v>441</v>
@@ -14122,7 +14134,7 @@
       </c>
       <c r="F4" s="187">
         <f ca="1">Statement!AC150</f>
-        <v>5530350.1999999993</v>
+        <v>5666180.8200000003</v>
       </c>
       <c r="H4" s="184" t="str">
         <f>'AVG target price'!B6</f>
@@ -14130,7 +14142,7 @@
       </c>
       <c r="I4" s="210">
         <f ca="1">'AVG target price'!C6</f>
-        <v>197.8129340897973</v>
+        <v>197.7481520390493</v>
       </c>
       <c r="K4" s="257" t="s">
         <v>442</v>
@@ -14142,7 +14154,7 @@
       </c>
       <c r="C5" s="207" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>138.6</v>
+        <v>141.31</v>
       </c>
       <c r="E5" s="184" t="s">
         <v>247</v>
@@ -14157,7 +14169,7 @@
       </c>
       <c r="I5" s="210">
         <f ca="1">'AVG target price'!C7</f>
-        <v>159.53703663079153</v>
+        <v>159.47310854801978</v>
       </c>
       <c r="K5" s="257" t="s">
         <v>443</v>
@@ -14169,14 +14181,14 @@
       </c>
       <c r="C6" s="207" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>138.56870000000001</v>
+        <v>141.78620000000001</v>
       </c>
       <c r="E6" s="184" t="s">
         <v>241</v>
       </c>
       <c r="F6" s="189">
         <f ca="1">Statement!AC146</f>
-        <v>44.131737927796031</v>
+        <v>44.994631216283246</v>
       </c>
       <c r="H6" s="184" t="str">
         <f>'AVG target price'!B8</f>
@@ -14184,7 +14196,7 @@
       </c>
       <c r="I6" s="210">
         <f ca="1">'AVG target price'!C8</f>
-        <v>203.33271050853264</v>
+        <v>203.26571662828579</v>
       </c>
       <c r="K6" s="258" t="s">
         <v>444</v>
@@ -14196,14 +14208,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>-4.4400000000000004</v>
+        <v>2.71</v>
       </c>
       <c r="E7" s="185" t="s">
         <v>205</v>
       </c>
       <c r="F7" s="190">
         <f ca="1">Statement!AC147</f>
-        <v>5.9521039572835237</v>
+        <v>6.0684834791034259</v>
       </c>
       <c r="H7" s="184" t="str">
         <f>'AVG target price'!B9</f>
@@ -14211,7 +14223,7 @@
       </c>
       <c r="I7" s="210">
         <f ca="1">'AVG target price'!C9</f>
-        <v>203.75453969996408</v>
+        <v>203.6873767885503</v>
       </c>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.2">
@@ -14220,14 +14232,14 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>-3.1300000000000001E-2</v>
+        <v>0.47620000000000001</v>
       </c>
       <c r="E8" s="184" t="s">
         <v>269</v>
       </c>
       <c r="F8" s="191">
         <f ca="1">Statement!AC157</f>
-        <v>3.6393163163842709E-2</v>
+        <v>3.5695226201320492E-2</v>
       </c>
       <c r="H8" s="183" t="str">
         <f>'AVG target price'!B10</f>
@@ -14235,7 +14247,7 @@
       </c>
       <c r="I8" s="211">
         <f ca="1">'AVG target price'!C10</f>
-        <v>182.22349496447771</v>
+        <v>182.14078529022774</v>
       </c>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.2">
@@ -14244,14 +14256,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>-3.1040000000000002E-2</v>
+        <v>1.9553000000000001E-2</v>
       </c>
       <c r="E9" s="184" t="s">
         <v>292</v>
       </c>
       <c r="F9" s="191">
         <f ca="1">Statement!AC158</f>
-        <v>2.2659429402850637E-2</v>
+        <v>2.2224873789789101E-2</v>
       </c>
       <c r="H9" s="183" t="str">
         <f>'AVG target price'!B12</f>
@@ -14259,7 +14271,7 @@
       </c>
       <c r="I9" s="212">
         <f ca="1">'AVG target price'!C12</f>
-        <v>0.31474383091253766</v>
+        <v>0.28894476887854886</v>
       </c>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.2">
@@ -14268,14 +14280,14 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>-2.2579999999999999E-4</v>
+        <v>3.3700000000000002E-3</v>
       </c>
       <c r="E10" s="184" t="s">
         <v>297</v>
       </c>
       <c r="F10" s="191">
         <f ca="1">Statement!AC160</f>
-        <v>1.0019275910501321E-2</v>
+        <v>9.8271292986730086E-3</v>
       </c>
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.2">
@@ -14323,7 +14335,7 @@
       </c>
       <c r="C13" s="208" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>1.0646</v>
+        <v>1.0669999999999999</v>
       </c>
       <c r="E13" s="184" t="s">
         <v>104</v>
@@ -14346,7 +14358,7 @@
       </c>
       <c r="C14" s="209" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>905489</v>
+        <v>901532</v>
       </c>
       <c r="E14" s="185" t="s">
         <v>105</v>
@@ -14360,7 +14372,7 @@
       </c>
       <c r="I14" s="260">
         <f ca="1">'Reverse DCF'!C16</f>
-        <v>153.51406475701702</v>
+        <v>153.35988200476922</v>
       </c>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.2">
@@ -14369,7 +14381,7 @@
       </c>
       <c r="F15" s="191">
         <f ca="1">Statement!AC172</f>
-        <v>0.20391212253069324</v>
+        <v>0.20000155815408732</v>
       </c>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.2">
@@ -14402,7 +14414,7 @@
       </c>
       <c r="I17" s="255">
         <f ca="1">DCF!C15</f>
-        <v>9.7786999999999999E-2</v>
+        <v>9.787499999999999E-2</v>
       </c>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.2">
@@ -14424,7 +14436,7 @@
       </c>
       <c r="I18" s="256">
         <f ca="1">Multiples!C54</f>
-        <v>9.7786999999999999E-2</v>
+        <v>9.787499999999999E-2</v>
       </c>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
@@ -14497,7 +14509,7 @@
       </c>
       <c r="F26" s="218" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>49.88</v>
+        <v>49.86</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -14512,7 +14524,7 @@
       </c>
       <c r="F27" s="219">
         <f ca="1">F26/1000</f>
-        <v>4.9880000000000001E-2</v>
+        <v>4.9860000000000002E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -14840,8 +14852,8 @@
       <c r="D2" s="265"/>
       <c r="E2" s="265"/>
       <c r="F2" s="265"/>
-      <c r="G2" s="271"/>
-      <c r="H2" s="272" t="s">
+      <c r="G2" s="274"/>
+      <c r="H2" s="275" t="s">
         <v>114</v>
       </c>
       <c r="I2" s="265"/>
@@ -14874,32 +14886,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="273" t="s">
+      <c r="C4" s="271" t="s">
         <v>116</v>
       </c>
-      <c r="D4" s="273"/>
-      <c r="E4" s="273"/>
-      <c r="F4" s="273"/>
-      <c r="G4" s="273"/>
-      <c r="H4" s="273"/>
-      <c r="I4" s="273"/>
-      <c r="J4" s="273"/>
-      <c r="K4" s="273"/>
-      <c r="L4" s="273"/>
+      <c r="D4" s="271"/>
+      <c r="E4" s="271"/>
+      <c r="F4" s="271"/>
+      <c r="G4" s="271"/>
+      <c r="H4" s="271"/>
+      <c r="I4" s="271"/>
+      <c r="J4" s="271"/>
+      <c r="K4" s="271"/>
+      <c r="L4" s="271"/>
       <c r="O4" s="5"/>
-      <c r="S4" s="274" t="s">
+      <c r="S4" s="272" t="s">
         <v>116</v>
       </c>
-      <c r="T4" s="275"/>
-      <c r="U4" s="275"/>
-      <c r="V4" s="275"/>
-      <c r="W4" s="275"/>
-      <c r="X4" s="275"/>
-      <c r="Y4" s="275"/>
-      <c r="Z4" s="275"/>
-      <c r="AA4" s="275"/>
-      <c r="AB4" s="275"/>
-      <c r="AC4" s="275"/>
+      <c r="T4" s="273"/>
+      <c r="U4" s="273"/>
+      <c r="V4" s="273"/>
+      <c r="W4" s="273"/>
+      <c r="X4" s="273"/>
+      <c r="Y4" s="273"/>
+      <c r="Z4" s="273"/>
+      <c r="AA4" s="273"/>
+      <c r="AB4" s="273"/>
+      <c r="AC4" s="273"/>
       <c r="AE4" s="88"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -15587,33 +15599,33 @@
       <c r="Q12" s="92"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="273" t="s">
+      <c r="C13" s="271" t="s">
         <v>122</v>
       </c>
-      <c r="D13" s="273"/>
-      <c r="E13" s="273"/>
-      <c r="F13" s="273"/>
-      <c r="G13" s="273"/>
-      <c r="H13" s="273"/>
-      <c r="I13" s="273"/>
-      <c r="J13" s="273"/>
-      <c r="K13" s="273"/>
-      <c r="L13" s="273"/>
+      <c r="D13" s="271"/>
+      <c r="E13" s="271"/>
+      <c r="F13" s="271"/>
+      <c r="G13" s="271"/>
+      <c r="H13" s="271"/>
+      <c r="I13" s="271"/>
+      <c r="J13" s="271"/>
+      <c r="K13" s="271"/>
+      <c r="L13" s="271"/>
       <c r="O13" s="5"/>
       <c r="Q13" s="92"/>
-      <c r="S13" s="274" t="s">
+      <c r="S13" s="272" t="s">
         <v>122</v>
       </c>
-      <c r="T13" s="275"/>
-      <c r="U13" s="275"/>
-      <c r="V13" s="275"/>
-      <c r="W13" s="275"/>
-      <c r="X13" s="275"/>
-      <c r="Y13" s="275"/>
-      <c r="Z13" s="275"/>
-      <c r="AA13" s="275"/>
-      <c r="AB13" s="275"/>
-      <c r="AC13" s="275"/>
+      <c r="T13" s="273"/>
+      <c r="U13" s="273"/>
+      <c r="V13" s="273"/>
+      <c r="W13" s="273"/>
+      <c r="X13" s="273"/>
+      <c r="Y13" s="273"/>
+      <c r="Z13" s="273"/>
+      <c r="AA13" s="273"/>
+      <c r="AB13" s="273"/>
+      <c r="AC13" s="273"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B14" s="16" t="s">
@@ -16222,33 +16234,33 @@
       <c r="Q22" s="92"/>
     </row>
     <row r="23" spans="2:31" x14ac:dyDescent="0.2">
-      <c r="C23" s="273" t="s">
+      <c r="C23" s="271" t="s">
         <v>124</v>
       </c>
-      <c r="D23" s="273"/>
-      <c r="E23" s="273"/>
-      <c r="F23" s="273"/>
-      <c r="G23" s="273"/>
-      <c r="H23" s="273"/>
-      <c r="I23" s="273"/>
-      <c r="J23" s="273"/>
-      <c r="K23" s="273"/>
-      <c r="L23" s="273"/>
+      <c r="D23" s="271"/>
+      <c r="E23" s="271"/>
+      <c r="F23" s="271"/>
+      <c r="G23" s="271"/>
+      <c r="H23" s="271"/>
+      <c r="I23" s="271"/>
+      <c r="J23" s="271"/>
+      <c r="K23" s="271"/>
+      <c r="L23" s="271"/>
       <c r="O23" s="5"/>
       <c r="Q23" s="92"/>
-      <c r="S23" s="274" t="s">
+      <c r="S23" s="272" t="s">
         <v>124</v>
       </c>
-      <c r="T23" s="275"/>
-      <c r="U23" s="275"/>
-      <c r="V23" s="275"/>
-      <c r="W23" s="275"/>
-      <c r="X23" s="275"/>
-      <c r="Y23" s="275"/>
-      <c r="Z23" s="275"/>
-      <c r="AA23" s="275"/>
-      <c r="AB23" s="275"/>
-      <c r="AC23" s="275"/>
+      <c r="T23" s="273"/>
+      <c r="U23" s="273"/>
+      <c r="V23" s="273"/>
+      <c r="W23" s="273"/>
+      <c r="X23" s="273"/>
+      <c r="Y23" s="273"/>
+      <c r="Z23" s="273"/>
+      <c r="AA23" s="273"/>
+      <c r="AB23" s="273"/>
+      <c r="AC23" s="273"/>
       <c r="AE23" s="88" t="str">
         <f>AE2</f>
         <v>TTM/YTD</v>
@@ -17567,32 +17579,32 @@
       <c r="O39" s="5"/>
     </row>
     <row r="40" spans="2:31" x14ac:dyDescent="0.2">
-      <c r="C40" s="273" t="s">
+      <c r="C40" s="271" t="s">
         <v>126</v>
       </c>
-      <c r="D40" s="273"/>
-      <c r="E40" s="273"/>
-      <c r="F40" s="273"/>
-      <c r="G40" s="273"/>
-      <c r="H40" s="273"/>
-      <c r="I40" s="273"/>
-      <c r="J40" s="273"/>
-      <c r="K40" s="273"/>
-      <c r="L40" s="273"/>
+      <c r="D40" s="271"/>
+      <c r="E40" s="271"/>
+      <c r="F40" s="271"/>
+      <c r="G40" s="271"/>
+      <c r="H40" s="271"/>
+      <c r="I40" s="271"/>
+      <c r="J40" s="271"/>
+      <c r="K40" s="271"/>
+      <c r="L40" s="271"/>
       <c r="O40" s="5"/>
-      <c r="S40" s="274" t="s">
+      <c r="S40" s="272" t="s">
         <v>126</v>
       </c>
-      <c r="T40" s="275"/>
-      <c r="U40" s="275"/>
-      <c r="V40" s="275"/>
-      <c r="W40" s="275"/>
-      <c r="X40" s="275"/>
-      <c r="Y40" s="275"/>
-      <c r="Z40" s="275"/>
-      <c r="AA40" s="275"/>
-      <c r="AB40" s="275"/>
-      <c r="AC40" s="275"/>
+      <c r="T40" s="273"/>
+      <c r="U40" s="273"/>
+      <c r="V40" s="273"/>
+      <c r="W40" s="273"/>
+      <c r="X40" s="273"/>
+      <c r="Y40" s="273"/>
+      <c r="Z40" s="273"/>
+      <c r="AA40" s="273"/>
+      <c r="AB40" s="273"/>
+      <c r="AC40" s="273"/>
     </row>
     <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -18159,18 +18171,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="S2:Z2"/>
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="S4:AC4"/>
     <mergeCell ref="C13:L13"/>
     <mergeCell ref="S13:AC13"/>
     <mergeCell ref="C23:L23"/>
     <mergeCell ref="S23:AC23"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="S40:AC40"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="S2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="S4:AC4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -18210,8 +18222,8 @@
       <c r="D2" s="265"/>
       <c r="E2" s="265"/>
       <c r="F2" s="265"/>
-      <c r="G2" s="271"/>
-      <c r="H2" s="272" t="s">
+      <c r="G2" s="274"/>
+      <c r="H2" s="275" t="s">
         <v>114</v>
       </c>
       <c r="I2" s="265"/>
@@ -18241,31 +18253,31 @@
     <row r="4" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="273" t="s">
+      <c r="C4" s="271" t="s">
         <v>116</v>
       </c>
-      <c r="D4" s="273"/>
-      <c r="E4" s="273"/>
-      <c r="F4" s="273"/>
-      <c r="G4" s="273"/>
-      <c r="H4" s="273"/>
-      <c r="I4" s="273"/>
-      <c r="J4" s="273"/>
-      <c r="K4" s="273"/>
-      <c r="L4" s="273"/>
-      <c r="P4" s="275" t="s">
+      <c r="D4" s="271"/>
+      <c r="E4" s="271"/>
+      <c r="F4" s="271"/>
+      <c r="G4" s="271"/>
+      <c r="H4" s="271"/>
+      <c r="I4" s="271"/>
+      <c r="J4" s="271"/>
+      <c r="K4" s="271"/>
+      <c r="L4" s="271"/>
+      <c r="P4" s="273" t="s">
         <v>116</v>
       </c>
-      <c r="Q4" s="275"/>
-      <c r="R4" s="275"/>
-      <c r="S4" s="275"/>
-      <c r="T4" s="275"/>
-      <c r="U4" s="275"/>
-      <c r="V4" s="275"/>
-      <c r="W4" s="275"/>
-      <c r="X4" s="275"/>
-      <c r="Y4" s="275"/>
-      <c r="Z4" s="275"/>
+      <c r="Q4" s="273"/>
+      <c r="R4" s="273"/>
+      <c r="S4" s="273"/>
+      <c r="T4" s="273"/>
+      <c r="U4" s="273"/>
+      <c r="V4" s="273"/>
+      <c r="W4" s="273"/>
+      <c r="X4" s="273"/>
+      <c r="Y4" s="273"/>
+      <c r="Z4" s="273"/>
       <c r="AB4" s="88"/>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
@@ -18460,32 +18472,32 @@
       <c r="N8" s="92"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C9" s="273" t="s">
+      <c r="C9" s="271" t="s">
         <v>129</v>
       </c>
-      <c r="D9" s="273"/>
-      <c r="E9" s="273"/>
-      <c r="F9" s="273"/>
-      <c r="G9" s="273"/>
-      <c r="H9" s="273"/>
-      <c r="I9" s="273"/>
-      <c r="J9" s="273"/>
-      <c r="K9" s="273"/>
-      <c r="L9" s="273"/>
+      <c r="D9" s="271"/>
+      <c r="E9" s="271"/>
+      <c r="F9" s="271"/>
+      <c r="G9" s="271"/>
+      <c r="H9" s="271"/>
+      <c r="I9" s="271"/>
+      <c r="J9" s="271"/>
+      <c r="K9" s="271"/>
+      <c r="L9" s="271"/>
       <c r="N9" s="92"/>
-      <c r="P9" s="275" t="s">
+      <c r="P9" s="273" t="s">
         <v>130</v>
       </c>
-      <c r="Q9" s="275"/>
-      <c r="R9" s="275"/>
-      <c r="S9" s="275"/>
-      <c r="T9" s="275"/>
-      <c r="U9" s="275"/>
-      <c r="V9" s="275"/>
-      <c r="W9" s="275"/>
-      <c r="X9" s="275"/>
-      <c r="Y9" s="275"/>
-      <c r="Z9" s="275"/>
+      <c r="Q9" s="273"/>
+      <c r="R9" s="273"/>
+      <c r="S9" s="273"/>
+      <c r="T9" s="273"/>
+      <c r="U9" s="273"/>
+      <c r="V9" s="273"/>
+      <c r="W9" s="273"/>
+      <c r="X9" s="273"/>
+      <c r="Y9" s="273"/>
+      <c r="Z9" s="273"/>
       <c r="AB9" s="88">
         <f>AB4</f>
         <v>0</v>
@@ -19055,31 +19067,31 @@
       </c>
     </row>
     <row r="18" spans="2:26" x14ac:dyDescent="0.2">
-      <c r="C18" s="273" t="s">
+      <c r="C18" s="271" t="s">
         <v>132</v>
       </c>
-      <c r="D18" s="273"/>
-      <c r="E18" s="273"/>
-      <c r="F18" s="273"/>
-      <c r="G18" s="273"/>
-      <c r="H18" s="273"/>
-      <c r="I18" s="273"/>
-      <c r="J18" s="273"/>
-      <c r="K18" s="273"/>
-      <c r="L18" s="273"/>
-      <c r="P18" s="275" t="s">
+      <c r="D18" s="271"/>
+      <c r="E18" s="271"/>
+      <c r="F18" s="271"/>
+      <c r="G18" s="271"/>
+      <c r="H18" s="271"/>
+      <c r="I18" s="271"/>
+      <c r="J18" s="271"/>
+      <c r="K18" s="271"/>
+      <c r="L18" s="271"/>
+      <c r="P18" s="273" t="s">
         <v>132</v>
       </c>
-      <c r="Q18" s="275"/>
-      <c r="R18" s="275"/>
-      <c r="S18" s="275"/>
-      <c r="T18" s="275"/>
-      <c r="U18" s="275"/>
-      <c r="V18" s="275"/>
-      <c r="W18" s="275"/>
-      <c r="X18" s="275"/>
-      <c r="Y18" s="275"/>
-      <c r="Z18" s="275"/>
+      <c r="Q18" s="273"/>
+      <c r="R18" s="273"/>
+      <c r="S18" s="273"/>
+      <c r="T18" s="273"/>
+      <c r="U18" s="273"/>
+      <c r="V18" s="273"/>
+      <c r="W18" s="273"/>
+      <c r="X18" s="273"/>
+      <c r="Y18" s="273"/>
+      <c r="Z18" s="273"/>
     </row>
     <row r="19" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -19645,8 +19657,8 @@
       <c r="D3" s="265"/>
       <c r="E3" s="265"/>
       <c r="F3" s="265"/>
-      <c r="G3" s="271"/>
-      <c r="H3" s="272" t="s">
+      <c r="G3" s="274"/>
+      <c r="H3" s="275" t="s">
         <v>114</v>
       </c>
       <c r="I3" s="265"/>
@@ -19670,18 +19682,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="87"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="273" t="s">
+      <c r="C5" s="271" t="s">
         <v>116</v>
       </c>
-      <c r="D5" s="273"/>
-      <c r="E5" s="273"/>
-      <c r="F5" s="273"/>
-      <c r="G5" s="273"/>
-      <c r="H5" s="273"/>
-      <c r="I5" s="273"/>
-      <c r="J5" s="273"/>
-      <c r="K5" s="273"/>
-      <c r="L5" s="273"/>
+      <c r="D5" s="271"/>
+      <c r="E5" s="271"/>
+      <c r="F5" s="271"/>
+      <c r="G5" s="271"/>
+      <c r="H5" s="271"/>
+      <c r="I5" s="271"/>
+      <c r="J5" s="271"/>
+      <c r="K5" s="271"/>
+      <c r="L5" s="271"/>
       <c r="P5" s="276"/>
       <c r="Q5" s="276"/>
       <c r="R5" s="276"/>
@@ -19878,18 +19890,18 @@
       <c r="N10" s="92"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="273" t="s">
+      <c r="C11" s="271" t="s">
         <v>136</v>
       </c>
-      <c r="D11" s="273"/>
-      <c r="E11" s="273"/>
-      <c r="F11" s="273"/>
-      <c r="G11" s="273"/>
-      <c r="H11" s="273"/>
-      <c r="I11" s="273"/>
-      <c r="J11" s="273"/>
-      <c r="K11" s="273"/>
-      <c r="L11" s="273"/>
+      <c r="D11" s="271"/>
+      <c r="E11" s="271"/>
+      <c r="F11" s="271"/>
+      <c r="G11" s="271"/>
+      <c r="H11" s="271"/>
+      <c r="I11" s="271"/>
+      <c r="J11" s="271"/>
+      <c r="K11" s="271"/>
+      <c r="L11" s="271"/>
       <c r="N11" s="92"/>
       <c r="P11" s="276"/>
       <c r="Q11" s="276"/>
@@ -20143,18 +20155,18 @@
       <c r="D16" s="24"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="273" t="s">
+      <c r="C18" s="271" t="s">
         <v>141</v>
       </c>
-      <c r="D18" s="273"/>
-      <c r="E18" s="273"/>
-      <c r="F18" s="273"/>
-      <c r="G18" s="273"/>
-      <c r="H18" s="273"/>
-      <c r="I18" s="273"/>
-      <c r="J18" s="273"/>
-      <c r="K18" s="273"/>
-      <c r="L18" s="273"/>
+      <c r="D18" s="271"/>
+      <c r="E18" s="271"/>
+      <c r="F18" s="271"/>
+      <c r="G18" s="271"/>
+      <c r="H18" s="271"/>
+      <c r="I18" s="271"/>
+      <c r="J18" s="271"/>
+      <c r="K18" s="271"/>
+      <c r="L18" s="271"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -20372,18 +20384,18 @@
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="111"/>
-      <c r="C26" s="273" t="s">
+      <c r="C26" s="271" t="s">
         <v>147</v>
       </c>
-      <c r="D26" s="273"/>
-      <c r="E26" s="273"/>
-      <c r="F26" s="273"/>
-      <c r="G26" s="273"/>
-      <c r="H26" s="273"/>
-      <c r="I26" s="273"/>
-      <c r="J26" s="273"/>
-      <c r="K26" s="273"/>
-      <c r="L26" s="273"/>
+      <c r="D26" s="271"/>
+      <c r="E26" s="271"/>
+      <c r="F26" s="271"/>
+      <c r="G26" s="271"/>
+      <c r="H26" s="271"/>
+      <c r="I26" s="271"/>
+      <c r="J26" s="271"/>
+      <c r="K26" s="271"/>
+      <c r="L26" s="271"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="16" t="s">
@@ -20575,18 +20587,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="111"/>
-      <c r="C33" s="273" t="s">
+      <c r="C33" s="271" t="s">
         <v>151</v>
       </c>
-      <c r="D33" s="273"/>
-      <c r="E33" s="273"/>
-      <c r="F33" s="273"/>
-      <c r="G33" s="273"/>
-      <c r="H33" s="273"/>
-      <c r="I33" s="273"/>
-      <c r="J33" s="273"/>
-      <c r="K33" s="273"/>
-      <c r="L33" s="273"/>
+      <c r="D33" s="271"/>
+      <c r="E33" s="271"/>
+      <c r="F33" s="271"/>
+      <c r="G33" s="271"/>
+      <c r="H33" s="271"/>
+      <c r="I33" s="271"/>
+      <c r="J33" s="271"/>
+      <c r="K33" s="271"/>
+      <c r="L33" s="271"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
@@ -20770,18 +20782,18 @@
       <c r="C39" s="127"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="273" t="s">
+      <c r="C40" s="271" t="s">
         <v>154</v>
       </c>
-      <c r="D40" s="273"/>
-      <c r="E40" s="273"/>
-      <c r="F40" s="273"/>
-      <c r="G40" s="273"/>
-      <c r="H40" s="273"/>
-      <c r="I40" s="273"/>
-      <c r="J40" s="273"/>
-      <c r="K40" s="273"/>
-      <c r="L40" s="273"/>
+      <c r="D40" s="271"/>
+      <c r="E40" s="271"/>
+      <c r="F40" s="271"/>
+      <c r="G40" s="271"/>
+      <c r="H40" s="271"/>
+      <c r="I40" s="271"/>
+      <c r="J40" s="271"/>
+      <c r="K40" s="271"/>
+      <c r="L40" s="271"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -21045,12 +21057,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -21058,6 +21064,12 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -21101,8 +21113,8 @@
       <c r="D2" s="265"/>
       <c r="E2" s="265"/>
       <c r="F2" s="265"/>
-      <c r="G2" s="271"/>
-      <c r="H2" s="272" t="s">
+      <c r="G2" s="274"/>
+      <c r="H2" s="275" t="s">
         <v>114</v>
       </c>
       <c r="I2" s="265"/>
@@ -21126,18 +21138,18 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="273" t="s">
+      <c r="C4" s="271" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="273"/>
-      <c r="E4" s="273"/>
-      <c r="F4" s="273"/>
-      <c r="G4" s="273"/>
-      <c r="H4" s="273"/>
-      <c r="I4" s="273"/>
-      <c r="J4" s="273"/>
-      <c r="K4" s="273"/>
-      <c r="L4" s="273"/>
+      <c r="D4" s="271"/>
+      <c r="E4" s="271"/>
+      <c r="F4" s="271"/>
+      <c r="G4" s="271"/>
+      <c r="H4" s="271"/>
+      <c r="I4" s="271"/>
+      <c r="J4" s="271"/>
+      <c r="K4" s="271"/>
+      <c r="L4" s="271"/>
       <c r="S4" s="276"/>
       <c r="T4" s="276"/>
       <c r="U4" s="276"/>
@@ -21511,18 +21523,18 @@
       <c r="AE10" s="64"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="273" t="s">
+      <c r="C13" s="271" t="s">
         <v>162</v>
       </c>
-      <c r="D13" s="273"/>
-      <c r="E13" s="273"/>
-      <c r="F13" s="273"/>
-      <c r="G13" s="273"/>
-      <c r="H13" s="273"/>
-      <c r="I13" s="273"/>
-      <c r="J13" s="273"/>
-      <c r="K13" s="273"/>
-      <c r="L13" s="273"/>
+      <c r="D13" s="271"/>
+      <c r="E13" s="271"/>
+      <c r="F13" s="271"/>
+      <c r="G13" s="271"/>
+      <c r="H13" s="271"/>
+      <c r="I13" s="271"/>
+      <c r="J13" s="271"/>
+      <c r="K13" s="271"/>
+      <c r="L13" s="271"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="12">
@@ -21615,18 +21627,18 @@
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C18" s="273" t="s">
+      <c r="C18" s="271" t="s">
         <v>163</v>
       </c>
-      <c r="D18" s="273"/>
-      <c r="E18" s="273"/>
-      <c r="F18" s="273"/>
-      <c r="G18" s="273"/>
-      <c r="H18" s="273"/>
-      <c r="I18" s="273"/>
-      <c r="J18" s="273"/>
-      <c r="K18" s="273"/>
-      <c r="L18" s="273"/>
+      <c r="D18" s="271"/>
+      <c r="E18" s="271"/>
+      <c r="F18" s="271"/>
+      <c r="G18" s="271"/>
+      <c r="H18" s="271"/>
+      <c r="I18" s="271"/>
+      <c r="J18" s="271"/>
+      <c r="K18" s="271"/>
+      <c r="L18" s="271"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -21818,18 +21830,18 @@
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C25" s="273" t="s">
+      <c r="C25" s="271" t="s">
         <v>266</v>
       </c>
-      <c r="D25" s="273"/>
-      <c r="E25" s="273"/>
-      <c r="F25" s="273"/>
-      <c r="G25" s="273"/>
-      <c r="H25" s="273"/>
-      <c r="I25" s="273"/>
-      <c r="J25" s="273"/>
-      <c r="K25" s="273"/>
-      <c r="L25" s="273"/>
+      <c r="D25" s="271"/>
+      <c r="E25" s="271"/>
+      <c r="F25" s="271"/>
+      <c r="G25" s="271"/>
+      <c r="H25" s="271"/>
+      <c r="I25" s="271"/>
+      <c r="J25" s="271"/>
+      <c r="K25" s="271"/>
+      <c r="L25" s="271"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B26" s="16" t="s">
@@ -21967,18 +21979,18 @@
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C31" s="273" t="s">
+      <c r="C31" s="271" t="s">
         <v>78</v>
       </c>
-      <c r="D31" s="273"/>
-      <c r="E31" s="273"/>
-      <c r="F31" s="273"/>
-      <c r="G31" s="273"/>
-      <c r="H31" s="273"/>
-      <c r="I31" s="273"/>
-      <c r="J31" s="273"/>
-      <c r="K31" s="273"/>
-      <c r="L31" s="273"/>
+      <c r="D31" s="271"/>
+      <c r="E31" s="271"/>
+      <c r="F31" s="271"/>
+      <c r="G31" s="271"/>
+      <c r="H31" s="271"/>
+      <c r="I31" s="271"/>
+      <c r="J31" s="271"/>
+      <c r="K31" s="271"/>
+      <c r="L31" s="271"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="16" t="s">
@@ -22117,16 +22129,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C31:L31"/>
+    <mergeCell ref="C25:L25"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="S2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
     <mergeCell ref="C13:L13"/>
     <mergeCell ref="C18:L18"/>
-    <mergeCell ref="C31:L31"/>
-    <mergeCell ref="C25:L25"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="S2:Z2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -22248,7 +22260,7 @@
       </c>
       <c r="C6" s="135">
         <f ca="1">Overview!C5</f>
-        <v>138.6</v>
+        <v>141.31</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22257,7 +22269,7 @@
       </c>
       <c r="C7" s="136">
         <f ca="1">C5*C6</f>
-        <v>6946909.1999999993</v>
+        <v>7082739.8200000003</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22275,7 +22287,7 @@
       </c>
       <c r="C9" s="137">
         <f ca="1">Overview!F27</f>
-        <v>4.9880000000000001E-2</v>
+        <v>4.9860000000000002E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22284,7 +22296,7 @@
       </c>
       <c r="C10" s="135">
         <f ca="1">Overview!C13</f>
-        <v>1.0646</v>
+        <v>1.0669999999999999</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22354,7 +22366,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>9.7786999999999999E-2</v>
+        <v>9.787499999999999E-2</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22363,7 +22375,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>9.7786999999999999E-2</v>
+        <v>9.787499999999999E-2</v>
       </c>
     </row>
   </sheetData>
@@ -22414,8 +22426,8 @@
       <c r="D3" s="265"/>
       <c r="E3" s="265"/>
       <c r="F3" s="265"/>
-      <c r="G3" s="271"/>
-      <c r="H3" s="272" t="s">
+      <c r="G3" s="274"/>
+      <c r="H3" s="275" t="s">
         <v>114</v>
       </c>
       <c r="I3" s="265"/>
@@ -22439,18 +22451,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="87"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="273" t="s">
+      <c r="C5" s="271" t="s">
         <v>184</v>
       </c>
-      <c r="D5" s="273"/>
-      <c r="E5" s="273"/>
-      <c r="F5" s="273"/>
-      <c r="G5" s="273"/>
-      <c r="H5" s="273"/>
-      <c r="I5" s="273"/>
-      <c r="J5" s="273"/>
-      <c r="K5" s="273"/>
-      <c r="L5" s="273"/>
+      <c r="D5" s="271"/>
+      <c r="E5" s="271"/>
+      <c r="F5" s="271"/>
+      <c r="G5" s="271"/>
+      <c r="H5" s="271"/>
+      <c r="I5" s="271"/>
+      <c r="J5" s="271"/>
+      <c r="K5" s="271"/>
+      <c r="L5" s="271"/>
       <c r="P5" s="276"/>
       <c r="Q5" s="276"/>
       <c r="R5" s="276"/>
@@ -22614,7 +22626,7 @@
       </c>
       <c r="L8" s="128">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>7526690.3384721829</v>
+        <v>7518185.0575760612</v>
       </c>
       <c r="N8" s="92"/>
       <c r="O8" s="16"/>
@@ -22668,23 +22680,23 @@
       <c r="G10" s="140"/>
       <c r="H10" s="128">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>164670.5344764</v>
+        <v>164657.33533530115</v>
       </c>
       <c r="I10" s="128">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>199580.66016047809</v>
+        <v>199548.66672914865</v>
       </c>
       <c r="J10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>227886.48667114065</v>
+        <v>227831.69244563085</v>
       </c>
       <c r="K10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>262417.52039291413</v>
+        <v>262333.39436599764</v>
       </c>
       <c r="L10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>360014.90520035184</v>
+        <v>359870.64363485732</v>
       </c>
       <c r="N10" s="92"/>
     </row>
@@ -22703,7 +22715,7 @@
       <c r="K11" s="139"/>
       <c r="L11" s="128">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>4720778.5787388496</v>
+        <v>4713554.4976893039</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
@@ -22726,7 +22738,7 @@
       </c>
       <c r="C15" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>9.7786999999999999E-2</v>
+        <v>9.787499999999999E-2</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
@@ -22741,7 +22753,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>1214570.1069012848</v>
+        <v>1214241.7325109355</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -22750,7 +22762,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>4720778.5787388496</v>
+        <v>4713554.4976893039</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -22759,7 +22771,7 @@
       </c>
       <c r="C21" s="95">
         <f ca="1">C19+C20</f>
-        <v>5935348.6856401339</v>
+        <v>5927796.2302002395</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -22786,7 +22798,7 @@
       </c>
       <c r="C24" s="95">
         <f ca="1">C21+C22-C23</f>
-        <v>7351907.6856401339</v>
+        <v>7344355.2302002395</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -22804,7 +22816,7 @@
       </c>
       <c r="C26" s="254">
         <f ca="1">C24/C25</f>
-        <v>146.68025389330302</v>
+        <v>146.52957244723353</v>
       </c>
     </row>
   </sheetData>
@@ -22853,8 +22865,8 @@
       <c r="D2" s="265"/>
       <c r="E2" s="265"/>
       <c r="F2" s="265"/>
-      <c r="G2" s="271"/>
-      <c r="H2" s="272" t="s">
+      <c r="G2" s="274"/>
+      <c r="H2" s="275" t="s">
         <v>114</v>
       </c>
       <c r="I2" s="265"/>
@@ -22866,18 +22878,18 @@
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="273" t="s">
+      <c r="C4" s="271" t="s">
         <v>198</v>
       </c>
-      <c r="D4" s="273"/>
-      <c r="E4" s="273"/>
-      <c r="F4" s="273"/>
-      <c r="G4" s="273"/>
-      <c r="H4" s="273"/>
-      <c r="I4" s="273"/>
-      <c r="J4" s="273"/>
-      <c r="K4" s="273"/>
-      <c r="L4" s="273"/>
+      <c r="D4" s="271"/>
+      <c r="E4" s="271"/>
+      <c r="F4" s="271"/>
+      <c r="G4" s="271"/>
+      <c r="H4" s="271"/>
+      <c r="I4" s="271"/>
+      <c r="J4" s="271"/>
+      <c r="K4" s="271"/>
+      <c r="L4" s="271"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -23073,23 +23085,23 @@
       <c r="G9" s="140"/>
       <c r="H9" s="93">
         <f ca="1">DCF!H10</f>
-        <v>164670.5344764</v>
+        <v>164657.33533530115</v>
       </c>
       <c r="I9" s="93">
         <f ca="1">DCF!I10</f>
-        <v>199580.66016047809</v>
+        <v>199548.66672914865</v>
       </c>
       <c r="J9" s="93">
         <f ca="1">DCF!J10</f>
-        <v>227886.48667114065</v>
+        <v>227831.69244563085</v>
       </c>
       <c r="K9" s="93">
         <f ca="1">DCF!K10</f>
-        <v>262417.52039291413</v>
+        <v>262333.39436599764</v>
       </c>
       <c r="L9" s="93">
         <f ca="1">DCF!L10</f>
-        <v>360014.90520035184</v>
+        <v>359870.64363485732</v>
       </c>
       <c r="N9" s="92"/>
     </row>
@@ -23097,18 +23109,18 @@
       <c r="N10" s="92"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C11" s="273" t="s">
+      <c r="C11" s="271" t="s">
         <v>122</v>
       </c>
-      <c r="D11" s="273"/>
-      <c r="E11" s="273"/>
-      <c r="F11" s="273"/>
-      <c r="G11" s="273"/>
-      <c r="H11" s="273"/>
-      <c r="I11" s="273"/>
-      <c r="J11" s="273"/>
-      <c r="K11" s="273"/>
-      <c r="L11" s="273"/>
+      <c r="D11" s="271"/>
+      <c r="E11" s="271"/>
+      <c r="F11" s="271"/>
+      <c r="G11" s="271"/>
+      <c r="H11" s="271"/>
+      <c r="I11" s="271"/>
+      <c r="J11" s="271"/>
+      <c r="K11" s="271"/>
+      <c r="L11" s="271"/>
       <c r="N11" s="92"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -23302,18 +23314,18 @@
       <c r="N16" s="92"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C17" s="273" t="s">
+      <c r="C17" s="271" t="s">
         <v>200</v>
       </c>
-      <c r="D17" s="273"/>
-      <c r="E17" s="273"/>
-      <c r="F17" s="273"/>
-      <c r="G17" s="273"/>
-      <c r="H17" s="273"/>
-      <c r="I17" s="273"/>
-      <c r="J17" s="273"/>
-      <c r="K17" s="273"/>
-      <c r="L17" s="273"/>
+      <c r="D17" s="271"/>
+      <c r="E17" s="271"/>
+      <c r="F17" s="271"/>
+      <c r="G17" s="271"/>
+      <c r="H17" s="271"/>
+      <c r="I17" s="271"/>
+      <c r="J17" s="271"/>
+      <c r="K17" s="271"/>
+      <c r="L17" s="271"/>
       <c r="N17" s="92"/>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
@@ -23447,18 +23459,18 @@
       <c r="N21" s="92"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C22" s="273" t="s">
+      <c r="C22" s="271" t="s">
         <v>203</v>
       </c>
-      <c r="D22" s="273"/>
-      <c r="E22" s="273"/>
-      <c r="F22" s="273"/>
-      <c r="G22" s="273"/>
-      <c r="H22" s="273"/>
-      <c r="I22" s="273"/>
-      <c r="J22" s="273"/>
-      <c r="K22" s="273"/>
-      <c r="L22" s="273"/>
+      <c r="D22" s="271"/>
+      <c r="E22" s="271"/>
+      <c r="F22" s="271"/>
+      <c r="G22" s="271"/>
+      <c r="H22" s="271"/>
+      <c r="I22" s="271"/>
+      <c r="J22" s="271"/>
+      <c r="K22" s="271"/>
+      <c r="L22" s="271"/>
       <c r="N22" s="92"/>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.2">
@@ -23542,18 +23554,18 @@
       <c r="N26" s="92"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C27" s="273" t="s">
+      <c r="C27" s="271" t="s">
         <v>204</v>
       </c>
-      <c r="D27" s="273"/>
-      <c r="E27" s="273"/>
-      <c r="F27" s="273"/>
-      <c r="G27" s="273"/>
-      <c r="H27" s="273"/>
-      <c r="I27" s="273"/>
-      <c r="J27" s="273"/>
-      <c r="K27" s="273"/>
-      <c r="L27" s="273"/>
+      <c r="D27" s="271"/>
+      <c r="E27" s="271"/>
+      <c r="F27" s="271"/>
+      <c r="G27" s="271"/>
+      <c r="H27" s="271"/>
+      <c r="I27" s="271"/>
+      <c r="J27" s="271"/>
+      <c r="K27" s="271"/>
+      <c r="L27" s="271"/>
       <c r="N27" s="92"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.2">
@@ -23875,7 +23887,7 @@
       </c>
       <c r="C41" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>9.7786999999999999E-2</v>
+        <v>9.787499999999999E-2</v>
       </c>
     </row>
     <row r="42" spans="2:14" x14ac:dyDescent="0.2">
@@ -23901,7 +23913,7 @@
       </c>
       <c r="C44" s="24">
         <f ca="1">C43/(1+C41)^5</f>
-        <v>7643665.6807478881</v>
+        <v>7640602.7876251498</v>
       </c>
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.2">
@@ -23910,7 +23922,7 @@
       </c>
       <c r="C45" s="110">
         <f ca="1">SUM(H9:K9)+C44</f>
-        <v>8498220.8824488204</v>
+        <v>8494973.8765012287</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -23937,7 +23949,7 @@
       </c>
       <c r="C48" s="110">
         <f ca="1">C45+C46-C47</f>
-        <v>9914779.8824488204</v>
+        <v>9911532.8765012287</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
@@ -23955,7 +23967,7 @@
       </c>
       <c r="C50" s="254">
         <f ca="1">C48/C49</f>
-        <v>197.8129340897973</v>
+        <v>197.7481520390493</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
@@ -23979,7 +23991,7 @@
       </c>
       <c r="C54" s="137">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>9.7786999999999999E-2</v>
+        <v>9.787499999999999E-2</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
@@ -24014,7 +24026,7 @@
       </c>
       <c r="C58" s="254">
         <f ca="1">C57/(1+C54)^5</f>
-        <v>159.53703663079153</v>
+        <v>159.47310854801978</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
@@ -24038,7 +24050,7 @@
       </c>
       <c r="C62" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>9.7786999999999999E-2</v>
+        <v>9.787499999999999E-2</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
@@ -24064,7 +24076,7 @@
       </c>
       <c r="C65" s="24">
         <f ca="1">C64/(1+C62)^5</f>
-        <v>7920327.9144077403</v>
+        <v>7917154.1599668609</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -24073,7 +24085,7 @@
       </c>
       <c r="C66" s="110">
         <f ca="1">SUM(H9:K9)+C65</f>
-        <v>8774883.1161086727</v>
+        <v>8771525.2488429397</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.2">
@@ -24100,7 +24112,7 @@
       </c>
       <c r="C69" s="110">
         <f ca="1">C66+C67-C68</f>
-        <v>10191442.116108673</v>
+        <v>10188084.24884294</v>
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.2">
@@ -24118,7 +24130,7 @@
       </c>
       <c r="C71" s="254">
         <f ca="1">C69/C70</f>
-        <v>203.33271050853264</v>
+        <v>203.26571662828579</v>
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.2">
@@ -24142,7 +24154,7 @@
       </c>
       <c r="C75" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>9.7786999999999999E-2</v>
+        <v>9.787499999999999E-2</v>
       </c>
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.2">
@@ -24168,7 +24180,7 @@
       </c>
       <c r="C78" s="24">
         <f ca="1">C77/(1+C75)^5</f>
-        <v>7941470.8371406673</v>
+        <v>7938288.6105196401</v>
       </c>
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.2">
@@ -24177,7 +24189,7 @@
       </c>
       <c r="C79" s="110">
         <f ca="1">SUM(H9:K9)+C78</f>
-        <v>8796026.0388415996</v>
+        <v>8792659.6993957181</v>
       </c>
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.2">
@@ -24204,7 +24216,7 @@
       </c>
       <c r="C82" s="110">
         <f ca="1">C79+C80-C81</f>
-        <v>10212585.0388416</v>
+        <v>10209218.699395718</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.2">
@@ -24222,22 +24234,22 @@
       </c>
       <c r="C84" s="254">
         <f ca="1">C82/C83</f>
-        <v>203.75453969996408</v>
+        <v>203.6873767885503</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="C27:L27"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B60:C60"/>
     <mergeCell ref="C22:L22"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="C17:L17"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="C27:L27"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B60:C60"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -24287,7 +24299,7 @@
       </c>
       <c r="C5" s="135">
         <f ca="1">DCF!C26</f>
-        <v>146.68025389330302</v>
+        <v>146.52957244723353</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -24296,7 +24308,7 @@
       </c>
       <c r="C6" s="135">
         <f ca="1">Multiples!C50</f>
-        <v>197.8129340897973</v>
+        <v>197.7481520390493</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -24305,7 +24317,7 @@
       </c>
       <c r="C7" s="135">
         <f ca="1">Multiples!C58</f>
-        <v>159.53703663079153</v>
+        <v>159.47310854801978</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -24314,7 +24326,7 @@
       </c>
       <c r="C8" s="135">
         <f ca="1">Multiples!C71</f>
-        <v>203.33271050853264</v>
+        <v>203.26571662828579</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -24323,7 +24335,7 @@
       </c>
       <c r="C9" s="135">
         <f ca="1">Multiples!C84</f>
-        <v>203.75453969996408</v>
+        <v>203.6873767885503</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -24332,7 +24344,7 @@
       </c>
       <c r="C10" s="254">
         <f ca="1">AVERAGE(C5:C9)</f>
-        <v>182.22349496447771</v>
+        <v>182.14078529022774</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -24341,7 +24353,7 @@
       </c>
       <c r="C11" s="135">
         <f ca="1">Overview!C5</f>
-        <v>138.6</v>
+        <v>141.31</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -24350,7 +24362,7 @@
       </c>
       <c r="C12" s="154">
         <f ca="1">(C10-C11)/C11</f>
-        <v>0.31474383091253766</v>
+        <v>0.28894476887854886</v>
       </c>
     </row>
   </sheetData>
@@ -24451,8 +24463,8 @@
       <c r="D2" s="265"/>
       <c r="E2" s="265"/>
       <c r="F2" s="265"/>
-      <c r="G2" s="271"/>
-      <c r="H2" s="272" t="s">
+      <c r="G2" s="274"/>
+      <c r="H2" s="275" t="s">
         <v>114</v>
       </c>
       <c r="I2" s="265"/>
@@ -24464,18 +24476,18 @@
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="273" t="s">
+      <c r="C4" s="271" t="s">
         <v>198</v>
       </c>
-      <c r="D4" s="273"/>
-      <c r="E4" s="273"/>
-      <c r="F4" s="273"/>
-      <c r="G4" s="273"/>
-      <c r="H4" s="273"/>
-      <c r="I4" s="273"/>
-      <c r="J4" s="273"/>
-      <c r="K4" s="273"/>
-      <c r="L4" s="273"/>
+      <c r="D4" s="271"/>
+      <c r="E4" s="271"/>
+      <c r="F4" s="271"/>
+      <c r="G4" s="271"/>
+      <c r="H4" s="271"/>
+      <c r="I4" s="271"/>
+      <c r="J4" s="271"/>
+      <c r="K4" s="271"/>
+      <c r="L4" s="271"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -24588,18 +24600,18 @@
       <c r="N8" s="92"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C9" s="273" t="s">
+      <c r="C9" s="271" t="s">
         <v>122</v>
       </c>
-      <c r="D9" s="273"/>
-      <c r="E9" s="273"/>
-      <c r="F9" s="273"/>
-      <c r="G9" s="273"/>
-      <c r="H9" s="273"/>
-      <c r="I9" s="273"/>
-      <c r="J9" s="273"/>
-      <c r="K9" s="273"/>
-      <c r="L9" s="273"/>
+      <c r="D9" s="271"/>
+      <c r="E9" s="271"/>
+      <c r="F9" s="271"/>
+      <c r="G9" s="271"/>
+      <c r="H9" s="271"/>
+      <c r="I9" s="271"/>
+      <c r="J9" s="271"/>
+      <c r="K9" s="271"/>
+      <c r="L9" s="271"/>
       <c r="N9" s="92"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -24720,18 +24732,18 @@
       <c r="N13" s="92"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C14" s="273" t="s">
+      <c r="C14" s="271" t="s">
         <v>413</v>
       </c>
-      <c r="D14" s="273"/>
-      <c r="E14" s="273"/>
-      <c r="F14" s="273"/>
-      <c r="G14" s="273"/>
-      <c r="H14" s="273"/>
-      <c r="I14" s="273"/>
-      <c r="J14" s="273"/>
-      <c r="K14" s="273"/>
-      <c r="L14" s="273"/>
+      <c r="D14" s="271"/>
+      <c r="E14" s="271"/>
+      <c r="F14" s="271"/>
+      <c r="G14" s="271"/>
+      <c r="H14" s="271"/>
+      <c r="I14" s="271"/>
+      <c r="J14" s="271"/>
+      <c r="K14" s="271"/>
+      <c r="L14" s="271"/>
       <c r="N14" s="92"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
@@ -24859,7 +24871,7 @@
       </c>
       <c r="C24" s="137">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>9.7786999999999999E-2</v>
+        <v>9.787499999999999E-2</v>
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
@@ -24932,8 +24944,8 @@
       <c r="D3" s="265"/>
       <c r="E3" s="265"/>
       <c r="F3" s="265"/>
-      <c r="G3" s="271"/>
-      <c r="H3" s="272" t="s">
+      <c r="G3" s="274"/>
+      <c r="H3" s="275" t="s">
         <v>114</v>
       </c>
       <c r="I3" s="265"/>
@@ -24957,18 +24969,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="87"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="273" t="s">
+      <c r="C5" s="271" t="s">
         <v>184</v>
       </c>
-      <c r="D5" s="273"/>
-      <c r="E5" s="273"/>
-      <c r="F5" s="273"/>
-      <c r="G5" s="273"/>
-      <c r="H5" s="273"/>
-      <c r="I5" s="273"/>
-      <c r="J5" s="273"/>
-      <c r="K5" s="273"/>
-      <c r="L5" s="273"/>
+      <c r="D5" s="271"/>
+      <c r="E5" s="271"/>
+      <c r="F5" s="271"/>
+      <c r="G5" s="271"/>
+      <c r="H5" s="271"/>
+      <c r="I5" s="271"/>
+      <c r="J5" s="271"/>
+      <c r="K5" s="271"/>
+      <c r="L5" s="271"/>
       <c r="P5" s="276"/>
       <c r="Q5" s="276"/>
       <c r="R5" s="276"/>
@@ -25114,7 +25126,7 @@
       <c r="K8" s="139"/>
       <c r="L8" s="128">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>7162908.4874820141</v>
+        <v>7154814.2859167065</v>
       </c>
       <c r="N8" s="92"/>
       <c r="O8" s="16"/>
@@ -25168,23 +25180,23 @@
       <c r="G10" s="140"/>
       <c r="H10" s="128">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>179688.10500025837</v>
+        <v>179673.70212812812</v>
       </c>
       <c r="I10" s="128">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>211149.9366000265</v>
+        <v>211116.08857591735</v>
       </c>
       <c r="J10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>248120.46254331135</v>
+        <v>248060.80315421466</v>
       </c>
       <c r="K10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>291564.20752010337</v>
+        <v>291470.737623989</v>
       </c>
       <c r="L10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>342614.57614358095</v>
+        <v>342477.2870635963</v>
       </c>
       <c r="N10" s="92"/>
     </row>
@@ -25203,15 +25215,15 @@
       <c r="K11" s="139"/>
       <c r="L11" s="128">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>4492612.7459145179</v>
+        <v>4485737.8209292879</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="278" t="s">
+      <c r="B14" s="277" t="s">
         <v>226</v>
       </c>
-      <c r="C14" s="279"/>
+      <c r="C14" s="278"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="155" t="s">
@@ -25219,7 +25231,7 @@
       </c>
       <c r="C15" s="156">
         <f ca="1">Overview!C5</f>
-        <v>138.6</v>
+        <v>141.31</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -25228,7 +25240,7 @@
       </c>
       <c r="C16" s="156">
         <f ca="1">C36</f>
-        <v>153.51406475701702</v>
+        <v>153.35988200476922</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -25238,20 +25250,20 @@
       <c r="C17" s="158">
         <v>0.28999999999999998</v>
       </c>
-      <c r="E17" s="277" t="s">
+      <c r="E17" s="279" t="s">
         <v>229</v>
       </c>
-      <c r="F17" s="277"/>
-      <c r="G17" s="277"/>
-      <c r="H17" s="277"/>
-      <c r="I17" s="277"/>
+      <c r="F17" s="279"/>
+      <c r="G17" s="279"/>
+      <c r="H17" s="279"/>
+      <c r="I17" s="279"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="278" t="s">
+      <c r="B19" s="277" t="s">
         <v>188</v>
       </c>
-      <c r="C19" s="279"/>
+      <c r="C19" s="278"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="159" t="s">
@@ -25267,7 +25279,7 @@
       </c>
       <c r="C21" s="221">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>9.7786999999999999E-2</v>
+        <v>9.787499999999999E-2</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -25285,7 +25297,7 @@
       </c>
       <c r="C23" s="161">
         <f ca="1">C15*C22</f>
-        <v>6484539.5999999996</v>
+        <v>6611329.6600000001</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -25312,15 +25324,15 @@
       </c>
       <c r="C26" s="162">
         <f ca="1">C23+C25-C24</f>
-        <v>5067980.5999999996</v>
+        <v>5194770.66</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="278" t="s">
+      <c r="B28" s="277" t="s">
         <v>190</v>
       </c>
-      <c r="C28" s="279"/>
+      <c r="C28" s="278"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="159" t="s">
@@ -25328,7 +25340,7 @@
       </c>
       <c r="C29" s="161">
         <f ca="1">SUM(H10:L10)</f>
-        <v>1273137.2878072804</v>
+        <v>1272798.6185458454</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -25337,7 +25349,7 @@
       </c>
       <c r="C30" s="161">
         <f ca="1">L11</f>
-        <v>4492612.7459145179</v>
+        <v>4485737.8209292879</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -25346,7 +25358,7 @@
       </c>
       <c r="C31" s="164">
         <f ca="1">C29+C30</f>
-        <v>5765750.0337217981</v>
+        <v>5758536.4394751331</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -25373,7 +25385,7 @@
       </c>
       <c r="C34" s="164">
         <f ca="1">C31+C32-C33</f>
-        <v>7182309.0337217981</v>
+        <v>7175095.4394751331</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.2">
@@ -25391,21 +25403,21 @@
       </c>
       <c r="C36" s="167">
         <f ca="1">C34/C35</f>
-        <v>153.51406475701702</v>
+        <v>153.35988200476922</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
     <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -32097,7 +32109,7 @@
       </c>
       <c r="AC116" s="63">
         <f ca="1">Overview!C5</f>
-        <v>138.6</v>
+        <v>141.31</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -32168,7 +32180,7 @@
       </c>
       <c r="AC117" s="65">
         <f ca="1">AC116/AC85</f>
-        <v>138.6</v>
+        <v>141.31</v>
       </c>
     </row>
     <row r="119" spans="1:31" x14ac:dyDescent="0.2">
@@ -33278,7 +33290,7 @@
       <c r="AA146" s="49"/>
       <c r="AC146" s="72">
         <f ca="1">AC117/Statement!AC26</f>
-        <v>44.131737927796031</v>
+        <v>44.994631216283246</v>
       </c>
     </row>
     <row r="147" spans="2:29" x14ac:dyDescent="0.2">
@@ -33315,7 +33327,7 @@
       <c r="AA147" s="49"/>
       <c r="AC147" s="72">
         <f ca="1">AC117/(Statement!AC5/Statement!AC22)</f>
-        <v>5.9521039572835237</v>
+        <v>6.0684834791034259</v>
       </c>
     </row>
     <row r="148" spans="2:29" x14ac:dyDescent="0.2">
@@ -33376,7 +33388,7 @@
       </c>
       <c r="AC148" s="72">
         <f ca="1">AC117/(Statement!AC49/Statement!AC75)</f>
-        <v>4.5998059219346521</v>
+        <v>4.6897444071326531</v>
       </c>
     </row>
     <row r="149" spans="2:29" x14ac:dyDescent="0.2">
@@ -33437,7 +33449,7 @@
       </c>
       <c r="AC149" s="143">
         <f ca="1">Statement!AC117*Statement!AC78</f>
-        <v>6946909.1999999993</v>
+        <v>7082739.8200000003</v>
       </c>
     </row>
     <row r="150" spans="2:29" x14ac:dyDescent="0.2">
@@ -33498,7 +33510,7 @@
       </c>
       <c r="AC150" s="143">
         <f ca="1">AC149+AC108-AC107+AC48+AC45</f>
-        <v>5530350.1999999993</v>
+        <v>5666180.8200000003</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -33535,7 +33547,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="182">
         <f ca="1">AC150/AC5</f>
-        <v>4.8299917380056971</v>
+        <v>4.9486208932386146</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -33572,7 +33584,7 @@
       <c r="AA152" s="49"/>
       <c r="AC152" s="182">
         <f ca="1">AC150/AC12</f>
-        <v>35.20609988222936</v>
+        <v>36.070794919947801</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -33707,7 +33719,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="72">
         <f t="shared" ref="AC155:AC156" ca="1" si="151">AC149/AC153</f>
-        <v>27.477688474013128</v>
+        <v>28.01495063681671</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -33744,7 +33756,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="72">
         <f t="shared" ca="1" si="151"/>
-        <v>33.169234867465619</v>
+        <v>33.9839025781964</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -33781,7 +33793,7 @@
       <c r="AA157" s="49"/>
       <c r="AC157" s="74">
         <f t="shared" ref="AC157" ca="1" si="154">AC153/AC149</f>
-        <v>3.6393163163842709E-2</v>
+        <v>3.5695226201320492E-2</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
@@ -33818,7 +33830,7 @@
       <c r="AA158" s="49"/>
       <c r="AC158" s="74">
         <f ca="1">AC26/AC117</f>
-        <v>2.2659429402850637E-2</v>
+        <v>2.2224873789789101E-2</v>
       </c>
     </row>
     <row r="159" spans="2:29" x14ac:dyDescent="0.2">
@@ -33892,7 +33904,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="154">
         <f ca="1">-AC63/AC149</f>
-        <v>1.0019275910501321E-2</v>
+        <v>9.8271292986730086E-3</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -33929,7 +33941,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="154">
         <f ca="1">-(AC63+AC64)/AC149</f>
-        <v>1.0019275910501321E-2</v>
+        <v>9.8271292986730086E-3</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -34432,7 +34444,7 @@
       <c r="AA172" s="49"/>
       <c r="AC172" s="154">
         <f ca="1">(AC107-AC108)/AC149</f>
-        <v>0.20391212253069324</v>
+        <v>0.20000155815408732</v>
       </c>
     </row>
     <row r="173" spans="2:29" x14ac:dyDescent="0.2">
@@ -36376,7 +36388,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9420C07F-23F5-F443-9A67-3073516055F8}">
-  <dimension ref="B1:G54"/>
+  <dimension ref="B1:G61"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.1640625" style="1" customWidth="1"/>
@@ -36409,7 +36421,7 @@
       </c>
       <c r="C5" s="171">
         <f ca="1">Overview!C5</f>
-        <v>138.6</v>
+        <v>141.31</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="134" t="s">
@@ -36425,7 +36437,7 @@
       </c>
       <c r="C6" s="172">
         <f ca="1">Statement!AC149</f>
-        <v>6946909.1999999993</v>
+        <v>7082739.8200000003</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>20</v>
@@ -36445,7 +36457,7 @@
       </c>
       <c r="C7" s="172">
         <f ca="1">Statement!AC150</f>
-        <v>5530350.1999999993</v>
+        <v>5666180.8200000003</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>32</v>
@@ -36465,7 +36477,7 @@
       </c>
       <c r="C8" s="173">
         <f ca="1">Statement!AC146</f>
-        <v>44.131737927796031</v>
+        <v>44.994631216283246</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>247</v>
@@ -36485,7 +36497,7 @@
       </c>
       <c r="C9" s="173">
         <f ca="1">Statement!AC147</f>
-        <v>5.9521039572835237</v>
+        <v>6.0684834791034259</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>248</v>
@@ -36505,7 +36517,7 @@
       </c>
       <c r="C10" s="173">
         <f ca="1">Statement!AC148</f>
-        <v>4.5998059219346521</v>
+        <v>4.6897444071326531</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -36525,7 +36537,7 @@
       </c>
       <c r="C11" s="173">
         <f ca="1">Statement!AC151</f>
-        <v>4.8299917380056971</v>
+        <v>4.9486208932386146</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -36534,7 +36546,7 @@
       </c>
       <c r="C12" s="173">
         <f ca="1">Statement!AC152</f>
-        <v>35.20609988222936</v>
+        <v>36.070794919947801</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
@@ -36770,7 +36782,7 @@
       </c>
       <c r="C38" s="174">
         <f ca="1">Statement!AC158</f>
-        <v>2.2659429402850637E-2</v>
+        <v>2.2224873789789101E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>274</v>
@@ -36786,7 +36798,7 @@
       </c>
       <c r="C39" s="214">
         <f ca="1">Statement!AC157</f>
-        <v>3.6393163163842709E-2</v>
+        <v>3.5695226201320492E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>276</v>
@@ -36818,7 +36830,7 @@
       </c>
       <c r="C41" s="174">
         <f ca="1">Statement!AC160</f>
-        <v>1.0019275910501321E-2</v>
+        <v>9.8271292986730086E-3</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -36827,7 +36839,7 @@
       </c>
       <c r="C42" s="174">
         <f ca="1">Statement!AC161</f>
-        <v>1.0019275910501321E-2</v>
+        <v>9.8271292986730086E-3</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
@@ -36871,7 +36883,7 @@
       </c>
       <c r="F48" s="174">
         <f ca="1">Statement!AC172</f>
-        <v>0.20391212253069324</v>
+        <v>0.20000155815408732</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
@@ -36925,8 +36937,51 @@
         <v>2.0915247800493701</v>
       </c>
     </row>
+    <row r="57" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B57" s="265" t="s">
+        <v>447</v>
+      </c>
+      <c r="C57" s="265"/>
+    </row>
+    <row r="58" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B58" s="20" t="s">
+        <v>267</v>
+      </c>
+      <c r="C58" s="173">
+        <f ca="1">Statement!AC155</f>
+        <v>28.01495063681671</v>
+      </c>
+    </row>
+    <row r="59" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B59" s="20" t="s">
+        <v>268</v>
+      </c>
+      <c r="C59" s="173">
+        <f ca="1">Statement!AC156</f>
+        <v>33.9839025781964</v>
+      </c>
+    </row>
+    <row r="60" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B60" s="20" t="s">
+        <v>448</v>
+      </c>
+      <c r="C60" s="174">
+        <f>Statement!AC162</f>
+        <v>0.14561661603907672</v>
+      </c>
+    </row>
+    <row r="61" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B61" s="20" t="s">
+        <v>449</v>
+      </c>
+      <c r="C61" s="174">
+        <f>Statement!AC163</f>
+        <v>0.22080310776749734</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="15">
+    <mergeCell ref="B57:C57"/>
     <mergeCell ref="B51:C51"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="E4:G4"/>
@@ -36951,7 +37006,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{978EC990-97E1-EA42-B427-9F214546EBED}">
-  <dimension ref="B1:I96"/>
+  <dimension ref="B1:I102"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.33203125" style="1" customWidth="1"/>
@@ -37050,7 +37105,7 @@
       </c>
       <c r="I6" s="171">
         <f ca="1">Statement!AC116</f>
-        <v>138.6</v>
+        <v>141.31</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -37079,7 +37134,7 @@
       </c>
       <c r="I7" s="172">
         <f ca="1">Statement!AC149</f>
-        <v>6946909.1999999993</v>
+        <v>7082739.8200000003</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -37108,7 +37163,7 @@
       </c>
       <c r="I8" s="172">
         <f ca="1">Statement!AC150</f>
-        <v>5530350.1999999993</v>
+        <v>5666180.8200000003</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -37137,7 +37192,7 @@
       </c>
       <c r="I9" s="173">
         <f ca="1">Statement!AC146</f>
-        <v>44.131737927796031</v>
+        <v>44.994631216283246</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -37166,7 +37221,7 @@
       </c>
       <c r="I10" s="173">
         <f ca="1">Statement!AC147</f>
-        <v>5.9521039572835237</v>
+        <v>6.0684834791034259</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -37195,7 +37250,7 @@
       </c>
       <c r="I11" s="173">
         <f ca="1">Statement!AC148</f>
-        <v>4.5998059219346521</v>
+        <v>4.6897444071326531</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -37224,7 +37279,7 @@
       </c>
       <c r="I12" s="173">
         <f ca="1">Statement!AC151</f>
-        <v>4.8299917380056971</v>
+        <v>4.9486208932386146</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -37253,7 +37308,7 @@
       </c>
       <c r="I13" s="173">
         <f ca="1">Statement!AC152</f>
-        <v>35.20609988222936</v>
+        <v>36.070794919947801</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -38026,7 +38081,7 @@
       </c>
       <c r="I51" s="174">
         <f ca="1">Statement!AC158</f>
-        <v>2.2659429402850637E-2</v>
+        <v>2.2224873789789101E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -38055,7 +38110,7 @@
       </c>
       <c r="I52" s="174">
         <f ca="1">Statement!AC157</f>
-        <v>3.6393163163842709E-2</v>
+        <v>3.5695226201320492E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -38113,7 +38168,7 @@
       </c>
       <c r="I54" s="174">
         <f ca="1">Statement!AC160</f>
-        <v>1.0019275910501321E-2</v>
+        <v>9.8271292986730086E-3</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -38142,7 +38197,7 @@
       </c>
       <c r="I55" s="174">
         <f ca="1">Statement!AC161</f>
-        <v>1.0019275910501321E-2</v>
+        <v>9.8271292986730086E-3</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -38378,7 +38433,7 @@
       </c>
       <c r="I68" s="195">
         <f ca="1">Statement!AC172</f>
-        <v>0.20391212253069324</v>
+        <v>0.20000155815408732</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -38715,188 +38770,315 @@
       </c>
       <c r="I85" s="196"/>
     </row>
-    <row r="88" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B88" s="14" t="s">
+    <row r="87" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B87" s="14" t="s">
+        <v>447</v>
+      </c>
+      <c r="C87" s="14"/>
+      <c r="D87" s="14"/>
+      <c r="E87" s="14"/>
+      <c r="F87" s="14"/>
+      <c r="G87" s="14"/>
+      <c r="I87" s="14"/>
+    </row>
+    <row r="88" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B88" s="20" t="s">
+        <v>267</v>
+      </c>
+      <c r="C88" s="173">
+        <f>Statement!M155</f>
+        <v>-112.87400898520085</v>
+      </c>
+      <c r="D88" s="173">
+        <f>Statement!N155</f>
+        <v>-95.43181061806655</v>
+      </c>
+      <c r="E88" s="173">
+        <f>Statement!O155</f>
+        <v>243.27936097877384</v>
+      </c>
+      <c r="F88" s="173">
+        <f>Statement!P155</f>
+        <v>103.20455372459323</v>
+      </c>
+      <c r="G88" s="173">
+        <f>Statement!Q155</f>
+        <v>39.668168547942251</v>
+      </c>
+      <c r="I88" s="173">
+        <f ca="1">Statement!AC155</f>
+        <v>28.01495063681671</v>
+      </c>
+    </row>
+    <row r="89" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B89" s="20" t="s">
+        <v>268</v>
+      </c>
+      <c r="C89" s="173">
+        <f>Statement!M156</f>
+        <v>-98.568903797199823</v>
+      </c>
+      <c r="D89" s="173">
+        <f>Statement!N156</f>
+        <v>-63.556731738561353</v>
+      </c>
+      <c r="E89" s="173">
+        <f>Statement!O156</f>
+        <v>673.03434883720922</v>
+      </c>
+      <c r="F89" s="173">
+        <f>Statement!P156</f>
+        <v>124.4016933148245</v>
+      </c>
+      <c r="G89" s="173">
+        <f>Statement!Q156</f>
+        <v>49.504381582091227</v>
+      </c>
+      <c r="I89" s="173">
+        <f ca="1">Statement!AC156</f>
+        <v>33.9839025781964</v>
+      </c>
+    </row>
+    <row r="90" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B90" s="20" t="s">
+        <v>448</v>
+      </c>
+      <c r="C90" s="174">
+        <f>Statement!M162</f>
+        <v>-0.1503836153956582</v>
+      </c>
+      <c r="D90" s="174">
+        <f>Statement!N162</f>
+        <v>-9.7183994370695137E-2</v>
+      </c>
+      <c r="E90" s="174">
+        <f>Statement!O162</f>
+        <v>2.8336932720025455E-2</v>
+      </c>
+      <c r="F90" s="174">
+        <f>Statement!P162</f>
+        <v>0.16019298860138934</v>
+      </c>
+      <c r="G90" s="174">
+        <f>Statement!Q162</f>
+        <v>0.14737449941730871</v>
+      </c>
+      <c r="I90" s="174">
+        <f>Statement!AC162</f>
+        <v>0.14561661603907672</v>
+      </c>
+    </row>
+    <row r="91" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B91" s="20" t="s">
+        <v>449</v>
+      </c>
+      <c r="C91" s="174">
+        <f>Statement!M163</f>
+        <v>-0.15089403920692901</v>
+      </c>
+      <c r="D91" s="174">
+        <f>Statement!N163</f>
+        <v>-8.1971339260341822E-2</v>
+      </c>
+      <c r="E91" s="174">
+        <f>Statement!O163</f>
+        <v>8.4180460131536086E-2</v>
+      </c>
+      <c r="F91" s="174">
+        <f>Statement!P163</f>
+        <v>0.2057367143300215</v>
+      </c>
+      <c r="G91" s="174">
+        <f>Statement!Q163</f>
+        <v>0.21490879336615942</v>
+      </c>
+      <c r="I91" s="174">
+        <f>Statement!AC163</f>
+        <v>0.22080310776749734</v>
+      </c>
+    </row>
+    <row r="93" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B93" s="14" t="s">
+        <v>450</v>
+      </c>
+      <c r="C93" s="14"/>
+      <c r="D93" s="14"/>
+      <c r="E93" s="14"/>
+      <c r="F93" s="14"/>
+      <c r="G93" s="14"/>
+      <c r="I93" s="14"/>
+    </row>
+    <row r="94" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B94" s="20" t="s">
+        <v>288</v>
+      </c>
+      <c r="C94" s="174">
+        <f>Statement!M199</f>
+        <v>0</v>
+      </c>
+      <c r="D94" s="174">
+        <f>Statement!N199</f>
+        <v>0</v>
+      </c>
+      <c r="E94" s="174">
+        <f>Statement!O199</f>
+        <v>0</v>
+      </c>
+      <c r="F94" s="174">
+        <f>Statement!P199</f>
+        <v>0</v>
+      </c>
+      <c r="G94" s="174">
+        <f>Statement!Q199</f>
+        <v>0</v>
+      </c>
+      <c r="I94" s="196"/>
+    </row>
+    <row r="97" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B97" s="14" t="s">
         <v>314</v>
       </c>
-      <c r="C88" s="14"/>
-      <c r="D88" s="14"/>
-      <c r="E88" s="14"/>
-      <c r="F88" s="14"/>
-      <c r="G88" s="14"/>
-      <c r="I88" s="14"/>
-    </row>
-    <row r="89" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B89" s="20" t="str">
+      <c r="C97" s="14"/>
+      <c r="D97" s="14"/>
+      <c r="E97" s="14"/>
+      <c r="F97" s="14"/>
+      <c r="G97" s="14"/>
+      <c r="I97" s="14"/>
+    </row>
+    <row r="98" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B98" s="20" t="str">
         <f>Statement!B191&amp;" Revenue"</f>
         <v>Subscription Revenue</v>
       </c>
-      <c r="C89" s="174">
+      <c r="C98" s="174">
         <f>Statement!M191</f>
         <v>1</v>
       </c>
-      <c r="D89" s="174">
+      <c r="D98" s="174">
         <f>Statement!N191</f>
         <v>0.51361387508439493</v>
       </c>
-      <c r="E89" s="174">
+      <c r="E98" s="174">
         <f>Statement!O191</f>
         <v>0.47961112512659637</v>
       </c>
-      <c r="F89" s="174">
+      <c r="F98" s="174">
         <f>Statement!P191</f>
         <v>0.50124788724041469</v>
       </c>
-      <c r="G89" s="174">
+      <c r="G98" s="174">
         <f>Statement!Q191</f>
         <v>0.43769124538500914</v>
       </c>
-      <c r="I89" s="196"/>
-    </row>
-    <row r="90" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B90" s="20" t="str">
+      <c r="I98" s="196"/>
+    </row>
+    <row r="99" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B99" s="20" t="str">
         <f>Statement!B192&amp;" Revenue"</f>
         <v>Advertising Revenue</v>
       </c>
-      <c r="C90" s="174">
+      <c r="C99" s="174">
         <f>Statement!M192</f>
         <v>1</v>
       </c>
-      <c r="D90" s="174">
+      <c r="D99" s="174">
         <f>Statement!N192</f>
         <v>0.161813978857692</v>
       </c>
-      <c r="E90" s="174">
+      <c r="E99" s="174">
         <f>Statement!O192</f>
         <v>0.11461849723905122</v>
       </c>
-      <c r="F90" s="174">
+      <c r="F99" s="174">
         <f>Statement!P192</f>
         <v>0.10126759998395443</v>
       </c>
-      <c r="G90" s="174">
+      <c r="G99" s="174">
         <f>Statement!Q192</f>
         <v>0.45200065565410602</v>
       </c>
-      <c r="I90" s="196"/>
-    </row>
-    <row r="91" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B91" s="20" t="str">
+      <c r="I99" s="196"/>
+    </row>
+    <row r="100" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B100" s="20" t="str">
         <f>Statement!B193&amp;" Revenue"</f>
         <v>English test Revenue</v>
       </c>
-      <c r="C91" s="174">
+      <c r="C100" s="174">
         <f>Statement!M193</f>
         <v>1</v>
       </c>
-      <c r="D91" s="174">
+      <c r="D100" s="174">
         <f>Statement!N193</f>
         <v>0.32687160353637762</v>
       </c>
-      <c r="E91" s="174">
+      <c r="E100" s="174">
         <f>Statement!O193</f>
         <v>0.25961244574851766</v>
       </c>
-      <c r="F91" s="174">
+      <c r="F100" s="174">
         <f>Statement!P193</f>
         <v>0.107444433660099</v>
       </c>
-      <c r="G91" s="174">
+      <c r="G100" s="174">
         <f>Statement!Q193</f>
         <v>-7.9623137598597724E-2</v>
       </c>
-      <c r="I91" s="196"/>
-    </row>
-    <row r="92" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B92" s="20" t="str">
+      <c r="I100" s="196"/>
+    </row>
+    <row r="101" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B101" s="20" t="str">
         <f>Statement!B194&amp;" Revenue"</f>
         <v>In-App purchases Revenue</v>
       </c>
-      <c r="C92" s="174">
+      <c r="C101" s="174">
         <f>Statement!M194</f>
         <v>1</v>
       </c>
-      <c r="D92" s="174">
+      <c r="D101" s="174">
         <f>Statement!N194</f>
         <v>1.6809833694866232</v>
       </c>
-      <c r="E92" s="174">
+      <c r="E101" s="174">
         <f>Statement!O194</f>
         <v>0.87027347753384754</v>
       </c>
-      <c r="F92" s="174">
+      <c r="F101" s="174">
         <f>Statement!P194</f>
         <v>0.11478672165662042</v>
       </c>
-      <c r="G92" s="174">
+      <c r="G101" s="174">
         <f>Statement!Q194</f>
         <v>4.7240835122758909E-2</v>
       </c>
-      <c r="I92" s="196"/>
-    </row>
-    <row r="93" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B93" s="20" t="str">
+      <c r="I101" s="196"/>
+    </row>
+    <row r="102" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B102" s="20" t="str">
         <f>Statement!B195&amp;" Revenue"</f>
         <v>Other Revenue</v>
       </c>
-      <c r="C93" s="174">
+      <c r="C102" s="174">
         <f>Statement!M195</f>
         <v>1</v>
       </c>
-      <c r="D93" s="174">
+      <c r="D102" s="174">
         <f>Statement!N195</f>
         <v>6.9113924050632916</v>
       </c>
-      <c r="E93" s="174">
+      <c r="E102" s="174">
         <f>Statement!O195</f>
         <v>9.1200000000000003E-2</v>
       </c>
-      <c r="F93" s="174">
+      <c r="F102" s="174">
         <f>Statement!P195</f>
         <v>0.89589442815249265</v>
       </c>
-      <c r="G93" s="174">
+      <c r="G102" s="174">
         <f>Statement!Q195</f>
         <v>0.49806651198762569</v>
       </c>
-      <c r="I93" s="196"/>
-    </row>
-    <row r="95" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B95" s="14" t="s">
-        <v>316</v>
-      </c>
-      <c r="C95" s="14"/>
-      <c r="D95" s="14"/>
-      <c r="E95" s="14"/>
-      <c r="F95" s="14"/>
-      <c r="G95" s="14"/>
-      <c r="I95" s="14"/>
-    </row>
-    <row r="96" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B96" s="20" t="s">
-        <v>288</v>
-      </c>
-      <c r="C96" s="174">
-        <f>Statement!M199</f>
-        <v>0</v>
-      </c>
-      <c r="D96" s="174">
-        <f>Statement!N199</f>
-        <v>0</v>
-      </c>
-      <c r="E96" s="174">
-        <f>Statement!O199</f>
-        <v>0</v>
-      </c>
-      <c r="F96" s="174">
-        <f>Statement!P199</f>
-        <v>0</v>
-      </c>
-      <c r="G96" s="174">
-        <f>Statement!Q199</f>
-        <v>0</v>
-      </c>
-      <c r="I96" s="196"/>
+      <c r="I102" s="196"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -38921,14 +39103,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="268" t="s">
+      <c r="C3" s="266" t="s">
         <v>317</v>
       </c>
-      <c r="D3" s="269"/>
-      <c r="F3" s="270" t="s">
+      <c r="D3" s="267"/>
+      <c r="F3" s="268" t="s">
         <v>318</v>
       </c>
-      <c r="G3" s="269"/>
+      <c r="G3" s="267"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -38995,19 +39177,19 @@
       <c r="B7" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C7" s="266">
+      <c r="C7" s="269">
         <f>Statement!AA89</f>
         <v>2.2218264392893719E-2</v>
       </c>
-      <c r="D7" s="267"/>
-      <c r="F7" s="266">
+      <c r="D7" s="270"/>
+      <c r="F7" s="269">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.18309713991239371</v>
       </c>
-      <c r="G7" s="267"/>
+      <c r="G7" s="270"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="206" t="s">
@@ -39034,19 +39216,19 @@
       <c r="B9" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C9" s="266">
+      <c r="C9" s="269">
         <f>Statement!AA90</f>
         <v>3.6046202026093238E-2</v>
       </c>
-      <c r="D9" s="267"/>
-      <c r="F9" s="266">
+      <c r="D9" s="270"/>
+      <c r="F9" s="269">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.17263647322197348</v>
       </c>
-      <c r="G9" s="267"/>
+      <c r="G9" s="270"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="206" t="s">
@@ -39073,19 +39255,19 @@
       <c r="B11" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C11" s="266">
+      <c r="C11" s="269">
         <f>Statement!AA91</f>
         <v>1.710027405488606E-2</v>
       </c>
-      <c r="D11" s="267"/>
-      <c r="F11" s="266">
+      <c r="D11" s="270"/>
+      <c r="F11" s="269">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>0.1870895657269924</v>
       </c>
-      <c r="G11" s="267"/>
+      <c r="G11" s="270"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="206" t="s">
@@ -39112,19 +39294,19 @@
       <c r="B13" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C13" s="266">
+      <c r="C13" s="269">
         <f>Statement!AA95</f>
         <v>8.4392741251357012E-2</v>
       </c>
-      <c r="D13" s="267"/>
-      <c r="F13" s="266">
+      <c r="D13" s="270"/>
+      <c r="F13" s="269">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.22501976973287405</v>
       </c>
-      <c r="G13" s="267"/>
+      <c r="G13" s="270"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="206" t="s">
@@ -39151,19 +39333,19 @@
       <c r="B15" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C15" s="266">
+      <c r="C15" s="269">
         <f>Statement!AA96</f>
         <v>-0.23765355851505829</v>
       </c>
-      <c r="D15" s="267"/>
-      <c r="F15" s="266">
+      <c r="D15" s="270"/>
+      <c r="F15" s="269">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>1.7444474417768186E-2</v>
       </c>
-      <c r="G15" s="267"/>
+      <c r="G15" s="270"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="206" t="s">
@@ -39190,19 +39372,19 @@
       <c r="B17" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C17" s="266">
+      <c r="C17" s="269">
         <f>Statement!AA98</f>
         <v>-0.23704555913483663</v>
       </c>
-      <c r="D17" s="267"/>
-      <c r="F17" s="266">
+      <c r="D17" s="270"/>
+      <c r="F17" s="269">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>-0.25955204216073779</v>
       </c>
-      <c r="G17" s="267"/>
+      <c r="G17" s="270"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="206" t="s">
@@ -39229,22 +39411,22 @@
       <c r="B19" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C19" s="266">
+      <c r="C19" s="269">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>2.5565842762241744E-2</v>
       </c>
-      <c r="D19" s="267"/>
-      <c r="F19" s="266">
+      <c r="D19" s="270"/>
+      <c r="F19" s="269">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>2.5293753865182372E-2</v>
       </c>
-      <c r="G19" s="267"/>
+      <c r="G19" s="270"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="206" t="s">
@@ -39271,22 +39453,22 @@
       <c r="B21" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C21" s="266">
+      <c r="C21" s="269">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>-0.2584269662921348</v>
       </c>
-      <c r="D21" s="267"/>
-      <c r="F21" s="266">
+      <c r="D21" s="270"/>
+      <c r="F21" s="269">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>-0.27472527472527469</v>
       </c>
-      <c r="G21" s="267"/>
+      <c r="G21" s="270"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -39335,22 +39517,22 @@
       <c r="B25" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C25" s="266">
+      <c r="C25" s="269">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>2.840483364420425E-2</v>
       </c>
-      <c r="D25" s="267"/>
-      <c r="F25" s="266">
+      <c r="D25" s="270"/>
+      <c r="F25" s="269">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>0.22478379327694395</v>
       </c>
-      <c r="G25" s="267"/>
+      <c r="G25" s="270"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="str">
@@ -39378,22 +39560,22 @@
       <c r="B27" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C27" s="266">
+      <c r="C27" s="269">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>2.1247695740758708E-2</v>
       </c>
-      <c r="D27" s="267"/>
-      <c r="F27" s="266">
+      <c r="D27" s="270"/>
+      <c r="F27" s="269">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>2.1792942775323981E-2</v>
       </c>
-      <c r="G27" s="267"/>
+      <c r="G27" s="270"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="str">
@@ -39421,22 +39603,22 @@
       <c r="B29" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C29" s="266">
+      <c r="C29" s="269">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>-0.10674206945303526</v>
       </c>
-      <c r="D29" s="267"/>
-      <c r="F29" s="266">
+      <c r="D29" s="270"/>
+      <c r="F29" s="269">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>2.0816812053925456E-3</v>
       </c>
-      <c r="G29" s="267"/>
+      <c r="G29" s="270"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="str">
@@ -39464,22 +39646,22 @@
       <c r="B31" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C31" s="266">
+      <c r="C31" s="269">
         <f>IF(C30=0,
 IF(D30=0,0,IF(D30&gt;0,1,-1)),
 (D30-C30)/ABS(C30)
 )</f>
         <v>-5.2569263556713236E-2</v>
       </c>
-      <c r="D31" s="267"/>
-      <c r="F31" s="266">
+      <c r="D31" s="270"/>
+      <c r="F31" s="269">
         <f>IF(F30=0,
 IF(G30=0,0,IF(G30&gt;0,1,-1)),
 (G30-F30)/ABS(F30)
 )</f>
         <v>-0.22983638113570742</v>
       </c>
-      <c r="G31" s="267"/>
+      <c r="G31" s="270"/>
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B32" s="20" t="str">
@@ -39507,22 +39689,22 @@
       <c r="B33" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C33" s="266">
+      <c r="C33" s="269">
         <f>IF(C32=0,
 IF(D32=0,0,IF(D32&gt;0,1,-1)),
 (D32-C32)/ABS(C32)
 )</f>
         <v>0.84164222873900296</v>
       </c>
-      <c r="D33" s="267"/>
-      <c r="F33" s="266">
+      <c r="D33" s="270"/>
+      <c r="F33" s="269">
         <f>IF(F32=0,
 IF(G32=0,0,IF(G32&gt;0,1,-1)),
 (G32-F32)/ABS(F32)
 )</f>
         <v>1.482213438735178</v>
       </c>
-      <c r="G33" s="267"/>
+      <c r="G33" s="270"/>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B35" s="8" t="s">
@@ -39571,22 +39753,22 @@
       <c r="B37" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C37" s="266">
+      <c r="C37" s="269">
         <f>IF(C36=0,
 IF(D36=0,0,IF(D36&gt;0,1,-1)),
 (D36-C36)/ABS(C36)
 )</f>
         <v>3.8938053097345132E-2</v>
       </c>
-      <c r="D37" s="267"/>
-      <c r="F37" s="266">
+      <c r="D37" s="270"/>
+      <c r="F37" s="269">
         <f>IF(F36=0,
 IF(G36=0,0,IF(G36&gt;0,1,-1)),
 (G36-F36)/ABS(F36)
 )</f>
         <v>0.23060796645702306</v>
       </c>
-      <c r="G37" s="267"/>
+      <c r="G37" s="270"/>
     </row>
     <row r="38" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="str">
@@ -39614,22 +39796,22 @@
       <c r="B39" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C39" s="266">
+      <c r="C39" s="269">
         <f>IF(C38=0,
 IF(D38=0,0,IF(D38&gt;0,1,-1)),
 (D38-C38)/ABS(C38)
 )</f>
         <v>2.0319303338171262E-2</v>
       </c>
-      <c r="D39" s="267"/>
-      <c r="F39" s="266">
+      <c r="D39" s="270"/>
+      <c r="F39" s="269">
         <f>IF(F38=0,
 IF(G38=0,0,IF(G38&gt;0,1,-1)),
 (G38-F38)/ABS(F38)
 )</f>
         <v>9.5869056897895558E-2</v>
       </c>
-      <c r="G39" s="267"/>
+      <c r="G39" s="270"/>
     </row>
     <row r="40" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B40" s="20" t="str">
@@ -39657,22 +39839,22 @@
       <c r="B41" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C41" s="266">
+      <c r="C41" s="269">
         <f>IF(C40=0,
 IF(D40=0,0,IF(D40&gt;0,1,-1)),
 (D40-C40)/ABS(C40)
 )</f>
         <v>1.6E-2</v>
       </c>
-      <c r="D41" s="267"/>
-      <c r="F41" s="266">
+      <c r="D41" s="270"/>
+      <c r="F41" s="269">
         <f>IF(F40=0,
 IF(G40=0,0,IF(G40&gt;0,1,-1)),
 (G40-F40)/ABS(F40)
 )</f>
         <v>0.16513761467889909</v>
       </c>
-      <c r="G41" s="267"/>
+      <c r="G41" s="270"/>
     </row>
     <row r="42" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B42" s="20" t="str">
@@ -39700,22 +39882,22 @@
       <c r="B43" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C43" s="266">
+      <c r="C43" s="269">
         <f>IF(C42=0,
 IF(D42=0,0,IF(D42&gt;0,1,-1)),
 (D42-C42)/ABS(C42)
 )</f>
         <v>2.0750199521149242E-2</v>
       </c>
-      <c r="D43" s="267"/>
-      <c r="F43" s="266">
+      <c r="D43" s="270"/>
+      <c r="F43" s="269">
         <f>IF(F42=0,
 IF(G42=0,0,IF(G42&gt;0,1,-1)),
 (G42-F42)/ABS(F42)
 )</f>
         <v>8.9437819420783646E-2</v>
       </c>
-      <c r="G43" s="267"/>
+      <c r="G43" s="270"/>
     </row>
     <row r="44" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B44" s="20" t="str">
@@ -39743,22 +39925,22 @@
       <c r="B45" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C45" s="266">
+      <c r="C45" s="269">
         <f>IF(C44=0,
 IF(D44=0,0,IF(D44&gt;0,1,-1)),
 (D44-C44)/ABS(C44)
 )</f>
         <v>1.2209481933271921E-2</v>
       </c>
-      <c r="D45" s="267"/>
-      <c r="F45" s="266">
+      <c r="D45" s="270"/>
+      <c r="F45" s="269">
         <f>IF(F44=0,
 IF(G44=0,0,IF(G44&gt;0,1,-1)),
 (G44-F44)/ABS(F44)
 )</f>
         <v>5.119238950540856E-2</v>
       </c>
-      <c r="G45" s="267"/>
+      <c r="G45" s="270"/>
     </row>
     <row r="46" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="str">
@@ -39786,22 +39968,22 @@
       <c r="B47" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C47" s="266">
+      <c r="C47" s="269">
         <f>IF(C46=0,
 IF(D46=0,0,IF(D46&gt;0,1,-1)),
 (D46-C46)/ABS(C46)
 )</f>
         <v>1.8247963846473435E-2</v>
       </c>
-      <c r="D47" s="267"/>
-      <c r="F47" s="266">
+      <c r="D47" s="270"/>
+      <c r="F47" s="269">
         <f>IF(F46=0,
 IF(G46=0,0,IF(G46&gt;0,1,-1)),
 (G46-F46)/ABS(F46)
 )</f>
         <v>0.1229516507570132</v>
       </c>
-      <c r="G47" s="267"/>
+      <c r="G47" s="270"/>
     </row>
     <row r="48" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B48" s="20" t="str">
@@ -39829,22 +40011,22 @@
       <c r="B49" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C49" s="266">
+      <c r="C49" s="269">
         <f>IF(C48=0,
 IF(D48=0,0,IF(D48&gt;0,1,-1)),
 (D48-C48)/ABS(C48)
 )</f>
         <v>-4.2332859174963834E-3</v>
       </c>
-      <c r="D49" s="267"/>
-      <c r="F49" s="266">
+      <c r="D49" s="270"/>
+      <c r="F49" s="269">
         <f>IF(F48=0,
 IF(G48=0,0,IF(G48&gt;0,1,-1)),
 (G48-F48)/ABS(F48)
 )</f>
         <v>6.3208790635154666E-2</v>
       </c>
-      <c r="G49" s="267"/>
+      <c r="G49" s="270"/>
     </row>
     <row r="50" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B50" s="20" t="str">
@@ -39872,22 +40054,22 @@
       <c r="B51" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C51" s="266">
+      <c r="C51" s="269">
         <f>IF(C50=0,
 IF(D50=0,0,IF(D50&gt;0,1,-1)),
 (D50-C50)/ABS(C50)
 )</f>
         <v>4.8738292663854846E-4</v>
       </c>
-      <c r="D51" s="267"/>
-      <c r="F51" s="266">
+      <c r="D51" s="270"/>
+      <c r="F51" s="269">
         <f>IF(F50=0,
 IF(G50=0,0,IF(G50&gt;0,1,-1)),
 (G50-F50)/ABS(F50)
 )</f>
         <v>-6.2091544317255373E-2</v>
       </c>
-      <c r="G51" s="267"/>
+      <c r="G51" s="270"/>
     </row>
     <row r="52" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="str">
@@ -39915,43 +40097,39 @@
       <c r="B53" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="C53" s="266">
+      <c r="C53" s="269">
         <f>IF(C52=0,
 IF(D52=0,0,IF(D52&gt;0,1,-1)),
 (D52-C52)/ABS(C52)
 )</f>
         <v>-8.8077740902117604E-2</v>
       </c>
-      <c r="D53" s="267"/>
-      <c r="F53" s="266">
+      <c r="D53" s="270"/>
+      <c r="F53" s="269">
         <f>IF(F52=0,
 IF(G52=0,0,IF(G52&gt;0,1,-1)),
 (G52-F52)/ABS(F52)
 )</f>
         <v>-0.37416005758387127</v>
       </c>
-      <c r="G53" s="267"/>
+      <c r="G53" s="270"/>
     </row>
   </sheetData>
   <mergeCells count="46">
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C53:D53"/>
+    <mergeCell ref="F53:G53"/>
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="F47:G47"/>
+    <mergeCell ref="C49:D49"/>
+    <mergeCell ref="F49:G49"/>
+    <mergeCell ref="C51:D51"/>
+    <mergeCell ref="F51:G51"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="F41:G41"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="F43:G43"/>
+    <mergeCell ref="C45:D45"/>
+    <mergeCell ref="F45:G45"/>
     <mergeCell ref="C37:D37"/>
     <mergeCell ref="F37:G37"/>
     <mergeCell ref="C39:D39"/>
@@ -39966,20 +40144,24 @@
     <mergeCell ref="F31:G31"/>
     <mergeCell ref="C33:D33"/>
     <mergeCell ref="F33:G33"/>
-    <mergeCell ref="C41:D41"/>
-    <mergeCell ref="F41:G41"/>
-    <mergeCell ref="C43:D43"/>
-    <mergeCell ref="F43:G43"/>
-    <mergeCell ref="C45:D45"/>
-    <mergeCell ref="F45:G45"/>
-    <mergeCell ref="C53:D53"/>
-    <mergeCell ref="F53:G53"/>
-    <mergeCell ref="C47:D47"/>
-    <mergeCell ref="F47:G47"/>
-    <mergeCell ref="C49:D49"/>
-    <mergeCell ref="F49:G49"/>
-    <mergeCell ref="C51:D51"/>
-    <mergeCell ref="F51:G51"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
